--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B2" t="n">
-        <v>244.0345597996414</v>
+        <v>241.2084729659526</v>
       </c>
       <c r="C2" t="n">
-        <v>245.5120449761291</v>
+        <v>242.6562262649122</v>
       </c>
       <c r="D2" t="n">
-        <v>239.2252583971897</v>
+        <v>238.8186957689135</v>
       </c>
       <c r="E2" t="n">
-        <v>240.7225799560547</v>
+        <v>240.4846038818359</v>
       </c>
       <c r="F2" t="n">
-        <v>8386400</v>
+        <v>7244600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B3" t="n">
-        <v>241.2084729659526</v>
+        <v>240.4845948654329</v>
       </c>
       <c r="C3" t="n">
-        <v>242.6562262649122</v>
+        <v>240.643240526318</v>
       </c>
       <c r="D3" t="n">
-        <v>238.8186957689135</v>
+        <v>235.2489097880788</v>
       </c>
       <c r="E3" t="n">
-        <v>240.4846038818359</v>
+        <v>237.3015289306641</v>
       </c>
       <c r="F3" t="n">
-        <v>7244600</v>
+        <v>8779800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B4" t="n">
-        <v>240.4845948654329</v>
+        <v>238.3703397912324</v>
       </c>
       <c r="C4" t="n">
-        <v>240.643240526318</v>
+        <v>241.380140328441</v>
       </c>
       <c r="D4" t="n">
-        <v>235.2489097880788</v>
+        <v>237.784276421548</v>
       </c>
       <c r="E4" t="n">
-        <v>237.3015289306641</v>
+        <v>240.5954132080078</v>
       </c>
       <c r="F4" t="n">
-        <v>8779800</v>
+        <v>10124000</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,25 +547,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B5" t="n">
-        <v>238.3703397912324</v>
+        <v>242.5324313580229</v>
       </c>
       <c r="C5" t="n">
-        <v>241.380140328441</v>
+        <v>245.6415564491674</v>
       </c>
       <c r="D5" t="n">
-        <v>237.784276421548</v>
+        <v>241.3304905574327</v>
       </c>
       <c r="E5" t="n">
-        <v>240.5954132080078</v>
+        <v>242.6516265869141</v>
       </c>
       <c r="F5" t="n">
-        <v>10124000</v>
+        <v>9344400</v>
       </c>
       <c r="G5" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B6" t="n">
-        <v>242.5324313580229</v>
+        <v>244.3800268891626</v>
       </c>
       <c r="C6" t="n">
-        <v>245.6415564491674</v>
+        <v>245.5521536952295</v>
       </c>
       <c r="D6" t="n">
-        <v>241.3304905574327</v>
+        <v>241.7278270152115</v>
       </c>
       <c r="E6" t="n">
-        <v>242.6516265869141</v>
+        <v>245.4428863525391</v>
       </c>
       <c r="F6" t="n">
-        <v>9344400</v>
+        <v>11813900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B7" t="n">
-        <v>244.3800268891626</v>
+        <v>243.6449370886138</v>
       </c>
       <c r="C7" t="n">
-        <v>245.5521536952295</v>
+        <v>248.8102703225537</v>
       </c>
       <c r="D7" t="n">
-        <v>241.7278270152115</v>
+        <v>241.5390740768479</v>
       </c>
       <c r="E7" t="n">
-        <v>245.4428863525391</v>
+        <v>248.0255432128906</v>
       </c>
       <c r="F7" t="n">
-        <v>11813900</v>
+        <v>7523800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B8" t="n">
-        <v>243.6449370886138</v>
+        <v>248.0752262809752</v>
       </c>
       <c r="C8" t="n">
-        <v>248.8102703225537</v>
+        <v>249.6844224306941</v>
       </c>
       <c r="D8" t="n">
-        <v>241.5390740768479</v>
+        <v>242.5026222117907</v>
       </c>
       <c r="E8" t="n">
-        <v>248.0255432128906</v>
+        <v>242.9297485351562</v>
       </c>
       <c r="F8" t="n">
-        <v>7523800</v>
+        <v>7669800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B9" t="n">
-        <v>248.0752418629596</v>
+        <v>244.0323655727545</v>
       </c>
       <c r="C9" t="n">
-        <v>249.6844381137545</v>
+        <v>247.1812325805079</v>
       </c>
       <c r="D9" t="n">
-        <v>242.5026374437513</v>
+        <v>241.390093455952</v>
       </c>
       <c r="E9" t="n">
-        <v>242.9297637939453</v>
+        <v>244.2509002685547</v>
       </c>
       <c r="F9" t="n">
-        <v>7669800</v>
+        <v>6707100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B10" t="n">
-        <v>244.0323655727545</v>
+        <v>242.8701495715982</v>
       </c>
       <c r="C10" t="n">
-        <v>247.1812325805079</v>
+        <v>243.0290866405082</v>
       </c>
       <c r="D10" t="n">
-        <v>241.390093455952</v>
+        <v>237.8935519633032</v>
       </c>
       <c r="E10" t="n">
-        <v>244.2509002685547</v>
+        <v>239.3438110351562</v>
       </c>
       <c r="F10" t="n">
-        <v>6707100</v>
+        <v>8145500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B11" t="n">
-        <v>242.8701495715982</v>
+        <v>239.0855561117752</v>
       </c>
       <c r="C11" t="n">
-        <v>243.0290866405082</v>
+        <v>242.8999549260145</v>
       </c>
       <c r="D11" t="n">
-        <v>237.8935519633032</v>
+        <v>238.7478261990409</v>
       </c>
       <c r="E11" t="n">
-        <v>239.3438110351562</v>
+        <v>241.8072814941406</v>
       </c>
       <c r="F11" t="n">
-        <v>8145500</v>
+        <v>4974600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="n">
-        <v>239.0855711988149</v>
+        <v>243.0886994915912</v>
       </c>
       <c r="C12" t="n">
-        <v>242.8999702537546</v>
+        <v>244.1813729625073</v>
       </c>
       <c r="D12" t="n">
-        <v>238.7478412647688</v>
+        <v>241.2510255151616</v>
       </c>
       <c r="E12" t="n">
-        <v>241.8072967529297</v>
+        <v>243.4661712646484</v>
       </c>
       <c r="F12" t="n">
-        <v>4974600</v>
+        <v>6373500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B13" t="n">
-        <v>243.0886994915912</v>
+        <v>243.4165080193006</v>
       </c>
       <c r="C13" t="n">
-        <v>244.1813729625073</v>
+        <v>243.5754451024098</v>
       </c>
       <c r="D13" t="n">
-        <v>241.2510255151616</v>
+        <v>234.2380960902458</v>
       </c>
       <c r="E13" t="n">
-        <v>243.4661712646484</v>
+        <v>235.420166015625</v>
       </c>
       <c r="F13" t="n">
-        <v>6373500</v>
+        <v>10801100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B14" t="n">
-        <v>243.4164922422276</v>
+        <v>234.9135667280067</v>
       </c>
       <c r="C14" t="n">
-        <v>243.5754293150353</v>
+        <v>240.853699895347</v>
       </c>
       <c r="D14" t="n">
-        <v>234.2380809080728</v>
+        <v>231.9534204494054</v>
       </c>
       <c r="E14" t="n">
-        <v>235.4201507568359</v>
+        <v>234.118896484375</v>
       </c>
       <c r="F14" t="n">
-        <v>10801100</v>
+        <v>10016600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B15" t="n">
-        <v>234.9135667280067</v>
+        <v>233.8606137856679</v>
       </c>
       <c r="C15" t="n">
-        <v>240.853699895347</v>
+        <v>237.804150935083</v>
       </c>
       <c r="D15" t="n">
-        <v>231.9534204494054</v>
+        <v>232.0428259237834</v>
       </c>
       <c r="E15" t="n">
-        <v>234.118896484375</v>
+        <v>237.2876281738281</v>
       </c>
       <c r="F15" t="n">
-        <v>10016600</v>
+        <v>7679200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B16" t="n">
-        <v>233.8605987472531</v>
+        <v>237.1584831814004</v>
       </c>
       <c r="C16" t="n">
-        <v>237.8041356430789</v>
+        <v>241.1914166378037</v>
       </c>
       <c r="D16" t="n">
-        <v>232.0428110022616</v>
+        <v>236.9101496911581</v>
       </c>
       <c r="E16" t="n">
-        <v>237.2876129150391</v>
+        <v>238.7577514648438</v>
       </c>
       <c r="F16" t="n">
-        <v>7679200</v>
+        <v>8849800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>237.1584831814004</v>
+        <v>237.7346158803774</v>
       </c>
       <c r="C17" t="n">
-        <v>241.1914166378037</v>
+        <v>248.8003554681588</v>
       </c>
       <c r="D17" t="n">
-        <v>236.9101496911581</v>
+        <v>233.8407486183705</v>
       </c>
       <c r="E17" t="n">
-        <v>238.7577514648438</v>
+        <v>244.1416168212891</v>
       </c>
       <c r="F17" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>237.7346158803774</v>
+        <v>244.8369527383155</v>
       </c>
       <c r="C18" t="n">
-        <v>248.8003554681588</v>
+        <v>245.7110914823814</v>
       </c>
       <c r="D18" t="n">
-        <v>233.8407486183705</v>
+        <v>235.9664876595567</v>
       </c>
       <c r="E18" t="n">
-        <v>244.1416168212891</v>
+        <v>238.1418914794922</v>
       </c>
       <c r="F18" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>244.8369370505447</v>
+        <v>238.1418828252031</v>
       </c>
       <c r="C19" t="n">
-        <v>245.7110757386007</v>
+        <v>239.7113522599795</v>
       </c>
       <c r="D19" t="n">
-        <v>235.9664725401552</v>
+        <v>234.0791355152303</v>
       </c>
       <c r="E19" t="n">
-        <v>238.1418762207031</v>
+        <v>238.8272705078125</v>
       </c>
       <c r="F19" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>238.1418828252031</v>
+        <v>237.6750243923864</v>
       </c>
       <c r="C20" t="n">
-        <v>239.7113522599795</v>
+        <v>244.3204311088745</v>
       </c>
       <c r="D20" t="n">
-        <v>234.0791355152303</v>
+        <v>235.569146059018</v>
       </c>
       <c r="E20" t="n">
-        <v>238.8272705078125</v>
+        <v>243.6946258544922</v>
       </c>
       <c r="F20" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>237.6750243923864</v>
+        <v>244.8766869952599</v>
       </c>
       <c r="C21" t="n">
-        <v>244.3204311088745</v>
+        <v>247.3898206494827</v>
       </c>
       <c r="D21" t="n">
-        <v>235.569146059018</v>
+        <v>239.1153471150808</v>
       </c>
       <c r="E21" t="n">
-        <v>243.6946258544922</v>
+        <v>240.0689392089844</v>
       </c>
       <c r="F21" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B22" t="n">
-        <v>244.8767025596296</v>
+        <v>241.2708896666147</v>
       </c>
       <c r="C22" t="n">
-        <v>247.3898363735872</v>
+        <v>247.6878338430882</v>
       </c>
       <c r="D22" t="n">
-        <v>239.1153623132595</v>
+        <v>240.7543517533109</v>
       </c>
       <c r="E22" t="n">
-        <v>240.0689544677734</v>
+        <v>247.0918273925781</v>
       </c>
       <c r="F22" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B23" t="n">
-        <v>241.2708896666147</v>
+        <v>246.4560936245009</v>
       </c>
       <c r="C23" t="n">
-        <v>247.6878338430882</v>
+        <v>246.6249585817316</v>
       </c>
       <c r="D23" t="n">
-        <v>240.7543517533109</v>
+        <v>237.9531572070389</v>
       </c>
       <c r="E23" t="n">
-        <v>247.0918273925781</v>
+        <v>238.1716918945312</v>
       </c>
       <c r="F23" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>246.4560778349605</v>
+        <v>239.2643408725642</v>
       </c>
       <c r="C24" t="n">
-        <v>246.6249427813727</v>
+        <v>239.711353270466</v>
       </c>
       <c r="D24" t="n">
-        <v>237.9531419622505</v>
+        <v>234.3274699865544</v>
       </c>
       <c r="E24" t="n">
-        <v>238.1716766357422</v>
+        <v>235.0029449462891</v>
       </c>
       <c r="F24" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B25" t="n">
-        <v>239.2643564080466</v>
+        <v>251.502226767664</v>
       </c>
       <c r="C25" t="n">
-        <v>239.711368834973</v>
+        <v>255.0285501861264</v>
       </c>
       <c r="D25" t="n">
-        <v>234.3274852014847</v>
+        <v>241.0523493056123</v>
       </c>
       <c r="E25" t="n">
-        <v>235.0029602050781</v>
+        <v>244.3601531982422</v>
       </c>
       <c r="F25" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B26" t="n">
-        <v>251.502226767664</v>
+        <v>244.9263662846688</v>
       </c>
       <c r="C26" t="n">
-        <v>255.0285501861264</v>
+        <v>249.1082938450064</v>
       </c>
       <c r="D26" t="n">
-        <v>241.0523493056123</v>
+        <v>240.5457598030287</v>
       </c>
       <c r="E26" t="n">
-        <v>244.3601531982422</v>
+        <v>241.4596252441406</v>
       </c>
       <c r="F26" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B27" t="n">
-        <v>244.926381762535</v>
+        <v>243.3668228990331</v>
       </c>
       <c r="C27" t="n">
-        <v>249.1083095871451</v>
+        <v>253.6974901347749</v>
       </c>
       <c r="D27" t="n">
-        <v>240.5457750040669</v>
+        <v>242.6714921507363</v>
       </c>
       <c r="E27" t="n">
-        <v>241.4596405029297</v>
+        <v>252.5849609375</v>
       </c>
       <c r="F27" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B28" t="n">
-        <v>243.3668228990331</v>
+        <v>252.8034746662165</v>
       </c>
       <c r="C28" t="n">
-        <v>253.6974901347749</v>
+        <v>265.349286530367</v>
       </c>
       <c r="D28" t="n">
-        <v>242.6714921507363</v>
+        <v>252.3068077218821</v>
       </c>
       <c r="E28" t="n">
-        <v>252.5849609375</v>
+        <v>261.6540832519531</v>
       </c>
       <c r="F28" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>252.803504151519</v>
+        <v>260.4521950408587</v>
       </c>
       <c r="C29" t="n">
-        <v>265.3493174789288</v>
+        <v>260.6508436585594</v>
       </c>
       <c r="D29" t="n">
-        <v>252.3068371492567</v>
+        <v>254.8001219796189</v>
       </c>
       <c r="E29" t="n">
-        <v>261.6541137695312</v>
+        <v>254.9292602539062</v>
       </c>
       <c r="F29" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B30" t="n">
-        <v>260.4521950408587</v>
+        <v>255.8828429735078</v>
       </c>
       <c r="C30" t="n">
-        <v>260.6508436585594</v>
+        <v>256.8364351199962</v>
       </c>
       <c r="D30" t="n">
-        <v>254.8001219796189</v>
+        <v>252.4260297605343</v>
       </c>
       <c r="E30" t="n">
-        <v>254.9292602539062</v>
+        <v>253.3498382568359</v>
       </c>
       <c r="F30" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="n">
-        <v>255.8828429735078</v>
+        <v>255.7040484271523</v>
       </c>
       <c r="C31" t="n">
-        <v>256.8364351199962</v>
+        <v>256.7768357955393</v>
       </c>
       <c r="D31" t="n">
-        <v>252.4260297605343</v>
+        <v>252.306832851323</v>
       </c>
       <c r="E31" t="n">
-        <v>253.3498382568359</v>
+        <v>253.1313018798828</v>
       </c>
       <c r="F31" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B32" t="n">
-        <v>255.7040638410269</v>
+        <v>255.3662819386644</v>
       </c>
       <c r="C32" t="n">
-        <v>256.7768512740817</v>
+        <v>256.3795019822516</v>
       </c>
       <c r="D32" t="n">
-        <v>252.3068480604129</v>
+        <v>253.2206920973818</v>
       </c>
       <c r="E32" t="n">
-        <v>253.1313171386719</v>
+        <v>253.7670288085938</v>
       </c>
       <c r="F32" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B33" t="n">
-        <v>255.3662819386644</v>
+        <v>253.7670347871236</v>
       </c>
       <c r="C33" t="n">
-        <v>256.3795019822516</v>
+        <v>257.1145654719376</v>
       </c>
       <c r="D33" t="n">
-        <v>253.2206920973818</v>
+        <v>252.4458987660038</v>
       </c>
       <c r="E33" t="n">
-        <v>253.7670288085938</v>
+        <v>252.5650939941406</v>
       </c>
       <c r="F33" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B34" t="n">
-        <v>253.7670347871236</v>
+        <v>250.3201613768906</v>
       </c>
       <c r="C34" t="n">
-        <v>257.1145654719376</v>
+        <v>251.8797029910229</v>
       </c>
       <c r="D34" t="n">
-        <v>252.4458987660038</v>
+        <v>247.3798861455735</v>
       </c>
       <c r="E34" t="n">
-        <v>252.5650939941406</v>
+        <v>249.7837677001953</v>
       </c>
       <c r="F34" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B35" t="n">
-        <v>250.3201460853343</v>
+        <v>248.8301503215196</v>
       </c>
       <c r="C35" t="n">
-        <v>251.8796876041973</v>
+        <v>257.5516210443747</v>
       </c>
       <c r="D35" t="n">
-        <v>247.3798710336327</v>
+        <v>248.33348335481</v>
       </c>
       <c r="E35" t="n">
-        <v>249.7837524414062</v>
+        <v>254.9391479492188</v>
       </c>
       <c r="F35" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B36" t="n">
-        <v>248.8301503215196</v>
+        <v>253.1014986048366</v>
       </c>
       <c r="C36" t="n">
-        <v>257.5516210443747</v>
+        <v>260.0747073186972</v>
       </c>
       <c r="D36" t="n">
-        <v>248.33348335481</v>
+        <v>250.945965708637</v>
       </c>
       <c r="E36" t="n">
-        <v>254.9391479492188</v>
+        <v>258.6741027832031</v>
       </c>
       <c r="F36" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B37" t="n">
-        <v>253.1014986048366</v>
+        <v>258.2668364864311</v>
       </c>
       <c r="C37" t="n">
-        <v>260.0747073186972</v>
+        <v>259.8164350802179</v>
       </c>
       <c r="D37" t="n">
-        <v>250.945965708637</v>
+        <v>253.3995060154779</v>
       </c>
       <c r="E37" t="n">
-        <v>258.6741027832031</v>
+        <v>259.597900390625</v>
       </c>
       <c r="F37" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B38" t="n">
-        <v>258.2668364864311</v>
+        <v>256.4291570066316</v>
       </c>
       <c r="C38" t="n">
-        <v>259.8164350802179</v>
+        <v>257.5317734711582</v>
       </c>
       <c r="D38" t="n">
-        <v>253.3995060154779</v>
+        <v>251.7704334426377</v>
       </c>
       <c r="E38" t="n">
-        <v>259.597900390625</v>
+        <v>252.743896484375</v>
       </c>
       <c r="F38" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B39" t="n">
-        <v>256.4291570066316</v>
+        <v>253.0021595946237</v>
       </c>
       <c r="C39" t="n">
-        <v>257.5317734711582</v>
+        <v>255.1179506478194</v>
       </c>
       <c r="D39" t="n">
-        <v>251.7704334426377</v>
+        <v>250.3300887852593</v>
       </c>
       <c r="E39" t="n">
-        <v>252.743896484375</v>
+        <v>250.9956207275391</v>
       </c>
       <c r="F39" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B40" t="n">
-        <v>253.0021749753964</v>
+        <v>248.8698810068921</v>
       </c>
       <c r="C40" t="n">
-        <v>255.1179661572175</v>
+        <v>248.8698810068921</v>
       </c>
       <c r="D40" t="n">
-        <v>250.3301040035887</v>
+        <v>232.9169402050875</v>
       </c>
       <c r="E40" t="n">
-        <v>250.9956359863281</v>
+        <v>237.6750183105469</v>
       </c>
       <c r="F40" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B41" t="n">
-        <v>248.8698969843938</v>
+        <v>234.575813422799</v>
       </c>
       <c r="C41" t="n">
-        <v>248.8698969843938</v>
+        <v>239.3636904840115</v>
       </c>
       <c r="D41" t="n">
-        <v>232.9169551584068</v>
+        <v>234.2182125835504</v>
       </c>
       <c r="E41" t="n">
-        <v>237.6750335693359</v>
+        <v>238.2809600830078</v>
       </c>
       <c r="F41" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B42" t="n">
-        <v>234.575813422799</v>
+        <v>238.4001471651486</v>
       </c>
       <c r="C42" t="n">
-        <v>239.3636904840115</v>
+        <v>240.2974186407021</v>
       </c>
       <c r="D42" t="n">
-        <v>234.2182125835504</v>
+        <v>233.5129459671118</v>
       </c>
       <c r="E42" t="n">
-        <v>238.2809600830078</v>
+        <v>240.0987548828125</v>
       </c>
       <c r="F42" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B43" t="n">
-        <v>238.4001623159876</v>
+        <v>240.2874885014218</v>
       </c>
       <c r="C43" t="n">
-        <v>240.2974339121167</v>
+        <v>244.062160732275</v>
       </c>
       <c r="D43" t="n">
-        <v>233.5129608073587</v>
+        <v>239.5524310420585</v>
       </c>
       <c r="E43" t="n">
-        <v>240.0987701416016</v>
+        <v>242.8701629638672</v>
       </c>
       <c r="F43" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B44" t="n">
-        <v>240.2874885014218</v>
+        <v>244.1019030924143</v>
       </c>
       <c r="C44" t="n">
-        <v>244.062160732275</v>
+        <v>246.7739588256813</v>
       </c>
       <c r="D44" t="n">
-        <v>239.5524310420585</v>
+        <v>242.055622316483</v>
       </c>
       <c r="E44" t="n">
-        <v>242.8701629638672</v>
+        <v>244.3800354003906</v>
       </c>
       <c r="F44" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B45" t="n">
-        <v>244.1019030924143</v>
+        <v>243.6151473457208</v>
       </c>
       <c r="C45" t="n">
-        <v>246.7739588256813</v>
+        <v>244.260808340077</v>
       </c>
       <c r="D45" t="n">
-        <v>242.055622316483</v>
+        <v>238.3107477751567</v>
       </c>
       <c r="E45" t="n">
-        <v>244.3800354003906</v>
+        <v>238.8272705078125</v>
       </c>
       <c r="F45" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="n">
-        <v>243.6151473457208</v>
+        <v>236.7214236272305</v>
       </c>
       <c r="C46" t="n">
-        <v>244.260808340077</v>
+        <v>243.5456233717372</v>
       </c>
       <c r="D46" t="n">
-        <v>238.3107477751567</v>
+        <v>235.8373569715999</v>
       </c>
       <c r="E46" t="n">
-        <v>238.8272705078125</v>
+        <v>242.0357666015625</v>
       </c>
       <c r="F46" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="n">
-        <v>236.7214087034764</v>
+        <v>240.4563473167674</v>
       </c>
       <c r="C47" t="n">
-        <v>243.5456080177614</v>
+        <v>241.2112756332267</v>
       </c>
       <c r="D47" t="n">
-        <v>235.8373421035805</v>
+        <v>234.0195326548913</v>
       </c>
       <c r="E47" t="n">
-        <v>242.0357513427734</v>
+        <v>235.4499359130859</v>
       </c>
       <c r="F47" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B48" t="n">
-        <v>240.4563629000066</v>
+        <v>234.6652219732086</v>
       </c>
       <c r="C48" t="n">
-        <v>241.2112912653905</v>
+        <v>236.204877497401</v>
       </c>
       <c r="D48" t="n">
-        <v>234.0195478209803</v>
+        <v>228.7350169737969</v>
       </c>
       <c r="E48" t="n">
-        <v>235.449951171875</v>
+        <v>231.9434814453125</v>
       </c>
       <c r="F48" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
-        <v>234.6652065353653</v>
+        <v>230.453493236797</v>
       </c>
       <c r="C49" t="n">
-        <v>236.2048619582689</v>
+        <v>230.7316255505513</v>
       </c>
       <c r="D49" t="n">
-        <v>228.735001926082</v>
+        <v>223.5597526950127</v>
       </c>
       <c r="E49" t="n">
-        <v>231.9434661865234</v>
+        <v>226.3609619140625</v>
       </c>
       <c r="F49" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B50" t="n">
-        <v>230.4534777021341</v>
+        <v>227.7218165007521</v>
       </c>
       <c r="C50" t="n">
-        <v>230.7316099971398</v>
+        <v>229.5296916323367</v>
       </c>
       <c r="D50" t="n">
-        <v>223.5597376250506</v>
+        <v>221.8114823100099</v>
       </c>
       <c r="E50" t="n">
-        <v>226.3609466552734</v>
+        <v>223.86767578125</v>
       </c>
       <c r="F50" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B51" t="n">
-        <v>227.7218165007521</v>
+        <v>223.3610679945535</v>
       </c>
       <c r="C51" t="n">
-        <v>229.5296916323367</v>
+        <v>227.1555957235809</v>
       </c>
       <c r="D51" t="n">
-        <v>221.8114823100099</v>
+        <v>220.480405661821</v>
       </c>
       <c r="E51" t="n">
-        <v>223.86767578125</v>
+        <v>225.5960693359375</v>
       </c>
       <c r="F51" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B52" t="n">
-        <v>223.3610831021723</v>
+        <v>225.824551950926</v>
       </c>
       <c r="C52" t="n">
-        <v>227.1556110878527</v>
+        <v>227.314552977507</v>
       </c>
       <c r="D52" t="n">
-        <v>220.4804205745986</v>
+        <v>223.5398806787535</v>
       </c>
       <c r="E52" t="n">
-        <v>225.5960845947266</v>
+        <v>225.3080291748047</v>
       </c>
       <c r="F52" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B53" t="n">
-        <v>225.824551950926</v>
+        <v>225.2881447387201</v>
       </c>
       <c r="C53" t="n">
-        <v>227.314552977507</v>
+        <v>233.065951449845</v>
       </c>
       <c r="D53" t="n">
-        <v>223.5398806787535</v>
+        <v>225.0100124430054</v>
       </c>
       <c r="E53" t="n">
-        <v>225.3080291748047</v>
+        <v>232.5593414306641</v>
       </c>
       <c r="F53" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B54" t="n">
-        <v>225.2881447387201</v>
+        <v>228.9734038653133</v>
       </c>
       <c r="C54" t="n">
-        <v>233.065951449845</v>
+        <v>231.2680180268392</v>
       </c>
       <c r="D54" t="n">
-        <v>225.0100124430054</v>
+        <v>224.493473197433</v>
       </c>
       <c r="E54" t="n">
-        <v>232.5593414306641</v>
+        <v>226.6291351318359</v>
       </c>
       <c r="F54" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B55" t="n">
-        <v>228.9734038653133</v>
+        <v>227.4734767172409</v>
       </c>
       <c r="C55" t="n">
-        <v>231.2680180268392</v>
+        <v>231.0097431878008</v>
       </c>
       <c r="D55" t="n">
-        <v>224.493473197433</v>
+        <v>227.1059480025027</v>
       </c>
       <c r="E55" t="n">
-        <v>226.6291351318359</v>
+        <v>229.0032043457031</v>
       </c>
       <c r="F55" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B56" t="n">
-        <v>227.4734767172409</v>
+        <v>227.1456810763456</v>
       </c>
       <c r="C56" t="n">
-        <v>231.0097431878008</v>
+        <v>232.6884865447995</v>
       </c>
       <c r="D56" t="n">
-        <v>227.1059480025027</v>
+        <v>227.0761555789071</v>
       </c>
       <c r="E56" t="n">
-        <v>229.0032043457031</v>
+        <v>231.2779541015625</v>
       </c>
       <c r="F56" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B57" t="n">
-        <v>227.1456660901873</v>
+        <v>231.4666946211142</v>
       </c>
       <c r="C57" t="n">
-        <v>232.6884711929492</v>
+        <v>235.0724867607419</v>
       </c>
       <c r="D57" t="n">
-        <v>227.0761405973358</v>
+        <v>230.0760179166733</v>
       </c>
       <c r="E57" t="n">
-        <v>231.2779388427734</v>
+        <v>233.1454315185547</v>
       </c>
       <c r="F57" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B58" t="n">
-        <v>231.4666946211142</v>
+        <v>233.7910897956687</v>
       </c>
       <c r="C58" t="n">
-        <v>235.0724867607419</v>
+        <v>237.6650863154301</v>
       </c>
       <c r="D58" t="n">
-        <v>230.0760179166733</v>
+        <v>231.605758036904</v>
       </c>
       <c r="E58" t="n">
-        <v>233.1454315185547</v>
+        <v>237.1286926269531</v>
       </c>
       <c r="F58" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B59" t="n">
-        <v>233.7910747516482</v>
+        <v>242.065551586444</v>
       </c>
       <c r="C59" t="n">
-        <v>237.6650710221251</v>
+        <v>247.3103536057372</v>
       </c>
       <c r="D59" t="n">
-        <v>231.6057431335055</v>
+        <v>236.016151496486</v>
       </c>
       <c r="E59" t="n">
-        <v>237.1286773681641</v>
+        <v>245.8104248046875</v>
       </c>
       <c r="F59" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B60" t="n">
-        <v>242.065551586444</v>
+        <v>249.1579600621082</v>
       </c>
       <c r="C60" t="n">
-        <v>247.3103536057372</v>
+        <v>260.1343033980639</v>
       </c>
       <c r="D60" t="n">
-        <v>236.016151496486</v>
+        <v>247.8368240708576</v>
       </c>
       <c r="E60" t="n">
-        <v>245.8104248046875</v>
+        <v>258.8330383300781</v>
       </c>
       <c r="F60" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B61" t="n">
-        <v>249.1579600621082</v>
+        <v>260.1342981066347</v>
       </c>
       <c r="C61" t="n">
-        <v>260.1343033980639</v>
+        <v>262.5182935094206</v>
       </c>
       <c r="D61" t="n">
-        <v>247.8368240708576</v>
+        <v>254.6312195688788</v>
       </c>
       <c r="E61" t="n">
-        <v>258.8330383300781</v>
+        <v>257.7999572753906</v>
       </c>
       <c r="F61" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B62" t="n">
-        <v>260.134328900545</v>
+        <v>258.266839531805</v>
       </c>
       <c r="C62" t="n">
-        <v>262.5183245855411</v>
+        <v>260.5018410277533</v>
       </c>
       <c r="D62" t="n">
-        <v>254.6312497113514</v>
+        <v>257.2735055336058</v>
       </c>
       <c r="E62" t="n">
-        <v>257.7999877929688</v>
+        <v>259.280029296875</v>
       </c>
       <c r="F62" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B63" t="n">
-        <v>258.2668091334806</v>
+        <v>259.0118285064661</v>
       </c>
       <c r="C63" t="n">
-        <v>260.5018103663664</v>
+        <v>264.1572911128101</v>
       </c>
       <c r="D63" t="n">
-        <v>257.273475252198</v>
+        <v>257.4224881172308</v>
       </c>
       <c r="E63" t="n">
-        <v>259.2799987792969</v>
+        <v>262.4388427734375</v>
       </c>
       <c r="F63" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B64" t="n">
-        <v>259.0117983873967</v>
+        <v>261.7434937420645</v>
       </c>
       <c r="C64" t="n">
-        <v>264.157260395403</v>
+        <v>266.1141570244538</v>
       </c>
       <c r="D64" t="n">
-        <v>257.4224581829772</v>
+        <v>259.0316811670522</v>
       </c>
       <c r="E64" t="n">
-        <v>262.4388122558594</v>
+        <v>260.6011657714844</v>
       </c>
       <c r="F64" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B65" t="n">
-        <v>261.7434937420645</v>
+        <v>261.7633737064805</v>
       </c>
       <c r="C65" t="n">
-        <v>266.1141570244538</v>
+        <v>262.7269089319525</v>
       </c>
       <c r="D65" t="n">
-        <v>259.0316811670522</v>
+        <v>259.1707864287312</v>
       </c>
       <c r="E65" t="n">
-        <v>260.6011657714844</v>
+        <v>260.4819946289062</v>
       </c>
       <c r="F65" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B66" t="n">
-        <v>261.7633737064805</v>
+        <v>259.468759033079</v>
       </c>
       <c r="C66" t="n">
-        <v>262.7269089319525</v>
+        <v>260.5316336613609</v>
       </c>
       <c r="D66" t="n">
-        <v>259.1707864287312</v>
+        <v>251.4028920091002</v>
       </c>
       <c r="E66" t="n">
-        <v>260.4819946289062</v>
+        <v>252.8829650878906</v>
       </c>
       <c r="F66" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B67" t="n">
-        <v>259.468759033079</v>
+        <v>252.3068168853155</v>
       </c>
       <c r="C67" t="n">
-        <v>260.5316336613609</v>
+        <v>254.1544185916248</v>
       </c>
       <c r="D67" t="n">
-        <v>251.4028920091002</v>
+        <v>250.4294163738298</v>
       </c>
       <c r="E67" t="n">
-        <v>252.8829650878906</v>
+        <v>253.2107543945312</v>
       </c>
       <c r="F67" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B68" t="n">
-        <v>252.3068168853155</v>
+        <v>254.621288079056</v>
       </c>
       <c r="C68" t="n">
-        <v>254.1544185916248</v>
+        <v>260.223706328179</v>
       </c>
       <c r="D68" t="n">
-        <v>250.4294163738298</v>
+        <v>254.5418346981557</v>
       </c>
       <c r="E68" t="n">
-        <v>253.2107543945312</v>
+        <v>256.4192504882812</v>
       </c>
       <c r="F68" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B69" t="n">
-        <v>254.621288079056</v>
+        <v>257.1117077238193</v>
       </c>
       <c r="C69" t="n">
-        <v>260.223706328179</v>
+        <v>258.7533481789523</v>
       </c>
       <c r="D69" t="n">
-        <v>254.5418346981557</v>
+        <v>254.8631397332645</v>
       </c>
       <c r="E69" t="n">
-        <v>256.4192504882812</v>
+        <v>256.5445861816406</v>
       </c>
       <c r="F69" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B70" t="n">
-        <v>257.11173830886</v>
+        <v>259.3602680955166</v>
       </c>
       <c r="C70" t="n">
-        <v>258.7533789592764</v>
+        <v>260.7133987167576</v>
       </c>
       <c r="D70" t="n">
-        <v>254.863170050824</v>
+        <v>254.2064997708628</v>
       </c>
       <c r="E70" t="n">
-        <v>256.5446166992188</v>
+        <v>258.5941772460938</v>
       </c>
       <c r="F70" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G70" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B71" t="n">
-        <v>259.3602680955166</v>
+        <v>259.3005746010855</v>
       </c>
       <c r="C71" t="n">
-        <v>260.7133987167576</v>
+        <v>263.290283203125</v>
       </c>
       <c r="D71" t="n">
-        <v>254.2064997708628</v>
+        <v>257.1017714973269</v>
       </c>
       <c r="E71" t="n">
-        <v>258.5941772460938</v>
+        <v>263.290283203125</v>
       </c>
       <c r="F71" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B72" t="n">
-        <v>259.3005746010855</v>
+        <v>261.3899469633664</v>
       </c>
       <c r="C72" t="n">
-        <v>263.290283203125</v>
+        <v>262.9022408344935</v>
       </c>
       <c r="D72" t="n">
-        <v>257.1017714973269</v>
+        <v>259.2010726049517</v>
       </c>
       <c r="E72" t="n">
-        <v>263.290283203125</v>
+        <v>262.0963439941406</v>
       </c>
       <c r="F72" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B73" t="n">
-        <v>261.3899469633664</v>
+        <v>261.8973924752027</v>
       </c>
       <c r="C73" t="n">
-        <v>262.9022408344935</v>
+        <v>264.951827330886</v>
       </c>
       <c r="D73" t="n">
-        <v>259.2010726049517</v>
+        <v>261.2208119420935</v>
       </c>
       <c r="E73" t="n">
-        <v>262.0963439941406</v>
+        <v>263.9171142578125</v>
       </c>
       <c r="F73" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="n">
-        <v>261.8973621911715</v>
+        <v>263.4593915943883</v>
       </c>
       <c r="C74" t="n">
-        <v>264.9517966936607</v>
+        <v>266.5536624648736</v>
       </c>
       <c r="D74" t="n">
-        <v>261.2207817362974</v>
+        <v>263.4593915943883</v>
       </c>
       <c r="E74" t="n">
-        <v>263.9170837402344</v>
+        <v>264.73291015625</v>
       </c>
       <c r="F74" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B75" t="n">
-        <v>263.4593915943883</v>
+        <v>263.3698474835284</v>
       </c>
       <c r="C75" t="n">
-        <v>266.5536624648736</v>
+        <v>267.7475655858019</v>
       </c>
       <c r="D75" t="n">
-        <v>263.4593915943883</v>
+        <v>263.3698474835284</v>
       </c>
       <c r="E75" t="n">
-        <v>264.73291015625</v>
+        <v>264.8821716308594</v>
       </c>
       <c r="F75" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B76" t="n">
-        <v>263.3698474835284</v>
+        <v>265.3100049300543</v>
       </c>
       <c r="C76" t="n">
-        <v>267.7475655858019</v>
+        <v>266.9217986247408</v>
       </c>
       <c r="D76" t="n">
-        <v>263.3698474835284</v>
+        <v>263.9867212136458</v>
       </c>
       <c r="E76" t="n">
-        <v>264.8821716308594</v>
+        <v>264.5737609863281</v>
       </c>
       <c r="F76" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="n">
-        <v>265.3100049300543</v>
+        <v>263.9469286938932</v>
       </c>
       <c r="C77" t="n">
-        <v>266.9217986247408</v>
+        <v>264.7528254896791</v>
       </c>
       <c r="D77" t="n">
-        <v>263.9867212136458</v>
+        <v>263.0514911833619</v>
       </c>
       <c r="E77" t="n">
-        <v>264.5737609863281</v>
+        <v>263.56884765625</v>
       </c>
       <c r="F77" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B78" t="n">
-        <v>263.9469286938932</v>
+        <v>263.6583901080786</v>
       </c>
       <c r="C78" t="n">
-        <v>264.7528254896791</v>
+        <v>264.0364711482127</v>
       </c>
       <c r="D78" t="n">
-        <v>263.0514911833619</v>
+        <v>251.2017705962925</v>
       </c>
       <c r="E78" t="n">
-        <v>263.56884765625</v>
+        <v>252.3359985351562</v>
       </c>
       <c r="F78" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B79" t="n">
-        <v>263.6584060515341</v>
+        <v>252.3359973941062</v>
       </c>
       <c r="C79" t="n">
-        <v>264.0364871145308</v>
+        <v>258.2757743891104</v>
       </c>
       <c r="D79" t="n">
-        <v>251.2017857864946</v>
+        <v>251.0326319383232</v>
       </c>
       <c r="E79" t="n">
-        <v>252.3360137939453</v>
+        <v>254.962646484375</v>
       </c>
       <c r="F79" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B80" t="n">
-        <v>252.3359973941062</v>
+        <v>253.9079863590369</v>
       </c>
       <c r="C80" t="n">
-        <v>258.2757743891104</v>
+        <v>262.2157033921641</v>
       </c>
       <c r="D80" t="n">
-        <v>251.0326319383232</v>
+        <v>253.7090019428403</v>
       </c>
       <c r="E80" t="n">
-        <v>254.962646484375</v>
+        <v>261.5690002441406</v>
       </c>
       <c r="F80" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B81" t="n">
-        <v>253.9080159827951</v>
+        <v>262.1659742529432</v>
       </c>
       <c r="C81" t="n">
-        <v>262.2157339851939</v>
+        <v>266.4740393315776</v>
       </c>
       <c r="D81" t="n">
-        <v>253.7090315433827</v>
+        <v>262.1659742529432</v>
       </c>
       <c r="E81" t="n">
-        <v>261.5690307617188</v>
+        <v>264.772705078125</v>
       </c>
       <c r="F81" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B82" t="n">
-        <v>262.1659742529432</v>
+        <v>263.0614317758581</v>
       </c>
       <c r="C82" t="n">
-        <v>266.4740393315776</v>
+        <v>263.8573998812952</v>
       </c>
       <c r="D82" t="n">
-        <v>262.1659742529432</v>
+        <v>259.0916414276884</v>
       </c>
       <c r="E82" t="n">
-        <v>264.772705078125</v>
+        <v>259.2110290527344</v>
       </c>
       <c r="F82" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B83" t="n">
-        <v>263.0614317758581</v>
+        <v>258.6836867262742</v>
       </c>
       <c r="C83" t="n">
-        <v>263.8573998812952</v>
+        <v>259.7084708860899</v>
       </c>
       <c r="D83" t="n">
-        <v>259.0916414276884</v>
+        <v>255.2113654167864</v>
       </c>
       <c r="E83" t="n">
-        <v>259.2110290527344</v>
+        <v>258.6239929199219</v>
       </c>
       <c r="F83" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B84" t="n">
-        <v>258.6837172508962</v>
+        <v>257.6887925779931</v>
       </c>
       <c r="C84" t="n">
-        <v>259.7085015316362</v>
+        <v>260.2358299520341</v>
       </c>
       <c r="D84" t="n">
-        <v>255.2113955316752</v>
+        <v>254.4751489522725</v>
       </c>
       <c r="E84" t="n">
-        <v>258.6240234375</v>
+        <v>258.0867614746094</v>
       </c>
       <c r="F84" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B85" t="n">
-        <v>257.6887621074729</v>
+        <v>256.3555659982514</v>
       </c>
       <c r="C85" t="n">
-        <v>260.2357991803385</v>
+        <v>259.5891124457121</v>
       </c>
       <c r="D85" t="n">
-        <v>254.475118861751</v>
+        <v>239.1431464877683</v>
       </c>
       <c r="E85" t="n">
-        <v>258.0867309570312</v>
+        <v>239.839599609375</v>
       </c>
       <c r="F85" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B86" t="n">
-        <v>256.3555659982514</v>
+        <v>237.9691070776633</v>
       </c>
       <c r="C86" t="n">
-        <v>259.5891124457121</v>
+        <v>241.0136281082575</v>
       </c>
       <c r="D86" t="n">
-        <v>239.1431464877683</v>
+        <v>235.2628914641447</v>
       </c>
       <c r="E86" t="n">
-        <v>239.839599609375</v>
+        <v>238.3571472167969</v>
       </c>
       <c r="F86" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B87" t="n">
-        <v>237.9691070776633</v>
+        <v>235.8200540893699</v>
       </c>
       <c r="C87" t="n">
-        <v>241.0136281082575</v>
+        <v>237.6308321653778</v>
       </c>
       <c r="D87" t="n">
-        <v>235.2628914641447</v>
+        <v>230.4971332136314</v>
       </c>
       <c r="E87" t="n">
-        <v>238.3571472167969</v>
+        <v>232.3477172851562</v>
       </c>
       <c r="F87" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B88" t="n">
-        <v>235.8200540893699</v>
+        <v>231.770650770317</v>
       </c>
       <c r="C88" t="n">
-        <v>237.6308321653778</v>
+        <v>231.770650770317</v>
       </c>
       <c r="D88" t="n">
-        <v>230.4971332136314</v>
+        <v>225.2936141395941</v>
       </c>
       <c r="E88" t="n">
-        <v>232.3477172851562</v>
+        <v>225.9602203369141</v>
       </c>
       <c r="F88" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B89" t="n">
-        <v>231.770650770317</v>
+        <v>222.4082747466268</v>
       </c>
       <c r="C89" t="n">
-        <v>231.770650770317</v>
+        <v>226.7860079240682</v>
       </c>
       <c r="D89" t="n">
-        <v>225.2936141395941</v>
+        <v>218.2494441686726</v>
       </c>
       <c r="E89" t="n">
-        <v>225.9602203369141</v>
+        <v>218.9558563232422</v>
       </c>
       <c r="F89" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B90" t="n">
-        <v>222.4082902460111</v>
+        <v>219.0354531203157</v>
       </c>
       <c r="C90" t="n">
-        <v>226.7860237285318</v>
+        <v>222.2590556230766</v>
       </c>
       <c r="D90" t="n">
-        <v>218.2494593782326</v>
+        <v>217.8514904177117</v>
       </c>
       <c r="E90" t="n">
-        <v>218.9558715820312</v>
+        <v>220.4582214355469</v>
       </c>
       <c r="F90" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B91" t="n">
-        <v>219.0354531203157</v>
+        <v>221.1148825581443</v>
       </c>
       <c r="C91" t="n">
-        <v>222.2590556230766</v>
+        <v>227.5620723478159</v>
       </c>
       <c r="D91" t="n">
-        <v>217.8514904177117</v>
+        <v>219.9905984923716</v>
       </c>
       <c r="E91" t="n">
-        <v>220.4582214355469</v>
+        <v>226.9352569580078</v>
       </c>
       <c r="F91" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B92" t="n">
-        <v>221.1148825581443</v>
+        <v>225.631887371227</v>
       </c>
       <c r="C92" t="n">
-        <v>227.5620723478159</v>
+        <v>229.6812896074088</v>
       </c>
       <c r="D92" t="n">
-        <v>219.9905984923716</v>
+        <v>225.5025406597253</v>
       </c>
       <c r="E92" t="n">
-        <v>226.9352569580078</v>
+        <v>226.8954620361328</v>
       </c>
       <c r="F92" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B93" t="n">
-        <v>225.631887371227</v>
+        <v>228.2684638486727</v>
       </c>
       <c r="C93" t="n">
-        <v>229.6812896074088</v>
+        <v>229.7807728378832</v>
       </c>
       <c r="D93" t="n">
-        <v>225.5025406597253</v>
+        <v>226.4377828089404</v>
       </c>
       <c r="E93" t="n">
-        <v>226.8954620361328</v>
+        <v>228.2386169433594</v>
       </c>
       <c r="F93" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B94" t="n">
-        <v>228.2684791094572</v>
+        <v>230.7657716267904</v>
       </c>
       <c r="C94" t="n">
-        <v>229.7807881997724</v>
+        <v>234.5465365970097</v>
       </c>
       <c r="D94" t="n">
-        <v>226.4377979473355</v>
+        <v>225.1244786682387</v>
       </c>
       <c r="E94" t="n">
-        <v>228.2386322021484</v>
+        <v>227.3730316162109</v>
       </c>
       <c r="F94" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B95" t="n">
-        <v>230.7657561403177</v>
+        <v>228.2286765757154</v>
       </c>
       <c r="C95" t="n">
-        <v>234.5465208568135</v>
+        <v>230.6861730282261</v>
       </c>
       <c r="D95" t="n">
-        <v>225.1244635603479</v>
+        <v>226.5173831306909</v>
       </c>
       <c r="E95" t="n">
-        <v>227.3730163574219</v>
+        <v>226.8059234619141</v>
       </c>
       <c r="F95" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B96" t="n">
-        <v>228.2286765757154</v>
+        <v>215.5730693423473</v>
       </c>
       <c r="C96" t="n">
-        <v>230.6861730282261</v>
+        <v>216.1799817205514</v>
       </c>
       <c r="D96" t="n">
-        <v>226.5173831306909</v>
+        <v>207.7230144205324</v>
       </c>
       <c r="E96" t="n">
-        <v>226.8059234619141</v>
+        <v>212.9961853027344</v>
       </c>
       <c r="F96" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B97" t="n">
-        <v>215.5730693423473</v>
+        <v>213.0757836211538</v>
       </c>
       <c r="C97" t="n">
-        <v>216.1799817205514</v>
+        <v>214.4587459115801</v>
       </c>
       <c r="D97" t="n">
-        <v>207.7230144205324</v>
+        <v>209.9616248999223</v>
       </c>
       <c r="E97" t="n">
-        <v>212.9961853027344</v>
+        <v>211.2152404785156</v>
       </c>
       <c r="F97" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B98" t="n">
-        <v>213.0757836211538</v>
+        <v>213.2648234781596</v>
       </c>
       <c r="C98" t="n">
-        <v>214.4587459115801</v>
+        <v>215.7919576250148</v>
       </c>
       <c r="D98" t="n">
-        <v>209.9616248999223</v>
+        <v>208.7378555750675</v>
       </c>
       <c r="E98" t="n">
-        <v>211.2152404785156</v>
+        <v>209.7427368164062</v>
       </c>
       <c r="F98" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B99" t="n">
-        <v>213.2648234781596</v>
+        <v>203.9621583905467</v>
       </c>
       <c r="C99" t="n">
-        <v>215.7919576250148</v>
+        <v>204.5193208819819</v>
       </c>
       <c r="D99" t="n">
-        <v>208.7378555750675</v>
+        <v>192.1323538111565</v>
       </c>
       <c r="E99" t="n">
-        <v>209.7427368164062</v>
+        <v>195.3858032226562</v>
       </c>
       <c r="F99" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B100" t="n">
-        <v>203.9621583905467</v>
+        <v>192.3313273349262</v>
       </c>
       <c r="C100" t="n">
-        <v>204.5193208819819</v>
+        <v>199.6540664816468</v>
       </c>
       <c r="D100" t="n">
-        <v>192.1323538111565</v>
+        <v>186.3318566210609</v>
       </c>
       <c r="E100" t="n">
-        <v>195.3858032226562</v>
+        <v>198.4302978515625</v>
       </c>
       <c r="F100" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B101" t="n">
-        <v>192.3313273349262</v>
+        <v>193.0079075172144</v>
       </c>
       <c r="C101" t="n">
-        <v>199.6540664816468</v>
+        <v>198.5497008209625</v>
       </c>
       <c r="D101" t="n">
-        <v>186.3318566210609</v>
+        <v>187.8342210038726</v>
       </c>
       <c r="E101" t="n">
-        <v>198.4302978515625</v>
+        <v>189.0082550048828</v>
       </c>
       <c r="F101" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B102" t="n">
-        <v>193.0079075172144</v>
+        <v>190.6598526107087</v>
       </c>
       <c r="C102" t="n">
-        <v>198.5497008209625</v>
+        <v>193.614817806995</v>
       </c>
       <c r="D102" t="n">
-        <v>187.8342210038726</v>
+        <v>186.1726753666609</v>
       </c>
       <c r="E102" t="n">
-        <v>189.0082550048828</v>
+        <v>190.3812713623047</v>
       </c>
       <c r="F102" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B103" t="n">
-        <v>190.6598526107087</v>
+        <v>188.3416494095636</v>
       </c>
       <c r="C103" t="n">
-        <v>193.614817806995</v>
+        <v>194.2117738895214</v>
       </c>
       <c r="D103" t="n">
-        <v>186.1726753666609</v>
+        <v>184.7897156694265</v>
       </c>
       <c r="E103" t="n">
-        <v>190.3812713623047</v>
+        <v>193.0476989746094</v>
       </c>
       <c r="F103" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B104" t="n">
-        <v>188.3416494095636</v>
+        <v>190.928470906174</v>
       </c>
       <c r="C104" t="n">
-        <v>194.2117738895214</v>
+        <v>198.0920319531629</v>
       </c>
       <c r="D104" t="n">
-        <v>184.7897156694265</v>
+        <v>189.7842990292034</v>
       </c>
       <c r="E104" t="n">
-        <v>193.0476989746094</v>
+        <v>192.4706268310547</v>
       </c>
       <c r="F104" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B105" t="n">
-        <v>190.928470906174</v>
+        <v>192.1721331807432</v>
       </c>
       <c r="C105" t="n">
-        <v>198.0920319531629</v>
+        <v>192.6895048269234</v>
       </c>
       <c r="D105" t="n">
-        <v>189.7842990292034</v>
+        <v>180.8895478564994</v>
       </c>
       <c r="E105" t="n">
-        <v>192.4706268310547</v>
+        <v>184.0634002685547</v>
       </c>
       <c r="F105" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B106" t="n">
-        <v>192.1721331807432</v>
+        <v>185.0185569607285</v>
       </c>
       <c r="C106" t="n">
-        <v>192.6895048269234</v>
+        <v>187.3666097225546</v>
       </c>
       <c r="D106" t="n">
-        <v>180.8895478564994</v>
+        <v>179.3275140834474</v>
       </c>
       <c r="E106" t="n">
-        <v>184.0634002685547</v>
+        <v>184.4912261962891</v>
       </c>
       <c r="F106" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B107" t="n">
-        <v>185.0185569607285</v>
+        <v>185.4961280832271</v>
       </c>
       <c r="C107" t="n">
-        <v>187.3666097225546</v>
+        <v>192.4706336714869</v>
       </c>
       <c r="D107" t="n">
-        <v>179.3275140834474</v>
+        <v>183.3669626912399</v>
       </c>
       <c r="E107" t="n">
-        <v>184.4912261962891</v>
+        <v>188.759521484375</v>
       </c>
       <c r="F107" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B108" t="n">
-        <v>185.4961130882416</v>
+        <v>190.0031839153662</v>
       </c>
       <c r="C108" t="n">
-        <v>192.470618112702</v>
+        <v>192.0229054891486</v>
       </c>
       <c r="D108" t="n">
-        <v>183.3669478683701</v>
+        <v>182.2426696727612</v>
       </c>
       <c r="E108" t="n">
-        <v>188.7595062255859</v>
+        <v>183.3569946289062</v>
       </c>
       <c r="F108" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B109" t="n">
-        <v>190.0031839153662</v>
+        <v>182.9490856555733</v>
       </c>
       <c r="C109" t="n">
-        <v>192.0229054891486</v>
+        <v>187.1875133215944</v>
       </c>
       <c r="D109" t="n">
-        <v>182.2426696727612</v>
+        <v>180.9393079480809</v>
       </c>
       <c r="E109" t="n">
-        <v>183.3569946289062</v>
+        <v>186.8392791748047</v>
       </c>
       <c r="F109" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B110" t="n">
-        <v>182.9490856555733</v>
+        <v>185.6553247148316</v>
       </c>
       <c r="C110" t="n">
-        <v>187.1875133215944</v>
+        <v>186.0035436955366</v>
       </c>
       <c r="D110" t="n">
-        <v>180.9393079480809</v>
+        <v>182.3023753569564</v>
       </c>
       <c r="E110" t="n">
-        <v>186.8392791748047</v>
+        <v>184.3519439697266</v>
       </c>
       <c r="F110" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B111" t="n">
-        <v>185.6553247148316</v>
+        <v>184.3817888273663</v>
       </c>
       <c r="C111" t="n">
-        <v>186.0035436955366</v>
+        <v>190.759325420591</v>
       </c>
       <c r="D111" t="n">
-        <v>182.3023753569564</v>
+        <v>182.7998269729231</v>
       </c>
       <c r="E111" t="n">
-        <v>184.3519439697266</v>
+        <v>184.2225952148438</v>
       </c>
       <c r="F111" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B112" t="n">
-        <v>184.3817888273663</v>
+        <v>180.3522971382107</v>
       </c>
       <c r="C112" t="n">
-        <v>190.759325420591</v>
+        <v>181.546218918281</v>
       </c>
       <c r="D112" t="n">
-        <v>182.7998269729231</v>
+        <v>173.6862199497409</v>
       </c>
       <c r="E112" t="n">
-        <v>184.2225952148438</v>
+        <v>177.2580413818359</v>
       </c>
       <c r="F112" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B113" t="n">
-        <v>180.3522971382107</v>
+        <v>176.7406808899958</v>
       </c>
       <c r="C113" t="n">
-        <v>181.546218918281</v>
+        <v>187.7148393068323</v>
       </c>
       <c r="D113" t="n">
-        <v>173.6862199497409</v>
+        <v>175.3875654052501</v>
       </c>
       <c r="E113" t="n">
-        <v>177.2580413818359</v>
+        <v>184.4812927246094</v>
       </c>
       <c r="F113" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B114" t="n">
-        <v>176.7406808899958</v>
+        <v>182.07353407401</v>
       </c>
       <c r="C114" t="n">
-        <v>187.7148393068323</v>
+        <v>191.6249386554261</v>
       </c>
       <c r="D114" t="n">
-        <v>175.3875654052501</v>
+        <v>181.3372749736025</v>
       </c>
       <c r="E114" t="n">
-        <v>184.4812927246094</v>
+        <v>190.7792358398438</v>
       </c>
       <c r="F114" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B115" t="n">
-        <v>182.07353407401</v>
+        <v>195.763857285561</v>
       </c>
       <c r="C115" t="n">
-        <v>191.6249386554261</v>
+        <v>200.0221877064004</v>
       </c>
       <c r="D115" t="n">
-        <v>181.3372749736025</v>
+        <v>190.3613550446578</v>
       </c>
       <c r="E115" t="n">
-        <v>190.7792358398438</v>
+        <v>198.4601440429688</v>
       </c>
       <c r="F115" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B116" t="n">
-        <v>195.763857285561</v>
+        <v>190.9384388957837</v>
       </c>
       <c r="C116" t="n">
-        <v>200.0221877064004</v>
+        <v>194.9281323797358</v>
       </c>
       <c r="D116" t="n">
-        <v>190.3613550446578</v>
+        <v>188.9585080166839</v>
       </c>
       <c r="E116" t="n">
-        <v>198.4601440429688</v>
+        <v>193.8038482666016</v>
       </c>
       <c r="F116" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B117" t="n">
-        <v>190.9384388957837</v>
+        <v>191.5254257929766</v>
       </c>
       <c r="C117" t="n">
-        <v>194.9281323797358</v>
+        <v>194.9480124543751</v>
       </c>
       <c r="D117" t="n">
-        <v>188.9585080166839</v>
+        <v>189.7146326619775</v>
       </c>
       <c r="E117" t="n">
-        <v>193.8038482666016</v>
+        <v>191.97314453125</v>
       </c>
       <c r="F117" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B118" t="n">
-        <v>191.5254410161792</v>
+        <v>189.7843086141992</v>
       </c>
       <c r="C118" t="n">
-        <v>194.9480279496185</v>
+        <v>197.6642109823198</v>
       </c>
       <c r="D118" t="n">
-        <v>189.714647741251</v>
+        <v>188.6202336806571</v>
       </c>
       <c r="E118" t="n">
-        <v>191.9731597900391</v>
+        <v>195.0574798583984</v>
       </c>
       <c r="F118" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B119" t="n">
-        <v>189.7842937679152</v>
+        <v>194.1122862760758</v>
       </c>
       <c r="C119" t="n">
-        <v>197.6641955196137</v>
+        <v>195.4753456100833</v>
       </c>
       <c r="D119" t="n">
-        <v>188.6202189254354</v>
+        <v>191.1274741765864</v>
       </c>
       <c r="E119" t="n">
-        <v>195.0574645996094</v>
+        <v>192.1025085449219</v>
       </c>
       <c r="F119" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B120" t="n">
-        <v>194.1122708576492</v>
+        <v>193.3760290806364</v>
       </c>
       <c r="C120" t="n">
-        <v>195.4753300833883</v>
+        <v>203.385096657981</v>
       </c>
       <c r="D120" t="n">
-        <v>191.1274589952447</v>
+        <v>193.2566414535633</v>
       </c>
       <c r="E120" t="n">
-        <v>192.1024932861328</v>
+        <v>200.3704376220703</v>
       </c>
       <c r="F120" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B121" t="n">
-        <v>193.3760143544918</v>
+        <v>199.7734673796906</v>
       </c>
       <c r="C121" t="n">
-        <v>203.3850811696169</v>
+        <v>201.9324948273444</v>
       </c>
       <c r="D121" t="n">
-        <v>193.2566267365104</v>
+        <v>196.3707834039569</v>
       </c>
       <c r="E121" t="n">
-        <v>200.3704223632812</v>
+        <v>201.0867919921875</v>
       </c>
       <c r="F121" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B122" t="n">
-        <v>199.7734673796906</v>
+        <v>197.5547685014358</v>
       </c>
       <c r="C122" t="n">
-        <v>201.9324948273444</v>
+        <v>202.6388992429378</v>
       </c>
       <c r="D122" t="n">
-        <v>196.3707834039569</v>
+        <v>194.8783844557345</v>
       </c>
       <c r="E122" t="n">
-        <v>201.0867919921875</v>
+        <v>197.7835998535156</v>
       </c>
       <c r="F122" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B123" t="n">
-        <v>197.5547532603008</v>
+        <v>196.2613420240266</v>
       </c>
       <c r="C123" t="n">
-        <v>202.6388836095676</v>
+        <v>198.5596601232727</v>
       </c>
       <c r="D123" t="n">
-        <v>194.8783694210796</v>
+        <v>189.6350706142157</v>
       </c>
       <c r="E123" t="n">
-        <v>197.7835845947266</v>
+        <v>193.9232482910156</v>
       </c>
       <c r="F123" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B124" t="n">
-        <v>196.2613420240266</v>
+        <v>195.4056984962331</v>
       </c>
       <c r="C124" t="n">
-        <v>198.5596601232727</v>
+        <v>198.5397604024679</v>
       </c>
       <c r="D124" t="n">
-        <v>189.6350706142157</v>
+        <v>190.3215677955559</v>
       </c>
       <c r="E124" t="n">
-        <v>193.9232482910156</v>
+        <v>193.1472015380859</v>
       </c>
       <c r="F124" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B125" t="n">
-        <v>195.4056830590209</v>
+        <v>193.1471819093573</v>
       </c>
       <c r="C125" t="n">
-        <v>198.5397447176623</v>
+        <v>203.8228548323795</v>
       </c>
       <c r="D125" t="n">
-        <v>190.3215527599943</v>
+        <v>192.1721324296864</v>
       </c>
       <c r="E125" t="n">
-        <v>193.1471862792969</v>
+        <v>198.2711029052734</v>
       </c>
       <c r="F125" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B126" t="n">
-        <v>193.1471819093573</v>
+        <v>198.7188368100057</v>
       </c>
       <c r="C126" t="n">
-        <v>203.8228548323795</v>
+        <v>199.9824115216952</v>
       </c>
       <c r="D126" t="n">
-        <v>192.1721324296864</v>
+        <v>190.7792408422143</v>
       </c>
       <c r="E126" t="n">
-        <v>198.2711029052734</v>
+        <v>191.8537750244141</v>
       </c>
       <c r="F126" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B127" t="n">
-        <v>198.7188210052147</v>
+        <v>194.1620087776625</v>
       </c>
       <c r="C127" t="n">
-        <v>199.9823956164078</v>
+        <v>197.6244015258386</v>
       </c>
       <c r="D127" t="n">
-        <v>190.7792256688866</v>
+        <v>194.1620087776625</v>
       </c>
       <c r="E127" t="n">
-        <v>191.853759765625</v>
+        <v>197.3358612060547</v>
       </c>
       <c r="F127" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B128" t="n">
-        <v>194.1620237910367</v>
+        <v>197.2164841210229</v>
       </c>
       <c r="C128" t="n">
-        <v>197.6244168069387</v>
+        <v>201.3554271697534</v>
       </c>
       <c r="D128" t="n">
-        <v>194.1620237910367</v>
+        <v>193.4655660342646</v>
       </c>
       <c r="E128" t="n">
-        <v>197.3358764648438</v>
+        <v>194.3212127685547</v>
       </c>
       <c r="F128" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B129" t="n">
-        <v>197.2164841210229</v>
+        <v>192.4208813209107</v>
       </c>
       <c r="C129" t="n">
-        <v>201.3554271697534</v>
+        <v>195.1569590889159</v>
       </c>
       <c r="D129" t="n">
-        <v>193.4655660342646</v>
+        <v>191.6647343849253</v>
       </c>
       <c r="E129" t="n">
-        <v>194.3212127685547</v>
+        <v>193.3561248779297</v>
       </c>
       <c r="F129" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B130" t="n">
-        <v>192.4208813209107</v>
+        <v>194.5997914321279</v>
       </c>
       <c r="C130" t="n">
-        <v>195.1569590889159</v>
+        <v>199.3854376268052</v>
       </c>
       <c r="D130" t="n">
-        <v>191.6647343849253</v>
+        <v>192.3213915946813</v>
       </c>
       <c r="E130" t="n">
-        <v>193.3561248779297</v>
+        <v>194.0028381347656</v>
       </c>
       <c r="F130" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B131" t="n">
-        <v>194.5997914321279</v>
+        <v>192.2318417698426</v>
       </c>
       <c r="C131" t="n">
-        <v>199.3854376268052</v>
+        <v>194.6793790179939</v>
       </c>
       <c r="D131" t="n">
-        <v>192.3213915946813</v>
+        <v>189.0380863676492</v>
       </c>
       <c r="E131" t="n">
-        <v>194.0028381347656</v>
+        <v>194.3908538818359</v>
       </c>
       <c r="F131" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B132" t="n">
-        <v>192.2318417698426</v>
+        <v>196.0921979891633</v>
       </c>
       <c r="C132" t="n">
-        <v>194.6793790179939</v>
+        <v>197.0473445217343</v>
       </c>
       <c r="D132" t="n">
-        <v>189.0380863676492</v>
+        <v>191.0279705387624</v>
       </c>
       <c r="E132" t="n">
-        <v>194.3908538818359</v>
+        <v>194.1918640136719</v>
       </c>
       <c r="F132" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B133" t="n">
-        <v>196.0921979891633</v>
+        <v>191.1672689357976</v>
       </c>
       <c r="C133" t="n">
-        <v>197.0473445217343</v>
+        <v>191.1672689357976</v>
       </c>
       <c r="D133" t="n">
-        <v>191.0279705387624</v>
+        <v>181.3671296009816</v>
       </c>
       <c r="E133" t="n">
-        <v>194.1918640136719</v>
+        <v>182.0934448242188</v>
       </c>
       <c r="F133" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B134" t="n">
-        <v>191.1672689357976</v>
+        <v>184.7598589955983</v>
       </c>
       <c r="C134" t="n">
-        <v>191.1672689357976</v>
+        <v>186.4413055109877</v>
       </c>
       <c r="D134" t="n">
-        <v>181.3671296009816</v>
+        <v>178.9394847287185</v>
       </c>
       <c r="E134" t="n">
-        <v>182.0934448242188</v>
+        <v>181.0388031005859</v>
       </c>
       <c r="F134" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B135" t="n">
-        <v>184.7598589955983</v>
+        <v>180.2627525283908</v>
       </c>
       <c r="C135" t="n">
-        <v>186.4413055109877</v>
+        <v>186.5209173345002</v>
       </c>
       <c r="D135" t="n">
-        <v>178.9394847287185</v>
+        <v>178.621111875675</v>
       </c>
       <c r="E135" t="n">
-        <v>181.0388031005859</v>
+        <v>184.7001800537109</v>
       </c>
       <c r="F135" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B136" t="n">
-        <v>180.2627525283908</v>
+        <v>183.0684804863479</v>
       </c>
       <c r="C136" t="n">
-        <v>186.5209173345002</v>
+        <v>183.1779242069437</v>
       </c>
       <c r="D136" t="n">
-        <v>178.621111875675</v>
+        <v>177.9147120728387</v>
       </c>
       <c r="E136" t="n">
-        <v>184.7001800537109</v>
+        <v>178.4022216796875</v>
       </c>
       <c r="F136" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B137" t="n">
-        <v>183.0684648284524</v>
+        <v>179.1882128832653</v>
       </c>
       <c r="C137" t="n">
-        <v>183.1779085396875</v>
+        <v>185.4463617882801</v>
       </c>
       <c r="D137" t="n">
-        <v>177.9146968557465</v>
+        <v>178.670841239089</v>
       </c>
       <c r="E137" t="n">
-        <v>178.4022064208984</v>
+        <v>184.0932464599609</v>
       </c>
       <c r="F137" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B138" t="n">
-        <v>179.1882128832653</v>
+        <v>183.9639017861065</v>
       </c>
       <c r="C138" t="n">
-        <v>185.4463617882801</v>
+        <v>187.5456821599193</v>
       </c>
       <c r="D138" t="n">
-        <v>178.670841239089</v>
+        <v>181.3870178074254</v>
       </c>
       <c r="E138" t="n">
-        <v>184.0932464599609</v>
+        <v>185.7249450683594</v>
       </c>
       <c r="F138" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B139" t="n">
-        <v>183.9639169002118</v>
+        <v>185.904046779924</v>
       </c>
       <c r="C139" t="n">
-        <v>187.5456975682965</v>
+        <v>188.0232529761809</v>
       </c>
       <c r="D139" t="n">
-        <v>181.3870327098191</v>
+        <v>182.0834758824893</v>
       </c>
       <c r="E139" t="n">
-        <v>185.7249603271484</v>
+        <v>185.2971343994141</v>
       </c>
       <c r="F139" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B140" t="n">
-        <v>185.904046779924</v>
+        <v>184.3618889959713</v>
       </c>
       <c r="C140" t="n">
-        <v>188.0232529761809</v>
+        <v>186.6303448779838</v>
       </c>
       <c r="D140" t="n">
-        <v>182.0834758824893</v>
+        <v>180.6607209397324</v>
       </c>
       <c r="E140" t="n">
-        <v>185.2971343994141</v>
+        <v>186.2323608398438</v>
       </c>
       <c r="F140" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B141" t="n">
-        <v>184.3619041015049</v>
+        <v>186.5507427928755</v>
       </c>
       <c r="C141" t="n">
-        <v>186.6303601693813</v>
+        <v>187.187502054347</v>
       </c>
       <c r="D141" t="n">
-        <v>180.6607357420139</v>
+        <v>182.670493415399</v>
       </c>
       <c r="E141" t="n">
-        <v>186.2323760986328</v>
+        <v>184.0932464599609</v>
       </c>
       <c r="F141" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B142" t="n">
-        <v>186.5507427928755</v>
+        <v>184.0136681409698</v>
       </c>
       <c r="C142" t="n">
-        <v>187.187502054347</v>
+        <v>185.635420952666</v>
       </c>
       <c r="D142" t="n">
-        <v>182.670493415399</v>
+        <v>181.098508861202</v>
       </c>
       <c r="E142" t="n">
-        <v>184.0932464599609</v>
+        <v>182.0337524414062</v>
       </c>
       <c r="F142" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B143" t="n">
-        <v>184.0136681409698</v>
+        <v>185.5558168284281</v>
       </c>
       <c r="C143" t="n">
-        <v>185.635420952666</v>
+        <v>185.8244541652842</v>
       </c>
       <c r="D143" t="n">
-        <v>181.098508861202</v>
+        <v>174.890087161354</v>
       </c>
       <c r="E143" t="n">
-        <v>182.0337524414062</v>
+        <v>175.4770965576172</v>
       </c>
       <c r="F143" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,25 +4161,25 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B144" t="n">
-        <v>185.5558006932337</v>
+        <v>172.7242064751902</v>
       </c>
       <c r="C144" t="n">
-        <v>185.8244380067301</v>
+        <v>173.8413183878644</v>
       </c>
       <c r="D144" t="n">
-        <v>174.890071953609</v>
+        <v>166.6897779521393</v>
       </c>
       <c r="E144" t="n">
-        <v>175.4770812988281</v>
+        <v>170.4101867675781</v>
       </c>
       <c r="F144" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4187,25 +4187,25 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B145" t="n">
-        <v>172.7242064751902</v>
+        <v>170.8191086768984</v>
       </c>
       <c r="C145" t="n">
-        <v>173.8413183878644</v>
+        <v>170.8191086768984</v>
       </c>
       <c r="D145" t="n">
-        <v>166.6897779521393</v>
+        <v>163.0990440067395</v>
       </c>
       <c r="E145" t="n">
-        <v>170.4101867675781</v>
+        <v>164.5353393554688</v>
       </c>
       <c r="F145" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G145" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B146" t="n">
-        <v>170.8191086768984</v>
+        <v>166.619956593861</v>
       </c>
       <c r="C146" t="n">
-        <v>170.8191086768984</v>
+        <v>172.9536002909039</v>
       </c>
       <c r="D146" t="n">
-        <v>163.0990440067395</v>
+        <v>165.3432529892489</v>
       </c>
       <c r="E146" t="n">
-        <v>164.5353393554688</v>
+        <v>172.3751068115234</v>
       </c>
       <c r="F146" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B147" t="n">
-        <v>166.619956593861</v>
+        <v>174.7589572577855</v>
       </c>
       <c r="C147" t="n">
-        <v>172.9536002909039</v>
+        <v>177.043055331393</v>
       </c>
       <c r="D147" t="n">
-        <v>165.3432529892489</v>
+        <v>170.0610756845212</v>
       </c>
       <c r="E147" t="n">
-        <v>172.3751068115234</v>
+        <v>170.8689880371094</v>
       </c>
       <c r="F147" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B148" t="n">
-        <v>174.7589572577855</v>
+        <v>173.771503335319</v>
       </c>
       <c r="C148" t="n">
-        <v>177.043055331393</v>
+        <v>179.157595924108</v>
       </c>
       <c r="D148" t="n">
-        <v>170.0610756845212</v>
+        <v>172.4349565756613</v>
       </c>
       <c r="E148" t="n">
-        <v>170.8689880371094</v>
+        <v>177.1428070068359</v>
       </c>
       <c r="F148" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B149" t="n">
-        <v>173.771503335319</v>
+        <v>183.5263211162543</v>
       </c>
       <c r="C149" t="n">
-        <v>179.157595924108</v>
+        <v>184.0749082721881</v>
       </c>
       <c r="D149" t="n">
-        <v>172.4349565756613</v>
+        <v>178.110307097372</v>
       </c>
       <c r="E149" t="n">
-        <v>177.1428070068359</v>
+        <v>180.7534790039062</v>
       </c>
       <c r="F149" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B150" t="n">
-        <v>183.5263211162543</v>
+        <v>184.9526358387744</v>
       </c>
       <c r="C150" t="n">
-        <v>184.0749082721881</v>
+        <v>187.4960743570736</v>
       </c>
       <c r="D150" t="n">
-        <v>178.110307097372</v>
+        <v>180.5639689511464</v>
       </c>
       <c r="E150" t="n">
-        <v>180.7534790039062</v>
+        <v>181.6711120605469</v>
       </c>
       <c r="F150" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="n">
-        <v>184.9526358387744</v>
+        <v>182.0301825754578</v>
       </c>
       <c r="C151" t="n">
-        <v>187.4960743570736</v>
+        <v>188.5134493521179</v>
       </c>
       <c r="D151" t="n">
-        <v>180.5639689511464</v>
+        <v>181.6511559551952</v>
       </c>
       <c r="E151" t="n">
-        <v>181.6711120605469</v>
+        <v>185.7904815673828</v>
       </c>
       <c r="F151" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B152" t="n">
-        <v>182.0301825754578</v>
+        <v>186.1196295624439</v>
       </c>
       <c r="C152" t="n">
-        <v>188.5134493521179</v>
+        <v>193.0617034585096</v>
       </c>
       <c r="D152" t="n">
-        <v>181.6511559551952</v>
+        <v>183.6260654751631</v>
       </c>
       <c r="E152" t="n">
-        <v>185.7904815673828</v>
+        <v>186.6283111572266</v>
       </c>
       <c r="F152" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B153" t="n">
-        <v>186.1196295624439</v>
+        <v>187.7155141554787</v>
       </c>
       <c r="C153" t="n">
-        <v>193.0617034585096</v>
+        <v>190.6579169337777</v>
       </c>
       <c r="D153" t="n">
-        <v>183.6260654751631</v>
+        <v>186.5485279099638</v>
       </c>
       <c r="E153" t="n">
-        <v>186.6283111572266</v>
+        <v>189.3114013671875</v>
       </c>
       <c r="F153" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B154" t="n">
-        <v>187.7155141554787</v>
+        <v>177.1028943275062</v>
       </c>
       <c r="C154" t="n">
-        <v>190.6579169337777</v>
+        <v>178.4095194817015</v>
       </c>
       <c r="D154" t="n">
-        <v>186.5485279099638</v>
+        <v>170.2106794975899</v>
       </c>
       <c r="E154" t="n">
-        <v>189.3114013671875</v>
+        <v>172.8538665771484</v>
       </c>
       <c r="F154" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="n">
-        <v>177.1028943275062</v>
+        <v>175.1678853418476</v>
       </c>
       <c r="C155" t="n">
-        <v>178.4095194817015</v>
+        <v>177.9906017183548</v>
       </c>
       <c r="D155" t="n">
-        <v>170.2106794975899</v>
+        <v>173.9510248482436</v>
       </c>
       <c r="E155" t="n">
-        <v>172.8538665771484</v>
+        <v>177.7013549804688</v>
       </c>
       <c r="F155" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="n">
-        <v>175.1678853418476</v>
+        <v>177.8011004808986</v>
       </c>
       <c r="C156" t="n">
-        <v>177.9906017183548</v>
+        <v>183.81557625727</v>
       </c>
       <c r="D156" t="n">
-        <v>173.9510248482436</v>
+        <v>177.0530312030464</v>
       </c>
       <c r="E156" t="n">
-        <v>177.7013549804688</v>
+        <v>179.7161560058594</v>
       </c>
       <c r="F156" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B157" t="n">
-        <v>177.8011004808986</v>
+        <v>181.960353565993</v>
       </c>
       <c r="C157" t="n">
-        <v>183.81557625727</v>
+        <v>183.9452360835181</v>
       </c>
       <c r="D157" t="n">
-        <v>177.0530312030464</v>
+        <v>180.8532257080078</v>
       </c>
       <c r="E157" t="n">
-        <v>179.7161560058594</v>
+        <v>180.8532257080078</v>
       </c>
       <c r="F157" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="n">
-        <v>181.960353565993</v>
+        <v>178.7386749127982</v>
       </c>
       <c r="C158" t="n">
-        <v>183.9452360835181</v>
+        <v>181.3120349373997</v>
       </c>
       <c r="D158" t="n">
-        <v>180.8532257080078</v>
+        <v>176.8934465767579</v>
       </c>
       <c r="E158" t="n">
-        <v>180.8532257080078</v>
+        <v>180.7534790039062</v>
       </c>
       <c r="F158" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B159" t="n">
-        <v>178.7386749127982</v>
+        <v>177.8409939014207</v>
       </c>
       <c r="C159" t="n">
-        <v>181.3120349373997</v>
+        <v>178.2299892905901</v>
       </c>
       <c r="D159" t="n">
-        <v>176.8934465767579</v>
+        <v>172.5546349879463</v>
       </c>
       <c r="E159" t="n">
-        <v>180.7534790039062</v>
+        <v>176.0755462646484</v>
       </c>
       <c r="F159" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="n">
-        <v>177.8409939014207</v>
+        <v>181.7209929763659</v>
       </c>
       <c r="C160" t="n">
-        <v>178.2299892905901</v>
+        <v>185.5610728373815</v>
       </c>
       <c r="D160" t="n">
-        <v>172.5546349879463</v>
+        <v>178.2898460906057</v>
       </c>
       <c r="E160" t="n">
-        <v>176.0755462646484</v>
+        <v>183.3468017578125</v>
       </c>
       <c r="F160" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="n">
-        <v>181.7209929763659</v>
+        <v>183.7657043950053</v>
       </c>
       <c r="C161" t="n">
-        <v>185.5610728373815</v>
+        <v>189.8200700827938</v>
       </c>
       <c r="D161" t="n">
-        <v>178.2898460906057</v>
+        <v>183.4963952122052</v>
       </c>
       <c r="E161" t="n">
-        <v>183.3468017578125</v>
+        <v>185.0025024414062</v>
       </c>
       <c r="F161" t="n">
-        <v>12324400</v>
+        <v>8444700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B162" t="n">
-        <v>183.7657043950053</v>
+        <v>185.0723410364737</v>
       </c>
       <c r="C162" t="n">
-        <v>189.8200700827938</v>
+        <v>186.9076006654211</v>
       </c>
       <c r="D162" t="n">
-        <v>183.4963952122052</v>
+        <v>180.6337997307826</v>
       </c>
       <c r="E162" t="n">
-        <v>185.0025024414062</v>
+        <v>186.5086364746094</v>
       </c>
       <c r="F162" t="n">
-        <v>8444700</v>
+        <v>9740800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="n">
-        <v>185.0723410364737</v>
+        <v>185.0424114227766</v>
       </c>
       <c r="C163" t="n">
-        <v>186.9076006654211</v>
+        <v>186.6183457810002</v>
       </c>
       <c r="D163" t="n">
-        <v>180.6337997307826</v>
+        <v>179.117700608299</v>
       </c>
       <c r="E163" t="n">
-        <v>186.5086364746094</v>
+        <v>180.7235565185547</v>
       </c>
       <c r="F163" t="n">
-        <v>9740800</v>
+        <v>11303400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B164" t="n">
-        <v>185.0424114227766</v>
+        <v>184.124779650284</v>
       </c>
       <c r="C164" t="n">
-        <v>186.6183457810002</v>
+        <v>188.0945294450444</v>
       </c>
       <c r="D164" t="n">
-        <v>179.117700608299</v>
+        <v>183.5263181771209</v>
       </c>
       <c r="E164" t="n">
-        <v>180.7235565185547</v>
+        <v>185.8602905273438</v>
       </c>
       <c r="F164" t="n">
-        <v>11303400</v>
+        <v>13955100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B165" t="n">
-        <v>184.124779650284</v>
+        <v>179.2174384093688</v>
       </c>
       <c r="C165" t="n">
-        <v>188.0945294450444</v>
+        <v>181.40180307799</v>
       </c>
       <c r="D165" t="n">
-        <v>183.5263181771209</v>
+        <v>176.424658688263</v>
       </c>
       <c r="E165" t="n">
-        <v>185.8602905273438</v>
+        <v>181.3519439697266</v>
       </c>
       <c r="F165" t="n">
-        <v>13955100</v>
+        <v>15123900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B166" t="n">
-        <v>179.2174384093688</v>
+        <v>179.4468492598589</v>
       </c>
       <c r="C166" t="n">
-        <v>181.40180307799</v>
+        <v>182.0301779962749</v>
       </c>
       <c r="D166" t="n">
-        <v>176.424658688263</v>
+        <v>175.8561108937732</v>
       </c>
       <c r="E166" t="n">
-        <v>181.3519439697266</v>
+        <v>177.0330810546875</v>
       </c>
       <c r="F166" t="n">
-        <v>15123900</v>
+        <v>11145000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B167" t="n">
-        <v>179.4468492598589</v>
+        <v>177.122851210841</v>
       </c>
       <c r="C167" t="n">
-        <v>182.0301779962749</v>
+        <v>177.122851210841</v>
       </c>
       <c r="D167" t="n">
-        <v>175.8561108937732</v>
+        <v>170.1408715639692</v>
       </c>
       <c r="E167" t="n">
-        <v>177.0330810546875</v>
+        <v>170.8689880371094</v>
       </c>
       <c r="F167" t="n">
-        <v>11145000</v>
+        <v>10214000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B168" t="n">
-        <v>177.122851210841</v>
+        <v>169.3429302825834</v>
       </c>
       <c r="C168" t="n">
-        <v>177.122851210841</v>
+        <v>169.3429302825834</v>
       </c>
       <c r="D168" t="n">
-        <v>170.1408715639692</v>
+        <v>164.3258803430835</v>
       </c>
       <c r="E168" t="n">
-        <v>170.8689880371094</v>
+        <v>165.4130706787109</v>
       </c>
       <c r="F168" t="n">
-        <v>10214000</v>
+        <v>11951900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B169" t="n">
-        <v>169.3429302825834</v>
+        <v>165.5726557549663</v>
       </c>
       <c r="C169" t="n">
-        <v>169.3429302825834</v>
+        <v>168.914037726981</v>
       </c>
       <c r="D169" t="n">
-        <v>164.3258803430835</v>
+        <v>163.9069567673868</v>
       </c>
       <c r="E169" t="n">
-        <v>165.4130706787109</v>
+        <v>167.1485900878906</v>
       </c>
       <c r="F169" t="n">
-        <v>11951900</v>
+        <v>9749400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B170" t="n">
-        <v>165.5726557549663</v>
+        <v>168.8142960637846</v>
       </c>
       <c r="C170" t="n">
-        <v>168.914037726981</v>
+        <v>175.5169978399782</v>
       </c>
       <c r="D170" t="n">
-        <v>163.9069567673868</v>
+        <v>168.5649396441926</v>
       </c>
       <c r="E170" t="n">
-        <v>167.1485900878906</v>
+        <v>173.0633239746094</v>
       </c>
       <c r="F170" t="n">
-        <v>9749400</v>
+        <v>13883400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B171" t="n">
-        <v>168.8142960637846</v>
+        <v>172.444927913041</v>
       </c>
       <c r="C171" t="n">
-        <v>175.5169978399782</v>
+        <v>180.3146160429799</v>
       </c>
       <c r="D171" t="n">
-        <v>168.5649396441926</v>
+        <v>171.3577375574589</v>
       </c>
       <c r="E171" t="n">
-        <v>173.0633239746094</v>
+        <v>179.0179595947266</v>
       </c>
       <c r="F171" t="n">
-        <v>13883400</v>
+        <v>13671200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B172" t="n">
-        <v>172.444927913041</v>
+        <v>184.5237517741468</v>
       </c>
       <c r="C172" t="n">
-        <v>180.3146160429799</v>
+        <v>186.9574728813163</v>
       </c>
       <c r="D172" t="n">
-        <v>171.3577375574589</v>
+        <v>178.3496843472311</v>
       </c>
       <c r="E172" t="n">
-        <v>179.0179595947266</v>
+        <v>178.9581146240234</v>
       </c>
       <c r="F172" t="n">
-        <v>13671200</v>
+        <v>17510800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B173" t="n">
-        <v>184.5237517741468</v>
+        <v>175.5868068261091</v>
       </c>
       <c r="C173" t="n">
-        <v>186.9574728813163</v>
+        <v>179.8458186639284</v>
       </c>
       <c r="D173" t="n">
-        <v>178.3496843472311</v>
+        <v>172.8937605828528</v>
       </c>
       <c r="E173" t="n">
-        <v>178.9581146240234</v>
+        <v>179.6363677978516</v>
       </c>
       <c r="F173" t="n">
-        <v>17510800</v>
+        <v>13025300</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B174" t="n">
-        <v>175.5868068261091</v>
+        <v>174.9285262709738</v>
       </c>
       <c r="C174" t="n">
-        <v>179.8458186639284</v>
+        <v>176.8834721439062</v>
       </c>
       <c r="D174" t="n">
-        <v>172.8937605828528</v>
+        <v>171.547253715491</v>
       </c>
       <c r="E174" t="n">
-        <v>179.6363677978516</v>
+        <v>175.8561248779297</v>
       </c>
       <c r="F174" t="n">
-        <v>13025300</v>
+        <v>10949100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B175" t="n">
-        <v>174.9285262709738</v>
+        <v>179.3770264534069</v>
       </c>
       <c r="C175" t="n">
-        <v>176.8834721439062</v>
+        <v>182.8780002490095</v>
       </c>
       <c r="D175" t="n">
-        <v>171.547253715491</v>
+        <v>177.222583382191</v>
       </c>
       <c r="E175" t="n">
-        <v>175.8561248779297</v>
+        <v>179.6064453125</v>
       </c>
       <c r="F175" t="n">
-        <v>10949100</v>
+        <v>10176700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B176" t="n">
-        <v>179.3770264534069</v>
+        <v>177.9706522299692</v>
       </c>
       <c r="C176" t="n">
-        <v>182.8780002490095</v>
+        <v>181.890542966362</v>
       </c>
       <c r="D176" t="n">
-        <v>177.222583382191</v>
+        <v>177.222582989082</v>
       </c>
       <c r="E176" t="n">
-        <v>179.6064453125</v>
+        <v>178.6189880371094</v>
       </c>
       <c r="F176" t="n">
-        <v>10176700</v>
+        <v>13617200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B177" t="n">
-        <v>177.9706522299692</v>
+        <v>177.5417683468011</v>
       </c>
       <c r="C177" t="n">
-        <v>181.890542966362</v>
+        <v>183.4465264564886</v>
       </c>
       <c r="D177" t="n">
-        <v>177.222582989082</v>
+        <v>176.4346252500155</v>
       </c>
       <c r="E177" t="n">
-        <v>178.6189880371094</v>
+        <v>177.0530242919922</v>
       </c>
       <c r="F177" t="n">
-        <v>13617200</v>
+        <v>18524900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B178" t="n">
-        <v>177.5417683468011</v>
+        <v>177.9706529497301</v>
       </c>
       <c r="C178" t="n">
-        <v>183.4465264564886</v>
+        <v>182.0102299107596</v>
       </c>
       <c r="D178" t="n">
-        <v>176.4346252500155</v>
+        <v>171.2081082023211</v>
       </c>
       <c r="E178" t="n">
-        <v>177.0530242919922</v>
+        <v>175.7164764404297</v>
       </c>
       <c r="F178" t="n">
-        <v>18524900</v>
+        <v>22559400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B179" t="n">
-        <v>177.9706529497301</v>
+        <v>179.7760043356117</v>
       </c>
       <c r="C179" t="n">
-        <v>182.0102299107596</v>
+        <v>193.6402147597182</v>
       </c>
       <c r="D179" t="n">
-        <v>171.2081082023211</v>
+        <v>179.5565694754165</v>
       </c>
       <c r="E179" t="n">
-        <v>175.7164764404297</v>
+        <v>190.6080474853516</v>
       </c>
       <c r="F179" t="n">
-        <v>22559400</v>
+        <v>33998900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B180" t="n">
-        <v>179.7760043356117</v>
+        <v>198.2383502861678</v>
       </c>
       <c r="C180" t="n">
-        <v>193.6402147597182</v>
+        <v>210.7959357157644</v>
       </c>
       <c r="D180" t="n">
-        <v>179.5565694754165</v>
+        <v>197.69974712537</v>
       </c>
       <c r="E180" t="n">
-        <v>190.6080474853516</v>
+        <v>209.0604248046875</v>
       </c>
       <c r="F180" t="n">
-        <v>33998900</v>
+        <v>27594800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B181" t="n">
-        <v>198.2383502861678</v>
+        <v>200.5025120636997</v>
       </c>
       <c r="C181" t="n">
-        <v>210.7959357157644</v>
+        <v>203.8638316949671</v>
       </c>
       <c r="D181" t="n">
-        <v>197.69974712537</v>
+        <v>195.2560433089883</v>
       </c>
       <c r="E181" t="n">
-        <v>209.0604248046875</v>
+        <v>200.3229675292969</v>
       </c>
       <c r="F181" t="n">
-        <v>27594800</v>
+        <v>19216600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B182" t="n">
-        <v>200.5025120636997</v>
+        <v>196.7621671181547</v>
       </c>
       <c r="C182" t="n">
-        <v>203.8638316949671</v>
+        <v>197.1711000779736</v>
       </c>
       <c r="D182" t="n">
-        <v>195.2560433089883</v>
+        <v>189.2415690076627</v>
       </c>
       <c r="E182" t="n">
-        <v>200.3229675292969</v>
+        <v>190.1193084716797</v>
       </c>
       <c r="F182" t="n">
-        <v>19216600</v>
+        <v>14154400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B183" t="n">
-        <v>196.7621671181547</v>
+        <v>197.3007734437849</v>
       </c>
       <c r="C183" t="n">
-        <v>197.1711000779736</v>
+        <v>197.5800514196224</v>
       </c>
       <c r="D183" t="n">
-        <v>189.2415690076627</v>
+        <v>185.6308959064055</v>
       </c>
       <c r="E183" t="n">
-        <v>190.1193084716797</v>
+        <v>188.2640991210938</v>
       </c>
       <c r="F183" t="n">
-        <v>14154400</v>
+        <v>14453600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B184" t="n">
-        <v>197.3007734437849</v>
+        <v>189.311394256529</v>
       </c>
       <c r="C184" t="n">
-        <v>197.5800514196224</v>
+        <v>192.0144092856922</v>
       </c>
       <c r="D184" t="n">
-        <v>185.6308959064055</v>
+        <v>184.3541874840329</v>
       </c>
       <c r="E184" t="n">
-        <v>188.2640991210938</v>
+        <v>185.1820526123047</v>
       </c>
       <c r="F184" t="n">
-        <v>14453600</v>
+        <v>13183900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B185" t="n">
-        <v>189.311394256529</v>
+        <v>183.4365624142317</v>
       </c>
       <c r="C185" t="n">
-        <v>192.0144092856922</v>
+        <v>184.543705539598</v>
       </c>
       <c r="D185" t="n">
-        <v>184.3541874840329</v>
+        <v>181.2422289387738</v>
       </c>
       <c r="E185" t="n">
-        <v>185.1820526123047</v>
+        <v>182.0800628662109</v>
       </c>
       <c r="F185" t="n">
-        <v>13183900</v>
+        <v>11177800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B186" t="n">
-        <v>183.4365624142317</v>
+        <v>179.0379159792888</v>
       </c>
       <c r="C186" t="n">
-        <v>184.543705539598</v>
+        <v>181.9903027945282</v>
       </c>
       <c r="D186" t="n">
-        <v>181.2422289387738</v>
+        <v>171.1183533610167</v>
       </c>
       <c r="E186" t="n">
-        <v>182.0800628662109</v>
+        <v>174.8986053466797</v>
       </c>
       <c r="F186" t="n">
-        <v>11177800</v>
+        <v>15427800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B187" t="n">
-        <v>179.0379159792888</v>
+        <v>170.1608274234686</v>
       </c>
       <c r="C187" t="n">
-        <v>181.9903027945282</v>
+        <v>175.0781287299737</v>
       </c>
       <c r="D187" t="n">
-        <v>171.1183533610167</v>
+        <v>169.59228747941</v>
       </c>
       <c r="E187" t="n">
-        <v>174.8986053466797</v>
+        <v>170.4799957275391</v>
       </c>
       <c r="F187" t="n">
-        <v>15427800</v>
+        <v>10820500</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B188" t="n">
-        <v>170.1608274234686</v>
+        <v>168.2700042724609</v>
       </c>
       <c r="C188" t="n">
-        <v>175.0781287299737</v>
+        <v>168.9799957275391</v>
       </c>
       <c r="D188" t="n">
-        <v>169.59228747941</v>
+        <v>163.3099975585938</v>
       </c>
       <c r="E188" t="n">
-        <v>170.4799957275391</v>
+        <v>166.4499969482422</v>
       </c>
       <c r="F188" t="n">
-        <v>10820500</v>
+        <v>16666000</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5331,25 +5331,25 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B189" t="n">
-        <v>168.2700042724609</v>
+        <v>164.7400054931641</v>
       </c>
       <c r="C189" t="n">
-        <v>168.9799957275391</v>
+        <v>166.5399932861328</v>
       </c>
       <c r="D189" t="n">
-        <v>163.3099975585938</v>
+        <v>161.3999938964844</v>
       </c>
       <c r="E189" t="n">
-        <v>166.4499969482422</v>
+        <v>165.8899993896484</v>
       </c>
       <c r="F189" t="n">
-        <v>16666000</v>
+        <v>13589400</v>
       </c>
       <c r="G189" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B190" t="n">
-        <v>164.7400054931641</v>
+        <v>166.0299987792969</v>
       </c>
       <c r="C190" t="n">
-        <v>166.5399932861328</v>
+        <v>169.9499969482422</v>
       </c>
       <c r="D190" t="n">
-        <v>161.3999938964844</v>
+        <v>164.1699981689453</v>
       </c>
       <c r="E190" t="n">
-        <v>165.8899993896484</v>
+        <v>164.5500030517578</v>
       </c>
       <c r="F190" t="n">
-        <v>13589400</v>
+        <v>13541800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B191" t="n">
-        <v>166.0299987792969</v>
+        <v>164.0599975585938</v>
       </c>
       <c r="C191" t="n">
-        <v>169.9499969482422</v>
+        <v>166.3000030517578</v>
       </c>
       <c r="D191" t="n">
-        <v>164.1699981689453</v>
+        <v>160.5</v>
       </c>
       <c r="E191" t="n">
-        <v>164.5500030517578</v>
+        <v>161.7100067138672</v>
       </c>
       <c r="F191" t="n">
-        <v>13541800</v>
+        <v>16385300</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B192" t="n">
-        <v>164.0599975585938</v>
+        <v>160.25</v>
       </c>
       <c r="C192" t="n">
-        <v>166.3000030517578</v>
+        <v>161.4299926757812</v>
       </c>
       <c r="D192" t="n">
-        <v>160.5</v>
+        <v>154.2299957275391</v>
       </c>
       <c r="E192" t="n">
-        <v>161.7100067138672</v>
+        <v>155.0200042724609</v>
       </c>
       <c r="F192" t="n">
-        <v>16385300</v>
+        <v>19986200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B193" t="n">
-        <v>160.25</v>
+        <v>152.7299957275391</v>
       </c>
       <c r="C193" t="n">
-        <v>161.4299926757812</v>
+        <v>154.4700012207031</v>
       </c>
       <c r="D193" t="n">
-        <v>154.2299957275391</v>
+        <v>149.8000030517578</v>
       </c>
       <c r="E193" t="n">
-        <v>155.0200042724609</v>
+        <v>151.7799987792969</v>
       </c>
       <c r="F193" t="n">
-        <v>19986200</v>
+        <v>57940800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B194" t="n">
-        <v>152.7299957275391</v>
+        <v>150.1600036621094</v>
       </c>
       <c r="C194" t="n">
-        <v>154.4700012207031</v>
+        <v>153.8699951171875</v>
       </c>
       <c r="D194" t="n">
-        <v>149.8000030517578</v>
+        <v>146.3200073242188</v>
       </c>
       <c r="E194" t="n">
-        <v>151.7799987792969</v>
+        <v>150.1199951171875</v>
       </c>
       <c r="F194" t="n">
-        <v>57940800</v>
+        <v>20502800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B195" t="n">
-        <v>150.1600036621094</v>
+        <v>151.6499938964844</v>
       </c>
       <c r="C195" t="n">
-        <v>153.8699951171875</v>
+        <v>155.1799926757812</v>
       </c>
       <c r="D195" t="n">
-        <v>146.3200073242188</v>
+        <v>150.8500061035156</v>
       </c>
       <c r="E195" t="n">
-        <v>150.1199951171875</v>
+        <v>153.4199981689453</v>
       </c>
       <c r="F195" t="n">
-        <v>20502800</v>
+        <v>20720700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B196" t="n">
-        <v>151.6499938964844</v>
+        <v>151.8099975585938</v>
       </c>
       <c r="C196" t="n">
-        <v>155.1799926757812</v>
+        <v>157.0599975585938</v>
       </c>
       <c r="D196" t="n">
-        <v>150.8500061035156</v>
+        <v>150.3999938964844</v>
       </c>
       <c r="E196" t="n">
-        <v>153.4199981689453</v>
+        <v>152.7599945068359</v>
       </c>
       <c r="F196" t="n">
-        <v>20720700</v>
+        <v>13146800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B197" t="n">
-        <v>151.8099975585938</v>
+        <v>150.0099945068359</v>
       </c>
       <c r="C197" t="n">
-        <v>157.0599975585938</v>
+        <v>154</v>
       </c>
       <c r="D197" t="n">
-        <v>150.3999938964844</v>
+        <v>148.7799987792969</v>
       </c>
       <c r="E197" t="n">
-        <v>152.7599945068359</v>
+        <v>150.1900024414062</v>
       </c>
       <c r="F197" t="n">
-        <v>13146800</v>
+        <v>11324700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B198" t="n">
-        <v>150.0099945068359</v>
+        <v>151.4900054931641</v>
       </c>
       <c r="C198" t="n">
-        <v>154</v>
+        <v>158.4600067138672</v>
       </c>
       <c r="D198" t="n">
-        <v>148.7799987792969</v>
+        <v>151.4900054931641</v>
       </c>
       <c r="E198" t="n">
-        <v>150.1900024414062</v>
+        <v>158.3699951171875</v>
       </c>
       <c r="F198" t="n">
-        <v>11324700</v>
+        <v>21267900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B199" t="n">
-        <v>151.4900054931641</v>
+        <v>160.2700042724609</v>
       </c>
       <c r="C199" t="n">
-        <v>158.4600067138672</v>
+        <v>161.7599945068359</v>
       </c>
       <c r="D199" t="n">
-        <v>151.4900054931641</v>
+        <v>157.6999969482422</v>
       </c>
       <c r="E199" t="n">
-        <v>158.3699951171875</v>
+        <v>157.9299926757812</v>
       </c>
       <c r="F199" t="n">
-        <v>21267900</v>
+        <v>12664100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B200" t="n">
-        <v>160.2700042724609</v>
+        <v>155.0899963378906</v>
       </c>
       <c r="C200" t="n">
-        <v>161.7599945068359</v>
+        <v>157.6900024414062</v>
       </c>
       <c r="D200" t="n">
-        <v>157.6999969482422</v>
+        <v>154.0700073242188</v>
       </c>
       <c r="E200" t="n">
-        <v>157.9299926757812</v>
+        <v>156.6600036621094</v>
       </c>
       <c r="F200" t="n">
-        <v>12664100</v>
+        <v>13690500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B201" t="n">
-        <v>155.0899963378906</v>
+        <v>162.2200012207031</v>
       </c>
       <c r="C201" t="n">
-        <v>157.6900024414062</v>
+        <v>165.8099975585938</v>
       </c>
       <c r="D201" t="n">
-        <v>154.0700073242188</v>
+        <v>161.1999969482422</v>
       </c>
       <c r="E201" t="n">
-        <v>156.6600036621094</v>
+        <v>163.2299957275391</v>
       </c>
       <c r="F201" t="n">
-        <v>13690500</v>
+        <v>14164600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B202" t="n">
-        <v>162.2200012207031</v>
+        <v>163</v>
       </c>
       <c r="C202" t="n">
-        <v>165.8099975585938</v>
+        <v>167.2100067138672</v>
       </c>
       <c r="D202" t="n">
-        <v>161.1999969482422</v>
+        <v>162</v>
       </c>
       <c r="E202" t="n">
-        <v>163.2299957275391</v>
+        <v>166.1100006103516</v>
       </c>
       <c r="F202" t="n">
-        <v>14164600</v>
+        <v>10486300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B203" t="n">
-        <v>163</v>
+        <v>163.9900054931641</v>
       </c>
       <c r="C203" t="n">
-        <v>167.2100067138672</v>
+        <v>167.7200012207031</v>
       </c>
       <c r="D203" t="n">
-        <v>162</v>
+        <v>162.3699951171875</v>
       </c>
       <c r="E203" t="n">
-        <v>166.1100006103516</v>
+        <v>165.6499938964844</v>
       </c>
       <c r="F203" t="n">
-        <v>10486300</v>
+        <v>10595500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B204" t="n">
-        <v>163.9900054931641</v>
+        <v>169.2200012207031</v>
       </c>
       <c r="C204" t="n">
-        <v>167.7200012207031</v>
+        <v>172.3800048828125</v>
       </c>
       <c r="D204" t="n">
-        <v>162.3699951171875</v>
+        <v>167.6799926757812</v>
       </c>
       <c r="E204" t="n">
-        <v>165.6499938964844</v>
+        <v>169.5200042724609</v>
       </c>
       <c r="F204" t="n">
-        <v>10595500</v>
+        <v>13057900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B205" t="n">
-        <v>169.2200012207031</v>
+        <v>167.3699951171875</v>
       </c>
       <c r="C205" t="n">
-        <v>172.3800048828125</v>
+        <v>167.5299987792969</v>
       </c>
       <c r="D205" t="n">
-        <v>167.6799926757812</v>
+        <v>164.7799987792969</v>
       </c>
       <c r="E205" t="n">
-        <v>169.5200042724609</v>
+        <v>166.5800018310547</v>
       </c>
       <c r="F205" t="n">
-        <v>13057900</v>
+        <v>9792400</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B206" t="n">
-        <v>167.3699951171875</v>
+        <v>158.3300018310547</v>
       </c>
       <c r="C206" t="n">
-        <v>167.5299987792969</v>
+        <v>163.8000030517578</v>
       </c>
       <c r="D206" t="n">
-        <v>164.7799987792969</v>
+        <v>156.4799957275391</v>
       </c>
       <c r="E206" t="n">
-        <v>166.5800018310547</v>
+        <v>162.5</v>
       </c>
       <c r="F206" t="n">
-        <v>9792400</v>
+        <v>13858600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B207" t="n">
-        <v>158.3300018310547</v>
+        <v>165.6000061035156</v>
       </c>
       <c r="C207" t="n">
-        <v>163.8000030517578</v>
+        <v>166.3000030517578</v>
       </c>
       <c r="D207" t="n">
-        <v>156.4799957275391</v>
+        <v>162.4199981689453</v>
       </c>
       <c r="E207" t="n">
-        <v>162.5</v>
+        <v>163.3200073242188</v>
       </c>
       <c r="F207" t="n">
-        <v>13858600</v>
+        <v>8321500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B208" t="n">
-        <v>165.6000061035156</v>
+        <v>165.9199981689453</v>
       </c>
       <c r="C208" t="n">
-        <v>166.3000030517578</v>
+        <v>172.7599945068359</v>
       </c>
       <c r="D208" t="n">
-        <v>162.4199981689453</v>
+        <v>165.9199981689453</v>
       </c>
       <c r="E208" t="n">
-        <v>163.3200073242188</v>
+        <v>171.2200012207031</v>
       </c>
       <c r="F208" t="n">
-        <v>8321500</v>
+        <v>14020700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>165.9199981689453</v>
+        <v>162.4900054931641</v>
       </c>
       <c r="C209" t="n">
-        <v>172.7599945068359</v>
+        <v>171.3500061035156</v>
       </c>
       <c r="D209" t="n">
-        <v>165.9199981689453</v>
+        <v>161.4700012207031</v>
       </c>
       <c r="E209" t="n">
-        <v>171.2200012207031</v>
+        <v>167.5599975585938</v>
       </c>
       <c r="F209" t="n">
-        <v>14020700</v>
+        <v>13507900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>162.4900054931641</v>
+        <v>170.5200042724609</v>
       </c>
       <c r="C210" t="n">
-        <v>171.3500061035156</v>
+        <v>172.8000030517578</v>
       </c>
       <c r="D210" t="n">
-        <v>161.4700012207031</v>
+        <v>166.5599975585938</v>
       </c>
       <c r="E210" t="n">
-        <v>167.5599975585938</v>
+        <v>167</v>
       </c>
       <c r="F210" t="n">
-        <v>13507900</v>
+        <v>13328100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>170.5200042724609</v>
+        <v>170.8399963378906</v>
       </c>
       <c r="C211" t="n">
-        <v>172.8000030517578</v>
+        <v>174.5399932861328</v>
       </c>
       <c r="D211" t="n">
-        <v>166.5599975585938</v>
+        <v>166.8800048828125</v>
       </c>
       <c r="E211" t="n">
-        <v>167</v>
+        <v>172.6799926757812</v>
       </c>
       <c r="F211" t="n">
-        <v>13328100</v>
+        <v>12057500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B212" t="n">
-        <v>170.8399963378906</v>
+        <v>171.5</v>
       </c>
       <c r="C212" t="n">
-        <v>174.5399932861328</v>
+        <v>175.4299926757812</v>
       </c>
       <c r="D212" t="n">
-        <v>166.8800048828125</v>
+        <v>169.75</v>
       </c>
       <c r="E212" t="n">
-        <v>172.6799926757812</v>
+        <v>170.7700042724609</v>
       </c>
       <c r="F212" t="n">
-        <v>12057500</v>
+        <v>10191500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B213" t="n">
-        <v>171.5</v>
+        <v>167.8600006103516</v>
       </c>
       <c r="C213" t="n">
-        <v>175.4299926757812</v>
+        <v>175.3899993896484</v>
       </c>
       <c r="D213" t="n">
-        <v>169.75</v>
+        <v>166.5</v>
       </c>
       <c r="E213" t="n">
-        <v>170.7700042724609</v>
+        <v>173.7899932861328</v>
       </c>
       <c r="F213" t="n">
-        <v>10191500</v>
+        <v>13426500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B214" t="n">
-        <v>167.8600006103516</v>
+        <v>167.0599975585938</v>
       </c>
       <c r="C214" t="n">
-        <v>175.3899993896484</v>
+        <v>172.4299926757812</v>
       </c>
       <c r="D214" t="n">
-        <v>166.5</v>
+        <v>166.9299926757812</v>
       </c>
       <c r="E214" t="n">
-        <v>173.7899932861328</v>
+        <v>170.0599975585938</v>
       </c>
       <c r="F214" t="n">
-        <v>13426500</v>
+        <v>12831800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B215" t="n">
-        <v>167.0599975585938</v>
+        <v>169.4700012207031</v>
       </c>
       <c r="C215" t="n">
-        <v>172.4299926757812</v>
+        <v>169.5700073242188</v>
       </c>
       <c r="D215" t="n">
-        <v>166.9299926757812</v>
+        <v>162.2100067138672</v>
       </c>
       <c r="E215" t="n">
-        <v>170.0599975585938</v>
+        <v>163</v>
       </c>
       <c r="F215" t="n">
-        <v>12831800</v>
+        <v>12194500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B216" t="n">
-        <v>169.4700012207031</v>
+        <v>165.0500030517578</v>
       </c>
       <c r="C216" t="n">
-        <v>169.5700073242188</v>
+        <v>165.8800048828125</v>
       </c>
       <c r="D216" t="n">
-        <v>162.2100067138672</v>
+        <v>155.1499938964844</v>
       </c>
       <c r="E216" t="n">
-        <v>163</v>
+        <v>156.9299926757812</v>
       </c>
       <c r="F216" t="n">
-        <v>12194500</v>
+        <v>12775000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B217" t="n">
-        <v>165.0500030517578</v>
+        <v>160.3800048828125</v>
       </c>
       <c r="C217" t="n">
-        <v>165.8800048828125</v>
+        <v>164.4499969482422</v>
       </c>
       <c r="D217" t="n">
-        <v>155.1499938964844</v>
+        <v>159.5500030517578</v>
       </c>
       <c r="E217" t="n">
-        <v>156.9299926757812</v>
+        <v>163.6600036621094</v>
       </c>
       <c r="F217" t="n">
-        <v>12775000</v>
+        <v>10899100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B218" t="n">
-        <v>160.3800048828125</v>
+        <v>168</v>
       </c>
       <c r="C218" t="n">
-        <v>164.4499969482422</v>
+        <v>176.9499969482422</v>
       </c>
       <c r="D218" t="n">
-        <v>159.5500030517578</v>
+        <v>167.1399993896484</v>
       </c>
       <c r="E218" t="n">
-        <v>163.6600036621094</v>
+        <v>173.6000061035156</v>
       </c>
       <c r="F218" t="n">
-        <v>10899100</v>
+        <v>17312000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B219" t="n">
-        <v>168</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="C219" t="n">
-        <v>176.9499969482422</v>
+        <v>184.5399932861328</v>
       </c>
       <c r="D219" t="n">
-        <v>167.1399993896484</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="E219" t="n">
-        <v>173.6000061035156</v>
+        <v>181.5</v>
       </c>
       <c r="F219" t="n">
-        <v>17312000</v>
+        <v>17204600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B220" t="n">
-        <v>176.9100036621094</v>
+        <v>182.0099945068359</v>
       </c>
       <c r="C220" t="n">
-        <v>184.5399932861328</v>
+        <v>190.1799926757812</v>
       </c>
       <c r="D220" t="n">
-        <v>176.9100036621094</v>
+        <v>182.0099945068359</v>
       </c>
       <c r="E220" t="n">
-        <v>181.5</v>
+        <v>188.3800048828125</v>
       </c>
       <c r="F220" t="n">
-        <v>17204600</v>
+        <v>18139500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B221" t="n">
-        <v>182.0099945068359</v>
+        <v>180.9900054931641</v>
       </c>
       <c r="C221" t="n">
-        <v>190.1799926757812</v>
+        <v>182.5099945068359</v>
       </c>
       <c r="D221" t="n">
-        <v>182.0099945068359</v>
+        <v>175.8999938964844</v>
       </c>
       <c r="E221" t="n">
-        <v>188.3800048828125</v>
+        <v>180.7100067138672</v>
       </c>
       <c r="F221" t="n">
-        <v>18139500</v>
+        <v>12182400</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B222" t="n">
-        <v>180.9900054931641</v>
+        <v>177.6999969482422</v>
       </c>
       <c r="C222" t="n">
-        <v>182.5099945068359</v>
+        <v>184.4499969482422</v>
       </c>
       <c r="D222" t="n">
-        <v>175.8999938964844</v>
+        <v>177.0299987792969</v>
       </c>
       <c r="E222" t="n">
-        <v>180.7100067138672</v>
+        <v>184.0200042724609</v>
       </c>
       <c r="F222" t="n">
-        <v>12182400</v>
+        <v>9691500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B223" t="n">
-        <v>177.6999969482422</v>
+        <v>188.9900054931641</v>
       </c>
       <c r="C223" t="n">
-        <v>184.4499969482422</v>
+        <v>193.6999969482422</v>
       </c>
       <c r="D223" t="n">
-        <v>177.0299987792969</v>
+        <v>185.8999938964844</v>
       </c>
       <c r="E223" t="n">
-        <v>184.0200042724609</v>
+        <v>185.9499969482422</v>
       </c>
       <c r="F223" t="n">
-        <v>9691500</v>
+        <v>12908000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B224" t="n">
-        <v>188.9900054931641</v>
+        <v>183.0899963378906</v>
       </c>
       <c r="C224" t="n">
-        <v>193.6999969482422</v>
+        <v>191.2899932861328</v>
       </c>
       <c r="D224" t="n">
-        <v>185.8999938964844</v>
+        <v>183</v>
       </c>
       <c r="E224" t="n">
-        <v>185.9499969482422</v>
+        <v>190.9900054931641</v>
       </c>
       <c r="F224" t="n">
-        <v>12908000</v>
+        <v>9326900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B225" t="n">
-        <v>183.0899963378906</v>
+        <v>193.2799987792969</v>
       </c>
       <c r="C225" t="n">
-        <v>191.2899932861328</v>
+        <v>194.9400024414062</v>
       </c>
       <c r="D225" t="n">
-        <v>183</v>
+        <v>190.4299926757812</v>
       </c>
       <c r="E225" t="n">
-        <v>190.9900054931641</v>
+        <v>192.9799957275391</v>
       </c>
       <c r="F225" t="n">
-        <v>9326900</v>
+        <v>9605500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B226" t="n">
-        <v>193.2799987792969</v>
+        <v>183.4400024414062</v>
       </c>
       <c r="C226" t="n">
-        <v>194.9400024414062</v>
+        <v>187.0200042724609</v>
       </c>
       <c r="D226" t="n">
-        <v>190.4299926757812</v>
+        <v>183</v>
       </c>
       <c r="E226" t="n">
-        <v>192.9799957275391</v>
+        <v>186.7700042724609</v>
       </c>
       <c r="F226" t="n">
-        <v>9605500</v>
+        <v>13297600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B227" t="n">
-        <v>183.4400024414062</v>
+        <v>191.0899963378906</v>
       </c>
       <c r="C227" t="n">
-        <v>187.0200042724609</v>
+        <v>194.6999969482422</v>
       </c>
       <c r="D227" t="n">
-        <v>183</v>
+        <v>190.6000061035156</v>
       </c>
       <c r="E227" t="n">
-        <v>186.7700042724609</v>
+        <v>192.7400054931641</v>
       </c>
       <c r="F227" t="n">
-        <v>13297600</v>
+        <v>11392800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B228" t="n">
-        <v>191.0899963378906</v>
+        <v>190.1699981689453</v>
       </c>
       <c r="C228" t="n">
-        <v>194.6999969482422</v>
+        <v>198.1799926757812</v>
       </c>
       <c r="D228" t="n">
-        <v>190.6000061035156</v>
+        <v>190</v>
       </c>
       <c r="E228" t="n">
-        <v>192.7400054931641</v>
+        <v>197.5099945068359</v>
       </c>
       <c r="F228" t="n">
-        <v>11392800</v>
+        <v>9706600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B229" t="n">
-        <v>190.1699981689453</v>
+        <v>196.9400024414062</v>
       </c>
       <c r="C229" t="n">
-        <v>198.1799926757812</v>
+        <v>199.3899993896484</v>
       </c>
       <c r="D229" t="n">
-        <v>190</v>
+        <v>195.5</v>
       </c>
       <c r="E229" t="n">
-        <v>197.5099945068359</v>
+        <v>197.4700012207031</v>
       </c>
       <c r="F229" t="n">
-        <v>9706600</v>
+        <v>11171600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B230" t="n">
-        <v>196.9400024414062</v>
+        <v>192</v>
       </c>
       <c r="C230" t="n">
-        <v>199.3899993896484</v>
+        <v>196.5</v>
       </c>
       <c r="D230" t="n">
-        <v>195.5</v>
+        <v>191.7799987792969</v>
       </c>
       <c r="E230" t="n">
-        <v>197.4700012207031</v>
+        <v>193.3200073242188</v>
       </c>
       <c r="F230" t="n">
-        <v>11171600</v>
+        <v>12787900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B231" t="n">
-        <v>192</v>
+        <v>196.8399963378906</v>
       </c>
       <c r="C231" t="n">
-        <v>196.5</v>
+        <v>202.9900054931641</v>
       </c>
       <c r="D231" t="n">
-        <v>191.7799987792969</v>
+        <v>191.3899993896484</v>
       </c>
       <c r="E231" t="n">
-        <v>193.3200073242188</v>
+        <v>201.3699951171875</v>
       </c>
       <c r="F231" t="n">
-        <v>12787900</v>
+        <v>15058700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="n">
-        <v>196.8399963378906</v>
+        <v>202.75</v>
       </c>
       <c r="C232" t="n">
-        <v>202.9900054931641</v>
+        <v>204.3999938964844</v>
       </c>
       <c r="D232" t="n">
-        <v>191.3899993896484</v>
+        <v>195.3200073242188</v>
       </c>
       <c r="E232" t="n">
-        <v>201.3699951171875</v>
+        <v>196.2100067138672</v>
       </c>
       <c r="F232" t="n">
-        <v>15058700</v>
+        <v>8664800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B233" t="n">
-        <v>202.75</v>
+        <v>193.8300018310547</v>
       </c>
       <c r="C233" t="n">
-        <v>204.3999938964844</v>
+        <v>194.9400024414062</v>
       </c>
       <c r="D233" t="n">
-        <v>195.3200073242188</v>
+        <v>189.9100036621094</v>
       </c>
       <c r="E233" t="n">
-        <v>196.2100067138672</v>
+        <v>190.9700012207031</v>
       </c>
       <c r="F233" t="n">
-        <v>8664800</v>
+        <v>14378800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B234" t="n">
-        <v>193.8300018310547</v>
+        <v>194.0899963378906</v>
       </c>
       <c r="C234" t="n">
-        <v>194.9400024414062</v>
+        <v>199.4100036621094</v>
       </c>
       <c r="D234" t="n">
-        <v>189.9100036621094</v>
+        <v>193.2299957275391</v>
       </c>
       <c r="E234" t="n">
-        <v>190.9700012207031</v>
+        <v>196.1399993896484</v>
       </c>
       <c r="F234" t="n">
-        <v>14378800</v>
+        <v>14152900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B235" t="n">
-        <v>194.0899963378906</v>
+        <v>194.2100067138672</v>
       </c>
       <c r="C235" t="n">
-        <v>199.4100036621094</v>
+        <v>207.9499969482422</v>
       </c>
       <c r="D235" t="n">
-        <v>193.2299957275391</v>
+        <v>194.2100067138672</v>
       </c>
       <c r="E235" t="n">
-        <v>196.1399993896484</v>
+        <v>206.0899963378906</v>
       </c>
       <c r="F235" t="n">
-        <v>14152900</v>
+        <v>17843600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B236" t="n">
-        <v>194.2100067138672</v>
+        <v>205.2200012207031</v>
       </c>
       <c r="C236" t="n">
-        <v>207.9499969482422</v>
+        <v>207.8800048828125</v>
       </c>
       <c r="D236" t="n">
-        <v>194.2100067138672</v>
+        <v>203</v>
       </c>
       <c r="E236" t="n">
-        <v>206.0899963378906</v>
+        <v>205.4299926757812</v>
       </c>
       <c r="F236" t="n">
-        <v>17843600</v>
+        <v>11482300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="n">
-        <v>205.2200012207031</v>
+        <v>205.5800018310547</v>
       </c>
       <c r="C237" t="n">
-        <v>207.8800048828125</v>
+        <v>211.0700073242188</v>
       </c>
       <c r="D237" t="n">
-        <v>203</v>
+        <v>204.7299957275391</v>
       </c>
       <c r="E237" t="n">
-        <v>205.4299926757812</v>
+        <v>209.1699981689453</v>
       </c>
       <c r="F237" t="n">
-        <v>11482300</v>
+        <v>9685400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B238" t="n">
-        <v>205.5800018310547</v>
+        <v>208.4199981689453</v>
       </c>
       <c r="C238" t="n">
-        <v>211.0700073242188</v>
+        <v>213.1699981689453</v>
       </c>
       <c r="D238" t="n">
-        <v>204.7299957275391</v>
+        <v>207.3899993896484</v>
       </c>
       <c r="E238" t="n">
-        <v>209.1699981689453</v>
+        <v>209.0599975585938</v>
       </c>
       <c r="F238" t="n">
-        <v>9685400</v>
+        <v>9580200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B239" t="n">
-        <v>208.4199981689453</v>
+        <v>205.8500061035156</v>
       </c>
       <c r="C239" t="n">
-        <v>213.1699981689453</v>
+        <v>210.3099975585938</v>
       </c>
       <c r="D239" t="n">
-        <v>207.3899993896484</v>
+        <v>204.7599945068359</v>
       </c>
       <c r="E239" t="n">
-        <v>209.0599975585938</v>
+        <v>205.6900024414062</v>
       </c>
       <c r="F239" t="n">
-        <v>9580200</v>
+        <v>10081800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B240" t="n">
-        <v>205.8500061035156</v>
+        <v>199.9400024414062</v>
       </c>
       <c r="C240" t="n">
-        <v>210.3099975585938</v>
+        <v>206.4400024414062</v>
       </c>
       <c r="D240" t="n">
-        <v>204.7599945068359</v>
+        <v>198.9499969482422</v>
       </c>
       <c r="E240" t="n">
-        <v>205.6900024414062</v>
+        <v>205.6199951171875</v>
       </c>
       <c r="F240" t="n">
-        <v>10081800</v>
+        <v>14888900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B241" t="n">
-        <v>199.9400024414062</v>
+        <v>230.0500030517578</v>
       </c>
       <c r="C241" t="n">
-        <v>206.4400024414062</v>
+        <v>254.4799957275391</v>
       </c>
       <c r="D241" t="n">
-        <v>198.9499969482422</v>
+        <v>230.0500030517578</v>
       </c>
       <c r="E241" t="n">
-        <v>205.6199951171875</v>
+        <v>252.0500030517578</v>
       </c>
       <c r="F241" t="n">
-        <v>14888900</v>
+        <v>55517500</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B242" t="n">
-        <v>230.0500030517578</v>
+        <v>250.4700012207031</v>
       </c>
       <c r="C242" t="n">
-        <v>254.4799957275391</v>
+        <v>263.5299987792969</v>
       </c>
       <c r="D242" t="n">
-        <v>230.0500030517578</v>
+        <v>249</v>
       </c>
       <c r="E242" t="n">
-        <v>252.0500030517578</v>
+        <v>256</v>
       </c>
       <c r="F242" t="n">
-        <v>55517500</v>
+        <v>34362700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B243" t="n">
-        <v>250.4700012207031</v>
+        <v>254.3899993896484</v>
       </c>
       <c r="C243" t="n">
-        <v>263.5299987792969</v>
+        <v>262.2799987792969</v>
       </c>
       <c r="D243" t="n">
-        <v>249</v>
+        <v>254.3899993896484</v>
       </c>
       <c r="E243" t="n">
-        <v>256</v>
+        <v>257.5400085449219</v>
       </c>
       <c r="F243" t="n">
-        <v>34362700</v>
+        <v>22471500</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B244" t="n">
-        <v>254.3899993896484</v>
+        <v>255.0099945068359</v>
       </c>
       <c r="C244" t="n">
-        <v>262.2799987792969</v>
+        <v>262.3200073242188</v>
       </c>
       <c r="D244" t="n">
-        <v>254.3899993896484</v>
+        <v>254.25</v>
       </c>
       <c r="E244" t="n">
-        <v>257.5400085449219</v>
+        <v>258.1099853515625</v>
       </c>
       <c r="F244" t="n">
-        <v>22471500</v>
+        <v>15897500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B245" t="n">
-        <v>255.0099945068359</v>
+        <v>259.3800048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>262.3200073242188</v>
+        <v>264.5499877929688</v>
       </c>
       <c r="D245" t="n">
-        <v>254.25</v>
+        <v>253.6000061035156</v>
       </c>
       <c r="E245" t="n">
-        <v>258.1099853515625</v>
+        <v>256.9299926757812</v>
       </c>
       <c r="F245" t="n">
-        <v>15897500</v>
+        <v>14393700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B246" t="n">
-        <v>259.3800048828125</v>
+        <v>261.9800109863281</v>
       </c>
       <c r="C246" t="n">
-        <v>264.5499877929688</v>
+        <v>268.2699890136719</v>
       </c>
       <c r="D246" t="n">
-        <v>253.6000061035156</v>
+        <v>261.6000061035156</v>
       </c>
       <c r="E246" t="n">
-        <v>256.9299926757812</v>
+        <v>264.4299926757812</v>
       </c>
       <c r="F246" t="n">
-        <v>14393700</v>
+        <v>16028300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B247" t="n">
-        <v>261.9800109863281</v>
+        <v>263.3599853515625</v>
       </c>
       <c r="C247" t="n">
-        <v>268.2699890136719</v>
+        <v>263.6000061035156</v>
       </c>
       <c r="D247" t="n">
-        <v>261.6000061035156</v>
+        <v>257.8200073242188</v>
       </c>
       <c r="E247" t="n">
-        <v>264.4299926757812</v>
+        <v>259.2300109863281</v>
       </c>
       <c r="F247" t="n">
-        <v>16028300</v>
+        <v>10490600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B248" t="n">
-        <v>263.3599853515625</v>
+        <v>253.7200012207031</v>
       </c>
       <c r="C248" t="n">
-        <v>263.6000061035156</v>
+        <v>254</v>
       </c>
       <c r="D248" t="n">
-        <v>257.8200073242188</v>
+        <v>245.8899993896484</v>
       </c>
       <c r="E248" t="n">
-        <v>259.2300109863281</v>
+        <v>249.1199951171875</v>
       </c>
       <c r="F248" t="n">
-        <v>10490600</v>
+        <v>17482700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B249" t="n">
-        <v>253.7200012207031</v>
+        <v>249.7799987792969</v>
       </c>
       <c r="C249" t="n">
-        <v>254</v>
+        <v>254.8000030517578</v>
       </c>
       <c r="D249" t="n">
-        <v>245.8899993896484</v>
+        <v>243.4499969482422</v>
       </c>
       <c r="E249" t="n">
-        <v>249.1199951171875</v>
+        <v>244.1600036621094</v>
       </c>
       <c r="F249" t="n">
-        <v>17482700</v>
+        <v>11853700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B250" t="n">
-        <v>249.7799987792969</v>
+        <v>245.3500061035156</v>
       </c>
       <c r="C250" t="n">
-        <v>254.8000030517578</v>
+        <v>248.5</v>
       </c>
       <c r="D250" t="n">
-        <v>243.4499969482422</v>
+        <v>241.75</v>
       </c>
       <c r="E250" t="n">
-        <v>244.1600036621094</v>
+        <v>243</v>
       </c>
       <c r="F250" t="n">
-        <v>11853700</v>
+        <v>10732600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B251" t="n">
-        <v>245.3500061035156</v>
+        <v>242.0200042724609</v>
       </c>
       <c r="C251" t="n">
-        <v>248.5</v>
+        <v>250.5500030517578</v>
       </c>
       <c r="D251" t="n">
-        <v>241.75</v>
+        <v>242.0200042724609</v>
       </c>
       <c r="E251" t="n">
-        <v>243</v>
+        <v>247.7200012207031</v>
       </c>
       <c r="F251" t="n">
-        <v>10732600</v>
+        <v>9738300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B252" t="n">
-        <v>242.0200042724609</v>
+        <v>255.75</v>
       </c>
       <c r="C252" t="n">
-        <v>250.5500030517578</v>
+        <v>260.1799926757812</v>
       </c>
       <c r="D252" t="n">
-        <v>242.0200042724609</v>
+        <v>251.5</v>
       </c>
       <c r="E252" t="n">
-        <v>247.7200012207031</v>
+        <v>259.4299926757812</v>
       </c>
       <c r="F252" t="n">
-        <v>9738300</v>
+        <v>12963700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10654,37 +10654,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>259.43</v>
+      </c>
+      <c r="D2" t="n">
         <v>247.72</v>
       </c>
-      <c r="D2" t="n">
-        <v>243</v>
-      </c>
       <c r="E2" t="n">
-        <v>242.02</v>
+        <v>255.75</v>
       </c>
       <c r="F2" t="n">
-        <v>250.5472</v>
+        <v>260.18</v>
       </c>
       <c r="G2" t="n">
-        <v>243.255</v>
+        <v>251.55</v>
       </c>
       <c r="H2" t="n">
-        <v>9664041</v>
+        <v>12961044</v>
       </c>
       <c r="I2" t="n">
-        <v>15099909</v>
+        <v>15066001</v>
       </c>
       <c r="J2" t="n">
-        <v>203873566720</v>
+        <v>213510881280</v>
       </c>
       <c r="K2" t="n">
-        <v>22.684982</v>
+        <v>23.757324</v>
       </c>
       <c r="L2" t="n">
-        <v>15.474599</v>
+        <v>16.2061</v>
       </c>
       <c r="M2" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="N2" t="n">
         <v>269.11</v>
@@ -10720,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.312232</v>
+        <v>5.563347</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10732,7 +10732,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>234846552064</v>
+        <v>244483883008</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:47:43</t>
+          <t>2026-09-15 14:14:49</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,25 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B2" t="n">
-        <v>241.2084729659526</v>
+        <v>238.3703397912324</v>
       </c>
       <c r="C2" t="n">
-        <v>242.6562262649122</v>
+        <v>241.380140328441</v>
       </c>
       <c r="D2" t="n">
-        <v>238.8186957689135</v>
+        <v>237.784276421548</v>
       </c>
       <c r="E2" t="n">
-        <v>240.4846038818359</v>
+        <v>240.5954132080078</v>
       </c>
       <c r="F2" t="n">
-        <v>7244600</v>
+        <v>10124000</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>240.4845948654329</v>
+        <v>242.5324313580229</v>
       </c>
       <c r="C3" t="n">
-        <v>240.643240526318</v>
+        <v>245.6415564491674</v>
       </c>
       <c r="D3" t="n">
-        <v>235.2489097880788</v>
+        <v>241.3304905574327</v>
       </c>
       <c r="E3" t="n">
-        <v>237.3015289306641</v>
+        <v>242.6516265869141</v>
       </c>
       <c r="F3" t="n">
-        <v>8779800</v>
+        <v>9344400</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>238.3703397912324</v>
+        <v>244.3800268891626</v>
       </c>
       <c r="C4" t="n">
-        <v>241.380140328441</v>
+        <v>245.5521536952295</v>
       </c>
       <c r="D4" t="n">
-        <v>237.784276421548</v>
+        <v>241.7278270152115</v>
       </c>
       <c r="E4" t="n">
-        <v>240.5954132080078</v>
+        <v>245.4428863525391</v>
       </c>
       <c r="F4" t="n">
-        <v>10124000</v>
+        <v>11813900</v>
       </c>
       <c r="G4" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>242.5324313580229</v>
+        <v>243.6449370886138</v>
       </c>
       <c r="C5" t="n">
-        <v>245.6415564491674</v>
+        <v>248.8102703225537</v>
       </c>
       <c r="D5" t="n">
-        <v>241.3304905574327</v>
+        <v>241.5390740768479</v>
       </c>
       <c r="E5" t="n">
-        <v>242.6516265869141</v>
+        <v>248.0255432128906</v>
       </c>
       <c r="F5" t="n">
-        <v>9344400</v>
+        <v>7523800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>244.3800268891626</v>
+        <v>248.0752418629596</v>
       </c>
       <c r="C6" t="n">
-        <v>245.5521536952295</v>
+        <v>249.6844381137545</v>
       </c>
       <c r="D6" t="n">
-        <v>241.7278270152115</v>
+        <v>242.5026374437513</v>
       </c>
       <c r="E6" t="n">
-        <v>245.4428863525391</v>
+        <v>242.9297637939453</v>
       </c>
       <c r="F6" t="n">
-        <v>11813900</v>
+        <v>7669800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>243.6449370886138</v>
+        <v>244.0323655727545</v>
       </c>
       <c r="C7" t="n">
-        <v>248.8102703225537</v>
+        <v>247.1812325805079</v>
       </c>
       <c r="D7" t="n">
-        <v>241.5390740768479</v>
+        <v>241.390093455952</v>
       </c>
       <c r="E7" t="n">
-        <v>248.0255432128906</v>
+        <v>244.2509002685547</v>
       </c>
       <c r="F7" t="n">
-        <v>7523800</v>
+        <v>6707100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>248.0752262809752</v>
+        <v>242.8701495715982</v>
       </c>
       <c r="C8" t="n">
-        <v>249.6844224306941</v>
+        <v>243.0290866405082</v>
       </c>
       <c r="D8" t="n">
-        <v>242.5026222117907</v>
+        <v>237.8935519633032</v>
       </c>
       <c r="E8" t="n">
-        <v>242.9297485351562</v>
+        <v>239.3438110351562</v>
       </c>
       <c r="F8" t="n">
-        <v>7669800</v>
+        <v>8145500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>244.0323655727545</v>
+        <v>239.0855711988149</v>
       </c>
       <c r="C9" t="n">
-        <v>247.1812325805079</v>
+        <v>242.8999702537546</v>
       </c>
       <c r="D9" t="n">
-        <v>241.390093455952</v>
+        <v>238.7478412647688</v>
       </c>
       <c r="E9" t="n">
-        <v>244.2509002685547</v>
+        <v>241.8072967529297</v>
       </c>
       <c r="F9" t="n">
-        <v>6707100</v>
+        <v>4974600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>242.8701495715982</v>
+        <v>243.0886994915912</v>
       </c>
       <c r="C10" t="n">
-        <v>243.0290866405082</v>
+        <v>244.1813729625073</v>
       </c>
       <c r="D10" t="n">
-        <v>237.8935519633032</v>
+        <v>241.2510255151616</v>
       </c>
       <c r="E10" t="n">
-        <v>239.3438110351562</v>
+        <v>243.4661712646484</v>
       </c>
       <c r="F10" t="n">
-        <v>8145500</v>
+        <v>6373500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>239.0855561117752</v>
+        <v>243.4164922422276</v>
       </c>
       <c r="C11" t="n">
-        <v>242.8999549260145</v>
+        <v>243.5754293150353</v>
       </c>
       <c r="D11" t="n">
-        <v>238.7478261990409</v>
+        <v>234.2380809080728</v>
       </c>
       <c r="E11" t="n">
-        <v>241.8072814941406</v>
+        <v>235.4201507568359</v>
       </c>
       <c r="F11" t="n">
-        <v>4974600</v>
+        <v>10801100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>243.0886994915912</v>
+        <v>234.9135667280067</v>
       </c>
       <c r="C12" t="n">
-        <v>244.1813729625073</v>
+        <v>240.853699895347</v>
       </c>
       <c r="D12" t="n">
-        <v>241.2510255151616</v>
+        <v>231.9534204494054</v>
       </c>
       <c r="E12" t="n">
-        <v>243.4661712646484</v>
+        <v>234.118896484375</v>
       </c>
       <c r="F12" t="n">
-        <v>6373500</v>
+        <v>10016600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>243.4165080193006</v>
+        <v>233.8605987472531</v>
       </c>
       <c r="C13" t="n">
-        <v>243.5754451024098</v>
+        <v>237.8041356430789</v>
       </c>
       <c r="D13" t="n">
-        <v>234.2380960902458</v>
+        <v>232.0428110022616</v>
       </c>
       <c r="E13" t="n">
-        <v>235.420166015625</v>
+        <v>237.2876129150391</v>
       </c>
       <c r="F13" t="n">
-        <v>10801100</v>
+        <v>7679200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>234.9135667280067</v>
+        <v>237.1584831814004</v>
       </c>
       <c r="C14" t="n">
-        <v>240.853699895347</v>
+        <v>241.1914166378037</v>
       </c>
       <c r="D14" t="n">
-        <v>231.9534204494054</v>
+        <v>236.9101496911581</v>
       </c>
       <c r="E14" t="n">
-        <v>234.118896484375</v>
+        <v>238.7577514648438</v>
       </c>
       <c r="F14" t="n">
-        <v>10016600</v>
+        <v>8849800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>233.8606137856679</v>
+        <v>237.7346158803774</v>
       </c>
       <c r="C15" t="n">
-        <v>237.804150935083</v>
+        <v>248.8003554681588</v>
       </c>
       <c r="D15" t="n">
-        <v>232.0428259237834</v>
+        <v>233.8407486183705</v>
       </c>
       <c r="E15" t="n">
-        <v>237.2876281738281</v>
+        <v>244.1416168212891</v>
       </c>
       <c r="F15" t="n">
-        <v>7679200</v>
+        <v>13922600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>237.1584831814004</v>
+        <v>244.8369370505447</v>
       </c>
       <c r="C16" t="n">
-        <v>241.1914166378037</v>
+        <v>245.7110757386007</v>
       </c>
       <c r="D16" t="n">
-        <v>236.9101496911581</v>
+        <v>235.9664725401552</v>
       </c>
       <c r="E16" t="n">
-        <v>238.7577514648438</v>
+        <v>238.1418762207031</v>
       </c>
       <c r="F16" t="n">
-        <v>8849800</v>
+        <v>8387400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>237.7346158803774</v>
+        <v>238.1418828252031</v>
       </c>
       <c r="C17" t="n">
-        <v>248.8003554681588</v>
+        <v>239.7113522599795</v>
       </c>
       <c r="D17" t="n">
-        <v>233.8407486183705</v>
+        <v>234.0791355152303</v>
       </c>
       <c r="E17" t="n">
-        <v>244.1416168212891</v>
+        <v>238.8272705078125</v>
       </c>
       <c r="F17" t="n">
-        <v>13922600</v>
+        <v>7120200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>244.8369527383155</v>
+        <v>237.6750243923864</v>
       </c>
       <c r="C18" t="n">
-        <v>245.7110914823814</v>
+        <v>244.3204311088745</v>
       </c>
       <c r="D18" t="n">
-        <v>235.9664876595567</v>
+        <v>235.569146059018</v>
       </c>
       <c r="E18" t="n">
-        <v>238.1418914794922</v>
+        <v>243.6946258544922</v>
       </c>
       <c r="F18" t="n">
-        <v>8387400</v>
+        <v>7929100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>238.1418828252031</v>
+        <v>244.8767025596296</v>
       </c>
       <c r="C19" t="n">
-        <v>239.7113522599795</v>
+        <v>247.3898363735872</v>
       </c>
       <c r="D19" t="n">
-        <v>234.0791355152303</v>
+        <v>239.1153623132595</v>
       </c>
       <c r="E19" t="n">
-        <v>238.8272705078125</v>
+        <v>240.0689544677734</v>
       </c>
       <c r="F19" t="n">
-        <v>7120200</v>
+        <v>7988300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>237.6750243923864</v>
+        <v>241.2708896666147</v>
       </c>
       <c r="C20" t="n">
-        <v>244.3204311088745</v>
+        <v>247.6878338430882</v>
       </c>
       <c r="D20" t="n">
-        <v>235.569146059018</v>
+        <v>240.7543517533109</v>
       </c>
       <c r="E20" t="n">
-        <v>243.6946258544922</v>
+        <v>247.0918273925781</v>
       </c>
       <c r="F20" t="n">
-        <v>7929100</v>
+        <v>8276500</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>244.8766869952599</v>
+        <v>246.4560778349605</v>
       </c>
       <c r="C21" t="n">
-        <v>247.3898206494827</v>
+        <v>246.6249427813727</v>
       </c>
       <c r="D21" t="n">
-        <v>239.1153471150808</v>
+        <v>237.9531419622505</v>
       </c>
       <c r="E21" t="n">
-        <v>240.0689392089844</v>
+        <v>238.1716766357422</v>
       </c>
       <c r="F21" t="n">
-        <v>7988300</v>
+        <v>9123900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>241.2708896666147</v>
+        <v>239.2643564080466</v>
       </c>
       <c r="C22" t="n">
-        <v>247.6878338430882</v>
+        <v>239.711368834973</v>
       </c>
       <c r="D22" t="n">
-        <v>240.7543517533109</v>
+        <v>234.3274852014847</v>
       </c>
       <c r="E22" t="n">
-        <v>247.0918273925781</v>
+        <v>235.0029602050781</v>
       </c>
       <c r="F22" t="n">
-        <v>8276500</v>
+        <v>8389200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>246.4560936245009</v>
+        <v>251.502226767664</v>
       </c>
       <c r="C23" t="n">
-        <v>246.6249585817316</v>
+        <v>255.0285501861264</v>
       </c>
       <c r="D23" t="n">
-        <v>237.9531572070389</v>
+        <v>241.0523493056123</v>
       </c>
       <c r="E23" t="n">
-        <v>238.1716918945312</v>
+        <v>244.3601531982422</v>
       </c>
       <c r="F23" t="n">
-        <v>9123900</v>
+        <v>24869700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>239.2643408725642</v>
+        <v>244.926381762535</v>
       </c>
       <c r="C24" t="n">
-        <v>239.711353270466</v>
+        <v>249.1083095871451</v>
       </c>
       <c r="D24" t="n">
-        <v>234.3274699865544</v>
+        <v>240.5457750040669</v>
       </c>
       <c r="E24" t="n">
-        <v>235.0029449462891</v>
+        <v>241.4596405029297</v>
       </c>
       <c r="F24" t="n">
-        <v>8389200</v>
+        <v>10851200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>251.502226767664</v>
+        <v>243.3668228990331</v>
       </c>
       <c r="C25" t="n">
-        <v>255.0285501861264</v>
+        <v>253.6974901347749</v>
       </c>
       <c r="D25" t="n">
-        <v>241.0523493056123</v>
+        <v>242.6714921507363</v>
       </c>
       <c r="E25" t="n">
-        <v>244.3601531982422</v>
+        <v>252.5849609375</v>
       </c>
       <c r="F25" t="n">
-        <v>24869700</v>
+        <v>9963900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>244.9263662846688</v>
+        <v>252.803504151519</v>
       </c>
       <c r="C26" t="n">
-        <v>249.1082938450064</v>
+        <v>265.3493174789288</v>
       </c>
       <c r="D26" t="n">
-        <v>240.5457598030287</v>
+        <v>252.3068371492567</v>
       </c>
       <c r="E26" t="n">
-        <v>241.4596252441406</v>
+        <v>261.6541137695312</v>
       </c>
       <c r="F26" t="n">
-        <v>10851200</v>
+        <v>13354700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>243.3668228990331</v>
+        <v>260.4521950408587</v>
       </c>
       <c r="C27" t="n">
-        <v>253.6974901347749</v>
+        <v>260.6508436585594</v>
       </c>
       <c r="D27" t="n">
-        <v>242.6714921507363</v>
+        <v>254.8001219796189</v>
       </c>
       <c r="E27" t="n">
-        <v>252.5849609375</v>
+        <v>254.9292602539062</v>
       </c>
       <c r="F27" t="n">
-        <v>9963900</v>
+        <v>9370000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>252.8034746662165</v>
+        <v>255.8828429735078</v>
       </c>
       <c r="C28" t="n">
-        <v>265.349286530367</v>
+        <v>256.8364351199962</v>
       </c>
       <c r="D28" t="n">
-        <v>252.3068077218821</v>
+        <v>252.4260297605343</v>
       </c>
       <c r="E28" t="n">
-        <v>261.6540832519531</v>
+        <v>253.3498382568359</v>
       </c>
       <c r="F28" t="n">
-        <v>13354700</v>
+        <v>6110100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>260.4521950408587</v>
+        <v>255.7040638410269</v>
       </c>
       <c r="C29" t="n">
-        <v>260.6508436585594</v>
+        <v>256.7768512740817</v>
       </c>
       <c r="D29" t="n">
-        <v>254.8001219796189</v>
+        <v>252.3068480604129</v>
       </c>
       <c r="E29" t="n">
-        <v>254.9292602539062</v>
+        <v>253.1313171386719</v>
       </c>
       <c r="F29" t="n">
-        <v>9370000</v>
+        <v>5490800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>255.8828429735078</v>
+        <v>255.3662819386644</v>
       </c>
       <c r="C30" t="n">
-        <v>256.8364351199962</v>
+        <v>256.3795019822516</v>
       </c>
       <c r="D30" t="n">
-        <v>252.4260297605343</v>
+        <v>253.2206920973818</v>
       </c>
       <c r="E30" t="n">
-        <v>253.3498382568359</v>
+        <v>253.7670288085938</v>
       </c>
       <c r="F30" t="n">
-        <v>6110100</v>
+        <v>4942400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>255.7040484271523</v>
+        <v>253.7670347871236</v>
       </c>
       <c r="C31" t="n">
-        <v>256.7768357955393</v>
+        <v>257.1145654719376</v>
       </c>
       <c r="D31" t="n">
-        <v>252.306832851323</v>
+        <v>252.4458987660038</v>
       </c>
       <c r="E31" t="n">
-        <v>253.1313018798828</v>
+        <v>252.5650939941406</v>
       </c>
       <c r="F31" t="n">
-        <v>5490800</v>
+        <v>6435600</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>255.3662819386644</v>
+        <v>250.3201460853343</v>
       </c>
       <c r="C32" t="n">
-        <v>256.3795019822516</v>
+        <v>251.8796876041973</v>
       </c>
       <c r="D32" t="n">
-        <v>253.2206920973818</v>
+        <v>247.3798710336327</v>
       </c>
       <c r="E32" t="n">
-        <v>253.7670288085938</v>
+        <v>249.7837524414062</v>
       </c>
       <c r="F32" t="n">
-        <v>4942400</v>
+        <v>7904200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>253.7670347871236</v>
+        <v>248.8301503215196</v>
       </c>
       <c r="C33" t="n">
-        <v>257.1145654719376</v>
+        <v>257.5516210443747</v>
       </c>
       <c r="D33" t="n">
-        <v>252.4458987660038</v>
+        <v>248.33348335481</v>
       </c>
       <c r="E33" t="n">
-        <v>252.5650939941406</v>
+        <v>254.9391479492188</v>
       </c>
       <c r="F33" t="n">
-        <v>6435600</v>
+        <v>7767800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>250.3201613768906</v>
+        <v>253.1014986048366</v>
       </c>
       <c r="C34" t="n">
-        <v>251.8797029910229</v>
+        <v>260.0747073186972</v>
       </c>
       <c r="D34" t="n">
-        <v>247.3798861455735</v>
+        <v>250.945965708637</v>
       </c>
       <c r="E34" t="n">
-        <v>249.7837677001953</v>
+        <v>258.6741027832031</v>
       </c>
       <c r="F34" t="n">
-        <v>7904200</v>
+        <v>6878300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>248.8301503215196</v>
+        <v>258.2668364864311</v>
       </c>
       <c r="C35" t="n">
-        <v>257.5516210443747</v>
+        <v>259.8164350802179</v>
       </c>
       <c r="D35" t="n">
-        <v>248.33348335481</v>
+        <v>253.3995060154779</v>
       </c>
       <c r="E35" t="n">
-        <v>254.9391479492188</v>
+        <v>259.597900390625</v>
       </c>
       <c r="F35" t="n">
-        <v>7767800</v>
+        <v>7054300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>253.1014986048366</v>
+        <v>256.4291570066316</v>
       </c>
       <c r="C36" t="n">
-        <v>260.0747073186972</v>
+        <v>257.5317734711582</v>
       </c>
       <c r="D36" t="n">
-        <v>250.945965708637</v>
+        <v>251.7704334426377</v>
       </c>
       <c r="E36" t="n">
-        <v>258.6741027832031</v>
+        <v>252.743896484375</v>
       </c>
       <c r="F36" t="n">
-        <v>6878300</v>
+        <v>6792200</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>258.2668364864311</v>
+        <v>253.0021749753964</v>
       </c>
       <c r="C37" t="n">
-        <v>259.8164350802179</v>
+        <v>255.1179661572175</v>
       </c>
       <c r="D37" t="n">
-        <v>253.3995060154779</v>
+        <v>250.3301040035887</v>
       </c>
       <c r="E37" t="n">
-        <v>259.597900390625</v>
+        <v>250.9956359863281</v>
       </c>
       <c r="F37" t="n">
-        <v>7054300</v>
+        <v>5241200</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>256.4291570066316</v>
+        <v>248.8698969843938</v>
       </c>
       <c r="C38" t="n">
-        <v>257.5317734711582</v>
+        <v>248.8698969843938</v>
       </c>
       <c r="D38" t="n">
-        <v>251.7704334426377</v>
+        <v>232.9169551584068</v>
       </c>
       <c r="E38" t="n">
-        <v>252.743896484375</v>
+        <v>237.6750335693359</v>
       </c>
       <c r="F38" t="n">
-        <v>6792200</v>
+        <v>11041800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>253.0021595946237</v>
+        <v>234.575813422799</v>
       </c>
       <c r="C39" t="n">
-        <v>255.1179506478194</v>
+        <v>239.3636904840115</v>
       </c>
       <c r="D39" t="n">
-        <v>250.3300887852593</v>
+        <v>234.2182125835504</v>
       </c>
       <c r="E39" t="n">
-        <v>250.9956207275391</v>
+        <v>238.2809600830078</v>
       </c>
       <c r="F39" t="n">
-        <v>5241200</v>
+        <v>5741500</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>248.8698810068921</v>
+        <v>238.4001623159876</v>
       </c>
       <c r="C40" t="n">
-        <v>248.8698810068921</v>
+        <v>240.2974339121167</v>
       </c>
       <c r="D40" t="n">
-        <v>232.9169402050875</v>
+        <v>233.5129608073587</v>
       </c>
       <c r="E40" t="n">
-        <v>237.6750183105469</v>
+        <v>240.0987701416016</v>
       </c>
       <c r="F40" t="n">
-        <v>11041800</v>
+        <v>6486600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>234.575813422799</v>
+        <v>240.2874885014218</v>
       </c>
       <c r="C41" t="n">
-        <v>239.3636904840115</v>
+        <v>244.062160732275</v>
       </c>
       <c r="D41" t="n">
-        <v>234.2182125835504</v>
+        <v>239.5524310420585</v>
       </c>
       <c r="E41" t="n">
-        <v>238.2809600830078</v>
+        <v>242.8701629638672</v>
       </c>
       <c r="F41" t="n">
-        <v>5741500</v>
+        <v>5762800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>238.4001471651486</v>
+        <v>244.1019030924143</v>
       </c>
       <c r="C42" t="n">
-        <v>240.2974186407021</v>
+        <v>246.7739588256813</v>
       </c>
       <c r="D42" t="n">
-        <v>233.5129459671118</v>
+        <v>242.055622316483</v>
       </c>
       <c r="E42" t="n">
-        <v>240.0987548828125</v>
+        <v>244.3800354003906</v>
       </c>
       <c r="F42" t="n">
-        <v>6486600</v>
+        <v>4278200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>240.2874885014218</v>
+        <v>243.6151473457208</v>
       </c>
       <c r="C43" t="n">
-        <v>244.062160732275</v>
+        <v>244.260808340077</v>
       </c>
       <c r="D43" t="n">
-        <v>239.5524310420585</v>
+        <v>238.3107477751567</v>
       </c>
       <c r="E43" t="n">
-        <v>242.8701629638672</v>
+        <v>238.8272705078125</v>
       </c>
       <c r="F43" t="n">
-        <v>5762800</v>
+        <v>5542100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>244.1019030924143</v>
+        <v>236.7214087034764</v>
       </c>
       <c r="C44" t="n">
-        <v>246.7739588256813</v>
+        <v>243.5456080177614</v>
       </c>
       <c r="D44" t="n">
-        <v>242.055622316483</v>
+        <v>235.8373421035805</v>
       </c>
       <c r="E44" t="n">
-        <v>244.3800354003906</v>
+        <v>242.0357513427734</v>
       </c>
       <c r="F44" t="n">
-        <v>4278200</v>
+        <v>5512900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>243.6151473457208</v>
+        <v>240.4563629000066</v>
       </c>
       <c r="C45" t="n">
-        <v>244.260808340077</v>
+        <v>241.2112912653905</v>
       </c>
       <c r="D45" t="n">
-        <v>238.3107477751567</v>
+        <v>234.0195478209803</v>
       </c>
       <c r="E45" t="n">
-        <v>238.8272705078125</v>
+        <v>235.449951171875</v>
       </c>
       <c r="F45" t="n">
-        <v>5542100</v>
+        <v>5280900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>236.7214236272305</v>
+        <v>234.6652065353653</v>
       </c>
       <c r="C46" t="n">
-        <v>243.5456233717372</v>
+        <v>236.2048619582689</v>
       </c>
       <c r="D46" t="n">
-        <v>235.8373569715999</v>
+        <v>228.735001926082</v>
       </c>
       <c r="E46" t="n">
-        <v>242.0357666015625</v>
+        <v>231.9434661865234</v>
       </c>
       <c r="F46" t="n">
-        <v>5512900</v>
+        <v>8045100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>240.4563473167674</v>
+        <v>230.4534777021341</v>
       </c>
       <c r="C47" t="n">
-        <v>241.2112756332267</v>
+        <v>230.7316099971398</v>
       </c>
       <c r="D47" t="n">
-        <v>234.0195326548913</v>
+        <v>223.5597376250506</v>
       </c>
       <c r="E47" t="n">
-        <v>235.4499359130859</v>
+        <v>226.3609466552734</v>
       </c>
       <c r="F47" t="n">
-        <v>5280900</v>
+        <v>9710700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>234.6652219732086</v>
+        <v>227.7218165007521</v>
       </c>
       <c r="C48" t="n">
-        <v>236.204877497401</v>
+        <v>229.5296916323367</v>
       </c>
       <c r="D48" t="n">
-        <v>228.7350169737969</v>
+        <v>221.8114823100099</v>
       </c>
       <c r="E48" t="n">
-        <v>231.9434814453125</v>
+        <v>223.86767578125</v>
       </c>
       <c r="F48" t="n">
-        <v>8045100</v>
+        <v>7521100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>230.453493236797</v>
+        <v>223.3610831021723</v>
       </c>
       <c r="C49" t="n">
-        <v>230.7316255505513</v>
+        <v>227.1556110878527</v>
       </c>
       <c r="D49" t="n">
-        <v>223.5597526950127</v>
+        <v>220.4804205745986</v>
       </c>
       <c r="E49" t="n">
-        <v>226.3609619140625</v>
+        <v>225.5960845947266</v>
       </c>
       <c r="F49" t="n">
-        <v>9710700</v>
+        <v>7479300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>227.7218165007521</v>
+        <v>225.824551950926</v>
       </c>
       <c r="C50" t="n">
-        <v>229.5296916323367</v>
+        <v>227.314552977507</v>
       </c>
       <c r="D50" t="n">
-        <v>221.8114823100099</v>
+        <v>223.5398806787535</v>
       </c>
       <c r="E50" t="n">
-        <v>223.86767578125</v>
+        <v>225.3080291748047</v>
       </c>
       <c r="F50" t="n">
-        <v>7521100</v>
+        <v>8563300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>223.3610679945535</v>
+        <v>225.2881447387201</v>
       </c>
       <c r="C51" t="n">
-        <v>227.1555957235809</v>
+        <v>233.065951449845</v>
       </c>
       <c r="D51" t="n">
-        <v>220.480405661821</v>
+        <v>225.0100124430054</v>
       </c>
       <c r="E51" t="n">
-        <v>225.5960693359375</v>
+        <v>232.5593414306641</v>
       </c>
       <c r="F51" t="n">
-        <v>7479300</v>
+        <v>10233000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>225.824551950926</v>
+        <v>228.9734038653133</v>
       </c>
       <c r="C52" t="n">
-        <v>227.314552977507</v>
+        <v>231.2680180268392</v>
       </c>
       <c r="D52" t="n">
-        <v>223.5398806787535</v>
+        <v>224.493473197433</v>
       </c>
       <c r="E52" t="n">
-        <v>225.3080291748047</v>
+        <v>226.6291351318359</v>
       </c>
       <c r="F52" t="n">
-        <v>8563300</v>
+        <v>8506600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>225.2881447387201</v>
+        <v>227.4734767172409</v>
       </c>
       <c r="C53" t="n">
-        <v>233.065951449845</v>
+        <v>231.0097431878008</v>
       </c>
       <c r="D53" t="n">
-        <v>225.0100124430054</v>
+        <v>227.1059480025027</v>
       </c>
       <c r="E53" t="n">
-        <v>232.5593414306641</v>
+        <v>229.0032043457031</v>
       </c>
       <c r="F53" t="n">
-        <v>10233000</v>
+        <v>3691500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>228.9734038653133</v>
+        <v>227.1456660901873</v>
       </c>
       <c r="C54" t="n">
-        <v>231.2680180268392</v>
+        <v>232.6884711929492</v>
       </c>
       <c r="D54" t="n">
-        <v>224.493473197433</v>
+        <v>227.0761405973358</v>
       </c>
       <c r="E54" t="n">
-        <v>226.6291351318359</v>
+        <v>231.2779388427734</v>
       </c>
       <c r="F54" t="n">
-        <v>8506600</v>
+        <v>5634700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>227.4734767172409</v>
+        <v>231.4666946211142</v>
       </c>
       <c r="C55" t="n">
-        <v>231.0097431878008</v>
+        <v>235.0724867607419</v>
       </c>
       <c r="D55" t="n">
-        <v>227.1059480025027</v>
+        <v>230.0760179166733</v>
       </c>
       <c r="E55" t="n">
-        <v>229.0032043457031</v>
+        <v>233.1454315185547</v>
       </c>
       <c r="F55" t="n">
-        <v>3691500</v>
+        <v>7626200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>227.1456810763456</v>
+        <v>233.7910747516482</v>
       </c>
       <c r="C56" t="n">
-        <v>232.6884865447995</v>
+        <v>237.6650710221251</v>
       </c>
       <c r="D56" t="n">
-        <v>227.0761555789071</v>
+        <v>231.6057431335055</v>
       </c>
       <c r="E56" t="n">
-        <v>231.2779541015625</v>
+        <v>237.1286773681641</v>
       </c>
       <c r="F56" t="n">
-        <v>5634700</v>
+        <v>13782000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>231.4666946211142</v>
+        <v>242.065551586444</v>
       </c>
       <c r="C57" t="n">
-        <v>235.0724867607419</v>
+        <v>247.3103536057372</v>
       </c>
       <c r="D57" t="n">
-        <v>230.0760179166733</v>
+        <v>236.016151496486</v>
       </c>
       <c r="E57" t="n">
-        <v>233.1454315185547</v>
+        <v>245.8104248046875</v>
       </c>
       <c r="F57" t="n">
-        <v>7626200</v>
+        <v>20912100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>233.7910897956687</v>
+        <v>249.1579600621082</v>
       </c>
       <c r="C58" t="n">
-        <v>237.6650863154301</v>
+        <v>260.1343033980639</v>
       </c>
       <c r="D58" t="n">
-        <v>231.605758036904</v>
+        <v>247.8368240708576</v>
       </c>
       <c r="E58" t="n">
-        <v>237.1286926269531</v>
+        <v>258.8330383300781</v>
       </c>
       <c r="F58" t="n">
-        <v>13782000</v>
+        <v>15852400</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>242.065551586444</v>
+        <v>260.134328900545</v>
       </c>
       <c r="C59" t="n">
-        <v>247.3103536057372</v>
+        <v>262.5183245855411</v>
       </c>
       <c r="D59" t="n">
-        <v>236.016151496486</v>
+        <v>254.6312497113514</v>
       </c>
       <c r="E59" t="n">
-        <v>245.8104248046875</v>
+        <v>257.7999877929688</v>
       </c>
       <c r="F59" t="n">
-        <v>20912100</v>
+        <v>10805400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>249.1579600621082</v>
+        <v>258.2668091334806</v>
       </c>
       <c r="C60" t="n">
-        <v>260.1343033980639</v>
+        <v>260.5018103663664</v>
       </c>
       <c r="D60" t="n">
-        <v>247.8368240708576</v>
+        <v>257.273475252198</v>
       </c>
       <c r="E60" t="n">
-        <v>258.8330383300781</v>
+        <v>259.2799987792969</v>
       </c>
       <c r="F60" t="n">
-        <v>15852400</v>
+        <v>8045900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>260.1342981066347</v>
+        <v>259.0117983873967</v>
       </c>
       <c r="C61" t="n">
-        <v>262.5182935094206</v>
+        <v>264.157260395403</v>
       </c>
       <c r="D61" t="n">
-        <v>254.6312195688788</v>
+        <v>257.4224581829772</v>
       </c>
       <c r="E61" t="n">
-        <v>257.7999572753906</v>
+        <v>262.4388122558594</v>
       </c>
       <c r="F61" t="n">
-        <v>10805400</v>
+        <v>8894700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>258.266839531805</v>
+        <v>261.7434937420645</v>
       </c>
       <c r="C62" t="n">
-        <v>260.5018410277533</v>
+        <v>266.1141570244538</v>
       </c>
       <c r="D62" t="n">
-        <v>257.2735055336058</v>
+        <v>259.0316811670522</v>
       </c>
       <c r="E62" t="n">
-        <v>259.280029296875</v>
+        <v>260.6011657714844</v>
       </c>
       <c r="F62" t="n">
-        <v>8045900</v>
+        <v>7783800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>259.0118285064661</v>
+        <v>261.7633737064805</v>
       </c>
       <c r="C63" t="n">
-        <v>264.1572911128101</v>
+        <v>262.7269089319525</v>
       </c>
       <c r="D63" t="n">
-        <v>257.4224881172308</v>
+        <v>259.1707864287312</v>
       </c>
       <c r="E63" t="n">
-        <v>262.4388427734375</v>
+        <v>260.4819946289062</v>
       </c>
       <c r="F63" t="n">
-        <v>8894700</v>
+        <v>6006600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>261.7434937420645</v>
+        <v>259.468759033079</v>
       </c>
       <c r="C64" t="n">
-        <v>266.1141570244538</v>
+        <v>260.5316336613609</v>
       </c>
       <c r="D64" t="n">
-        <v>259.0316811670522</v>
+        <v>251.4028920091002</v>
       </c>
       <c r="E64" t="n">
-        <v>260.6011657714844</v>
+        <v>252.8829650878906</v>
       </c>
       <c r="F64" t="n">
-        <v>7783800</v>
+        <v>10271800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>261.7633737064805</v>
+        <v>252.3068168853155</v>
       </c>
       <c r="C65" t="n">
-        <v>262.7269089319525</v>
+        <v>254.1544185916248</v>
       </c>
       <c r="D65" t="n">
-        <v>259.1707864287312</v>
+        <v>250.4294163738298</v>
       </c>
       <c r="E65" t="n">
-        <v>260.4819946289062</v>
+        <v>253.2107543945312</v>
       </c>
       <c r="F65" t="n">
-        <v>6006600</v>
+        <v>6145300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>259.468759033079</v>
+        <v>254.621288079056</v>
       </c>
       <c r="C66" t="n">
-        <v>260.5316336613609</v>
+        <v>260.223706328179</v>
       </c>
       <c r="D66" t="n">
-        <v>251.4028920091002</v>
+        <v>254.5418346981557</v>
       </c>
       <c r="E66" t="n">
-        <v>252.8829650878906</v>
+        <v>256.4192504882812</v>
       </c>
       <c r="F66" t="n">
-        <v>10271800</v>
+        <v>6269000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>252.3068168853155</v>
+        <v>257.11173830886</v>
       </c>
       <c r="C67" t="n">
-        <v>254.1544185916248</v>
+        <v>258.7533789592764</v>
       </c>
       <c r="D67" t="n">
-        <v>250.4294163738298</v>
+        <v>254.863170050824</v>
       </c>
       <c r="E67" t="n">
-        <v>253.2107543945312</v>
+        <v>256.5446166992188</v>
       </c>
       <c r="F67" t="n">
-        <v>6145300</v>
+        <v>5654200</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>254.621288079056</v>
+        <v>259.3602680955166</v>
       </c>
       <c r="C68" t="n">
-        <v>260.223706328179</v>
+        <v>260.7133987167576</v>
       </c>
       <c r="D68" t="n">
-        <v>254.5418346981557</v>
+        <v>254.2064997708628</v>
       </c>
       <c r="E68" t="n">
-        <v>256.4192504882812</v>
+        <v>258.5941772460938</v>
       </c>
       <c r="F68" t="n">
-        <v>6269000</v>
+        <v>20732100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>257.1117077238193</v>
+        <v>259.3005746010855</v>
       </c>
       <c r="C69" t="n">
-        <v>258.7533481789523</v>
+        <v>263.290283203125</v>
       </c>
       <c r="D69" t="n">
-        <v>254.8631397332645</v>
+        <v>257.1017714973269</v>
       </c>
       <c r="E69" t="n">
-        <v>256.5445861816406</v>
+        <v>263.290283203125</v>
       </c>
       <c r="F69" t="n">
-        <v>5654200</v>
+        <v>5664200</v>
       </c>
       <c r="G69" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>259.3602680955166</v>
+        <v>261.3899469633664</v>
       </c>
       <c r="C70" t="n">
-        <v>260.7133987167576</v>
+        <v>262.9022408344935</v>
       </c>
       <c r="D70" t="n">
-        <v>254.2064997708628</v>
+        <v>259.2010726049517</v>
       </c>
       <c r="E70" t="n">
-        <v>258.5941772460938</v>
+        <v>262.0963439941406</v>
       </c>
       <c r="F70" t="n">
-        <v>20732100</v>
+        <v>4745100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>259.3005746010855</v>
+        <v>261.8973621911715</v>
       </c>
       <c r="C71" t="n">
-        <v>263.290283203125</v>
+        <v>264.9517966936607</v>
       </c>
       <c r="D71" t="n">
-        <v>257.1017714973269</v>
+        <v>261.2207817362974</v>
       </c>
       <c r="E71" t="n">
-        <v>263.290283203125</v>
+        <v>263.9170837402344</v>
       </c>
       <c r="F71" t="n">
-        <v>5664200</v>
+        <v>2076600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>261.3899469633664</v>
+        <v>263.4593915943883</v>
       </c>
       <c r="C72" t="n">
-        <v>262.9022408344935</v>
+        <v>266.5536624648736</v>
       </c>
       <c r="D72" t="n">
-        <v>259.2010726049517</v>
+        <v>263.4593915943883</v>
       </c>
       <c r="E72" t="n">
-        <v>262.0963439941406</v>
+        <v>264.73291015625</v>
       </c>
       <c r="F72" t="n">
-        <v>4745100</v>
+        <v>2456400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>261.8973924752027</v>
+        <v>263.3698474835284</v>
       </c>
       <c r="C73" t="n">
-        <v>264.951827330886</v>
+        <v>267.7475655858019</v>
       </c>
       <c r="D73" t="n">
-        <v>261.2208119420935</v>
+        <v>263.3698474835284</v>
       </c>
       <c r="E73" t="n">
-        <v>263.9171142578125</v>
+        <v>264.8821716308594</v>
       </c>
       <c r="F73" t="n">
-        <v>2076600</v>
+        <v>4300100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>263.4593915943883</v>
+        <v>265.3100049300543</v>
       </c>
       <c r="C74" t="n">
-        <v>266.5536624648736</v>
+        <v>266.9217986247408</v>
       </c>
       <c r="D74" t="n">
-        <v>263.4593915943883</v>
+        <v>263.9867212136458</v>
       </c>
       <c r="E74" t="n">
-        <v>264.73291015625</v>
+        <v>264.5737609863281</v>
       </c>
       <c r="F74" t="n">
-        <v>2456400</v>
+        <v>3291800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>263.3698474835284</v>
+        <v>263.9469286938932</v>
       </c>
       <c r="C75" t="n">
-        <v>267.7475655858019</v>
+        <v>264.7528254896791</v>
       </c>
       <c r="D75" t="n">
-        <v>263.3698474835284</v>
+        <v>263.0514911833619</v>
       </c>
       <c r="E75" t="n">
-        <v>264.8821716308594</v>
+        <v>263.56884765625</v>
       </c>
       <c r="F75" t="n">
-        <v>4300100</v>
+        <v>3367900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>265.3100049300543</v>
+        <v>263.6584060515341</v>
       </c>
       <c r="C76" t="n">
-        <v>266.9217986247408</v>
+        <v>264.0364871145308</v>
       </c>
       <c r="D76" t="n">
-        <v>263.9867212136458</v>
+        <v>251.2017857864946</v>
       </c>
       <c r="E76" t="n">
-        <v>264.5737609863281</v>
+        <v>252.3360137939453</v>
       </c>
       <c r="F76" t="n">
-        <v>3291800</v>
+        <v>9680600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>263.9469286938932</v>
+        <v>252.3359973941062</v>
       </c>
       <c r="C77" t="n">
-        <v>264.7528254896791</v>
+        <v>258.2757743891104</v>
       </c>
       <c r="D77" t="n">
-        <v>263.0514911833619</v>
+        <v>251.0326319383232</v>
       </c>
       <c r="E77" t="n">
-        <v>263.56884765625</v>
+        <v>254.962646484375</v>
       </c>
       <c r="F77" t="n">
-        <v>3367900</v>
+        <v>6421500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>263.6583901080786</v>
+        <v>253.9080159827951</v>
       </c>
       <c r="C78" t="n">
-        <v>264.0364711482127</v>
+        <v>262.2157339851939</v>
       </c>
       <c r="D78" t="n">
-        <v>251.2017705962925</v>
+        <v>253.7090315433827</v>
       </c>
       <c r="E78" t="n">
-        <v>252.3359985351562</v>
+        <v>261.5690307617188</v>
       </c>
       <c r="F78" t="n">
-        <v>9680600</v>
+        <v>6103300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>252.3359973941062</v>
+        <v>262.1659742529432</v>
       </c>
       <c r="C79" t="n">
-        <v>258.2757743891104</v>
+        <v>266.4740393315776</v>
       </c>
       <c r="D79" t="n">
-        <v>251.0326319383232</v>
+        <v>262.1659742529432</v>
       </c>
       <c r="E79" t="n">
-        <v>254.962646484375</v>
+        <v>264.772705078125</v>
       </c>
       <c r="F79" t="n">
-        <v>6421500</v>
+        <v>5976200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>253.9079863590369</v>
+        <v>263.0614317758581</v>
       </c>
       <c r="C80" t="n">
-        <v>262.2157033921641</v>
+        <v>263.8573998812952</v>
       </c>
       <c r="D80" t="n">
-        <v>253.7090019428403</v>
+        <v>259.0916414276884</v>
       </c>
       <c r="E80" t="n">
-        <v>261.5690002441406</v>
+        <v>259.2110290527344</v>
       </c>
       <c r="F80" t="n">
-        <v>6103300</v>
+        <v>5243500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>262.1659742529432</v>
+        <v>258.6837172508962</v>
       </c>
       <c r="C81" t="n">
-        <v>266.4740393315776</v>
+        <v>259.7085015316362</v>
       </c>
       <c r="D81" t="n">
-        <v>262.1659742529432</v>
+        <v>255.2113955316752</v>
       </c>
       <c r="E81" t="n">
-        <v>264.772705078125</v>
+        <v>258.6240234375</v>
       </c>
       <c r="F81" t="n">
-        <v>5976200</v>
+        <v>5174400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>263.0614317758581</v>
+        <v>257.6887621074729</v>
       </c>
       <c r="C82" t="n">
-        <v>263.8573998812952</v>
+        <v>260.2357991803385</v>
       </c>
       <c r="D82" t="n">
-        <v>259.0916414276884</v>
+        <v>254.475118861751</v>
       </c>
       <c r="E82" t="n">
-        <v>259.2110290527344</v>
+        <v>258.0867309570312</v>
       </c>
       <c r="F82" t="n">
-        <v>5243500</v>
+        <v>4927700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>258.6836867262742</v>
+        <v>256.3555659982514</v>
       </c>
       <c r="C83" t="n">
-        <v>259.7084708860899</v>
+        <v>259.5891124457121</v>
       </c>
       <c r="D83" t="n">
-        <v>255.2113654167864</v>
+        <v>239.1431464877683</v>
       </c>
       <c r="E83" t="n">
-        <v>258.6239929199219</v>
+        <v>239.839599609375</v>
       </c>
       <c r="F83" t="n">
-        <v>5174400</v>
+        <v>13661000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>257.6887925779931</v>
+        <v>237.9691070776633</v>
       </c>
       <c r="C84" t="n">
-        <v>260.2358299520341</v>
+        <v>241.0136281082575</v>
       </c>
       <c r="D84" t="n">
-        <v>254.4751489522725</v>
+        <v>235.2628914641447</v>
       </c>
       <c r="E84" t="n">
-        <v>258.0867614746094</v>
+        <v>238.3571472167969</v>
       </c>
       <c r="F84" t="n">
-        <v>4927700</v>
+        <v>10149300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>256.3555659982514</v>
+        <v>235.8200540893699</v>
       </c>
       <c r="C85" t="n">
-        <v>259.5891124457121</v>
+        <v>237.6308321653778</v>
       </c>
       <c r="D85" t="n">
-        <v>239.1431464877683</v>
+        <v>230.4971332136314</v>
       </c>
       <c r="E85" t="n">
-        <v>239.839599609375</v>
+        <v>232.3477172851562</v>
       </c>
       <c r="F85" t="n">
-        <v>13661000</v>
+        <v>11489600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>237.9691070776633</v>
+        <v>231.770650770317</v>
       </c>
       <c r="C86" t="n">
-        <v>241.0136281082575</v>
+        <v>231.770650770317</v>
       </c>
       <c r="D86" t="n">
-        <v>235.2628914641447</v>
+        <v>225.2936141395941</v>
       </c>
       <c r="E86" t="n">
-        <v>238.3571472167969</v>
+        <v>225.9602203369141</v>
       </c>
       <c r="F86" t="n">
-        <v>10149300</v>
+        <v>13902600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>235.8200540893699</v>
+        <v>222.4082902460111</v>
       </c>
       <c r="C87" t="n">
-        <v>237.6308321653778</v>
+        <v>226.7860237285318</v>
       </c>
       <c r="D87" t="n">
-        <v>230.4971332136314</v>
+        <v>218.2494593782326</v>
       </c>
       <c r="E87" t="n">
-        <v>232.3477172851562</v>
+        <v>218.9558715820312</v>
       </c>
       <c r="F87" t="n">
-        <v>11489600</v>
+        <v>13050800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>231.770650770317</v>
+        <v>219.0354531203157</v>
       </c>
       <c r="C88" t="n">
-        <v>231.770650770317</v>
+        <v>222.2590556230766</v>
       </c>
       <c r="D88" t="n">
-        <v>225.2936141395941</v>
+        <v>217.8514904177117</v>
       </c>
       <c r="E88" t="n">
-        <v>225.9602203369141</v>
+        <v>220.4582214355469</v>
       </c>
       <c r="F88" t="n">
-        <v>13902600</v>
+        <v>12616600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>222.4082747466268</v>
+        <v>221.1148825581443</v>
       </c>
       <c r="C89" t="n">
-        <v>226.7860079240682</v>
+        <v>227.5620723478159</v>
       </c>
       <c r="D89" t="n">
-        <v>218.2494441686726</v>
+        <v>219.9905984923716</v>
       </c>
       <c r="E89" t="n">
-        <v>218.9558563232422</v>
+        <v>226.9352569580078</v>
       </c>
       <c r="F89" t="n">
-        <v>13050800</v>
+        <v>9483000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>219.0354531203157</v>
+        <v>225.631887371227</v>
       </c>
       <c r="C90" t="n">
-        <v>222.2590556230766</v>
+        <v>229.6812896074088</v>
       </c>
       <c r="D90" t="n">
-        <v>217.8514904177117</v>
+        <v>225.5025406597253</v>
       </c>
       <c r="E90" t="n">
-        <v>220.4582214355469</v>
+        <v>226.8954620361328</v>
       </c>
       <c r="F90" t="n">
-        <v>12616600</v>
+        <v>9408000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>221.1148825581443</v>
+        <v>228.2684791094572</v>
       </c>
       <c r="C91" t="n">
-        <v>227.5620723478159</v>
+        <v>229.7807881997724</v>
       </c>
       <c r="D91" t="n">
-        <v>219.9905984923716</v>
+        <v>226.4377979473355</v>
       </c>
       <c r="E91" t="n">
-        <v>226.9352569580078</v>
+        <v>228.2386322021484</v>
       </c>
       <c r="F91" t="n">
-        <v>9483000</v>
+        <v>7239600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>225.631887371227</v>
+        <v>230.7657561403177</v>
       </c>
       <c r="C92" t="n">
-        <v>229.6812896074088</v>
+        <v>234.5465208568135</v>
       </c>
       <c r="D92" t="n">
-        <v>225.5025406597253</v>
+        <v>225.1244635603479</v>
       </c>
       <c r="E92" t="n">
-        <v>226.8954620361328</v>
+        <v>227.3730163574219</v>
       </c>
       <c r="F92" t="n">
-        <v>9408000</v>
+        <v>9838400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>228.2684638486727</v>
+        <v>228.2286765757154</v>
       </c>
       <c r="C93" t="n">
-        <v>229.7807728378832</v>
+        <v>230.6861730282261</v>
       </c>
       <c r="D93" t="n">
-        <v>226.4377828089404</v>
+        <v>226.5173831306909</v>
       </c>
       <c r="E93" t="n">
-        <v>228.2386169433594</v>
+        <v>226.8059234619141</v>
       </c>
       <c r="F93" t="n">
-        <v>7239600</v>
+        <v>8465900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>230.7657716267904</v>
+        <v>215.5730693423473</v>
       </c>
       <c r="C94" t="n">
-        <v>234.5465365970097</v>
+        <v>216.1799817205514</v>
       </c>
       <c r="D94" t="n">
-        <v>225.1244786682387</v>
+        <v>207.7230144205324</v>
       </c>
       <c r="E94" t="n">
-        <v>227.3730316162109</v>
+        <v>212.9961853027344</v>
       </c>
       <c r="F94" t="n">
-        <v>9838400</v>
+        <v>18555600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>228.2286765757154</v>
+        <v>213.0757836211538</v>
       </c>
       <c r="C95" t="n">
-        <v>230.6861730282261</v>
+        <v>214.4587459115801</v>
       </c>
       <c r="D95" t="n">
-        <v>226.5173831306909</v>
+        <v>209.9616248999223</v>
       </c>
       <c r="E95" t="n">
-        <v>226.8059234619141</v>
+        <v>211.2152404785156</v>
       </c>
       <c r="F95" t="n">
-        <v>8465900</v>
+        <v>11090400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>215.5730693423473</v>
+        <v>213.2648234781596</v>
       </c>
       <c r="C96" t="n">
-        <v>216.1799817205514</v>
+        <v>215.7919576250148</v>
       </c>
       <c r="D96" t="n">
-        <v>207.7230144205324</v>
+        <v>208.7378555750675</v>
       </c>
       <c r="E96" t="n">
-        <v>212.9961853027344</v>
+        <v>209.7427368164062</v>
       </c>
       <c r="F96" t="n">
-        <v>18555600</v>
+        <v>7950900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>213.0757836211538</v>
+        <v>203.9621583905467</v>
       </c>
       <c r="C97" t="n">
-        <v>214.4587459115801</v>
+        <v>204.5193208819819</v>
       </c>
       <c r="D97" t="n">
-        <v>209.9616248999223</v>
+        <v>192.1323538111565</v>
       </c>
       <c r="E97" t="n">
-        <v>211.2152404785156</v>
+        <v>195.3858032226562</v>
       </c>
       <c r="F97" t="n">
-        <v>11090400</v>
+        <v>20194200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>213.2648234781596</v>
+        <v>192.3313273349262</v>
       </c>
       <c r="C98" t="n">
-        <v>215.7919576250148</v>
+        <v>199.6540664816468</v>
       </c>
       <c r="D98" t="n">
-        <v>208.7378555750675</v>
+        <v>186.3318566210609</v>
       </c>
       <c r="E98" t="n">
-        <v>209.7427368164062</v>
+        <v>198.4302978515625</v>
       </c>
       <c r="F98" t="n">
-        <v>7950900</v>
+        <v>23010000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>203.9621583905467</v>
+        <v>193.0079075172144</v>
       </c>
       <c r="C99" t="n">
-        <v>204.5193208819819</v>
+        <v>198.5497008209625</v>
       </c>
       <c r="D99" t="n">
-        <v>192.1323538111565</v>
+        <v>187.8342210038726</v>
       </c>
       <c r="E99" t="n">
-        <v>195.3858032226562</v>
+        <v>189.0082550048828</v>
       </c>
       <c r="F99" t="n">
-        <v>20194200</v>
+        <v>21956300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>192.3313273349262</v>
+        <v>190.6598526107087</v>
       </c>
       <c r="C100" t="n">
-        <v>199.6540664816468</v>
+        <v>193.614817806995</v>
       </c>
       <c r="D100" t="n">
-        <v>186.3318566210609</v>
+        <v>186.1726753666609</v>
       </c>
       <c r="E100" t="n">
-        <v>198.4302978515625</v>
+        <v>190.3812713623047</v>
       </c>
       <c r="F100" t="n">
-        <v>23010000</v>
+        <v>13652600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>193.0079075172144</v>
+        <v>188.3416494095636</v>
       </c>
       <c r="C101" t="n">
-        <v>198.5497008209625</v>
+        <v>194.2117738895214</v>
       </c>
       <c r="D101" t="n">
-        <v>187.8342210038726</v>
+        <v>184.7897156694265</v>
       </c>
       <c r="E101" t="n">
-        <v>189.0082550048828</v>
+        <v>193.0476989746094</v>
       </c>
       <c r="F101" t="n">
-        <v>21956300</v>
+        <v>12112000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>190.6598526107087</v>
+        <v>190.928470906174</v>
       </c>
       <c r="C102" t="n">
-        <v>193.614817806995</v>
+        <v>198.0920319531629</v>
       </c>
       <c r="D102" t="n">
-        <v>186.1726753666609</v>
+        <v>189.7842990292034</v>
       </c>
       <c r="E102" t="n">
-        <v>190.3812713623047</v>
+        <v>192.4706268310547</v>
       </c>
       <c r="F102" t="n">
-        <v>13652600</v>
+        <v>13393000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>188.3416494095636</v>
+        <v>192.1721331807432</v>
       </c>
       <c r="C103" t="n">
-        <v>194.2117738895214</v>
+        <v>192.6895048269234</v>
       </c>
       <c r="D103" t="n">
-        <v>184.7897156694265</v>
+        <v>180.8895478564994</v>
       </c>
       <c r="E103" t="n">
-        <v>193.0476989746094</v>
+        <v>184.0634002685547</v>
       </c>
       <c r="F103" t="n">
-        <v>12112000</v>
+        <v>16350200</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>190.928470906174</v>
+        <v>185.0185569607285</v>
       </c>
       <c r="C104" t="n">
-        <v>198.0920319531629</v>
+        <v>187.3666097225546</v>
       </c>
       <c r="D104" t="n">
-        <v>189.7842990292034</v>
+        <v>179.3275140834474</v>
       </c>
       <c r="E104" t="n">
-        <v>192.4706268310547</v>
+        <v>184.4912261962891</v>
       </c>
       <c r="F104" t="n">
-        <v>13393000</v>
+        <v>16849100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>192.1721331807432</v>
+        <v>185.4961130882416</v>
       </c>
       <c r="C105" t="n">
-        <v>192.6895048269234</v>
+        <v>192.470618112702</v>
       </c>
       <c r="D105" t="n">
-        <v>180.8895478564994</v>
+        <v>183.3669478683701</v>
       </c>
       <c r="E105" t="n">
-        <v>184.0634002685547</v>
+        <v>188.7595062255859</v>
       </c>
       <c r="F105" t="n">
-        <v>16350200</v>
+        <v>14822900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>185.0185569607285</v>
+        <v>190.0031839153662</v>
       </c>
       <c r="C106" t="n">
-        <v>187.3666097225546</v>
+        <v>192.0229054891486</v>
       </c>
       <c r="D106" t="n">
-        <v>179.3275140834474</v>
+        <v>182.2426696727612</v>
       </c>
       <c r="E106" t="n">
-        <v>184.4912261962891</v>
+        <v>183.3569946289062</v>
       </c>
       <c r="F106" t="n">
-        <v>16849100</v>
+        <v>13692900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>185.4961280832271</v>
+        <v>182.9490856555733</v>
       </c>
       <c r="C107" t="n">
-        <v>192.4706336714869</v>
+        <v>187.1875133215944</v>
       </c>
       <c r="D107" t="n">
-        <v>183.3669626912399</v>
+        <v>180.9393079480809</v>
       </c>
       <c r="E107" t="n">
-        <v>188.759521484375</v>
+        <v>186.8392791748047</v>
       </c>
       <c r="F107" t="n">
-        <v>14822900</v>
+        <v>9852900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>190.0031839153662</v>
+        <v>185.6553247148316</v>
       </c>
       <c r="C108" t="n">
-        <v>192.0229054891486</v>
+        <v>186.0035436955366</v>
       </c>
       <c r="D108" t="n">
-        <v>182.2426696727612</v>
+        <v>182.3023753569564</v>
       </c>
       <c r="E108" t="n">
-        <v>183.3569946289062</v>
+        <v>184.3519439697266</v>
       </c>
       <c r="F108" t="n">
-        <v>13692900</v>
+        <v>9565100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>182.9490856555733</v>
+        <v>184.3817888273663</v>
       </c>
       <c r="C109" t="n">
-        <v>187.1875133215944</v>
+        <v>190.759325420591</v>
       </c>
       <c r="D109" t="n">
-        <v>180.9393079480809</v>
+        <v>182.7998269729231</v>
       </c>
       <c r="E109" t="n">
-        <v>186.8392791748047</v>
+        <v>184.2225952148438</v>
       </c>
       <c r="F109" t="n">
-        <v>9852900</v>
+        <v>10816200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>185.6553247148316</v>
+        <v>180.3522971382107</v>
       </c>
       <c r="C110" t="n">
-        <v>186.0035436955366</v>
+        <v>181.546218918281</v>
       </c>
       <c r="D110" t="n">
-        <v>182.3023753569564</v>
+        <v>173.6862199497409</v>
       </c>
       <c r="E110" t="n">
-        <v>184.3519439697266</v>
+        <v>177.2580413818359</v>
       </c>
       <c r="F110" t="n">
-        <v>9565100</v>
+        <v>15498600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>184.3817888273663</v>
+        <v>176.7406808899958</v>
       </c>
       <c r="C111" t="n">
-        <v>190.759325420591</v>
+        <v>187.7148393068323</v>
       </c>
       <c r="D111" t="n">
-        <v>182.7998269729231</v>
+        <v>175.3875654052501</v>
       </c>
       <c r="E111" t="n">
-        <v>184.2225952148438</v>
+        <v>184.4812927246094</v>
       </c>
       <c r="F111" t="n">
-        <v>10816200</v>
+        <v>15564700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>180.3522971382107</v>
+        <v>182.07353407401</v>
       </c>
       <c r="C112" t="n">
-        <v>181.546218918281</v>
+        <v>191.6249386554261</v>
       </c>
       <c r="D112" t="n">
-        <v>173.6862199497409</v>
+        <v>181.3372749736025</v>
       </c>
       <c r="E112" t="n">
-        <v>177.2580413818359</v>
+        <v>190.7792358398438</v>
       </c>
       <c r="F112" t="n">
-        <v>15498600</v>
+        <v>21875100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>176.7406808899958</v>
+        <v>195.763857285561</v>
       </c>
       <c r="C113" t="n">
-        <v>187.7148393068323</v>
+        <v>200.0221877064004</v>
       </c>
       <c r="D113" t="n">
-        <v>175.3875654052501</v>
+        <v>190.3613550446578</v>
       </c>
       <c r="E113" t="n">
-        <v>184.4812927246094</v>
+        <v>198.4601440429688</v>
       </c>
       <c r="F113" t="n">
-        <v>15564700</v>
+        <v>26680500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>182.07353407401</v>
+        <v>190.9384388957837</v>
       </c>
       <c r="C114" t="n">
-        <v>191.6249386554261</v>
+        <v>194.9281323797358</v>
       </c>
       <c r="D114" t="n">
-        <v>181.3372749736025</v>
+        <v>188.9585080166839</v>
       </c>
       <c r="E114" t="n">
-        <v>190.7792358398438</v>
+        <v>193.8038482666016</v>
       </c>
       <c r="F114" t="n">
-        <v>21875100</v>
+        <v>16346500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>195.763857285561</v>
+        <v>191.5254410161792</v>
       </c>
       <c r="C115" t="n">
-        <v>200.0221877064004</v>
+        <v>194.9480279496185</v>
       </c>
       <c r="D115" t="n">
-        <v>190.3613550446578</v>
+        <v>189.714647741251</v>
       </c>
       <c r="E115" t="n">
-        <v>198.4601440429688</v>
+        <v>191.9731597900391</v>
       </c>
       <c r="F115" t="n">
-        <v>26680500</v>
+        <v>9932700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>190.9384388957837</v>
+        <v>189.7842937679152</v>
       </c>
       <c r="C116" t="n">
-        <v>194.9281323797358</v>
+        <v>197.6641955196137</v>
       </c>
       <c r="D116" t="n">
-        <v>188.9585080166839</v>
+        <v>188.6202189254354</v>
       </c>
       <c r="E116" t="n">
-        <v>193.8038482666016</v>
+        <v>195.0574645996094</v>
       </c>
       <c r="F116" t="n">
-        <v>16346500</v>
+        <v>13208900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>191.5254257929766</v>
+        <v>194.1122708576492</v>
       </c>
       <c r="C117" t="n">
-        <v>194.9480124543751</v>
+        <v>195.4753300833883</v>
       </c>
       <c r="D117" t="n">
-        <v>189.7146326619775</v>
+        <v>191.1274589952447</v>
       </c>
       <c r="E117" t="n">
-        <v>191.97314453125</v>
+        <v>192.1024932861328</v>
       </c>
       <c r="F117" t="n">
-        <v>9932700</v>
+        <v>11583700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>189.7843086141992</v>
+        <v>193.3760143544918</v>
       </c>
       <c r="C118" t="n">
-        <v>197.6642109823198</v>
+        <v>203.3850811696169</v>
       </c>
       <c r="D118" t="n">
-        <v>188.6202336806571</v>
+        <v>193.2566267365104</v>
       </c>
       <c r="E118" t="n">
-        <v>195.0574798583984</v>
+        <v>200.3704223632812</v>
       </c>
       <c r="F118" t="n">
-        <v>13208900</v>
+        <v>15860900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>194.1122862760758</v>
+        <v>199.7734673796906</v>
       </c>
       <c r="C119" t="n">
-        <v>195.4753456100833</v>
+        <v>201.9324948273444</v>
       </c>
       <c r="D119" t="n">
-        <v>191.1274741765864</v>
+        <v>196.3707834039569</v>
       </c>
       <c r="E119" t="n">
-        <v>192.1025085449219</v>
+        <v>201.0867919921875</v>
       </c>
       <c r="F119" t="n">
-        <v>11583700</v>
+        <v>9657400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>193.3760290806364</v>
+        <v>197.5547532603008</v>
       </c>
       <c r="C120" t="n">
-        <v>203.385096657981</v>
+        <v>202.6388836095676</v>
       </c>
       <c r="D120" t="n">
-        <v>193.2566414535633</v>
+        <v>194.8783694210796</v>
       </c>
       <c r="E120" t="n">
-        <v>200.3704376220703</v>
+        <v>197.7835845947266</v>
       </c>
       <c r="F120" t="n">
-        <v>15860900</v>
+        <v>10754800</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>199.7734673796906</v>
+        <v>196.2613420240266</v>
       </c>
       <c r="C121" t="n">
-        <v>201.9324948273444</v>
+        <v>198.5596601232727</v>
       </c>
       <c r="D121" t="n">
-        <v>196.3707834039569</v>
+        <v>189.6350706142157</v>
       </c>
       <c r="E121" t="n">
-        <v>201.0867919921875</v>
+        <v>193.9232482910156</v>
       </c>
       <c r="F121" t="n">
-        <v>9657400</v>
+        <v>14467400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>197.5547685014358</v>
+        <v>195.4056830590209</v>
       </c>
       <c r="C122" t="n">
-        <v>202.6388992429378</v>
+        <v>198.5397447176623</v>
       </c>
       <c r="D122" t="n">
-        <v>194.8783844557345</v>
+        <v>190.3215527599943</v>
       </c>
       <c r="E122" t="n">
-        <v>197.7835998535156</v>
+        <v>193.1471862792969</v>
       </c>
       <c r="F122" t="n">
-        <v>10754800</v>
+        <v>9580000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>196.2613420240266</v>
+        <v>193.1471819093573</v>
       </c>
       <c r="C123" t="n">
-        <v>198.5596601232727</v>
+        <v>203.8228548323795</v>
       </c>
       <c r="D123" t="n">
-        <v>189.6350706142157</v>
+        <v>192.1721324296864</v>
       </c>
       <c r="E123" t="n">
-        <v>193.9232482910156</v>
+        <v>198.2711029052734</v>
       </c>
       <c r="F123" t="n">
-        <v>14467400</v>
+        <v>26309700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>195.4056984962331</v>
+        <v>198.7188210052147</v>
       </c>
       <c r="C124" t="n">
-        <v>198.5397604024679</v>
+        <v>199.9823956164078</v>
       </c>
       <c r="D124" t="n">
-        <v>190.3215677955559</v>
+        <v>190.7792256688866</v>
       </c>
       <c r="E124" t="n">
-        <v>193.1472015380859</v>
+        <v>191.853759765625</v>
       </c>
       <c r="F124" t="n">
-        <v>9580000</v>
+        <v>14834700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>193.1471819093573</v>
+        <v>194.1620237910367</v>
       </c>
       <c r="C125" t="n">
-        <v>203.8228548323795</v>
+        <v>197.6244168069387</v>
       </c>
       <c r="D125" t="n">
-        <v>192.1721324296864</v>
+        <v>194.1620237910367</v>
       </c>
       <c r="E125" t="n">
-        <v>198.2711029052734</v>
+        <v>197.3358764648438</v>
       </c>
       <c r="F125" t="n">
-        <v>26309700</v>
+        <v>13419600</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>198.7188368100057</v>
+        <v>197.2164841210229</v>
       </c>
       <c r="C126" t="n">
-        <v>199.9824115216952</v>
+        <v>201.3554271697534</v>
       </c>
       <c r="D126" t="n">
-        <v>190.7792408422143</v>
+        <v>193.4655660342646</v>
       </c>
       <c r="E126" t="n">
-        <v>191.8537750244141</v>
+        <v>194.3212127685547</v>
       </c>
       <c r="F126" t="n">
-        <v>14834700</v>
+        <v>11559300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>194.1620087776625</v>
+        <v>192.4208813209107</v>
       </c>
       <c r="C127" t="n">
-        <v>197.6244015258386</v>
+        <v>195.1569590889159</v>
       </c>
       <c r="D127" t="n">
-        <v>194.1620087776625</v>
+        <v>191.6647343849253</v>
       </c>
       <c r="E127" t="n">
-        <v>197.3358612060547</v>
+        <v>193.3561248779297</v>
       </c>
       <c r="F127" t="n">
-        <v>13419600</v>
+        <v>10525100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>197.2164841210229</v>
+        <v>194.5997914321279</v>
       </c>
       <c r="C128" t="n">
-        <v>201.3554271697534</v>
+        <v>199.3854376268052</v>
       </c>
       <c r="D128" t="n">
-        <v>193.4655660342646</v>
+        <v>192.3213915946813</v>
       </c>
       <c r="E128" t="n">
-        <v>194.3212127685547</v>
+        <v>194.0028381347656</v>
       </c>
       <c r="F128" t="n">
-        <v>11559300</v>
+        <v>9254300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>192.4208813209107</v>
+        <v>192.2318417698426</v>
       </c>
       <c r="C129" t="n">
-        <v>195.1569590889159</v>
+        <v>194.6793790179939</v>
       </c>
       <c r="D129" t="n">
-        <v>191.6647343849253</v>
+        <v>189.0380863676492</v>
       </c>
       <c r="E129" t="n">
-        <v>193.3561248779297</v>
+        <v>194.3908538818359</v>
       </c>
       <c r="F129" t="n">
-        <v>10525100</v>
+        <v>20201100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>194.5997914321279</v>
+        <v>196.0921979891633</v>
       </c>
       <c r="C130" t="n">
-        <v>199.3854376268052</v>
+        <v>197.0473445217343</v>
       </c>
       <c r="D130" t="n">
-        <v>192.3213915946813</v>
+        <v>191.0279705387624</v>
       </c>
       <c r="E130" t="n">
-        <v>194.0028381347656</v>
+        <v>194.1918640136719</v>
       </c>
       <c r="F130" t="n">
-        <v>9254300</v>
+        <v>13976200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>192.2318417698426</v>
+        <v>191.1672689357976</v>
       </c>
       <c r="C131" t="n">
-        <v>194.6793790179939</v>
+        <v>191.1672689357976</v>
       </c>
       <c r="D131" t="n">
-        <v>189.0380863676492</v>
+        <v>181.3671296009816</v>
       </c>
       <c r="E131" t="n">
-        <v>194.3908538818359</v>
+        <v>182.0934448242188</v>
       </c>
       <c r="F131" t="n">
-        <v>20201100</v>
+        <v>18631400</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>196.0921979891633</v>
+        <v>184.7598589955983</v>
       </c>
       <c r="C132" t="n">
-        <v>197.0473445217343</v>
+        <v>186.4413055109877</v>
       </c>
       <c r="D132" t="n">
-        <v>191.0279705387624</v>
+        <v>178.9394847287185</v>
       </c>
       <c r="E132" t="n">
-        <v>194.1918640136719</v>
+        <v>181.0388031005859</v>
       </c>
       <c r="F132" t="n">
-        <v>13976200</v>
+        <v>12565200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>191.1672689357976</v>
+        <v>180.2627525283908</v>
       </c>
       <c r="C133" t="n">
-        <v>191.1672689357976</v>
+        <v>186.5209173345002</v>
       </c>
       <c r="D133" t="n">
-        <v>181.3671296009816</v>
+        <v>178.621111875675</v>
       </c>
       <c r="E133" t="n">
-        <v>182.0934448242188</v>
+        <v>184.7001800537109</v>
       </c>
       <c r="F133" t="n">
-        <v>18631400</v>
+        <v>10330700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>184.7598589955983</v>
+        <v>183.0684648284524</v>
       </c>
       <c r="C134" t="n">
-        <v>186.4413055109877</v>
+        <v>183.1779085396875</v>
       </c>
       <c r="D134" t="n">
-        <v>178.9394847287185</v>
+        <v>177.9146968557465</v>
       </c>
       <c r="E134" t="n">
-        <v>181.0388031005859</v>
+        <v>178.4022064208984</v>
       </c>
       <c r="F134" t="n">
-        <v>12565200</v>
+        <v>9902000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>180.2627525283908</v>
+        <v>179.1882128832653</v>
       </c>
       <c r="C135" t="n">
-        <v>186.5209173345002</v>
+        <v>185.4463617882801</v>
       </c>
       <c r="D135" t="n">
-        <v>178.621111875675</v>
+        <v>178.670841239089</v>
       </c>
       <c r="E135" t="n">
-        <v>184.7001800537109</v>
+        <v>184.0932464599609</v>
       </c>
       <c r="F135" t="n">
-        <v>10330700</v>
+        <v>11617700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>183.0684804863479</v>
+        <v>183.9639169002118</v>
       </c>
       <c r="C136" t="n">
-        <v>183.1779242069437</v>
+        <v>187.5456975682965</v>
       </c>
       <c r="D136" t="n">
-        <v>177.9147120728387</v>
+        <v>181.3870327098191</v>
       </c>
       <c r="E136" t="n">
-        <v>178.4022216796875</v>
+        <v>185.7249603271484</v>
       </c>
       <c r="F136" t="n">
-        <v>9902000</v>
+        <v>11041400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>179.1882128832653</v>
+        <v>185.904046779924</v>
       </c>
       <c r="C137" t="n">
-        <v>185.4463617882801</v>
+        <v>188.0232529761809</v>
       </c>
       <c r="D137" t="n">
-        <v>178.670841239089</v>
+        <v>182.0834758824893</v>
       </c>
       <c r="E137" t="n">
-        <v>184.0932464599609</v>
+        <v>185.2971343994141</v>
       </c>
       <c r="F137" t="n">
-        <v>11617700</v>
+        <v>11677700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>183.9639017861065</v>
+        <v>184.3619041015049</v>
       </c>
       <c r="C138" t="n">
-        <v>187.5456821599193</v>
+        <v>186.6303601693813</v>
       </c>
       <c r="D138" t="n">
-        <v>181.3870178074254</v>
+        <v>180.6607357420139</v>
       </c>
       <c r="E138" t="n">
-        <v>185.7249450683594</v>
+        <v>186.2323760986328</v>
       </c>
       <c r="F138" t="n">
-        <v>11041400</v>
+        <v>11635500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>185.904046779924</v>
+        <v>186.5507427928755</v>
       </c>
       <c r="C139" t="n">
-        <v>188.0232529761809</v>
+        <v>187.187502054347</v>
       </c>
       <c r="D139" t="n">
-        <v>182.0834758824893</v>
+        <v>182.670493415399</v>
       </c>
       <c r="E139" t="n">
-        <v>185.2971343994141</v>
+        <v>184.0932464599609</v>
       </c>
       <c r="F139" t="n">
-        <v>11677700</v>
+        <v>14391000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>184.3618889959713</v>
+        <v>184.0136681409698</v>
       </c>
       <c r="C140" t="n">
-        <v>186.6303448779838</v>
+        <v>185.635420952666</v>
       </c>
       <c r="D140" t="n">
-        <v>180.6607209397324</v>
+        <v>181.098508861202</v>
       </c>
       <c r="E140" t="n">
-        <v>186.2323608398438</v>
+        <v>182.0337524414062</v>
       </c>
       <c r="F140" t="n">
-        <v>11635500</v>
+        <v>12344600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>186.5507427928755</v>
+        <v>185.5558006932337</v>
       </c>
       <c r="C141" t="n">
-        <v>187.187502054347</v>
+        <v>185.8244380067301</v>
       </c>
       <c r="D141" t="n">
-        <v>182.670493415399</v>
+        <v>174.890071953609</v>
       </c>
       <c r="E141" t="n">
-        <v>184.0932464599609</v>
+        <v>175.4770812988281</v>
       </c>
       <c r="F141" t="n">
-        <v>14391000</v>
+        <v>13472100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,25 +4109,25 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>184.0136681409698</v>
+        <v>172.7242064751902</v>
       </c>
       <c r="C142" t="n">
-        <v>185.635420952666</v>
+        <v>173.8413183878644</v>
       </c>
       <c r="D142" t="n">
-        <v>181.098508861202</v>
+        <v>166.6897779521393</v>
       </c>
       <c r="E142" t="n">
-        <v>182.0337524414062</v>
+        <v>170.4101867675781</v>
       </c>
       <c r="F142" t="n">
-        <v>12344600</v>
+        <v>20855400</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>185.5558168284281</v>
+        <v>170.8191086768984</v>
       </c>
       <c r="C143" t="n">
-        <v>185.8244541652842</v>
+        <v>170.8191086768984</v>
       </c>
       <c r="D143" t="n">
-        <v>174.890087161354</v>
+        <v>163.0990440067395</v>
       </c>
       <c r="E143" t="n">
-        <v>175.4770965576172</v>
+        <v>164.5353393554688</v>
       </c>
       <c r="F143" t="n">
-        <v>13472100</v>
+        <v>18109300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,25 +4161,25 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>172.7242064751902</v>
+        <v>166.619956593861</v>
       </c>
       <c r="C144" t="n">
-        <v>173.8413183878644</v>
+        <v>172.9536002909039</v>
       </c>
       <c r="D144" t="n">
-        <v>166.6897779521393</v>
+        <v>165.3432529892489</v>
       </c>
       <c r="E144" t="n">
-        <v>170.4101867675781</v>
+        <v>172.3751068115234</v>
       </c>
       <c r="F144" t="n">
-        <v>20855400</v>
+        <v>12390800</v>
       </c>
       <c r="G144" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>170.8191086768984</v>
+        <v>174.7589572577855</v>
       </c>
       <c r="C145" t="n">
-        <v>170.8191086768984</v>
+        <v>177.043055331393</v>
       </c>
       <c r="D145" t="n">
-        <v>163.0990440067395</v>
+        <v>170.0610756845212</v>
       </c>
       <c r="E145" t="n">
-        <v>164.5353393554688</v>
+        <v>170.8689880371094</v>
       </c>
       <c r="F145" t="n">
-        <v>18109300</v>
+        <v>13123600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>166.619956593861</v>
+        <v>173.771503335319</v>
       </c>
       <c r="C146" t="n">
-        <v>172.9536002909039</v>
+        <v>179.157595924108</v>
       </c>
       <c r="D146" t="n">
-        <v>165.3432529892489</v>
+        <v>172.4349565756613</v>
       </c>
       <c r="E146" t="n">
-        <v>172.3751068115234</v>
+        <v>177.1428070068359</v>
       </c>
       <c r="F146" t="n">
-        <v>12390800</v>
+        <v>14340300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>174.7589572577855</v>
+        <v>183.5263211162543</v>
       </c>
       <c r="C147" t="n">
-        <v>177.043055331393</v>
+        <v>184.0749082721881</v>
       </c>
       <c r="D147" t="n">
-        <v>170.0610756845212</v>
+        <v>178.110307097372</v>
       </c>
       <c r="E147" t="n">
-        <v>170.8689880371094</v>
+        <v>180.7534790039062</v>
       </c>
       <c r="F147" t="n">
-        <v>13123600</v>
+        <v>11866700</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>173.771503335319</v>
+        <v>184.9526358387744</v>
       </c>
       <c r="C148" t="n">
-        <v>179.157595924108</v>
+        <v>187.4960743570736</v>
       </c>
       <c r="D148" t="n">
-        <v>172.4349565756613</v>
+        <v>180.5639689511464</v>
       </c>
       <c r="E148" t="n">
-        <v>177.1428070068359</v>
+        <v>181.6711120605469</v>
       </c>
       <c r="F148" t="n">
-        <v>14340300</v>
+        <v>17225700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>183.5263211162543</v>
+        <v>182.0301825754578</v>
       </c>
       <c r="C149" t="n">
-        <v>184.0749082721881</v>
+        <v>188.5134493521179</v>
       </c>
       <c r="D149" t="n">
-        <v>178.110307097372</v>
+        <v>181.6511559551952</v>
       </c>
       <c r="E149" t="n">
-        <v>180.7534790039062</v>
+        <v>185.7904815673828</v>
       </c>
       <c r="F149" t="n">
-        <v>11866700</v>
+        <v>14382300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>184.9526358387744</v>
+        <v>186.1196295624439</v>
       </c>
       <c r="C150" t="n">
-        <v>187.4960743570736</v>
+        <v>193.0617034585096</v>
       </c>
       <c r="D150" t="n">
-        <v>180.5639689511464</v>
+        <v>183.6260654751631</v>
       </c>
       <c r="E150" t="n">
-        <v>181.6711120605469</v>
+        <v>186.6283111572266</v>
       </c>
       <c r="F150" t="n">
-        <v>17225700</v>
+        <v>12073700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>182.0301825754578</v>
+        <v>187.7155141554787</v>
       </c>
       <c r="C151" t="n">
-        <v>188.5134493521179</v>
+        <v>190.6579169337777</v>
       </c>
       <c r="D151" t="n">
-        <v>181.6511559551952</v>
+        <v>186.5485279099638</v>
       </c>
       <c r="E151" t="n">
-        <v>185.7904815673828</v>
+        <v>189.3114013671875</v>
       </c>
       <c r="F151" t="n">
-        <v>14382300</v>
+        <v>14565900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>186.1196295624439</v>
+        <v>177.1028943275062</v>
       </c>
       <c r="C152" t="n">
-        <v>193.0617034585096</v>
+        <v>178.4095194817015</v>
       </c>
       <c r="D152" t="n">
-        <v>183.6260654751631</v>
+        <v>170.2106794975899</v>
       </c>
       <c r="E152" t="n">
-        <v>186.6283111572266</v>
+        <v>172.8538665771484</v>
       </c>
       <c r="F152" t="n">
-        <v>12073700</v>
+        <v>22719900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>187.7155141554787</v>
+        <v>175.1678853418476</v>
       </c>
       <c r="C153" t="n">
-        <v>190.6579169337777</v>
+        <v>177.9906017183548</v>
       </c>
       <c r="D153" t="n">
-        <v>186.5485279099638</v>
+        <v>173.9510248482436</v>
       </c>
       <c r="E153" t="n">
-        <v>189.3114013671875</v>
+        <v>177.7013549804688</v>
       </c>
       <c r="F153" t="n">
-        <v>14565900</v>
+        <v>10817600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>177.1028943275062</v>
+        <v>177.8011004808986</v>
       </c>
       <c r="C154" t="n">
-        <v>178.4095194817015</v>
+        <v>183.81557625727</v>
       </c>
       <c r="D154" t="n">
-        <v>170.2106794975899</v>
+        <v>177.0530312030464</v>
       </c>
       <c r="E154" t="n">
-        <v>172.8538665771484</v>
+        <v>179.7161560058594</v>
       </c>
       <c r="F154" t="n">
-        <v>22719900</v>
+        <v>11907000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>175.1678853418476</v>
+        <v>181.960353565993</v>
       </c>
       <c r="C155" t="n">
-        <v>177.9906017183548</v>
+        <v>183.9452360835181</v>
       </c>
       <c r="D155" t="n">
-        <v>173.9510248482436</v>
+        <v>180.8532257080078</v>
       </c>
       <c r="E155" t="n">
-        <v>177.7013549804688</v>
+        <v>180.8532257080078</v>
       </c>
       <c r="F155" t="n">
-        <v>10817600</v>
+        <v>8711700</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>177.8011004808986</v>
+        <v>178.7386749127982</v>
       </c>
       <c r="C156" t="n">
-        <v>183.81557625727</v>
+        <v>181.3120349373997</v>
       </c>
       <c r="D156" t="n">
-        <v>177.0530312030464</v>
+        <v>176.8934465767579</v>
       </c>
       <c r="E156" t="n">
-        <v>179.7161560058594</v>
+        <v>180.7534790039062</v>
       </c>
       <c r="F156" t="n">
-        <v>11907000</v>
+        <v>6882800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>181.960353565993</v>
+        <v>177.8409939014207</v>
       </c>
       <c r="C157" t="n">
-        <v>183.9452360835181</v>
+        <v>178.2299892905901</v>
       </c>
       <c r="D157" t="n">
-        <v>180.8532257080078</v>
+        <v>172.5546349879463</v>
       </c>
       <c r="E157" t="n">
-        <v>180.8532257080078</v>
+        <v>176.0755462646484</v>
       </c>
       <c r="F157" t="n">
-        <v>8711700</v>
+        <v>14408300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>178.7386749127982</v>
+        <v>181.7209929763659</v>
       </c>
       <c r="C158" t="n">
-        <v>181.3120349373997</v>
+        <v>185.5610728373815</v>
       </c>
       <c r="D158" t="n">
-        <v>176.8934465767579</v>
+        <v>178.2898460906057</v>
       </c>
       <c r="E158" t="n">
-        <v>180.7534790039062</v>
+        <v>183.3468017578125</v>
       </c>
       <c r="F158" t="n">
-        <v>6882800</v>
+        <v>12324400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>177.8409939014207</v>
+        <v>183.7657043950053</v>
       </c>
       <c r="C159" t="n">
-        <v>178.2299892905901</v>
+        <v>189.8200700827938</v>
       </c>
       <c r="D159" t="n">
-        <v>172.5546349879463</v>
+        <v>183.4963952122052</v>
       </c>
       <c r="E159" t="n">
-        <v>176.0755462646484</v>
+        <v>185.0025024414062</v>
       </c>
       <c r="F159" t="n">
-        <v>14408300</v>
+        <v>8444700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>181.7209929763659</v>
+        <v>185.0723410364737</v>
       </c>
       <c r="C160" t="n">
-        <v>185.5610728373815</v>
+        <v>186.9076006654211</v>
       </c>
       <c r="D160" t="n">
-        <v>178.2898460906057</v>
+        <v>180.6337997307826</v>
       </c>
       <c r="E160" t="n">
-        <v>183.3468017578125</v>
+        <v>186.5086364746094</v>
       </c>
       <c r="F160" t="n">
-        <v>12324400</v>
+        <v>9740800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>183.7657043950053</v>
+        <v>185.0424114227766</v>
       </c>
       <c r="C161" t="n">
-        <v>189.8200700827938</v>
+        <v>186.6183457810002</v>
       </c>
       <c r="D161" t="n">
-        <v>183.4963952122052</v>
+        <v>179.117700608299</v>
       </c>
       <c r="E161" t="n">
-        <v>185.0025024414062</v>
+        <v>180.7235565185547</v>
       </c>
       <c r="F161" t="n">
-        <v>8444700</v>
+        <v>11303400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>185.0723410364737</v>
+        <v>184.124779650284</v>
       </c>
       <c r="C162" t="n">
-        <v>186.9076006654211</v>
+        <v>188.0945294450444</v>
       </c>
       <c r="D162" t="n">
-        <v>180.6337997307826</v>
+        <v>183.5263181771209</v>
       </c>
       <c r="E162" t="n">
-        <v>186.5086364746094</v>
+        <v>185.8602905273438</v>
       </c>
       <c r="F162" t="n">
-        <v>9740800</v>
+        <v>13955100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>185.0424114227766</v>
+        <v>179.2174384093688</v>
       </c>
       <c r="C163" t="n">
-        <v>186.6183457810002</v>
+        <v>181.40180307799</v>
       </c>
       <c r="D163" t="n">
-        <v>179.117700608299</v>
+        <v>176.424658688263</v>
       </c>
       <c r="E163" t="n">
-        <v>180.7235565185547</v>
+        <v>181.3519439697266</v>
       </c>
       <c r="F163" t="n">
-        <v>11303400</v>
+        <v>15123900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>184.124779650284</v>
+        <v>179.4468492598589</v>
       </c>
       <c r="C164" t="n">
-        <v>188.0945294450444</v>
+        <v>182.0301779962749</v>
       </c>
       <c r="D164" t="n">
-        <v>183.5263181771209</v>
+        <v>175.8561108937732</v>
       </c>
       <c r="E164" t="n">
-        <v>185.8602905273438</v>
+        <v>177.0330810546875</v>
       </c>
       <c r="F164" t="n">
-        <v>13955100</v>
+        <v>11145000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>179.2174384093688</v>
+        <v>177.122851210841</v>
       </c>
       <c r="C165" t="n">
-        <v>181.40180307799</v>
+        <v>177.122851210841</v>
       </c>
       <c r="D165" t="n">
-        <v>176.424658688263</v>
+        <v>170.1408715639692</v>
       </c>
       <c r="E165" t="n">
-        <v>181.3519439697266</v>
+        <v>170.8689880371094</v>
       </c>
       <c r="F165" t="n">
-        <v>15123900</v>
+        <v>10214000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>179.4468492598589</v>
+        <v>169.3429302825834</v>
       </c>
       <c r="C166" t="n">
-        <v>182.0301779962749</v>
+        <v>169.3429302825834</v>
       </c>
       <c r="D166" t="n">
-        <v>175.8561108937732</v>
+        <v>164.3258803430835</v>
       </c>
       <c r="E166" t="n">
-        <v>177.0330810546875</v>
+        <v>165.4130706787109</v>
       </c>
       <c r="F166" t="n">
-        <v>11145000</v>
+        <v>11951900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>177.122851210841</v>
+        <v>165.5726557549663</v>
       </c>
       <c r="C167" t="n">
-        <v>177.122851210841</v>
+        <v>168.914037726981</v>
       </c>
       <c r="D167" t="n">
-        <v>170.1408715639692</v>
+        <v>163.9069567673868</v>
       </c>
       <c r="E167" t="n">
-        <v>170.8689880371094</v>
+        <v>167.1485900878906</v>
       </c>
       <c r="F167" t="n">
-        <v>10214000</v>
+        <v>9749400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>169.3429302825834</v>
+        <v>168.8142960637846</v>
       </c>
       <c r="C168" t="n">
-        <v>169.3429302825834</v>
+        <v>175.5169978399782</v>
       </c>
       <c r="D168" t="n">
-        <v>164.3258803430835</v>
+        <v>168.5649396441926</v>
       </c>
       <c r="E168" t="n">
-        <v>165.4130706787109</v>
+        <v>173.0633239746094</v>
       </c>
       <c r="F168" t="n">
-        <v>11951900</v>
+        <v>13883400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>165.5726557549663</v>
+        <v>172.444927913041</v>
       </c>
       <c r="C169" t="n">
-        <v>168.914037726981</v>
+        <v>180.3146160429799</v>
       </c>
       <c r="D169" t="n">
-        <v>163.9069567673868</v>
+        <v>171.3577375574589</v>
       </c>
       <c r="E169" t="n">
-        <v>167.1485900878906</v>
+        <v>179.0179595947266</v>
       </c>
       <c r="F169" t="n">
-        <v>9749400</v>
+        <v>13671200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>168.8142960637846</v>
+        <v>184.5237517741468</v>
       </c>
       <c r="C170" t="n">
-        <v>175.5169978399782</v>
+        <v>186.9574728813163</v>
       </c>
       <c r="D170" t="n">
-        <v>168.5649396441926</v>
+        <v>178.3496843472311</v>
       </c>
       <c r="E170" t="n">
-        <v>173.0633239746094</v>
+        <v>178.9581146240234</v>
       </c>
       <c r="F170" t="n">
-        <v>13883400</v>
+        <v>17510800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>172.444927913041</v>
+        <v>175.5868068261091</v>
       </c>
       <c r="C171" t="n">
-        <v>180.3146160429799</v>
+        <v>179.8458186639284</v>
       </c>
       <c r="D171" t="n">
-        <v>171.3577375574589</v>
+        <v>172.8937605828528</v>
       </c>
       <c r="E171" t="n">
-        <v>179.0179595947266</v>
+        <v>179.6363677978516</v>
       </c>
       <c r="F171" t="n">
-        <v>13671200</v>
+        <v>13025300</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>184.5237517741468</v>
+        <v>174.9285262709738</v>
       </c>
       <c r="C172" t="n">
-        <v>186.9574728813163</v>
+        <v>176.8834721439062</v>
       </c>
       <c r="D172" t="n">
-        <v>178.3496843472311</v>
+        <v>171.547253715491</v>
       </c>
       <c r="E172" t="n">
-        <v>178.9581146240234</v>
+        <v>175.8561248779297</v>
       </c>
       <c r="F172" t="n">
-        <v>17510800</v>
+        <v>10949100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>175.5868068261091</v>
+        <v>179.3770264534069</v>
       </c>
       <c r="C173" t="n">
-        <v>179.8458186639284</v>
+        <v>182.8780002490095</v>
       </c>
       <c r="D173" t="n">
-        <v>172.8937605828528</v>
+        <v>177.222583382191</v>
       </c>
       <c r="E173" t="n">
-        <v>179.6363677978516</v>
+        <v>179.6064453125</v>
       </c>
       <c r="F173" t="n">
-        <v>13025300</v>
+        <v>10176700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>174.9285262709738</v>
+        <v>177.9706522299692</v>
       </c>
       <c r="C174" t="n">
-        <v>176.8834721439062</v>
+        <v>181.890542966362</v>
       </c>
       <c r="D174" t="n">
-        <v>171.547253715491</v>
+        <v>177.222582989082</v>
       </c>
       <c r="E174" t="n">
-        <v>175.8561248779297</v>
+        <v>178.6189880371094</v>
       </c>
       <c r="F174" t="n">
-        <v>10949100</v>
+        <v>13617200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>179.3770264534069</v>
+        <v>177.5417683468011</v>
       </c>
       <c r="C175" t="n">
-        <v>182.8780002490095</v>
+        <v>183.4465264564886</v>
       </c>
       <c r="D175" t="n">
-        <v>177.222583382191</v>
+        <v>176.4346252500155</v>
       </c>
       <c r="E175" t="n">
-        <v>179.6064453125</v>
+        <v>177.0530242919922</v>
       </c>
       <c r="F175" t="n">
-        <v>10176700</v>
+        <v>18524900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>177.9706522299692</v>
+        <v>177.9706529497301</v>
       </c>
       <c r="C176" t="n">
-        <v>181.890542966362</v>
+        <v>182.0102299107596</v>
       </c>
       <c r="D176" t="n">
-        <v>177.222582989082</v>
+        <v>171.2081082023211</v>
       </c>
       <c r="E176" t="n">
-        <v>178.6189880371094</v>
+        <v>175.7164764404297</v>
       </c>
       <c r="F176" t="n">
-        <v>13617200</v>
+        <v>22559400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>177.5417683468011</v>
+        <v>179.7760043356117</v>
       </c>
       <c r="C177" t="n">
-        <v>183.4465264564886</v>
+        <v>193.6402147597182</v>
       </c>
       <c r="D177" t="n">
-        <v>176.4346252500155</v>
+        <v>179.5565694754165</v>
       </c>
       <c r="E177" t="n">
-        <v>177.0530242919922</v>
+        <v>190.6080474853516</v>
       </c>
       <c r="F177" t="n">
-        <v>18524900</v>
+        <v>33998900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>177.9706529497301</v>
+        <v>198.2383502861678</v>
       </c>
       <c r="C178" t="n">
-        <v>182.0102299107596</v>
+        <v>210.7959357157644</v>
       </c>
       <c r="D178" t="n">
-        <v>171.2081082023211</v>
+        <v>197.69974712537</v>
       </c>
       <c r="E178" t="n">
-        <v>175.7164764404297</v>
+        <v>209.0604248046875</v>
       </c>
       <c r="F178" t="n">
-        <v>22559400</v>
+        <v>27594800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>179.7760043356117</v>
+        <v>200.5025120636997</v>
       </c>
       <c r="C179" t="n">
-        <v>193.6402147597182</v>
+        <v>203.8638316949671</v>
       </c>
       <c r="D179" t="n">
-        <v>179.5565694754165</v>
+        <v>195.2560433089883</v>
       </c>
       <c r="E179" t="n">
-        <v>190.6080474853516</v>
+        <v>200.3229675292969</v>
       </c>
       <c r="F179" t="n">
-        <v>33998900</v>
+        <v>19216600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>198.2383502861678</v>
+        <v>196.7621671181547</v>
       </c>
       <c r="C180" t="n">
-        <v>210.7959357157644</v>
+        <v>197.1711000779736</v>
       </c>
       <c r="D180" t="n">
-        <v>197.69974712537</v>
+        <v>189.2415690076627</v>
       </c>
       <c r="E180" t="n">
-        <v>209.0604248046875</v>
+        <v>190.1193084716797</v>
       </c>
       <c r="F180" t="n">
-        <v>27594800</v>
+        <v>14154400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>200.5025120636997</v>
+        <v>197.3007734437849</v>
       </c>
       <c r="C181" t="n">
-        <v>203.8638316949671</v>
+        <v>197.5800514196224</v>
       </c>
       <c r="D181" t="n">
-        <v>195.2560433089883</v>
+        <v>185.6308959064055</v>
       </c>
       <c r="E181" t="n">
-        <v>200.3229675292969</v>
+        <v>188.2640991210938</v>
       </c>
       <c r="F181" t="n">
-        <v>19216600</v>
+        <v>14453600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>196.7621671181547</v>
+        <v>189.311394256529</v>
       </c>
       <c r="C182" t="n">
-        <v>197.1711000779736</v>
+        <v>192.0144092856922</v>
       </c>
       <c r="D182" t="n">
-        <v>189.2415690076627</v>
+        <v>184.3541874840329</v>
       </c>
       <c r="E182" t="n">
-        <v>190.1193084716797</v>
+        <v>185.1820526123047</v>
       </c>
       <c r="F182" t="n">
-        <v>14154400</v>
+        <v>13183900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>197.3007734437849</v>
+        <v>183.4365624142317</v>
       </c>
       <c r="C183" t="n">
-        <v>197.5800514196224</v>
+        <v>184.543705539598</v>
       </c>
       <c r="D183" t="n">
-        <v>185.6308959064055</v>
+        <v>181.2422289387738</v>
       </c>
       <c r="E183" t="n">
-        <v>188.2640991210938</v>
+        <v>182.0800628662109</v>
       </c>
       <c r="F183" t="n">
-        <v>14453600</v>
+        <v>11177800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>189.311394256529</v>
+        <v>179.0379159792888</v>
       </c>
       <c r="C184" t="n">
-        <v>192.0144092856922</v>
+        <v>181.9903027945282</v>
       </c>
       <c r="D184" t="n">
-        <v>184.3541874840329</v>
+        <v>171.1183533610167</v>
       </c>
       <c r="E184" t="n">
-        <v>185.1820526123047</v>
+        <v>174.8986053466797</v>
       </c>
       <c r="F184" t="n">
-        <v>13183900</v>
+        <v>15427800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>183.4365624142317</v>
+        <v>170.1608274234686</v>
       </c>
       <c r="C185" t="n">
-        <v>184.543705539598</v>
+        <v>175.0781287299737</v>
       </c>
       <c r="D185" t="n">
-        <v>181.2422289387738</v>
+        <v>169.59228747941</v>
       </c>
       <c r="E185" t="n">
-        <v>182.0800628662109</v>
+        <v>170.4799957275391</v>
       </c>
       <c r="F185" t="n">
-        <v>11177800</v>
+        <v>10820500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>179.0379159792888</v>
+        <v>168.2700042724609</v>
       </c>
       <c r="C186" t="n">
-        <v>181.9903027945282</v>
+        <v>168.9799957275391</v>
       </c>
       <c r="D186" t="n">
-        <v>171.1183533610167</v>
+        <v>163.3099975585938</v>
       </c>
       <c r="E186" t="n">
-        <v>174.8986053466797</v>
+        <v>166.4499969482422</v>
       </c>
       <c r="F186" t="n">
-        <v>15427800</v>
+        <v>16666000</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>170.1608274234686</v>
+        <v>164.7400054931641</v>
       </c>
       <c r="C187" t="n">
-        <v>175.0781287299737</v>
+        <v>166.5399932861328</v>
       </c>
       <c r="D187" t="n">
-        <v>169.59228747941</v>
+        <v>161.3999938964844</v>
       </c>
       <c r="E187" t="n">
-        <v>170.4799957275391</v>
+        <v>165.8899993896484</v>
       </c>
       <c r="F187" t="n">
-        <v>10820500</v>
+        <v>13589400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>168.2700042724609</v>
+        <v>166.0299987792969</v>
       </c>
       <c r="C188" t="n">
-        <v>168.9799957275391</v>
+        <v>169.9499969482422</v>
       </c>
       <c r="D188" t="n">
-        <v>163.3099975585938</v>
+        <v>164.1699981689453</v>
       </c>
       <c r="E188" t="n">
-        <v>166.4499969482422</v>
+        <v>164.5500030517578</v>
       </c>
       <c r="F188" t="n">
-        <v>16666000</v>
+        <v>13541800</v>
       </c>
       <c r="G188" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>164.7400054931641</v>
+        <v>164.0599975585938</v>
       </c>
       <c r="C189" t="n">
-        <v>166.5399932861328</v>
+        <v>166.3000030517578</v>
       </c>
       <c r="D189" t="n">
-        <v>161.3999938964844</v>
+        <v>160.5</v>
       </c>
       <c r="E189" t="n">
-        <v>165.8899993896484</v>
+        <v>161.7100067138672</v>
       </c>
       <c r="F189" t="n">
-        <v>13589400</v>
+        <v>16385300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>166.0299987792969</v>
+        <v>160.25</v>
       </c>
       <c r="C190" t="n">
-        <v>169.9499969482422</v>
+        <v>161.4299926757812</v>
       </c>
       <c r="D190" t="n">
-        <v>164.1699981689453</v>
+        <v>154.2299957275391</v>
       </c>
       <c r="E190" t="n">
-        <v>164.5500030517578</v>
+        <v>155.0200042724609</v>
       </c>
       <c r="F190" t="n">
-        <v>13541800</v>
+        <v>19986200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>164.0599975585938</v>
+        <v>152.7299957275391</v>
       </c>
       <c r="C191" t="n">
-        <v>166.3000030517578</v>
+        <v>154.4700012207031</v>
       </c>
       <c r="D191" t="n">
-        <v>160.5</v>
+        <v>149.8000030517578</v>
       </c>
       <c r="E191" t="n">
-        <v>161.7100067138672</v>
+        <v>151.7799987792969</v>
       </c>
       <c r="F191" t="n">
-        <v>16385300</v>
+        <v>57940800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>160.25</v>
+        <v>150.1600036621094</v>
       </c>
       <c r="C192" t="n">
-        <v>161.4299926757812</v>
+        <v>153.8699951171875</v>
       </c>
       <c r="D192" t="n">
-        <v>154.2299957275391</v>
+        <v>146.3200073242188</v>
       </c>
       <c r="E192" t="n">
-        <v>155.0200042724609</v>
+        <v>150.1199951171875</v>
       </c>
       <c r="F192" t="n">
-        <v>19986200</v>
+        <v>20502800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>152.7299957275391</v>
+        <v>151.6499938964844</v>
       </c>
       <c r="C193" t="n">
-        <v>154.4700012207031</v>
+        <v>155.1799926757812</v>
       </c>
       <c r="D193" t="n">
-        <v>149.8000030517578</v>
+        <v>150.8500061035156</v>
       </c>
       <c r="E193" t="n">
-        <v>151.7799987792969</v>
+        <v>153.4199981689453</v>
       </c>
       <c r="F193" t="n">
-        <v>57940800</v>
+        <v>20720700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>150.1600036621094</v>
+        <v>151.8099975585938</v>
       </c>
       <c r="C194" t="n">
-        <v>153.8699951171875</v>
+        <v>157.0599975585938</v>
       </c>
       <c r="D194" t="n">
-        <v>146.3200073242188</v>
+        <v>150.3999938964844</v>
       </c>
       <c r="E194" t="n">
-        <v>150.1199951171875</v>
+        <v>152.7599945068359</v>
       </c>
       <c r="F194" t="n">
-        <v>20502800</v>
+        <v>13146800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>151.6499938964844</v>
+        <v>150.0099945068359</v>
       </c>
       <c r="C195" t="n">
-        <v>155.1799926757812</v>
+        <v>154</v>
       </c>
       <c r="D195" t="n">
-        <v>150.8500061035156</v>
+        <v>148.7799987792969</v>
       </c>
       <c r="E195" t="n">
-        <v>153.4199981689453</v>
+        <v>150.1900024414062</v>
       </c>
       <c r="F195" t="n">
-        <v>20720700</v>
+        <v>11324700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>151.8099975585938</v>
+        <v>151.4900054931641</v>
       </c>
       <c r="C196" t="n">
-        <v>157.0599975585938</v>
+        <v>158.4600067138672</v>
       </c>
       <c r="D196" t="n">
-        <v>150.3999938964844</v>
+        <v>151.4900054931641</v>
       </c>
       <c r="E196" t="n">
-        <v>152.7599945068359</v>
+        <v>158.3699951171875</v>
       </c>
       <c r="F196" t="n">
-        <v>13146800</v>
+        <v>21267900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>150.0099945068359</v>
+        <v>160.2700042724609</v>
       </c>
       <c r="C197" t="n">
-        <v>154</v>
+        <v>161.7599945068359</v>
       </c>
       <c r="D197" t="n">
-        <v>148.7799987792969</v>
+        <v>157.6999969482422</v>
       </c>
       <c r="E197" t="n">
-        <v>150.1900024414062</v>
+        <v>157.9299926757812</v>
       </c>
       <c r="F197" t="n">
-        <v>11324700</v>
+        <v>12664100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>151.4900054931641</v>
+        <v>155.0899963378906</v>
       </c>
       <c r="C198" t="n">
-        <v>158.4600067138672</v>
+        <v>157.6900024414062</v>
       </c>
       <c r="D198" t="n">
-        <v>151.4900054931641</v>
+        <v>154.0700073242188</v>
       </c>
       <c r="E198" t="n">
-        <v>158.3699951171875</v>
+        <v>156.6600036621094</v>
       </c>
       <c r="F198" t="n">
-        <v>21267900</v>
+        <v>13690500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>160.2700042724609</v>
+        <v>162.2200012207031</v>
       </c>
       <c r="C199" t="n">
-        <v>161.7599945068359</v>
+        <v>165.8099975585938</v>
       </c>
       <c r="D199" t="n">
-        <v>157.6999969482422</v>
+        <v>161.1999969482422</v>
       </c>
       <c r="E199" t="n">
-        <v>157.9299926757812</v>
+        <v>163.2299957275391</v>
       </c>
       <c r="F199" t="n">
-        <v>12664100</v>
+        <v>14164600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>155.0899963378906</v>
+        <v>163</v>
       </c>
       <c r="C200" t="n">
-        <v>157.6900024414062</v>
+        <v>167.2100067138672</v>
       </c>
       <c r="D200" t="n">
-        <v>154.0700073242188</v>
+        <v>162</v>
       </c>
       <c r="E200" t="n">
-        <v>156.6600036621094</v>
+        <v>166.1100006103516</v>
       </c>
       <c r="F200" t="n">
-        <v>13690500</v>
+        <v>10486300</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>162.2200012207031</v>
+        <v>163.9900054931641</v>
       </c>
       <c r="C201" t="n">
-        <v>165.8099975585938</v>
+        <v>167.7200012207031</v>
       </c>
       <c r="D201" t="n">
-        <v>161.1999969482422</v>
+        <v>162.3699951171875</v>
       </c>
       <c r="E201" t="n">
-        <v>163.2299957275391</v>
+        <v>165.6499938964844</v>
       </c>
       <c r="F201" t="n">
-        <v>14164600</v>
+        <v>10595500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>163</v>
+        <v>169.2200012207031</v>
       </c>
       <c r="C202" t="n">
-        <v>167.2100067138672</v>
+        <v>172.3800048828125</v>
       </c>
       <c r="D202" t="n">
-        <v>162</v>
+        <v>167.6799926757812</v>
       </c>
       <c r="E202" t="n">
-        <v>166.1100006103516</v>
+        <v>169.5200042724609</v>
       </c>
       <c r="F202" t="n">
-        <v>10486300</v>
+        <v>13057900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>163.9900054931641</v>
+        <v>167.3699951171875</v>
       </c>
       <c r="C203" t="n">
-        <v>167.7200012207031</v>
+        <v>167.5299987792969</v>
       </c>
       <c r="D203" t="n">
-        <v>162.3699951171875</v>
+        <v>164.7799987792969</v>
       </c>
       <c r="E203" t="n">
-        <v>165.6499938964844</v>
+        <v>166.5800018310547</v>
       </c>
       <c r="F203" t="n">
-        <v>10595500</v>
+        <v>9792400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>169.2200012207031</v>
+        <v>158.3300018310547</v>
       </c>
       <c r="C204" t="n">
-        <v>172.3800048828125</v>
+        <v>163.8000030517578</v>
       </c>
       <c r="D204" t="n">
-        <v>167.6799926757812</v>
+        <v>156.4799957275391</v>
       </c>
       <c r="E204" t="n">
-        <v>169.5200042724609</v>
+        <v>162.5</v>
       </c>
       <c r="F204" t="n">
-        <v>13057900</v>
+        <v>13858600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>167.3699951171875</v>
+        <v>165.6000061035156</v>
       </c>
       <c r="C205" t="n">
-        <v>167.5299987792969</v>
+        <v>166.3000030517578</v>
       </c>
       <c r="D205" t="n">
-        <v>164.7799987792969</v>
+        <v>162.4199981689453</v>
       </c>
       <c r="E205" t="n">
-        <v>166.5800018310547</v>
+        <v>163.3200073242188</v>
       </c>
       <c r="F205" t="n">
-        <v>9792400</v>
+        <v>8321500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>158.3300018310547</v>
+        <v>165.9199981689453</v>
       </c>
       <c r="C206" t="n">
-        <v>163.8000030517578</v>
+        <v>172.7599945068359</v>
       </c>
       <c r="D206" t="n">
-        <v>156.4799957275391</v>
+        <v>165.9199981689453</v>
       </c>
       <c r="E206" t="n">
-        <v>162.5</v>
+        <v>171.2200012207031</v>
       </c>
       <c r="F206" t="n">
-        <v>13858600</v>
+        <v>14020700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>165.6000061035156</v>
+        <v>162.4900054931641</v>
       </c>
       <c r="C207" t="n">
-        <v>166.3000030517578</v>
+        <v>171.3500061035156</v>
       </c>
       <c r="D207" t="n">
-        <v>162.4199981689453</v>
+        <v>161.4700012207031</v>
       </c>
       <c r="E207" t="n">
-        <v>163.3200073242188</v>
+        <v>167.5599975585938</v>
       </c>
       <c r="F207" t="n">
-        <v>8321500</v>
+        <v>13507900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>165.9199981689453</v>
+        <v>170.5200042724609</v>
       </c>
       <c r="C208" t="n">
-        <v>172.7599945068359</v>
+        <v>172.8000030517578</v>
       </c>
       <c r="D208" t="n">
-        <v>165.9199981689453</v>
+        <v>166.5599975585938</v>
       </c>
       <c r="E208" t="n">
-        <v>171.2200012207031</v>
+        <v>167</v>
       </c>
       <c r="F208" t="n">
-        <v>14020700</v>
+        <v>13328100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>162.4900054931641</v>
+        <v>170.8399963378906</v>
       </c>
       <c r="C209" t="n">
-        <v>171.3500061035156</v>
+        <v>174.5399932861328</v>
       </c>
       <c r="D209" t="n">
-        <v>161.4700012207031</v>
+        <v>166.8800048828125</v>
       </c>
       <c r="E209" t="n">
-        <v>167.5599975585938</v>
+        <v>172.6799926757812</v>
       </c>
       <c r="F209" t="n">
-        <v>13507900</v>
+        <v>12057500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>170.5200042724609</v>
+        <v>171.5</v>
       </c>
       <c r="C210" t="n">
-        <v>172.8000030517578</v>
+        <v>175.4299926757812</v>
       </c>
       <c r="D210" t="n">
-        <v>166.5599975585938</v>
+        <v>169.75</v>
       </c>
       <c r="E210" t="n">
-        <v>167</v>
+        <v>170.7700042724609</v>
       </c>
       <c r="F210" t="n">
-        <v>13328100</v>
+        <v>10191500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>170.8399963378906</v>
+        <v>167.8600006103516</v>
       </c>
       <c r="C211" t="n">
-        <v>174.5399932861328</v>
+        <v>175.3899993896484</v>
       </c>
       <c r="D211" t="n">
-        <v>166.8800048828125</v>
+        <v>166.5</v>
       </c>
       <c r="E211" t="n">
-        <v>172.6799926757812</v>
+        <v>173.7899932861328</v>
       </c>
       <c r="F211" t="n">
-        <v>12057500</v>
+        <v>13426500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>171.5</v>
+        <v>167.0599975585938</v>
       </c>
       <c r="C212" t="n">
-        <v>175.4299926757812</v>
+        <v>172.4299926757812</v>
       </c>
       <c r="D212" t="n">
-        <v>169.75</v>
+        <v>166.9299926757812</v>
       </c>
       <c r="E212" t="n">
-        <v>170.7700042724609</v>
+        <v>170.0599975585938</v>
       </c>
       <c r="F212" t="n">
-        <v>10191500</v>
+        <v>12831800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>167.8600006103516</v>
+        <v>169.4700012207031</v>
       </c>
       <c r="C213" t="n">
-        <v>175.3899993896484</v>
+        <v>169.5700073242188</v>
       </c>
       <c r="D213" t="n">
-        <v>166.5</v>
+        <v>162.2100067138672</v>
       </c>
       <c r="E213" t="n">
-        <v>173.7899932861328</v>
+        <v>163</v>
       </c>
       <c r="F213" t="n">
-        <v>13426500</v>
+        <v>12194500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>167.0599975585938</v>
+        <v>165.0500030517578</v>
       </c>
       <c r="C214" t="n">
-        <v>172.4299926757812</v>
+        <v>165.8800048828125</v>
       </c>
       <c r="D214" t="n">
-        <v>166.9299926757812</v>
+        <v>155.1499938964844</v>
       </c>
       <c r="E214" t="n">
-        <v>170.0599975585938</v>
+        <v>156.9299926757812</v>
       </c>
       <c r="F214" t="n">
-        <v>12831800</v>
+        <v>12775000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>169.4700012207031</v>
+        <v>160.3800048828125</v>
       </c>
       <c r="C215" t="n">
-        <v>169.5700073242188</v>
+        <v>164.4499969482422</v>
       </c>
       <c r="D215" t="n">
-        <v>162.2100067138672</v>
+        <v>159.5500030517578</v>
       </c>
       <c r="E215" t="n">
-        <v>163</v>
+        <v>163.6600036621094</v>
       </c>
       <c r="F215" t="n">
-        <v>12194500</v>
+        <v>10899100</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>165.0500030517578</v>
+        <v>168</v>
       </c>
       <c r="C216" t="n">
-        <v>165.8800048828125</v>
+        <v>176.9499969482422</v>
       </c>
       <c r="D216" t="n">
-        <v>155.1499938964844</v>
+        <v>167.1399993896484</v>
       </c>
       <c r="E216" t="n">
-        <v>156.9299926757812</v>
+        <v>173.6000061035156</v>
       </c>
       <c r="F216" t="n">
-        <v>12775000</v>
+        <v>17312000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>160.3800048828125</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="C217" t="n">
-        <v>164.4499969482422</v>
+        <v>184.5399932861328</v>
       </c>
       <c r="D217" t="n">
-        <v>159.5500030517578</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="E217" t="n">
-        <v>163.6600036621094</v>
+        <v>181.5</v>
       </c>
       <c r="F217" t="n">
-        <v>10899100</v>
+        <v>17204600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>168</v>
+        <v>182.0099945068359</v>
       </c>
       <c r="C218" t="n">
-        <v>176.9499969482422</v>
+        <v>190.1799926757812</v>
       </c>
       <c r="D218" t="n">
-        <v>167.1399993896484</v>
+        <v>182.0099945068359</v>
       </c>
       <c r="E218" t="n">
-        <v>173.6000061035156</v>
+        <v>188.3800048828125</v>
       </c>
       <c r="F218" t="n">
-        <v>17312000</v>
+        <v>18139500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>176.9100036621094</v>
+        <v>180.9900054931641</v>
       </c>
       <c r="C219" t="n">
-        <v>184.5399932861328</v>
+        <v>182.5099945068359</v>
       </c>
       <c r="D219" t="n">
-        <v>176.9100036621094</v>
+        <v>175.8999938964844</v>
       </c>
       <c r="E219" t="n">
-        <v>181.5</v>
+        <v>180.7100067138672</v>
       </c>
       <c r="F219" t="n">
-        <v>17204600</v>
+        <v>12182400</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>182.0099945068359</v>
+        <v>177.6999969482422</v>
       </c>
       <c r="C220" t="n">
-        <v>190.1799926757812</v>
+        <v>184.4499969482422</v>
       </c>
       <c r="D220" t="n">
-        <v>182.0099945068359</v>
+        <v>177.0299987792969</v>
       </c>
       <c r="E220" t="n">
-        <v>188.3800048828125</v>
+        <v>184.0200042724609</v>
       </c>
       <c r="F220" t="n">
-        <v>18139500</v>
+        <v>9691500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>180.9900054931641</v>
+        <v>188.9900054931641</v>
       </c>
       <c r="C221" t="n">
-        <v>182.5099945068359</v>
+        <v>193.6999969482422</v>
       </c>
       <c r="D221" t="n">
-        <v>175.8999938964844</v>
+        <v>185.8999938964844</v>
       </c>
       <c r="E221" t="n">
-        <v>180.7100067138672</v>
+        <v>185.9499969482422</v>
       </c>
       <c r="F221" t="n">
-        <v>12182400</v>
+        <v>12908000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>177.6999969482422</v>
+        <v>183.0899963378906</v>
       </c>
       <c r="C222" t="n">
-        <v>184.4499969482422</v>
+        <v>191.2899932861328</v>
       </c>
       <c r="D222" t="n">
-        <v>177.0299987792969</v>
+        <v>183</v>
       </c>
       <c r="E222" t="n">
-        <v>184.0200042724609</v>
+        <v>190.9900054931641</v>
       </c>
       <c r="F222" t="n">
-        <v>9691500</v>
+        <v>9326900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>188.9900054931641</v>
+        <v>193.2799987792969</v>
       </c>
       <c r="C223" t="n">
-        <v>193.6999969482422</v>
+        <v>194.9400024414062</v>
       </c>
       <c r="D223" t="n">
-        <v>185.8999938964844</v>
+        <v>190.4299926757812</v>
       </c>
       <c r="E223" t="n">
-        <v>185.9499969482422</v>
+        <v>192.9799957275391</v>
       </c>
       <c r="F223" t="n">
-        <v>12908000</v>
+        <v>9605500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>183.0899963378906</v>
+        <v>183.4400024414062</v>
       </c>
       <c r="C224" t="n">
-        <v>191.2899932861328</v>
+        <v>187.0200042724609</v>
       </c>
       <c r="D224" t="n">
         <v>183</v>
       </c>
       <c r="E224" t="n">
-        <v>190.9900054931641</v>
+        <v>186.7700042724609</v>
       </c>
       <c r="F224" t="n">
-        <v>9326900</v>
+        <v>13297600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>193.2799987792969</v>
+        <v>191.0899963378906</v>
       </c>
       <c r="C225" t="n">
-        <v>194.9400024414062</v>
+        <v>194.6999969482422</v>
       </c>
       <c r="D225" t="n">
-        <v>190.4299926757812</v>
+        <v>190.6000061035156</v>
       </c>
       <c r="E225" t="n">
-        <v>192.9799957275391</v>
+        <v>192.7400054931641</v>
       </c>
       <c r="F225" t="n">
-        <v>9605500</v>
+        <v>11392800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>183.4400024414062</v>
+        <v>190.1699981689453</v>
       </c>
       <c r="C226" t="n">
-        <v>187.0200042724609</v>
+        <v>198.1799926757812</v>
       </c>
       <c r="D226" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E226" t="n">
-        <v>186.7700042724609</v>
+        <v>197.5099945068359</v>
       </c>
       <c r="F226" t="n">
-        <v>13297600</v>
+        <v>9706600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>191.0899963378906</v>
+        <v>196.9400024414062</v>
       </c>
       <c r="C227" t="n">
-        <v>194.6999969482422</v>
+        <v>199.3899993896484</v>
       </c>
       <c r="D227" t="n">
-        <v>190.6000061035156</v>
+        <v>195.5</v>
       </c>
       <c r="E227" t="n">
-        <v>192.7400054931641</v>
+        <v>197.4700012207031</v>
       </c>
       <c r="F227" t="n">
-        <v>11392800</v>
+        <v>11171600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>190.1699981689453</v>
+        <v>192</v>
       </c>
       <c r="C228" t="n">
-        <v>198.1799926757812</v>
+        <v>196.5</v>
       </c>
       <c r="D228" t="n">
-        <v>190</v>
+        <v>191.7799987792969</v>
       </c>
       <c r="E228" t="n">
-        <v>197.5099945068359</v>
+        <v>193.3200073242188</v>
       </c>
       <c r="F228" t="n">
-        <v>9706600</v>
+        <v>12787900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>196.9400024414062</v>
+        <v>196.8399963378906</v>
       </c>
       <c r="C229" t="n">
-        <v>199.3899993896484</v>
+        <v>202.9900054931641</v>
       </c>
       <c r="D229" t="n">
-        <v>195.5</v>
+        <v>191.3899993896484</v>
       </c>
       <c r="E229" t="n">
-        <v>197.4700012207031</v>
+        <v>201.3699951171875</v>
       </c>
       <c r="F229" t="n">
-        <v>11171600</v>
+        <v>15058700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>192</v>
+        <v>202.75</v>
       </c>
       <c r="C230" t="n">
-        <v>196.5</v>
+        <v>204.3999938964844</v>
       </c>
       <c r="D230" t="n">
-        <v>191.7799987792969</v>
+        <v>195.3200073242188</v>
       </c>
       <c r="E230" t="n">
-        <v>193.3200073242188</v>
+        <v>196.2100067138672</v>
       </c>
       <c r="F230" t="n">
-        <v>12787900</v>
+        <v>8664800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>196.8399963378906</v>
+        <v>193.8300018310547</v>
       </c>
       <c r="C231" t="n">
-        <v>202.9900054931641</v>
+        <v>194.9400024414062</v>
       </c>
       <c r="D231" t="n">
-        <v>191.3899993896484</v>
+        <v>189.9100036621094</v>
       </c>
       <c r="E231" t="n">
-        <v>201.3699951171875</v>
+        <v>190.9700012207031</v>
       </c>
       <c r="F231" t="n">
-        <v>15058700</v>
+        <v>14378800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>202.75</v>
+        <v>194.0899963378906</v>
       </c>
       <c r="C232" t="n">
-        <v>204.3999938964844</v>
+        <v>199.4100036621094</v>
       </c>
       <c r="D232" t="n">
-        <v>195.3200073242188</v>
+        <v>193.2299957275391</v>
       </c>
       <c r="E232" t="n">
-        <v>196.2100067138672</v>
+        <v>196.1399993896484</v>
       </c>
       <c r="F232" t="n">
-        <v>8664800</v>
+        <v>14152900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>193.8300018310547</v>
+        <v>194.2100067138672</v>
       </c>
       <c r="C233" t="n">
-        <v>194.9400024414062</v>
+        <v>207.9499969482422</v>
       </c>
       <c r="D233" t="n">
-        <v>189.9100036621094</v>
+        <v>194.2100067138672</v>
       </c>
       <c r="E233" t="n">
-        <v>190.9700012207031</v>
+        <v>206.0899963378906</v>
       </c>
       <c r="F233" t="n">
-        <v>14378800</v>
+        <v>17843600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>194.0899963378906</v>
+        <v>205.2200012207031</v>
       </c>
       <c r="C234" t="n">
-        <v>199.4100036621094</v>
+        <v>207.8800048828125</v>
       </c>
       <c r="D234" t="n">
-        <v>193.2299957275391</v>
+        <v>203</v>
       </c>
       <c r="E234" t="n">
-        <v>196.1399993896484</v>
+        <v>205.4299926757812</v>
       </c>
       <c r="F234" t="n">
-        <v>14152900</v>
+        <v>11482300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>194.2100067138672</v>
+        <v>205.5800018310547</v>
       </c>
       <c r="C235" t="n">
-        <v>207.9499969482422</v>
+        <v>211.0700073242188</v>
       </c>
       <c r="D235" t="n">
-        <v>194.2100067138672</v>
+        <v>204.7299957275391</v>
       </c>
       <c r="E235" t="n">
-        <v>206.0899963378906</v>
+        <v>209.1699981689453</v>
       </c>
       <c r="F235" t="n">
-        <v>17843600</v>
+        <v>9685400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>205.2200012207031</v>
+        <v>208.4199981689453</v>
       </c>
       <c r="C236" t="n">
-        <v>207.8800048828125</v>
+        <v>213.1699981689453</v>
       </c>
       <c r="D236" t="n">
-        <v>203</v>
+        <v>207.3899993896484</v>
       </c>
       <c r="E236" t="n">
-        <v>205.4299926757812</v>
+        <v>209.0599975585938</v>
       </c>
       <c r="F236" t="n">
-        <v>11482300</v>
+        <v>9580200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>205.5800018310547</v>
+        <v>205.8500061035156</v>
       </c>
       <c r="C237" t="n">
-        <v>211.0700073242188</v>
+        <v>210.3099975585938</v>
       </c>
       <c r="D237" t="n">
-        <v>204.7299957275391</v>
+        <v>204.7599945068359</v>
       </c>
       <c r="E237" t="n">
-        <v>209.1699981689453</v>
+        <v>205.6900024414062</v>
       </c>
       <c r="F237" t="n">
-        <v>9685400</v>
+        <v>10081800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>208.4199981689453</v>
+        <v>199.9400024414062</v>
       </c>
       <c r="C238" t="n">
-        <v>213.1699981689453</v>
+        <v>206.4400024414062</v>
       </c>
       <c r="D238" t="n">
-        <v>207.3899993896484</v>
+        <v>198.9499969482422</v>
       </c>
       <c r="E238" t="n">
-        <v>209.0599975585938</v>
+        <v>205.6199951171875</v>
       </c>
       <c r="F238" t="n">
-        <v>9580200</v>
+        <v>14888900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>205.8500061035156</v>
+        <v>230.0500030517578</v>
       </c>
       <c r="C239" t="n">
-        <v>210.3099975585938</v>
+        <v>254.4799957275391</v>
       </c>
       <c r="D239" t="n">
-        <v>204.7599945068359</v>
+        <v>230.0500030517578</v>
       </c>
       <c r="E239" t="n">
-        <v>205.6900024414062</v>
+        <v>252.0500030517578</v>
       </c>
       <c r="F239" t="n">
-        <v>10081800</v>
+        <v>55517500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>199.9400024414062</v>
+        <v>250.4700012207031</v>
       </c>
       <c r="C240" t="n">
-        <v>206.4400024414062</v>
+        <v>263.5299987792969</v>
       </c>
       <c r="D240" t="n">
-        <v>198.9499969482422</v>
+        <v>249</v>
       </c>
       <c r="E240" t="n">
-        <v>205.6199951171875</v>
+        <v>256</v>
       </c>
       <c r="F240" t="n">
-        <v>14888900</v>
+        <v>34362700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>230.0500030517578</v>
+        <v>254.3899993896484</v>
       </c>
       <c r="C241" t="n">
-        <v>254.4799957275391</v>
+        <v>262.2799987792969</v>
       </c>
       <c r="D241" t="n">
-        <v>230.0500030517578</v>
+        <v>254.3899993896484</v>
       </c>
       <c r="E241" t="n">
-        <v>252.0500030517578</v>
+        <v>257.5400085449219</v>
       </c>
       <c r="F241" t="n">
-        <v>55517500</v>
+        <v>22471500</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>250.4700012207031</v>
+        <v>255.0099945068359</v>
       </c>
       <c r="C242" t="n">
-        <v>263.5299987792969</v>
+        <v>262.3200073242188</v>
       </c>
       <c r="D242" t="n">
-        <v>249</v>
+        <v>254.25</v>
       </c>
       <c r="E242" t="n">
-        <v>256</v>
+        <v>258.1099853515625</v>
       </c>
       <c r="F242" t="n">
-        <v>34362700</v>
+        <v>15897500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>254.3899993896484</v>
+        <v>259.3800048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>262.2799987792969</v>
+        <v>264.5499877929688</v>
       </c>
       <c r="D243" t="n">
-        <v>254.3899993896484</v>
+        <v>253.6000061035156</v>
       </c>
       <c r="E243" t="n">
-        <v>257.5400085449219</v>
+        <v>256.9299926757812</v>
       </c>
       <c r="F243" t="n">
-        <v>22471500</v>
+        <v>14393700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>255.0099945068359</v>
+        <v>261.9800109863281</v>
       </c>
       <c r="C244" t="n">
-        <v>262.3200073242188</v>
+        <v>268.2699890136719</v>
       </c>
       <c r="D244" t="n">
-        <v>254.25</v>
+        <v>261.6000061035156</v>
       </c>
       <c r="E244" t="n">
-        <v>258.1099853515625</v>
+        <v>264.4299926757812</v>
       </c>
       <c r="F244" t="n">
-        <v>15897500</v>
+        <v>16028300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>259.3800048828125</v>
+        <v>263.3599853515625</v>
       </c>
       <c r="C245" t="n">
-        <v>264.5499877929688</v>
+        <v>263.6000061035156</v>
       </c>
       <c r="D245" t="n">
-        <v>253.6000061035156</v>
+        <v>257.8200073242188</v>
       </c>
       <c r="E245" t="n">
-        <v>256.9299926757812</v>
+        <v>259.2300109863281</v>
       </c>
       <c r="F245" t="n">
-        <v>14393700</v>
+        <v>10490600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>261.9800109863281</v>
+        <v>253.7200012207031</v>
       </c>
       <c r="C246" t="n">
-        <v>268.2699890136719</v>
+        <v>254</v>
       </c>
       <c r="D246" t="n">
-        <v>261.6000061035156</v>
+        <v>245.8899993896484</v>
       </c>
       <c r="E246" t="n">
-        <v>264.4299926757812</v>
+        <v>249.1199951171875</v>
       </c>
       <c r="F246" t="n">
-        <v>16028300</v>
+        <v>17482700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>263.3599853515625</v>
+        <v>249.7799987792969</v>
       </c>
       <c r="C247" t="n">
-        <v>263.6000061035156</v>
+        <v>254.8000030517578</v>
       </c>
       <c r="D247" t="n">
-        <v>257.8200073242188</v>
+        <v>243.4499969482422</v>
       </c>
       <c r="E247" t="n">
-        <v>259.2300109863281</v>
+        <v>244.1600036621094</v>
       </c>
       <c r="F247" t="n">
-        <v>10490600</v>
+        <v>11853700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>253.7200012207031</v>
+        <v>245.3500061035156</v>
       </c>
       <c r="C248" t="n">
-        <v>254</v>
+        <v>248.5</v>
       </c>
       <c r="D248" t="n">
-        <v>245.8899993896484</v>
+        <v>241.75</v>
       </c>
       <c r="E248" t="n">
-        <v>249.1199951171875</v>
+        <v>243</v>
       </c>
       <c r="F248" t="n">
-        <v>17482700</v>
+        <v>10732600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>249.7799987792969</v>
+        <v>242.0200042724609</v>
       </c>
       <c r="C249" t="n">
-        <v>254.8000030517578</v>
+        <v>250.5500030517578</v>
       </c>
       <c r="D249" t="n">
-        <v>243.4499969482422</v>
+        <v>242.0200042724609</v>
       </c>
       <c r="E249" t="n">
-        <v>244.1600036621094</v>
+        <v>247.7200012207031</v>
       </c>
       <c r="F249" t="n">
-        <v>11853700</v>
+        <v>9738300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>245.3500061035156</v>
+        <v>255.75</v>
       </c>
       <c r="C250" t="n">
-        <v>248.5</v>
+        <v>260.1799926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>241.75</v>
+        <v>251.5</v>
       </c>
       <c r="E250" t="n">
-        <v>243</v>
+        <v>259.4299926757812</v>
       </c>
       <c r="F250" t="n">
-        <v>10732600</v>
+        <v>12963700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>242.0200042724609</v>
+        <v>256.8900146484375</v>
       </c>
       <c r="C251" t="n">
-        <v>250.5500030517578</v>
+        <v>262.3399963378906</v>
       </c>
       <c r="D251" t="n">
-        <v>242.0200042724609</v>
+        <v>255.0800018310547</v>
       </c>
       <c r="E251" t="n">
-        <v>247.7200012207031</v>
+        <v>255.6499938964844</v>
       </c>
       <c r="F251" t="n">
-        <v>9738300</v>
+        <v>11502800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,14 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B252" t="n">
-        <v>255.75</v>
-      </c>
-      <c r="C252" t="n">
-        <v>260.1799926757812</v>
-      </c>
-      <c r="D252" t="n">
-        <v>251.5</v>
-      </c>
-      <c r="E252" t="n">
-        <v>259.4299926757812</v>
-      </c>
+        <v>46281</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>12963700</v>
+        <v>9423825</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10654,34 +10646,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>259.43</v>
+        <v>250.54</v>
       </c>
       <c r="D2" t="n">
-        <v>247.72</v>
+        <v>255.65</v>
       </c>
       <c r="E2" t="n">
-        <v>255.75</v>
+        <v>251.85</v>
       </c>
       <c r="F2" t="n">
-        <v>260.18</v>
+        <v>256.4</v>
       </c>
       <c r="G2" t="n">
-        <v>251.55</v>
+        <v>249.6</v>
       </c>
       <c r="H2" t="n">
-        <v>12961044</v>
+        <v>9423825</v>
       </c>
       <c r="I2" t="n">
-        <v>15066001</v>
+        <v>15011672</v>
       </c>
       <c r="J2" t="n">
-        <v>213510881280</v>
+        <v>206194409472</v>
       </c>
       <c r="K2" t="n">
-        <v>23.757324</v>
+        <v>22.943222</v>
       </c>
       <c r="L2" t="n">
-        <v>16.2061</v>
+        <v>15.638098</v>
       </c>
       <c r="M2" t="n">
         <v>10.92</v>
@@ -10696,7 +10688,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10720,7 +10712,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.563347</v>
+        <v>5.3727055</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10732,7 +10724,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>244483883008</v>
+        <v>237167427584</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10759,7 +10751,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:14:49</t>
+          <t>2026-09-17 08:10:36</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,22 +433,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Open</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Close</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -471,20 +471,12 @@
       <c r="A2" s="1" t="n">
         <v>45917</v>
       </c>
-      <c r="B2" t="n">
-        <v>238.3703397912324</v>
-      </c>
-      <c r="C2" t="n">
-        <v>241.380140328441</v>
-      </c>
-      <c r="D2" t="n">
-        <v>237.784276421548</v>
-      </c>
-      <c r="E2" t="n">
-        <v>240.5954132080078</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>10124000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0.416</v>
@@ -498,16 +490,16 @@
         <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>242.5324313580229</v>
+        <v>242.2254791259766</v>
       </c>
       <c r="C3" t="n">
-        <v>245.6415564491674</v>
+        <v>245.210158040453</v>
       </c>
       <c r="D3" t="n">
-        <v>241.3304905574327</v>
+        <v>240.9066632901507</v>
       </c>
       <c r="E3" t="n">
-        <v>242.6516265869141</v>
+        <v>242.10649322906</v>
       </c>
       <c r="F3" t="n">
         <v>9344400</v>
@@ -524,16 +516,16 @@
         <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>244.3800268891626</v>
+        <v>245.0118255615234</v>
       </c>
       <c r="C4" t="n">
-        <v>245.5521536952295</v>
+        <v>245.1209010026767</v>
       </c>
       <c r="D4" t="n">
-        <v>241.7278270152115</v>
+        <v>241.3032908232194</v>
       </c>
       <c r="E4" t="n">
-        <v>245.4428863525391</v>
+        <v>243.9508327525358</v>
       </c>
       <c r="F4" t="n">
         <v>11813900</v>
@@ -550,16 +542,16 @@
         <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>243.6449370886138</v>
+        <v>247.5899810791016</v>
       </c>
       <c r="C5" t="n">
-        <v>248.8102703225537</v>
+        <v>248.3733301153215</v>
       </c>
       <c r="D5" t="n">
-        <v>241.5390740768479</v>
+        <v>241.1149029486022</v>
       </c>
       <c r="E5" t="n">
-        <v>248.0255432128906</v>
+        <v>243.2170678163182</v>
       </c>
       <c r="F5" t="n">
         <v>7523800</v>
@@ -576,16 +568,16 @@
         <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>248.0752418629596</v>
+        <v>242.5031433105469</v>
       </c>
       <c r="C6" t="n">
-        <v>249.6844381137545</v>
+        <v>249.2459554263243</v>
       </c>
       <c r="D6" t="n">
-        <v>242.5026374437513</v>
+        <v>242.0767670572004</v>
       </c>
       <c r="E6" t="n">
-        <v>242.9297637939453</v>
+        <v>247.6395851614097</v>
       </c>
       <c r="F6" t="n">
         <v>7669800</v>
@@ -602,16 +594,16 @@
         <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>244.0323655727545</v>
+        <v>243.8219299316406</v>
       </c>
       <c r="C7" t="n">
-        <v>247.1812325805079</v>
+        <v>246.7471157911642</v>
       </c>
       <c r="D7" t="n">
-        <v>241.390093455952</v>
+        <v>240.9661474659734</v>
       </c>
       <c r="E7" t="n">
-        <v>244.2509002685547</v>
+        <v>243.6037790415992</v>
       </c>
       <c r="F7" t="n">
         <v>6707100</v>
@@ -628,16 +620,16 @@
         <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>242.8701495715982</v>
+        <v>238.9234771728516</v>
       </c>
       <c r="C8" t="n">
-        <v>243.0290866405082</v>
+        <v>242.6022807239559</v>
       </c>
       <c r="D8" t="n">
-        <v>237.8935519633032</v>
+        <v>237.4757650354455</v>
       </c>
       <c r="E8" t="n">
-        <v>239.3438110351562</v>
+        <v>242.4436227791717</v>
       </c>
       <c r="F8" t="n">
         <v>8145500</v>
@@ -654,16 +646,16 @@
         <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>239.0855711988149</v>
+        <v>241.3826293945312</v>
       </c>
       <c r="C9" t="n">
-        <v>242.8999702537546</v>
+        <v>242.4733839178257</v>
       </c>
       <c r="D9" t="n">
-        <v>238.7478412647688</v>
+        <v>238.3285469902175</v>
       </c>
       <c r="E9" t="n">
-        <v>241.8072967529297</v>
+        <v>238.6656837954339</v>
       </c>
       <c r="F9" t="n">
         <v>4974600</v>
@@ -680,16 +672,16 @@
         <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>243.0886994915912</v>
+        <v>243.0386047363281</v>
       </c>
       <c r="C10" t="n">
-        <v>244.1813729625073</v>
+        <v>243.7525504227033</v>
       </c>
       <c r="D10" t="n">
-        <v>241.2510255151616</v>
+        <v>240.8273491460897</v>
       </c>
       <c r="E10" t="n">
-        <v>243.4661712646484</v>
+        <v>242.6617958656146</v>
       </c>
       <c r="F10" t="n">
         <v>6373500</v>
@@ -706,16 +698,16 @@
         <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>243.4164922422276</v>
+        <v>235.0067138671875</v>
       </c>
       <c r="C11" t="n">
-        <v>243.5754293150353</v>
+        <v>243.1476704015903</v>
       </c>
       <c r="D11" t="n">
-        <v>234.2380809080728</v>
+        <v>233.8267199294288</v>
       </c>
       <c r="E11" t="n">
-        <v>235.4201507568359</v>
+        <v>242.989012448683</v>
       </c>
       <c r="F11" t="n">
         <v>10801100</v>
@@ -732,16 +724,16 @@
         <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>234.9135667280067</v>
+        <v>233.7077331542969</v>
       </c>
       <c r="C12" t="n">
-        <v>240.853699895347</v>
+        <v>240.4307087963897</v>
       </c>
       <c r="D12" t="n">
-        <v>231.9534204494054</v>
+        <v>231.5460601627856</v>
       </c>
       <c r="E12" t="n">
-        <v>234.118896484375</v>
+        <v>234.5010077854061</v>
       </c>
       <c r="F12" t="n">
         <v>10016600</v>
@@ -758,16 +750,16 @@
         <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>233.8605987472531</v>
+        <v>236.8708953857422</v>
       </c>
       <c r="C13" t="n">
-        <v>237.8041356430789</v>
+        <v>237.3865110117534</v>
       </c>
       <c r="D13" t="n">
-        <v>232.0428110022616</v>
+        <v>231.6353042398812</v>
       </c>
       <c r="E13" t="n">
-        <v>237.2876129150391</v>
+        <v>233.4498996394798</v>
       </c>
       <c r="F13" t="n">
         <v>7679200</v>
@@ -784,16 +776,16 @@
         <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>237.1584831814004</v>
+        <v>238.3384399414062</v>
       </c>
       <c r="C14" t="n">
-        <v>241.1914166378037</v>
+        <v>240.7678310589901</v>
       </c>
       <c r="D14" t="n">
-        <v>236.9101496911581</v>
+        <v>236.4940829658881</v>
       </c>
       <c r="E14" t="n">
-        <v>238.7577514648438</v>
+        <v>236.7419803274875</v>
       </c>
       <c r="F14" t="n">
         <v>8849800</v>
@@ -810,16 +802,16 @@
         <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>237.7346158803774</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="C15" t="n">
-        <v>248.8003554681588</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D15" t="n">
-        <v>233.8407486183705</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E15" t="n">
-        <v>244.1416168212891</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="F15" t="n">
         <v>13922600</v>
@@ -836,16 +828,16 @@
         <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>244.8369370505447</v>
+        <v>237.7236633300781</v>
       </c>
       <c r="C16" t="n">
-        <v>245.7110757386007</v>
+        <v>245.2795701971395</v>
       </c>
       <c r="D16" t="n">
-        <v>235.9664725401552</v>
+        <v>235.5520799850208</v>
       </c>
       <c r="E16" t="n">
-        <v>238.1418762207031</v>
+        <v>244.4069666278678</v>
       </c>
       <c r="F16" t="n">
         <v>8387400</v>
@@ -862,16 +854,16 @@
         <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>238.1418828252031</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="C17" t="n">
-        <v>239.7113522599795</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D17" t="n">
-        <v>234.0791355152303</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E17" t="n">
-        <v>238.8272705078125</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="F17" t="n">
         <v>7120200</v>
@@ -888,16 +880,16 @@
         <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>237.6750243923864</v>
+        <v>243.2666320800781</v>
       </c>
       <c r="C18" t="n">
-        <v>244.3204311088745</v>
+        <v>243.8913382509171</v>
       </c>
       <c r="D18" t="n">
-        <v>235.569146059018</v>
+        <v>235.1554228281352</v>
       </c>
       <c r="E18" t="n">
-        <v>243.6946258544922</v>
+        <v>237.2576026687149</v>
       </c>
       <c r="F18" t="n">
         <v>7929100</v>
@@ -914,16 +906,16 @@
         <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>244.8767025596296</v>
+        <v>239.6473388671875</v>
       </c>
       <c r="C19" t="n">
-        <v>247.3898363735872</v>
+        <v>246.9553636418975</v>
       </c>
       <c r="D19" t="n">
-        <v>239.1153623132595</v>
+        <v>238.6954214370453</v>
       </c>
       <c r="E19" t="n">
-        <v>240.0689544677734</v>
+        <v>244.4466434616172</v>
       </c>
       <c r="F19" t="n">
         <v>7988300</v>
@@ -940,16 +932,16 @@
         <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>241.2708896666147</v>
+        <v>246.6578826904297</v>
       </c>
       <c r="C20" t="n">
-        <v>247.6878338430882</v>
+        <v>247.252842429503</v>
       </c>
       <c r="D20" t="n">
-        <v>240.7543517533109</v>
+        <v>240.3315369780713</v>
       </c>
       <c r="E20" t="n">
-        <v>247.0918273925781</v>
+        <v>240.8471677432379</v>
       </c>
       <c r="F20" t="n">
         <v>8276500</v>
@@ -966,16 +958,16 @@
         <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>246.4560778349605</v>
+        <v>237.75341796875</v>
       </c>
       <c r="C21" t="n">
-        <v>246.6249427813727</v>
+        <v>246.1918391425529</v>
       </c>
       <c r="D21" t="n">
-        <v>237.9531419622505</v>
+        <v>237.5352670689401</v>
       </c>
       <c r="E21" t="n">
-        <v>238.1716766357422</v>
+        <v>246.0232707436915</v>
       </c>
       <c r="F21" t="n">
         <v>9123900</v>
@@ -992,16 +984,16 @@
         <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>239.2643564080466</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="C22" t="n">
-        <v>239.711368834973</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D22" t="n">
-        <v>234.3274852014847</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E22" t="n">
-        <v>235.0029602050781</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="F22" t="n">
         <v>8389200</v>
@@ -1018,16 +1010,16 @@
         <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>251.502226767664</v>
+        <v>243.9310150146484</v>
       </c>
       <c r="C23" t="n">
-        <v>255.0285501861264</v>
+        <v>254.5806764744798</v>
       </c>
       <c r="D23" t="n">
-        <v>241.0523493056123</v>
+        <v>240.6290201908687</v>
       </c>
       <c r="E23" t="n">
-        <v>244.3601531982422</v>
+        <v>251.0605458824941</v>
       </c>
       <c r="F23" t="n">
         <v>24869700</v>
@@ -1044,16 +1036,16 @@
         <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>244.926381762535</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="C24" t="n">
-        <v>249.1083095871451</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D24" t="n">
-        <v>240.5457750040669</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E24" t="n">
-        <v>241.4596405029297</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="F24" t="n">
         <v>10851200</v>
@@ -1070,16 +1062,16 @@
         <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>243.3668228990331</v>
+        <v>252.1413879394531</v>
       </c>
       <c r="C25" t="n">
-        <v>253.6974901347749</v>
+        <v>253.2519633865538</v>
       </c>
       <c r="D25" t="n">
-        <v>242.6714921507363</v>
+        <v>242.2453285307239</v>
       </c>
       <c r="E25" t="n">
-        <v>252.5849609375</v>
+        <v>242.9394381851618</v>
       </c>
       <c r="F25" t="n">
         <v>9963900</v>
@@ -1096,16 +1088,16 @@
         <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>252.803504151519</v>
+        <v>261.1946105957031</v>
       </c>
       <c r="C26" t="n">
-        <v>265.3493174789288</v>
+        <v>264.8833249829649</v>
       </c>
       <c r="D26" t="n">
-        <v>252.3068371492567</v>
+        <v>251.8637491703276</v>
       </c>
       <c r="E26" t="n">
-        <v>261.6541137695312</v>
+        <v>252.359543952159</v>
       </c>
       <c r="F26" t="n">
         <v>13354700</v>
@@ -1122,16 +1114,16 @@
         <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>260.4521950408587</v>
+        <v>254.4815368652344</v>
       </c>
       <c r="C27" t="n">
-        <v>260.6508436585594</v>
+        <v>260.1930716520554</v>
       </c>
       <c r="D27" t="n">
-        <v>254.8001219796189</v>
+        <v>254.3526253920043</v>
       </c>
       <c r="E27" t="n">
-        <v>254.9292602539062</v>
+        <v>259.9947719140093</v>
       </c>
       <c r="F27" t="n">
         <v>9370000</v>
@@ -1148,16 +1140,16 @@
         <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>255.8828429735078</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="C28" t="n">
-        <v>256.8364351199962</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D28" t="n">
-        <v>252.4260297605343</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E28" t="n">
-        <v>253.3498382568359</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="F28" t="n">
         <v>6110100</v>
@@ -1174,16 +1166,16 @@
         <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>255.7040638410269</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="C29" t="n">
-        <v>256.7768512740817</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D29" t="n">
-        <v>252.3068480604129</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E29" t="n">
-        <v>253.1313171386719</v>
+        <v>255.254980605377</v>
       </c>
       <c r="F29" t="n">
         <v>5490800</v>
@@ -1200,16 +1192,16 @@
         <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>255.3662819386644</v>
+        <v>253.3213500976562</v>
       </c>
       <c r="C30" t="n">
-        <v>256.3795019822516</v>
+        <v>255.9292351115289</v>
       </c>
       <c r="D30" t="n">
-        <v>253.2206920973818</v>
+        <v>252.7759728910826</v>
       </c>
       <c r="E30" t="n">
-        <v>253.7670288085938</v>
+        <v>254.917794537107</v>
       </c>
       <c r="F30" t="n">
         <v>4942400</v>
@@ -1226,16 +1218,16 @@
         <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>253.7670347871236</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="C31" t="n">
-        <v>257.1145654719376</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D31" t="n">
-        <v>252.4458987660038</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E31" t="n">
-        <v>252.5650939941406</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="F31" t="n">
         <v>6435600</v>
@@ -1252,16 +1244,16 @@
         <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>250.3201460853343</v>
+        <v>249.3451080322266</v>
       </c>
       <c r="C32" t="n">
-        <v>251.8796876041973</v>
+        <v>251.4373625303139</v>
       </c>
       <c r="D32" t="n">
-        <v>247.3798710336327</v>
+        <v>246.9454480725237</v>
       </c>
       <c r="E32" t="n">
-        <v>249.7837524414062</v>
+        <v>249.8805597170771</v>
       </c>
       <c r="F32" t="n">
         <v>7904200</v>
@@ -1278,16 +1270,16 @@
         <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>248.8301503215196</v>
+        <v>254.491455078125</v>
       </c>
       <c r="C33" t="n">
-        <v>257.5516210443747</v>
+        <v>257.0993404683716</v>
       </c>
       <c r="D33" t="n">
-        <v>248.33348335481</v>
+        <v>247.897390541893</v>
       </c>
       <c r="E33" t="n">
-        <v>254.9391479492188</v>
+        <v>248.3931853229768</v>
       </c>
       <c r="F33" t="n">
         <v>7767800</v>
@@ -1304,16 +1296,16 @@
         <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>253.1014986048366</v>
+        <v>258.2198181152344</v>
       </c>
       <c r="C34" t="n">
-        <v>260.0747073186972</v>
+        <v>259.6179629024988</v>
       </c>
       <c r="D34" t="n">
-        <v>250.945965708637</v>
+        <v>250.5052532311086</v>
       </c>
       <c r="E34" t="n">
-        <v>258.6741027832031</v>
+        <v>252.657000570364</v>
       </c>
       <c r="F34" t="n">
         <v>6878300</v>
@@ -1330,16 +1322,16 @@
         <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>258.2668364864311</v>
+        <v>259.1420288085938</v>
       </c>
       <c r="C35" t="n">
-        <v>259.8164350802179</v>
+        <v>259.3601797363976</v>
       </c>
       <c r="D35" t="n">
-        <v>253.3995060154779</v>
+        <v>252.9545192358491</v>
       </c>
       <c r="E35" t="n">
-        <v>259.597900390625</v>
+        <v>257.8133023432115</v>
       </c>
       <c r="F35" t="n">
         <v>7054300</v>
@@ -1356,16 +1348,16 @@
         <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>256.4291570066316</v>
+        <v>252.300048828125</v>
       </c>
       <c r="C36" t="n">
-        <v>257.5317734711582</v>
+        <v>257.0795177464699</v>
       </c>
       <c r="D36" t="n">
-        <v>251.7704334426377</v>
+        <v>251.3282953006253</v>
       </c>
       <c r="E36" t="n">
-        <v>252.743896484375</v>
+        <v>255.9788376046017</v>
       </c>
       <c r="F36" t="n">
         <v>6792200</v>
@@ -1382,16 +1374,16 @@
         <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>253.0021749753964</v>
+        <v>250.5548400878906</v>
       </c>
       <c r="C37" t="n">
-        <v>255.1179661572175</v>
+        <v>254.6699306658516</v>
       </c>
       <c r="D37" t="n">
-        <v>250.3301040035887</v>
+        <v>249.8904769054258</v>
       </c>
       <c r="E37" t="n">
-        <v>250.9956359863281</v>
+        <v>252.5578552142711</v>
       </c>
       <c r="F37" t="n">
         <v>5241200</v>
@@ -1408,16 +1400,16 @@
         <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>248.8698969843938</v>
+        <v>237.2576141357422</v>
       </c>
       <c r="C38" t="n">
-        <v>248.8698969843938</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="D38" t="n">
-        <v>232.9169551584068</v>
+        <v>232.5078921531912</v>
       </c>
       <c r="E38" t="n">
-        <v>237.6750335693359</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="F38" t="n">
         <v>11041800</v>
@@ -1434,16 +1426,16 @@
         <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>234.575813422799</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="C39" t="n">
-        <v>239.3636904840115</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D39" t="n">
-        <v>234.2182125835504</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E39" t="n">
-        <v>238.2809600830078</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="F39" t="n">
         <v>5741500</v>
@@ -1460,16 +1452,16 @@
         <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>238.4001623159876</v>
+        <v>239.6771087646484</v>
       </c>
       <c r="C40" t="n">
-        <v>240.2974339121167</v>
+        <v>239.8754236419186</v>
       </c>
       <c r="D40" t="n">
-        <v>233.5129608073587</v>
+        <v>233.1028654264771</v>
       </c>
       <c r="E40" t="n">
-        <v>240.0987701416016</v>
+        <v>237.9814840335094</v>
       </c>
       <c r="F40" t="n">
         <v>6486600</v>
@@ -1486,16 +1478,16 @@
         <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>240.2874885014218</v>
+        <v>242.4436340332031</v>
       </c>
       <c r="C41" t="n">
-        <v>244.062160732275</v>
+        <v>243.63353841341</v>
       </c>
       <c r="D41" t="n">
-        <v>239.5524310420585</v>
+        <v>239.1317287169831</v>
       </c>
       <c r="E41" t="n">
-        <v>242.8701629638672</v>
+        <v>239.8654952673756</v>
       </c>
       <c r="F41" t="n">
         <v>5762800</v>
@@ -1512,16 +1504,16 @@
         <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>244.1019030924143</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="C42" t="n">
-        <v>246.7739588256813</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D42" t="n">
-        <v>242.055622316483</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E42" t="n">
-        <v>244.3800354003906</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="F42" t="n">
         <v>4278200</v>
@@ -1538,16 +1530,16 @@
         <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>243.6151473457208</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="C43" t="n">
-        <v>244.260808340077</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D43" t="n">
-        <v>238.3107477751567</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E43" t="n">
-        <v>238.8272705078125</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="F43" t="n">
         <v>5542100</v>
@@ -1564,16 +1556,16 @@
         <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>236.7214087034764</v>
+        <v>241.6106872558594</v>
       </c>
       <c r="C44" t="n">
-        <v>243.5456080177614</v>
+        <v>243.1178923149379</v>
       </c>
       <c r="D44" t="n">
-        <v>235.8373421035805</v>
+        <v>235.4231636860313</v>
       </c>
       <c r="E44" t="n">
-        <v>242.0357513427734</v>
+        <v>236.3056776848755</v>
       </c>
       <c r="F44" t="n">
         <v>5512900</v>
@@ -1590,16 +1582,16 @@
         <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>240.4563629000066</v>
+        <v>235.0364379882812</v>
       </c>
       <c r="C45" t="n">
-        <v>241.2112912653905</v>
+        <v>240.7876596253181</v>
       </c>
       <c r="D45" t="n">
-        <v>234.0195478209803</v>
+        <v>233.6085468088289</v>
       </c>
       <c r="E45" t="n">
-        <v>235.449951171875</v>
+        <v>240.0340571163644</v>
       </c>
       <c r="F45" t="n">
         <v>5280900</v>
@@ -1616,16 +1608,16 @@
         <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>234.6652065353653</v>
+        <v>231.5361633300781</v>
       </c>
       <c r="C46" t="n">
-        <v>236.2048619582689</v>
+        <v>235.7900759047376</v>
       </c>
       <c r="D46" t="n">
-        <v>228.735001926082</v>
+        <v>228.3333332730034</v>
       </c>
       <c r="E46" t="n">
-        <v>231.9434661865234</v>
+        <v>234.2531241839991</v>
       </c>
       <c r="F46" t="n">
         <v>8045100</v>
@@ -1642,16 +1634,16 @@
         <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>230.4534777021341</v>
+        <v>225.9634094238281</v>
       </c>
       <c r="C47" t="n">
-        <v>230.7316099971398</v>
+        <v>230.3263969654728</v>
       </c>
       <c r="D47" t="n">
-        <v>223.5597376250506</v>
+        <v>223.1671199033486</v>
       </c>
       <c r="E47" t="n">
-        <v>226.3609466552734</v>
+        <v>230.0487531290293</v>
       </c>
       <c r="F47" t="n">
         <v>9710700</v>
@@ -1668,16 +1660,16 @@
         <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>227.7218165007521</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="C48" t="n">
-        <v>229.5296916323367</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D48" t="n">
-        <v>221.8114823100099</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E48" t="n">
-        <v>223.86767578125</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="F48" t="n">
         <v>7521100</v>
@@ -1694,16 +1686,16 @@
         <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>223.3610831021723</v>
+        <v>225.1998901367188</v>
       </c>
       <c r="C49" t="n">
-        <v>227.1556110878527</v>
+        <v>226.7566777713456</v>
       </c>
       <c r="D49" t="n">
-        <v>220.4804205745986</v>
+        <v>220.0932103050241</v>
       </c>
       <c r="E49" t="n">
-        <v>225.5960845947266</v>
+        <v>222.9688137796853</v>
       </c>
       <c r="F49" t="n">
         <v>7479300</v>
@@ -1720,16 +1712,16 @@
         <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>225.824551950926</v>
+        <v>224.9123382568359</v>
       </c>
       <c r="C50" t="n">
-        <v>227.314552977507</v>
+        <v>226.9153381582893</v>
       </c>
       <c r="D50" t="n">
-        <v>223.5398806787535</v>
+        <v>223.1472950220756</v>
       </c>
       <c r="E50" t="n">
-        <v>225.3080291748047</v>
+        <v>225.4279539042935</v>
       </c>
       <c r="F50" t="n">
         <v>8563300</v>
@@ -1746,16 +1738,16 @@
         <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>225.2881447387201</v>
+        <v>232.1509094238281</v>
       </c>
       <c r="C51" t="n">
-        <v>233.065951449845</v>
+        <v>232.656629709896</v>
       </c>
       <c r="D51" t="n">
-        <v>225.0100124430054</v>
+        <v>224.6148389342789</v>
       </c>
       <c r="E51" t="n">
-        <v>232.5593414306641</v>
+        <v>224.8924827605518</v>
       </c>
       <c r="F51" t="n">
         <v>10233000</v>
@@ -1772,16 +1764,16 @@
         <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>228.9734038653133</v>
+        <v>226.2311401367188</v>
       </c>
       <c r="C52" t="n">
-        <v>231.2680180268392</v>
+        <v>230.8618764526245</v>
       </c>
       <c r="D52" t="n">
-        <v>224.493473197433</v>
+        <v>224.0992287472785</v>
       </c>
       <c r="E52" t="n">
-        <v>226.6291351318359</v>
+        <v>228.5712919801828</v>
       </c>
       <c r="F52" t="n">
         <v>8506600</v>
@@ -1798,16 +1790,16 @@
         <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>227.4734767172409</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="C53" t="n">
-        <v>231.0097431878008</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D53" t="n">
-        <v>227.1059480025027</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E53" t="n">
-        <v>229.0032043457031</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="F53" t="n">
         <v>3691500</v>
@@ -1824,16 +1816,16 @@
         <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>227.1456660901873</v>
+        <v>230.8717803955078</v>
       </c>
       <c r="C54" t="n">
-        <v>232.6884711929492</v>
+        <v>232.2798356411572</v>
       </c>
       <c r="D54" t="n">
-        <v>227.0761405973358</v>
+        <v>226.6773611325171</v>
       </c>
       <c r="E54" t="n">
-        <v>231.2779388427734</v>
+        <v>226.7467645282661</v>
       </c>
       <c r="F54" t="n">
         <v>5634700</v>
@@ -1850,16 +1842,16 @@
         <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>231.4666946211142</v>
+        <v>232.7359619140625</v>
       </c>
       <c r="C55" t="n">
-        <v>235.0724867607419</v>
+        <v>234.6596326998496</v>
       </c>
       <c r="D55" t="n">
-        <v>230.0760179166733</v>
+        <v>229.6719390743564</v>
       </c>
       <c r="E55" t="n">
-        <v>233.1454315185547</v>
+        <v>231.060173355472</v>
       </c>
       <c r="F55" t="n">
         <v>7626200</v>
@@ -1876,16 +1868,16 @@
         <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>233.7910747516482</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="C56" t="n">
-        <v>237.6650710221251</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D56" t="n">
-        <v>231.6057431335055</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E56" t="n">
-        <v>237.1286773681641</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="F56" t="n">
         <v>13782000</v>
@@ -1902,16 +1894,16 @@
         <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>242.065551586444</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="C57" t="n">
-        <v>247.3103536057372</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D57" t="n">
-        <v>236.016151496486</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E57" t="n">
-        <v>245.8104248046875</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="F57" t="n">
         <v>20912100</v>
@@ -1928,16 +1920,16 @@
         <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>249.1579600621082</v>
+        <v>258.3784484863281</v>
       </c>
       <c r="C58" t="n">
-        <v>260.1343033980639</v>
+        <v>259.6774281355445</v>
       </c>
       <c r="D58" t="n">
-        <v>247.8368240708576</v>
+        <v>247.4015469367764</v>
       </c>
       <c r="E58" t="n">
-        <v>258.8330383300781</v>
+        <v>248.7203626098492</v>
       </c>
       <c r="F58" t="n">
         <v>15852400</v>
@@ -1954,16 +1946,16 @@
         <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>260.134328900545</v>
+        <v>257.3472290039062</v>
       </c>
       <c r="C59" t="n">
-        <v>262.5183245855411</v>
+        <v>262.0572792621351</v>
       </c>
       <c r="D59" t="n">
-        <v>254.6312497113514</v>
+        <v>254.1840559885597</v>
       </c>
       <c r="E59" t="n">
-        <v>257.7999877929688</v>
+        <v>259.6774704470017</v>
       </c>
       <c r="F59" t="n">
         <v>10805400</v>
@@ -1980,16 +1972,16 @@
         <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>258.2668091334806</v>
+        <v>258.82470703125</v>
       </c>
       <c r="C60" t="n">
-        <v>260.5018103663664</v>
+        <v>260.0443731356912</v>
       </c>
       <c r="D60" t="n">
-        <v>257.273475252198</v>
+        <v>256.8217069290525</v>
       </c>
       <c r="E60" t="n">
-        <v>259.2799987792969</v>
+        <v>257.8132965310952</v>
       </c>
       <c r="F60" t="n">
         <v>8045900</v>
@@ -2006,16 +1998,16 @@
         <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>259.0117983873967</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="C61" t="n">
-        <v>264.157260395403</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D61" t="n">
-        <v>257.4224581829772</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E61" t="n">
-        <v>262.4388122558594</v>
+        <v>258.556940201721</v>
       </c>
       <c r="F61" t="n">
         <v>8894700</v>
@@ -2032,16 +2024,16 @@
         <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>261.7434937420645</v>
+        <v>260.1435546875</v>
       </c>
       <c r="C62" t="n">
-        <v>266.1141570244538</v>
+        <v>265.6468652243614</v>
       </c>
       <c r="D62" t="n">
-        <v>259.0316811670522</v>
+        <v>258.5768260705516</v>
       </c>
       <c r="E62" t="n">
-        <v>260.6011657714844</v>
+        <v>261.2838767501659</v>
       </c>
       <c r="F62" t="n">
         <v>7783800</v>
@@ -2058,16 +2050,16 @@
         <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>261.7633737064805</v>
+        <v>260.0245056152344</v>
       </c>
       <c r="C63" t="n">
-        <v>262.7269089319525</v>
+        <v>262.2654771366241</v>
       </c>
       <c r="D63" t="n">
-        <v>259.1707864287312</v>
+        <v>258.7156003126054</v>
       </c>
       <c r="E63" t="n">
-        <v>260.4819946289062</v>
+        <v>261.3036341846645</v>
       </c>
       <c r="F63" t="n">
         <v>6006600</v>
@@ -2084,16 +2076,16 @@
         <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>259.468759033079</v>
+        <v>252.4388427734375</v>
       </c>
       <c r="C64" t="n">
-        <v>260.5316336613609</v>
+        <v>260.0740784753494</v>
       </c>
       <c r="D64" t="n">
-        <v>251.4028920091002</v>
+        <v>250.9613690531332</v>
       </c>
       <c r="E64" t="n">
-        <v>252.8829650878906</v>
+        <v>259.0130705063725</v>
       </c>
       <c r="F64" t="n">
         <v>10271800</v>
@@ -2110,16 +2102,16 @@
         <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>252.3068168853155</v>
+        <v>252.7660675048828</v>
       </c>
       <c r="C65" t="n">
-        <v>254.1544185916248</v>
+        <v>253.7080744457603</v>
       </c>
       <c r="D65" t="n">
-        <v>250.4294163738298</v>
+        <v>249.9896140498327</v>
       </c>
       <c r="E65" t="n">
-        <v>253.2107543945312</v>
+        <v>251.8637174841621</v>
       </c>
       <c r="F65" t="n">
         <v>6145300</v>
@@ -2136,16 +2128,16 @@
         <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>254.621288079056</v>
+        <v>255.9689178466797</v>
       </c>
       <c r="C66" t="n">
-        <v>260.223706328179</v>
+        <v>259.7666921654164</v>
       </c>
       <c r="D66" t="n">
-        <v>254.5418346981557</v>
+        <v>254.0947992411865</v>
       </c>
       <c r="E66" t="n">
-        <v>256.4192504882812</v>
+        <v>254.1741130832229</v>
       </c>
       <c r="F66" t="n">
         <v>6269000</v>
@@ -2162,16 +2154,16 @@
         <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>257.11173830886</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="C67" t="n">
-        <v>258.7533789592764</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D67" t="n">
-        <v>254.863170050824</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E67" t="n">
-        <v>256.5446166992188</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="F67" t="n">
         <v>5654200</v>
@@ -2188,16 +2180,16 @@
         <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>259.3602680955166</v>
+        <v>258.1400451660156</v>
       </c>
       <c r="C68" t="n">
-        <v>260.7133987167576</v>
+        <v>260.2555449501942</v>
       </c>
       <c r="D68" t="n">
-        <v>254.2064997708628</v>
+        <v>253.7600731430874</v>
       </c>
       <c r="E68" t="n">
-        <v>258.5941772460938</v>
+        <v>258.904790639318</v>
       </c>
       <c r="F68" t="n">
         <v>20732100</v>
@@ -2214,16 +2206,16 @@
         <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>259.3005746010855</v>
+        <v>262.827880859375</v>
       </c>
       <c r="C69" t="n">
-        <v>263.290283203125</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D69" t="n">
-        <v>257.1017714973269</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E69" t="n">
-        <v>263.290283203125</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="F69" t="n">
         <v>5664200</v>
@@ -2240,16 +2232,16 @@
         <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>261.3899469633664</v>
+        <v>261.6360168457031</v>
       </c>
       <c r="C70" t="n">
-        <v>262.9022408344935</v>
+        <v>262.4404982668678</v>
       </c>
       <c r="D70" t="n">
-        <v>259.2010726049517</v>
+        <v>258.7458305027313</v>
       </c>
       <c r="E70" t="n">
-        <v>262.0963439941406</v>
+        <v>260.9308604798152</v>
       </c>
       <c r="F70" t="n">
         <v>4745100</v>
@@ -2266,16 +2258,16 @@
         <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>261.8973621911715</v>
+        <v>263.4535827636719</v>
       </c>
       <c r="C71" t="n">
-        <v>264.9517966936607</v>
+        <v>264.4864785158107</v>
       </c>
       <c r="D71" t="n">
-        <v>261.2207817362974</v>
+        <v>260.7620161053754</v>
       </c>
       <c r="E71" t="n">
-        <v>263.9170837402344</v>
+        <v>261.4374083245464</v>
       </c>
       <c r="F71" t="n">
         <v>2076600</v>
@@ -2292,16 +2284,16 @@
         <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>263.4593915943883</v>
+        <v>264.2680053710938</v>
       </c>
       <c r="C72" t="n">
-        <v>266.5536624648736</v>
+        <v>266.0855602062323</v>
       </c>
       <c r="D72" t="n">
-        <v>263.4593915943883</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="E72" t="n">
-        <v>264.73291015625</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="F72" t="n">
         <v>2456400</v>
@@ -2318,16 +2310,16 @@
         <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>263.3698474835284</v>
+        <v>264.4169616699219</v>
       </c>
       <c r="C73" t="n">
-        <v>267.7475655858019</v>
+        <v>267.2773231615557</v>
       </c>
       <c r="D73" t="n">
-        <v>263.3698474835284</v>
+        <v>262.9072936026629</v>
       </c>
       <c r="E73" t="n">
-        <v>264.8821716308594</v>
+        <v>262.9072936026629</v>
       </c>
       <c r="F73" t="n">
         <v>4300100</v>
@@ -2344,16 +2336,16 @@
         <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>265.3100049300543</v>
+        <v>264.109130859375</v>
       </c>
       <c r="C74" t="n">
-        <v>266.9217986247408</v>
+        <v>266.453045001104</v>
       </c>
       <c r="D74" t="n">
-        <v>263.9867212136458</v>
+        <v>263.5231220141856</v>
       </c>
       <c r="E74" t="n">
-        <v>264.5737609863281</v>
+        <v>264.8440818513142</v>
       </c>
       <c r="F74" t="n">
         <v>3291800</v>
@@ -2370,16 +2362,16 @@
         <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>263.9469286938932</v>
+        <v>263.1059875488281</v>
       </c>
       <c r="C75" t="n">
-        <v>264.7528254896791</v>
+        <v>264.2878861679949</v>
       </c>
       <c r="D75" t="n">
-        <v>263.0514911833619</v>
+        <v>262.5895396190958</v>
       </c>
       <c r="E75" t="n">
-        <v>263.56884765625</v>
+        <v>263.4834046285292</v>
       </c>
       <c r="F75" t="n">
         <v>3367900</v>
@@ -2396,16 +2388,16 @@
         <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>263.6584060515341</v>
+        <v>251.8928680419922</v>
       </c>
       <c r="C76" t="n">
-        <v>264.0364871145308</v>
+        <v>263.572793304574</v>
       </c>
       <c r="D76" t="n">
-        <v>251.2017857864946</v>
+        <v>250.760631935403</v>
       </c>
       <c r="E76" t="n">
-        <v>252.3360137939453</v>
+        <v>263.1953762174182</v>
       </c>
       <c r="F76" t="n">
         <v>9680600</v>
@@ -2422,16 +2414,16 @@
         <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>252.3359973941062</v>
+        <v>254.514892578125</v>
       </c>
       <c r="C77" t="n">
-        <v>258.2757743891104</v>
+        <v>257.8222021169872</v>
       </c>
       <c r="D77" t="n">
-        <v>251.0326319383232</v>
+        <v>250.5917797464572</v>
       </c>
       <c r="E77" t="n">
-        <v>254.962646484375</v>
+        <v>251.8928562905814</v>
       </c>
       <c r="F77" t="n">
         <v>6421500</v>
@@ -2448,16 +2440,16 @@
         <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>253.9080159827951</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="C78" t="n">
-        <v>262.2157339851939</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D78" t="n">
-        <v>253.7090315433827</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E78" t="n">
-        <v>261.5690307617188</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="F78" t="n">
         <v>6103300</v>
@@ -2474,16 +2466,16 @@
         <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>262.1659742529432</v>
+        <v>264.3077392578125</v>
       </c>
       <c r="C79" t="n">
-        <v>266.4740393315776</v>
+        <v>266.0060858079951</v>
       </c>
       <c r="D79" t="n">
-        <v>262.1659742529432</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="E79" t="n">
-        <v>264.772705078125</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="F79" t="n">
         <v>5976200</v>
@@ -2500,16 +2492,16 @@
         <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>263.0614317758581</v>
+        <v>258.7557678222656</v>
       </c>
       <c r="C80" t="n">
-        <v>263.8573998812952</v>
+        <v>263.3939780702048</v>
       </c>
       <c r="D80" t="n">
-        <v>259.0916414276884</v>
+        <v>258.6365898818048</v>
       </c>
       <c r="E80" t="n">
-        <v>259.2110290527344</v>
+        <v>262.5994079508812</v>
       </c>
       <c r="F80" t="n">
         <v>5243500</v>
@@ -2526,16 +2518,16 @@
         <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>258.6837172508962</v>
+        <v>258.1697998046875</v>
       </c>
       <c r="C81" t="n">
-        <v>259.7085015316362</v>
+        <v>259.2523732204683</v>
       </c>
       <c r="D81" t="n">
-        <v>255.2113955316752</v>
+        <v>254.7631655270811</v>
       </c>
       <c r="E81" t="n">
-        <v>258.6240234375</v>
+        <v>258.2293887773175</v>
       </c>
       <c r="F81" t="n">
         <v>5174400</v>
@@ -2552,16 +2544,16 @@
         <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>257.6887621074729</v>
+        <v>257.6334838867188</v>
       </c>
       <c r="C82" t="n">
-        <v>260.2357991803385</v>
+        <v>259.7787779567694</v>
       </c>
       <c r="D82" t="n">
-        <v>254.475118861751</v>
+        <v>254.028214436778</v>
       </c>
       <c r="E82" t="n">
-        <v>258.0867309570312</v>
+        <v>257.2362139425806</v>
       </c>
       <c r="F82" t="n">
         <v>4927700</v>
@@ -2578,16 +2570,16 @@
         <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>256.3555659982514</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="C83" t="n">
-        <v>259.5891124457121</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D83" t="n">
-        <v>239.1431464877683</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E83" t="n">
-        <v>239.839599609375</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="F83" t="n">
         <v>13661000</v>
@@ -2604,16 +2596,16 @@
         <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>237.9691070776633</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="C84" t="n">
-        <v>241.0136281082575</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D84" t="n">
-        <v>235.2628914641447</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E84" t="n">
-        <v>238.3571472167969</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="F84" t="n">
         <v>10149300</v>
@@ -2630,16 +2622,16 @@
         <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>235.8200540893699</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="C85" t="n">
-        <v>237.6308321653778</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D85" t="n">
-        <v>230.4971332136314</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E85" t="n">
-        <v>232.3477172851562</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="F85" t="n">
         <v>11489600</v>
@@ -2656,16 +2648,16 @@
         <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>231.770650770317</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="C86" t="n">
-        <v>231.770650770317</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D86" t="n">
-        <v>225.2936141395941</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E86" t="n">
-        <v>225.9602203369141</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="F86" t="n">
         <v>13902600</v>
@@ -2682,16 +2674,16 @@
         <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>222.4082902460111</v>
+        <v>218.5713348388672</v>
       </c>
       <c r="C87" t="n">
-        <v>226.7860237285318</v>
+        <v>226.3877354418118</v>
       </c>
       <c r="D87" t="n">
-        <v>218.2494593782326</v>
+        <v>217.8661632569629</v>
       </c>
       <c r="E87" t="n">
-        <v>218.9558715820312</v>
+        <v>222.0176902636222</v>
       </c>
       <c r="F87" t="n">
         <v>13050800</v>
@@ -2708,16 +2700,16 @@
         <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>219.0354531203157</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="C88" t="n">
-        <v>222.2590556230766</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D88" t="n">
-        <v>217.8514904177117</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E88" t="n">
-        <v>220.4582214355469</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="F88" t="n">
         <v>12616600</v>
@@ -2734,16 +2726,16 @@
         <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>221.1148825581443</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="C89" t="n">
-        <v>227.5620723478159</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D89" t="n">
-        <v>219.9905984923716</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E89" t="n">
-        <v>226.9352569580078</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="F89" t="n">
         <v>9483000</v>
@@ -2760,16 +2752,16 @@
         <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>225.631887371227</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="C90" t="n">
-        <v>229.6812896074088</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D90" t="n">
-        <v>225.5025406597253</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E90" t="n">
-        <v>226.8954620361328</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="F90" t="n">
         <v>9408000</v>
@@ -2786,16 +2778,16 @@
         <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>228.2684791094572</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="C91" t="n">
-        <v>229.7807881997724</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D91" t="n">
-        <v>226.4377979473355</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E91" t="n">
-        <v>228.2386322021484</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="F91" t="n">
         <v>7239600</v>
@@ -2812,16 +2804,16 @@
         <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>230.7657561403177</v>
+        <v>226.9737243652344</v>
       </c>
       <c r="C92" t="n">
-        <v>234.5465208568135</v>
+        <v>234.1346314027617</v>
       </c>
       <c r="D92" t="n">
-        <v>225.1244635603479</v>
+        <v>224.7291202738612</v>
       </c>
       <c r="E92" t="n">
-        <v>227.3730163574219</v>
+        <v>230.3605061244008</v>
       </c>
       <c r="F92" t="n">
         <v>9838400</v>
@@ -2838,16 +2830,16 @@
         <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>228.2286765757154</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="C93" t="n">
-        <v>230.6861730282261</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D93" t="n">
-        <v>226.5173831306909</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E93" t="n">
-        <v>226.8059234619141</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="F93" t="n">
         <v>8465900</v>
@@ -2864,16 +2856,16 @@
         <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>215.5730693423473</v>
+        <v>212.6221313476562</v>
       </c>
       <c r="C94" t="n">
-        <v>216.1799817205514</v>
+        <v>215.8003365308671</v>
       </c>
       <c r="D94" t="n">
-        <v>207.7230144205324</v>
+        <v>207.3582209619344</v>
       </c>
       <c r="E94" t="n">
-        <v>212.9961853027344</v>
+        <v>215.1944899838427</v>
       </c>
       <c r="F94" t="n">
         <v>18555600</v>
@@ -2890,16 +2882,16 @@
         <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>213.0757836211538</v>
+        <v>210.8443145751953</v>
       </c>
       <c r="C95" t="n">
-        <v>214.4587459115801</v>
+        <v>214.08212392222</v>
       </c>
       <c r="D95" t="n">
-        <v>209.9616248999223</v>
+        <v>209.5929005351361</v>
       </c>
       <c r="E95" t="n">
-        <v>211.2152404785156</v>
+        <v>212.7015903227142</v>
       </c>
       <c r="F95" t="n">
         <v>11090400</v>
@@ -2916,16 +2908,16 @@
         <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>213.2648234781596</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="C96" t="n">
-        <v>215.7919576250148</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D96" t="n">
-        <v>208.7378555750675</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E96" t="n">
-        <v>209.7427368164062</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="F96" t="n">
         <v>7950900</v>
@@ -2942,16 +2934,16 @@
         <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>203.9621583905467</v>
+        <v>195.0426788330078</v>
       </c>
       <c r="C97" t="n">
-        <v>204.5193208819819</v>
+        <v>204.1601567769575</v>
       </c>
       <c r="D97" t="n">
-        <v>192.1323538111565</v>
+        <v>191.7949429269172</v>
       </c>
       <c r="E97" t="n">
-        <v>195.3858032226562</v>
+        <v>203.60397273962</v>
       </c>
       <c r="F97" t="n">
         <v>20194200</v>
@@ -2968,16 +2960,16 @@
         <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>192.3313273349262</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="C98" t="n">
-        <v>199.6540664816468</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D98" t="n">
-        <v>186.3318566210609</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E98" t="n">
-        <v>198.4302978515625</v>
+        <v>191.993558028148</v>
       </c>
       <c r="F98" t="n">
         <v>23010000</v>
@@ -2994,16 +2986,16 @@
         <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>193.0079075172144</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="C99" t="n">
-        <v>198.5497008209625</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D99" t="n">
-        <v>187.8342210038726</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E99" t="n">
-        <v>189.0082550048828</v>
+        <v>192.668943558262</v>
       </c>
       <c r="F99" t="n">
         <v>21956300</v>
@@ -3020,16 +3012,16 @@
         <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>190.6598526107087</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="C100" t="n">
-        <v>193.614817806995</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1726753666609</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E100" t="n">
-        <v>190.3812713623047</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="F100" t="n">
         <v>13652600</v>
@@ -3046,16 +3038,16 @@
         <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>188.3416494095636</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="C101" t="n">
-        <v>194.2117738895214</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D101" t="n">
-        <v>184.7897156694265</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E101" t="n">
-        <v>193.0476989746094</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="F101" t="n">
         <v>12112000</v>
@@ -3072,16 +3064,16 @@
         <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>190.928470906174</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="C102" t="n">
-        <v>198.0920319531629</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D102" t="n">
-        <v>189.7842990292034</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E102" t="n">
-        <v>192.4706268310547</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="F102" t="n">
         <v>13393000</v>
@@ -3098,16 +3090,16 @@
         <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>192.1721331807432</v>
+        <v>183.7401580810547</v>
       </c>
       <c r="C103" t="n">
-        <v>192.6895048269234</v>
+        <v>192.3511139411869</v>
       </c>
       <c r="D103" t="n">
-        <v>180.8895478564994</v>
+        <v>180.5718794169307</v>
       </c>
       <c r="E103" t="n">
-        <v>184.0634002685547</v>
+        <v>191.8346508751069</v>
       </c>
       <c r="F103" t="n">
         <v>16350200</v>
@@ -3124,16 +3116,16 @@
         <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>185.0185569607285</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.3666097225546</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D104" t="n">
-        <v>179.3275140834474</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E104" t="n">
-        <v>184.4912261962891</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="F104" t="n">
         <v>16849100</v>
@@ -3150,16 +3142,16 @@
         <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>185.4961130882416</v>
+        <v>188.4280090332031</v>
       </c>
       <c r="C105" t="n">
-        <v>192.470618112702</v>
+        <v>192.1326035099074</v>
       </c>
       <c r="D105" t="n">
-        <v>183.3669478683701</v>
+        <v>183.0449210226253</v>
       </c>
       <c r="E105" t="n">
-        <v>188.7595062255859</v>
+        <v>185.1703470279448</v>
       </c>
       <c r="F105" t="n">
         <v>14822900</v>
@@ -3176,16 +3168,16 @@
         <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>190.0031839153662</v>
+        <v>183.0349884033203</v>
       </c>
       <c r="C106" t="n">
-        <v>192.0229054891486</v>
+        <v>191.6856804427425</v>
       </c>
       <c r="D106" t="n">
-        <v>182.2426696727612</v>
+        <v>181.9226203922807</v>
       </c>
       <c r="E106" t="n">
-        <v>183.3569946289062</v>
+        <v>189.6695058452945</v>
       </c>
       <c r="F106" t="n">
         <v>13692900</v>
@@ -3202,16 +3194,16 @@
         <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>182.9490856555733</v>
+        <v>186.5111541748047</v>
       </c>
       <c r="C107" t="n">
-        <v>187.1875133215944</v>
+        <v>186.8587767567783</v>
       </c>
       <c r="D107" t="n">
-        <v>180.9393079480809</v>
+        <v>180.6215444099069</v>
       </c>
       <c r="E107" t="n">
-        <v>186.8392791748047</v>
+        <v>182.6277925688313</v>
       </c>
       <c r="F107" t="n">
         <v>9852900</v>
@@ -3228,16 +3220,16 @@
         <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>185.6553247148316</v>
+        <v>184.0281677246094</v>
       </c>
       <c r="C108" t="n">
-        <v>186.0035436955366</v>
+        <v>185.6768667554436</v>
       </c>
       <c r="D108" t="n">
-        <v>182.3023753569564</v>
+        <v>181.9821987572526</v>
       </c>
       <c r="E108" t="n">
-        <v>184.3519439697266</v>
+        <v>185.3292593497056</v>
       </c>
       <c r="F108" t="n">
         <v>9565100</v>
@@ -3254,16 +3246,16 @@
         <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>184.3817888273663</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="C109" t="n">
-        <v>190.759325420591</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D109" t="n">
-        <v>182.7998269729231</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E109" t="n">
-        <v>184.2225952148438</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="F109" t="n">
         <v>10816200</v>
@@ -3280,16 +3272,16 @@
         <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>180.3522971382107</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="C110" t="n">
-        <v>181.546218918281</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D110" t="n">
-        <v>173.6862199497409</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E110" t="n">
-        <v>177.2580413818359</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="F110" t="n">
         <v>15498600</v>
@@ -3306,16 +3298,16 @@
         <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>176.7406808899958</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="C111" t="n">
-        <v>187.7148393068323</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D111" t="n">
-        <v>175.3875654052501</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E111" t="n">
-        <v>184.4812927246094</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="F111" t="n">
         <v>15564700</v>
@@ -3332,16 +3324,16 @@
         <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>182.07353407401</v>
+        <v>190.4441833496094</v>
       </c>
       <c r="C112" t="n">
-        <v>191.6249386554261</v>
+        <v>191.2884009153263</v>
       </c>
       <c r="D112" t="n">
-        <v>181.3372749736025</v>
+        <v>181.0188047518053</v>
       </c>
       <c r="E112" t="n">
-        <v>190.7792358398438</v>
+        <v>181.7537708108397</v>
       </c>
       <c r="F112" t="n">
         <v>21875100</v>
@@ -3358,16 +3350,16 @@
         <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>195.763857285561</v>
+        <v>198.1116180419922</v>
       </c>
       <c r="C113" t="n">
-        <v>200.0221877064004</v>
+        <v>199.6709185207204</v>
       </c>
       <c r="D113" t="n">
-        <v>190.3613550446578</v>
+        <v>190.0270517409182</v>
       </c>
       <c r="E113" t="n">
-        <v>198.4601440429688</v>
+        <v>195.420066371549</v>
       </c>
       <c r="F113" t="n">
         <v>26680500</v>
@@ -3384,16 +3376,16 @@
         <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>190.9384388957837</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="C114" t="n">
-        <v>194.9281323797358</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D114" t="n">
-        <v>188.9585080166839</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E114" t="n">
-        <v>193.8038482666016</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="F114" t="n">
         <v>16346500</v>
@@ -3410,16 +3402,16 @@
         <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>191.5254410161792</v>
+        <v>191.6360168457031</v>
       </c>
       <c r="C115" t="n">
-        <v>194.9480279496185</v>
+        <v>194.6056605467623</v>
       </c>
       <c r="D115" t="n">
-        <v>189.714647741251</v>
+        <v>189.3814711920236</v>
       </c>
       <c r="E115" t="n">
-        <v>191.9731597900391</v>
+        <v>191.1890843548102</v>
       </c>
       <c r="F115" t="n">
         <v>9932700</v>
@@ -3436,16 +3428,16 @@
         <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>189.7842937679152</v>
+        <v>194.7149047851562</v>
       </c>
       <c r="C116" t="n">
-        <v>197.6641955196137</v>
+        <v>197.3170577657204</v>
       </c>
       <c r="D116" t="n">
-        <v>188.6202189254354</v>
+        <v>188.2889641983741</v>
       </c>
       <c r="E116" t="n">
-        <v>195.0574645996094</v>
+        <v>189.4509946932415</v>
       </c>
       <c r="F116" t="n">
         <v>13208900</v>
@@ -3462,16 +3454,16 @@
         <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>194.1122708576492</v>
+        <v>191.76513671875</v>
       </c>
       <c r="C117" t="n">
-        <v>195.4753300833883</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D117" t="n">
-        <v>191.1274589952447</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E117" t="n">
-        <v>192.1024932861328</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="F117" t="n">
         <v>11583700</v>
@@ -3488,16 +3480,16 @@
         <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>193.3760143544918</v>
+        <v>200.0185394287109</v>
       </c>
       <c r="C118" t="n">
-        <v>203.3850811696169</v>
+        <v>203.027904005614</v>
       </c>
       <c r="D118" t="n">
-        <v>193.2566267365104</v>
+        <v>192.9172367799533</v>
       </c>
       <c r="E118" t="n">
-        <v>200.3704223632812</v>
+        <v>193.036414733929</v>
       </c>
       <c r="F118" t="n">
         <v>15860900</v>
@@ -3514,16 +3506,16 @@
         <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>199.7734673796906</v>
+        <v>200.733642578125</v>
       </c>
       <c r="C119" t="n">
-        <v>201.9324948273444</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D119" t="n">
-        <v>196.3707834039569</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E119" t="n">
-        <v>201.0867919921875</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="F119" t="n">
         <v>9657400</v>
@@ -3540,16 +3532,16 @@
         <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>197.5547532603008</v>
+        <v>197.4362487792969</v>
       </c>
       <c r="C120" t="n">
-        <v>202.6388836095676</v>
+        <v>202.2830212056148</v>
       </c>
       <c r="D120" t="n">
-        <v>194.8783694210796</v>
+        <v>194.5361355724457</v>
       </c>
       <c r="E120" t="n">
-        <v>197.7835845947266</v>
+        <v>197.2078193049057</v>
       </c>
       <c r="F120" t="n">
         <v>10754800</v>
@@ -3566,16 +3558,16 @@
         <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>196.2613420240266</v>
+        <v>193.5826721191406</v>
       </c>
       <c r="C121" t="n">
-        <v>198.5596601232727</v>
+        <v>198.2109412897675</v>
       </c>
       <c r="D121" t="n">
-        <v>189.6350706142157</v>
+        <v>189.3020255204881</v>
       </c>
       <c r="E121" t="n">
-        <v>193.9232482910156</v>
+        <v>195.9166595935153</v>
       </c>
       <c r="F121" t="n">
         <v>14467400</v>
@@ -3592,16 +3584,16 @@
         <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>195.4056830590209</v>
+        <v>192.8079986572266</v>
       </c>
       <c r="C122" t="n">
-        <v>198.5397447176623</v>
+        <v>198.1910871721164</v>
       </c>
       <c r="D122" t="n">
-        <v>190.3215527599943</v>
+        <v>189.987327259986</v>
       </c>
       <c r="E122" t="n">
-        <v>193.1471862792969</v>
+        <v>195.0625292691439</v>
       </c>
       <c r="F122" t="n">
         <v>9580000</v>
@@ -3618,16 +3610,16 @@
         <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>193.1471819093573</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="C123" t="n">
-        <v>203.8228548323795</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D123" t="n">
-        <v>192.1721324296864</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E123" t="n">
-        <v>198.2711029052734</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="F123" t="n">
         <v>26309700</v>
@@ -3644,16 +3636,16 @@
         <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>198.7188210052147</v>
+        <v>191.5168304443359</v>
       </c>
       <c r="C124" t="n">
-        <v>199.9823956164078</v>
+        <v>199.6311909649738</v>
       </c>
       <c r="D124" t="n">
-        <v>190.7792256688866</v>
+        <v>190.4441834205658</v>
       </c>
       <c r="E124" t="n">
-        <v>191.853759765625</v>
+        <v>198.3698354155112</v>
       </c>
       <c r="F124" t="n">
         <v>14834700</v>
@@ -3670,16 +3662,16 @@
         <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>194.1620237910367</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="C125" t="n">
-        <v>197.6244168069387</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D125" t="n">
-        <v>194.1620237910367</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E125" t="n">
-        <v>197.3358764648438</v>
+        <v>193.821025021851</v>
       </c>
       <c r="F125" t="n">
         <v>13419600</v>
@@ -3696,16 +3688,16 @@
         <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>197.2164841210229</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="C126" t="n">
-        <v>201.3554271697534</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D126" t="n">
-        <v>193.4655660342646</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E126" t="n">
-        <v>194.3212127685547</v>
+        <v>196.870136689126</v>
       </c>
       <c r="F126" t="n">
         <v>11559300</v>
@@ -3722,16 +3714,16 @@
         <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>192.4208813209107</v>
+        <v>193.0165557861328</v>
       </c>
       <c r="C127" t="n">
-        <v>195.1569590889159</v>
+        <v>194.8142273994103</v>
       </c>
       <c r="D127" t="n">
-        <v>191.6647343849253</v>
+        <v>191.3281356874407</v>
       </c>
       <c r="E127" t="n">
-        <v>193.3561248779297</v>
+        <v>192.0829546896537</v>
       </c>
       <c r="F127" t="n">
         <v>10525100</v>
@@ -3748,16 +3740,16 @@
         <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>194.5997914321279</v>
+        <v>193.6621398925781</v>
       </c>
       <c r="C128" t="n">
-        <v>199.3854376268052</v>
+        <v>199.0352867281362</v>
       </c>
       <c r="D128" t="n">
-        <v>192.3213915946813</v>
+        <v>191.9836462262046</v>
       </c>
       <c r="E128" t="n">
-        <v>194.0028381347656</v>
+        <v>194.2580448499211</v>
       </c>
       <c r="F128" t="n">
         <v>9254300</v>
@@ -3774,16 +3766,16 @@
         <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>192.2318417698426</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="C129" t="n">
-        <v>194.6793790179939</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D129" t="n">
-        <v>189.0380863676492</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E129" t="n">
-        <v>194.3908538818359</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="F129" t="n">
         <v>20201100</v>
@@ -3800,16 +3792,16 @@
         <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>196.0921979891633</v>
+        <v>193.850830078125</v>
       </c>
       <c r="C130" t="n">
-        <v>197.0473445217343</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D130" t="n">
-        <v>191.0279705387624</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E130" t="n">
-        <v>194.1918640136719</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="F130" t="n">
         <v>13976200</v>
@@ -3826,16 +3818,16 @@
         <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1672689357976</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="C131" t="n">
-        <v>191.1672689357976</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D131" t="n">
-        <v>181.3671296009816</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E131" t="n">
-        <v>182.0934448242188</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="F131" t="n">
         <v>18631400</v>
@@ -3852,16 +3844,16 @@
         <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>184.7598589955983</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="C132" t="n">
-        <v>186.4413055109877</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D132" t="n">
-        <v>178.9394847287185</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E132" t="n">
-        <v>181.0388031005859</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="F132" t="n">
         <v>12565200</v>
@@ -3878,16 +3870,16 @@
         <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>180.2627525283908</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="C133" t="n">
-        <v>186.5209173345002</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D133" t="n">
-        <v>178.621111875675</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E133" t="n">
-        <v>184.7001800537109</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="F133" t="n">
         <v>10330700</v>
@@ -3904,16 +3896,16 @@
         <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>183.0684648284524</v>
+        <v>178.0889129638672</v>
       </c>
       <c r="C134" t="n">
-        <v>183.1779085396875</v>
+        <v>182.8562284362321</v>
       </c>
       <c r="D134" t="n">
-        <v>177.9146968557465</v>
+        <v>177.6022595179307</v>
       </c>
       <c r="E134" t="n">
-        <v>178.4022064208984</v>
+        <v>182.7469769199218</v>
       </c>
       <c r="F134" t="n">
         <v>9902000</v>
@@ -3930,16 +3922,16 @@
         <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>179.1882128832653</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="C135" t="n">
-        <v>185.4463617882801</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D135" t="n">
-        <v>178.670841239089</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E135" t="n">
-        <v>184.0932464599609</v>
+        <v>178.873523844959</v>
       </c>
       <c r="F135" t="n">
         <v>11617700</v>
@@ -3956,16 +3948,16 @@
         <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>183.9639169002118</v>
+        <v>185.3987731933594</v>
       </c>
       <c r="C136" t="n">
-        <v>187.5456975682965</v>
+        <v>187.2163126895138</v>
       </c>
       <c r="D136" t="n">
-        <v>181.3870327098191</v>
+        <v>181.0684642406058</v>
       </c>
       <c r="E136" t="n">
-        <v>185.7249603271484</v>
+        <v>183.6408226716892</v>
       </c>
       <c r="F136" t="n">
         <v>11041400</v>
@@ -3982,16 +3974,16 @@
         <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>185.904046779924</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="C137" t="n">
-        <v>188.0232529761809</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D137" t="n">
-        <v>182.0834758824893</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E137" t="n">
-        <v>185.2971343994141</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="F137" t="n">
         <v>11677700</v>
@@ -4008,16 +4000,16 @@
         <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>184.3619041015049</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="C138" t="n">
-        <v>186.6303601693813</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D138" t="n">
-        <v>180.6607357420139</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E138" t="n">
-        <v>186.2323760986328</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="F138" t="n">
         <v>11635500</v>
@@ -4034,16 +4026,16 @@
         <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>186.5507427928755</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="C139" t="n">
-        <v>187.187502054347</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D139" t="n">
-        <v>182.670493415399</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E139" t="n">
-        <v>184.0932464599609</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="F139" t="n">
         <v>14391000</v>
@@ -4060,16 +4052,16 @@
         <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>184.0136681409698</v>
+        <v>181.7140502929688</v>
       </c>
       <c r="C140" t="n">
-        <v>185.635420952666</v>
+        <v>185.3093932676422</v>
       </c>
       <c r="D140" t="n">
-        <v>181.098508861202</v>
+        <v>180.7804492618957</v>
       </c>
       <c r="E140" t="n">
-        <v>182.0337524414062</v>
+        <v>183.6904887071696</v>
       </c>
       <c r="F140" t="n">
         <v>12344600</v>
@@ -4086,16 +4078,16 @@
         <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>185.5558006932337</v>
+        <v>175.1689300537109</v>
       </c>
       <c r="C141" t="n">
-        <v>185.8244380067301</v>
+        <v>185.4981160077481</v>
       </c>
       <c r="D141" t="n">
-        <v>174.890071953609</v>
+        <v>174.5829515420302</v>
       </c>
       <c r="E141" t="n">
-        <v>175.4770812988281</v>
+        <v>185.2299504420264</v>
       </c>
       <c r="F141" t="n">
         <v>13472100</v>
@@ -4112,16 +4104,16 @@
         <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>172.7242064751902</v>
+        <v>170.1109008789062</v>
       </c>
       <c r="C142" t="n">
-        <v>173.8413183878644</v>
+        <v>173.5360065139178</v>
       </c>
       <c r="D142" t="n">
-        <v>166.6897779521393</v>
+        <v>166.3970260969056</v>
       </c>
       <c r="E142" t="n">
-        <v>170.4101867675781</v>
+        <v>172.4208565486944</v>
       </c>
       <c r="F142" t="n">
         <v>20855400</v>
@@ -4138,16 +4130,16 @@
         <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>170.8191086768984</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="C143" t="n">
-        <v>170.8191086768984</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D143" t="n">
-        <v>163.0990440067395</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E143" t="n">
-        <v>164.5353393554688</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="F143" t="n">
         <v>18109300</v>
@@ -4164,16 +4156,16 @@
         <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>166.619956593861</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="C144" t="n">
-        <v>172.9536002909039</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D144" t="n">
-        <v>165.3432529892489</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E144" t="n">
-        <v>172.3751068115234</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="F144" t="n">
         <v>12390800</v>
@@ -4190,16 +4182,16 @@
         <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>174.7589572577855</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="C145" t="n">
-        <v>177.043055331393</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D145" t="n">
-        <v>170.0610756845212</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E145" t="n">
-        <v>170.8689880371094</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="F145" t="n">
         <v>13123600</v>
@@ -4216,16 +4208,16 @@
         <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>173.771503335319</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="C146" t="n">
-        <v>179.157595924108</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D146" t="n">
-        <v>172.4349565756613</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E146" t="n">
-        <v>177.1428070068359</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="F146" t="n">
         <v>14340300</v>
@@ -4242,16 +4234,16 @@
         <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>183.5263211162543</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="C147" t="n">
-        <v>184.0749082721881</v>
+        <v>183.7516467853238</v>
       </c>
       <c r="D147" t="n">
-        <v>178.110307097372</v>
+        <v>177.7975202909648</v>
       </c>
       <c r="E147" t="n">
-        <v>180.7534790039062</v>
+        <v>183.2040230257668</v>
       </c>
       <c r="F147" t="n">
         <v>11866700</v>
@@ -4268,16 +4260,16 @@
         <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>184.9526358387744</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="C148" t="n">
-        <v>187.4960743570736</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D148" t="n">
-        <v>180.5639689511464</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E148" t="n">
-        <v>181.6711120605469</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="F148" t="n">
         <v>17225700</v>
@@ -4294,16 +4286,16 @@
         <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>182.0301825754578</v>
+        <v>185.4641876220703</v>
       </c>
       <c r="C149" t="n">
-        <v>188.5134493521179</v>
+        <v>188.1823732032504</v>
       </c>
       <c r="D149" t="n">
-        <v>181.6511559551952</v>
+        <v>181.33213168739</v>
       </c>
       <c r="E149" t="n">
-        <v>185.7904815673828</v>
+        <v>181.7104926433502</v>
       </c>
       <c r="F149" t="n">
         <v>14382300</v>
@@ -4320,16 +4312,16 @@
         <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>186.1196295624439</v>
+        <v>186.3005676269531</v>
       </c>
       <c r="C150" t="n">
-        <v>193.0617034585096</v>
+        <v>192.7226620565929</v>
       </c>
       <c r="D150" t="n">
-        <v>183.6260654751631</v>
+        <v>183.3035942778625</v>
       </c>
       <c r="E150" t="n">
-        <v>186.6283111572266</v>
+        <v>185.7927793430547</v>
       </c>
       <c r="F150" t="n">
         <v>12073700</v>
@@ -4346,16 +4338,16 @@
         <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>187.7155141554787</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="C151" t="n">
-        <v>190.6579169337777</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D151" t="n">
-        <v>186.5485279099638</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E151" t="n">
-        <v>189.3114013671875</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="F151" t="n">
         <v>14565900</v>
@@ -4372,16 +4364,16 @@
         <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>177.1028943275062</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="C152" t="n">
-        <v>178.4095194817015</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D152" t="n">
-        <v>170.2106794975899</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E152" t="n">
-        <v>172.8538665771484</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="F152" t="n">
         <v>22719900</v>
@@ -4398,16 +4390,16 @@
         <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>175.1678853418476</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="C153" t="n">
-        <v>177.9906017183548</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D153" t="n">
-        <v>173.9510248482436</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E153" t="n">
-        <v>177.7013549804688</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="F153" t="n">
         <v>10817600</v>
@@ -4424,16 +4416,16 @@
         <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>177.8011004808986</v>
+        <v>179.4005279541016</v>
       </c>
       <c r="C154" t="n">
-        <v>183.81557625727</v>
+        <v>183.4927485632761</v>
       </c>
       <c r="D154" t="n">
-        <v>177.0530312030464</v>
+        <v>176.7420802872333</v>
       </c>
       <c r="E154" t="n">
-        <v>179.7161560058594</v>
+        <v>177.4888357619529</v>
       </c>
       <c r="F154" t="n">
         <v>11907000</v>
@@ -4450,16 +4442,16 @@
         <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>181.960353565993</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="C155" t="n">
-        <v>183.9452360835181</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D155" t="n">
-        <v>180.8532257080078</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E155" t="n">
-        <v>180.8532257080078</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="F155" t="n">
         <v>8711700</v>
@@ -4476,16 +4468,16 @@
         <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>178.7386749127982</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="C156" t="n">
-        <v>181.3120349373997</v>
+        <v>180.993625445577</v>
       </c>
       <c r="D156" t="n">
-        <v>176.8934465767579</v>
+        <v>176.5827967489585</v>
       </c>
       <c r="E156" t="n">
-        <v>180.7534790039062</v>
+        <v>178.4247846039299</v>
       </c>
       <c r="F156" t="n">
         <v>6882800</v>
@@ -4502,16 +4494,16 @@
         <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>177.8409939014207</v>
+        <v>175.7663421630859</v>
       </c>
       <c r="C157" t="n">
-        <v>178.2299892905901</v>
+        <v>177.9170017981234</v>
       </c>
       <c r="D157" t="n">
-        <v>172.5546349879463</v>
+        <v>172.2516139153796</v>
       </c>
       <c r="E157" t="n">
-        <v>176.0755462646484</v>
+        <v>177.5286895189733</v>
       </c>
       <c r="F157" t="n">
         <v>14408300</v>
@@ -4528,16 +4520,16 @@
         <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>181.7209929763659</v>
+        <v>183.0247955322266</v>
       </c>
       <c r="C158" t="n">
-        <v>185.5610728373815</v>
+        <v>185.2351777570901</v>
       </c>
       <c r="D158" t="n">
-        <v>178.2898460906057</v>
+        <v>177.9767212373249</v>
       </c>
       <c r="E158" t="n">
-        <v>183.3468017578125</v>
+        <v>181.4018421076459</v>
       </c>
       <c r="F158" t="n">
         <v>12324400</v>
@@ -4554,16 +4546,16 @@
         <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>183.7657043950053</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="C159" t="n">
-        <v>189.8200700827938</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D159" t="n">
-        <v>183.4963952122052</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E159" t="n">
-        <v>185.0025024414062</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="F159" t="n">
         <v>8444700</v>
@@ -4580,16 +4572,16 @@
         <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>185.0723410364737</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="C160" t="n">
-        <v>186.9076006654211</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D160" t="n">
-        <v>180.6337997307826</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E160" t="n">
-        <v>186.5086364746094</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="F160" t="n">
         <v>9740800</v>
@@ -4606,16 +4598,16 @@
         <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>185.0424114227766</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="C161" t="n">
-        <v>186.6183457810002</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D161" t="n">
-        <v>179.117700608299</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E161" t="n">
-        <v>180.7235565185547</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="F161" t="n">
         <v>11303400</v>
@@ -4632,16 +4624,16 @@
         <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>184.124779650284</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="C162" t="n">
-        <v>188.0945294450444</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D162" t="n">
-        <v>183.5263181771209</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E162" t="n">
-        <v>185.8602905273438</v>
+        <v>183.801426731489</v>
       </c>
       <c r="F162" t="n">
         <v>13955100</v>
@@ -4658,16 +4650,16 @@
         <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>179.2174384093688</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="C163" t="n">
-        <v>181.40180307799</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D163" t="n">
-        <v>176.424658688263</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E163" t="n">
-        <v>181.3519439697266</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="F163" t="n">
         <v>15123900</v>
@@ -4684,16 +4676,16 @@
         <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>179.4468492598589</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="C164" t="n">
-        <v>182.0301779962749</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D164" t="n">
-        <v>175.8561108937732</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E164" t="n">
-        <v>177.0330810546875</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="F164" t="n">
         <v>11145000</v>
@@ -4710,16 +4702,16 @@
         <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>177.122851210841</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="C165" t="n">
-        <v>177.122851210841</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D165" t="n">
-        <v>170.1408715639692</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E165" t="n">
-        <v>170.8689880371094</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="F165" t="n">
         <v>10214000</v>
@@ -4736,16 +4728,16 @@
         <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>169.3429302825834</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="C166" t="n">
-        <v>169.3429302825834</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D166" t="n">
-        <v>164.3258803430835</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E166" t="n">
-        <v>165.4130706787109</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="F166" t="n">
         <v>11951900</v>
@@ -4762,16 +4754,16 @@
         <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>165.5726557549663</v>
+        <v>166.8550567626953</v>
       </c>
       <c r="C167" t="n">
-        <v>168.914037726981</v>
+        <v>168.6174040602531</v>
       </c>
       <c r="D167" t="n">
-        <v>163.9069567673868</v>
+        <v>163.6191161459536</v>
       </c>
       <c r="E167" t="n">
-        <v>167.1485900878906</v>
+        <v>165.2818899628073</v>
       </c>
       <c r="F167" t="n">
         <v>9749400</v>
@@ -4788,16 +4780,16 @@
         <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>168.8142960637846</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="C168" t="n">
-        <v>175.5169978399782</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D168" t="n">
-        <v>168.5649396441926</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E168" t="n">
-        <v>173.0633239746094</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="F168" t="n">
         <v>13883400</v>
@@ -4814,16 +4806,16 @@
         <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>172.444927913041</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="C169" t="n">
-        <v>180.3146160429799</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D169" t="n">
-        <v>171.3577375574589</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E169" t="n">
-        <v>179.0179595947266</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="F169" t="n">
         <v>13671200</v>
@@ -4840,16 +4832,16 @@
         <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>184.5237517741468</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="C170" t="n">
-        <v>186.9574728813163</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D170" t="n">
-        <v>178.3496843472311</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E170" t="n">
-        <v>178.9581146240234</v>
+        <v>184.1996921538</v>
       </c>
       <c r="F170" t="n">
         <v>17510800</v>
@@ -4866,16 +4858,16 @@
         <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>175.5868068261091</v>
+        <v>179.3209075927734</v>
       </c>
       <c r="C171" t="n">
-        <v>179.8458186639284</v>
+        <v>179.5299906412754</v>
       </c>
       <c r="D171" t="n">
-        <v>172.8937605828528</v>
+        <v>172.5901410995666</v>
       </c>
       <c r="E171" t="n">
-        <v>179.6363677978516</v>
+        <v>175.2784580726278</v>
       </c>
       <c r="F171" t="n">
         <v>13025300</v>
@@ -4892,16 +4884,16 @@
         <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>174.9285262709738</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="C172" t="n">
-        <v>176.8834721439062</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D172" t="n">
-        <v>171.547253715491</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E172" t="n">
-        <v>175.8561248779297</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="F172" t="n">
         <v>10949100</v>
@@ -4918,16 +4910,16 @@
         <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>179.3770264534069</v>
+        <v>179.2910308837891</v>
       </c>
       <c r="C173" t="n">
-        <v>182.8780002490095</v>
+        <v>182.5568405051486</v>
       </c>
       <c r="D173" t="n">
-        <v>177.222583382191</v>
+        <v>176.9113553536261</v>
       </c>
       <c r="E173" t="n">
-        <v>179.6064453125</v>
+        <v>179.0620149167984</v>
       </c>
       <c r="F173" t="n">
         <v>10176700</v>
@@ -4944,16 +4936,16 @@
         <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>177.9706522299692</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="C174" t="n">
-        <v>181.890542966362</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D174" t="n">
-        <v>177.222582989082</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E174" t="n">
-        <v>178.6189880371094</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="F174" t="n">
         <v>13617200</v>
@@ -4970,16 +4962,16 @@
         <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>177.5417683468011</v>
+        <v>176.7420959472656</v>
       </c>
       <c r="C175" t="n">
-        <v>183.4465264564886</v>
+        <v>183.1243702829636</v>
       </c>
       <c r="D175" t="n">
-        <v>176.4346252500155</v>
+        <v>176.1247828951571</v>
       </c>
       <c r="E175" t="n">
-        <v>177.0530242919922</v>
+        <v>177.2299817033781</v>
       </c>
       <c r="F175" t="n">
         <v>18524900</v>
@@ -4996,16 +4988,16 @@
         <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>177.9706529497301</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="C176" t="n">
-        <v>182.0102299107596</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D176" t="n">
-        <v>171.2081082023211</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E176" t="n">
-        <v>175.7164764404297</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="F176" t="n">
         <v>22559400</v>
@@ -5022,16 +5014,16 @@
         <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>179.7760043356117</v>
+        <v>190.2733154296875</v>
       </c>
       <c r="C177" t="n">
-        <v>193.6402147597182</v>
+        <v>193.300157831373</v>
       </c>
       <c r="D177" t="n">
-        <v>179.5565694754165</v>
+        <v>179.2412452254626</v>
       </c>
       <c r="E177" t="n">
-        <v>190.6080474853516</v>
+        <v>179.4602947300403</v>
       </c>
       <c r="F177" t="n">
         <v>33998900</v>
@@ -5048,16 +5040,16 @@
         <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>198.2383502861678</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="C178" t="n">
-        <v>210.7959357157644</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D178" t="n">
-        <v>197.69974712537</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E178" t="n">
-        <v>209.0604248046875</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="F178" t="n">
         <v>27594800</v>
@@ -5074,16 +5066,16 @@
         <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>200.5025120636997</v>
+        <v>199.9711761474609</v>
       </c>
       <c r="C179" t="n">
-        <v>203.8638316949671</v>
+        <v>203.5058221270036</v>
       </c>
       <c r="D179" t="n">
-        <v>195.2560433089883</v>
+        <v>194.9131500594789</v>
       </c>
       <c r="E179" t="n">
-        <v>200.3229675292969</v>
+        <v>200.1504053799259</v>
       </c>
       <c r="F179" t="n">
         <v>19216600</v>
@@ -5100,16 +5092,16 @@
         <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>196.7621671181547</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="C180" t="n">
-        <v>197.1711000779736</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D180" t="n">
-        <v>189.2415690076627</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E180" t="n">
-        <v>190.1193084716797</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="F180" t="n">
         <v>14154400</v>
@@ -5126,16 +5118,16 @@
         <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>197.3007734437849</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="C181" t="n">
-        <v>197.5800514196224</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D181" t="n">
-        <v>185.6308959064055</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E181" t="n">
-        <v>188.2640991210938</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="F181" t="n">
         <v>14453600</v>
@@ -5152,16 +5144,16 @@
         <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>189.311394256529</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="C182" t="n">
-        <v>192.0144092856922</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D182" t="n">
-        <v>184.3541874840329</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E182" t="n">
-        <v>185.1820526123047</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="F182" t="n">
         <v>13183900</v>
@@ -5178,16 +5170,16 @@
         <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>183.4365624142317</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="C183" t="n">
-        <v>184.543705539598</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D183" t="n">
-        <v>181.2422289387738</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E183" t="n">
-        <v>182.0800628662109</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="F183" t="n">
         <v>11177800</v>
@@ -5204,16 +5196,16 @@
         <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>179.0379159792888</v>
+        <v>174.5914306640625</v>
       </c>
       <c r="C184" t="n">
-        <v>181.9903027945282</v>
+        <v>181.670672953058</v>
       </c>
       <c r="D184" t="n">
-        <v>171.1183533610167</v>
+        <v>170.8178179406258</v>
       </c>
       <c r="E184" t="n">
-        <v>174.8986053466797</v>
+        <v>178.7234714192057</v>
       </c>
       <c r="F184" t="n">
         <v>15427800</v>
@@ -5230,16 +5222,16 @@
         <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>170.1608274234686</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="C185" t="n">
-        <v>175.0781287299737</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D185" t="n">
-        <v>169.59228747941</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E185" t="n">
-        <v>170.4799957275391</v>
+        <v>169.861995238658</v>
       </c>
       <c r="F185" t="n">
         <v>10820500</v>
@@ -5256,16 +5248,16 @@
         <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>168.2700042724609</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="C186" t="n">
-        <v>168.9799957275391</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D186" t="n">
-        <v>163.3099975585938</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E186" t="n">
-        <v>166.4499969482422</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="F186" t="n">
         <v>16666000</v>
@@ -5282,16 +5274,16 @@
         <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>164.7400054931641</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="C187" t="n">
-        <v>166.5399932861328</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D187" t="n">
-        <v>161.3999938964844</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E187" t="n">
-        <v>165.8899993896484</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="F187" t="n">
         <v>13589400</v>
@@ -5308,16 +5300,16 @@
         <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>166.0299987792969</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="C188" t="n">
-        <v>169.9499969482422</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D188" t="n">
-        <v>164.1699981689453</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E188" t="n">
-        <v>164.5500030517578</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="F188" t="n">
         <v>13541800</v>
@@ -5334,16 +5326,16 @@
         <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>164.0599975585938</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="C189" t="n">
-        <v>166.3000030517578</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D189" t="n">
-        <v>160.5</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E189" t="n">
-        <v>161.7100067138672</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="F189" t="n">
         <v>16385300</v>
@@ -5360,16 +5352,16 @@
         <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>160.25</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="C190" t="n">
-        <v>161.4299926757812</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D190" t="n">
-        <v>154.2299957275391</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E190" t="n">
-        <v>155.0200042724609</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="F190" t="n">
         <v>19986200</v>
@@ -5386,16 +5378,16 @@
         <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>152.7299957275391</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="C191" t="n">
-        <v>154.4700012207031</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D191" t="n">
-        <v>149.8000030517578</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E191" t="n">
-        <v>151.7799987792969</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="F191" t="n">
         <v>57940800</v>
@@ -5412,16 +5404,16 @@
         <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>150.1600036621094</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="C192" t="n">
-        <v>153.8699951171875</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D192" t="n">
-        <v>146.3200073242188</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E192" t="n">
-        <v>150.1199951171875</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="F192" t="n">
         <v>20502800</v>
@@ -5438,16 +5430,16 @@
         <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>151.6499938964844</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="C193" t="n">
-        <v>155.1799926757812</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D193" t="n">
-        <v>150.8500061035156</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E193" t="n">
-        <v>153.4199981689453</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="F193" t="n">
         <v>20720700</v>
@@ -5464,16 +5456,16 @@
         <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>151.8099975585938</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="C194" t="n">
-        <v>157.0599975585938</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D194" t="n">
-        <v>150.3999938964844</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E194" t="n">
-        <v>152.7599945068359</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="F194" t="n">
         <v>13146800</v>
@@ -5490,16 +5482,16 @@
         <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>150.0099945068359</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="C195" t="n">
-        <v>154</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D195" t="n">
-        <v>148.7799987792969</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E195" t="n">
-        <v>150.1900024414062</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="F195" t="n">
         <v>11324700</v>
@@ -5516,16 +5508,16 @@
         <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>151.4900054931641</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="C196" t="n">
-        <v>158.4600067138672</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D196" t="n">
-        <v>151.4900054931641</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E196" t="n">
-        <v>158.3699951171875</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="F196" t="n">
         <v>21267900</v>
@@ -5542,16 +5534,16 @@
         <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>160.2700042724609</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="C197" t="n">
-        <v>161.7599945068359</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D197" t="n">
-        <v>157.6999969482422</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E197" t="n">
-        <v>157.9299926757812</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="F197" t="n">
         <v>12664100</v>
@@ -5568,16 +5560,16 @@
         <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>155.0899963378906</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="C198" t="n">
-        <v>157.6900024414062</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D198" t="n">
-        <v>154.0700073242188</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E198" t="n">
-        <v>156.6600036621094</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="F198" t="n">
         <v>13690500</v>
@@ -5594,16 +5586,16 @@
         <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>162.2200012207031</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="C199" t="n">
-        <v>165.8099975585938</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D199" t="n">
-        <v>161.1999969482422</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E199" t="n">
-        <v>163.2299957275391</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="F199" t="n">
         <v>14164600</v>
@@ -5620,16 +5612,16 @@
         <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>163</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="C200" t="n">
-        <v>167.2100067138672</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D200" t="n">
-        <v>162</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E200" t="n">
-        <v>166.1100006103516</v>
+        <v>162.7137441629</v>
       </c>
       <c r="F200" t="n">
         <v>10486300</v>
@@ -5646,16 +5638,16 @@
         <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>163.9900054931641</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="C201" t="n">
-        <v>167.7200012207031</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D201" t="n">
-        <v>162.3699951171875</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E201" t="n">
-        <v>165.6499938964844</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="F201" t="n">
         <v>10595500</v>
@@ -5672,16 +5664,16 @@
         <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>169.2200012207031</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="C202" t="n">
-        <v>172.3800048828125</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D202" t="n">
-        <v>167.6799926757812</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E202" t="n">
-        <v>169.5200042724609</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="F202" t="n">
         <v>13057900</v>
@@ -5698,16 +5690,16 @@
         <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>167.3699951171875</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="C203" t="n">
-        <v>167.5299987792969</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D203" t="n">
-        <v>164.7799987792969</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E203" t="n">
-        <v>166.5800018310547</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="F203" t="n">
         <v>9792400</v>
@@ -5724,16 +5716,16 @@
         <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>158.3300018310547</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="C204" t="n">
-        <v>163.8000030517578</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D204" t="n">
-        <v>156.4799957275391</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E204" t="n">
-        <v>162.5</v>
+        <v>158.05194011754</v>
       </c>
       <c r="F204" t="n">
         <v>13858600</v>
@@ -5750,16 +5742,16 @@
         <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>165.6000061035156</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="C205" t="n">
-        <v>166.3000030517578</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D205" t="n">
-        <v>162.4199981689453</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E205" t="n">
-        <v>163.3200073242188</v>
+        <v>165.309182555471</v>
       </c>
       <c r="F205" t="n">
         <v>8321500</v>
@@ -5776,16 +5768,16 @@
         <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>165.9199981689453</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="C206" t="n">
-        <v>172.7599945068359</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D206" t="n">
-        <v>165.9199981689453</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E206" t="n">
-        <v>171.2200012207031</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="F206" t="n">
         <v>14020700</v>
@@ -5802,16 +5794,16 @@
         <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>162.4900054931641</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="C207" t="n">
-        <v>171.3500061035156</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D207" t="n">
-        <v>161.4700012207031</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E207" t="n">
-        <v>167.5599975585938</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="F207" t="n">
         <v>13507900</v>
@@ -5828,16 +5820,16 @@
         <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>170.5200042724609</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="C208" t="n">
-        <v>172.8000030517578</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D208" t="n">
-        <v>166.5599975585938</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E208" t="n">
-        <v>167</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="F208" t="n">
         <v>13328100</v>
@@ -5854,16 +5846,16 @@
         <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>170.8399963378906</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="C209" t="n">
-        <v>174.5399932861328</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D209" t="n">
-        <v>166.8800048828125</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E209" t="n">
-        <v>172.6799926757812</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="F209" t="n">
         <v>12057500</v>
@@ -5880,16 +5872,16 @@
         <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>171.5</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="C210" t="n">
-        <v>175.4299926757812</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D210" t="n">
-        <v>169.75</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E210" t="n">
-        <v>170.7700042724609</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="F210" t="n">
         <v>10191500</v>
@@ -5906,16 +5898,16 @@
         <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>167.8600006103516</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="C211" t="n">
-        <v>175.3899993896484</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D211" t="n">
-        <v>166.5</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E211" t="n">
-        <v>173.7899932861328</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="F211" t="n">
         <v>13426500</v>
@@ -5932,16 +5924,16 @@
         <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>167.0599975585938</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="C212" t="n">
-        <v>172.4299926757812</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D212" t="n">
-        <v>166.9299926757812</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E212" t="n">
-        <v>170.0599975585938</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="F212" t="n">
         <v>12831800</v>
@@ -5958,16 +5950,16 @@
         <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>169.4700012207031</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="C213" t="n">
-        <v>169.5700073242188</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D213" t="n">
-        <v>162.2100067138672</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E213" t="n">
-        <v>163</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="F213" t="n">
         <v>12194500</v>
@@ -5984,16 +5976,16 @@
         <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>165.0500030517578</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="C214" t="n">
-        <v>165.8800048828125</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D214" t="n">
-        <v>155.1499938964844</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E214" t="n">
-        <v>156.9299926757812</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="F214" t="n">
         <v>12775000</v>
@@ -6010,16 +6002,16 @@
         <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>160.3800048828125</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="C215" t="n">
-        <v>164.4499969482422</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D215" t="n">
-        <v>159.5500030517578</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E215" t="n">
-        <v>163.6600036621094</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="F215" t="n">
         <v>10899100</v>
@@ -6036,16 +6028,16 @@
         <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>168</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="C216" t="n">
-        <v>176.9499969482422</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D216" t="n">
-        <v>167.1399993896484</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E216" t="n">
-        <v>173.6000061035156</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="F216" t="n">
         <v>17312000</v>
@@ -6062,16 +6054,16 @@
         <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>176.9100036621094</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="C217" t="n">
-        <v>184.5399932861328</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D217" t="n">
-        <v>176.9100036621094</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E217" t="n">
-        <v>181.5</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="F217" t="n">
         <v>17204600</v>
@@ -6088,16 +6080,16 @@
         <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>182.0099945068359</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="C218" t="n">
-        <v>190.1799926757812</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D218" t="n">
-        <v>182.0099945068359</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E218" t="n">
-        <v>188.3800048828125</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="F218" t="n">
         <v>18139500</v>
@@ -6114,16 +6106,16 @@
         <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>180.9900054931641</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="C219" t="n">
-        <v>182.5099945068359</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D219" t="n">
-        <v>175.8999938964844</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E219" t="n">
-        <v>180.7100067138672</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="F219" t="n">
         <v>12182400</v>
@@ -6140,16 +6132,16 @@
         <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>177.6999969482422</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="C220" t="n">
-        <v>184.4499969482422</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D220" t="n">
-        <v>177.0299987792969</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E220" t="n">
-        <v>184.0200042724609</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="F220" t="n">
         <v>9691500</v>
@@ -6166,16 +6158,16 @@
         <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>188.9900054931641</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="C221" t="n">
-        <v>193.6999969482422</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D221" t="n">
-        <v>185.8999938964844</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E221" t="n">
-        <v>185.9499969482422</v>
+        <v>188.658097974018</v>
       </c>
       <c r="F221" t="n">
         <v>12908000</v>
@@ -6192,16 +6184,16 @@
         <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>183.0899963378906</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="C222" t="n">
-        <v>191.2899932861328</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D222" t="n">
-        <v>183</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E222" t="n">
-        <v>190.9900054931641</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="F222" t="n">
         <v>9326900</v>
@@ -6218,16 +6210,16 @@
         <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>193.2799987792969</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="C223" t="n">
-        <v>194.9400024414062</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D223" t="n">
-        <v>190.4299926757812</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E223" t="n">
-        <v>192.9799957275391</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="F223" t="n">
         <v>9605500</v>
@@ -6244,16 +6236,16 @@
         <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>183.4400024414062</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="C224" t="n">
-        <v>187.0200042724609</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D224" t="n">
-        <v>183</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E224" t="n">
-        <v>186.7700042724609</v>
+        <v>183.117847615437</v>
       </c>
       <c r="F224" t="n">
         <v>13297600</v>
@@ -6270,16 +6262,16 @@
         <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>191.0899963378906</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="C225" t="n">
-        <v>194.6999969482422</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D225" t="n">
-        <v>190.6000061035156</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E225" t="n">
-        <v>192.7400054931641</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="F225" t="n">
         <v>11392800</v>
@@ -6296,16 +6288,16 @@
         <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>190.1699981689453</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="C226" t="n">
-        <v>198.1799926757812</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D226" t="n">
-        <v>190</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E226" t="n">
-        <v>197.5099945068359</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="F226" t="n">
         <v>9706600</v>
@@ -6322,16 +6314,16 @@
         <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>196.9400024414062</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="C227" t="n">
-        <v>199.3899993896484</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D227" t="n">
-        <v>195.5</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E227" t="n">
-        <v>197.4700012207031</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="F227" t="n">
         <v>11171600</v>
@@ -6348,16 +6340,16 @@
         <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>192</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="C228" t="n">
-        <v>196.5</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D228" t="n">
-        <v>191.7799987792969</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E228" t="n">
-        <v>193.3200073242188</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="F228" t="n">
         <v>12787900</v>
@@ -6374,16 +6366,16 @@
         <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>196.8399963378906</v>
+        <v>201.016357421875</v>
       </c>
       <c r="C229" t="n">
-        <v>202.9900054931641</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D229" t="n">
-        <v>191.3899993896484</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E229" t="n">
-        <v>201.3699951171875</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="F229" t="n">
         <v>15058700</v>
@@ -6400,16 +6392,16 @@
         <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>202.75</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="C230" t="n">
-        <v>204.3999938964844</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D230" t="n">
-        <v>195.3200073242188</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E230" t="n">
-        <v>196.2100067138672</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="F230" t="n">
         <v>8664800</v>
@@ -6426,16 +6418,16 @@
         <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>193.8300018310547</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="C231" t="n">
-        <v>194.9400024414062</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D231" t="n">
-        <v>189.9100036621094</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E231" t="n">
-        <v>190.9700012207031</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="F231" t="n">
         <v>14378800</v>
@@ -6452,16 +6444,16 @@
         <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>194.0899963378906</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="C232" t="n">
-        <v>199.4100036621094</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D232" t="n">
-        <v>193.2299957275391</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E232" t="n">
-        <v>196.1399993896484</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="F232" t="n">
         <v>14152900</v>
@@ -6478,16 +6470,16 @@
         <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>194.2100067138672</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="C233" t="n">
-        <v>207.9499969482422</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D233" t="n">
-        <v>194.2100067138672</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E233" t="n">
-        <v>206.0899963378906</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="F233" t="n">
         <v>17843600</v>
@@ -6504,16 +6496,16 @@
         <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>205.2200012207031</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="C234" t="n">
-        <v>207.8800048828125</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D234" t="n">
-        <v>203</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E234" t="n">
-        <v>205.4299926757812</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="F234" t="n">
         <v>11482300</v>
@@ -6530,16 +6522,16 @@
         <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>205.5800018310547</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="C235" t="n">
-        <v>211.0700073242188</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D235" t="n">
-        <v>204.7299957275391</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E235" t="n">
-        <v>209.1699981689453</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="F235" t="n">
         <v>9685400</v>
@@ -6556,16 +6548,16 @@
         <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>208.4199981689453</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="C236" t="n">
-        <v>213.1699981689453</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D236" t="n">
-        <v>207.3899993896484</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E236" t="n">
-        <v>209.0599975585938</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="F236" t="n">
         <v>9580200</v>
@@ -6582,16 +6574,16 @@
         <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>205.8500061035156</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="C237" t="n">
-        <v>210.3099975585938</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D237" t="n">
-        <v>204.7599945068359</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E237" t="n">
-        <v>205.6900024414062</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="F237" t="n">
         <v>10081800</v>
@@ -6608,16 +6600,16 @@
         <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>199.9400024414062</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="C238" t="n">
-        <v>206.4400024414062</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D238" t="n">
-        <v>198.9499969482422</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E238" t="n">
-        <v>205.6199951171875</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="F238" t="n">
         <v>14888900</v>
@@ -6634,16 +6626,16 @@
         <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>230.0500030517578</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="C239" t="n">
-        <v>254.4799957275391</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D239" t="n">
-        <v>230.0500030517578</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E239" t="n">
-        <v>252.0500030517578</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="F239" t="n">
         <v>55517500</v>
@@ -6660,16 +6652,16 @@
         <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>250.4700012207031</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="C240" t="n">
-        <v>263.5299987792969</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D240" t="n">
-        <v>249</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E240" t="n">
-        <v>256</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="F240" t="n">
         <v>34362700</v>
@@ -6686,16 +6678,16 @@
         <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>254.3899993896484</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="C241" t="n">
-        <v>262.2799987792969</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D241" t="n">
-        <v>254.3899993896484</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E241" t="n">
-        <v>257.5400085449219</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="F241" t="n">
         <v>22471500</v>
@@ -6712,16 +6704,16 @@
         <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>255.0099945068359</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="C242" t="n">
-        <v>262.3200073242188</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D242" t="n">
-        <v>254.25</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E242" t="n">
-        <v>258.1099853515625</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="F242" t="n">
         <v>15897500</v>
@@ -6738,16 +6730,16 @@
         <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>259.3800048828125</v>
+        <v>256.478759765625</v>
       </c>
       <c r="C243" t="n">
-        <v>264.5499877929688</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D243" t="n">
-        <v>253.6000061035156</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E243" t="n">
-        <v>256.9299926757812</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="F243" t="n">
         <v>14393700</v>
@@ -6764,16 +6756,16 @@
         <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>261.9800109863281</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="C244" t="n">
-        <v>268.2699890136719</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D244" t="n">
-        <v>261.6000061035156</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E244" t="n">
-        <v>264.4299926757812</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="F244" t="n">
         <v>16028300</v>
@@ -6790,16 +6782,16 @@
         <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>263.3599853515625</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="C245" t="n">
-        <v>263.6000061035156</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D245" t="n">
-        <v>257.8200073242188</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E245" t="n">
-        <v>259.2300109863281</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="F245" t="n">
         <v>10490600</v>
@@ -6816,16 +6808,16 @@
         <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>253.7200012207031</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="C246" t="n">
-        <v>254</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D246" t="n">
-        <v>245.8899993896484</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E246" t="n">
-        <v>249.1199951171875</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="F246" t="n">
         <v>17482700</v>
@@ -6842,16 +6834,16 @@
         <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>249.7799987792969</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="C247" t="n">
-        <v>254.8000030517578</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D247" t="n">
-        <v>243.4499969482422</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E247" t="n">
-        <v>244.1600036621094</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="F247" t="n">
         <v>11853700</v>
@@ -6868,16 +6860,16 @@
         <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>245.3500061035156</v>
+        <v>242.5732421875</v>
       </c>
       <c r="C248" t="n">
-        <v>248.5</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D248" t="n">
-        <v>241.75</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E248" t="n">
-        <v>243</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="F248" t="n">
         <v>10732600</v>
@@ -6894,16 +6886,16 @@
         <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>242.0200042724609</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="C249" t="n">
-        <v>250.5500030517578</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D249" t="n">
-        <v>242.0200042724609</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E249" t="n">
-        <v>247.7200012207031</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="F249" t="n">
         <v>9738300</v>
@@ -6920,16 +6912,16 @@
         <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>255.75</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="C250" t="n">
-        <v>260.1799926757812</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D250" t="n">
-        <v>251.5</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E250" t="n">
-        <v>259.4299926757812</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="F250" t="n">
         <v>12963700</v>
@@ -6946,16 +6938,16 @@
         <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>256.8900146484375</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="C251" t="n">
-        <v>262.3399963378906</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D251" t="n">
-        <v>255.0800018310547</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E251" t="n">
-        <v>255.6499938964844</v>
+        <v>256.43886230448</v>
       </c>
       <c r="F251" t="n">
         <v>11502800</v>
@@ -6971,17 +6963,51 @@
       <c r="A252" s="1" t="n">
         <v>46281</v>
       </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+      <c r="B252" t="n">
+        <v>250.0999908447266</v>
+      </c>
+      <c r="C252" t="n">
+        <v>255.9497000259878</v>
+      </c>
+      <c r="D252" t="n">
+        <v>249.1616544830015</v>
+      </c>
+      <c r="E252" t="n">
+        <v>251.4077029961344</v>
+      </c>
       <c r="F252" t="n">
-        <v>9423825</v>
+        <v>9423800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B253" t="n">
+        <v>242.8500061035156</v>
+      </c>
+      <c r="C253" t="n">
+        <v>247</v>
+      </c>
+      <c r="D253" t="n">
+        <v>241.5200042724609</v>
+      </c>
+      <c r="E253" t="n">
+        <v>244.1799926757812</v>
+      </c>
+      <c r="F253" t="n">
+        <v>16590200</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10646,37 +10672,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>250.54</v>
+        <v>242.85</v>
       </c>
       <c r="D2" t="n">
-        <v>255.65</v>
+        <v>250.1</v>
       </c>
       <c r="E2" t="n">
-        <v>251.85</v>
+        <v>244.18</v>
       </c>
       <c r="F2" t="n">
-        <v>256.4</v>
+        <v>246.915</v>
       </c>
       <c r="G2" t="n">
-        <v>249.6</v>
+        <v>241.52</v>
       </c>
       <c r="H2" t="n">
-        <v>9423825</v>
+        <v>15020557</v>
       </c>
       <c r="I2" t="n">
-        <v>15011672</v>
+        <v>14134927</v>
       </c>
       <c r="J2" t="n">
-        <v>206194409472</v>
+        <v>199865548800</v>
       </c>
       <c r="K2" t="n">
-        <v>22.943222</v>
+        <v>22.93201</v>
       </c>
       <c r="L2" t="n">
-        <v>15.638098</v>
+        <v>15.167262</v>
       </c>
       <c r="M2" t="n">
-        <v>10.92</v>
+        <v>10.59</v>
       </c>
       <c r="N2" t="n">
         <v>269.11</v>
@@ -10688,7 +10714,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10712,7 +10738,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.3727055</v>
+        <v>5.2077975</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10724,7 +10750,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>237167427584</v>
+        <v>230838550528</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10751,7 +10777,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:10:36</t>
+          <t>2026-09-18 13:16:05</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,22 +433,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Close</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -469,17 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>45919</v>
+      </c>
+      <c r="B2" t="n">
+        <v>243.9508327525358</v>
+      </c>
+      <c r="C2" t="n">
+        <v>245.1209010026767</v>
+      </c>
+      <c r="D2" t="n">
+        <v>241.3032908232194</v>
+      </c>
+      <c r="E2" t="n">
+        <v>245.0118255615234</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>11813900</v>
       </c>
       <c r="G2" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -487,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>242.2254791259766</v>
+        <v>243.2170528270286</v>
       </c>
       <c r="C3" t="n">
-        <v>245.210158040453</v>
+        <v>248.3733148082552</v>
       </c>
       <c r="D3" t="n">
-        <v>240.9066632901507</v>
+        <v>241.1148880888675</v>
       </c>
       <c r="E3" t="n">
-        <v>242.10649322906</v>
+        <v>247.5899658203125</v>
       </c>
       <c r="F3" t="n">
-        <v>9344400</v>
+        <v>7523800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -513,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>245.0118255615234</v>
+        <v>247.6395695794253</v>
       </c>
       <c r="C4" t="n">
-        <v>245.1209010026767</v>
+        <v>249.2459397432638</v>
       </c>
       <c r="D4" t="n">
-        <v>241.3032908232194</v>
+        <v>242.0767518252397</v>
       </c>
       <c r="E4" t="n">
-        <v>243.9508327525358</v>
+        <v>242.5031280517578</v>
       </c>
       <c r="F4" t="n">
-        <v>11813900</v>
+        <v>7669800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -539,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>247.5899810791016</v>
+        <v>243.6037942867359</v>
       </c>
       <c r="C5" t="n">
-        <v>248.3733301153215</v>
+        <v>246.7471312330163</v>
       </c>
       <c r="D5" t="n">
-        <v>241.1149029486022</v>
+        <v>240.9661625460427</v>
       </c>
       <c r="E5" t="n">
-        <v>243.2170678163182</v>
+        <v>243.8219451904297</v>
       </c>
       <c r="F5" t="n">
-        <v>7523800</v>
+        <v>6707100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -565,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>242.5031433105469</v>
+        <v>242.4436227791717</v>
       </c>
       <c r="C6" t="n">
-        <v>249.2459554263243</v>
+        <v>242.6022807239559</v>
       </c>
       <c r="D6" t="n">
-        <v>242.0767670572004</v>
+        <v>237.4757650354455</v>
       </c>
       <c r="E6" t="n">
-        <v>247.6395851614097</v>
+        <v>238.9234771728516</v>
       </c>
       <c r="F6" t="n">
-        <v>7669800</v>
+        <v>8145500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -591,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>243.8219299316406</v>
+        <v>238.6656837954339</v>
       </c>
       <c r="C7" t="n">
-        <v>246.7471157911642</v>
+        <v>242.4733839178257</v>
       </c>
       <c r="D7" t="n">
-        <v>240.9661474659734</v>
+        <v>238.3285469902175</v>
       </c>
       <c r="E7" t="n">
-        <v>243.6037790415992</v>
+        <v>241.3826293945312</v>
       </c>
       <c r="F7" t="n">
-        <v>6707100</v>
+        <v>4974600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -617,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B8" t="n">
-        <v>238.9234771728516</v>
+        <v>242.6617806304829</v>
       </c>
       <c r="C8" t="n">
-        <v>242.6022807239559</v>
+        <v>243.7525351190903</v>
       </c>
       <c r="D8" t="n">
-        <v>237.4757650354455</v>
+        <v>240.8273340261308</v>
       </c>
       <c r="E8" t="n">
-        <v>242.4436227791717</v>
+        <v>243.0385894775391</v>
       </c>
       <c r="F8" t="n">
-        <v>8145500</v>
+        <v>6373500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -643,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B9" t="n">
-        <v>241.3826293945312</v>
+        <v>242.989012448683</v>
       </c>
       <c r="C9" t="n">
-        <v>242.4733839178257</v>
+        <v>243.1476704015903</v>
       </c>
       <c r="D9" t="n">
-        <v>238.3285469902175</v>
+        <v>233.8267199294288</v>
       </c>
       <c r="E9" t="n">
-        <v>238.6656837954339</v>
+        <v>235.0067138671875</v>
       </c>
       <c r="F9" t="n">
-        <v>4974600</v>
+        <v>10801100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -669,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B10" t="n">
-        <v>243.0386047363281</v>
+        <v>234.5010077854061</v>
       </c>
       <c r="C10" t="n">
-        <v>243.7525504227033</v>
+        <v>240.4307087963897</v>
       </c>
       <c r="D10" t="n">
-        <v>240.8273491460897</v>
+        <v>231.5460601627856</v>
       </c>
       <c r="E10" t="n">
-        <v>242.6617958656146</v>
+        <v>233.7077331542969</v>
       </c>
       <c r="F10" t="n">
-        <v>6373500</v>
+        <v>10016600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -695,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B11" t="n">
-        <v>235.0067138671875</v>
+        <v>233.4498996394798</v>
       </c>
       <c r="C11" t="n">
-        <v>243.1476704015903</v>
+        <v>237.3865110117534</v>
       </c>
       <c r="D11" t="n">
-        <v>233.8267199294288</v>
+        <v>231.6353042398812</v>
       </c>
       <c r="E11" t="n">
-        <v>242.989012448683</v>
+        <v>236.8708953857422</v>
       </c>
       <c r="F11" t="n">
-        <v>10801100</v>
+        <v>7679200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -721,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B12" t="n">
-        <v>233.7077331542969</v>
+        <v>236.7419954840688</v>
       </c>
       <c r="C12" t="n">
-        <v>240.4307087963897</v>
+        <v>240.7678464733125</v>
       </c>
       <c r="D12" t="n">
-        <v>231.5460601627856</v>
+        <v>236.4940981065986</v>
       </c>
       <c r="E12" t="n">
-        <v>234.5010077854061</v>
+        <v>238.3384552001953</v>
       </c>
       <c r="F12" t="n">
-        <v>10016600</v>
+        <v>8849800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -747,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B13" t="n">
-        <v>236.8708953857422</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="C13" t="n">
-        <v>237.3865110117534</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D13" t="n">
-        <v>231.6353042398812</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E13" t="n">
-        <v>233.4498996394798</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="F13" t="n">
-        <v>7679200</v>
+        <v>13922600</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -773,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B14" t="n">
-        <v>238.3384399414062</v>
+        <v>244.4069666278678</v>
       </c>
       <c r="C14" t="n">
-        <v>240.7678310589901</v>
+        <v>245.2795701971395</v>
       </c>
       <c r="D14" t="n">
-        <v>236.4940829658881</v>
+        <v>235.5520799850208</v>
       </c>
       <c r="E14" t="n">
-        <v>236.7419803274875</v>
+        <v>237.7236633300781</v>
       </c>
       <c r="F14" t="n">
-        <v>8849800</v>
+        <v>8387400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -799,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B15" t="n">
-        <v>243.7128601074219</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C15" t="n">
-        <v>248.3634171689519</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D15" t="n">
-        <v>233.430082086989</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E15" t="n">
-        <v>237.3171110157645</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F15" t="n">
-        <v>13922600</v>
+        <v>7120200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -825,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B16" t="n">
-        <v>237.7236633300781</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C16" t="n">
-        <v>245.2795701971395</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D16" t="n">
-        <v>235.5520799850208</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E16" t="n">
-        <v>244.4069666278678</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F16" t="n">
-        <v>8387400</v>
+        <v>7929100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -851,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B17" t="n">
-        <v>238.4078521728516</v>
+        <v>244.4466434616172</v>
       </c>
       <c r="C17" t="n">
-        <v>239.290381338098</v>
+        <v>246.9553636418975</v>
       </c>
       <c r="D17" t="n">
-        <v>233.6680556537968</v>
+        <v>238.6954214370453</v>
       </c>
       <c r="E17" t="n">
-        <v>237.7236681390551</v>
+        <v>239.6473388671875</v>
       </c>
       <c r="F17" t="n">
-        <v>7120200</v>
+        <v>7988300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -877,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B18" t="n">
-        <v>243.2666320800781</v>
+        <v>240.8471826425636</v>
       </c>
       <c r="C18" t="n">
-        <v>243.8913382509171</v>
+        <v>247.2528577250976</v>
       </c>
       <c r="D18" t="n">
-        <v>235.1554228281352</v>
+        <v>240.331551845499</v>
       </c>
       <c r="E18" t="n">
-        <v>237.2576026687149</v>
+        <v>246.6578979492188</v>
       </c>
       <c r="F18" t="n">
-        <v>7929100</v>
+        <v>8276500</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -903,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B19" t="n">
-        <v>239.6473388671875</v>
+        <v>246.0232549541512</v>
       </c>
       <c r="C19" t="n">
-        <v>246.9553636418975</v>
+        <v>246.1918233421939</v>
       </c>
       <c r="D19" t="n">
-        <v>238.6954214370453</v>
+        <v>237.5352518241517</v>
       </c>
       <c r="E19" t="n">
-        <v>244.4466434616172</v>
+        <v>237.7534027099609</v>
       </c>
       <c r="F19" t="n">
-        <v>7988300</v>
+        <v>9123900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -929,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B20" t="n">
-        <v>246.6578826904297</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C20" t="n">
-        <v>247.252842429503</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D20" t="n">
-        <v>240.3315369780713</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E20" t="n">
-        <v>240.8471677432379</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F20" t="n">
-        <v>8276500</v>
+        <v>8389200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -955,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B21" t="n">
-        <v>237.75341796875</v>
+        <v>251.0605301777264</v>
       </c>
       <c r="C21" t="n">
-        <v>246.1918391425529</v>
+        <v>254.5806605495149</v>
       </c>
       <c r="D21" t="n">
-        <v>237.5352670689401</v>
+        <v>240.6290051386317</v>
       </c>
       <c r="E21" t="n">
-        <v>246.0232707436915</v>
+        <v>243.9309997558594</v>
       </c>
       <c r="F21" t="n">
-        <v>9123900</v>
+        <v>24869700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -981,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B22" t="n">
-        <v>234.5902404785156</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="C22" t="n">
-        <v>239.2903800503502</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D22" t="n">
-        <v>233.915951765761</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E22" t="n">
-        <v>238.8441526809671</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="F22" t="n">
-        <v>8389200</v>
+        <v>10851200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1007,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B23" t="n">
-        <v>243.9310150146484</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C23" t="n">
-        <v>254.5806764744798</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D23" t="n">
-        <v>240.6290201908687</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E23" t="n">
-        <v>251.0605458824941</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F23" t="n">
-        <v>24869700</v>
+        <v>9963900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1033,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B24" t="n">
-        <v>241.0355834960938</v>
+        <v>252.3595144668565</v>
       </c>
       <c r="C24" t="n">
-        <v>248.670819810711</v>
+        <v>264.883294034403</v>
       </c>
       <c r="D24" t="n">
-        <v>240.1233229489625</v>
+        <v>251.863719742953</v>
       </c>
       <c r="E24" t="n">
-        <v>244.4962363844956</v>
+        <v>261.194580078125</v>
       </c>
       <c r="F24" t="n">
-        <v>10851200</v>
+        <v>13354700</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1059,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B25" t="n">
-        <v>252.1413879394531</v>
+        <v>259.9947875033736</v>
       </c>
       <c r="C25" t="n">
-        <v>253.2519633865538</v>
+        <v>260.1930872533099</v>
       </c>
       <c r="D25" t="n">
-        <v>242.2453285307239</v>
+        <v>254.3526406430638</v>
       </c>
       <c r="E25" t="n">
-        <v>242.9394381851618</v>
+        <v>254.4815521240234</v>
       </c>
       <c r="F25" t="n">
-        <v>9963900</v>
+        <v>9370000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1085,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B26" t="n">
-        <v>261.1946105957031</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C26" t="n">
-        <v>264.8833249829649</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D26" t="n">
-        <v>251.8637491703276</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E26" t="n">
-        <v>252.359543952159</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F26" t="n">
-        <v>13354700</v>
+        <v>6110100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1111,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B27" t="n">
-        <v>254.4815368652344</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C27" t="n">
-        <v>260.1930716520554</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D27" t="n">
-        <v>254.3526253920043</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E27" t="n">
-        <v>259.9947719140093</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F27" t="n">
-        <v>9370000</v>
+        <v>5490800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1137,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B28" t="n">
-        <v>252.9049072265625</v>
+        <v>254.9178098920577</v>
       </c>
       <c r="C28" t="n">
-        <v>256.3853809552256</v>
+        <v>255.9292505274036</v>
       </c>
       <c r="D28" t="n">
-        <v>251.982721115611</v>
+        <v>252.7759881170209</v>
       </c>
       <c r="E28" t="n">
-        <v>255.4334634999039</v>
+        <v>253.3213653564453</v>
       </c>
       <c r="F28" t="n">
-        <v>6110100</v>
+        <v>4942400</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1163,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B29" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213815169481</v>
       </c>
       <c r="C29" t="n">
-        <v>256.3258839430272</v>
+        <v>256.6630334318976</v>
       </c>
       <c r="D29" t="n">
-        <v>251.8637312244832</v>
+        <v>252.0025656103722</v>
       </c>
       <c r="E29" t="n">
-        <v>255.254980605377</v>
+        <v>252.1215515136719</v>
       </c>
       <c r="F29" t="n">
-        <v>5490800</v>
+        <v>6435600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1189,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B30" t="n">
-        <v>253.3213500976562</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C30" t="n">
-        <v>255.9292351115289</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D30" t="n">
-        <v>252.7759728910826</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E30" t="n">
-        <v>254.917794537107</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F30" t="n">
-        <v>4942400</v>
+        <v>7904200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1215,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B31" t="n">
-        <v>252.1215362548828</v>
+        <v>248.3931704298276</v>
       </c>
       <c r="C31" t="n">
-        <v>256.663017898251</v>
+        <v>257.099325053219</v>
       </c>
       <c r="D31" t="n">
-        <v>252.0025503587843</v>
+        <v>247.8973756784706</v>
       </c>
       <c r="E31" t="n">
-        <v>253.3213661855435</v>
+        <v>254.4914398193359</v>
       </c>
       <c r="F31" t="n">
-        <v>6435600</v>
+        <v>7767800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1241,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B32" t="n">
-        <v>249.3451080322266</v>
+        <v>252.657000570364</v>
       </c>
       <c r="C32" t="n">
-        <v>251.4373625303139</v>
+        <v>259.6179629024988</v>
       </c>
       <c r="D32" t="n">
-        <v>246.9454480725237</v>
+        <v>250.5052532311086</v>
       </c>
       <c r="E32" t="n">
-        <v>249.8805597170771</v>
+        <v>258.2198181152344</v>
       </c>
       <c r="F32" t="n">
-        <v>7904200</v>
+        <v>6878300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1267,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B33" t="n">
-        <v>254.491455078125</v>
+        <v>257.8133023432115</v>
       </c>
       <c r="C33" t="n">
-        <v>257.0993404683716</v>
+        <v>259.3601797363976</v>
       </c>
       <c r="D33" t="n">
-        <v>247.897390541893</v>
+        <v>252.9545192358491</v>
       </c>
       <c r="E33" t="n">
-        <v>248.3931853229768</v>
+        <v>259.1420288085938</v>
       </c>
       <c r="F33" t="n">
-        <v>7767800</v>
+        <v>7054300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1293,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B34" t="n">
-        <v>258.2198181152344</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C34" t="n">
-        <v>259.6179629024988</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D34" t="n">
-        <v>250.5052532311086</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E34" t="n">
-        <v>252.657000570364</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F34" t="n">
-        <v>6878300</v>
+        <v>6792200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1319,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B35" t="n">
-        <v>259.1420288085938</v>
+        <v>252.5578552142711</v>
       </c>
       <c r="C35" t="n">
-        <v>259.3601797363976</v>
+        <v>254.6699306658516</v>
       </c>
       <c r="D35" t="n">
-        <v>252.9545192358491</v>
+        <v>249.8904769054258</v>
       </c>
       <c r="E35" t="n">
-        <v>257.8133023432115</v>
+        <v>250.5548400878906</v>
       </c>
       <c r="F35" t="n">
-        <v>7054300</v>
+        <v>5241200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1345,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B36" t="n">
-        <v>252.300048828125</v>
+        <v>248.4328324243326</v>
       </c>
       <c r="C36" t="n">
-        <v>257.0795177464699</v>
+        <v>248.4328324243326</v>
       </c>
       <c r="D36" t="n">
-        <v>251.3282953006253</v>
+        <v>232.5079071065105</v>
       </c>
       <c r="E36" t="n">
-        <v>255.9788376046017</v>
+        <v>237.2576293945312</v>
       </c>
       <c r="F36" t="n">
-        <v>6792200</v>
+        <v>11041800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1371,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B37" t="n">
-        <v>250.5548400878906</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="C37" t="n">
-        <v>254.6699306658516</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D37" t="n">
-        <v>249.8904769054258</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E37" t="n">
-        <v>252.5578552142711</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="F37" t="n">
-        <v>5241200</v>
+        <v>5741500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1397,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B38" t="n">
-        <v>237.2576141357422</v>
+        <v>237.9814840335094</v>
       </c>
       <c r="C38" t="n">
-        <v>248.4328164468309</v>
+        <v>239.8754236419186</v>
       </c>
       <c r="D38" t="n">
-        <v>232.5078921531912</v>
+        <v>233.1028654264771</v>
       </c>
       <c r="E38" t="n">
-        <v>248.4328164468309</v>
+        <v>239.6771087646484</v>
       </c>
       <c r="F38" t="n">
-        <v>11041800</v>
+        <v>6486600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1423,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B39" t="n">
-        <v>237.8624877929688</v>
+        <v>239.8654952673756</v>
       </c>
       <c r="C39" t="n">
-        <v>238.943316687993</v>
+        <v>243.63353841341</v>
       </c>
       <c r="D39" t="n">
-        <v>233.8068753463891</v>
+        <v>239.1317287169831</v>
       </c>
       <c r="E39" t="n">
-        <v>234.1638481621394</v>
+        <v>242.4436340332031</v>
       </c>
       <c r="F39" t="n">
-        <v>5741500</v>
+        <v>5762800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1449,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B40" t="n">
-        <v>239.6771087646484</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="C40" t="n">
-        <v>239.8754236419186</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D40" t="n">
-        <v>233.1028654264771</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E40" t="n">
-        <v>237.9814840335094</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="F40" t="n">
-        <v>6486600</v>
+        <v>4278200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1475,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B41" t="n">
-        <v>242.4436340332031</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C41" t="n">
-        <v>243.63353841341</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D41" t="n">
-        <v>239.1317287169831</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E41" t="n">
-        <v>239.8654952673756</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F41" t="n">
-        <v>5762800</v>
+        <v>5542100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1501,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="n">
-        <v>243.9508514404297</v>
+        <v>236.3056926086296</v>
       </c>
       <c r="C42" t="n">
-        <v>246.3405706207466</v>
+        <v>243.1179076689137</v>
       </c>
       <c r="D42" t="n">
-        <v>241.63052052637</v>
+        <v>235.4231785540507</v>
       </c>
       <c r="E42" t="n">
-        <v>243.6732075926712</v>
+        <v>241.6107025146484</v>
       </c>
       <c r="F42" t="n">
-        <v>4278200</v>
+        <v>5512900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1527,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B43" t="n">
-        <v>238.4078521728516</v>
+        <v>240.0340571163644</v>
       </c>
       <c r="C43" t="n">
-        <v>243.8318478561575</v>
+        <v>240.7876596253181</v>
       </c>
       <c r="D43" t="n">
-        <v>237.8922365355373</v>
+        <v>233.6085468088289</v>
       </c>
       <c r="E43" t="n">
-        <v>243.1873207442872</v>
+        <v>235.0364379882812</v>
       </c>
       <c r="F43" t="n">
-        <v>5542100</v>
+        <v>5280900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1553,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B44" t="n">
-        <v>241.6106872558594</v>
+        <v>234.2530933083125</v>
       </c>
       <c r="C44" t="n">
-        <v>243.1178923149379</v>
+        <v>235.7900448264734</v>
       </c>
       <c r="D44" t="n">
-        <v>235.4231636860313</v>
+        <v>228.3333031775737</v>
       </c>
       <c r="E44" t="n">
-        <v>236.3056776848755</v>
+        <v>231.5361328125</v>
       </c>
       <c r="F44" t="n">
-        <v>5512900</v>
+        <v>8045100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1579,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B45" t="n">
-        <v>235.0364379882812</v>
+        <v>230.0487531290293</v>
       </c>
       <c r="C45" t="n">
-        <v>240.7876596253181</v>
+        <v>230.3263969654728</v>
       </c>
       <c r="D45" t="n">
-        <v>233.6085468088289</v>
+        <v>223.1671199033486</v>
       </c>
       <c r="E45" t="n">
-        <v>240.0340571163644</v>
+        <v>225.9634094238281</v>
       </c>
       <c r="F45" t="n">
-        <v>5280900</v>
+        <v>9710700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1605,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B46" t="n">
-        <v>231.5361633300781</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C46" t="n">
-        <v>235.7900759047376</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D46" t="n">
-        <v>228.3333332730034</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E46" t="n">
-        <v>234.2531241839991</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F46" t="n">
-        <v>8045100</v>
+        <v>7521100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1631,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B47" t="n">
-        <v>225.9634094238281</v>
+        <v>222.9688137796853</v>
       </c>
       <c r="C47" t="n">
-        <v>230.3263969654728</v>
+        <v>226.7566777713456</v>
       </c>
       <c r="D47" t="n">
-        <v>223.1671199033486</v>
+        <v>220.0932103050241</v>
       </c>
       <c r="E47" t="n">
-        <v>230.0487531290293</v>
+        <v>225.1998901367188</v>
       </c>
       <c r="F47" t="n">
-        <v>9710700</v>
+        <v>7479300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1657,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B48" t="n">
-        <v>223.4745178222656</v>
+        <v>225.4279691980636</v>
       </c>
       <c r="C48" t="n">
-        <v>229.1265900019938</v>
+        <v>226.9153535529684</v>
       </c>
       <c r="D48" t="n">
-        <v>221.4219354522067</v>
+        <v>223.1473101611184</v>
       </c>
       <c r="E48" t="n">
-        <v>227.3218898732066</v>
+        <v>224.912353515625</v>
       </c>
       <c r="F48" t="n">
-        <v>7521100</v>
+        <v>8563300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1683,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B49" t="n">
-        <v>225.1998901367188</v>
+        <v>224.8924975422598</v>
       </c>
       <c r="C49" t="n">
-        <v>226.7566777713456</v>
+        <v>232.656645001925</v>
       </c>
       <c r="D49" t="n">
-        <v>220.0932103050241</v>
+        <v>224.614853697738</v>
       </c>
       <c r="E49" t="n">
-        <v>222.9688137796853</v>
+        <v>232.1509246826172</v>
       </c>
       <c r="F49" t="n">
-        <v>7479300</v>
+        <v>10233000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1709,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B50" t="n">
-        <v>224.9123382568359</v>
+        <v>228.5712919801828</v>
       </c>
       <c r="C50" t="n">
-        <v>226.9153381582893</v>
+        <v>230.8618764526245</v>
       </c>
       <c r="D50" t="n">
-        <v>223.1472950220756</v>
+        <v>224.0992287472785</v>
       </c>
       <c r="E50" t="n">
-        <v>225.4279539042935</v>
+        <v>226.2311401367188</v>
       </c>
       <c r="F50" t="n">
-        <v>8563300</v>
+        <v>8506600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1735,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B51" t="n">
-        <v>232.1509094238281</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C51" t="n">
-        <v>232.656629709896</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D51" t="n">
-        <v>224.6148389342789</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E51" t="n">
-        <v>224.8924827605518</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F51" t="n">
-        <v>10233000</v>
+        <v>3691500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1761,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B52" t="n">
-        <v>226.2311401367188</v>
+        <v>226.7467645282661</v>
       </c>
       <c r="C52" t="n">
-        <v>230.8618764526245</v>
+        <v>232.2798356411572</v>
       </c>
       <c r="D52" t="n">
-        <v>224.0992287472785</v>
+        <v>226.6773611325171</v>
       </c>
       <c r="E52" t="n">
-        <v>228.5712919801828</v>
+        <v>230.8717803955078</v>
       </c>
       <c r="F52" t="n">
-        <v>8506600</v>
+        <v>5634700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1787,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B53" t="n">
-        <v>228.6010284423828</v>
+        <v>231.0601885043919</v>
       </c>
       <c r="C53" t="n">
-        <v>230.6040433967966</v>
+        <v>234.6596480847597</v>
       </c>
       <c r="D53" t="n">
-        <v>226.7071040647147</v>
+        <v>229.67195413226</v>
       </c>
       <c r="E53" t="n">
-        <v>227.0739873247604</v>
+        <v>232.7359771728516</v>
       </c>
       <c r="F53" t="n">
-        <v>3691500</v>
+        <v>7626200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1813,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B54" t="n">
-        <v>230.8717803955078</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="C54" t="n">
-        <v>232.2798356411572</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D54" t="n">
-        <v>226.6773611325171</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E54" t="n">
-        <v>226.7467645282661</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="F54" t="n">
-        <v>5634700</v>
+        <v>13782000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1839,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B55" t="n">
-        <v>232.7359619140625</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C55" t="n">
-        <v>234.6596326998496</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D55" t="n">
-        <v>229.6719390743564</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E55" t="n">
-        <v>231.060173355472</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F55" t="n">
-        <v>7626200</v>
+        <v>20912100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1865,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B56" t="n">
-        <v>236.7122497558594</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C56" t="n">
-        <v>237.2477014354837</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D56" t="n">
-        <v>231.1990144844042</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E56" t="n">
-        <v>233.3805083869321</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F56" t="n">
-        <v>13782000</v>
+        <v>15852400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1891,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B57" t="n">
-        <v>245.3787384033203</v>
+        <v>259.6774704470017</v>
       </c>
       <c r="C57" t="n">
-        <v>246.8760330652079</v>
+        <v>262.0572792621351</v>
       </c>
       <c r="D57" t="n">
-        <v>235.6016655641461</v>
+        <v>254.1840559885597</v>
       </c>
       <c r="E57" t="n">
-        <v>241.6404418420451</v>
+        <v>257.3472290039062</v>
       </c>
       <c r="F57" t="n">
-        <v>20912100</v>
+        <v>10805400</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1917,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B58" t="n">
-        <v>258.3784484863281</v>
+        <v>257.8132661327708</v>
       </c>
       <c r="C58" t="n">
-        <v>259.6774281355445</v>
+        <v>260.0443424743044</v>
       </c>
       <c r="D58" t="n">
-        <v>247.4015469367764</v>
+        <v>256.8216766476447</v>
       </c>
       <c r="E58" t="n">
-        <v>248.7203626098492</v>
+        <v>258.8246765136719</v>
       </c>
       <c r="F58" t="n">
-        <v>15852400</v>
+        <v>8045900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1943,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B59" t="n">
-        <v>257.3472290039062</v>
+        <v>258.556940201721</v>
       </c>
       <c r="C59" t="n">
-        <v>262.0572792621351</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D59" t="n">
-        <v>254.1840559885597</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E59" t="n">
-        <v>259.6774704470017</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="F59" t="n">
-        <v>10805400</v>
+        <v>8894700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1969,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B60" t="n">
-        <v>258.82470703125</v>
+        <v>261.283846098816</v>
       </c>
       <c r="C60" t="n">
-        <v>260.0443731356912</v>
+        <v>265.646834061187</v>
       </c>
       <c r="D60" t="n">
-        <v>256.8217069290525</v>
+        <v>258.5767957367673</v>
       </c>
       <c r="E60" t="n">
-        <v>257.8132965310952</v>
+        <v>260.1435241699219</v>
       </c>
       <c r="F60" t="n">
-        <v>8045900</v>
+        <v>7783800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1995,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B61" t="n">
-        <v>261.9779357910156</v>
+        <v>261.3036648523665</v>
       </c>
       <c r="C61" t="n">
-        <v>263.6933661135803</v>
+        <v>262.2655079172122</v>
       </c>
       <c r="D61" t="n">
-        <v>256.9703910840639</v>
+        <v>258.7156306765648</v>
       </c>
       <c r="E61" t="n">
-        <v>258.556940201721</v>
+        <v>260.0245361328125</v>
       </c>
       <c r="F61" t="n">
-        <v>8894700</v>
+        <v>6006600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2021,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B62" t="n">
-        <v>260.1435546875</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C62" t="n">
-        <v>265.6468652243614</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D62" t="n">
-        <v>258.5768260705516</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E62" t="n">
-        <v>261.2838767501659</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F62" t="n">
-        <v>7783800</v>
+        <v>10271800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2047,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B63" t="n">
-        <v>260.0245056152344</v>
+        <v>251.8637174841621</v>
       </c>
       <c r="C63" t="n">
-        <v>262.2654771366241</v>
+        <v>253.7080744457603</v>
       </c>
       <c r="D63" t="n">
-        <v>258.7156003126054</v>
+        <v>249.9896140498327</v>
       </c>
       <c r="E63" t="n">
-        <v>261.3036341846645</v>
+        <v>252.7660675048828</v>
       </c>
       <c r="F63" t="n">
-        <v>6006600</v>
+        <v>6145300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2073,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B64" t="n">
-        <v>252.4388427734375</v>
+        <v>254.1741130832229</v>
       </c>
       <c r="C64" t="n">
-        <v>260.0740784753494</v>
+        <v>259.7666921654164</v>
       </c>
       <c r="D64" t="n">
-        <v>250.9613690531332</v>
+        <v>254.0947992411865</v>
       </c>
       <c r="E64" t="n">
-        <v>259.0130705063725</v>
+        <v>255.9689178466797</v>
       </c>
       <c r="F64" t="n">
-        <v>10271800</v>
+        <v>6269000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2099,25 +2107,25 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B65" t="n">
-        <v>252.7660675048828</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C65" t="n">
-        <v>253.7080744457603</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D65" t="n">
-        <v>249.9896140498327</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E65" t="n">
-        <v>251.8637174841621</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F65" t="n">
-        <v>6145300</v>
+        <v>5654200</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2125,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B66" t="n">
-        <v>255.9689178466797</v>
+        <v>258.9047600313309</v>
       </c>
       <c r="C66" t="n">
-        <v>259.7666921654164</v>
+        <v>260.2555141825196</v>
       </c>
       <c r="D66" t="n">
-        <v>254.0947992411865</v>
+        <v>253.760043143314</v>
       </c>
       <c r="E66" t="n">
-        <v>254.1741130832229</v>
+        <v>258.1400146484375</v>
       </c>
       <c r="F66" t="n">
-        <v>6269000</v>
+        <v>20732100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2151,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B67" t="n">
-        <v>256.0940551757812</v>
+        <v>258.8452092197766</v>
       </c>
       <c r="C67" t="n">
-        <v>258.2989382537239</v>
+        <v>262.8279113769531</v>
       </c>
       <c r="D67" t="n">
-        <v>254.4155616010984</v>
+        <v>256.6502674989528</v>
       </c>
       <c r="E67" t="n">
-        <v>256.6601807669533</v>
+        <v>262.8279113769531</v>
       </c>
       <c r="F67" t="n">
-        <v>5654200</v>
+        <v>5664200</v>
       </c>
       <c r="G67" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2177,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B68" t="n">
-        <v>258.1400451660156</v>
+        <v>260.9308604798152</v>
       </c>
       <c r="C68" t="n">
-        <v>260.2555449501942</v>
+        <v>262.4404982668678</v>
       </c>
       <c r="D68" t="n">
-        <v>253.7600731430874</v>
+        <v>258.7458305027313</v>
       </c>
       <c r="E68" t="n">
-        <v>258.904790639318</v>
+        <v>261.6360168457031</v>
       </c>
       <c r="F68" t="n">
-        <v>20732100</v>
+        <v>4745100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2203,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B69" t="n">
-        <v>262.827880859375</v>
+        <v>261.4374083245464</v>
       </c>
       <c r="C69" t="n">
-        <v>262.827880859375</v>
+        <v>264.4864785158107</v>
       </c>
       <c r="D69" t="n">
-        <v>256.6502376986757</v>
+        <v>260.7620161053754</v>
       </c>
       <c r="E69" t="n">
-        <v>258.8451791646396</v>
+        <v>263.4535827636719</v>
       </c>
       <c r="F69" t="n">
-        <v>5664200</v>
+        <v>2076600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2229,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B70" t="n">
-        <v>261.6360168457031</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="C70" t="n">
-        <v>262.4404982668678</v>
+        <v>266.0855602062323</v>
       </c>
       <c r="D70" t="n">
-        <v>258.7458305027313</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="E70" t="n">
-        <v>260.9308604798152</v>
+        <v>264.2680053710938</v>
       </c>
       <c r="F70" t="n">
-        <v>4745100</v>
+        <v>2456400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2255,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B71" t="n">
-        <v>263.4535827636719</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C71" t="n">
-        <v>264.4864785158107</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D71" t="n">
-        <v>260.7620161053754</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E71" t="n">
-        <v>261.4374083245464</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F71" t="n">
-        <v>2076600</v>
+        <v>4300100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2281,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B72" t="n">
-        <v>264.2680053710938</v>
+        <v>264.8440818513142</v>
       </c>
       <c r="C72" t="n">
-        <v>266.0855602062323</v>
+        <v>266.453045001104</v>
       </c>
       <c r="D72" t="n">
-        <v>262.9967232703997</v>
+        <v>263.5231220141856</v>
       </c>
       <c r="E72" t="n">
-        <v>262.9967232703997</v>
+        <v>264.109130859375</v>
       </c>
       <c r="F72" t="n">
-        <v>2456400</v>
+        <v>3291800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2307,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="n">
-        <v>264.4169616699219</v>
+        <v>263.4834046285292</v>
       </c>
       <c r="C73" t="n">
-        <v>267.2773231615557</v>
+        <v>264.2878861679949</v>
       </c>
       <c r="D73" t="n">
-        <v>262.9072936026629</v>
+        <v>262.5895396190958</v>
       </c>
       <c r="E73" t="n">
-        <v>262.9072936026629</v>
+        <v>263.1059875488281</v>
       </c>
       <c r="F73" t="n">
-        <v>4300100</v>
+        <v>3367900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2333,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B74" t="n">
-        <v>264.109130859375</v>
+        <v>263.1953762174182</v>
       </c>
       <c r="C74" t="n">
-        <v>266.453045001104</v>
+        <v>263.572793304574</v>
       </c>
       <c r="D74" t="n">
-        <v>263.5231220141856</v>
+        <v>250.760631935403</v>
       </c>
       <c r="E74" t="n">
-        <v>264.8440818513142</v>
+        <v>251.8928680419922</v>
       </c>
       <c r="F74" t="n">
-        <v>3291800</v>
+        <v>9680600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2359,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B75" t="n">
-        <v>263.1059875488281</v>
+        <v>251.8928562905814</v>
       </c>
       <c r="C75" t="n">
-        <v>264.2878861679949</v>
+        <v>257.8222021169872</v>
       </c>
       <c r="D75" t="n">
-        <v>262.5895396190958</v>
+        <v>250.5917797464572</v>
       </c>
       <c r="E75" t="n">
-        <v>263.4834046285292</v>
+        <v>254.514892578125</v>
       </c>
       <c r="F75" t="n">
-        <v>3367900</v>
+        <v>6421500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2385,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B76" t="n">
-        <v>251.8928680419922</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C76" t="n">
-        <v>263.572793304574</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D76" t="n">
-        <v>250.760631935403</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E76" t="n">
-        <v>263.1953762174182</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F76" t="n">
-        <v>9680600</v>
+        <v>6103300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2411,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B77" t="n">
-        <v>254.514892578125</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="C77" t="n">
-        <v>257.8222021169872</v>
+        <v>266.0060550943219</v>
       </c>
       <c r="D77" t="n">
-        <v>250.5917797464572</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="E77" t="n">
-        <v>251.8928562905814</v>
+        <v>264.3077087402344</v>
       </c>
       <c r="F77" t="n">
-        <v>6421500</v>
+        <v>5976200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2437,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B78" t="n">
-        <v>261.1096496582031</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C78" t="n">
-        <v>261.7552171079225</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D78" t="n">
-        <v>253.2634545783159</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E78" t="n">
-        <v>253.4620895509313</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F78" t="n">
-        <v>6103300</v>
+        <v>5243500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2463,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B79" t="n">
-        <v>264.3077392578125</v>
+        <v>258.2294193019395</v>
       </c>
       <c r="C79" t="n">
-        <v>266.0060858079951</v>
+        <v>259.2524038660146</v>
       </c>
       <c r="D79" t="n">
-        <v>261.7055860975985</v>
+        <v>254.7631956419699</v>
       </c>
       <c r="E79" t="n">
-        <v>261.7055860975985</v>
+        <v>258.1698303222656</v>
       </c>
       <c r="F79" t="n">
-        <v>5976200</v>
+        <v>5174400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2489,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B80" t="n">
-        <v>258.7557678222656</v>
+        <v>257.2362139425806</v>
       </c>
       <c r="C80" t="n">
-        <v>263.3939780702048</v>
+        <v>259.7787779567694</v>
       </c>
       <c r="D80" t="n">
-        <v>258.6365898818048</v>
+        <v>254.028214436778</v>
       </c>
       <c r="E80" t="n">
-        <v>262.5994079508812</v>
+        <v>257.6334838867188</v>
       </c>
       <c r="F80" t="n">
-        <v>5243500</v>
+        <v>4927700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2515,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B81" t="n">
-        <v>258.1697998046875</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C81" t="n">
-        <v>259.2523732204683</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D81" t="n">
-        <v>254.7631655270811</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E81" t="n">
-        <v>258.2293887773175</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F81" t="n">
-        <v>5174400</v>
+        <v>13661000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2541,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B82" t="n">
-        <v>257.6334838867188</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C82" t="n">
-        <v>259.7787779567694</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D82" t="n">
-        <v>254.028214436778</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E82" t="n">
-        <v>257.2362139425806</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F82" t="n">
-        <v>4927700</v>
+        <v>10149300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2567,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B83" t="n">
-        <v>239.4183959960938</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C83" t="n">
-        <v>259.1332249596227</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D83" t="n">
-        <v>238.7231659776434</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E83" t="n">
-        <v>255.9053572301452</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F83" t="n">
-        <v>13661000</v>
+        <v>11489600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2593,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="n">
-        <v>237.9385528564453</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C84" t="n">
-        <v>240.5903685304685</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D84" t="n">
-        <v>234.849731125901</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E84" t="n">
-        <v>237.5511941796288</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F84" t="n">
-        <v>10149300</v>
+        <v>13902600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2619,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B85" t="n">
-        <v>231.9396667480469</v>
+        <v>222.0177057630064</v>
       </c>
       <c r="C85" t="n">
-        <v>237.2135033883542</v>
+        <v>226.3877512462753</v>
       </c>
       <c r="D85" t="n">
-        <v>230.0923326840245</v>
+        <v>217.8661784665229</v>
       </c>
       <c r="E85" t="n">
-        <v>235.4059054123066</v>
+        <v>218.5713500976562</v>
       </c>
       <c r="F85" t="n">
-        <v>11489600</v>
+        <v>13050800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2645,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B86" t="n">
-        <v>225.5633850097656</v>
+        <v>218.6507753226022</v>
       </c>
       <c r="C86" t="n">
-        <v>231.3636110626874</v>
+        <v>221.8687164208105</v>
       </c>
       <c r="D86" t="n">
-        <v>224.8979495180149</v>
+        <v>217.4688919371066</v>
       </c>
       <c r="E86" t="n">
-        <v>231.3636110626874</v>
+        <v>220.071044921875</v>
       </c>
       <c r="F86" t="n">
-        <v>13902600</v>
+        <v>12616600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2671,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B87" t="n">
-        <v>218.5713348388672</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C87" t="n">
-        <v>226.3877354418118</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D87" t="n">
-        <v>217.8661632569629</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E87" t="n">
-        <v>222.0176902636222</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F87" t="n">
-        <v>13050800</v>
+        <v>9483000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2697,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="n">
-        <v>220.0710601806641</v>
+        <v>225.2356232374019</v>
       </c>
       <c r="C88" t="n">
-        <v>221.8687318042425</v>
+        <v>229.277913744438</v>
       </c>
       <c r="D88" t="n">
-        <v>217.4689070154735</v>
+        <v>225.1065036899912</v>
       </c>
       <c r="E88" t="n">
-        <v>218.6507904829158</v>
+        <v>226.4969787597656</v>
       </c>
       <c r="F88" t="n">
-        <v>12616600</v>
+        <v>9408000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2723,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B89" t="n">
-        <v>226.5367126464844</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C89" t="n">
-        <v>227.162427221411</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D89" t="n">
-        <v>219.6042504088122</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E89" t="n">
-        <v>220.7265600038705</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F89" t="n">
-        <v>9483000</v>
+        <v>7239600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2749,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="n">
-        <v>226.4969940185547</v>
+        <v>230.3604906379282</v>
       </c>
       <c r="C90" t="n">
-        <v>229.2779291905748</v>
+        <v>234.1346156625655</v>
       </c>
       <c r="D90" t="n">
-        <v>225.1065188551059</v>
+        <v>224.7291051659704</v>
       </c>
       <c r="E90" t="n">
-        <v>225.2356384112152</v>
+        <v>226.9737091064453</v>
       </c>
       <c r="F90" t="n">
-        <v>9408000</v>
+        <v>9838400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2775,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B91" t="n">
-        <v>227.8377838134766</v>
+        <v>227.8278778686248</v>
       </c>
       <c r="C91" t="n">
-        <v>229.3772313706373</v>
+        <v>230.2810586434755</v>
       </c>
       <c r="D91" t="n">
-        <v>226.0401123076792</v>
+        <v>226.1195896734686</v>
       </c>
       <c r="E91" t="n">
-        <v>227.8675783015932</v>
+        <v>226.4076232910156</v>
       </c>
       <c r="F91" t="n">
-        <v>7239600</v>
+        <v>8465900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2801,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B92" t="n">
-        <v>226.9737243652344</v>
+        <v>215.1944745404488</v>
       </c>
       <c r="C92" t="n">
-        <v>234.1346314027617</v>
+        <v>215.8003210439947</v>
       </c>
       <c r="D92" t="n">
-        <v>224.7291202738612</v>
+        <v>207.358206080909</v>
       </c>
       <c r="E92" t="n">
-        <v>230.3605061244008</v>
+        <v>212.6221160888672</v>
       </c>
       <c r="F92" t="n">
-        <v>9838400</v>
+        <v>18555600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2827,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="n">
-        <v>226.4076080322266</v>
+        <v>212.7015903227142</v>
       </c>
       <c r="C93" t="n">
-        <v>230.2810431236355</v>
+        <v>214.08212392222</v>
       </c>
       <c r="D93" t="n">
-        <v>226.1195744340916</v>
+        <v>209.5929005351361</v>
       </c>
       <c r="E93" t="n">
-        <v>227.8278625141174</v>
+        <v>210.8443145751953</v>
       </c>
       <c r="F93" t="n">
-        <v>8465900</v>
+        <v>11090400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2853,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B94" t="n">
-        <v>212.6221313476562</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C94" t="n">
-        <v>215.8003365308671</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D94" t="n">
-        <v>207.3582209619344</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E94" t="n">
-        <v>215.1944899838427</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F94" t="n">
-        <v>18555600</v>
+        <v>7950900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2879,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B95" t="n">
-        <v>210.8443145751953</v>
+        <v>203.60397273962</v>
       </c>
       <c r="C95" t="n">
-        <v>214.08212392222</v>
+        <v>204.1601567769575</v>
       </c>
       <c r="D95" t="n">
-        <v>209.5929005351361</v>
+        <v>191.7949429269172</v>
       </c>
       <c r="E95" t="n">
-        <v>212.7015903227142</v>
+        <v>195.0426788330078</v>
       </c>
       <c r="F95" t="n">
-        <v>11090400</v>
+        <v>20194200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2905,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B96" t="n">
-        <v>209.3743896484375</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C96" t="n">
-        <v>215.4129869027477</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D96" t="n">
-        <v>208.3712731650351</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E96" t="n">
-        <v>212.8902908724165</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F96" t="n">
-        <v>7950900</v>
+        <v>23010000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2931,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B97" t="n">
-        <v>195.0426788330078</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C97" t="n">
-        <v>204.1601567769575</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D97" t="n">
-        <v>191.7949429269172</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E97" t="n">
-        <v>203.60397273962</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F97" t="n">
-        <v>20194200</v>
+        <v>21956300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2957,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B98" t="n">
-        <v>198.0818176269531</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C98" t="n">
-        <v>199.3034370934686</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D98" t="n">
-        <v>186.0046234920971</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E98" t="n">
-        <v>191.993558028148</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F98" t="n">
-        <v>23010000</v>
+        <v>13652600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2983,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B99" t="n">
-        <v>188.6763153076172</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C99" t="n">
-        <v>198.2010042649258</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D99" t="n">
-        <v>187.5043431662378</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E99" t="n">
-        <v>192.668943558262</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F99" t="n">
-        <v>21956300</v>
+        <v>12112000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3009,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B100" t="n">
-        <v>190.0469207763672</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C100" t="n">
-        <v>193.2747884158856</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D100" t="n">
-        <v>185.8457159832669</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E100" t="n">
-        <v>190.3250127759971</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F100" t="n">
-        <v>13652600</v>
+        <v>13393000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3035,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B101" t="n">
-        <v>192.7086639404297</v>
+        <v>191.8346349441069</v>
       </c>
       <c r="C101" t="n">
-        <v>193.8706944788449</v>
+        <v>192.3510979672969</v>
       </c>
       <c r="D101" t="n">
-        <v>184.465183505092</v>
+        <v>180.5718644212529</v>
       </c>
       <c r="E101" t="n">
-        <v>188.0108792533576</v>
+        <v>183.7401428222656</v>
       </c>
       <c r="F101" t="n">
-        <v>12112000</v>
+        <v>16350200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3061,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B102" t="n">
-        <v>192.1326141357422</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C102" t="n">
-        <v>197.7441470694129</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D102" t="n">
-        <v>189.4510040038842</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E102" t="n">
-        <v>190.5931665112882</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F102" t="n">
-        <v>13393000</v>
+        <v>16849100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3087,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B103" t="n">
-        <v>183.7401580810547</v>
+        <v>185.1703620229303</v>
       </c>
       <c r="C103" t="n">
-        <v>192.3511139411869</v>
+        <v>192.1326190686923</v>
       </c>
       <c r="D103" t="n">
-        <v>180.5718794169307</v>
+        <v>183.0449358454951</v>
       </c>
       <c r="E103" t="n">
-        <v>191.8346508751069</v>
+        <v>188.4280242919922</v>
       </c>
       <c r="F103" t="n">
-        <v>16350200</v>
+        <v>14822900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3113,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B104" t="n">
-        <v>184.1672210693359</v>
+        <v>189.6695058452945</v>
       </c>
       <c r="C104" t="n">
-        <v>187.0375548215625</v>
+        <v>191.6856804427425</v>
       </c>
       <c r="D104" t="n">
-        <v>179.012577513483</v>
+        <v>181.9226203922807</v>
       </c>
       <c r="E104" t="n">
-        <v>184.6936257308121</v>
+        <v>183.0349884033203</v>
       </c>
       <c r="F104" t="n">
-        <v>16849100</v>
+        <v>13692900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3139,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B105" t="n">
-        <v>188.4280090332031</v>
+        <v>182.6277925688313</v>
       </c>
       <c r="C105" t="n">
-        <v>192.1326035099074</v>
+        <v>186.8587767567783</v>
       </c>
       <c r="D105" t="n">
-        <v>183.0449210226253</v>
+        <v>180.6215444099069</v>
       </c>
       <c r="E105" t="n">
-        <v>185.1703470279448</v>
+        <v>186.5111541748047</v>
       </c>
       <c r="F105" t="n">
-        <v>14822900</v>
+        <v>9852900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3165,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B106" t="n">
-        <v>183.0349884033203</v>
+        <v>185.3292747163753</v>
       </c>
       <c r="C106" t="n">
-        <v>191.6856804427425</v>
+        <v>185.6768821509354</v>
       </c>
       <c r="D106" t="n">
-        <v>181.9226203922807</v>
+        <v>181.9822138463991</v>
       </c>
       <c r="E106" t="n">
-        <v>189.6695058452945</v>
+        <v>184.0281829833984</v>
       </c>
       <c r="F106" t="n">
-        <v>13692900</v>
+        <v>9565100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3191,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B107" t="n">
-        <v>186.5111541748047</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C107" t="n">
-        <v>186.8587767567783</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D107" t="n">
-        <v>180.6215444099069</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E107" t="n">
-        <v>182.6277925688313</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F107" t="n">
-        <v>9852900</v>
+        <v>10816200</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3217,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B108" t="n">
-        <v>184.0281677246094</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C108" t="n">
-        <v>185.6768667554436</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D108" t="n">
-        <v>181.9821987572526</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E108" t="n">
-        <v>185.3292593497056</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F108" t="n">
-        <v>9565100</v>
+        <v>15498600</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3243,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B109" t="n">
-        <v>183.8990631103516</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C109" t="n">
-        <v>190.4243134969296</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D109" t="n">
-        <v>182.4787935369736</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E109" t="n">
-        <v>184.0579771467211</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F109" t="n">
-        <v>10816200</v>
+        <v>15564700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3269,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B110" t="n">
-        <v>176.9467468261719</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C110" t="n">
-        <v>181.2273936107796</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D110" t="n">
-        <v>173.3811981056387</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E110" t="n">
-        <v>180.0355685556146</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F110" t="n">
-        <v>15498600</v>
+        <v>21875100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3295,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B111" t="n">
-        <v>184.1573028564453</v>
+        <v>195.420066371549</v>
       </c>
       <c r="C111" t="n">
-        <v>187.3851706171715</v>
+        <v>199.6709185207204</v>
       </c>
       <c r="D111" t="n">
-        <v>175.0795461293982</v>
+        <v>190.0270517409182</v>
       </c>
       <c r="E111" t="n">
-        <v>176.4302852446972</v>
+        <v>198.1116180419922</v>
       </c>
       <c r="F111" t="n">
-        <v>15564700</v>
+        <v>26680500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3321,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B112" t="n">
-        <v>190.4441833496094</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C112" t="n">
-        <v>191.2884009153263</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D112" t="n">
-        <v>181.0188047518053</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E112" t="n">
-        <v>181.7537708108397</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F112" t="n">
-        <v>21875100</v>
+        <v>16346500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3347,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B113" t="n">
-        <v>198.1116180419922</v>
+        <v>191.1890843548102</v>
       </c>
       <c r="C113" t="n">
-        <v>199.6709185207204</v>
+        <v>194.6056605467623</v>
       </c>
       <c r="D113" t="n">
-        <v>190.0270517409182</v>
+        <v>189.3814711920236</v>
       </c>
       <c r="E113" t="n">
-        <v>195.420066371549</v>
+        <v>191.6360168457031</v>
       </c>
       <c r="F113" t="n">
-        <v>26680500</v>
+        <v>9932700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3373,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B114" t="n">
-        <v>193.4634857177734</v>
+        <v>189.4509946932415</v>
       </c>
       <c r="C114" t="n">
-        <v>194.5857953386064</v>
+        <v>197.3170577657204</v>
       </c>
       <c r="D114" t="n">
-        <v>188.6266549601705</v>
+        <v>188.2889641983741</v>
       </c>
       <c r="E114" t="n">
-        <v>190.6031086414411</v>
+        <v>194.7149047851562</v>
       </c>
       <c r="F114" t="n">
-        <v>16346500</v>
+        <v>13208900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3399,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B115" t="n">
-        <v>191.6360168457031</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C115" t="n">
-        <v>194.6056605467623</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D115" t="n">
-        <v>189.3814711920236</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E115" t="n">
-        <v>191.1890843548102</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F115" t="n">
-        <v>9932700</v>
+        <v>11583700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3425,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B116" t="n">
-        <v>194.7149047851562</v>
+        <v>193.036414733929</v>
       </c>
       <c r="C116" t="n">
-        <v>197.3170577657204</v>
+        <v>203.027904005614</v>
       </c>
       <c r="D116" t="n">
-        <v>188.2889641983741</v>
+        <v>192.9172367799533</v>
       </c>
       <c r="E116" t="n">
-        <v>189.4509946932415</v>
+        <v>200.0185394287109</v>
       </c>
       <c r="F116" t="n">
-        <v>13208900</v>
+        <v>15860900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3451,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B117" t="n">
-        <v>191.76513671875</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C117" t="n">
-        <v>195.1320503828654</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D117" t="n">
-        <v>190.7918147128814</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E117" t="n">
-        <v>193.7713848635987</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F117" t="n">
-        <v>11583700</v>
+        <v>9657400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3477,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B118" t="n">
-        <v>200.0185394287109</v>
+        <v>197.2078040637707</v>
       </c>
       <c r="C118" t="n">
-        <v>203.027904005614</v>
+        <v>202.2830055722447</v>
       </c>
       <c r="D118" t="n">
-        <v>192.9172367799533</v>
+        <v>194.5361205377908</v>
       </c>
       <c r="E118" t="n">
-        <v>193.036414733929</v>
+        <v>197.4362335205078</v>
       </c>
       <c r="F118" t="n">
-        <v>15860900</v>
+        <v>10754800</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3503,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B119" t="n">
-        <v>200.733642578125</v>
+        <v>195.9166750362765</v>
       </c>
       <c r="C119" t="n">
-        <v>201.5778601866405</v>
+        <v>198.2109569133711</v>
       </c>
       <c r="D119" t="n">
-        <v>196.0259162627038</v>
+        <v>189.3020404418633</v>
       </c>
       <c r="E119" t="n">
-        <v>199.4226244314719</v>
+        <v>193.5826873779297</v>
       </c>
       <c r="F119" t="n">
-        <v>9657400</v>
+        <v>14467400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3529,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B120" t="n">
-        <v>197.4362487792969</v>
+        <v>195.0625138319317</v>
       </c>
       <c r="C120" t="n">
-        <v>202.2830212056148</v>
+        <v>198.1910714873107</v>
       </c>
       <c r="D120" t="n">
-        <v>194.5361355724457</v>
+        <v>189.9873122244243</v>
       </c>
       <c r="E120" t="n">
-        <v>197.2078193049057</v>
+        <v>192.8079833984375</v>
       </c>
       <c r="F120" t="n">
-        <v>10754800</v>
+        <v>9580000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3555,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B121" t="n">
-        <v>193.5826721191406</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C121" t="n">
-        <v>198.2109412897675</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D121" t="n">
-        <v>189.3020255204881</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E121" t="n">
-        <v>195.9166595935153</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F121" t="n">
-        <v>14467400</v>
+        <v>26309700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3581,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B122" t="n">
-        <v>192.8079986572266</v>
+        <v>198.3698354155112</v>
       </c>
       <c r="C122" t="n">
-        <v>198.1910871721164</v>
+        <v>199.6311909649738</v>
       </c>
       <c r="D122" t="n">
-        <v>189.987327259986</v>
+        <v>190.4441834205658</v>
       </c>
       <c r="E122" t="n">
-        <v>195.0625292691439</v>
+        <v>191.5168304443359</v>
       </c>
       <c r="F122" t="n">
-        <v>9580000</v>
+        <v>14834700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3607,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B123" t="n">
-        <v>197.9228973388672</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C123" t="n">
-        <v>203.4648992272838</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D123" t="n">
-        <v>191.8346379323055</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E123" t="n">
-        <v>192.8079750209554</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F123" t="n">
-        <v>26309700</v>
+        <v>13419600</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3633,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B124" t="n">
-        <v>191.5168304443359</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C124" t="n">
-        <v>199.6311909649738</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D124" t="n">
-        <v>190.4441834205658</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E124" t="n">
-        <v>198.3698354155112</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F124" t="n">
-        <v>14834700</v>
+        <v>11559300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3659,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B125" t="n">
-        <v>196.9893035888672</v>
+        <v>192.0829546896537</v>
       </c>
       <c r="C125" t="n">
-        <v>197.2773371794379</v>
+        <v>194.8142273994103</v>
       </c>
       <c r="D125" t="n">
-        <v>193.821025021851</v>
+        <v>191.3281356874407</v>
       </c>
       <c r="E125" t="n">
-        <v>193.821025021851</v>
+        <v>193.0165557861328</v>
       </c>
       <c r="F125" t="n">
-        <v>13419600</v>
+        <v>10525100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3685,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B126" t="n">
-        <v>193.9799499511719</v>
+        <v>194.2580448499211</v>
       </c>
       <c r="C126" t="n">
-        <v>201.0018110133274</v>
+        <v>199.0352867281362</v>
       </c>
       <c r="D126" t="n">
-        <v>193.1258058856387</v>
+        <v>191.9836462262046</v>
       </c>
       <c r="E126" t="n">
-        <v>196.870136689126</v>
+        <v>193.6621398925781</v>
       </c>
       <c r="F126" t="n">
-        <v>11559300</v>
+        <v>9254300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3711,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B127" t="n">
-        <v>193.0165557861328</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C127" t="n">
-        <v>194.8142273994103</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D127" t="n">
-        <v>191.3281356874407</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E127" t="n">
-        <v>192.0829546896537</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F127" t="n">
-        <v>10525100</v>
+        <v>20201100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3737,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B128" t="n">
-        <v>193.6621398925781</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C128" t="n">
-        <v>199.0352867281362</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D128" t="n">
-        <v>191.9836462262046</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E128" t="n">
-        <v>194.2580448499211</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F128" t="n">
-        <v>9254300</v>
+        <v>13976200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3763,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B129" t="n">
-        <v>194.0494689941406</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C129" t="n">
-        <v>194.3374874288811</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D129" t="n">
-        <v>188.7061018910339</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E129" t="n">
-        <v>191.8942484911283</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F129" t="n">
-        <v>20201100</v>
+        <v>18631400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3789,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B130" t="n">
-        <v>193.850830078125</v>
+        <v>184.4353765448059</v>
       </c>
       <c r="C130" t="n">
-        <v>196.7012958768407</v>
+        <v>186.1138700384234</v>
       </c>
       <c r="D130" t="n">
-        <v>190.6924929381777</v>
+        <v>178.625224245603</v>
       </c>
       <c r="E130" t="n">
-        <v>195.7478267440036</v>
+        <v>180.7208557128906</v>
       </c>
       <c r="F130" t="n">
-        <v>13976200</v>
+        <v>12565200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3815,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B131" t="n">
-        <v>181.7736511230469</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C131" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D131" t="n">
-        <v>181.0486114593648</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E131" t="n">
-        <v>190.8315397252546</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F131" t="n">
-        <v>18631400</v>
+        <v>10330700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3841,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B132" t="n">
-        <v>180.7208709716797</v>
+        <v>182.7469612620264</v>
       </c>
       <c r="C132" t="n">
-        <v>186.1138857525603</v>
+        <v>182.8562127689759</v>
       </c>
       <c r="D132" t="n">
-        <v>178.6252393274517</v>
+        <v>177.6022443008385</v>
       </c>
       <c r="E132" t="n">
-        <v>184.4353921172228</v>
+        <v>178.0888977050781</v>
       </c>
       <c r="F132" t="n">
-        <v>12565200</v>
+        <v>9902000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3867,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B133" t="n">
-        <v>184.3758087158203</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C133" t="n">
-        <v>186.1933484091056</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D133" t="n">
-        <v>178.3074166263376</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E133" t="n">
-        <v>179.9461742219026</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F133" t="n">
-        <v>10330700</v>
+        <v>11617700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3893,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B134" t="n">
-        <v>178.0889129638672</v>
+        <v>183.6408377857945</v>
       </c>
       <c r="C134" t="n">
-        <v>182.8562284362321</v>
+        <v>187.216328097891</v>
       </c>
       <c r="D134" t="n">
-        <v>177.6022595179307</v>
+        <v>181.0684791429995</v>
       </c>
       <c r="E134" t="n">
-        <v>182.7469769199218</v>
+        <v>185.3987884521484</v>
       </c>
       <c r="F134" t="n">
-        <v>9902000</v>
+        <v>11041400</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3919,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>183.7699432373047</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C135" t="n">
-        <v>185.1206822343098</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D135" t="n">
-        <v>178.3570608051074</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E135" t="n">
-        <v>178.873523844959</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F135" t="n">
-        <v>11617700</v>
+        <v>11677700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3945,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B136" t="n">
-        <v>185.3987731933594</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C136" t="n">
-        <v>187.2163126895138</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D136" t="n">
-        <v>181.0684642406058</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E136" t="n">
-        <v>183.6408226716892</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F136" t="n">
-        <v>11041400</v>
+        <v>11635500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3971,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B137" t="n">
-        <v>184.9717102050781</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C137" t="n">
-        <v>187.6930410934417</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D137" t="n">
-        <v>181.7636956083204</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E137" t="n">
-        <v>185.5775567084869</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F137" t="n">
-        <v>11677700</v>
+        <v>14391000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -3997,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B138" t="n">
-        <v>185.9053039550781</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C138" t="n">
-        <v>186.3025890630262</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D138" t="n">
-        <v>180.3434488377003</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E138" t="n">
-        <v>184.0381169897925</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F138" t="n">
-        <v>11635500</v>
+        <v>12344600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4023,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B139" t="n">
-        <v>183.7699432373047</v>
+        <v>185.229934306832</v>
       </c>
       <c r="C139" t="n">
-        <v>186.8587647224845</v>
+        <v>185.498099849194</v>
       </c>
       <c r="D139" t="n">
-        <v>182.3496888213084</v>
+        <v>174.5829363342851</v>
       </c>
       <c r="E139" t="n">
-        <v>186.2231237330043</v>
+        <v>175.1689147949219</v>
       </c>
       <c r="F139" t="n">
-        <v>14391000</v>
+        <v>13472100</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4049,25 +4057,25 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B140" t="n">
-        <v>181.7140502929688</v>
+        <v>172.4208720146844</v>
       </c>
       <c r="C140" t="n">
-        <v>185.3093932676422</v>
+        <v>173.5360220799356</v>
       </c>
       <c r="D140" t="n">
-        <v>180.7804492618957</v>
+        <v>166.3970410225636</v>
       </c>
       <c r="E140" t="n">
-        <v>183.6904887071696</v>
+        <v>170.1109161376953</v>
       </c>
       <c r="F140" t="n">
-        <v>12344600</v>
+        <v>20855400</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4075,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B141" t="n">
-        <v>175.1689300537109</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C141" t="n">
-        <v>185.4981160077481</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D141" t="n">
-        <v>174.5829515420302</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E141" t="n">
-        <v>185.2299504420264</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F141" t="n">
-        <v>13472100</v>
+        <v>18109300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4101,25 +4109,25 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B142" t="n">
-        <v>170.1109008789062</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C142" t="n">
-        <v>173.5360065139178</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D142" t="n">
-        <v>166.3970260969056</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E142" t="n">
-        <v>172.4208565486944</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F142" t="n">
-        <v>20855400</v>
+        <v>12390800</v>
       </c>
       <c r="G142" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4127,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B143" t="n">
-        <v>164.2463836669922</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C143" t="n">
-        <v>170.5191174814139</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D143" t="n">
-        <v>162.8126107290287</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E143" t="n">
-        <v>170.5191174814139</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F143" t="n">
-        <v>18109300</v>
+        <v>13123600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4153,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B144" t="n">
-        <v>172.0723876953125</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C144" t="n">
-        <v>172.6498652447362</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D144" t="n">
-        <v>165.0528829680655</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E144" t="n">
-        <v>166.3273444705899</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F144" t="n">
-        <v>12390800</v>
+        <v>14340300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4179,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B145" t="n">
-        <v>170.5689086914062</v>
+        <v>183.2040075329009</v>
       </c>
       <c r="C145" t="n">
-        <v>176.7321331165696</v>
+        <v>183.7516312461474</v>
       </c>
       <c r="D145" t="n">
-        <v>169.7624151908458</v>
+        <v>177.7975052553062</v>
       </c>
       <c r="E145" t="n">
-        <v>174.4520463656914</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F145" t="n">
-        <v>13123600</v>
+        <v>11866700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4205,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B146" t="n">
-        <v>176.8317108154297</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C146" t="n">
-        <v>178.842961383224</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D146" t="n">
-        <v>172.1321282578628</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E146" t="n">
-        <v>173.4663277892384</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F146" t="n">
-        <v>14340300</v>
+        <v>17225700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4231,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="n">
-        <v>180.4360504150391</v>
+        <v>181.7105075933097</v>
       </c>
       <c r="C147" t="n">
-        <v>183.7516467853238</v>
+        <v>188.1823886856741</v>
       </c>
       <c r="D147" t="n">
-        <v>177.7975202909648</v>
+        <v>181.3321466062204</v>
       </c>
       <c r="E147" t="n">
-        <v>183.2040230257668</v>
+        <v>185.4642028808594</v>
       </c>
       <c r="F147" t="n">
-        <v>11866700</v>
+        <v>14382300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4257,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B148" t="n">
-        <v>181.3520660400391</v>
+        <v>185.7927641258556</v>
       </c>
       <c r="C148" t="n">
-        <v>187.1667986912511</v>
+        <v>192.7226462718077</v>
       </c>
       <c r="D148" t="n">
-        <v>180.2468672661974</v>
+        <v>183.303579264538</v>
       </c>
       <c r="E148" t="n">
-        <v>184.6278268926657</v>
+        <v>186.3005523681641</v>
       </c>
       <c r="F148" t="n">
-        <v>17225700</v>
+        <v>12073700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4283,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B149" t="n">
-        <v>185.4641876220703</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C149" t="n">
-        <v>188.1823732032504</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D149" t="n">
-        <v>181.33213168739</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E149" t="n">
-        <v>181.7104926433502</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F149" t="n">
-        <v>14382300</v>
+        <v>14565900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4309,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B150" t="n">
-        <v>186.3005676269531</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C150" t="n">
-        <v>192.7226620565929</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D150" t="n">
-        <v>183.3035942778625</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E150" t="n">
-        <v>185.7927793430547</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F150" t="n">
-        <v>12073700</v>
+        <v>22719900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4335,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B151" t="n">
-        <v>188.9789276123047</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C151" t="n">
-        <v>190.3230783921826</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D151" t="n">
-        <v>186.2209063874661</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E151" t="n">
-        <v>187.3858431404722</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F151" t="n">
-        <v>14565900</v>
+        <v>10817600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4361,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B152" t="n">
-        <v>172.5503082275391</v>
+        <v>177.4888508581443</v>
       </c>
       <c r="C152" t="n">
-        <v>178.0962045390804</v>
+        <v>183.4927641701262</v>
       </c>
       <c r="D152" t="n">
-        <v>169.9117629967484</v>
+        <v>176.7420953199099</v>
       </c>
       <c r="E152" t="n">
-        <v>176.7918740224492</v>
+        <v>179.4005432128906</v>
       </c>
       <c r="F152" t="n">
-        <v>22719900</v>
+        <v>11907000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4387,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="n">
-        <v>177.3892822265625</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C153" t="n">
-        <v>177.6780209996891</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D153" t="n">
-        <v>173.6455382897692</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E153" t="n">
-        <v>174.8602617765654</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F153" t="n">
-        <v>10817600</v>
+        <v>8711700</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4413,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B154" t="n">
-        <v>179.4005279541016</v>
+        <v>178.424769515226</v>
       </c>
       <c r="C154" t="n">
-        <v>183.4927485632761</v>
+        <v>180.993610139636</v>
       </c>
       <c r="D154" t="n">
-        <v>176.7420802872333</v>
+        <v>176.5827818160244</v>
       </c>
       <c r="E154" t="n">
-        <v>177.4888357619529</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F154" t="n">
-        <v>11907000</v>
+        <v>6882800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4439,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="n">
-        <v>180.5356140136719</v>
+        <v>177.5286741071897</v>
       </c>
       <c r="C155" t="n">
-        <v>183.6221942474171</v>
+        <v>177.9169863526292</v>
       </c>
       <c r="D155" t="n">
-        <v>180.5356140136719</v>
+        <v>172.2515989617143</v>
       </c>
       <c r="E155" t="n">
-        <v>181.6407975504903</v>
+        <v>175.7663269042969</v>
       </c>
       <c r="F155" t="n">
-        <v>8711700</v>
+        <v>14408300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4465,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B156" t="n">
-        <v>180.4360504150391</v>
+        <v>181.4018572311292</v>
       </c>
       <c r="C156" t="n">
-        <v>180.993625445577</v>
+        <v>185.2351932001588</v>
       </c>
       <c r="D156" t="n">
-        <v>176.5827967489585</v>
+        <v>177.9767360752557</v>
       </c>
       <c r="E156" t="n">
-        <v>178.4247846039299</v>
+        <v>183.0248107910156</v>
       </c>
       <c r="F156" t="n">
-        <v>6882800</v>
+        <v>12324400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4491,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="n">
-        <v>175.7663421630859</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C157" t="n">
-        <v>177.9170017981234</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D157" t="n">
-        <v>172.2516139153796</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E157" t="n">
-        <v>177.5286895189733</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F157" t="n">
-        <v>14408300</v>
+        <v>8444700</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4517,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="n">
-        <v>183.0247955322266</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C158" t="n">
-        <v>185.2351777570901</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D158" t="n">
-        <v>177.9767212373249</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E158" t="n">
-        <v>181.4018421076459</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F158" t="n">
-        <v>12324400</v>
+        <v>9740800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4543,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B159" t="n">
-        <v>184.6775970458984</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C159" t="n">
-        <v>189.4867039708132</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D159" t="n">
-        <v>183.1741348747832</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E159" t="n">
-        <v>183.4429710909726</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F159" t="n">
-        <v>8444700</v>
+        <v>11303400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4569,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="n">
-        <v>186.1810913085938</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C160" t="n">
-        <v>186.5793548412774</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D160" t="n">
-        <v>180.3165719120649</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E160" t="n">
-        <v>184.7473182824849</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F160" t="n">
-        <v>9740800</v>
+        <v>13955100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4595,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B161" t="n">
-        <v>180.4061737060547</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C161" t="n">
-        <v>186.2906106667237</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D161" t="n">
-        <v>178.8031379653169</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E161" t="n">
-        <v>184.7174439304337</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F161" t="n">
-        <v>11303400</v>
+        <v>15123900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4621,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="n">
-        <v>185.5338897705078</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C162" t="n">
-        <v>187.7642050029951</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D162" t="n">
-        <v>183.2040162535504</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E162" t="n">
-        <v>183.801426731489</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F162" t="n">
-        <v>13955100</v>
+        <v>11145000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4647,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="n">
-        <v>181.0334625244141</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C163" t="n">
-        <v>181.0832340725416</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D163" t="n">
-        <v>176.114830301217</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E163" t="n">
-        <v>178.9027054786904</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F163" t="n">
-        <v>15123900</v>
+        <v>10214000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4673,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="n">
-        <v>176.7221832275391</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C164" t="n">
-        <v>181.7105044839724</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D164" t="n">
-        <v>175.5472800106302</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E164" t="n">
-        <v>179.1317124775628</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F164" t="n">
-        <v>11145000</v>
+        <v>11951900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4699,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="n">
-        <v>170.5689086914062</v>
+        <v>165.2818748478833</v>
       </c>
       <c r="C165" t="n">
-        <v>176.8117888588543</v>
+        <v>168.6173886402985</v>
       </c>
       <c r="D165" t="n">
-        <v>169.8420709331304</v>
+        <v>163.6191011830893</v>
       </c>
       <c r="E165" t="n">
-        <v>176.8117888588543</v>
+        <v>166.8550415039062</v>
       </c>
       <c r="F165" t="n">
-        <v>10214000</v>
+        <v>9749400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4725,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="n">
-        <v>165.1225738525391</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C166" t="n">
-        <v>169.0455318751909</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D166" t="n">
-        <v>164.0372928300067</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E166" t="n">
-        <v>169.0455318751909</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F166" t="n">
-        <v>11951900</v>
+        <v>13883400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4751,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="n">
-        <v>166.8550567626953</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C167" t="n">
-        <v>168.6174040602531</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D167" t="n">
-        <v>163.6191161459536</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E167" t="n">
-        <v>165.2818899628073</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F167" t="n">
-        <v>9749400</v>
+        <v>13671200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4777,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="n">
-        <v>172.7593841552734</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C168" t="n">
-        <v>175.208748793394</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D168" t="n">
-        <v>168.268900043628</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E168" t="n">
-        <v>168.5178185348167</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F168" t="n">
-        <v>13883400</v>
+        <v>17510800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4803,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="n">
-        <v>178.7035675048828</v>
+        <v>175.2784431578192</v>
       </c>
       <c r="C169" t="n">
-        <v>179.9979467596552</v>
+        <v>179.529975364695</v>
       </c>
       <c r="D169" t="n">
-        <v>171.0567983816156</v>
+        <v>172.5901264135125</v>
       </c>
       <c r="E169" t="n">
-        <v>172.1420794089453</v>
+        <v>179.3208923339844</v>
       </c>
       <c r="F169" t="n">
-        <v>13671200</v>
+        <v>13025300</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4829,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="n">
-        <v>178.6438293457031</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C170" t="n">
-        <v>186.6291391730516</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D170" t="n">
-        <v>178.0364675908902</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E170" t="n">
-        <v>184.1996921538</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F170" t="n">
-        <v>17510800</v>
+        <v>10949100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4855,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="n">
-        <v>179.3209075927734</v>
+        <v>179.0619996775001</v>
       </c>
       <c r="C171" t="n">
-        <v>179.5299906412754</v>
+        <v>182.5568249684187</v>
       </c>
       <c r="D171" t="n">
-        <v>172.5901410995666</v>
+        <v>176.9113402973623</v>
       </c>
       <c r="E171" t="n">
-        <v>175.2784580726278</v>
+        <v>179.291015625</v>
       </c>
       <c r="F171" t="n">
-        <v>13025300</v>
+        <v>10176700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4881,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B172" t="n">
-        <v>175.5472869873047</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C172" t="n">
-        <v>176.5728300297275</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D172" t="n">
-        <v>171.2459830488208</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E172" t="n">
-        <v>174.6213174256682</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F172" t="n">
-        <v>10949100</v>
+        <v>13617200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4907,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B173" t="n">
-        <v>179.2910308837891</v>
+        <v>177.2299664024681</v>
       </c>
       <c r="C173" t="n">
-        <v>182.5568405051486</v>
+        <v>183.1243544731695</v>
       </c>
       <c r="D173" t="n">
-        <v>176.9113553536261</v>
+        <v>176.1247676896629</v>
       </c>
       <c r="E173" t="n">
-        <v>179.0620149167984</v>
+        <v>176.7420806884766</v>
       </c>
       <c r="F173" t="n">
-        <v>10176700</v>
+        <v>18524900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4933,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B174" t="n">
-        <v>178.3052978515625</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C174" t="n">
-        <v>181.5711072848628</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D174" t="n">
-        <v>176.9113451663183</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E174" t="n">
-        <v>177.6581006500201</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F174" t="n">
-        <v>13617200</v>
+        <v>22559400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4959,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B175" t="n">
-        <v>176.7420959472656</v>
+        <v>179.4602803383912</v>
       </c>
       <c r="C175" t="n">
-        <v>183.1243702829636</v>
+        <v>193.3001423298492</v>
       </c>
       <c r="D175" t="n">
-        <v>176.1247828951571</v>
+        <v>179.24123085138</v>
       </c>
       <c r="E175" t="n">
-        <v>177.2299817033781</v>
+        <v>190.2733001708984</v>
       </c>
       <c r="F175" t="n">
-        <v>18524900</v>
+        <v>33998900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4985,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B176" t="n">
-        <v>175.4078826904297</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C176" t="n">
-        <v>181.6905830539347</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D176" t="n">
-        <v>170.9074320607842</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E176" t="n">
-        <v>177.6581004088628</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F176" t="n">
-        <v>22559400</v>
+        <v>27594800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5011,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B177" t="n">
-        <v>190.2733154296875</v>
+        <v>200.1503901074607</v>
       </c>
       <c r="C177" t="n">
-        <v>193.300157831373</v>
+        <v>203.5058065985036</v>
       </c>
       <c r="D177" t="n">
-        <v>179.2412452254626</v>
+        <v>194.9131351866423</v>
       </c>
       <c r="E177" t="n">
-        <v>179.4602947300403</v>
+        <v>199.9711608886719</v>
       </c>
       <c r="F177" t="n">
-        <v>33998900</v>
+        <v>19216600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5037,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B178" t="n">
-        <v>208.6932678222656</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C178" t="n">
-        <v>210.4257307870387</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D178" t="n">
-        <v>197.352542040295</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E178" t="n">
-        <v>197.8901992931745</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F178" t="n">
-        <v>27594800</v>
+        <v>14154400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5063,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B179" t="n">
-        <v>199.9711761474609</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C179" t="n">
-        <v>203.5058221270036</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D179" t="n">
-        <v>194.9131500594789</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E179" t="n">
-        <v>200.1504053799259</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F179" t="n">
-        <v>19216600</v>
+        <v>14453600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5089,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B180" t="n">
-        <v>189.7854156494141</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C180" t="n">
-        <v>196.8248227029743</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D180" t="n">
-        <v>188.9092176958791</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E180" t="n">
-        <v>196.4166079226038</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F180" t="n">
-        <v>14154400</v>
+        <v>13183900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5115,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B181" t="n">
-        <v>187.9334716796875</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C181" t="n">
-        <v>197.2330634002457</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D181" t="n">
-        <v>185.3048928689384</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E181" t="n">
-        <v>196.9542758894677</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F181" t="n">
-        <v>14453600</v>
+        <v>11177800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5141,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="n">
-        <v>184.8568420410156</v>
+        <v>178.7234870391233</v>
       </c>
       <c r="C182" t="n">
-        <v>191.6771999565016</v>
+        <v>181.6706888305526</v>
       </c>
       <c r="D182" t="n">
-        <v>184.0304307819904</v>
+        <v>170.8178328696119</v>
       </c>
       <c r="E182" t="n">
-        <v>188.9789318725711</v>
+        <v>174.5914459228516</v>
       </c>
       <c r="F182" t="n">
-        <v>13183900</v>
+        <v>15427800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5167,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="n">
-        <v>181.7602996826172</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C183" t="n">
-        <v>184.2196157855271</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D183" t="n">
-        <v>180.92393713233</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E183" t="n">
-        <v>183.1144169895118</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F183" t="n">
-        <v>11177800</v>
+        <v>10820500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5193,25 +5201,25 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="n">
-        <v>174.5914306640625</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C184" t="n">
-        <v>181.670672953058</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D184" t="n">
-        <v>170.8178179406258</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E184" t="n">
-        <v>178.7234714192057</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F184" t="n">
-        <v>15427800</v>
+        <v>16666000</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5219,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="n">
-        <v>170.1806030273438</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C185" t="n">
-        <v>174.7706609037228</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D185" t="n">
-        <v>169.2944537502145</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E185" t="n">
-        <v>169.861995238658</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F185" t="n">
-        <v>10820500</v>
+        <v>13589400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5245,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B186" t="n">
-        <v>166.1576843261719</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C186" t="n">
-        <v>168.6832400259219</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D186" t="n">
-        <v>163.0231992739924</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E186" t="n">
-        <v>167.9744954285649</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F186" t="n">
-        <v>16666000</v>
+        <v>13541800</v>
       </c>
       <c r="G186" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5271,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B187" t="n">
-        <v>165.5986633300781</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C187" t="n">
-        <v>166.2475157071144</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D187" t="n">
-        <v>161.1165431857153</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E187" t="n">
-        <v>164.4506890531704</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F187" t="n">
-        <v>13589400</v>
+        <v>16385300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5297,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B188" t="n">
-        <v>164.2610168457031</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C188" t="n">
-        <v>169.6515271583533</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D188" t="n">
-        <v>163.8816793355271</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E188" t="n">
-        <v>165.7384133733495</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F188" t="n">
-        <v>13541800</v>
+        <v>19986200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5323,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B189" t="n">
-        <v>161.4260101318359</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C189" t="n">
-        <v>166.0079454764833</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D189" t="n">
-        <v>160.2181284427459</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E189" t="n">
-        <v>163.7718739013043</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F189" t="n">
-        <v>16385300</v>
+        <v>57940800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5349,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B190" t="n">
-        <v>154.7477569580078</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C190" t="n">
-        <v>161.1464880907799</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D190" t="n">
-        <v>153.959135832121</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E190" t="n">
-        <v>159.9685677271403</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F190" t="n">
-        <v>19986200</v>
+        <v>20502800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5375,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B191" t="n">
-        <v>151.5134429931641</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C191" t="n">
-        <v>154.1987212566731</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D191" t="n">
-        <v>149.5369245308901</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E191" t="n">
-        <v>152.4617715583163</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F191" t="n">
-        <v>57940800</v>
+        <v>20720700</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5401,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B192" t="n">
-        <v>149.8563537597656</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C192" t="n">
-        <v>153.5997679942281</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D192" t="n">
-        <v>146.0630395211035</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E192" t="n">
-        <v>149.8962920415152</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F192" t="n">
-        <v>20502800</v>
+        <v>13146800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5427,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B193" t="n">
-        <v>153.1505584716797</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C193" t="n">
-        <v>154.907462036052</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D193" t="n">
-        <v>150.5850798848861</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E193" t="n">
-        <v>151.3836627210609</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F193" t="n">
-        <v>20720700</v>
+        <v>11324700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5453,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B194" t="n">
-        <v>152.4917144775391</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C194" t="n">
-        <v>156.7841657815476</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D194" t="n">
-        <v>150.135858545478</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E194" t="n">
-        <v>151.5433859321397</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F194" t="n">
-        <v>13146800</v>
+        <v>21267900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5479,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B195" t="n">
-        <v>149.9262390136719</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C195" t="n">
-        <v>153.7295454610107</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D195" t="n">
-        <v>148.5187115976041</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E195" t="n">
-        <v>149.7465472087312</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F195" t="n">
-        <v>11324700</v>
+        <v>12664100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5505,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B196" t="n">
-        <v>158.0918731689453</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C196" t="n">
-        <v>158.1817266914859</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D196" t="n">
-        <v>151.2239658596097</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E196" t="n">
-        <v>151.2239658596097</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F196" t="n">
-        <v>21267900</v>
+        <v>13690500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5531,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B197" t="n">
-        <v>157.6526336669922</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C197" t="n">
-        <v>161.4759091917036</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D197" t="n">
-        <v>157.4230418613804</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E197" t="n">
-        <v>159.9885357004027</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F197" t="n">
-        <v>12664100</v>
+        <v>14164600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5557,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B198" t="n">
-        <v>156.3848724365234</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C198" t="n">
-        <v>157.4130622995693</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D198" t="n">
-        <v>153.7994247316601</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E198" t="n">
-        <v>154.8176224085462</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F198" t="n">
-        <v>13690500</v>
+        <v>10486300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5583,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B199" t="n">
-        <v>162.9433288574219</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C199" t="n">
-        <v>165.5187996520913</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D199" t="n">
-        <v>160.916895191227</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E199" t="n">
-        <v>161.9351081174896</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F199" t="n">
-        <v>14164600</v>
+        <v>10595500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5609,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B200" t="n">
-        <v>165.8182830810547</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C200" t="n">
-        <v>166.9163573859938</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D200" t="n">
-        <v>161.7155003336798</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E200" t="n">
-        <v>162.7137441629</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F200" t="n">
-        <v>10486300</v>
+        <v>13057900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5635,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B201" t="n">
-        <v>165.3590850830078</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C201" t="n">
-        <v>167.425457131665</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D201" t="n">
-        <v>162.0848465245878</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E201" t="n">
-        <v>163.7020118941432</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F201" t="n">
-        <v>10595500</v>
+        <v>9792400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5661,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B202" t="n">
-        <v>169.2222900390625</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C202" t="n">
-        <v>172.0772678623225</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D202" t="n">
-        <v>167.3855099055031</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E202" t="n">
-        <v>168.9228138583306</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F202" t="n">
-        <v>13057900</v>
+        <v>13858600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5687,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B203" t="n">
-        <v>166.2874603271484</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C203" t="n">
-        <v>167.2357889266519</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D203" t="n">
-        <v>164.4906183727253</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E203" t="n">
-        <v>167.0760662569272</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F203" t="n">
-        <v>9792400</v>
+        <v>8321500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5713,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B204" t="n">
-        <v>162.2146148681641</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C204" t="n">
-        <v>163.5123348335076</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D204" t="n">
-        <v>156.2051830247059</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E204" t="n">
-        <v>158.05194011754</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F204" t="n">
-        <v>13858600</v>
+        <v>14020700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5739,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>163.0331878662109</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C205" t="n">
-        <v>166.007950182526</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D205" t="n">
-        <v>162.1347592897187</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E205" t="n">
-        <v>165.309182555471</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F205" t="n">
-        <v>8321500</v>
+        <v>13507900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5765,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>170.9193115234375</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C206" t="n">
-        <v>172.4566003351415</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D206" t="n">
-        <v>165.6286161244176</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E206" t="n">
-        <v>165.6286161244176</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F206" t="n">
-        <v>14020700</v>
+        <v>13328100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5791,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>167.2657318115234</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C207" t="n">
-        <v>171.049084414024</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D207" t="n">
-        <v>161.1864306117812</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E207" t="n">
-        <v>162.2046435717354</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F207" t="n">
-        <v>13507900</v>
+        <v>12057500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5817,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B208" t="n">
-        <v>166.7067108154297</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C208" t="n">
-        <v>172.4965277703878</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D208" t="n">
-        <v>166.2674811162824</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E208" t="n">
-        <v>170.2205331766167</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F208" t="n">
-        <v>13328100</v>
+        <v>10191500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5843,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B209" t="n">
-        <v>172.3767395019531</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C209" t="n">
-        <v>174.2334736592566</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D209" t="n">
-        <v>166.5869373980102</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E209" t="n">
-        <v>170.5399744864679</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F209" t="n">
-        <v>12057500</v>
+        <v>13426500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5869,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B210" t="n">
-        <v>170.4700927734375</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C210" t="n">
-        <v>175.1218971627477</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D210" t="n">
-        <v>169.4518798636439</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E210" t="n">
-        <v>171.1988064601764</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F210" t="n">
-        <v>10191500</v>
+        <v>12831800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5895,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B211" t="n">
-        <v>173.4847869873047</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C211" t="n">
-        <v>175.0819831940494</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D211" t="n">
-        <v>166.2075962327059</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E211" t="n">
-        <v>167.5652084388413</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F211" t="n">
-        <v>13426500</v>
+        <v>12194500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5921,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B212" t="n">
-        <v>169.7613372802734</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C212" t="n">
-        <v>172.1271701993457</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D212" t="n">
-        <v>166.6368293287962</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E212" t="n">
-        <v>166.7666058963373</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F212" t="n">
-        <v>12831800</v>
+        <v>12775000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5947,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B213" t="n">
-        <v>162.7137451171875</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C213" t="n">
-        <v>169.272214424985</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D213" t="n">
-        <v>161.925139189555</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E213" t="n">
-        <v>169.1723839486806</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F213" t="n">
-        <v>12194500</v>
+        <v>10899100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5973,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B214" t="n">
-        <v>156.6543884277344</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C214" t="n">
-        <v>165.5886824068968</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D214" t="n">
-        <v>154.877515725338</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E214" t="n">
-        <v>164.7601382451291</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F214" t="n">
-        <v>12775000</v>
+        <v>17312000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -5999,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B215" t="n">
-        <v>163.3725891113281</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C215" t="n">
-        <v>164.1611950360997</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D215" t="n">
-        <v>159.2698063547753</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E215" t="n">
-        <v>160.0983505627206</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F215" t="n">
-        <v>10899100</v>
+        <v>17204600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6025,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B216" t="n">
-        <v>173.2951354980469</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C216" t="n">
-        <v>176.6392431993331</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D216" t="n">
-        <v>166.8464736349225</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E216" t="n">
-        <v>167.7049639405646</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F216" t="n">
-        <v>17312000</v>
+        <v>18139500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6051,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B217" t="n">
-        <v>181.1812438964844</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C217" t="n">
-        <v>184.2158982492034</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D217" t="n">
-        <v>176.5993086569288</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E217" t="n">
-        <v>176.5993086569288</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F217" t="n">
-        <v>17204600</v>
+        <v>12182400</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6077,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B218" t="n">
-        <v>188.0491790771484</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C218" t="n">
-        <v>189.8460057999592</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D218" t="n">
-        <v>181.6903554713178</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E218" t="n">
-        <v>181.6903554713178</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F218" t="n">
-        <v>18139500</v>
+        <v>9691500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6103,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B219" t="n">
-        <v>180.3926391601562</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C219" t="n">
-        <v>182.1894657683464</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D219" t="n">
-        <v>175.5910738107855</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E219" t="n">
-        <v>180.6721461984077</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F219" t="n">
-        <v>12182400</v>
+        <v>12908000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6129,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B220" t="n">
-        <v>183.6968231201172</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C220" t="n">
-        <v>184.1260606305619</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D220" t="n">
-        <v>176.719093672914</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E220" t="n">
-        <v>177.3879151720665</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F220" t="n">
-        <v>9691500</v>
+        <v>9326900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6155,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B221" t="n">
-        <v>185.6234283447266</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C221" t="n">
-        <v>193.3598176605707</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D221" t="n">
-        <v>185.5735131091938</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E221" t="n">
-        <v>188.658097974018</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F221" t="n">
-        <v>12908000</v>
+        <v>9605500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6181,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B222" t="n">
-        <v>190.6545867919922</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C222" t="n">
-        <v>190.9540477431734</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D222" t="n">
-        <v>182.6786134323838</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E222" t="n">
-        <v>182.7684517177381</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F222" t="n">
-        <v>9326900</v>
+        <v>13297600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6207,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B223" t="n">
-        <v>192.6410827636719</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C223" t="n">
-        <v>194.5976472985604</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D223" t="n">
-        <v>190.0955580470331</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E223" t="n">
-        <v>192.9405589477455</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F223" t="n">
-        <v>9605500</v>
+        <v>11392800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6233,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B224" t="n">
-        <v>186.4420013427734</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C224" t="n">
-        <v>186.6915622961891</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D224" t="n">
-        <v>182.6786179003067</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E224" t="n">
-        <v>183.117847615437</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F224" t="n">
-        <v>13297600</v>
+        <v>9706600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6259,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B225" t="n">
-        <v>192.4015197753906</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C225" t="n">
-        <v>194.3580691369978</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D225" t="n">
-        <v>190.2652786051507</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E225" t="n">
-        <v>190.7544083295565</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F225" t="n">
-        <v>11392800</v>
+        <v>11171600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6285,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B226" t="n">
-        <v>197.1631317138672</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C226" t="n">
-        <v>197.831953246477</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D226" t="n">
-        <v>189.666326097428</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E226" t="n">
-        <v>189.8360257192551</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F226" t="n">
-        <v>9706600</v>
+        <v>12787900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6311,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B227" t="n">
-        <v>197.1231994628906</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C227" t="n">
-        <v>199.0398256830038</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D227" t="n">
-        <v>195.1566580076304</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E227" t="n">
-        <v>196.5941314807131</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F227" t="n">
-        <v>11171600</v>
+        <v>15058700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6337,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="n">
-        <v>192.9804992675781</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C228" t="n">
-        <v>196.1549072491085</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D228" t="n">
-        <v>191.4431952813594</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E228" t="n">
-        <v>191.6628101365335</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F228" t="n">
-        <v>12787900</v>
+        <v>8664800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6363,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B229" t="n">
-        <v>201.016357421875</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C229" t="n">
-        <v>202.6335228023228</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D229" t="n">
-        <v>191.0538881519706</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E229" t="n">
-        <v>196.4943140399408</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F229" t="n">
-        <v>15058700</v>
+        <v>14378800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6389,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B230" t="n">
-        <v>195.8654174804688</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C230" t="n">
-        <v>204.0410211897246</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D230" t="n">
-        <v>194.9769811314243</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E230" t="n">
-        <v>202.3939250564146</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F230" t="n">
-        <v>8664800</v>
+        <v>14152900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6415,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B231" t="n">
-        <v>190.6346282958984</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C231" t="n">
-        <v>194.5976575790598</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D231" t="n">
-        <v>189.57649225733</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E231" t="n">
-        <v>193.4896063018435</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F231" t="n">
-        <v>14378800</v>
+        <v>17843600</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6441,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B232" t="n">
-        <v>195.7955474853516</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C232" t="n">
-        <v>199.0598091290667</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D232" t="n">
-        <v>192.8906542357335</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E232" t="n">
-        <v>193.7491445531879</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F232" t="n">
-        <v>14152900</v>
+        <v>11482300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6467,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="n">
-        <v>205.7280578613281</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C233" t="n">
-        <v>207.5847919095016</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D233" t="n">
-        <v>193.8689320609861</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E233" t="n">
-        <v>193.8689320609861</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F233" t="n">
-        <v>17843600</v>
+        <v>9685400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6493,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B234" t="n">
-        <v>205.0692138671875</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C234" t="n">
-        <v>207.5149233311111</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D234" t="n">
-        <v>202.6434887759544</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E234" t="n">
-        <v>204.8595912018172</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F234" t="n">
-        <v>11482300</v>
+        <v>9580200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6519,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B235" t="n">
-        <v>208.8026580810547</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C235" t="n">
-        <v>210.6993304789719</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D235" t="n">
-        <v>204.3704530814486</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E235" t="n">
-        <v>205.2189664215684</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F235" t="n">
-        <v>9685400</v>
+        <v>10081800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6545,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B236" t="n">
-        <v>208.6928558349609</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C236" t="n">
-        <v>212.7956386479058</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D236" t="n">
-        <v>207.0257904413594</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E236" t="n">
-        <v>208.0539803833292</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F236" t="n">
-        <v>9580200</v>
+        <v>14888900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6571,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B237" t="n">
-        <v>205.3287658691406</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C237" t="n">
-        <v>209.9406472657768</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D237" t="n">
-        <v>204.400391231641</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E237" t="n">
-        <v>205.4884885298704</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F237" t="n">
-        <v>10081800</v>
+        <v>55517500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6597,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B238" t="n">
-        <v>205.2588806152344</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C238" t="n">
-        <v>206.0774478239803</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D238" t="n">
-        <v>198.6005964484484</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E238" t="n">
-        <v>199.5888632714973</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F238" t="n">
-        <v>14888900</v>
+        <v>34362700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6623,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B239" t="n">
-        <v>251.6073608398438</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C239" t="n">
-        <v>254.0330860396483</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D239" t="n">
-        <v>229.6459965412689</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E239" t="n">
-        <v>229.6459965412689</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F239" t="n">
-        <v>55517500</v>
+        <v>22471500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6649,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B240" t="n">
-        <v>255.5504150390625</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C240" t="n">
-        <v>263.0671897003631</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D240" t="n">
-        <v>248.5627083778381</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E240" t="n">
-        <v>250.0301279952546</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F240" t="n">
-        <v>34362700</v>
+        <v>15897500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6675,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B241" t="n">
-        <v>257.0877075195312</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C241" t="n">
-        <v>261.8193732125837</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D241" t="n">
-        <v>253.9432305236259</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E241" t="n">
-        <v>253.9432305236259</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F241" t="n">
-        <v>22471500</v>
+        <v>14393700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6701,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B242" t="n">
-        <v>257.6567077636719</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C242" t="n">
-        <v>261.8593363431507</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D242" t="n">
-        <v>253.8035010915435</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E242" t="n">
-        <v>254.5621609406893</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F242" t="n">
-        <v>15897500</v>
+        <v>16028300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6727,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B243" t="n">
-        <v>256.478759765625</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C243" t="n">
-        <v>264.0853722779391</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D243" t="n">
-        <v>253.154621477229</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E243" t="n">
-        <v>258.9244691424316</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F243" t="n">
-        <v>14393700</v>
+        <v>10490600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6753,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B244" t="n">
-        <v>263.9656066894531</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C244" t="n">
-        <v>267.7988593124239</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D244" t="n">
-        <v>261.1405900757476</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E244" t="n">
-        <v>261.5199276025597</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F244" t="n">
-        <v>16028300</v>
+        <v>17482700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6779,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B245" t="n">
-        <v>258.7747497558594</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C245" t="n">
-        <v>263.1370702625856</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D245" t="n">
-        <v>257.3672223502596</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E245" t="n">
-        <v>262.8974710364521</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F245" t="n">
-        <v>10490600</v>
+        <v>11853700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6805,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B246" t="n">
-        <v>248.6824951171875</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C246" t="n">
-        <v>253.5539298242691</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D246" t="n">
-        <v>245.4581718493405</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E246" t="n">
-        <v>253.2744227737308</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F246" t="n">
-        <v>17482700</v>
+        <v>10732600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6831,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B247" t="n">
-        <v>243.7312164306641</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C247" t="n">
-        <v>254.3525301395604</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D247" t="n">
-        <v>243.0224566114913</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E247" t="n">
-        <v>249.3413418635835</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F247" t="n">
-        <v>11853700</v>
+        <v>9738300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6857,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B248" t="n">
-        <v>242.5732421875</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C248" t="n">
-        <v>248.0635830600566</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D248" t="n">
-        <v>241.3254374437371</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E248" t="n">
-        <v>244.9191211985708</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F248" t="n">
-        <v>10732600</v>
+        <v>12963700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6883,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B249" t="n">
-        <v>247.2849578857422</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C249" t="n">
-        <v>250.1099896964979</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D249" t="n">
-        <v>241.5949712138984</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E249" t="n">
-        <v>241.5949712138984</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F249" t="n">
-        <v>9738300</v>
+        <v>11502800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6909,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B250" t="n">
-        <v>258.9743957519531</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C250" t="n">
-        <v>259.7230786425112</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D250" t="n">
-        <v>251.0583293004754</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E250" t="n">
-        <v>255.3008656803045</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F250" t="n">
-        <v>12963700</v>
+        <v>9423800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6935,25 +6943,25 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B251" t="n">
-        <v>255.2010192871094</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C251" t="n">
-        <v>261.8792726915332</v>
+        <v>247</v>
       </c>
       <c r="D251" t="n">
-        <v>254.632028246405</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E251" t="n">
-        <v>256.43886230448</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F251" t="n">
-        <v>11502800</v>
+        <v>16611300</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -6961,53 +6969,27 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B252" t="n">
-        <v>250.0999908447266</v>
+        <v>244.25</v>
       </c>
       <c r="C252" t="n">
-        <v>255.9497000259878</v>
+        <v>244.25</v>
       </c>
       <c r="D252" t="n">
-        <v>249.1616544830015</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E252" t="n">
-        <v>251.4077029961344</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F252" t="n">
-        <v>9423800</v>
+        <v>21947900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B253" t="n">
-        <v>242.8500061035156</v>
-      </c>
-      <c r="C253" t="n">
-        <v>247</v>
-      </c>
-      <c r="D253" t="n">
-        <v>241.5200042724609</v>
-      </c>
-      <c r="E253" t="n">
-        <v>244.1799926757812</v>
-      </c>
-      <c r="F253" t="n">
-        <v>16590200</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10672,37 +10654,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>237.92</v>
+      </c>
+      <c r="D2" t="n">
         <v>242.85</v>
       </c>
-      <c r="D2" t="n">
-        <v>250.1</v>
-      </c>
       <c r="E2" t="n">
-        <v>244.18</v>
+        <v>244.25</v>
       </c>
       <c r="F2" t="n">
-        <v>246.915</v>
+        <v>244.25</v>
       </c>
       <c r="G2" t="n">
-        <v>241.52</v>
+        <v>236.545</v>
       </c>
       <c r="H2" t="n">
-        <v>15020557</v>
+        <v>21529713</v>
       </c>
       <c r="I2" t="n">
-        <v>14134927</v>
+        <v>14298250</v>
       </c>
       <c r="J2" t="n">
-        <v>199865548800</v>
+        <v>195808165888</v>
       </c>
       <c r="K2" t="n">
-        <v>22.93201</v>
+        <v>22.214752</v>
       </c>
       <c r="L2" t="n">
-        <v>15.167262</v>
+        <v>14.859358</v>
       </c>
       <c r="M2" t="n">
-        <v>10.59</v>
+        <v>10.71</v>
       </c>
       <c r="N2" t="n">
         <v>269.11</v>
@@ -10714,7 +10696,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10738,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.2077975</v>
+        <v>5.1020756</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10750,7 +10732,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>230838550528</v>
+        <v>226781167616</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10777,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:16:05</t>
+          <t>2026-09-19 15:21:49</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="n">
-        <v>243.9508327525358</v>
+        <v>242.4436227791717</v>
       </c>
       <c r="C2" t="n">
-        <v>245.1209010026767</v>
+        <v>242.6022807239559</v>
       </c>
       <c r="D2" t="n">
-        <v>241.3032908232194</v>
+        <v>237.4757650354455</v>
       </c>
       <c r="E2" t="n">
-        <v>245.0118255615234</v>
+        <v>238.9234771728516</v>
       </c>
       <c r="F2" t="n">
-        <v>11813900</v>
+        <v>8145500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="B3" t="n">
-        <v>243.2170528270286</v>
+        <v>238.6656837954339</v>
       </c>
       <c r="C3" t="n">
-        <v>248.3733148082552</v>
+        <v>242.4733839178257</v>
       </c>
       <c r="D3" t="n">
-        <v>241.1148880888675</v>
+        <v>238.3285469902175</v>
       </c>
       <c r="E3" t="n">
-        <v>247.5899658203125</v>
+        <v>241.3826293945312</v>
       </c>
       <c r="F3" t="n">
-        <v>7523800</v>
+        <v>4974600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="n">
-        <v>247.6395695794253</v>
+        <v>242.6617806304829</v>
       </c>
       <c r="C4" t="n">
-        <v>249.2459397432638</v>
+        <v>243.7525351190903</v>
       </c>
       <c r="D4" t="n">
-        <v>242.0767518252397</v>
+        <v>240.8273340261308</v>
       </c>
       <c r="E4" t="n">
-        <v>242.5031280517578</v>
+        <v>243.0385894775391</v>
       </c>
       <c r="F4" t="n">
-        <v>7669800</v>
+        <v>6373500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="n">
-        <v>243.6037942867359</v>
+        <v>242.989012448683</v>
       </c>
       <c r="C5" t="n">
-        <v>246.7471312330163</v>
+        <v>243.1476704015903</v>
       </c>
       <c r="D5" t="n">
-        <v>240.9661625460427</v>
+        <v>233.8267199294288</v>
       </c>
       <c r="E5" t="n">
-        <v>243.8219451904297</v>
+        <v>235.0067138671875</v>
       </c>
       <c r="F5" t="n">
-        <v>6707100</v>
+        <v>10801100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="B6" t="n">
-        <v>242.4436227791717</v>
+        <v>234.5010077854061</v>
       </c>
       <c r="C6" t="n">
-        <v>242.6022807239559</v>
+        <v>240.4307087963897</v>
       </c>
       <c r="D6" t="n">
-        <v>237.4757650354455</v>
+        <v>231.5460601627856</v>
       </c>
       <c r="E6" t="n">
-        <v>238.9234771728516</v>
+        <v>233.7077331542969</v>
       </c>
       <c r="F6" t="n">
-        <v>8145500</v>
+        <v>10016600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="B7" t="n">
-        <v>238.6656837954339</v>
+        <v>233.4498996394798</v>
       </c>
       <c r="C7" t="n">
-        <v>242.4733839178257</v>
+        <v>237.3865110117534</v>
       </c>
       <c r="D7" t="n">
-        <v>238.3285469902175</v>
+        <v>231.6353042398812</v>
       </c>
       <c r="E7" t="n">
-        <v>241.3826293945312</v>
+        <v>236.8708953857422</v>
       </c>
       <c r="F7" t="n">
-        <v>4974600</v>
+        <v>7679200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45929</v>
+        <v>45933</v>
       </c>
       <c r="B8" t="n">
-        <v>242.6617806304829</v>
+        <v>236.7419954840688</v>
       </c>
       <c r="C8" t="n">
-        <v>243.7525351190903</v>
+        <v>240.7678464733125</v>
       </c>
       <c r="D8" t="n">
-        <v>240.8273340261308</v>
+        <v>236.4940981065986</v>
       </c>
       <c r="E8" t="n">
-        <v>243.0385894775391</v>
+        <v>238.3384552001953</v>
       </c>
       <c r="F8" t="n">
-        <v>6373500</v>
+        <v>8849800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45930</v>
+        <v>45936</v>
       </c>
       <c r="B9" t="n">
-        <v>242.989012448683</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="C9" t="n">
-        <v>243.1476704015903</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D9" t="n">
-        <v>233.8267199294288</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E9" t="n">
-        <v>235.0067138671875</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="F9" t="n">
-        <v>10801100</v>
+        <v>13922600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="B10" t="n">
-        <v>234.5010077854061</v>
+        <v>244.4069823156386</v>
       </c>
       <c r="C10" t="n">
-        <v>240.4307087963897</v>
+        <v>245.2795859409202</v>
       </c>
       <c r="D10" t="n">
-        <v>231.5460601627856</v>
+        <v>235.5520951044222</v>
       </c>
       <c r="E10" t="n">
-        <v>233.7077331542969</v>
+        <v>237.7236785888672</v>
       </c>
       <c r="F10" t="n">
-        <v>10016600</v>
+        <v>8387400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45932</v>
+        <v>45938</v>
       </c>
       <c r="B11" t="n">
-        <v>233.4498996394798</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C11" t="n">
-        <v>237.3865110117534</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D11" t="n">
-        <v>231.6353042398812</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E11" t="n">
-        <v>236.8708953857422</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F11" t="n">
-        <v>7679200</v>
+        <v>7120200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45933</v>
+        <v>45939</v>
       </c>
       <c r="B12" t="n">
-        <v>236.7419954840688</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C12" t="n">
-        <v>240.7678464733125</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D12" t="n">
-        <v>236.4940981065986</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E12" t="n">
-        <v>238.3384552001953</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F12" t="n">
-        <v>8849800</v>
+        <v>7929100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B13" t="n">
-        <v>237.3171110157645</v>
+        <v>244.4466434616172</v>
       </c>
       <c r="C13" t="n">
-        <v>248.3634171689519</v>
+        <v>246.9553636418975</v>
       </c>
       <c r="D13" t="n">
-        <v>233.430082086989</v>
+        <v>238.6954214370453</v>
       </c>
       <c r="E13" t="n">
-        <v>243.7128601074219</v>
+        <v>239.6473388671875</v>
       </c>
       <c r="F13" t="n">
-        <v>13922600</v>
+        <v>7988300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="B14" t="n">
-        <v>244.4069666278678</v>
+        <v>240.8471826425636</v>
       </c>
       <c r="C14" t="n">
-        <v>245.2795701971395</v>
+        <v>247.2528577250976</v>
       </c>
       <c r="D14" t="n">
-        <v>235.5520799850208</v>
+        <v>240.331551845499</v>
       </c>
       <c r="E14" t="n">
-        <v>237.7236633300781</v>
+        <v>246.6578979492188</v>
       </c>
       <c r="F14" t="n">
-        <v>8387400</v>
+        <v>8276500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45938</v>
+        <v>45944</v>
       </c>
       <c r="B15" t="n">
-        <v>237.7236681390551</v>
+        <v>246.0232707436915</v>
       </c>
       <c r="C15" t="n">
-        <v>239.290381338098</v>
+        <v>246.1918391425529</v>
       </c>
       <c r="D15" t="n">
-        <v>233.6680556537968</v>
+        <v>237.5352670689401</v>
       </c>
       <c r="E15" t="n">
-        <v>238.4078521728516</v>
+        <v>237.75341796875</v>
       </c>
       <c r="F15" t="n">
-        <v>7120200</v>
+        <v>9123900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="B16" t="n">
-        <v>237.2576175505903</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C16" t="n">
-        <v>243.8913535488906</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D16" t="n">
-        <v>235.1554375781523</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E16" t="n">
-        <v>243.2666473388672</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F16" t="n">
-        <v>7929100</v>
+        <v>8389200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="B17" t="n">
-        <v>244.4466434616172</v>
+        <v>251.0605458824941</v>
       </c>
       <c r="C17" t="n">
-        <v>246.9553636418975</v>
+        <v>254.5806764744798</v>
       </c>
       <c r="D17" t="n">
-        <v>238.6954214370453</v>
+        <v>240.6290201908687</v>
       </c>
       <c r="E17" t="n">
-        <v>239.6473388671875</v>
+        <v>243.9310150146484</v>
       </c>
       <c r="F17" t="n">
-        <v>7988300</v>
+        <v>24869700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="B18" t="n">
-        <v>240.8471826425636</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="C18" t="n">
-        <v>247.2528577250976</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D18" t="n">
-        <v>240.331551845499</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E18" t="n">
-        <v>246.6578979492188</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="F18" t="n">
-        <v>8276500</v>
+        <v>10851200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="B19" t="n">
-        <v>246.0232549541512</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C19" t="n">
-        <v>246.1918233421939</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D19" t="n">
-        <v>237.5352518241517</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E19" t="n">
-        <v>237.7534027099609</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F19" t="n">
-        <v>9123900</v>
+        <v>9963900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="B20" t="n">
-        <v>238.8441526809671</v>
+        <v>252.3595144668565</v>
       </c>
       <c r="C20" t="n">
-        <v>239.2903800503502</v>
+        <v>264.883294034403</v>
       </c>
       <c r="D20" t="n">
-        <v>233.915951765761</v>
+        <v>251.863719742953</v>
       </c>
       <c r="E20" t="n">
-        <v>234.5902404785156</v>
+        <v>261.194580078125</v>
       </c>
       <c r="F20" t="n">
-        <v>8389200</v>
+        <v>13354700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="B21" t="n">
-        <v>251.0605301777264</v>
+        <v>259.9947875033736</v>
       </c>
       <c r="C21" t="n">
-        <v>254.5806605495149</v>
+        <v>260.1930872533099</v>
       </c>
       <c r="D21" t="n">
-        <v>240.6290051386317</v>
+        <v>254.3526406430638</v>
       </c>
       <c r="E21" t="n">
-        <v>243.9309997558594</v>
+        <v>254.4815521240234</v>
       </c>
       <c r="F21" t="n">
-        <v>24869700</v>
+        <v>9370000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="B22" t="n">
-        <v>244.4962363844956</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C22" t="n">
-        <v>248.670819810711</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D22" t="n">
-        <v>240.1233229489625</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E22" t="n">
-        <v>241.0355834960938</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F22" t="n">
-        <v>10851200</v>
+        <v>6110100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="B23" t="n">
-        <v>242.9394234832453</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C23" t="n">
-        <v>253.2519480605562</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D23" t="n">
-        <v>242.2453138708127</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E23" t="n">
-        <v>252.1413726806641</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F23" t="n">
-        <v>9963900</v>
+        <v>5490800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="B24" t="n">
-        <v>252.3595144668565</v>
+        <v>254.9178252470085</v>
       </c>
       <c r="C24" t="n">
-        <v>264.883294034403</v>
+        <v>255.9292659432784</v>
       </c>
       <c r="D24" t="n">
-        <v>251.863719742953</v>
+        <v>252.7760033429592</v>
       </c>
       <c r="E24" t="n">
-        <v>261.194580078125</v>
+        <v>253.3213806152344</v>
       </c>
       <c r="F24" t="n">
-        <v>13354700</v>
+        <v>4942400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45952</v>
+        <v>45958</v>
       </c>
       <c r="B25" t="n">
-        <v>259.9947875033736</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="C25" t="n">
-        <v>260.1930872533099</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D25" t="n">
-        <v>254.3526406430638</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E25" t="n">
-        <v>254.4815521240234</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="F25" t="n">
-        <v>9370000</v>
+        <v>6435600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45953</v>
+        <v>45959</v>
       </c>
       <c r="B26" t="n">
-        <v>255.4334634999039</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C26" t="n">
-        <v>256.3853809552256</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D26" t="n">
-        <v>251.982721115611</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E26" t="n">
-        <v>252.9049072265625</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F26" t="n">
-        <v>6110100</v>
+        <v>7904200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45954</v>
+        <v>45960</v>
       </c>
       <c r="B27" t="n">
-        <v>255.254980605377</v>
+        <v>248.3931555366784</v>
       </c>
       <c r="C27" t="n">
-        <v>256.3258839430272</v>
+        <v>257.0993096380665</v>
       </c>
       <c r="D27" t="n">
-        <v>251.8637312244832</v>
+        <v>247.8973608150483</v>
       </c>
       <c r="E27" t="n">
-        <v>252.6867523193359</v>
+        <v>254.4914245605469</v>
       </c>
       <c r="F27" t="n">
-        <v>5490800</v>
+        <v>7767800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="B28" t="n">
-        <v>254.9178098920577</v>
+        <v>252.6570304305034</v>
       </c>
       <c r="C28" t="n">
-        <v>255.9292505274036</v>
+        <v>259.617993585316</v>
       </c>
       <c r="D28" t="n">
-        <v>252.7759881170209</v>
+        <v>250.5052828369448</v>
       </c>
       <c r="E28" t="n">
-        <v>253.3213653564453</v>
+        <v>258.2198486328125</v>
       </c>
       <c r="F28" t="n">
-        <v>4942400</v>
+        <v>6878300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="B29" t="n">
-        <v>253.3213815169481</v>
+        <v>257.8132719821094</v>
       </c>
       <c r="C29" t="n">
-        <v>256.6630334318976</v>
+        <v>259.3601491931292</v>
       </c>
       <c r="D29" t="n">
-        <v>252.0025656103722</v>
+        <v>252.9544894469363</v>
       </c>
       <c r="E29" t="n">
-        <v>252.1215515136719</v>
+        <v>259.1419982910156</v>
       </c>
       <c r="F29" t="n">
-        <v>6435600</v>
+        <v>7054300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="B30" t="n">
-        <v>249.8805444255208</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C30" t="n">
-        <v>251.4373471434884</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D30" t="n">
-        <v>246.945432960583</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E30" t="n">
-        <v>249.3450927734375</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F30" t="n">
-        <v>7904200</v>
+        <v>6792200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45960</v>
+        <v>45966</v>
       </c>
       <c r="B31" t="n">
-        <v>248.3931704298276</v>
+        <v>252.5578398334985</v>
       </c>
       <c r="C31" t="n">
-        <v>257.099325053219</v>
+        <v>254.6699151564536</v>
       </c>
       <c r="D31" t="n">
-        <v>247.8973756784706</v>
+        <v>249.8904616870965</v>
       </c>
       <c r="E31" t="n">
-        <v>254.4914398193359</v>
+        <v>250.5548248291016</v>
       </c>
       <c r="F31" t="n">
-        <v>7767800</v>
+        <v>5241200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45961</v>
+        <v>45967</v>
       </c>
       <c r="B32" t="n">
-        <v>252.657000570364</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="C32" t="n">
-        <v>259.6179629024988</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="D32" t="n">
-        <v>250.5052532311086</v>
+        <v>232.5078921531912</v>
       </c>
       <c r="E32" t="n">
-        <v>258.2198181152344</v>
+        <v>237.2576141357422</v>
       </c>
       <c r="F32" t="n">
-        <v>6878300</v>
+        <v>11041800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="B33" t="n">
-        <v>257.8133023432115</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="C33" t="n">
-        <v>259.3601797363976</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D33" t="n">
-        <v>252.9545192358491</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E33" t="n">
-        <v>259.1420288085938</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="F33" t="n">
-        <v>7054300</v>
+        <v>5741500</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="B34" t="n">
-        <v>255.9788221233241</v>
+        <v>237.9814688826704</v>
       </c>
       <c r="C34" t="n">
-        <v>257.0795021986246</v>
+        <v>239.8754083705041</v>
       </c>
       <c r="D34" t="n">
-        <v>251.3282801006067</v>
+        <v>233.1028505862302</v>
       </c>
       <c r="E34" t="n">
-        <v>252.3000335693359</v>
+        <v>239.6770935058594</v>
       </c>
       <c r="F34" t="n">
-        <v>6792200</v>
+        <v>6486600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="B35" t="n">
-        <v>252.5578552142711</v>
+        <v>239.8655103639031</v>
       </c>
       <c r="C35" t="n">
-        <v>254.6699306658516</v>
+        <v>243.6335537470887</v>
       </c>
       <c r="D35" t="n">
-        <v>249.8904769054258</v>
+        <v>239.1317437673292</v>
       </c>
       <c r="E35" t="n">
-        <v>250.5548400878906</v>
+        <v>242.4436492919922</v>
       </c>
       <c r="F35" t="n">
-        <v>5241200</v>
+        <v>5762800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45967</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="n">
-        <v>248.4328324243326</v>
+        <v>243.6732228340941</v>
       </c>
       <c r="C36" t="n">
-        <v>248.4328324243326</v>
+        <v>246.3405860290093</v>
       </c>
       <c r="D36" t="n">
-        <v>232.5079071065105</v>
+        <v>241.6305356400256</v>
       </c>
       <c r="E36" t="n">
-        <v>237.2576293945312</v>
+        <v>243.9508666992188</v>
       </c>
       <c r="F36" t="n">
-        <v>11041800</v>
+        <v>4278200</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45968</v>
+        <v>45974</v>
       </c>
       <c r="B37" t="n">
-        <v>234.1638481621394</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C37" t="n">
-        <v>238.943316687993</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D37" t="n">
-        <v>233.8068753463891</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E37" t="n">
-        <v>237.8624877929688</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F37" t="n">
-        <v>5741500</v>
+        <v>5542100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="B38" t="n">
-        <v>237.9814840335094</v>
+        <v>236.3056776848755</v>
       </c>
       <c r="C38" t="n">
-        <v>239.8754236419186</v>
+        <v>243.1178923149379</v>
       </c>
       <c r="D38" t="n">
-        <v>233.1028654264771</v>
+        <v>235.4231636860313</v>
       </c>
       <c r="E38" t="n">
-        <v>239.6771087646484</v>
+        <v>241.6106872558594</v>
       </c>
       <c r="F38" t="n">
-        <v>6486600</v>
+        <v>5512900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="B39" t="n">
-        <v>239.8654952673756</v>
+        <v>240.0340571163644</v>
       </c>
       <c r="C39" t="n">
-        <v>243.63353841341</v>
+        <v>240.7876596253181</v>
       </c>
       <c r="D39" t="n">
-        <v>239.1317287169831</v>
+        <v>233.6085468088289</v>
       </c>
       <c r="E39" t="n">
-        <v>242.4436340332031</v>
+        <v>235.0364379882812</v>
       </c>
       <c r="F39" t="n">
-        <v>5762800</v>
+        <v>5280900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45973</v>
+        <v>45979</v>
       </c>
       <c r="B40" t="n">
-        <v>243.6732075926712</v>
+        <v>234.2531087461558</v>
       </c>
       <c r="C40" t="n">
-        <v>246.3405706207466</v>
+        <v>235.7900603656055</v>
       </c>
       <c r="D40" t="n">
-        <v>241.63052052637</v>
+        <v>228.3333182252886</v>
       </c>
       <c r="E40" t="n">
-        <v>243.9508514404297</v>
+        <v>231.5361480712891</v>
       </c>
       <c r="F40" t="n">
-        <v>4278200</v>
+        <v>8045100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="B41" t="n">
-        <v>243.1873207442872</v>
+        <v>230.0487686636922</v>
       </c>
       <c r="C41" t="n">
-        <v>243.8318478561575</v>
+        <v>230.3264125188844</v>
       </c>
       <c r="D41" t="n">
-        <v>237.8922365355373</v>
+        <v>223.1671349733107</v>
       </c>
       <c r="E41" t="n">
-        <v>238.4078521728516</v>
+        <v>225.9634246826172</v>
       </c>
       <c r="F41" t="n">
-        <v>5542100</v>
+        <v>9710700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="B42" t="n">
-        <v>236.3056926086296</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C42" t="n">
-        <v>243.1179076689137</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D42" t="n">
-        <v>235.4231785540507</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E42" t="n">
-        <v>241.6107025146484</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F42" t="n">
-        <v>5512900</v>
+        <v>7521100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B43" t="n">
-        <v>240.0340571163644</v>
+        <v>222.9687986720664</v>
       </c>
       <c r="C43" t="n">
-        <v>240.7876596253181</v>
+        <v>226.7566624070738</v>
       </c>
       <c r="D43" t="n">
-        <v>233.6085468088289</v>
+        <v>220.0931953922465</v>
       </c>
       <c r="E43" t="n">
-        <v>235.0364379882812</v>
+        <v>225.1998748779297</v>
       </c>
       <c r="F43" t="n">
-        <v>5280900</v>
+        <v>7479300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="B44" t="n">
-        <v>234.2530933083125</v>
+        <v>225.4279691980636</v>
       </c>
       <c r="C44" t="n">
-        <v>235.7900448264734</v>
+        <v>226.9153535529684</v>
       </c>
       <c r="D44" t="n">
-        <v>228.3333031775737</v>
+        <v>223.1473101611184</v>
       </c>
       <c r="E44" t="n">
-        <v>231.5361328125</v>
+        <v>224.912353515625</v>
       </c>
       <c r="F44" t="n">
-        <v>8045100</v>
+        <v>8563300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="n">
-        <v>230.0487531290293</v>
+        <v>224.8925123239678</v>
       </c>
       <c r="C45" t="n">
-        <v>230.3263969654728</v>
+        <v>232.656660293954</v>
       </c>
       <c r="D45" t="n">
-        <v>223.1671199033486</v>
+        <v>224.6148684611971</v>
       </c>
       <c r="E45" t="n">
-        <v>225.9634094238281</v>
+        <v>232.1509399414062</v>
       </c>
       <c r="F45" t="n">
-        <v>9710700</v>
+        <v>10233000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="B46" t="n">
-        <v>227.3218898732066</v>
+        <v>228.5712765635558</v>
       </c>
       <c r="C46" t="n">
-        <v>229.1265900019938</v>
+        <v>230.8618608815026</v>
       </c>
       <c r="D46" t="n">
-        <v>221.4219354522067</v>
+        <v>224.0992136322821</v>
       </c>
       <c r="E46" t="n">
-        <v>223.4745178222656</v>
+        <v>226.2311248779297</v>
       </c>
       <c r="F46" t="n">
-        <v>7521100</v>
+        <v>8506600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B47" t="n">
-        <v>222.9688137796853</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C47" t="n">
-        <v>226.7566777713456</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D47" t="n">
-        <v>220.0932103050241</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E47" t="n">
-        <v>225.1998901367188</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F47" t="n">
-        <v>7479300</v>
+        <v>3691500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="B48" t="n">
-        <v>225.4279691980636</v>
+        <v>226.7467795144244</v>
       </c>
       <c r="C48" t="n">
-        <v>226.9153535529684</v>
+        <v>232.2798509930075</v>
       </c>
       <c r="D48" t="n">
-        <v>223.1473101611184</v>
+        <v>226.6773761140884</v>
       </c>
       <c r="E48" t="n">
-        <v>224.912353515625</v>
+        <v>230.8717956542969</v>
       </c>
       <c r="F48" t="n">
-        <v>8563300</v>
+        <v>5634700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="B49" t="n">
-        <v>224.8924975422598</v>
+        <v>231.0602036533118</v>
       </c>
       <c r="C49" t="n">
-        <v>232.656645001925</v>
+        <v>234.6596634696697</v>
       </c>
       <c r="D49" t="n">
-        <v>224.614853697738</v>
+        <v>229.6719691901636</v>
       </c>
       <c r="E49" t="n">
-        <v>232.1509246826172</v>
+        <v>232.7359924316406</v>
       </c>
       <c r="F49" t="n">
-        <v>10233000</v>
+        <v>7626200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B50" t="n">
-        <v>228.5712919801828</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="C50" t="n">
-        <v>230.8618764526245</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D50" t="n">
-        <v>224.0992287472785</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E50" t="n">
-        <v>226.2311401367188</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="F50" t="n">
-        <v>8506600</v>
+        <v>13782000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="B51" t="n">
-        <v>227.0739873247604</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C51" t="n">
-        <v>230.6040433967966</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D51" t="n">
-        <v>226.7071040647147</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E51" t="n">
-        <v>228.6010284423828</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F51" t="n">
-        <v>3691500</v>
+        <v>20912100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="B52" t="n">
-        <v>226.7467645282661</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C52" t="n">
-        <v>232.2798356411572</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D52" t="n">
-        <v>226.6773611325171</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E52" t="n">
-        <v>230.8717803955078</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F52" t="n">
-        <v>5634700</v>
+        <v>15852400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="B53" t="n">
-        <v>231.0601885043919</v>
+        <v>259.6774396530913</v>
       </c>
       <c r="C53" t="n">
-        <v>234.6596480847597</v>
+        <v>262.0572481860146</v>
       </c>
       <c r="D53" t="n">
-        <v>229.67195413226</v>
+        <v>254.1840258460871</v>
       </c>
       <c r="E53" t="n">
-        <v>232.7359771728516</v>
+        <v>257.3471984863281</v>
       </c>
       <c r="F53" t="n">
-        <v>7626200</v>
+        <v>10805400</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="B54" t="n">
-        <v>233.3805083869321</v>
+        <v>257.8132661327708</v>
       </c>
       <c r="C54" t="n">
-        <v>237.2477014354837</v>
+        <v>260.0443424743044</v>
       </c>
       <c r="D54" t="n">
-        <v>231.1990144844042</v>
+        <v>256.8216766476447</v>
       </c>
       <c r="E54" t="n">
-        <v>236.7122497558594</v>
+        <v>258.8246765136719</v>
       </c>
       <c r="F54" t="n">
-        <v>13782000</v>
+        <v>8045900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="B55" t="n">
-        <v>241.6404418420451</v>
+        <v>258.556940201721</v>
       </c>
       <c r="C55" t="n">
-        <v>246.8760330652079</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D55" t="n">
-        <v>235.6016655641461</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E55" t="n">
-        <v>245.3787384033203</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="F55" t="n">
-        <v>20912100</v>
+        <v>8894700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="B56" t="n">
-        <v>248.7203919866921</v>
+        <v>261.283846098816</v>
       </c>
       <c r="C56" t="n">
-        <v>259.6774588065476</v>
+        <v>265.646834061187</v>
       </c>
       <c r="D56" t="n">
-        <v>247.4015761578514</v>
+        <v>258.5767957367673</v>
       </c>
       <c r="E56" t="n">
-        <v>258.3784790039062</v>
+        <v>260.1435241699219</v>
       </c>
       <c r="F56" t="n">
-        <v>15852400</v>
+        <v>7783800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="B57" t="n">
-        <v>259.6774704470017</v>
+        <v>261.3036648523665</v>
       </c>
       <c r="C57" t="n">
-        <v>262.0572792621351</v>
+        <v>262.2655079172122</v>
       </c>
       <c r="D57" t="n">
-        <v>254.1840559885597</v>
+        <v>258.7156306765648</v>
       </c>
       <c r="E57" t="n">
-        <v>257.3472290039062</v>
+        <v>260.0245361328125</v>
       </c>
       <c r="F57" t="n">
-        <v>10805400</v>
+        <v>6006600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="B58" t="n">
-        <v>257.8132661327708</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C58" t="n">
-        <v>260.0443424743044</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D58" t="n">
-        <v>256.8216766476447</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E58" t="n">
-        <v>258.8246765136719</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F58" t="n">
-        <v>8045900</v>
+        <v>10271800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="B59" t="n">
-        <v>258.556940201721</v>
+        <v>251.8637326884788</v>
       </c>
       <c r="C59" t="n">
-        <v>263.6933661135803</v>
+        <v>253.7080897614157</v>
       </c>
       <c r="D59" t="n">
-        <v>256.9703910840639</v>
+        <v>249.989629141015</v>
       </c>
       <c r="E59" t="n">
-        <v>261.9779357910156</v>
+        <v>252.7660827636719</v>
       </c>
       <c r="F59" t="n">
-        <v>8894700</v>
+        <v>6145300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="B60" t="n">
-        <v>261.283846098816</v>
+        <v>254.1741282350202</v>
       </c>
       <c r="C60" t="n">
-        <v>265.646834061187</v>
+        <v>259.7667076505979</v>
       </c>
       <c r="D60" t="n">
-        <v>258.5767957367673</v>
+        <v>254.0948143882558</v>
       </c>
       <c r="E60" t="n">
-        <v>260.1435241699219</v>
+        <v>255.9689331054688</v>
       </c>
       <c r="F60" t="n">
-        <v>7783800</v>
+        <v>6269000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,25 +2003,25 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="B61" t="n">
-        <v>261.3036648523665</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C61" t="n">
-        <v>262.2655079172122</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D61" t="n">
-        <v>258.7156306765648</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E61" t="n">
-        <v>260.0245361328125</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F61" t="n">
-        <v>6006600</v>
+        <v>5654200</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="B62" t="n">
-        <v>259.013086162544</v>
+        <v>258.9047600313309</v>
       </c>
       <c r="C62" t="n">
-        <v>260.074094195654</v>
+        <v>260.2555141825196</v>
       </c>
       <c r="D62" t="n">
-        <v>250.9613842226157</v>
+        <v>253.760043143314</v>
       </c>
       <c r="E62" t="n">
-        <v>252.4388580322266</v>
+        <v>258.1400146484375</v>
       </c>
       <c r="F62" t="n">
-        <v>10271800</v>
+        <v>20732100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="B63" t="n">
-        <v>251.8637174841621</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="C63" t="n">
-        <v>253.7080744457603</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D63" t="n">
-        <v>249.9896140498327</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E63" t="n">
-        <v>252.7660675048828</v>
+        <v>262.827880859375</v>
       </c>
       <c r="F63" t="n">
-        <v>6145300</v>
+        <v>5664200</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="B64" t="n">
-        <v>254.1741130832229</v>
+        <v>260.930890915143</v>
       </c>
       <c r="C64" t="n">
-        <v>259.7666921654164</v>
+        <v>262.4405288782817</v>
       </c>
       <c r="D64" t="n">
-        <v>254.0947992411865</v>
+        <v>258.7458606831942</v>
       </c>
       <c r="E64" t="n">
-        <v>255.9689178466797</v>
+        <v>261.6360473632812</v>
       </c>
       <c r="F64" t="n">
-        <v>6269000</v>
+        <v>4745100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,25 +2107,25 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="B65" t="n">
-        <v>256.6601807669533</v>
+        <v>261.4374386085776</v>
       </c>
       <c r="C65" t="n">
-        <v>258.2989382537239</v>
+        <v>264.486509153036</v>
       </c>
       <c r="D65" t="n">
-        <v>254.4155616010984</v>
+        <v>260.7620463111714</v>
       </c>
       <c r="E65" t="n">
-        <v>256.0940551757812</v>
+        <v>263.45361328125</v>
       </c>
       <c r="F65" t="n">
-        <v>5654200</v>
+        <v>2076600</v>
       </c>
       <c r="G65" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="B66" t="n">
-        <v>258.9047600313309</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="C66" t="n">
-        <v>260.2555141825196</v>
+        <v>266.0855294787636</v>
       </c>
       <c r="D66" t="n">
-        <v>253.760043143314</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="E66" t="n">
-        <v>258.1400146484375</v>
+        <v>264.2679748535156</v>
       </c>
       <c r="F66" t="n">
-        <v>20732100</v>
+        <v>2456400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="B67" t="n">
-        <v>258.8452092197766</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C67" t="n">
-        <v>262.8279113769531</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D67" t="n">
-        <v>256.6502674989528</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E67" t="n">
-        <v>262.8279113769531</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F67" t="n">
-        <v>5664200</v>
+        <v>4300100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="B68" t="n">
-        <v>260.9308604798152</v>
+        <v>264.8440512488132</v>
       </c>
       <c r="C68" t="n">
-        <v>262.4404982668678</v>
+        <v>266.4530142126886</v>
       </c>
       <c r="D68" t="n">
-        <v>258.7458305027313</v>
+        <v>263.5230915643202</v>
       </c>
       <c r="E68" t="n">
-        <v>261.6360168457031</v>
+        <v>264.1091003417969</v>
       </c>
       <c r="F68" t="n">
-        <v>4745100</v>
+        <v>3291800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B69" t="n">
-        <v>261.4374083245464</v>
+        <v>263.4833740671746</v>
       </c>
       <c r="C69" t="n">
-        <v>264.4864785158107</v>
+        <v>264.2878555133287</v>
       </c>
       <c r="D69" t="n">
-        <v>260.7620161053754</v>
+        <v>262.5895091614203</v>
       </c>
       <c r="E69" t="n">
-        <v>263.4535827636719</v>
+        <v>263.10595703125</v>
       </c>
       <c r="F69" t="n">
-        <v>2076600</v>
+        <v>3367900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="B70" t="n">
-        <v>262.9967232703997</v>
+        <v>263.1953602739627</v>
       </c>
       <c r="C70" t="n">
-        <v>266.0855602062323</v>
+        <v>263.5727773382559</v>
       </c>
       <c r="D70" t="n">
-        <v>262.9967232703997</v>
+        <v>250.7606167452008</v>
       </c>
       <c r="E70" t="n">
-        <v>264.2680053710938</v>
+        <v>251.8928527832031</v>
       </c>
       <c r="F70" t="n">
-        <v>2456400</v>
+        <v>9680600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="B71" t="n">
-        <v>262.9073239460033</v>
+        <v>251.8928562905814</v>
       </c>
       <c r="C71" t="n">
-        <v>267.2773540092613</v>
+        <v>257.8222021169872</v>
       </c>
       <c r="D71" t="n">
-        <v>262.9073239460033</v>
+        <v>250.5917797464572</v>
       </c>
       <c r="E71" t="n">
-        <v>264.4169921875</v>
+        <v>254.514892578125</v>
       </c>
       <c r="F71" t="n">
-        <v>4300100</v>
+        <v>6421500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="B72" t="n">
-        <v>264.8440818513142</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C72" t="n">
-        <v>266.453045001104</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D72" t="n">
-        <v>263.5231220141856</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E72" t="n">
-        <v>264.109130859375</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F72" t="n">
-        <v>3291800</v>
+        <v>6103300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B73" t="n">
-        <v>263.4834046285292</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="C73" t="n">
-        <v>264.2878861679949</v>
+        <v>266.0060858079951</v>
       </c>
       <c r="D73" t="n">
-        <v>262.5895396190958</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="E73" t="n">
-        <v>263.1059875488281</v>
+        <v>264.3077392578125</v>
       </c>
       <c r="F73" t="n">
-        <v>3367900</v>
+        <v>5976200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B74" t="n">
-        <v>263.1953762174182</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C74" t="n">
-        <v>263.572793304574</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D74" t="n">
-        <v>250.760631935403</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E74" t="n">
-        <v>251.8928680419922</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F74" t="n">
-        <v>9680600</v>
+        <v>5243500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B75" t="n">
-        <v>251.8928562905814</v>
+        <v>258.2294193019395</v>
       </c>
       <c r="C75" t="n">
-        <v>257.8222021169872</v>
+        <v>259.2524038660146</v>
       </c>
       <c r="D75" t="n">
-        <v>250.5917797464572</v>
+        <v>254.7631956419699</v>
       </c>
       <c r="E75" t="n">
-        <v>254.514892578125</v>
+        <v>258.1698303222656</v>
       </c>
       <c r="F75" t="n">
-        <v>6421500</v>
+        <v>5174400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46028</v>
+        <v>46034</v>
       </c>
       <c r="B76" t="n">
-        <v>253.4620895509313</v>
+        <v>257.2362444131007</v>
       </c>
       <c r="C76" t="n">
-        <v>261.7552171079225</v>
+        <v>259.778808728465</v>
       </c>
       <c r="D76" t="n">
-        <v>253.2634545783159</v>
+        <v>254.0282445272995</v>
       </c>
       <c r="E76" t="n">
-        <v>261.1096496582031</v>
+        <v>257.6335144042969</v>
       </c>
       <c r="F76" t="n">
-        <v>6103300</v>
+        <v>4927700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="n">
-        <v>261.7055558804709</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C77" t="n">
-        <v>266.0060550943219</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D77" t="n">
-        <v>261.7055558804709</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E77" t="n">
-        <v>264.3077087402344</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F77" t="n">
-        <v>5976200</v>
+        <v>13661000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="n">
-        <v>262.5994389217771</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C78" t="n">
-        <v>263.394009134812</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D78" t="n">
-        <v>258.6366203853271</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E78" t="n">
-        <v>258.7557983398438</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F78" t="n">
-        <v>5243500</v>
+        <v>10149300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="B79" t="n">
-        <v>258.2294193019395</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C79" t="n">
-        <v>259.2524038660146</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D79" t="n">
-        <v>254.7631956419699</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E79" t="n">
-        <v>258.1698303222656</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F79" t="n">
-        <v>5174400</v>
+        <v>11489600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="B80" t="n">
-        <v>257.2362139425806</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C80" t="n">
-        <v>259.7787779567694</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D80" t="n">
-        <v>254.028214436778</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E80" t="n">
-        <v>257.6334838867188</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F80" t="n">
-        <v>4927700</v>
+        <v>13902600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B81" t="n">
-        <v>255.9053572301452</v>
+        <v>222.0176902636222</v>
       </c>
       <c r="C81" t="n">
-        <v>259.1332249596227</v>
+        <v>226.3877354418118</v>
       </c>
       <c r="D81" t="n">
-        <v>238.7231659776434</v>
+        <v>217.8661632569629</v>
       </c>
       <c r="E81" t="n">
-        <v>239.4183959960938</v>
+        <v>218.5713348388672</v>
       </c>
       <c r="F81" t="n">
-        <v>13661000</v>
+        <v>13050800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B82" t="n">
-        <v>237.5511941796288</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="C82" t="n">
-        <v>240.5903685304685</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D82" t="n">
-        <v>234.849731125901</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E82" t="n">
-        <v>237.9385528564453</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="F82" t="n">
-        <v>10149300</v>
+        <v>12616600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B83" t="n">
-        <v>235.4059054123066</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C83" t="n">
-        <v>237.2135033883542</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D83" t="n">
-        <v>230.0923326840245</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E83" t="n">
-        <v>231.9396667480469</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F83" t="n">
-        <v>11489600</v>
+        <v>9483000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="n">
-        <v>231.3636110626874</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="C84" t="n">
-        <v>231.3636110626874</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D84" t="n">
-        <v>224.8979495180149</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E84" t="n">
-        <v>225.5633850097656</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="F84" t="n">
-        <v>13902600</v>
+        <v>9408000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B85" t="n">
-        <v>222.0177057630064</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C85" t="n">
-        <v>226.3877512462753</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D85" t="n">
-        <v>217.8661784665229</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E85" t="n">
-        <v>218.5713500976562</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F85" t="n">
-        <v>13050800</v>
+        <v>7239600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="n">
-        <v>218.6507753226022</v>
+        <v>230.3604906379282</v>
       </c>
       <c r="C86" t="n">
-        <v>221.8687164208105</v>
+        <v>234.1346156625655</v>
       </c>
       <c r="D86" t="n">
-        <v>217.4688919371066</v>
+        <v>224.7291051659704</v>
       </c>
       <c r="E86" t="n">
-        <v>220.071044921875</v>
+        <v>226.9737091064453</v>
       </c>
       <c r="F86" t="n">
-        <v>12616600</v>
+        <v>9838400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B87" t="n">
-        <v>220.7265600038705</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="C87" t="n">
-        <v>227.162427221411</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D87" t="n">
-        <v>219.6042504088122</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E87" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="F87" t="n">
-        <v>9483000</v>
+        <v>8465900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="B88" t="n">
-        <v>225.2356232374019</v>
+        <v>215.1944899838427</v>
       </c>
       <c r="C88" t="n">
-        <v>229.277913744438</v>
+        <v>215.8003365308671</v>
       </c>
       <c r="D88" t="n">
-        <v>225.1065036899912</v>
+        <v>207.3582209619344</v>
       </c>
       <c r="E88" t="n">
-        <v>226.4969787597656</v>
+        <v>212.6221313476562</v>
       </c>
       <c r="F88" t="n">
-        <v>9408000</v>
+        <v>18555600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="n">
-        <v>227.8675783015932</v>
+        <v>212.7015749295142</v>
       </c>
       <c r="C89" t="n">
-        <v>229.3772313706373</v>
+        <v>214.0821084291109</v>
       </c>
       <c r="D89" t="n">
-        <v>226.0401123076792</v>
+        <v>209.5928853669118</v>
       </c>
       <c r="E89" t="n">
-        <v>227.8377838134766</v>
+        <v>210.8442993164062</v>
       </c>
       <c r="F89" t="n">
-        <v>7239600</v>
+        <v>11090400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B90" t="n">
-        <v>230.3604906379282</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C90" t="n">
-        <v>234.1346156625655</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D90" t="n">
-        <v>224.7291051659704</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E90" t="n">
-        <v>226.9737091064453</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F90" t="n">
-        <v>9838400</v>
+        <v>7950900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="B91" t="n">
-        <v>227.8278778686248</v>
+        <v>203.6039568110546</v>
       </c>
       <c r="C91" t="n">
-        <v>230.2810586434755</v>
+        <v>204.16014080488</v>
       </c>
       <c r="D91" t="n">
-        <v>226.1195896734686</v>
+        <v>191.7949279222085</v>
       </c>
       <c r="E91" t="n">
-        <v>226.4076232910156</v>
+        <v>195.0426635742188</v>
       </c>
       <c r="F91" t="n">
-        <v>8465900</v>
+        <v>20194200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="B92" t="n">
-        <v>215.1944745404488</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C92" t="n">
-        <v>215.8003210439947</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D92" t="n">
-        <v>207.358206080909</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E92" t="n">
-        <v>212.6221160888672</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F92" t="n">
-        <v>18555600</v>
+        <v>23010000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="B93" t="n">
-        <v>212.7015903227142</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C93" t="n">
-        <v>214.08212392222</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D93" t="n">
-        <v>209.5929005351361</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E93" t="n">
-        <v>210.8443145751953</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F93" t="n">
-        <v>11090400</v>
+        <v>21956300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="B94" t="n">
-        <v>212.8902908724165</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C94" t="n">
-        <v>215.4129869027477</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D94" t="n">
-        <v>208.3712731650351</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E94" t="n">
-        <v>209.3743896484375</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F94" t="n">
-        <v>7950900</v>
+        <v>13652600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="B95" t="n">
-        <v>203.60397273962</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C95" t="n">
-        <v>204.1601567769575</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D95" t="n">
-        <v>191.7949429269172</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E95" t="n">
-        <v>195.0426788330078</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F95" t="n">
-        <v>20194200</v>
+        <v>12112000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B96" t="n">
-        <v>191.993558028148</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C96" t="n">
-        <v>199.3034370934686</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0046234920971</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E96" t="n">
-        <v>198.0818176269531</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F96" t="n">
-        <v>23010000</v>
+        <v>13393000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B97" t="n">
-        <v>192.668943558262</v>
+        <v>191.8346508751069</v>
       </c>
       <c r="C97" t="n">
-        <v>198.2010042649258</v>
+        <v>192.3511139411869</v>
       </c>
       <c r="D97" t="n">
-        <v>187.5043431662378</v>
+        <v>180.5718794169307</v>
       </c>
       <c r="E97" t="n">
-        <v>188.6763153076172</v>
+        <v>183.7401580810547</v>
       </c>
       <c r="F97" t="n">
-        <v>21956300</v>
+        <v>16350200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="B98" t="n">
-        <v>190.3250127759971</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C98" t="n">
-        <v>193.2747884158856</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D98" t="n">
-        <v>185.8457159832669</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E98" t="n">
-        <v>190.0469207763672</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F98" t="n">
-        <v>13652600</v>
+        <v>16849100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B99" t="n">
-        <v>188.0108792533576</v>
+        <v>185.1703620229303</v>
       </c>
       <c r="C99" t="n">
-        <v>193.8706944788449</v>
+        <v>192.1326190686923</v>
       </c>
       <c r="D99" t="n">
-        <v>184.465183505092</v>
+        <v>183.0449358454951</v>
       </c>
       <c r="E99" t="n">
-        <v>192.7086639404297</v>
+        <v>188.4280242919922</v>
       </c>
       <c r="F99" t="n">
-        <v>12112000</v>
+        <v>14822900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="B100" t="n">
-        <v>190.5931665112882</v>
+        <v>189.6694900334161</v>
       </c>
       <c r="C100" t="n">
-        <v>197.7441470694129</v>
+        <v>191.6856644627849</v>
       </c>
       <c r="D100" t="n">
-        <v>189.4510040038842</v>
+        <v>181.9226052262247</v>
       </c>
       <c r="E100" t="n">
-        <v>192.1326141357422</v>
+        <v>183.0349731445312</v>
       </c>
       <c r="F100" t="n">
-        <v>13393000</v>
+        <v>13692900</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B101" t="n">
-        <v>191.8346349441069</v>
+        <v>182.6277776277465</v>
       </c>
       <c r="C101" t="n">
-        <v>192.3510979672969</v>
+        <v>186.8587614695496</v>
       </c>
       <c r="D101" t="n">
-        <v>180.5718644212529</v>
+        <v>180.6215296329567</v>
       </c>
       <c r="E101" t="n">
-        <v>183.7401428222656</v>
+        <v>186.5111389160156</v>
       </c>
       <c r="F101" t="n">
-        <v>16350200</v>
+        <v>9852900</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B102" t="n">
-        <v>184.6936257308121</v>
+        <v>185.3292593497056</v>
       </c>
       <c r="C102" t="n">
-        <v>187.0375548215625</v>
+        <v>185.6768667554436</v>
       </c>
       <c r="D102" t="n">
-        <v>179.012577513483</v>
+        <v>181.9821987572526</v>
       </c>
       <c r="E102" t="n">
-        <v>184.1672210693359</v>
+        <v>184.0281677246094</v>
       </c>
       <c r="F102" t="n">
-        <v>16849100</v>
+        <v>9565100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B103" t="n">
-        <v>185.1703620229303</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C103" t="n">
-        <v>192.1326190686923</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D103" t="n">
-        <v>183.0449358454951</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E103" t="n">
-        <v>188.4280242919922</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F103" t="n">
-        <v>14822900</v>
+        <v>10816200</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="B104" t="n">
-        <v>189.6695058452945</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C104" t="n">
-        <v>191.6856804427425</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D104" t="n">
-        <v>181.9226203922807</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E104" t="n">
-        <v>183.0349884033203</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F104" t="n">
-        <v>13692900</v>
+        <v>15498600</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
       <c r="B105" t="n">
-        <v>182.6277925688313</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C105" t="n">
-        <v>186.8587767567783</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D105" t="n">
-        <v>180.6215444099069</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E105" t="n">
-        <v>186.5111541748047</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F105" t="n">
-        <v>9852900</v>
+        <v>15564700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="B106" t="n">
-        <v>185.3292747163753</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C106" t="n">
-        <v>185.6768821509354</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D106" t="n">
-        <v>181.9822138463991</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E106" t="n">
-        <v>184.0281829833984</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F106" t="n">
-        <v>9565100</v>
+        <v>21875100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46073</v>
+        <v>46079</v>
       </c>
       <c r="B107" t="n">
-        <v>184.0579771467211</v>
+        <v>195.420066371549</v>
       </c>
       <c r="C107" t="n">
-        <v>190.4243134969296</v>
+        <v>199.6709185207204</v>
       </c>
       <c r="D107" t="n">
-        <v>182.4787935369736</v>
+        <v>190.0270517409182</v>
       </c>
       <c r="E107" t="n">
-        <v>183.8990631103516</v>
+        <v>198.1116180419922</v>
       </c>
       <c r="F107" t="n">
-        <v>10816200</v>
+        <v>26680500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="B108" t="n">
-        <v>180.0355685556146</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C108" t="n">
-        <v>181.2273936107796</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D108" t="n">
-        <v>173.3811981056387</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E108" t="n">
-        <v>176.9467468261719</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F108" t="n">
-        <v>15498600</v>
+        <v>16346500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="B109" t="n">
-        <v>176.4302852446972</v>
+        <v>191.1890691316076</v>
       </c>
       <c r="C109" t="n">
-        <v>187.3851706171715</v>
+        <v>194.6056450515189</v>
       </c>
       <c r="D109" t="n">
-        <v>175.0795461293982</v>
+        <v>189.38145611275</v>
       </c>
       <c r="E109" t="n">
-        <v>184.1573028564453</v>
+        <v>191.6360015869141</v>
       </c>
       <c r="F109" t="n">
-        <v>15564700</v>
+        <v>9932700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="B110" t="n">
-        <v>181.7537853733346</v>
+        <v>189.4510095395255</v>
       </c>
       <c r="C110" t="n">
-        <v>191.2884162417558</v>
+        <v>197.3170732284266</v>
       </c>
       <c r="D110" t="n">
-        <v>181.0188192554131</v>
+        <v>188.2889789535958</v>
       </c>
       <c r="E110" t="n">
-        <v>190.4441986083984</v>
+        <v>194.7149200439453</v>
       </c>
       <c r="F110" t="n">
-        <v>21875100</v>
+        <v>13208900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="B111" t="n">
-        <v>195.420066371549</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C111" t="n">
-        <v>199.6709185207204</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D111" t="n">
-        <v>190.0270517409182</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E111" t="n">
-        <v>198.1116180419922</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F111" t="n">
-        <v>26680500</v>
+        <v>11583700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="B112" t="n">
-        <v>190.6031086414411</v>
+        <v>193.0364294600736</v>
       </c>
       <c r="C112" t="n">
-        <v>194.5857953386064</v>
+        <v>203.0279194939781</v>
       </c>
       <c r="D112" t="n">
-        <v>188.6266549601705</v>
+        <v>192.9172514970062</v>
       </c>
       <c r="E112" t="n">
-        <v>193.4634857177734</v>
+        <v>200.0185546875</v>
       </c>
       <c r="F112" t="n">
-        <v>16346500</v>
+        <v>15860900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="B113" t="n">
-        <v>191.1890843548102</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C113" t="n">
-        <v>194.6056605467623</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D113" t="n">
-        <v>189.3814711920236</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E113" t="n">
-        <v>191.6360168457031</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F113" t="n">
-        <v>9932700</v>
+        <v>9657400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="B114" t="n">
-        <v>189.4509946932415</v>
+        <v>197.2078193049057</v>
       </c>
       <c r="C114" t="n">
-        <v>197.3170577657204</v>
+        <v>202.2830212056148</v>
       </c>
       <c r="D114" t="n">
-        <v>188.2889641983741</v>
+        <v>194.5361355724457</v>
       </c>
       <c r="E114" t="n">
-        <v>194.7149047851562</v>
+        <v>197.4362487792969</v>
       </c>
       <c r="F114" t="n">
-        <v>13208900</v>
+        <v>10754800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="B115" t="n">
-        <v>193.7713848635987</v>
+        <v>195.9166595935153</v>
       </c>
       <c r="C115" t="n">
-        <v>195.1320503828654</v>
+        <v>198.2109412897675</v>
       </c>
       <c r="D115" t="n">
-        <v>190.7918147128814</v>
+        <v>189.3020255204881</v>
       </c>
       <c r="E115" t="n">
-        <v>191.76513671875</v>
+        <v>193.5826721191406</v>
       </c>
       <c r="F115" t="n">
-        <v>11583700</v>
+        <v>14467400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B116" t="n">
-        <v>193.036414733929</v>
+        <v>195.0625292691439</v>
       </c>
       <c r="C116" t="n">
-        <v>203.027904005614</v>
+        <v>198.1910871721164</v>
       </c>
       <c r="D116" t="n">
-        <v>192.9172367799533</v>
+        <v>189.987327259986</v>
       </c>
       <c r="E116" t="n">
-        <v>200.0185394287109</v>
+        <v>192.8079986572266</v>
       </c>
       <c r="F116" t="n">
-        <v>15860900</v>
+        <v>9580000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="B117" t="n">
-        <v>199.4226244314719</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C117" t="n">
-        <v>201.5778601866405</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D117" t="n">
-        <v>196.0259162627038</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E117" t="n">
-        <v>200.733642578125</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F117" t="n">
-        <v>9657400</v>
+        <v>26309700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="B118" t="n">
-        <v>197.2078040637707</v>
+        <v>198.3698512203022</v>
       </c>
       <c r="C118" t="n">
-        <v>202.2830055722447</v>
+        <v>199.6312068702612</v>
       </c>
       <c r="D118" t="n">
-        <v>194.5361205377908</v>
+        <v>190.4441985938934</v>
       </c>
       <c r="E118" t="n">
-        <v>197.4362335205078</v>
+        <v>191.516845703125</v>
       </c>
       <c r="F118" t="n">
-        <v>10754800</v>
+        <v>14834700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="B119" t="n">
-        <v>195.9166750362765</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C119" t="n">
-        <v>198.2109569133711</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D119" t="n">
-        <v>189.3020404418633</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E119" t="n">
-        <v>193.5826873779297</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F119" t="n">
-        <v>14467400</v>
+        <v>13419600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="B120" t="n">
-        <v>195.0625138319317</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C120" t="n">
-        <v>198.1910714873107</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D120" t="n">
-        <v>189.9873122244243</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E120" t="n">
-        <v>192.8079833984375</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F120" t="n">
-        <v>9580000</v>
+        <v>11559300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="B121" t="n">
-        <v>192.8079750209554</v>
+        <v>192.0829395046699</v>
       </c>
       <c r="C121" t="n">
-        <v>203.4648992272838</v>
+        <v>194.8142119985075</v>
       </c>
       <c r="D121" t="n">
-        <v>191.8346379323055</v>
+        <v>191.3281205621285</v>
       </c>
       <c r="E121" t="n">
-        <v>197.9228973388672</v>
+        <v>193.0165405273438</v>
       </c>
       <c r="F121" t="n">
-        <v>26309700</v>
+        <v>10525100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B122" t="n">
-        <v>198.3698354155112</v>
+        <v>194.2580448499211</v>
       </c>
       <c r="C122" t="n">
-        <v>199.6311909649738</v>
+        <v>199.0352867281362</v>
       </c>
       <c r="D122" t="n">
-        <v>190.4441834205658</v>
+        <v>191.9836462262046</v>
       </c>
       <c r="E122" t="n">
-        <v>191.5168304443359</v>
+        <v>193.6621398925781</v>
       </c>
       <c r="F122" t="n">
-        <v>14834700</v>
+        <v>9254300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="B123" t="n">
-        <v>193.821025021851</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C123" t="n">
-        <v>197.2773371794379</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D123" t="n">
-        <v>193.821025021851</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E123" t="n">
-        <v>196.9893035888672</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F123" t="n">
-        <v>13419600</v>
+        <v>20201100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="B124" t="n">
-        <v>196.870136689126</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C124" t="n">
-        <v>201.0018110133274</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D124" t="n">
-        <v>193.1258058856387</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E124" t="n">
-        <v>193.9799499511719</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F124" t="n">
-        <v>11559300</v>
+        <v>13976200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="B125" t="n">
-        <v>192.0829546896537</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C125" t="n">
-        <v>194.8142273994103</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D125" t="n">
-        <v>191.3281356874407</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E125" t="n">
-        <v>193.0165557861328</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F125" t="n">
-        <v>10525100</v>
+        <v>18631400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="B126" t="n">
-        <v>194.2580448499211</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="C126" t="n">
-        <v>199.0352867281362</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D126" t="n">
-        <v>191.9836462262046</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E126" t="n">
-        <v>193.6621398925781</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="F126" t="n">
-        <v>9254300</v>
+        <v>12565200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B127" t="n">
-        <v>191.8942484911283</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C127" t="n">
-        <v>194.3374874288811</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D127" t="n">
-        <v>188.7061018910339</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E127" t="n">
-        <v>194.0494689941406</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F127" t="n">
-        <v>20201100</v>
+        <v>10330700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="B128" t="n">
-        <v>195.7478267440036</v>
+        <v>182.7469769199218</v>
       </c>
       <c r="C128" t="n">
-        <v>196.7012958768407</v>
+        <v>182.8562284362321</v>
       </c>
       <c r="D128" t="n">
-        <v>190.6924929381777</v>
+        <v>177.6022595179307</v>
       </c>
       <c r="E128" t="n">
-        <v>193.850830078125</v>
+        <v>178.0889129638672</v>
       </c>
       <c r="F128" t="n">
-        <v>13976200</v>
+        <v>9902000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="B129" t="n">
-        <v>190.8315397252546</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C129" t="n">
-        <v>190.8315397252546</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D129" t="n">
-        <v>181.0486114593648</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E129" t="n">
-        <v>181.7736511230469</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F129" t="n">
-        <v>18631400</v>
+        <v>11617700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B130" t="n">
-        <v>184.4353765448059</v>
+        <v>183.6408226716892</v>
       </c>
       <c r="C130" t="n">
-        <v>186.1138700384234</v>
+        <v>187.2163126895138</v>
       </c>
       <c r="D130" t="n">
-        <v>178.625224245603</v>
+        <v>181.0684642406058</v>
       </c>
       <c r="E130" t="n">
-        <v>180.7208557128906</v>
+        <v>185.3987731933594</v>
       </c>
       <c r="F130" t="n">
-        <v>12565200</v>
+        <v>11041400</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>179.9461742219026</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C131" t="n">
-        <v>186.1933484091056</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D131" t="n">
-        <v>178.3074166263376</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E131" t="n">
-        <v>184.3758087158203</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F131" t="n">
-        <v>10330700</v>
+        <v>11677700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B132" t="n">
-        <v>182.7469612620264</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C132" t="n">
-        <v>182.8562127689759</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D132" t="n">
-        <v>177.6022443008385</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E132" t="n">
-        <v>178.0888977050781</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F132" t="n">
-        <v>9902000</v>
+        <v>11635500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="B133" t="n">
-        <v>178.873523844959</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C133" t="n">
-        <v>185.1206822343098</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D133" t="n">
-        <v>178.3570608051074</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E133" t="n">
         <v>183.7699432373047</v>
       </c>
       <c r="F133" t="n">
-        <v>11617700</v>
+        <v>14391000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="B134" t="n">
-        <v>183.6408377857945</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C134" t="n">
-        <v>187.216328097891</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D134" t="n">
-        <v>181.0684791429995</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E134" t="n">
-        <v>185.3987884521484</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F134" t="n">
-        <v>11041400</v>
+        <v>12344600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B135" t="n">
-        <v>185.5775567084869</v>
+        <v>185.2299504420264</v>
       </c>
       <c r="C135" t="n">
-        <v>187.6930410934417</v>
+        <v>185.4981160077481</v>
       </c>
       <c r="D135" t="n">
-        <v>181.7636956083204</v>
+        <v>174.5829515420302</v>
       </c>
       <c r="E135" t="n">
-        <v>184.9717102050781</v>
+        <v>175.1689300537109</v>
       </c>
       <c r="F135" t="n">
-        <v>11677700</v>
+        <v>13472100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,25 +3953,25 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B136" t="n">
-        <v>184.0381169897925</v>
+        <v>172.4208565486944</v>
       </c>
       <c r="C136" t="n">
-        <v>186.3025890630262</v>
+        <v>173.5360065139178</v>
       </c>
       <c r="D136" t="n">
-        <v>180.3434488377003</v>
+        <v>166.3970260969056</v>
       </c>
       <c r="E136" t="n">
-        <v>185.9053039550781</v>
+        <v>170.1109008789062</v>
       </c>
       <c r="F136" t="n">
-        <v>11635500</v>
+        <v>20855400</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="B137" t="n">
-        <v>186.2231237330043</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C137" t="n">
-        <v>186.8587647224845</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D137" t="n">
-        <v>182.3496888213084</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E137" t="n">
-        <v>183.7699432373047</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F137" t="n">
-        <v>14391000</v>
+        <v>18109300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B138" t="n">
-        <v>183.690504131923</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C138" t="n">
-        <v>185.3094088283374</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D138" t="n">
-        <v>180.7804644422889</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E138" t="n">
-        <v>181.7140655517578</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F138" t="n">
-        <v>12344600</v>
+        <v>12390800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B139" t="n">
-        <v>185.229934306832</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C139" t="n">
-        <v>185.498099849194</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D139" t="n">
-        <v>174.5829363342851</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E139" t="n">
-        <v>175.1689147949219</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F139" t="n">
-        <v>13472100</v>
+        <v>13123600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,25 +4057,25 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B140" t="n">
-        <v>172.4208720146844</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C140" t="n">
-        <v>173.5360220799356</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D140" t="n">
-        <v>166.3970410225636</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E140" t="n">
-        <v>170.1109161376953</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F140" t="n">
-        <v>20855400</v>
+        <v>14340300</v>
       </c>
       <c r="G140" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B141" t="n">
-        <v>170.5191174814139</v>
+        <v>183.2040230257668</v>
       </c>
       <c r="C141" t="n">
-        <v>170.5191174814139</v>
+        <v>183.7516467853238</v>
       </c>
       <c r="D141" t="n">
-        <v>162.8126107290287</v>
+        <v>177.7975202909648</v>
       </c>
       <c r="E141" t="n">
-        <v>164.2463836669922</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F141" t="n">
-        <v>18109300</v>
+        <v>11866700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="B142" t="n">
-        <v>166.3273444705899</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C142" t="n">
-        <v>172.6498652447362</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D142" t="n">
-        <v>165.0528829680655</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E142" t="n">
-        <v>172.0723876953125</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F142" t="n">
-        <v>12390800</v>
+        <v>17225700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="n">
-        <v>174.4520463656914</v>
+        <v>181.7104926433502</v>
       </c>
       <c r="C143" t="n">
-        <v>176.7321331165696</v>
+        <v>188.1823732032504</v>
       </c>
       <c r="D143" t="n">
-        <v>169.7624151908458</v>
+        <v>181.33213168739</v>
       </c>
       <c r="E143" t="n">
-        <v>170.5689086914062</v>
+        <v>185.4641876220703</v>
       </c>
       <c r="F143" t="n">
-        <v>13123600</v>
+        <v>14382300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B144" t="n">
-        <v>173.4663277892384</v>
+        <v>185.7927793430547</v>
       </c>
       <c r="C144" t="n">
-        <v>178.842961383224</v>
+        <v>192.7226620565929</v>
       </c>
       <c r="D144" t="n">
-        <v>172.1321282578628</v>
+        <v>183.3035942778625</v>
       </c>
       <c r="E144" t="n">
-        <v>176.8317108154297</v>
+        <v>186.3005676269531</v>
       </c>
       <c r="F144" t="n">
-        <v>14340300</v>
+        <v>12073700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B145" t="n">
-        <v>183.2040075329009</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C145" t="n">
-        <v>183.7516312461474</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D145" t="n">
-        <v>177.7975052553062</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E145" t="n">
-        <v>180.43603515625</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F145" t="n">
-        <v>11866700</v>
+        <v>14565900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B146" t="n">
-        <v>184.6278268926657</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C146" t="n">
-        <v>187.1667986912511</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D146" t="n">
-        <v>180.2468672661974</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E146" t="n">
-        <v>181.3520660400391</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F146" t="n">
-        <v>17225700</v>
+        <v>22719900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="B147" t="n">
-        <v>181.7105075933097</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C147" t="n">
-        <v>188.1823886856741</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D147" t="n">
-        <v>181.3321466062204</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E147" t="n">
-        <v>185.4642028808594</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F147" t="n">
-        <v>14382300</v>
+        <v>10817600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B148" t="n">
-        <v>185.7927641258556</v>
+        <v>177.4888357619529</v>
       </c>
       <c r="C148" t="n">
-        <v>192.7226462718077</v>
+        <v>183.4927485632761</v>
       </c>
       <c r="D148" t="n">
-        <v>183.303579264538</v>
+        <v>176.7420802872333</v>
       </c>
       <c r="E148" t="n">
-        <v>186.3005523681641</v>
+        <v>179.4005279541016</v>
       </c>
       <c r="F148" t="n">
-        <v>12073700</v>
+        <v>11907000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B149" t="n">
-        <v>187.3858431404722</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C149" t="n">
-        <v>190.3230783921826</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D149" t="n">
-        <v>186.2209063874661</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E149" t="n">
-        <v>188.9789276123047</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F149" t="n">
-        <v>14565900</v>
+        <v>8711700</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="n">
-        <v>176.7918740224492</v>
+        <v>178.4247846039299</v>
       </c>
       <c r="C150" t="n">
-        <v>178.0962045390804</v>
+        <v>180.993625445577</v>
       </c>
       <c r="D150" t="n">
-        <v>169.9117629967484</v>
+        <v>176.5827967489585</v>
       </c>
       <c r="E150" t="n">
-        <v>172.5503082275391</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F150" t="n">
-        <v>22719900</v>
+        <v>6882800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B151" t="n">
-        <v>174.8602617765654</v>
+        <v>177.5286895189733</v>
       </c>
       <c r="C151" t="n">
-        <v>177.6780209996891</v>
+        <v>177.9170017981234</v>
       </c>
       <c r="D151" t="n">
-        <v>173.6455382897692</v>
+        <v>172.2516139153796</v>
       </c>
       <c r="E151" t="n">
-        <v>177.3892822265625</v>
+        <v>175.7663421630859</v>
       </c>
       <c r="F151" t="n">
-        <v>10817600</v>
+        <v>14408300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="n">
-        <v>177.4888508581443</v>
+        <v>181.4018421076459</v>
       </c>
       <c r="C152" t="n">
-        <v>183.4927641701262</v>
+        <v>185.2351777570901</v>
       </c>
       <c r="D152" t="n">
-        <v>176.7420953199099</v>
+        <v>177.9767212373249</v>
       </c>
       <c r="E152" t="n">
-        <v>179.4005432128906</v>
+        <v>183.0247955322266</v>
       </c>
       <c r="F152" t="n">
-        <v>11907000</v>
+        <v>12324400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="n">
-        <v>181.6407975504903</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C153" t="n">
-        <v>183.6221942474171</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D153" t="n">
-        <v>180.5356140136719</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E153" t="n">
-        <v>180.5356140136719</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F153" t="n">
-        <v>8711700</v>
+        <v>8444700</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="n">
-        <v>178.424769515226</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C154" t="n">
-        <v>180.993610139636</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D154" t="n">
-        <v>176.5827818160244</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E154" t="n">
-        <v>180.43603515625</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F154" t="n">
-        <v>6882800</v>
+        <v>9740800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="n">
-        <v>177.5286741071897</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C155" t="n">
-        <v>177.9169863526292</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D155" t="n">
-        <v>172.2515989617143</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E155" t="n">
-        <v>175.7663269042969</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F155" t="n">
-        <v>14408300</v>
+        <v>11303400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="n">
-        <v>181.4018572311292</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C156" t="n">
-        <v>185.2351932001588</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D156" t="n">
-        <v>177.9767360752557</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E156" t="n">
-        <v>183.0248107910156</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F156" t="n">
-        <v>12324400</v>
+        <v>13955100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="n">
-        <v>183.4429710909726</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C157" t="n">
-        <v>189.4867039708132</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D157" t="n">
-        <v>183.1741348747832</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E157" t="n">
-        <v>184.6775970458984</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F157" t="n">
-        <v>8444700</v>
+        <v>15123900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B158" t="n">
-        <v>184.7473182824849</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C158" t="n">
-        <v>186.5793548412774</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D158" t="n">
-        <v>180.3165719120649</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E158" t="n">
-        <v>186.1810913085938</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F158" t="n">
-        <v>9740800</v>
+        <v>11145000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B159" t="n">
-        <v>184.7174439304337</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C159" t="n">
-        <v>186.2906106667237</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D159" t="n">
-        <v>178.8031379653169</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E159" t="n">
-        <v>180.4061737060547</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F159" t="n">
-        <v>11303400</v>
+        <v>10214000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="n">
-        <v>183.801426731489</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C160" t="n">
-        <v>187.7642050029951</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D160" t="n">
-        <v>183.2040162535504</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E160" t="n">
-        <v>185.5338897705078</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F160" t="n">
-        <v>13955100</v>
+        <v>11951900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B161" t="n">
-        <v>178.9027054786904</v>
+        <v>165.2818899628073</v>
       </c>
       <c r="C161" t="n">
-        <v>181.0832340725416</v>
+        <v>168.6174040602531</v>
       </c>
       <c r="D161" t="n">
-        <v>176.114830301217</v>
+        <v>163.6191161459536</v>
       </c>
       <c r="E161" t="n">
-        <v>181.0334625244141</v>
+        <v>166.8550567626953</v>
       </c>
       <c r="F161" t="n">
-        <v>15123900</v>
+        <v>9749400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B162" t="n">
-        <v>179.1317124775628</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C162" t="n">
-        <v>181.7105044839724</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D162" t="n">
-        <v>175.5472800106302</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E162" t="n">
-        <v>176.7221832275391</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F162" t="n">
-        <v>11145000</v>
+        <v>13883400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B163" t="n">
-        <v>176.8117888588543</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C163" t="n">
-        <v>176.8117888588543</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D163" t="n">
-        <v>169.8420709331304</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E163" t="n">
-        <v>170.5689086914062</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F163" t="n">
-        <v>10214000</v>
+        <v>13671200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B164" t="n">
-        <v>169.0455318751909</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C164" t="n">
-        <v>169.0455318751909</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D164" t="n">
-        <v>164.0372928300067</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E164" t="n">
-        <v>165.1225738525391</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F164" t="n">
-        <v>11951900</v>
+        <v>17510800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B165" t="n">
-        <v>165.2818748478833</v>
+        <v>175.2784580726278</v>
       </c>
       <c r="C165" t="n">
-        <v>168.6173886402985</v>
+        <v>179.5299906412754</v>
       </c>
       <c r="D165" t="n">
-        <v>163.6191011830893</v>
+        <v>172.5901410995666</v>
       </c>
       <c r="E165" t="n">
-        <v>166.8550415039062</v>
+        <v>179.3209075927734</v>
       </c>
       <c r="F165" t="n">
-        <v>9749400</v>
+        <v>13025300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B166" t="n">
-        <v>168.5178185348167</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C166" t="n">
-        <v>175.208748793394</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D166" t="n">
-        <v>168.268900043628</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E166" t="n">
-        <v>172.7593841552734</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F166" t="n">
-        <v>13883400</v>
+        <v>10949100</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B167" t="n">
-        <v>172.1420794089453</v>
+        <v>179.0620149167984</v>
       </c>
       <c r="C167" t="n">
-        <v>179.9979467596552</v>
+        <v>182.5568405051486</v>
       </c>
       <c r="D167" t="n">
-        <v>171.0567983816156</v>
+        <v>176.9113553536261</v>
       </c>
       <c r="E167" t="n">
-        <v>178.7035675048828</v>
+        <v>179.2910308837891</v>
       </c>
       <c r="F167" t="n">
-        <v>13671200</v>
+        <v>10176700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B168" t="n">
-        <v>184.1996921538</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C168" t="n">
-        <v>186.6291391730516</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D168" t="n">
-        <v>178.0364675908902</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E168" t="n">
-        <v>178.6438293457031</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F168" t="n">
-        <v>17510800</v>
+        <v>13617200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B169" t="n">
-        <v>175.2784431578192</v>
+        <v>177.2299817033781</v>
       </c>
       <c r="C169" t="n">
-        <v>179.529975364695</v>
+        <v>183.1243702829636</v>
       </c>
       <c r="D169" t="n">
-        <v>172.5901264135125</v>
+        <v>176.1247828951571</v>
       </c>
       <c r="E169" t="n">
-        <v>179.3208923339844</v>
+        <v>176.7420959472656</v>
       </c>
       <c r="F169" t="n">
-        <v>13025300</v>
+        <v>18524900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="n">
-        <v>174.6213174256682</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C170" t="n">
-        <v>176.5728300297275</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D170" t="n">
-        <v>171.2459830488208</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E170" t="n">
-        <v>175.5472869873047</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F170" t="n">
-        <v>10949100</v>
+        <v>22559400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B171" t="n">
-        <v>179.0619996775001</v>
+        <v>179.4602947300403</v>
       </c>
       <c r="C171" t="n">
-        <v>182.5568249684187</v>
+        <v>193.300157831373</v>
       </c>
       <c r="D171" t="n">
-        <v>176.9113402973623</v>
+        <v>179.2412452254626</v>
       </c>
       <c r="E171" t="n">
-        <v>179.291015625</v>
+        <v>190.2733154296875</v>
       </c>
       <c r="F171" t="n">
-        <v>10176700</v>
+        <v>33998900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B172" t="n">
-        <v>177.6581006500201</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C172" t="n">
-        <v>181.5711072848628</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D172" t="n">
-        <v>176.9113451663183</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E172" t="n">
-        <v>178.3052978515625</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F172" t="n">
-        <v>13617200</v>
+        <v>27594800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B173" t="n">
-        <v>177.2299664024681</v>
+        <v>200.1504053799259</v>
       </c>
       <c r="C173" t="n">
-        <v>183.1243544731695</v>
+        <v>203.5058221270036</v>
       </c>
       <c r="D173" t="n">
-        <v>176.1247676896629</v>
+        <v>194.9131500594789</v>
       </c>
       <c r="E173" t="n">
-        <v>176.7420806884766</v>
+        <v>199.9711761474609</v>
       </c>
       <c r="F173" t="n">
-        <v>18524900</v>
+        <v>19216600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="n">
-        <v>177.6581004088628</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C174" t="n">
-        <v>181.6905830539347</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D174" t="n">
-        <v>170.9074320607842</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E174" t="n">
-        <v>175.4078826904297</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F174" t="n">
-        <v>22559400</v>
+        <v>14154400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="n">
-        <v>179.4602803383912</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C175" t="n">
-        <v>193.3001423298492</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D175" t="n">
-        <v>179.24123085138</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E175" t="n">
-        <v>190.2733001708984</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F175" t="n">
-        <v>33998900</v>
+        <v>14453600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="n">
-        <v>197.8901992931745</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C176" t="n">
-        <v>210.4257307870387</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D176" t="n">
-        <v>197.352542040295</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E176" t="n">
-        <v>208.6932678222656</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F176" t="n">
-        <v>27594800</v>
+        <v>13183900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B177" t="n">
-        <v>200.1503901074607</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C177" t="n">
-        <v>203.5058065985036</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D177" t="n">
-        <v>194.9131351866423</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E177" t="n">
-        <v>199.9711608886719</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F177" t="n">
-        <v>19216600</v>
+        <v>11177800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B178" t="n">
-        <v>196.4166079226038</v>
+        <v>178.7234714192057</v>
       </c>
       <c r="C178" t="n">
-        <v>196.8248227029743</v>
+        <v>181.670672953058</v>
       </c>
       <c r="D178" t="n">
-        <v>188.9092176958791</v>
+        <v>170.8178179406258</v>
       </c>
       <c r="E178" t="n">
-        <v>189.7854156494141</v>
+        <v>174.5914306640625</v>
       </c>
       <c r="F178" t="n">
-        <v>14154400</v>
+        <v>15427800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="n">
-        <v>196.9542758894677</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C179" t="n">
-        <v>197.2330634002457</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D179" t="n">
-        <v>185.3048928689384</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E179" t="n">
-        <v>187.9334716796875</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F179" t="n">
-        <v>14453600</v>
+        <v>10820500</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B180" t="n">
-        <v>188.9789318725711</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C180" t="n">
-        <v>191.6771999565016</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D180" t="n">
-        <v>184.0304307819904</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E180" t="n">
-        <v>184.8568420410156</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F180" t="n">
-        <v>13183900</v>
+        <v>16666000</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="n">
-        <v>183.1144169895118</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C181" t="n">
-        <v>184.2196157855271</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D181" t="n">
-        <v>180.92393713233</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E181" t="n">
-        <v>181.7602996826172</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F181" t="n">
-        <v>11177800</v>
+        <v>13589400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="B182" t="n">
-        <v>178.7234870391233</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C182" t="n">
-        <v>181.6706888305526</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D182" t="n">
-        <v>170.8178328696119</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E182" t="n">
-        <v>174.5914459228516</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F182" t="n">
-        <v>15427800</v>
+        <v>13541800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B183" t="n">
-        <v>169.861995238658</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C183" t="n">
-        <v>174.7706609037228</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D183" t="n">
-        <v>169.2944537502145</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E183" t="n">
-        <v>170.1806030273438</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F183" t="n">
-        <v>10820500</v>
+        <v>16385300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B184" t="n">
-        <v>167.9744954285649</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C184" t="n">
-        <v>168.6832400259219</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D184" t="n">
-        <v>163.0231992739924</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E184" t="n">
-        <v>166.1576843261719</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F184" t="n">
-        <v>16666000</v>
+        <v>19986200</v>
       </c>
       <c r="G184" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B185" t="n">
-        <v>164.4506890531704</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C185" t="n">
-        <v>166.2475157071144</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D185" t="n">
-        <v>161.1165431857153</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E185" t="n">
-        <v>165.5986633300781</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F185" t="n">
-        <v>13589400</v>
+        <v>57940800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B186" t="n">
-        <v>165.7384133733495</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C186" t="n">
-        <v>169.6515271583533</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D186" t="n">
-        <v>163.8816793355271</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E186" t="n">
-        <v>164.2610168457031</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F186" t="n">
-        <v>13541800</v>
+        <v>20502800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B187" t="n">
-        <v>163.7718739013043</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C187" t="n">
-        <v>166.0079454764833</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D187" t="n">
-        <v>160.2181284427459</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E187" t="n">
-        <v>161.4260101318359</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F187" t="n">
-        <v>16385300</v>
+        <v>20720700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B188" t="n">
-        <v>159.9685677271403</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C188" t="n">
-        <v>161.1464880907799</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D188" t="n">
-        <v>153.959135832121</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E188" t="n">
-        <v>154.7477569580078</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F188" t="n">
-        <v>19986200</v>
+        <v>13146800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B189" t="n">
-        <v>152.4617715583163</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C189" t="n">
-        <v>154.1987212566731</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D189" t="n">
-        <v>149.5369245308901</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E189" t="n">
-        <v>151.5134429931641</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F189" t="n">
-        <v>57940800</v>
+        <v>11324700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B190" t="n">
-        <v>149.8962920415152</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C190" t="n">
-        <v>153.5997679942281</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D190" t="n">
-        <v>146.0630395211035</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E190" t="n">
-        <v>149.8563537597656</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F190" t="n">
-        <v>20502800</v>
+        <v>21267900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="B191" t="n">
-        <v>151.3836627210609</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C191" t="n">
-        <v>154.907462036052</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D191" t="n">
-        <v>150.5850798848861</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E191" t="n">
-        <v>153.1505584716797</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F191" t="n">
-        <v>20720700</v>
+        <v>12664100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="B192" t="n">
-        <v>151.5433859321397</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C192" t="n">
-        <v>156.7841657815476</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D192" t="n">
-        <v>150.135858545478</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E192" t="n">
-        <v>152.4917144775391</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F192" t="n">
-        <v>13146800</v>
+        <v>13690500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B193" t="n">
-        <v>149.7465472087312</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C193" t="n">
-        <v>153.7295454610107</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D193" t="n">
-        <v>148.5187115976041</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E193" t="n">
-        <v>149.9262390136719</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F193" t="n">
-        <v>11324700</v>
+        <v>14164600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="B194" t="n">
-        <v>151.2239658596097</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C194" t="n">
-        <v>158.1817266914859</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D194" t="n">
-        <v>151.2239658596097</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E194" t="n">
-        <v>158.0918731689453</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F194" t="n">
-        <v>21267900</v>
+        <v>10486300</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B195" t="n">
-        <v>159.9885357004027</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C195" t="n">
-        <v>161.4759091917036</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D195" t="n">
-        <v>157.4230418613804</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E195" t="n">
-        <v>157.6526336669922</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F195" t="n">
-        <v>12664100</v>
+        <v>10595500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B196" t="n">
-        <v>154.8176224085462</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C196" t="n">
-        <v>157.4130622995693</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D196" t="n">
-        <v>153.7994247316601</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E196" t="n">
-        <v>156.3848724365234</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F196" t="n">
-        <v>13690500</v>
+        <v>13057900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B197" t="n">
-        <v>161.9351081174896</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C197" t="n">
-        <v>165.5187996520913</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D197" t="n">
-        <v>160.916895191227</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E197" t="n">
-        <v>162.9433288574219</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F197" t="n">
-        <v>14164600</v>
+        <v>9792400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B198" t="n">
-        <v>162.7137441629</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C198" t="n">
-        <v>166.9163573859938</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D198" t="n">
-        <v>161.7155003336798</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E198" t="n">
-        <v>165.8182830810547</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F198" t="n">
-        <v>10486300</v>
+        <v>13858600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B199" t="n">
-        <v>163.7020118941432</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C199" t="n">
-        <v>167.425457131665</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D199" t="n">
-        <v>162.0848465245878</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E199" t="n">
-        <v>165.3590850830078</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F199" t="n">
-        <v>10595500</v>
+        <v>8321500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B200" t="n">
-        <v>168.9228138583306</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C200" t="n">
-        <v>172.0772678623225</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D200" t="n">
-        <v>167.3855099055031</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E200" t="n">
-        <v>169.2222900390625</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F200" t="n">
-        <v>13057900</v>
+        <v>14020700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>167.0760662569272</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C201" t="n">
-        <v>167.2357889266519</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D201" t="n">
-        <v>164.4906183727253</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E201" t="n">
-        <v>166.2874603271484</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F201" t="n">
-        <v>9792400</v>
+        <v>13507900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>158.05194011754</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C202" t="n">
-        <v>163.5123348335076</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D202" t="n">
-        <v>156.2051830247059</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E202" t="n">
-        <v>162.2146148681641</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F202" t="n">
-        <v>13858600</v>
+        <v>13328100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>165.309182555471</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C203" t="n">
-        <v>166.007950182526</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D203" t="n">
-        <v>162.1347592897187</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E203" t="n">
-        <v>163.0331878662109</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F203" t="n">
-        <v>8321500</v>
+        <v>12057500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B204" t="n">
-        <v>165.6286161244176</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C204" t="n">
-        <v>172.4566003351415</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D204" t="n">
-        <v>165.6286161244176</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E204" t="n">
-        <v>170.9193115234375</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F204" t="n">
-        <v>14020700</v>
+        <v>10191500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B205" t="n">
-        <v>162.2046435717354</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C205" t="n">
-        <v>171.049084414024</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D205" t="n">
-        <v>161.1864306117812</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E205" t="n">
-        <v>167.2657318115234</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F205" t="n">
-        <v>13507900</v>
+        <v>13426500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B206" t="n">
-        <v>170.2205331766167</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C206" t="n">
-        <v>172.4965277703878</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D206" t="n">
-        <v>166.2674811162824</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E206" t="n">
-        <v>166.7067108154297</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F206" t="n">
-        <v>13328100</v>
+        <v>12831800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B207" t="n">
-        <v>170.5399744864679</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C207" t="n">
-        <v>174.2334736592566</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D207" t="n">
-        <v>166.5869373980102</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E207" t="n">
-        <v>172.3767395019531</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F207" t="n">
-        <v>12057500</v>
+        <v>12194500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B208" t="n">
-        <v>171.1988064601764</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C208" t="n">
-        <v>175.1218971627477</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D208" t="n">
-        <v>169.4518798636439</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E208" t="n">
-        <v>170.4700927734375</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F208" t="n">
-        <v>10191500</v>
+        <v>12775000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B209" t="n">
-        <v>167.5652084388413</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C209" t="n">
-        <v>175.0819831940494</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D209" t="n">
-        <v>166.2075962327059</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E209" t="n">
-        <v>173.4847869873047</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F209" t="n">
-        <v>13426500</v>
+        <v>10899100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B210" t="n">
-        <v>166.7666058963373</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C210" t="n">
-        <v>172.1271701993457</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D210" t="n">
-        <v>166.6368293287962</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E210" t="n">
-        <v>169.7613372802734</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F210" t="n">
-        <v>12831800</v>
+        <v>17312000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B211" t="n">
-        <v>169.1723839486806</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C211" t="n">
-        <v>169.272214424985</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D211" t="n">
-        <v>161.925139189555</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E211" t="n">
-        <v>162.7137451171875</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F211" t="n">
-        <v>12194500</v>
+        <v>17204600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B212" t="n">
-        <v>164.7601382451291</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C212" t="n">
-        <v>165.5886824068968</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D212" t="n">
-        <v>154.877515725338</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E212" t="n">
-        <v>156.6543884277344</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F212" t="n">
-        <v>12775000</v>
+        <v>18139500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B213" t="n">
-        <v>160.0983505627206</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C213" t="n">
-        <v>164.1611950360997</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D213" t="n">
-        <v>159.2698063547753</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E213" t="n">
-        <v>163.3725891113281</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F213" t="n">
-        <v>10899100</v>
+        <v>12182400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B214" t="n">
-        <v>167.7049639405646</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C214" t="n">
-        <v>176.6392431993331</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D214" t="n">
-        <v>166.8464736349225</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E214" t="n">
-        <v>173.2951354980469</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F214" t="n">
-        <v>17312000</v>
+        <v>9691500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B215" t="n">
-        <v>176.5993086569288</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C215" t="n">
-        <v>184.2158982492034</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D215" t="n">
-        <v>176.5993086569288</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E215" t="n">
-        <v>181.1812438964844</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F215" t="n">
-        <v>17204600</v>
+        <v>12908000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B216" t="n">
-        <v>181.6903554713178</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C216" t="n">
-        <v>189.8460057999592</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D216" t="n">
-        <v>181.6903554713178</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E216" t="n">
-        <v>188.0491790771484</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F216" t="n">
-        <v>18139500</v>
+        <v>9326900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B217" t="n">
-        <v>180.6721461984077</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C217" t="n">
-        <v>182.1894657683464</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D217" t="n">
-        <v>175.5910738107855</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E217" t="n">
-        <v>180.3926391601562</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F217" t="n">
-        <v>12182400</v>
+        <v>9605500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B218" t="n">
-        <v>177.3879151720665</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C218" t="n">
-        <v>184.1260606305619</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D218" t="n">
-        <v>176.719093672914</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E218" t="n">
-        <v>183.6968231201172</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F218" t="n">
-        <v>9691500</v>
+        <v>13297600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B219" t="n">
-        <v>188.658097974018</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C219" t="n">
-        <v>193.3598176605707</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D219" t="n">
-        <v>185.5735131091938</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E219" t="n">
-        <v>185.6234283447266</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F219" t="n">
-        <v>12908000</v>
+        <v>11392800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B220" t="n">
-        <v>182.7684517177381</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C220" t="n">
-        <v>190.9540477431734</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D220" t="n">
-        <v>182.6786134323838</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E220" t="n">
-        <v>190.6545867919922</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F220" t="n">
-        <v>9326900</v>
+        <v>9706600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B221" t="n">
-        <v>192.9405589477455</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C221" t="n">
-        <v>194.5976472985604</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D221" t="n">
-        <v>190.0955580470331</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E221" t="n">
-        <v>192.6410827636719</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F221" t="n">
-        <v>9605500</v>
+        <v>11171600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B222" t="n">
-        <v>183.117847615437</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C222" t="n">
-        <v>186.6915622961891</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D222" t="n">
-        <v>182.6786179003067</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E222" t="n">
-        <v>186.4420013427734</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F222" t="n">
-        <v>13297600</v>
+        <v>12787900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B223" t="n">
-        <v>190.7544083295565</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C223" t="n">
-        <v>194.3580691369978</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D223" t="n">
-        <v>190.2652786051507</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E223" t="n">
-        <v>192.4015197753906</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F223" t="n">
-        <v>11392800</v>
+        <v>15058700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="n">
-        <v>189.8360257192551</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C224" t="n">
-        <v>197.831953246477</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D224" t="n">
-        <v>189.666326097428</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E224" t="n">
-        <v>197.1631317138672</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F224" t="n">
-        <v>9706600</v>
+        <v>8664800</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B225" t="n">
-        <v>196.5941314807131</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C225" t="n">
-        <v>199.0398256830038</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D225" t="n">
-        <v>195.1566580076304</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E225" t="n">
-        <v>197.1231994628906</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F225" t="n">
-        <v>11171600</v>
+        <v>14378800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B226" t="n">
-        <v>191.6628101365335</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C226" t="n">
-        <v>196.1549072491085</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D226" t="n">
-        <v>191.4431952813594</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E226" t="n">
-        <v>192.9804992675781</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F226" t="n">
-        <v>12787900</v>
+        <v>14152900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B227" t="n">
-        <v>196.4943140399408</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C227" t="n">
-        <v>202.6335228023228</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D227" t="n">
-        <v>191.0538881519706</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E227" t="n">
-        <v>201.016357421875</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F227" t="n">
-        <v>15058700</v>
+        <v>17843600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B228" t="n">
-        <v>202.3939250564146</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C228" t="n">
-        <v>204.0410211897246</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D228" t="n">
-        <v>194.9769811314243</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E228" t="n">
-        <v>195.8654174804688</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F228" t="n">
-        <v>8664800</v>
+        <v>11482300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="n">
-        <v>193.4896063018435</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C229" t="n">
-        <v>194.5976575790598</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D229" t="n">
-        <v>189.57649225733</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E229" t="n">
-        <v>190.6346282958984</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F229" t="n">
-        <v>14378800</v>
+        <v>9685400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B230" t="n">
-        <v>193.7491445531879</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C230" t="n">
-        <v>199.0598091290667</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D230" t="n">
-        <v>192.8906542357335</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E230" t="n">
-        <v>195.7955474853516</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F230" t="n">
-        <v>14152900</v>
+        <v>9580200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B231" t="n">
-        <v>193.8689320609861</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C231" t="n">
-        <v>207.5847919095016</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D231" t="n">
-        <v>193.8689320609861</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E231" t="n">
-        <v>205.7280578613281</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F231" t="n">
-        <v>17843600</v>
+        <v>10081800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B232" t="n">
-        <v>204.8595912018172</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C232" t="n">
-        <v>207.5149233311111</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D232" t="n">
-        <v>202.6434887759544</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E232" t="n">
-        <v>205.0692138671875</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F232" t="n">
-        <v>11482300</v>
+        <v>14888900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B233" t="n">
-        <v>205.2189664215684</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C233" t="n">
-        <v>210.6993304789719</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D233" t="n">
-        <v>204.3704530814486</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E233" t="n">
-        <v>208.8026580810547</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F233" t="n">
-        <v>9685400</v>
+        <v>55517500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B234" t="n">
-        <v>208.0539803833292</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C234" t="n">
-        <v>212.7956386479058</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D234" t="n">
-        <v>207.0257904413594</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E234" t="n">
-        <v>208.6928558349609</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F234" t="n">
-        <v>9580200</v>
+        <v>34362700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B235" t="n">
-        <v>205.4884885298704</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C235" t="n">
-        <v>209.9406472657768</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D235" t="n">
-        <v>204.400391231641</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E235" t="n">
-        <v>205.3287658691406</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F235" t="n">
-        <v>10081800</v>
+        <v>22471500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B236" t="n">
-        <v>199.5888632714973</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C236" t="n">
-        <v>206.0774478239803</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D236" t="n">
-        <v>198.6005964484484</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E236" t="n">
-        <v>205.2588806152344</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F236" t="n">
-        <v>14888900</v>
+        <v>15897500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B237" t="n">
-        <v>229.6459965412689</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C237" t="n">
-        <v>254.0330860396483</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D237" t="n">
-        <v>229.6459965412689</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E237" t="n">
-        <v>251.6073608398438</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F237" t="n">
-        <v>55517500</v>
+        <v>14393700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B238" t="n">
-        <v>250.0301279952546</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C238" t="n">
-        <v>263.0671897003631</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D238" t="n">
-        <v>248.5627083778381</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E238" t="n">
-        <v>255.5504150390625</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F238" t="n">
-        <v>34362700</v>
+        <v>16028300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B239" t="n">
-        <v>253.9432305236259</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C239" t="n">
-        <v>261.8193732125837</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D239" t="n">
-        <v>253.9432305236259</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E239" t="n">
-        <v>257.0877075195312</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F239" t="n">
-        <v>22471500</v>
+        <v>10490600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B240" t="n">
-        <v>254.5621609406893</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C240" t="n">
-        <v>261.8593363431507</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D240" t="n">
-        <v>253.8035010915435</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E240" t="n">
-        <v>257.6567077636719</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F240" t="n">
-        <v>15897500</v>
+        <v>17482700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B241" t="n">
-        <v>258.9244691424316</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C241" t="n">
-        <v>264.0853722779391</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D241" t="n">
-        <v>253.154621477229</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E241" t="n">
-        <v>256.478759765625</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F241" t="n">
-        <v>14393700</v>
+        <v>11853700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B242" t="n">
-        <v>261.5199276025597</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C242" t="n">
-        <v>267.7988593124239</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D242" t="n">
-        <v>261.1405900757476</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E242" t="n">
-        <v>263.9656066894531</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F242" t="n">
-        <v>16028300</v>
+        <v>10732600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B243" t="n">
-        <v>262.8974710364521</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C243" t="n">
-        <v>263.1370702625856</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D243" t="n">
-        <v>257.3672223502596</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E243" t="n">
-        <v>258.7747497558594</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F243" t="n">
-        <v>10490600</v>
+        <v>9738300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B244" t="n">
-        <v>253.2744227737308</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C244" t="n">
-        <v>253.5539298242691</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D244" t="n">
-        <v>245.4581718493405</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E244" t="n">
-        <v>248.6824951171875</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F244" t="n">
-        <v>17482700</v>
+        <v>12963700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B245" t="n">
-        <v>249.3413418635835</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C245" t="n">
-        <v>254.3525301395604</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D245" t="n">
-        <v>243.0224566114913</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E245" t="n">
-        <v>243.7312164306641</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F245" t="n">
-        <v>11853700</v>
+        <v>11502800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B246" t="n">
-        <v>244.9191211985708</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C246" t="n">
-        <v>248.0635830600566</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D246" t="n">
-        <v>241.3254374437371</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E246" t="n">
-        <v>242.5732421875</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F246" t="n">
-        <v>10732600</v>
+        <v>9423800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,25 +6839,25 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B247" t="n">
-        <v>241.5949712138984</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C247" t="n">
-        <v>250.1099896964979</v>
+        <v>247</v>
       </c>
       <c r="D247" t="n">
-        <v>241.5949712138984</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E247" t="n">
-        <v>247.2849578857422</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F247" t="n">
-        <v>9738300</v>
+        <v>16611300</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B248" t="n">
-        <v>255.3008656803045</v>
+        <v>244.25</v>
       </c>
       <c r="C248" t="n">
-        <v>259.7230786425112</v>
+        <v>244.25</v>
       </c>
       <c r="D248" t="n">
-        <v>251.0583293004754</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E248" t="n">
-        <v>258.9743957519531</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F248" t="n">
-        <v>12963700</v>
+        <v>21962400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B249" t="n">
-        <v>256.43886230448</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C249" t="n">
-        <v>261.8792726915332</v>
+        <v>241.3399963378906</v>
       </c>
       <c r="D249" t="n">
-        <v>254.632028246405</v>
+        <v>236.25</v>
       </c>
       <c r="E249" t="n">
-        <v>255.2010192871094</v>
+        <v>236.4199981689453</v>
       </c>
       <c r="F249" t="n">
-        <v>11502800</v>
+        <v>10581900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B250" t="n">
-        <v>251.4077029961344</v>
+        <v>234.4199981689453</v>
       </c>
       <c r="C250" t="n">
-        <v>255.9497000259878</v>
+        <v>241.1199951171875</v>
       </c>
       <c r="D250" t="n">
-        <v>249.1616544830015</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="E250" t="n">
-        <v>250.0999908447266</v>
+        <v>237.5800018310547</v>
       </c>
       <c r="F250" t="n">
-        <v>9423800</v>
+        <v>12353500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,53 +6943,27 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B251" t="n">
-        <v>244.1799926757812</v>
+        <v>240.6399993896484</v>
       </c>
       <c r="C251" t="n">
-        <v>247</v>
+        <v>242.0899963378906</v>
       </c>
       <c r="D251" t="n">
-        <v>241.5200042724609</v>
+        <v>237</v>
       </c>
       <c r="E251" t="n">
-        <v>242.8500061035156</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="F251" t="n">
-        <v>16611300</v>
+        <v>11060900</v>
       </c>
       <c r="G251" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B252" t="n">
-        <v>244.25</v>
-      </c>
-      <c r="C252" t="n">
-        <v>244.25</v>
-      </c>
-      <c r="D252" t="n">
-        <v>236.5500030517578</v>
-      </c>
-      <c r="E252" t="n">
-        <v>237.9199981689453</v>
-      </c>
-      <c r="F252" t="n">
-        <v>21947900</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10654,37 +10628,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>237.92</v>
+        <v>238.22</v>
       </c>
       <c r="D2" t="n">
-        <v>242.85</v>
+        <v>237.58</v>
       </c>
       <c r="E2" t="n">
-        <v>244.25</v>
+        <v>240.64</v>
       </c>
       <c r="F2" t="n">
-        <v>244.25</v>
+        <v>242.01</v>
       </c>
       <c r="G2" t="n">
-        <v>236.545</v>
+        <v>237</v>
       </c>
       <c r="H2" t="n">
-        <v>21529713</v>
+        <v>9447985</v>
       </c>
       <c r="I2" t="n">
-        <v>14298250</v>
+        <v>14015952</v>
       </c>
       <c r="J2" t="n">
-        <v>195808165888</v>
+        <v>196055056384</v>
       </c>
       <c r="K2" t="n">
-        <v>22.214752</v>
+        <v>21.735401</v>
       </c>
       <c r="L2" t="n">
-        <v>14.859358</v>
+        <v>14.882481</v>
       </c>
       <c r="M2" t="n">
-        <v>10.71</v>
+        <v>10.96</v>
       </c>
       <c r="N2" t="n">
         <v>269.11</v>
@@ -10696,7 +10670,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10720,7 +10694,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.1020756</v>
+        <v>5.108509</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10732,7 +10706,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>226781167616</v>
+        <v>227028058112</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10759,7 +10733,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:49</t>
+          <t>2026-09-25 14:29:36</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="n">
-        <v>242.4436227791717</v>
+        <v>238.6656687083941</v>
       </c>
       <c r="C2" t="n">
-        <v>242.6022807239559</v>
+        <v>242.4733685900855</v>
       </c>
       <c r="D2" t="n">
-        <v>237.4757650354455</v>
+        <v>238.3285319244896</v>
       </c>
       <c r="E2" t="n">
-        <v>238.9234771728516</v>
+        <v>241.3826141357422</v>
       </c>
       <c r="F2" t="n">
-        <v>8145500</v>
+        <v>4974600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="n">
-        <v>238.6656837954339</v>
+        <v>242.6617958656146</v>
       </c>
       <c r="C3" t="n">
-        <v>242.4733839178257</v>
+        <v>243.7525504227033</v>
       </c>
       <c r="D3" t="n">
-        <v>238.3285469902175</v>
+        <v>240.8273491460897</v>
       </c>
       <c r="E3" t="n">
-        <v>241.3826293945312</v>
+        <v>243.0386047363281</v>
       </c>
       <c r="F3" t="n">
-        <v>4974600</v>
+        <v>6373500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>242.6617806304829</v>
+        <v>242.989028225756</v>
       </c>
       <c r="C4" t="n">
-        <v>243.7525351190903</v>
+        <v>243.1476861889649</v>
       </c>
       <c r="D4" t="n">
-        <v>240.8273340261308</v>
+        <v>233.8267351116018</v>
       </c>
       <c r="E4" t="n">
-        <v>243.0385894775391</v>
+        <v>235.0067291259766</v>
       </c>
       <c r="F4" t="n">
-        <v>6373500</v>
+        <v>10801100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>242.989012448683</v>
+        <v>234.5010077854061</v>
       </c>
       <c r="C5" t="n">
-        <v>243.1476704015903</v>
+        <v>240.4307087963897</v>
       </c>
       <c r="D5" t="n">
-        <v>233.8267199294288</v>
+        <v>231.5460601627856</v>
       </c>
       <c r="E5" t="n">
-        <v>235.0067138671875</v>
+        <v>233.7077331542969</v>
       </c>
       <c r="F5" t="n">
-        <v>10801100</v>
+        <v>10016600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>234.5010077854061</v>
+        <v>233.4499146778946</v>
       </c>
       <c r="C6" t="n">
-        <v>240.4307087963897</v>
+        <v>237.3865263037574</v>
       </c>
       <c r="D6" t="n">
-        <v>231.5460601627856</v>
+        <v>231.6353191614031</v>
       </c>
       <c r="E6" t="n">
-        <v>233.7077331542969</v>
+        <v>236.8709106445312</v>
       </c>
       <c r="F6" t="n">
-        <v>10016600</v>
+        <v>7679200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>233.4498996394798</v>
+        <v>236.7419803274875</v>
       </c>
       <c r="C7" t="n">
-        <v>237.3865110117534</v>
+        <v>240.7678310589901</v>
       </c>
       <c r="D7" t="n">
-        <v>231.6353042398812</v>
+        <v>236.4940829658881</v>
       </c>
       <c r="E7" t="n">
-        <v>236.8708953857422</v>
+        <v>238.3384399414062</v>
       </c>
       <c r="F7" t="n">
-        <v>7679200</v>
+        <v>8849800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B8" t="n">
-        <v>236.7419954840688</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="C8" t="n">
-        <v>240.7678464733125</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D8" t="n">
-        <v>236.4940981065986</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E8" t="n">
-        <v>238.3384552001953</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="F8" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B9" t="n">
-        <v>237.3171110157645</v>
+        <v>244.4069666278678</v>
       </c>
       <c r="C9" t="n">
-        <v>248.3634171689519</v>
+        <v>245.2795701971395</v>
       </c>
       <c r="D9" t="n">
-        <v>233.430082086989</v>
+        <v>235.5520799850208</v>
       </c>
       <c r="E9" t="n">
-        <v>243.7128601074219</v>
+        <v>237.7236633300781</v>
       </c>
       <c r="F9" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B10" t="n">
-        <v>244.4069823156386</v>
+        <v>237.7236529240558</v>
       </c>
       <c r="C10" t="n">
-        <v>245.2795859409202</v>
+        <v>239.2903660228245</v>
       </c>
       <c r="D10" t="n">
-        <v>235.5520951044222</v>
+        <v>233.6680406983684</v>
       </c>
       <c r="E10" t="n">
-        <v>237.7236785888672</v>
+        <v>238.4078369140625</v>
       </c>
       <c r="F10" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B11" t="n">
-        <v>237.7236681390551</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C11" t="n">
-        <v>239.290381338098</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D11" t="n">
-        <v>233.6680556537968</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E11" t="n">
-        <v>238.4078521728516</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F11" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B12" t="n">
-        <v>237.2576175505903</v>
+        <v>244.4466434616172</v>
       </c>
       <c r="C12" t="n">
-        <v>243.8913535488906</v>
+        <v>246.9553636418975</v>
       </c>
       <c r="D12" t="n">
-        <v>235.1554375781523</v>
+        <v>238.6954214370453</v>
       </c>
       <c r="E12" t="n">
-        <v>243.2666473388672</v>
+        <v>239.6473388671875</v>
       </c>
       <c r="F12" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B13" t="n">
-        <v>244.4466434616172</v>
+        <v>240.8471677432379</v>
       </c>
       <c r="C13" t="n">
-        <v>246.9553636418975</v>
+        <v>247.252842429503</v>
       </c>
       <c r="D13" t="n">
-        <v>238.6954214370453</v>
+        <v>240.3315369780713</v>
       </c>
       <c r="E13" t="n">
-        <v>239.6473388671875</v>
+        <v>246.6578826904297</v>
       </c>
       <c r="F13" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B14" t="n">
-        <v>240.8471826425636</v>
+        <v>246.0232707436915</v>
       </c>
       <c r="C14" t="n">
-        <v>247.2528577250976</v>
+        <v>246.1918391425529</v>
       </c>
       <c r="D14" t="n">
-        <v>240.331551845499</v>
+        <v>237.5352670689401</v>
       </c>
       <c r="E14" t="n">
-        <v>246.6578979492188</v>
+        <v>237.75341796875</v>
       </c>
       <c r="F14" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B15" t="n">
-        <v>246.0232707436915</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C15" t="n">
-        <v>246.1918391425529</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D15" t="n">
-        <v>237.5352670689401</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E15" t="n">
-        <v>237.75341796875</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F15" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B16" t="n">
-        <v>238.8441526809671</v>
+        <v>251.0605458824941</v>
       </c>
       <c r="C16" t="n">
-        <v>239.2903800503502</v>
+        <v>254.5806764744798</v>
       </c>
       <c r="D16" t="n">
-        <v>233.915951765761</v>
+        <v>240.6290201908687</v>
       </c>
       <c r="E16" t="n">
-        <v>234.5902404785156</v>
+        <v>243.9310150146484</v>
       </c>
       <c r="F16" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B17" t="n">
-        <v>251.0605458824941</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="C17" t="n">
-        <v>254.5806764744798</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D17" t="n">
-        <v>240.6290201908687</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E17" t="n">
-        <v>243.9310150146484</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="F17" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B18" t="n">
-        <v>244.4962363844956</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C18" t="n">
-        <v>248.670819810711</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D18" t="n">
-        <v>240.1233229489625</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E18" t="n">
-        <v>241.0355834960938</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F18" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B19" t="n">
-        <v>242.9394234832453</v>
+        <v>252.3595144668565</v>
       </c>
       <c r="C19" t="n">
-        <v>253.2519480605562</v>
+        <v>264.883294034403</v>
       </c>
       <c r="D19" t="n">
-        <v>242.2453138708127</v>
+        <v>251.863719742953</v>
       </c>
       <c r="E19" t="n">
-        <v>252.1413726806641</v>
+        <v>261.194580078125</v>
       </c>
       <c r="F19" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B20" t="n">
-        <v>252.3595144668565</v>
+        <v>259.9947875033736</v>
       </c>
       <c r="C20" t="n">
-        <v>264.883294034403</v>
+        <v>260.1930872533099</v>
       </c>
       <c r="D20" t="n">
-        <v>251.863719742953</v>
+        <v>254.3526406430638</v>
       </c>
       <c r="E20" t="n">
-        <v>261.194580078125</v>
+        <v>254.4815521240234</v>
       </c>
       <c r="F20" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B21" t="n">
-        <v>259.9947875033736</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C21" t="n">
-        <v>260.1930872533099</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D21" t="n">
-        <v>254.3526406430638</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E21" t="n">
-        <v>254.4815521240234</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F21" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B22" t="n">
-        <v>255.4334634999039</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C22" t="n">
-        <v>256.3853809552256</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D22" t="n">
-        <v>251.982721115611</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E22" t="n">
-        <v>252.9049072265625</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F22" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B23" t="n">
-        <v>255.254980605377</v>
+        <v>254.9178098920577</v>
       </c>
       <c r="C23" t="n">
-        <v>256.3258839430272</v>
+        <v>255.9292505274036</v>
       </c>
       <c r="D23" t="n">
-        <v>251.8637312244832</v>
+        <v>252.7759881170209</v>
       </c>
       <c r="E23" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213653564453</v>
       </c>
       <c r="F23" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B24" t="n">
-        <v>254.9178252470085</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="C24" t="n">
-        <v>255.9292659432784</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D24" t="n">
-        <v>252.7760033429592</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E24" t="n">
-        <v>253.3213806152344</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="F24" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B25" t="n">
-        <v>253.3213661855435</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C25" t="n">
-        <v>256.663017898251</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D25" t="n">
-        <v>252.0025503587843</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E25" t="n">
-        <v>252.1215362548828</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F25" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B26" t="n">
-        <v>249.8805444255208</v>
+        <v>248.3931555366784</v>
       </c>
       <c r="C26" t="n">
-        <v>251.4373471434884</v>
+        <v>257.0993096380665</v>
       </c>
       <c r="D26" t="n">
-        <v>246.945432960583</v>
+        <v>247.8973608150483</v>
       </c>
       <c r="E26" t="n">
-        <v>249.3450927734375</v>
+        <v>254.4914245605469</v>
       </c>
       <c r="F26" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B27" t="n">
-        <v>248.3931555366784</v>
+        <v>252.657000570364</v>
       </c>
       <c r="C27" t="n">
-        <v>257.0993096380665</v>
+        <v>259.6179629024988</v>
       </c>
       <c r="D27" t="n">
-        <v>247.8973608150483</v>
+        <v>250.5052532311086</v>
       </c>
       <c r="E27" t="n">
-        <v>254.4914245605469</v>
+        <v>258.2198181152344</v>
       </c>
       <c r="F27" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B28" t="n">
-        <v>252.6570304305034</v>
+        <v>257.8132719821094</v>
       </c>
       <c r="C28" t="n">
-        <v>259.617993585316</v>
+        <v>259.3601491931292</v>
       </c>
       <c r="D28" t="n">
-        <v>250.5052828369448</v>
+        <v>252.9544894469363</v>
       </c>
       <c r="E28" t="n">
-        <v>258.2198486328125</v>
+        <v>259.1419982910156</v>
       </c>
       <c r="F28" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B29" t="n">
-        <v>257.8132719821094</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C29" t="n">
-        <v>259.3601491931292</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D29" t="n">
-        <v>252.9544894469363</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E29" t="n">
-        <v>259.1419982910156</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F29" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B30" t="n">
-        <v>255.9788221233241</v>
+        <v>252.5578398334985</v>
       </c>
       <c r="C30" t="n">
-        <v>257.0795021986246</v>
+        <v>254.6699151564536</v>
       </c>
       <c r="D30" t="n">
-        <v>251.3282801006067</v>
+        <v>249.8904616870965</v>
       </c>
       <c r="E30" t="n">
-        <v>252.3000335693359</v>
+        <v>250.5548248291016</v>
       </c>
       <c r="F30" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B31" t="n">
-        <v>252.5578398334985</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="C31" t="n">
-        <v>254.6699151564536</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="D31" t="n">
-        <v>249.8904616870965</v>
+        <v>232.5078921531912</v>
       </c>
       <c r="E31" t="n">
-        <v>250.5548248291016</v>
+        <v>237.2576141357422</v>
       </c>
       <c r="F31" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B32" t="n">
-        <v>248.4328164468309</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="C32" t="n">
-        <v>248.4328164468309</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D32" t="n">
-        <v>232.5078921531912</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E32" t="n">
-        <v>237.2576141357422</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="F32" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B33" t="n">
-        <v>234.1638481621394</v>
+        <v>237.9814688826704</v>
       </c>
       <c r="C33" t="n">
-        <v>238.943316687993</v>
+        <v>239.8754083705041</v>
       </c>
       <c r="D33" t="n">
-        <v>233.8068753463891</v>
+        <v>233.1028505862302</v>
       </c>
       <c r="E33" t="n">
-        <v>237.8624877929688</v>
+        <v>239.6770935058594</v>
       </c>
       <c r="F33" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B34" t="n">
-        <v>237.9814688826704</v>
+        <v>239.8654952673756</v>
       </c>
       <c r="C34" t="n">
-        <v>239.8754083705041</v>
+        <v>243.63353841341</v>
       </c>
       <c r="D34" t="n">
-        <v>233.1028505862302</v>
+        <v>239.1317287169831</v>
       </c>
       <c r="E34" t="n">
-        <v>239.6770935058594</v>
+        <v>242.4436340332031</v>
       </c>
       <c r="F34" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="n">
-        <v>239.8655103639031</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="C35" t="n">
-        <v>243.6335537470887</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D35" t="n">
-        <v>239.1317437673292</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E35" t="n">
-        <v>242.4436492919922</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="F35" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B36" t="n">
-        <v>243.6732228340941</v>
+        <v>243.1873051795984</v>
       </c>
       <c r="C36" t="n">
-        <v>246.3405860290093</v>
+        <v>243.8318322502171</v>
       </c>
       <c r="D36" t="n">
-        <v>241.6305356400256</v>
+        <v>237.8922213097491</v>
       </c>
       <c r="E36" t="n">
-        <v>243.9508666992188</v>
+        <v>238.4078369140625</v>
       </c>
       <c r="F36" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B37" t="n">
-        <v>243.1873207442872</v>
+        <v>236.3056926086296</v>
       </c>
       <c r="C37" t="n">
-        <v>243.8318478561575</v>
+        <v>243.1179076689137</v>
       </c>
       <c r="D37" t="n">
-        <v>237.8922365355373</v>
+        <v>235.4231785540507</v>
       </c>
       <c r="E37" t="n">
-        <v>238.4078521728516</v>
+        <v>241.6107025146484</v>
       </c>
       <c r="F37" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B38" t="n">
-        <v>236.3056776848755</v>
+        <v>240.0340571163644</v>
       </c>
       <c r="C38" t="n">
-        <v>243.1178923149379</v>
+        <v>240.7876596253181</v>
       </c>
       <c r="D38" t="n">
-        <v>235.4231636860313</v>
+        <v>233.6085468088289</v>
       </c>
       <c r="E38" t="n">
-        <v>241.6106872558594</v>
+        <v>235.0364379882812</v>
       </c>
       <c r="F38" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B39" t="n">
-        <v>240.0340571163644</v>
+        <v>234.2531087461558</v>
       </c>
       <c r="C39" t="n">
-        <v>240.7876596253181</v>
+        <v>235.7900603656055</v>
       </c>
       <c r="D39" t="n">
-        <v>233.6085468088289</v>
+        <v>228.3333182252886</v>
       </c>
       <c r="E39" t="n">
-        <v>235.0364379882812</v>
+        <v>231.5361480712891</v>
       </c>
       <c r="F39" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B40" t="n">
-        <v>234.2531087461558</v>
+        <v>230.0487686636922</v>
       </c>
       <c r="C40" t="n">
-        <v>235.7900603656055</v>
+        <v>230.3264125188844</v>
       </c>
       <c r="D40" t="n">
-        <v>228.3333182252886</v>
+        <v>223.1671349733107</v>
       </c>
       <c r="E40" t="n">
-        <v>231.5361480712891</v>
+        <v>225.9634246826172</v>
       </c>
       <c r="F40" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B41" t="n">
-        <v>230.0487686636922</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C41" t="n">
-        <v>230.3264125188844</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D41" t="n">
-        <v>223.1671349733107</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E41" t="n">
-        <v>225.9634246826172</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F41" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B42" t="n">
-        <v>227.3218898732066</v>
+        <v>222.9687986720664</v>
       </c>
       <c r="C42" t="n">
-        <v>229.1265900019938</v>
+        <v>226.7566624070738</v>
       </c>
       <c r="D42" t="n">
-        <v>221.4219354522067</v>
+        <v>220.0931953922465</v>
       </c>
       <c r="E42" t="n">
-        <v>223.4745178222656</v>
+        <v>225.1998748779297</v>
       </c>
       <c r="F42" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B43" t="n">
-        <v>222.9687986720664</v>
+        <v>225.4279539042935</v>
       </c>
       <c r="C43" t="n">
-        <v>226.7566624070738</v>
+        <v>226.9153381582893</v>
       </c>
       <c r="D43" t="n">
-        <v>220.0931953922465</v>
+        <v>223.1472950220756</v>
       </c>
       <c r="E43" t="n">
-        <v>225.1998748779297</v>
+        <v>224.9123382568359</v>
       </c>
       <c r="F43" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B44" t="n">
-        <v>225.4279691980636</v>
+        <v>224.8924975422598</v>
       </c>
       <c r="C44" t="n">
-        <v>226.9153535529684</v>
+        <v>232.656645001925</v>
       </c>
       <c r="D44" t="n">
-        <v>223.1473101611184</v>
+        <v>224.614853697738</v>
       </c>
       <c r="E44" t="n">
-        <v>224.912353515625</v>
+        <v>232.1509246826172</v>
       </c>
       <c r="F44" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B45" t="n">
-        <v>224.8925123239678</v>
+        <v>228.5712765635558</v>
       </c>
       <c r="C45" t="n">
-        <v>232.656660293954</v>
+        <v>230.8618608815026</v>
       </c>
       <c r="D45" t="n">
-        <v>224.6148684611971</v>
+        <v>224.0992136322821</v>
       </c>
       <c r="E45" t="n">
-        <v>232.1509399414062</v>
+        <v>226.2311248779297</v>
       </c>
       <c r="F45" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B46" t="n">
-        <v>228.5712765635558</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C46" t="n">
-        <v>230.8618608815026</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D46" t="n">
-        <v>224.0992136322821</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E46" t="n">
-        <v>226.2311248779297</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F46" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="n">
-        <v>227.0739873247604</v>
+        <v>226.7467645282661</v>
       </c>
       <c r="C47" t="n">
-        <v>230.6040433967966</v>
+        <v>232.2798356411572</v>
       </c>
       <c r="D47" t="n">
-        <v>226.7071040647147</v>
+        <v>226.6773611325171</v>
       </c>
       <c r="E47" t="n">
-        <v>228.6010284423828</v>
+        <v>230.8717803955078</v>
       </c>
       <c r="F47" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B48" t="n">
-        <v>226.7467795144244</v>
+        <v>231.0601885043919</v>
       </c>
       <c r="C48" t="n">
-        <v>232.2798509930075</v>
+        <v>234.6596480847597</v>
       </c>
       <c r="D48" t="n">
-        <v>226.6773761140884</v>
+        <v>229.67195413226</v>
       </c>
       <c r="E48" t="n">
-        <v>230.8717956542969</v>
+        <v>232.7359771728516</v>
       </c>
       <c r="F48" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B49" t="n">
-        <v>231.0602036533118</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="C49" t="n">
-        <v>234.6596634696697</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D49" t="n">
-        <v>229.6719691901636</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E49" t="n">
-        <v>232.7359924316406</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="F49" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B50" t="n">
-        <v>233.3805083869321</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C50" t="n">
-        <v>237.2477014354837</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D50" t="n">
-        <v>231.1990144844042</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E50" t="n">
-        <v>236.7122497558594</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F50" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B51" t="n">
-        <v>241.6404418420451</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C51" t="n">
-        <v>246.8760330652079</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D51" t="n">
-        <v>235.6016655641461</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E51" t="n">
-        <v>245.3787384033203</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F51" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B52" t="n">
-        <v>248.7203919866921</v>
+        <v>259.6774396530913</v>
       </c>
       <c r="C52" t="n">
-        <v>259.6774588065476</v>
+        <v>262.0572481860146</v>
       </c>
       <c r="D52" t="n">
-        <v>247.4015761578514</v>
+        <v>254.1840258460871</v>
       </c>
       <c r="E52" t="n">
-        <v>258.3784790039062</v>
+        <v>257.3471984863281</v>
       </c>
       <c r="F52" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B53" t="n">
-        <v>259.6774396530913</v>
+        <v>257.8132661327708</v>
       </c>
       <c r="C53" t="n">
-        <v>262.0572481860146</v>
+        <v>260.0443424743044</v>
       </c>
       <c r="D53" t="n">
-        <v>254.1840258460871</v>
+        <v>256.8216766476447</v>
       </c>
       <c r="E53" t="n">
-        <v>257.3471984863281</v>
+        <v>258.8246765136719</v>
       </c>
       <c r="F53" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B54" t="n">
-        <v>257.8132661327708</v>
+        <v>258.556940201721</v>
       </c>
       <c r="C54" t="n">
-        <v>260.0443424743044</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D54" t="n">
-        <v>256.8216766476447</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E54" t="n">
-        <v>258.8246765136719</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="F54" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B55" t="n">
-        <v>258.556940201721</v>
+        <v>261.2838154474661</v>
       </c>
       <c r="C55" t="n">
-        <v>263.6933661135803</v>
+        <v>265.6468028980126</v>
       </c>
       <c r="D55" t="n">
-        <v>256.9703910840639</v>
+        <v>258.5767654029829</v>
       </c>
       <c r="E55" t="n">
-        <v>261.9779357910156</v>
+        <v>260.1434936523438</v>
       </c>
       <c r="F55" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B56" t="n">
-        <v>261.283846098816</v>
+        <v>261.3036648523665</v>
       </c>
       <c r="C56" t="n">
-        <v>265.646834061187</v>
+        <v>262.2655079172122</v>
       </c>
       <c r="D56" t="n">
-        <v>258.5767957367673</v>
+        <v>258.7156306765648</v>
       </c>
       <c r="E56" t="n">
-        <v>260.1435241699219</v>
+        <v>260.0245361328125</v>
       </c>
       <c r="F56" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B57" t="n">
-        <v>261.3036648523665</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C57" t="n">
-        <v>262.2655079172122</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D57" t="n">
-        <v>258.7156306765648</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E57" t="n">
-        <v>260.0245361328125</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F57" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B58" t="n">
-        <v>259.013086162544</v>
+        <v>251.8637174841621</v>
       </c>
       <c r="C58" t="n">
-        <v>260.074094195654</v>
+        <v>253.7080744457603</v>
       </c>
       <c r="D58" t="n">
-        <v>250.9613842226157</v>
+        <v>249.9896140498327</v>
       </c>
       <c r="E58" t="n">
-        <v>252.4388580322266</v>
+        <v>252.7660675048828</v>
       </c>
       <c r="F58" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B59" t="n">
-        <v>251.8637326884788</v>
+        <v>254.1741282350202</v>
       </c>
       <c r="C59" t="n">
-        <v>253.7080897614157</v>
+        <v>259.7667076505979</v>
       </c>
       <c r="D59" t="n">
-        <v>249.989629141015</v>
+        <v>254.0948143882558</v>
       </c>
       <c r="E59" t="n">
-        <v>252.7660827636719</v>
+        <v>255.9689331054688</v>
       </c>
       <c r="F59" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,25 +1977,25 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B60" t="n">
-        <v>254.1741282350202</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C60" t="n">
-        <v>259.7667076505979</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D60" t="n">
-        <v>254.0948143882558</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E60" t="n">
-        <v>255.9689331054688</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F60" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2003,25 +2003,25 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B61" t="n">
-        <v>256.6601807669533</v>
+        <v>258.904790639318</v>
       </c>
       <c r="C61" t="n">
-        <v>258.2989382537239</v>
+        <v>260.2555449501942</v>
       </c>
       <c r="D61" t="n">
-        <v>254.4155616010984</v>
+        <v>253.7600731430874</v>
       </c>
       <c r="E61" t="n">
-        <v>256.0940551757812</v>
+        <v>258.1400451660156</v>
       </c>
       <c r="F61" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B62" t="n">
-        <v>258.9047600313309</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="C62" t="n">
-        <v>260.2555141825196</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D62" t="n">
-        <v>253.760043143314</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E62" t="n">
-        <v>258.1400146484375</v>
+        <v>262.827880859375</v>
       </c>
       <c r="F62" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B63" t="n">
-        <v>258.8451791646396</v>
+        <v>260.930890915143</v>
       </c>
       <c r="C63" t="n">
-        <v>262.827880859375</v>
+        <v>262.4405288782817</v>
       </c>
       <c r="D63" t="n">
-        <v>256.6502376986757</v>
+        <v>258.7458606831942</v>
       </c>
       <c r="E63" t="n">
-        <v>262.827880859375</v>
+        <v>261.6360473632812</v>
       </c>
       <c r="F63" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B64" t="n">
-        <v>260.930890915143</v>
+        <v>261.4374386085776</v>
       </c>
       <c r="C64" t="n">
-        <v>262.4405288782817</v>
+        <v>264.486509153036</v>
       </c>
       <c r="D64" t="n">
-        <v>258.7458606831942</v>
+        <v>260.7620463111714</v>
       </c>
       <c r="E64" t="n">
-        <v>261.6360473632812</v>
+        <v>263.45361328125</v>
       </c>
       <c r="F64" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B65" t="n">
-        <v>261.4374386085776</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="C65" t="n">
-        <v>264.486509153036</v>
+        <v>266.0855294787636</v>
       </c>
       <c r="D65" t="n">
-        <v>260.7620463111714</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="E65" t="n">
-        <v>263.45361328125</v>
+        <v>264.2679748535156</v>
       </c>
       <c r="F65" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B66" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C66" t="n">
-        <v>266.0855294787636</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D66" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E66" t="n">
-        <v>264.2679748535156</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F66" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B67" t="n">
-        <v>262.9073239460033</v>
+        <v>264.8440818513142</v>
       </c>
       <c r="C67" t="n">
-        <v>267.2773540092613</v>
+        <v>266.453045001104</v>
       </c>
       <c r="D67" t="n">
-        <v>262.9073239460033</v>
+        <v>263.5231220141856</v>
       </c>
       <c r="E67" t="n">
-        <v>264.4169921875</v>
+        <v>264.109130859375</v>
       </c>
       <c r="F67" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B68" t="n">
-        <v>264.8440512488132</v>
+        <v>263.4833740671746</v>
       </c>
       <c r="C68" t="n">
-        <v>266.4530142126886</v>
+        <v>264.2878555133287</v>
       </c>
       <c r="D68" t="n">
-        <v>263.5230915643202</v>
+        <v>262.5895091614203</v>
       </c>
       <c r="E68" t="n">
-        <v>264.1091003417969</v>
+        <v>263.10595703125</v>
       </c>
       <c r="F68" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B69" t="n">
-        <v>263.4833740671746</v>
+        <v>263.1953602739627</v>
       </c>
       <c r="C69" t="n">
-        <v>264.2878555133287</v>
+        <v>263.5727773382559</v>
       </c>
       <c r="D69" t="n">
-        <v>262.5895091614203</v>
+        <v>250.7606167452008</v>
       </c>
       <c r="E69" t="n">
-        <v>263.10595703125</v>
+        <v>251.8928527832031</v>
       </c>
       <c r="F69" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B70" t="n">
-        <v>263.1953602739627</v>
+        <v>251.8928411889898</v>
       </c>
       <c r="C70" t="n">
-        <v>263.5727773382559</v>
+        <v>257.8221866599169</v>
       </c>
       <c r="D70" t="n">
-        <v>250.7606167452008</v>
+        <v>250.5917647228683</v>
       </c>
       <c r="E70" t="n">
-        <v>251.8928527832031</v>
+        <v>254.5148773193359</v>
       </c>
       <c r="F70" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B71" t="n">
-        <v>251.8928562905814</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C71" t="n">
-        <v>257.8222021169872</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D71" t="n">
-        <v>250.5917797464572</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E71" t="n">
-        <v>254.514892578125</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F71" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B72" t="n">
-        <v>253.4620895509313</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="C72" t="n">
-        <v>261.7552171079225</v>
+        <v>266.0060550943219</v>
       </c>
       <c r="D72" t="n">
-        <v>253.2634545783159</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="E72" t="n">
-        <v>261.1096496582031</v>
+        <v>264.3077087402344</v>
       </c>
       <c r="F72" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B73" t="n">
-        <v>261.7055860975985</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C73" t="n">
-        <v>266.0060858079951</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D73" t="n">
-        <v>261.7055860975985</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E73" t="n">
-        <v>264.3077392578125</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F73" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B74" t="n">
-        <v>262.5994389217771</v>
+        <v>258.2293887773175</v>
       </c>
       <c r="C74" t="n">
-        <v>263.394009134812</v>
+        <v>259.2523732204683</v>
       </c>
       <c r="D74" t="n">
-        <v>258.6366203853271</v>
+        <v>254.7631655270811</v>
       </c>
       <c r="E74" t="n">
-        <v>258.7557983398438</v>
+        <v>258.1697998046875</v>
       </c>
       <c r="F74" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B75" t="n">
-        <v>258.2294193019395</v>
+        <v>257.2362444131007</v>
       </c>
       <c r="C75" t="n">
-        <v>259.2524038660146</v>
+        <v>259.778808728465</v>
       </c>
       <c r="D75" t="n">
-        <v>254.7631956419699</v>
+        <v>254.0282445272995</v>
       </c>
       <c r="E75" t="n">
-        <v>258.1698303222656</v>
+        <v>257.6335144042969</v>
       </c>
       <c r="F75" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B76" t="n">
-        <v>257.2362444131007</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C76" t="n">
-        <v>259.778808728465</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D76" t="n">
-        <v>254.0282445272995</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E76" t="n">
-        <v>257.6335144042969</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F76" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B77" t="n">
-        <v>255.9053572301452</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C77" t="n">
-        <v>259.1332249596227</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D77" t="n">
-        <v>238.7231659776434</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E77" t="n">
-        <v>239.4183959960938</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F77" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B78" t="n">
-        <v>237.5511941796288</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C78" t="n">
-        <v>240.5903685304685</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D78" t="n">
-        <v>234.849731125901</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E78" t="n">
-        <v>237.9385528564453</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F78" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="n">
-        <v>235.4059054123066</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C79" t="n">
-        <v>237.2135033883542</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D79" t="n">
-        <v>230.0923326840245</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E79" t="n">
-        <v>231.9396667480469</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F79" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B80" t="n">
-        <v>231.3636110626874</v>
+        <v>222.0176902636222</v>
       </c>
       <c r="C80" t="n">
-        <v>231.3636110626874</v>
+        <v>226.3877354418118</v>
       </c>
       <c r="D80" t="n">
-        <v>224.8979495180149</v>
+        <v>217.8661632569629</v>
       </c>
       <c r="E80" t="n">
-        <v>225.5633850097656</v>
+        <v>218.5713348388672</v>
       </c>
       <c r="F80" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="n">
-        <v>222.0176902636222</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="C81" t="n">
-        <v>226.3877354418118</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D81" t="n">
-        <v>217.8661632569629</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E81" t="n">
-        <v>218.5713348388672</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="F81" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B82" t="n">
-        <v>218.6507904829158</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C82" t="n">
-        <v>221.8687318042425</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D82" t="n">
-        <v>217.4689070154735</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E82" t="n">
-        <v>220.0710601806641</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F82" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="n">
-        <v>220.7265600038705</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="C83" t="n">
-        <v>227.162427221411</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D83" t="n">
-        <v>219.6042504088122</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E83" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="F83" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B84" t="n">
-        <v>225.2356384112152</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C84" t="n">
-        <v>229.2779291905748</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D84" t="n">
-        <v>225.1065188551059</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E84" t="n">
-        <v>226.4969940185547</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F84" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="n">
-        <v>227.8675783015932</v>
+        <v>230.3605061244008</v>
       </c>
       <c r="C85" t="n">
-        <v>229.3772313706373</v>
+        <v>234.1346314027617</v>
       </c>
       <c r="D85" t="n">
-        <v>226.0401123076792</v>
+        <v>224.7291202738612</v>
       </c>
       <c r="E85" t="n">
-        <v>227.8377838134766</v>
+        <v>226.9737243652344</v>
       </c>
       <c r="F85" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B86" t="n">
-        <v>230.3604906379282</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="C86" t="n">
-        <v>234.1346156625655</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D86" t="n">
-        <v>224.7291051659704</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E86" t="n">
-        <v>226.9737091064453</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="F86" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="n">
-        <v>227.8278625141174</v>
+        <v>215.1944745404488</v>
       </c>
       <c r="C87" t="n">
-        <v>230.2810431236355</v>
+        <v>215.8003210439947</v>
       </c>
       <c r="D87" t="n">
-        <v>226.1195744340916</v>
+        <v>207.358206080909</v>
       </c>
       <c r="E87" t="n">
-        <v>226.4076080322266</v>
+        <v>212.6221160888672</v>
       </c>
       <c r="F87" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="n">
-        <v>215.1944899838427</v>
+        <v>212.7015749295142</v>
       </c>
       <c r="C88" t="n">
-        <v>215.8003365308671</v>
+        <v>214.0821084291109</v>
       </c>
       <c r="D88" t="n">
-        <v>207.3582209619344</v>
+        <v>209.5928853669118</v>
       </c>
       <c r="E88" t="n">
-        <v>212.6221313476562</v>
+        <v>210.8442993164062</v>
       </c>
       <c r="F88" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="n">
-        <v>212.7015749295142</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C89" t="n">
-        <v>214.0821084291109</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D89" t="n">
-        <v>209.5928853669118</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E89" t="n">
-        <v>210.8442993164062</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F89" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B90" t="n">
-        <v>212.8902908724165</v>
+        <v>203.6039568110546</v>
       </c>
       <c r="C90" t="n">
-        <v>215.4129869027477</v>
+        <v>204.16014080488</v>
       </c>
       <c r="D90" t="n">
-        <v>208.3712731650351</v>
+        <v>191.7949279222085</v>
       </c>
       <c r="E90" t="n">
-        <v>209.3743896484375</v>
+        <v>195.0426635742188</v>
       </c>
       <c r="F90" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B91" t="n">
-        <v>203.6039568110546</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C91" t="n">
-        <v>204.16014080488</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D91" t="n">
-        <v>191.7949279222085</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E91" t="n">
-        <v>195.0426635742188</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F91" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B92" t="n">
-        <v>191.993558028148</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C92" t="n">
-        <v>199.3034370934686</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D92" t="n">
-        <v>186.0046234920971</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E92" t="n">
-        <v>198.0818176269531</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F92" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B93" t="n">
-        <v>192.668943558262</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C93" t="n">
-        <v>198.2010042649258</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5043431662378</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E93" t="n">
-        <v>188.6763153076172</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F93" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B94" t="n">
-        <v>190.3250127759971</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C94" t="n">
-        <v>193.2747884158856</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D94" t="n">
-        <v>185.8457159832669</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E94" t="n">
-        <v>190.0469207763672</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F94" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B95" t="n">
-        <v>188.0108792533576</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C95" t="n">
-        <v>193.8706944788449</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D95" t="n">
-        <v>184.465183505092</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E95" t="n">
-        <v>192.7086639404297</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F95" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B96" t="n">
-        <v>190.5931665112882</v>
+        <v>191.8346349441069</v>
       </c>
       <c r="C96" t="n">
-        <v>197.7441470694129</v>
+        <v>192.3510979672969</v>
       </c>
       <c r="D96" t="n">
-        <v>189.4510040038842</v>
+        <v>180.5718644212529</v>
       </c>
       <c r="E96" t="n">
-        <v>192.1326141357422</v>
+        <v>183.7401428222656</v>
       </c>
       <c r="F96" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B97" t="n">
-        <v>191.8346508751069</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C97" t="n">
-        <v>192.3511139411869</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D97" t="n">
-        <v>180.5718794169307</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E97" t="n">
-        <v>183.7401580810547</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F97" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B98" t="n">
-        <v>184.6936257308121</v>
+        <v>185.1703620229303</v>
       </c>
       <c r="C98" t="n">
-        <v>187.0375548215625</v>
+        <v>192.1326190686923</v>
       </c>
       <c r="D98" t="n">
-        <v>179.012577513483</v>
+        <v>183.0449358454951</v>
       </c>
       <c r="E98" t="n">
-        <v>184.1672210693359</v>
+        <v>188.4280242919922</v>
       </c>
       <c r="F98" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B99" t="n">
-        <v>185.1703620229303</v>
+        <v>189.6695058452945</v>
       </c>
       <c r="C99" t="n">
-        <v>192.1326190686923</v>
+        <v>191.6856804427425</v>
       </c>
       <c r="D99" t="n">
-        <v>183.0449358454951</v>
+        <v>181.9226203922807</v>
       </c>
       <c r="E99" t="n">
-        <v>188.4280242919922</v>
+        <v>183.0349884033203</v>
       </c>
       <c r="F99" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B100" t="n">
-        <v>189.6694900334161</v>
+        <v>182.6277925688313</v>
       </c>
       <c r="C100" t="n">
-        <v>191.6856644627849</v>
+        <v>186.8587767567783</v>
       </c>
       <c r="D100" t="n">
-        <v>181.9226052262247</v>
+        <v>180.6215444099069</v>
       </c>
       <c r="E100" t="n">
-        <v>183.0349731445312</v>
+        <v>186.5111541748047</v>
       </c>
       <c r="F100" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B101" t="n">
-        <v>182.6277776277465</v>
+        <v>185.3292747163753</v>
       </c>
       <c r="C101" t="n">
-        <v>186.8587614695496</v>
+        <v>185.6768821509354</v>
       </c>
       <c r="D101" t="n">
-        <v>180.6215296329567</v>
+        <v>181.9822138463991</v>
       </c>
       <c r="E101" t="n">
-        <v>186.5111389160156</v>
+        <v>184.0281829833984</v>
       </c>
       <c r="F101" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B102" t="n">
-        <v>185.3292593497056</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C102" t="n">
-        <v>185.6768667554436</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D102" t="n">
-        <v>181.9821987572526</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E102" t="n">
-        <v>184.0281677246094</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F102" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B103" t="n">
-        <v>184.0579771467211</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C103" t="n">
-        <v>190.4243134969296</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D103" t="n">
-        <v>182.4787935369736</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E103" t="n">
-        <v>183.8990631103516</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F103" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B104" t="n">
-        <v>180.0355685556146</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C104" t="n">
-        <v>181.2273936107796</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D104" t="n">
-        <v>173.3811981056387</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E104" t="n">
-        <v>176.9467468261719</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F104" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B105" t="n">
-        <v>176.4302852446972</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C105" t="n">
-        <v>187.3851706171715</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D105" t="n">
-        <v>175.0795461293982</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E105" t="n">
-        <v>184.1573028564453</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F105" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B106" t="n">
-        <v>181.7537853733346</v>
+        <v>195.4200513200664</v>
       </c>
       <c r="C106" t="n">
-        <v>191.2884162417558</v>
+        <v>199.6709031418322</v>
       </c>
       <c r="D106" t="n">
-        <v>181.0188192554131</v>
+        <v>190.0270371048119</v>
       </c>
       <c r="E106" t="n">
-        <v>190.4441986083984</v>
+        <v>198.1116027832031</v>
       </c>
       <c r="F106" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B107" t="n">
-        <v>195.420066371549</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C107" t="n">
-        <v>199.6709185207204</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D107" t="n">
-        <v>190.0270517409182</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E107" t="n">
-        <v>198.1116180419922</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F107" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B108" t="n">
-        <v>190.6031086414411</v>
+        <v>191.1890691316076</v>
       </c>
       <c r="C108" t="n">
-        <v>194.5857953386064</v>
+        <v>194.6056450515189</v>
       </c>
       <c r="D108" t="n">
-        <v>188.6266549601705</v>
+        <v>189.38145611275</v>
       </c>
       <c r="E108" t="n">
-        <v>193.4634857177734</v>
+        <v>191.6360015869141</v>
       </c>
       <c r="F108" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B109" t="n">
-        <v>191.1890691316076</v>
+        <v>189.4510095395255</v>
       </c>
       <c r="C109" t="n">
-        <v>194.6056450515189</v>
+        <v>197.3170732284266</v>
       </c>
       <c r="D109" t="n">
-        <v>189.38145611275</v>
+        <v>188.2889789535958</v>
       </c>
       <c r="E109" t="n">
-        <v>191.6360015869141</v>
+        <v>194.7149200439453</v>
       </c>
       <c r="F109" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B110" t="n">
-        <v>189.4510095395255</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C110" t="n">
-        <v>197.3170732284266</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D110" t="n">
-        <v>188.2889789535958</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E110" t="n">
-        <v>194.7149200439453</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F110" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B111" t="n">
-        <v>193.7713848635987</v>
+        <v>193.0364294600736</v>
       </c>
       <c r="C111" t="n">
-        <v>195.1320503828654</v>
+        <v>203.0279194939781</v>
       </c>
       <c r="D111" t="n">
-        <v>190.7918147128814</v>
+        <v>192.9172514970062</v>
       </c>
       <c r="E111" t="n">
-        <v>191.76513671875</v>
+        <v>200.0185546875</v>
       </c>
       <c r="F111" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B112" t="n">
-        <v>193.0364294600736</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C112" t="n">
-        <v>203.0279194939781</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D112" t="n">
-        <v>192.9172514970062</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E112" t="n">
-        <v>200.0185546875</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F112" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B113" t="n">
-        <v>199.4226244314719</v>
+        <v>197.2078193049057</v>
       </c>
       <c r="C113" t="n">
-        <v>201.5778601866405</v>
+        <v>202.2830212056148</v>
       </c>
       <c r="D113" t="n">
-        <v>196.0259162627038</v>
+        <v>194.5361355724457</v>
       </c>
       <c r="E113" t="n">
-        <v>200.733642578125</v>
+        <v>197.4362487792969</v>
       </c>
       <c r="F113" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B114" t="n">
-        <v>197.2078193049057</v>
+        <v>195.9166750362765</v>
       </c>
       <c r="C114" t="n">
-        <v>202.2830212056148</v>
+        <v>198.2109569133711</v>
       </c>
       <c r="D114" t="n">
-        <v>194.5361355724457</v>
+        <v>189.3020404418633</v>
       </c>
       <c r="E114" t="n">
-        <v>197.4362487792969</v>
+        <v>193.5826873779297</v>
       </c>
       <c r="F114" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B115" t="n">
-        <v>195.9166595935153</v>
+        <v>195.0625292691439</v>
       </c>
       <c r="C115" t="n">
-        <v>198.2109412897675</v>
+        <v>198.1910871721164</v>
       </c>
       <c r="D115" t="n">
-        <v>189.3020255204881</v>
+        <v>189.987327259986</v>
       </c>
       <c r="E115" t="n">
-        <v>193.5826721191406</v>
+        <v>192.8079986572266</v>
       </c>
       <c r="F115" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B116" t="n">
-        <v>195.0625292691439</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C116" t="n">
-        <v>198.1910871721164</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D116" t="n">
-        <v>189.987327259986</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E116" t="n">
-        <v>192.8079986572266</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F116" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B117" t="n">
-        <v>192.8079750209554</v>
+        <v>198.3698512203022</v>
       </c>
       <c r="C117" t="n">
-        <v>203.4648992272838</v>
+        <v>199.6312068702612</v>
       </c>
       <c r="D117" t="n">
-        <v>191.8346379323055</v>
+        <v>190.4441985938934</v>
       </c>
       <c r="E117" t="n">
-        <v>197.9228973388672</v>
+        <v>191.516845703125</v>
       </c>
       <c r="F117" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B118" t="n">
-        <v>198.3698512203022</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C118" t="n">
-        <v>199.6312068702612</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D118" t="n">
-        <v>190.4441985938934</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E118" t="n">
-        <v>191.516845703125</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F118" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B119" t="n">
-        <v>193.821025021851</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C119" t="n">
-        <v>197.2773371794379</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D119" t="n">
-        <v>193.821025021851</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E119" t="n">
-        <v>196.9893035888672</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F119" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B120" t="n">
-        <v>196.870136689126</v>
+        <v>192.0829546896537</v>
       </c>
       <c r="C120" t="n">
-        <v>201.0018110133274</v>
+        <v>194.8142273994103</v>
       </c>
       <c r="D120" t="n">
-        <v>193.1258058856387</v>
+        <v>191.3281356874407</v>
       </c>
       <c r="E120" t="n">
-        <v>193.9799499511719</v>
+        <v>193.0165557861328</v>
       </c>
       <c r="F120" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B121" t="n">
-        <v>192.0829395046699</v>
+        <v>194.2580295441802</v>
       </c>
       <c r="C121" t="n">
-        <v>194.8142119985075</v>
+        <v>199.0352710459927</v>
       </c>
       <c r="D121" t="n">
-        <v>191.3281205621285</v>
+        <v>191.9836310996653</v>
       </c>
       <c r="E121" t="n">
-        <v>193.0165405273438</v>
+        <v>193.6621246337891</v>
       </c>
       <c r="F121" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B122" t="n">
-        <v>194.2580448499211</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C122" t="n">
-        <v>199.0352867281362</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D122" t="n">
-        <v>191.9836462262046</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E122" t="n">
-        <v>193.6621398925781</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F122" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B123" t="n">
-        <v>191.8942484911283</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C123" t="n">
-        <v>194.3374874288811</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D123" t="n">
-        <v>188.7061018910339</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E123" t="n">
-        <v>194.0494689941406</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F123" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B124" t="n">
-        <v>195.7478267440036</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C124" t="n">
-        <v>196.7012958768407</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D124" t="n">
-        <v>190.6924929381777</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E124" t="n">
-        <v>193.850830078125</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F124" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B125" t="n">
-        <v>190.8315397252546</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="C125" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D125" t="n">
-        <v>181.0486114593648</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E125" t="n">
-        <v>181.7736511230469</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="F125" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B126" t="n">
-        <v>184.4353921172228</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C126" t="n">
-        <v>186.1138857525603</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D126" t="n">
-        <v>178.6252393274517</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E126" t="n">
-        <v>180.7208709716797</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F126" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B127" t="n">
-        <v>179.9461742219026</v>
+        <v>182.7469769199218</v>
       </c>
       <c r="C127" t="n">
-        <v>186.1933484091056</v>
+        <v>182.8562284362321</v>
       </c>
       <c r="D127" t="n">
-        <v>178.3074166263376</v>
+        <v>177.6022595179307</v>
       </c>
       <c r="E127" t="n">
-        <v>184.3758087158203</v>
+        <v>178.0889129638672</v>
       </c>
       <c r="F127" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B128" t="n">
-        <v>182.7469769199218</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C128" t="n">
-        <v>182.8562284362321</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D128" t="n">
-        <v>177.6022595179307</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E128" t="n">
-        <v>178.0889129638672</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F128" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" t="n">
-        <v>178.873523844959</v>
+        <v>183.6408226716892</v>
       </c>
       <c r="C129" t="n">
-        <v>185.1206822343098</v>
+        <v>187.2163126895138</v>
       </c>
       <c r="D129" t="n">
-        <v>178.3570608051074</v>
+        <v>181.0684642406058</v>
       </c>
       <c r="E129" t="n">
-        <v>183.7699432373047</v>
+        <v>185.3987731933594</v>
       </c>
       <c r="F129" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" t="n">
-        <v>183.6408226716892</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C130" t="n">
-        <v>187.2163126895138</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D130" t="n">
-        <v>181.0684642406058</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E130" t="n">
-        <v>185.3987731933594</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F130" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B131" t="n">
-        <v>185.5775567084869</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C131" t="n">
-        <v>187.6930410934417</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D131" t="n">
-        <v>181.7636956083204</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E131" t="n">
-        <v>184.9717102050781</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F131" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B132" t="n">
-        <v>184.0381169897925</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C132" t="n">
-        <v>186.3025890630262</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D132" t="n">
-        <v>180.3434488377003</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E132" t="n">
-        <v>185.9053039550781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F132" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" t="n">
-        <v>186.2231237330043</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C133" t="n">
-        <v>186.8587647224845</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D133" t="n">
-        <v>182.3496888213084</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E133" t="n">
-        <v>183.7699432373047</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F133" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" t="n">
-        <v>183.690504131923</v>
+        <v>185.2299504420264</v>
       </c>
       <c r="C134" t="n">
-        <v>185.3094088283374</v>
+        <v>185.4981160077481</v>
       </c>
       <c r="D134" t="n">
-        <v>180.7804644422889</v>
+        <v>174.5829515420302</v>
       </c>
       <c r="E134" t="n">
-        <v>181.7140655517578</v>
+        <v>175.1689300537109</v>
       </c>
       <c r="F134" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,25 +3927,25 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B135" t="n">
-        <v>185.2299504420264</v>
+        <v>172.4208720146844</v>
       </c>
       <c r="C135" t="n">
-        <v>185.4981160077481</v>
+        <v>173.5360220799356</v>
       </c>
       <c r="D135" t="n">
-        <v>174.5829515420302</v>
+        <v>166.3970410225636</v>
       </c>
       <c r="E135" t="n">
-        <v>175.1689300537109</v>
+        <v>170.1109161376953</v>
       </c>
       <c r="F135" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -3953,25 +3953,25 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B136" t="n">
-        <v>172.4208565486944</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C136" t="n">
-        <v>173.5360065139178</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D136" t="n">
-        <v>166.3970260969056</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E136" t="n">
-        <v>170.1109008789062</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F136" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B137" t="n">
-        <v>170.5191174814139</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C137" t="n">
-        <v>170.5191174814139</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D137" t="n">
-        <v>162.8126107290287</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E137" t="n">
-        <v>164.2463836669922</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F137" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B138" t="n">
-        <v>166.3273444705899</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C138" t="n">
-        <v>172.6498652447362</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D138" t="n">
-        <v>165.0528829680655</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E138" t="n">
-        <v>172.0723876953125</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F138" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B139" t="n">
-        <v>174.4520463656914</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C139" t="n">
-        <v>176.7321331165696</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D139" t="n">
-        <v>169.7624151908458</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E139" t="n">
-        <v>170.5689086914062</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F139" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B140" t="n">
-        <v>173.4663277892384</v>
+        <v>183.2040075329009</v>
       </c>
       <c r="C140" t="n">
-        <v>178.842961383224</v>
+        <v>183.7516312461474</v>
       </c>
       <c r="D140" t="n">
-        <v>172.1321282578628</v>
+        <v>177.7975052553062</v>
       </c>
       <c r="E140" t="n">
-        <v>176.8317108154297</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F140" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B141" t="n">
-        <v>183.2040230257668</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C141" t="n">
-        <v>183.7516467853238</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D141" t="n">
-        <v>177.7975202909648</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E141" t="n">
-        <v>180.4360504150391</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F141" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="n">
-        <v>184.6278268926657</v>
+        <v>181.7105075933097</v>
       </c>
       <c r="C142" t="n">
-        <v>187.1667986912511</v>
+        <v>188.1823886856741</v>
       </c>
       <c r="D142" t="n">
-        <v>180.2468672661974</v>
+        <v>181.3321466062204</v>
       </c>
       <c r="E142" t="n">
-        <v>181.3520660400391</v>
+        <v>185.4642028808594</v>
       </c>
       <c r="F142" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B143" t="n">
-        <v>181.7104926433502</v>
+        <v>185.7927641258556</v>
       </c>
       <c r="C143" t="n">
-        <v>188.1823732032504</v>
+        <v>192.7226462718077</v>
       </c>
       <c r="D143" t="n">
-        <v>181.33213168739</v>
+        <v>183.303579264538</v>
       </c>
       <c r="E143" t="n">
-        <v>185.4641876220703</v>
+        <v>186.3005523681641</v>
       </c>
       <c r="F143" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B144" t="n">
-        <v>185.7927793430547</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C144" t="n">
-        <v>192.7226620565929</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D144" t="n">
-        <v>183.3035942778625</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E144" t="n">
-        <v>186.3005676269531</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F144" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" t="n">
-        <v>187.3858431404722</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C145" t="n">
-        <v>190.3230783921826</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D145" t="n">
-        <v>186.2209063874661</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E145" t="n">
-        <v>188.9789276123047</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F145" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B146" t="n">
-        <v>176.7918740224492</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C146" t="n">
-        <v>178.0962045390804</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D146" t="n">
-        <v>169.9117629967484</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E146" t="n">
-        <v>172.5503082275391</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F146" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B147" t="n">
-        <v>174.8602617765654</v>
+        <v>177.4888508581443</v>
       </c>
       <c r="C147" t="n">
-        <v>177.6780209996891</v>
+        <v>183.4927641701262</v>
       </c>
       <c r="D147" t="n">
-        <v>173.6455382897692</v>
+        <v>176.7420953199099</v>
       </c>
       <c r="E147" t="n">
-        <v>177.3892822265625</v>
+        <v>179.4005432128906</v>
       </c>
       <c r="F147" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="n">
-        <v>177.4888357619529</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C148" t="n">
-        <v>183.4927485632761</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D148" t="n">
-        <v>176.7420802872333</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E148" t="n">
-        <v>179.4005279541016</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F148" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="n">
-        <v>181.6407975504903</v>
+        <v>178.424769515226</v>
       </c>
       <c r="C149" t="n">
-        <v>183.6221942474171</v>
+        <v>180.993610139636</v>
       </c>
       <c r="D149" t="n">
-        <v>180.5356140136719</v>
+        <v>176.5827818160244</v>
       </c>
       <c r="E149" t="n">
-        <v>180.5356140136719</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F149" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B150" t="n">
-        <v>178.4247846039299</v>
+        <v>177.5286741071897</v>
       </c>
       <c r="C150" t="n">
-        <v>180.993625445577</v>
+        <v>177.9169863526292</v>
       </c>
       <c r="D150" t="n">
-        <v>176.5827967489585</v>
+        <v>172.2515989617143</v>
       </c>
       <c r="E150" t="n">
-        <v>180.4360504150391</v>
+        <v>175.7663269042969</v>
       </c>
       <c r="F150" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B151" t="n">
-        <v>177.5286895189733</v>
+        <v>181.4018572311292</v>
       </c>
       <c r="C151" t="n">
-        <v>177.9170017981234</v>
+        <v>185.2351932001588</v>
       </c>
       <c r="D151" t="n">
-        <v>172.2516139153796</v>
+        <v>177.9767360752557</v>
       </c>
       <c r="E151" t="n">
-        <v>175.7663421630859</v>
+        <v>183.0248107910156</v>
       </c>
       <c r="F151" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="n">
-        <v>181.4018421076459</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C152" t="n">
-        <v>185.2351777570901</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D152" t="n">
-        <v>177.9767212373249</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E152" t="n">
-        <v>183.0247955322266</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F152" t="n">
-        <v>12324400</v>
+        <v>8444700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="n">
-        <v>183.4429710909726</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C153" t="n">
-        <v>189.4867039708132</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D153" t="n">
-        <v>183.1741348747832</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E153" t="n">
-        <v>184.6775970458984</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F153" t="n">
-        <v>8444700</v>
+        <v>9740800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="n">
-        <v>184.7473182824849</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C154" t="n">
-        <v>186.5793548412774</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D154" t="n">
-        <v>180.3165719120649</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E154" t="n">
-        <v>186.1810913085938</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F154" t="n">
-        <v>9740800</v>
+        <v>11303400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="n">
-        <v>184.7174439304337</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C155" t="n">
-        <v>186.2906106667237</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D155" t="n">
-        <v>178.8031379653169</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E155" t="n">
-        <v>180.4061737060547</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F155" t="n">
-        <v>11303400</v>
+        <v>13955100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="n">
-        <v>183.801426731489</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C156" t="n">
-        <v>187.7642050029951</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D156" t="n">
-        <v>183.2040162535504</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E156" t="n">
-        <v>185.5338897705078</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F156" t="n">
-        <v>13955100</v>
+        <v>15123900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B157" t="n">
-        <v>178.9027054786904</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C157" t="n">
-        <v>181.0832340725416</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D157" t="n">
-        <v>176.114830301217</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E157" t="n">
-        <v>181.0334625244141</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F157" t="n">
-        <v>15123900</v>
+        <v>11145000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B158" t="n">
-        <v>179.1317124775628</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C158" t="n">
-        <v>181.7105044839724</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D158" t="n">
-        <v>175.5472800106302</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E158" t="n">
-        <v>176.7221832275391</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F158" t="n">
-        <v>11145000</v>
+        <v>10214000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B159" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C159" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D159" t="n">
-        <v>169.8420709331304</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E159" t="n">
-        <v>170.5689086914062</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F159" t="n">
-        <v>10214000</v>
+        <v>11951900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B160" t="n">
-        <v>169.0455318751909</v>
+        <v>165.2818748478833</v>
       </c>
       <c r="C160" t="n">
-        <v>169.0455318751909</v>
+        <v>168.6173886402985</v>
       </c>
       <c r="D160" t="n">
-        <v>164.0372928300067</v>
+        <v>163.6191011830893</v>
       </c>
       <c r="E160" t="n">
-        <v>165.1225738525391</v>
+        <v>166.8550415039062</v>
       </c>
       <c r="F160" t="n">
-        <v>11951900</v>
+        <v>9749400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B161" t="n">
-        <v>165.2818899628073</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C161" t="n">
-        <v>168.6174040602531</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D161" t="n">
-        <v>163.6191161459536</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E161" t="n">
-        <v>166.8550567626953</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F161" t="n">
-        <v>9749400</v>
+        <v>13883400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B162" t="n">
-        <v>168.5178185348167</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C162" t="n">
-        <v>175.208748793394</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D162" t="n">
-        <v>168.268900043628</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E162" t="n">
-        <v>172.7593841552734</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F162" t="n">
-        <v>13883400</v>
+        <v>13671200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B163" t="n">
-        <v>172.1420794089453</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C163" t="n">
-        <v>179.9979467596552</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D163" t="n">
-        <v>171.0567983816156</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E163" t="n">
-        <v>178.7035675048828</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F163" t="n">
-        <v>13671200</v>
+        <v>17510800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B164" t="n">
-        <v>184.1996921538</v>
+        <v>175.2784431578192</v>
       </c>
       <c r="C164" t="n">
-        <v>186.6291391730516</v>
+        <v>179.529975364695</v>
       </c>
       <c r="D164" t="n">
-        <v>178.0364675908902</v>
+        <v>172.5901264135125</v>
       </c>
       <c r="E164" t="n">
-        <v>178.6438293457031</v>
+        <v>179.3208923339844</v>
       </c>
       <c r="F164" t="n">
-        <v>17510800</v>
+        <v>13025300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B165" t="n">
-        <v>175.2784580726278</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C165" t="n">
-        <v>179.5299906412754</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D165" t="n">
-        <v>172.5901410995666</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E165" t="n">
-        <v>179.3209075927734</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F165" t="n">
-        <v>13025300</v>
+        <v>10949100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B166" t="n">
-        <v>174.6213174256682</v>
+        <v>179.0619996775001</v>
       </c>
       <c r="C166" t="n">
-        <v>176.5728300297275</v>
+        <v>182.5568249684187</v>
       </c>
       <c r="D166" t="n">
-        <v>171.2459830488208</v>
+        <v>176.9113402973623</v>
       </c>
       <c r="E166" t="n">
-        <v>175.5472869873047</v>
+        <v>179.291015625</v>
       </c>
       <c r="F166" t="n">
-        <v>10949100</v>
+        <v>10176700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B167" t="n">
-        <v>179.0620149167984</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C167" t="n">
-        <v>182.5568405051486</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D167" t="n">
-        <v>176.9113553536261</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E167" t="n">
-        <v>179.2910308837891</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F167" t="n">
-        <v>10176700</v>
+        <v>13617200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B168" t="n">
-        <v>177.6581006500201</v>
+        <v>177.2299664024681</v>
       </c>
       <c r="C168" t="n">
-        <v>181.5711072848628</v>
+        <v>183.1243544731695</v>
       </c>
       <c r="D168" t="n">
-        <v>176.9113451663183</v>
+        <v>176.1247676896629</v>
       </c>
       <c r="E168" t="n">
-        <v>178.3052978515625</v>
+        <v>176.7420806884766</v>
       </c>
       <c r="F168" t="n">
-        <v>13617200</v>
+        <v>18524900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B169" t="n">
-        <v>177.2299817033781</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C169" t="n">
-        <v>183.1243702829636</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D169" t="n">
-        <v>176.1247828951571</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E169" t="n">
-        <v>176.7420959472656</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F169" t="n">
-        <v>18524900</v>
+        <v>22559400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B170" t="n">
-        <v>177.6581004088628</v>
+        <v>179.4602803383912</v>
       </c>
       <c r="C170" t="n">
-        <v>181.6905830539347</v>
+        <v>193.3001423298492</v>
       </c>
       <c r="D170" t="n">
-        <v>170.9074320607842</v>
+        <v>179.24123085138</v>
       </c>
       <c r="E170" t="n">
-        <v>175.4078826904297</v>
+        <v>190.2733001708984</v>
       </c>
       <c r="F170" t="n">
-        <v>22559400</v>
+        <v>33998900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>179.4602947300403</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C171" t="n">
-        <v>193.300157831373</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D171" t="n">
-        <v>179.2412452254626</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E171" t="n">
-        <v>190.2733154296875</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F171" t="n">
-        <v>33998900</v>
+        <v>27594800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B172" t="n">
-        <v>197.8901992931745</v>
+        <v>200.1503901074607</v>
       </c>
       <c r="C172" t="n">
-        <v>210.4257307870387</v>
+        <v>203.5058065985036</v>
       </c>
       <c r="D172" t="n">
-        <v>197.352542040295</v>
+        <v>194.9131351866423</v>
       </c>
       <c r="E172" t="n">
-        <v>208.6932678222656</v>
+        <v>199.9711608886719</v>
       </c>
       <c r="F172" t="n">
-        <v>27594800</v>
+        <v>19216600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="n">
-        <v>200.1504053799259</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C173" t="n">
-        <v>203.5058221270036</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D173" t="n">
-        <v>194.9131500594789</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E173" t="n">
-        <v>199.9711761474609</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F173" t="n">
-        <v>19216600</v>
+        <v>14154400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="n">
-        <v>196.4166079226038</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C174" t="n">
-        <v>196.8248227029743</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D174" t="n">
-        <v>188.9092176958791</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E174" t="n">
-        <v>189.7854156494141</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F174" t="n">
-        <v>14154400</v>
+        <v>14453600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B175" t="n">
-        <v>196.9542758894677</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C175" t="n">
-        <v>197.2330634002457</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D175" t="n">
-        <v>185.3048928689384</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E175" t="n">
-        <v>187.9334716796875</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F175" t="n">
-        <v>14453600</v>
+        <v>13183900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B176" t="n">
-        <v>188.9789318725711</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C176" t="n">
-        <v>191.6771999565016</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D176" t="n">
-        <v>184.0304307819904</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E176" t="n">
-        <v>184.8568420410156</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F176" t="n">
-        <v>13183900</v>
+        <v>11177800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B177" t="n">
-        <v>183.1144169895118</v>
+        <v>178.7234870391233</v>
       </c>
       <c r="C177" t="n">
-        <v>184.2196157855271</v>
+        <v>181.6706888305526</v>
       </c>
       <c r="D177" t="n">
-        <v>180.92393713233</v>
+        <v>170.8178328696119</v>
       </c>
       <c r="E177" t="n">
-        <v>181.7602996826172</v>
+        <v>174.5914459228516</v>
       </c>
       <c r="F177" t="n">
-        <v>11177800</v>
+        <v>15427800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B178" t="n">
-        <v>178.7234714192057</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C178" t="n">
-        <v>181.670672953058</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D178" t="n">
-        <v>170.8178179406258</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E178" t="n">
-        <v>174.5914306640625</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F178" t="n">
-        <v>15427800</v>
+        <v>10820500</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B179" t="n">
-        <v>169.861995238658</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C179" t="n">
-        <v>174.7706609037228</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D179" t="n">
-        <v>169.2944537502145</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E179" t="n">
-        <v>170.1806030273438</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F179" t="n">
-        <v>10820500</v>
+        <v>16666000</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B180" t="n">
-        <v>167.9744954285649</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C180" t="n">
-        <v>168.6832400259219</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D180" t="n">
-        <v>163.0231992739924</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E180" t="n">
-        <v>166.1576843261719</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F180" t="n">
-        <v>16666000</v>
+        <v>13589400</v>
       </c>
       <c r="G180" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B181" t="n">
-        <v>164.4506890531704</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C181" t="n">
-        <v>166.2475157071144</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D181" t="n">
-        <v>161.1165431857153</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E181" t="n">
-        <v>165.5986633300781</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F181" t="n">
-        <v>13589400</v>
+        <v>13541800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="n">
-        <v>165.7384133733495</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C182" t="n">
-        <v>169.6515271583533</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D182" t="n">
-        <v>163.8816793355271</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E182" t="n">
-        <v>164.2610168457031</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F182" t="n">
-        <v>13541800</v>
+        <v>16385300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B183" t="n">
-        <v>163.7718739013043</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C183" t="n">
-        <v>166.0079454764833</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D183" t="n">
-        <v>160.2181284427459</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E183" t="n">
-        <v>161.4260101318359</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F183" t="n">
-        <v>16385300</v>
+        <v>19986200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B184" t="n">
-        <v>159.9685677271403</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C184" t="n">
-        <v>161.1464880907799</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D184" t="n">
-        <v>153.959135832121</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E184" t="n">
-        <v>154.7477569580078</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F184" t="n">
-        <v>19986200</v>
+        <v>57940800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B185" t="n">
-        <v>152.4617715583163</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C185" t="n">
-        <v>154.1987212566731</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D185" t="n">
-        <v>149.5369245308901</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E185" t="n">
-        <v>151.5134429931641</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F185" t="n">
-        <v>57940800</v>
+        <v>20502800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B186" t="n">
-        <v>149.8962920415152</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C186" t="n">
-        <v>153.5997679942281</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D186" t="n">
-        <v>146.0630395211035</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E186" t="n">
-        <v>149.8563537597656</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F186" t="n">
-        <v>20502800</v>
+        <v>20720700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B187" t="n">
-        <v>151.3836627210609</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C187" t="n">
-        <v>154.907462036052</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D187" t="n">
-        <v>150.5850798848861</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E187" t="n">
-        <v>153.1505584716797</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F187" t="n">
-        <v>20720700</v>
+        <v>13146800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B188" t="n">
-        <v>151.5433859321397</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C188" t="n">
-        <v>156.7841657815476</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D188" t="n">
-        <v>150.135858545478</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E188" t="n">
-        <v>152.4917144775391</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F188" t="n">
-        <v>13146800</v>
+        <v>11324700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B189" t="n">
-        <v>149.7465472087312</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C189" t="n">
-        <v>153.7295454610107</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D189" t="n">
-        <v>148.5187115976041</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E189" t="n">
-        <v>149.9262390136719</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F189" t="n">
-        <v>11324700</v>
+        <v>21267900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B190" t="n">
-        <v>151.2239658596097</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C190" t="n">
-        <v>158.1817266914859</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D190" t="n">
-        <v>151.2239658596097</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E190" t="n">
-        <v>158.0918731689453</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F190" t="n">
-        <v>21267900</v>
+        <v>12664100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B191" t="n">
-        <v>159.9885357004027</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C191" t="n">
-        <v>161.4759091917036</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D191" t="n">
-        <v>157.4230418613804</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E191" t="n">
-        <v>157.6526336669922</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F191" t="n">
-        <v>12664100</v>
+        <v>13690500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B192" t="n">
-        <v>154.8176224085462</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C192" t="n">
-        <v>157.4130622995693</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D192" t="n">
-        <v>153.7994247316601</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E192" t="n">
-        <v>156.3848724365234</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F192" t="n">
-        <v>13690500</v>
+        <v>14164600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B193" t="n">
-        <v>161.9351081174896</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C193" t="n">
-        <v>165.5187996520913</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D193" t="n">
-        <v>160.916895191227</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E193" t="n">
-        <v>162.9433288574219</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F193" t="n">
-        <v>14164600</v>
+        <v>10486300</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B194" t="n">
-        <v>162.7137441629</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C194" t="n">
-        <v>166.9163573859938</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D194" t="n">
-        <v>161.7155003336798</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E194" t="n">
-        <v>165.8182830810547</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F194" t="n">
-        <v>10486300</v>
+        <v>10595500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B195" t="n">
-        <v>163.7020118941432</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C195" t="n">
-        <v>167.425457131665</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D195" t="n">
-        <v>162.0848465245878</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E195" t="n">
-        <v>165.3590850830078</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F195" t="n">
-        <v>10595500</v>
+        <v>13057900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B196" t="n">
-        <v>168.9228138583306</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C196" t="n">
-        <v>172.0772678623225</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D196" t="n">
-        <v>167.3855099055031</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E196" t="n">
-        <v>169.2222900390625</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F196" t="n">
-        <v>13057900</v>
+        <v>9792400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B197" t="n">
-        <v>167.0760662569272</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C197" t="n">
-        <v>167.2357889266519</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D197" t="n">
-        <v>164.4906183727253</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E197" t="n">
-        <v>166.2874603271484</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F197" t="n">
-        <v>9792400</v>
+        <v>13858600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B198" t="n">
-        <v>158.05194011754</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C198" t="n">
-        <v>163.5123348335076</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D198" t="n">
-        <v>156.2051830247059</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E198" t="n">
-        <v>162.2146148681641</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F198" t="n">
-        <v>13858600</v>
+        <v>8321500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B199" t="n">
-        <v>165.309182555471</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C199" t="n">
-        <v>166.007950182526</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D199" t="n">
-        <v>162.1347592897187</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E199" t="n">
-        <v>163.0331878662109</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F199" t="n">
-        <v>8321500</v>
+        <v>14020700</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>165.6286161244176</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C200" t="n">
-        <v>172.4566003351415</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D200" t="n">
-        <v>165.6286161244176</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E200" t="n">
-        <v>170.9193115234375</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F200" t="n">
-        <v>14020700</v>
+        <v>13507900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>162.2046435717354</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C201" t="n">
-        <v>171.049084414024</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D201" t="n">
-        <v>161.1864306117812</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E201" t="n">
-        <v>167.2657318115234</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F201" t="n">
-        <v>13507900</v>
+        <v>13328100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>170.2205331766167</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C202" t="n">
-        <v>172.4965277703878</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D202" t="n">
-        <v>166.2674811162824</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E202" t="n">
-        <v>166.7067108154297</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F202" t="n">
-        <v>13328100</v>
+        <v>12057500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B203" t="n">
-        <v>170.5399744864679</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C203" t="n">
-        <v>174.2334736592566</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D203" t="n">
-        <v>166.5869373980102</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E203" t="n">
-        <v>172.3767395019531</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F203" t="n">
-        <v>12057500</v>
+        <v>10191500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B204" t="n">
-        <v>171.1988064601764</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C204" t="n">
-        <v>175.1218971627477</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D204" t="n">
-        <v>169.4518798636439</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E204" t="n">
-        <v>170.4700927734375</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F204" t="n">
-        <v>10191500</v>
+        <v>13426500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B205" t="n">
-        <v>167.5652084388413</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C205" t="n">
-        <v>175.0819831940494</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D205" t="n">
-        <v>166.2075962327059</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E205" t="n">
-        <v>173.4847869873047</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F205" t="n">
-        <v>13426500</v>
+        <v>12831800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B206" t="n">
-        <v>166.7666058963373</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C206" t="n">
-        <v>172.1271701993457</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D206" t="n">
-        <v>166.6368293287962</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E206" t="n">
-        <v>169.7613372802734</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F206" t="n">
-        <v>12831800</v>
+        <v>12194500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B207" t="n">
-        <v>169.1723839486806</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C207" t="n">
-        <v>169.272214424985</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D207" t="n">
-        <v>161.925139189555</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E207" t="n">
-        <v>162.7137451171875</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F207" t="n">
-        <v>12194500</v>
+        <v>12775000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B208" t="n">
-        <v>164.7601382451291</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C208" t="n">
-        <v>165.5886824068968</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D208" t="n">
-        <v>154.877515725338</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E208" t="n">
-        <v>156.6543884277344</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F208" t="n">
-        <v>12775000</v>
+        <v>10899100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B209" t="n">
-        <v>160.0983505627206</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C209" t="n">
-        <v>164.1611950360997</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D209" t="n">
-        <v>159.2698063547753</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E209" t="n">
-        <v>163.3725891113281</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F209" t="n">
-        <v>10899100</v>
+        <v>17312000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B210" t="n">
-        <v>167.7049639405646</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C210" t="n">
-        <v>176.6392431993331</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D210" t="n">
-        <v>166.8464736349225</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E210" t="n">
-        <v>173.2951354980469</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F210" t="n">
-        <v>17312000</v>
+        <v>17204600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B211" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C211" t="n">
-        <v>184.2158982492034</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D211" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E211" t="n">
-        <v>181.1812438964844</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F211" t="n">
-        <v>17204600</v>
+        <v>18139500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B212" t="n">
-        <v>181.6903554713178</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C212" t="n">
-        <v>189.8460057999592</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D212" t="n">
-        <v>181.6903554713178</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E212" t="n">
-        <v>188.0491790771484</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F212" t="n">
-        <v>18139500</v>
+        <v>12182400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B213" t="n">
-        <v>180.6721461984077</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C213" t="n">
-        <v>182.1894657683464</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D213" t="n">
-        <v>175.5910738107855</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E213" t="n">
-        <v>180.3926391601562</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F213" t="n">
-        <v>12182400</v>
+        <v>9691500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B214" t="n">
-        <v>177.3879151720665</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C214" t="n">
-        <v>184.1260606305619</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D214" t="n">
-        <v>176.719093672914</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E214" t="n">
-        <v>183.6968231201172</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F214" t="n">
-        <v>9691500</v>
+        <v>12908000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B215" t="n">
-        <v>188.658097974018</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C215" t="n">
-        <v>193.3598176605707</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D215" t="n">
-        <v>185.5735131091938</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E215" t="n">
-        <v>185.6234283447266</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F215" t="n">
-        <v>12908000</v>
+        <v>9326900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B216" t="n">
-        <v>182.7684517177381</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C216" t="n">
-        <v>190.9540477431734</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D216" t="n">
-        <v>182.6786134323838</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E216" t="n">
-        <v>190.6545867919922</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F216" t="n">
-        <v>9326900</v>
+        <v>9605500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B217" t="n">
-        <v>192.9405589477455</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C217" t="n">
-        <v>194.5976472985604</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D217" t="n">
-        <v>190.0955580470331</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E217" t="n">
-        <v>192.6410827636719</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F217" t="n">
-        <v>9605500</v>
+        <v>13297600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B218" t="n">
-        <v>183.117847615437</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C218" t="n">
-        <v>186.6915622961891</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D218" t="n">
-        <v>182.6786179003067</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E218" t="n">
-        <v>186.4420013427734</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F218" t="n">
-        <v>13297600</v>
+        <v>11392800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B219" t="n">
-        <v>190.7544083295565</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C219" t="n">
-        <v>194.3580691369978</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D219" t="n">
-        <v>190.2652786051507</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E219" t="n">
-        <v>192.4015197753906</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F219" t="n">
-        <v>11392800</v>
+        <v>9706600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B220" t="n">
-        <v>189.8360257192551</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C220" t="n">
-        <v>197.831953246477</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D220" t="n">
-        <v>189.666326097428</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E220" t="n">
-        <v>197.1631317138672</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F220" t="n">
-        <v>9706600</v>
+        <v>11171600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B221" t="n">
-        <v>196.5941314807131</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C221" t="n">
-        <v>199.0398256830038</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D221" t="n">
-        <v>195.1566580076304</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E221" t="n">
-        <v>197.1231994628906</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F221" t="n">
-        <v>11171600</v>
+        <v>12787900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B222" t="n">
-        <v>191.6628101365335</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C222" t="n">
-        <v>196.1549072491085</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D222" t="n">
-        <v>191.4431952813594</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E222" t="n">
-        <v>192.9804992675781</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F222" t="n">
-        <v>12787900</v>
+        <v>15058700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="n">
-        <v>196.4943140399408</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C223" t="n">
-        <v>202.6335228023228</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D223" t="n">
-        <v>191.0538881519706</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E223" t="n">
-        <v>201.016357421875</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F223" t="n">
-        <v>15058700</v>
+        <v>8664800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B224" t="n">
-        <v>202.3939250564146</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C224" t="n">
-        <v>204.0410211897246</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D224" t="n">
-        <v>194.9769811314243</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E224" t="n">
-        <v>195.8654174804688</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F224" t="n">
-        <v>8664800</v>
+        <v>14378800</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B225" t="n">
-        <v>193.4896063018435</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C225" t="n">
-        <v>194.5976575790598</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D225" t="n">
-        <v>189.57649225733</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E225" t="n">
-        <v>190.6346282958984</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F225" t="n">
-        <v>14378800</v>
+        <v>14152900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B226" t="n">
-        <v>193.7491445531879</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C226" t="n">
-        <v>199.0598091290667</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D226" t="n">
-        <v>192.8906542357335</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E226" t="n">
-        <v>195.7955474853516</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F226" t="n">
-        <v>14152900</v>
+        <v>17843600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B227" t="n">
-        <v>193.8689320609861</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C227" t="n">
-        <v>207.5847919095016</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D227" t="n">
-        <v>193.8689320609861</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E227" t="n">
-        <v>205.7280578613281</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F227" t="n">
-        <v>17843600</v>
+        <v>11482300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="n">
-        <v>204.8595912018172</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C228" t="n">
-        <v>207.5149233311111</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D228" t="n">
-        <v>202.6434887759544</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E228" t="n">
-        <v>205.0692138671875</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F228" t="n">
-        <v>11482300</v>
+        <v>9685400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B229" t="n">
-        <v>205.2189664215684</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C229" t="n">
-        <v>210.6993304789719</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D229" t="n">
-        <v>204.3704530814486</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E229" t="n">
-        <v>208.8026580810547</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F229" t="n">
-        <v>9685400</v>
+        <v>9580200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B230" t="n">
-        <v>208.0539803833292</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C230" t="n">
-        <v>212.7956386479058</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D230" t="n">
-        <v>207.0257904413594</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E230" t="n">
-        <v>208.6928558349609</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F230" t="n">
-        <v>9580200</v>
+        <v>10081800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B231" t="n">
-        <v>205.4884885298704</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C231" t="n">
-        <v>209.9406472657768</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D231" t="n">
-        <v>204.400391231641</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E231" t="n">
-        <v>205.3287658691406</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F231" t="n">
-        <v>10081800</v>
+        <v>14888900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B232" t="n">
-        <v>199.5888632714973</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C232" t="n">
-        <v>206.0774478239803</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D232" t="n">
-        <v>198.6005964484484</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E232" t="n">
-        <v>205.2588806152344</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F232" t="n">
-        <v>14888900</v>
+        <v>55517500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" t="n">
-        <v>229.6459965412689</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C233" t="n">
-        <v>254.0330860396483</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D233" t="n">
-        <v>229.6459965412689</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E233" t="n">
-        <v>251.6073608398438</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F233" t="n">
-        <v>55517500</v>
+        <v>34362700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B234" t="n">
-        <v>250.0301279952546</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C234" t="n">
-        <v>263.0671897003631</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D234" t="n">
-        <v>248.5627083778381</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E234" t="n">
-        <v>255.5504150390625</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F234" t="n">
-        <v>34362700</v>
+        <v>22471500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B235" t="n">
-        <v>253.9432305236259</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C235" t="n">
-        <v>261.8193732125837</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D235" t="n">
-        <v>253.9432305236259</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E235" t="n">
-        <v>257.0877075195312</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F235" t="n">
-        <v>22471500</v>
+        <v>15897500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B236" t="n">
-        <v>254.5621609406893</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C236" t="n">
-        <v>261.8593363431507</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D236" t="n">
-        <v>253.8035010915435</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E236" t="n">
-        <v>257.6567077636719</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F236" t="n">
-        <v>15897500</v>
+        <v>14393700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B237" t="n">
-        <v>258.9244691424316</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C237" t="n">
-        <v>264.0853722779391</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D237" t="n">
-        <v>253.154621477229</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E237" t="n">
-        <v>256.478759765625</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F237" t="n">
-        <v>14393700</v>
+        <v>16028300</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B238" t="n">
-        <v>261.5199276025597</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C238" t="n">
-        <v>267.7988593124239</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D238" t="n">
-        <v>261.1405900757476</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E238" t="n">
-        <v>263.9656066894531</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F238" t="n">
-        <v>16028300</v>
+        <v>10490600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B239" t="n">
-        <v>262.8974710364521</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C239" t="n">
-        <v>263.1370702625856</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D239" t="n">
-        <v>257.3672223502596</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E239" t="n">
-        <v>258.7747497558594</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F239" t="n">
-        <v>10490600</v>
+        <v>17482700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B240" t="n">
-        <v>253.2744227737308</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C240" t="n">
-        <v>253.5539298242691</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D240" t="n">
-        <v>245.4581718493405</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E240" t="n">
-        <v>248.6824951171875</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F240" t="n">
-        <v>17482700</v>
+        <v>11853700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B241" t="n">
-        <v>249.3413418635835</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C241" t="n">
-        <v>254.3525301395604</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D241" t="n">
-        <v>243.0224566114913</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E241" t="n">
-        <v>243.7312164306641</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F241" t="n">
-        <v>11853700</v>
+        <v>10732600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B242" t="n">
-        <v>244.9191211985708</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C242" t="n">
-        <v>248.0635830600566</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D242" t="n">
-        <v>241.3254374437371</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E242" t="n">
-        <v>242.5732421875</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F242" t="n">
-        <v>10732600</v>
+        <v>9738300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B243" t="n">
-        <v>241.5949712138984</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C243" t="n">
-        <v>250.1099896964979</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D243" t="n">
-        <v>241.5949712138984</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E243" t="n">
-        <v>247.2849578857422</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F243" t="n">
-        <v>9738300</v>
+        <v>12963700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" t="n">
-        <v>255.3008656803045</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C244" t="n">
-        <v>259.7230786425112</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D244" t="n">
-        <v>251.0583293004754</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E244" t="n">
-        <v>258.9743957519531</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F244" t="n">
-        <v>12963700</v>
+        <v>11502800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B245" t="n">
-        <v>256.43886230448</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C245" t="n">
-        <v>261.8792726915332</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D245" t="n">
-        <v>254.632028246405</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E245" t="n">
-        <v>255.2010192871094</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F245" t="n">
-        <v>11502800</v>
+        <v>9423800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,25 +6813,25 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B246" t="n">
-        <v>251.4077029961344</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C246" t="n">
-        <v>255.9497000259878</v>
+        <v>247</v>
       </c>
       <c r="D246" t="n">
-        <v>249.1616544830015</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E246" t="n">
-        <v>250.0999908447266</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F246" t="n">
-        <v>9423800</v>
+        <v>16611300</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -6839,25 +6839,25 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B247" t="n">
-        <v>244.1799926757812</v>
+        <v>244.25</v>
       </c>
       <c r="C247" t="n">
-        <v>247</v>
+        <v>244.25</v>
       </c>
       <c r="D247" t="n">
-        <v>241.5200042724609</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E247" t="n">
-        <v>242.8500061035156</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F247" t="n">
-        <v>16611300</v>
+        <v>21962400</v>
       </c>
       <c r="G247" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B248" t="n">
-        <v>244.25</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C248" t="n">
-        <v>244.25</v>
+        <v>241.3399963378906</v>
       </c>
       <c r="D248" t="n">
-        <v>236.5500030517578</v>
+        <v>236.25</v>
       </c>
       <c r="E248" t="n">
-        <v>237.9199981689453</v>
+        <v>236.4199981689453</v>
       </c>
       <c r="F248" t="n">
-        <v>21962400</v>
+        <v>10581900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B249" t="n">
-        <v>239.8000030517578</v>
+        <v>241.5</v>
       </c>
       <c r="C249" t="n">
-        <v>241.3399963378906</v>
+        <v>242.4400024414062</v>
       </c>
       <c r="D249" t="n">
-        <v>236.25</v>
+        <v>229.8099975585938</v>
       </c>
       <c r="E249" t="n">
-        <v>236.4199981689453</v>
+        <v>233.2799987792969</v>
       </c>
       <c r="F249" t="n">
-        <v>10581900</v>
+        <v>13635600</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6958,12 +6958,38 @@
         <v>238.2200012207031</v>
       </c>
       <c r="F251" t="n">
-        <v>11060900</v>
+        <v>11074000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
       </c>
       <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B252" t="n">
+        <v>237.0299987792969</v>
+      </c>
+      <c r="C252" t="n">
+        <v>239.3699951171875</v>
+      </c>
+      <c r="D252" t="n">
+        <v>233.3800048828125</v>
+      </c>
+      <c r="E252" t="n">
+        <v>234.0200042724609</v>
+      </c>
+      <c r="F252" t="n">
+        <v>8735500</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10628,34 +10654,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>234.02</v>
+      </c>
+      <c r="D2" t="n">
         <v>238.22</v>
       </c>
-      <c r="D2" t="n">
-        <v>237.58</v>
-      </c>
       <c r="E2" t="n">
-        <v>240.64</v>
+        <v>237.03</v>
       </c>
       <c r="F2" t="n">
-        <v>242.01</v>
+        <v>239.37</v>
       </c>
       <c r="G2" t="n">
-        <v>237</v>
+        <v>233.38</v>
       </c>
       <c r="H2" t="n">
-        <v>9447985</v>
+        <v>8483000</v>
       </c>
       <c r="I2" t="n">
-        <v>14015952</v>
+        <v>13894941</v>
       </c>
       <c r="J2" t="n">
-        <v>196055056384</v>
+        <v>192598458368</v>
       </c>
       <c r="K2" t="n">
-        <v>21.735401</v>
+        <v>21.35219</v>
       </c>
       <c r="L2" t="n">
-        <v>14.882481</v>
+        <v>14.620091</v>
       </c>
       <c r="M2" t="n">
         <v>10.96</v>
@@ -10694,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.108509</v>
+        <v>5.018442</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10706,7 +10732,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>227028058112</v>
+        <v>223571460096</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10733,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:29:36</t>
+          <t>2026-09-26 14:50:09</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>238.6656687083941</v>
+        <v>242.6617958656146</v>
       </c>
       <c r="C2" t="n">
-        <v>242.4733685900855</v>
+        <v>243.7525504227033</v>
       </c>
       <c r="D2" t="n">
-        <v>238.3285319244896</v>
+        <v>240.8273491460897</v>
       </c>
       <c r="E2" t="n">
-        <v>241.3826141357422</v>
+        <v>243.0386047363281</v>
       </c>
       <c r="F2" t="n">
-        <v>4974600</v>
+        <v>6373500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>242.6617958656146</v>
+        <v>242.989012448683</v>
       </c>
       <c r="C3" t="n">
-        <v>243.7525504227033</v>
+        <v>243.1476704015903</v>
       </c>
       <c r="D3" t="n">
-        <v>240.8273491460897</v>
+        <v>233.8267199294288</v>
       </c>
       <c r="E3" t="n">
-        <v>243.0386047363281</v>
+        <v>235.0067138671875</v>
       </c>
       <c r="F3" t="n">
-        <v>6373500</v>
+        <v>10801100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>242.989028225756</v>
+        <v>234.5010077854061</v>
       </c>
       <c r="C4" t="n">
-        <v>243.1476861889649</v>
+        <v>240.4307087963897</v>
       </c>
       <c r="D4" t="n">
-        <v>233.8267351116018</v>
+        <v>231.5460601627856</v>
       </c>
       <c r="E4" t="n">
-        <v>235.0067291259766</v>
+        <v>233.7077331542969</v>
       </c>
       <c r="F4" t="n">
-        <v>10801100</v>
+        <v>10016600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>234.5010077854061</v>
+        <v>233.4498996394798</v>
       </c>
       <c r="C5" t="n">
-        <v>240.4307087963897</v>
+        <v>237.3865110117534</v>
       </c>
       <c r="D5" t="n">
-        <v>231.5460601627856</v>
+        <v>231.6353042398812</v>
       </c>
       <c r="E5" t="n">
-        <v>233.7077331542969</v>
+        <v>236.8708953857422</v>
       </c>
       <c r="F5" t="n">
-        <v>10016600</v>
+        <v>7679200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>233.4499146778946</v>
+        <v>236.7419803274875</v>
       </c>
       <c r="C6" t="n">
-        <v>237.3865263037574</v>
+        <v>240.7678310589901</v>
       </c>
       <c r="D6" t="n">
-        <v>231.6353191614031</v>
+        <v>236.4940829658881</v>
       </c>
       <c r="E6" t="n">
-        <v>236.8709106445312</v>
+        <v>238.3384399414062</v>
       </c>
       <c r="F6" t="n">
-        <v>7679200</v>
+        <v>8849800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>236.7419803274875</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="C7" t="n">
-        <v>240.7678310589901</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D7" t="n">
-        <v>236.4940829658881</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E7" t="n">
-        <v>238.3384399414062</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="F7" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>237.3171110157645</v>
+        <v>244.4069666278678</v>
       </c>
       <c r="C8" t="n">
-        <v>248.3634171689519</v>
+        <v>245.2795701971395</v>
       </c>
       <c r="D8" t="n">
-        <v>233.430082086989</v>
+        <v>235.5520799850208</v>
       </c>
       <c r="E8" t="n">
-        <v>243.7128601074219</v>
+        <v>237.7236633300781</v>
       </c>
       <c r="F8" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>244.4069666278678</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C9" t="n">
-        <v>245.2795701971395</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D9" t="n">
-        <v>235.5520799850208</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E9" t="n">
-        <v>237.7236633300781</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F9" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>237.7236529240558</v>
+        <v>237.2576026687149</v>
       </c>
       <c r="C10" t="n">
-        <v>239.2903660228245</v>
+        <v>243.8913382509171</v>
       </c>
       <c r="D10" t="n">
-        <v>233.6680406983684</v>
+        <v>235.1554228281352</v>
       </c>
       <c r="E10" t="n">
-        <v>238.4078369140625</v>
+        <v>243.2666320800781</v>
       </c>
       <c r="F10" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>237.2576175505903</v>
+        <v>244.4466434616172</v>
       </c>
       <c r="C11" t="n">
-        <v>243.8913535488906</v>
+        <v>246.9553636418975</v>
       </c>
       <c r="D11" t="n">
-        <v>235.1554375781523</v>
+        <v>238.6954214370453</v>
       </c>
       <c r="E11" t="n">
-        <v>243.2666473388672</v>
+        <v>239.6473388671875</v>
       </c>
       <c r="F11" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>244.4466434616172</v>
+        <v>240.8471677432379</v>
       </c>
       <c r="C12" t="n">
-        <v>246.9553636418975</v>
+        <v>247.252842429503</v>
       </c>
       <c r="D12" t="n">
-        <v>238.6954214370453</v>
+        <v>240.3315369780713</v>
       </c>
       <c r="E12" t="n">
-        <v>239.6473388671875</v>
+        <v>246.6578826904297</v>
       </c>
       <c r="F12" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>240.8471677432379</v>
+        <v>246.0232707436915</v>
       </c>
       <c r="C13" t="n">
-        <v>247.252842429503</v>
+        <v>246.1918391425529</v>
       </c>
       <c r="D13" t="n">
-        <v>240.3315369780713</v>
+        <v>237.5352670689401</v>
       </c>
       <c r="E13" t="n">
-        <v>246.6578826904297</v>
+        <v>237.75341796875</v>
       </c>
       <c r="F13" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>246.0232707436915</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C14" t="n">
-        <v>246.1918391425529</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D14" t="n">
-        <v>237.5352670689401</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E14" t="n">
-        <v>237.75341796875</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F14" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>238.8441526809671</v>
+        <v>251.0605458824941</v>
       </c>
       <c r="C15" t="n">
-        <v>239.2903800503502</v>
+        <v>254.5806764744798</v>
       </c>
       <c r="D15" t="n">
-        <v>233.915951765761</v>
+        <v>240.6290201908687</v>
       </c>
       <c r="E15" t="n">
-        <v>234.5902404785156</v>
+        <v>243.9310150146484</v>
       </c>
       <c r="F15" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>251.0605458824941</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="C16" t="n">
-        <v>254.5806764744798</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D16" t="n">
-        <v>240.6290201908687</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E16" t="n">
-        <v>243.9310150146484</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="F16" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>244.4962363844956</v>
+        <v>242.9394381851618</v>
       </c>
       <c r="C17" t="n">
-        <v>248.670819810711</v>
+        <v>253.2519633865538</v>
       </c>
       <c r="D17" t="n">
-        <v>240.1233229489625</v>
+        <v>242.2453285307239</v>
       </c>
       <c r="E17" t="n">
-        <v>241.0355834960938</v>
+        <v>252.1413879394531</v>
       </c>
       <c r="F17" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>242.9394234832453</v>
+        <v>252.359543952159</v>
       </c>
       <c r="C18" t="n">
-        <v>253.2519480605562</v>
+        <v>264.8833249829649</v>
       </c>
       <c r="D18" t="n">
-        <v>242.2453138708127</v>
+        <v>251.8637491703276</v>
       </c>
       <c r="E18" t="n">
-        <v>252.1413726806641</v>
+        <v>261.1946105957031</v>
       </c>
       <c r="F18" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>252.3595144668565</v>
+        <v>259.9947719140093</v>
       </c>
       <c r="C19" t="n">
-        <v>264.883294034403</v>
+        <v>260.1930716520554</v>
       </c>
       <c r="D19" t="n">
-        <v>251.863719742953</v>
+        <v>254.3526253920043</v>
       </c>
       <c r="E19" t="n">
-        <v>261.194580078125</v>
+        <v>254.4815368652344</v>
       </c>
       <c r="F19" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>259.9947875033736</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C20" t="n">
-        <v>260.1930872533099</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D20" t="n">
-        <v>254.3526406430638</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E20" t="n">
-        <v>254.4815521240234</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F20" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>255.4334634999039</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C21" t="n">
-        <v>256.3853809552256</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D21" t="n">
-        <v>251.982721115611</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E21" t="n">
-        <v>252.9049072265625</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F21" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>255.254980605377</v>
+        <v>254.917794537107</v>
       </c>
       <c r="C22" t="n">
-        <v>256.3258839430272</v>
+        <v>255.9292351115289</v>
       </c>
       <c r="D22" t="n">
-        <v>251.8637312244832</v>
+        <v>252.7759728910826</v>
       </c>
       <c r="E22" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213500976562</v>
       </c>
       <c r="F22" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>254.9178098920577</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="C23" t="n">
-        <v>255.9292505274036</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D23" t="n">
-        <v>252.7759881170209</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E23" t="n">
-        <v>253.3213653564453</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="F23" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>253.3213661855435</v>
+        <v>249.8805597170771</v>
       </c>
       <c r="C24" t="n">
-        <v>256.663017898251</v>
+        <v>251.4373625303139</v>
       </c>
       <c r="D24" t="n">
-        <v>252.0025503587843</v>
+        <v>246.9454480725237</v>
       </c>
       <c r="E24" t="n">
-        <v>252.1215362548828</v>
+        <v>249.3451080322266</v>
       </c>
       <c r="F24" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>249.8805444255208</v>
+        <v>248.3931853229768</v>
       </c>
       <c r="C25" t="n">
-        <v>251.4373471434884</v>
+        <v>257.0993404683716</v>
       </c>
       <c r="D25" t="n">
-        <v>246.945432960583</v>
+        <v>247.897390541893</v>
       </c>
       <c r="E25" t="n">
-        <v>249.3450927734375</v>
+        <v>254.491455078125</v>
       </c>
       <c r="F25" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>248.3931555366784</v>
+        <v>252.657000570364</v>
       </c>
       <c r="C26" t="n">
-        <v>257.0993096380665</v>
+        <v>259.6179629024988</v>
       </c>
       <c r="D26" t="n">
-        <v>247.8973608150483</v>
+        <v>250.5052532311086</v>
       </c>
       <c r="E26" t="n">
-        <v>254.4914245605469</v>
+        <v>258.2198181152344</v>
       </c>
       <c r="F26" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>252.657000570364</v>
+        <v>257.8133023432115</v>
       </c>
       <c r="C27" t="n">
-        <v>259.6179629024988</v>
+        <v>259.3601797363976</v>
       </c>
       <c r="D27" t="n">
-        <v>250.5052532311086</v>
+        <v>252.9545192358491</v>
       </c>
       <c r="E27" t="n">
-        <v>258.2198181152344</v>
+        <v>259.1420288085938</v>
       </c>
       <c r="F27" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>257.8132719821094</v>
+        <v>255.9788376046017</v>
       </c>
       <c r="C28" t="n">
-        <v>259.3601491931292</v>
+        <v>257.0795177464699</v>
       </c>
       <c r="D28" t="n">
-        <v>252.9544894469363</v>
+        <v>251.3282953006253</v>
       </c>
       <c r="E28" t="n">
-        <v>259.1419982910156</v>
+        <v>252.300048828125</v>
       </c>
       <c r="F28" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>255.9788221233241</v>
+        <v>252.5578552142711</v>
       </c>
       <c r="C29" t="n">
-        <v>257.0795021986246</v>
+        <v>254.6699306658516</v>
       </c>
       <c r="D29" t="n">
-        <v>251.3282801006067</v>
+        <v>249.8904769054258</v>
       </c>
       <c r="E29" t="n">
-        <v>252.3000335693359</v>
+        <v>250.5548400878906</v>
       </c>
       <c r="F29" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>252.5578398334985</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="C30" t="n">
-        <v>254.6699151564536</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="D30" t="n">
-        <v>249.8904616870965</v>
+        <v>232.5078921531912</v>
       </c>
       <c r="E30" t="n">
-        <v>250.5548248291016</v>
+        <v>237.2576141357422</v>
       </c>
       <c r="F30" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>248.4328164468309</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="C31" t="n">
-        <v>248.4328164468309</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D31" t="n">
-        <v>232.5078921531912</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E31" t="n">
-        <v>237.2576141357422</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="F31" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>234.1638481621394</v>
+        <v>237.9814840335094</v>
       </c>
       <c r="C32" t="n">
-        <v>238.943316687993</v>
+        <v>239.8754236419186</v>
       </c>
       <c r="D32" t="n">
-        <v>233.8068753463891</v>
+        <v>233.1028654264771</v>
       </c>
       <c r="E32" t="n">
-        <v>237.8624877929688</v>
+        <v>239.6771087646484</v>
       </c>
       <c r="F32" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>237.9814688826704</v>
+        <v>239.8654952673756</v>
       </c>
       <c r="C33" t="n">
-        <v>239.8754083705041</v>
+        <v>243.63353841341</v>
       </c>
       <c r="D33" t="n">
-        <v>233.1028505862302</v>
+        <v>239.1317287169831</v>
       </c>
       <c r="E33" t="n">
-        <v>239.6770935058594</v>
+        <v>242.4436340332031</v>
       </c>
       <c r="F33" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>239.8654952673756</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="C34" t="n">
-        <v>243.63353841341</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D34" t="n">
-        <v>239.1317287169831</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E34" t="n">
-        <v>242.4436340332031</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="F34" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>243.6732075926712</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C35" t="n">
-        <v>246.3405706207466</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D35" t="n">
-        <v>241.63052052637</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E35" t="n">
-        <v>243.9508514404297</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F35" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>243.1873051795984</v>
+        <v>236.3056776848755</v>
       </c>
       <c r="C36" t="n">
-        <v>243.8318322502171</v>
+        <v>243.1178923149379</v>
       </c>
       <c r="D36" t="n">
-        <v>237.8922213097491</v>
+        <v>235.4231636860313</v>
       </c>
       <c r="E36" t="n">
-        <v>238.4078369140625</v>
+        <v>241.6106872558594</v>
       </c>
       <c r="F36" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>236.3056926086296</v>
+        <v>240.0340571163644</v>
       </c>
       <c r="C37" t="n">
-        <v>243.1179076689137</v>
+        <v>240.7876596253181</v>
       </c>
       <c r="D37" t="n">
-        <v>235.4231785540507</v>
+        <v>233.6085468088289</v>
       </c>
       <c r="E37" t="n">
-        <v>241.6107025146484</v>
+        <v>235.0364379882812</v>
       </c>
       <c r="F37" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>240.0340571163644</v>
+        <v>234.2531241839991</v>
       </c>
       <c r="C38" t="n">
-        <v>240.7876596253181</v>
+        <v>235.7900759047376</v>
       </c>
       <c r="D38" t="n">
-        <v>233.6085468088289</v>
+        <v>228.3333332730034</v>
       </c>
       <c r="E38" t="n">
-        <v>235.0364379882812</v>
+        <v>231.5361633300781</v>
       </c>
       <c r="F38" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>234.2531087461558</v>
+        <v>230.0487531290293</v>
       </c>
       <c r="C39" t="n">
-        <v>235.7900603656055</v>
+        <v>230.3263969654728</v>
       </c>
       <c r="D39" t="n">
-        <v>228.3333182252886</v>
+        <v>223.1671199033486</v>
       </c>
       <c r="E39" t="n">
-        <v>231.5361480712891</v>
+        <v>225.9634094238281</v>
       </c>
       <c r="F39" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>230.0487686636922</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C40" t="n">
-        <v>230.3264125188844</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D40" t="n">
-        <v>223.1671349733107</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E40" t="n">
-        <v>225.9634246826172</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F40" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>227.3218898732066</v>
+        <v>222.9688137796853</v>
       </c>
       <c r="C41" t="n">
-        <v>229.1265900019938</v>
+        <v>226.7566777713456</v>
       </c>
       <c r="D41" t="n">
-        <v>221.4219354522067</v>
+        <v>220.0932103050241</v>
       </c>
       <c r="E41" t="n">
-        <v>223.4745178222656</v>
+        <v>225.1998901367188</v>
       </c>
       <c r="F41" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>222.9687986720664</v>
+        <v>225.4279539042935</v>
       </c>
       <c r="C42" t="n">
-        <v>226.7566624070738</v>
+        <v>226.9153381582893</v>
       </c>
       <c r="D42" t="n">
-        <v>220.0931953922465</v>
+        <v>223.1472950220756</v>
       </c>
       <c r="E42" t="n">
-        <v>225.1998748779297</v>
+        <v>224.9123382568359</v>
       </c>
       <c r="F42" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>225.4279539042935</v>
+        <v>224.8924827605518</v>
       </c>
       <c r="C43" t="n">
-        <v>226.9153381582893</v>
+        <v>232.656629709896</v>
       </c>
       <c r="D43" t="n">
-        <v>223.1472950220756</v>
+        <v>224.6148389342789</v>
       </c>
       <c r="E43" t="n">
-        <v>224.9123382568359</v>
+        <v>232.1509094238281</v>
       </c>
       <c r="F43" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>224.8924975422598</v>
+        <v>228.5712919801828</v>
       </c>
       <c r="C44" t="n">
-        <v>232.656645001925</v>
+        <v>230.8618764526245</v>
       </c>
       <c r="D44" t="n">
-        <v>224.614853697738</v>
+        <v>224.0992287472785</v>
       </c>
       <c r="E44" t="n">
-        <v>232.1509246826172</v>
+        <v>226.2311401367188</v>
       </c>
       <c r="F44" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>228.5712765635558</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C45" t="n">
-        <v>230.8618608815026</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D45" t="n">
-        <v>224.0992136322821</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E45" t="n">
-        <v>226.2311248779297</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F45" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>227.0739873247604</v>
+        <v>226.7467645282661</v>
       </c>
       <c r="C46" t="n">
-        <v>230.6040433967966</v>
+        <v>232.2798356411572</v>
       </c>
       <c r="D46" t="n">
-        <v>226.7071040647147</v>
+        <v>226.6773611325171</v>
       </c>
       <c r="E46" t="n">
-        <v>228.6010284423828</v>
+        <v>230.8717803955078</v>
       </c>
       <c r="F46" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>226.7467645282661</v>
+        <v>231.060173355472</v>
       </c>
       <c r="C47" t="n">
-        <v>232.2798356411572</v>
+        <v>234.6596326998496</v>
       </c>
       <c r="D47" t="n">
-        <v>226.6773611325171</v>
+        <v>229.6719390743564</v>
       </c>
       <c r="E47" t="n">
-        <v>230.8717803955078</v>
+        <v>232.7359619140625</v>
       </c>
       <c r="F47" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>231.0601885043919</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="C48" t="n">
-        <v>234.6596480847597</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D48" t="n">
-        <v>229.67195413226</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E48" t="n">
-        <v>232.7359771728516</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="F48" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>233.3805083869321</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C49" t="n">
-        <v>237.2477014354837</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D49" t="n">
-        <v>231.1990144844042</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E49" t="n">
-        <v>236.7122497558594</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F49" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>241.6404418420451</v>
+        <v>248.7203626098492</v>
       </c>
       <c r="C50" t="n">
-        <v>246.8760330652079</v>
+        <v>259.6774281355445</v>
       </c>
       <c r="D50" t="n">
-        <v>235.6016655641461</v>
+        <v>247.4015469367764</v>
       </c>
       <c r="E50" t="n">
-        <v>245.3787384033203</v>
+        <v>258.3784484863281</v>
       </c>
       <c r="F50" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>248.7203919866921</v>
+        <v>259.6774704470017</v>
       </c>
       <c r="C51" t="n">
-        <v>259.6774588065476</v>
+        <v>262.0572792621351</v>
       </c>
       <c r="D51" t="n">
-        <v>247.4015761578514</v>
+        <v>254.1840559885597</v>
       </c>
       <c r="E51" t="n">
-        <v>258.3784790039062</v>
+        <v>257.3472290039062</v>
       </c>
       <c r="F51" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>259.6774396530913</v>
+        <v>257.8132965310952</v>
       </c>
       <c r="C52" t="n">
-        <v>262.0572481860146</v>
+        <v>260.0443731356912</v>
       </c>
       <c r="D52" t="n">
-        <v>254.1840258460871</v>
+        <v>256.8217069290525</v>
       </c>
       <c r="E52" t="n">
-        <v>257.3471984863281</v>
+        <v>258.82470703125</v>
       </c>
       <c r="F52" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>257.8132661327708</v>
+        <v>258.556940201721</v>
       </c>
       <c r="C53" t="n">
-        <v>260.0443424743044</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D53" t="n">
-        <v>256.8216766476447</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E53" t="n">
-        <v>258.8246765136719</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="F53" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>258.556940201721</v>
+        <v>261.2838767501659</v>
       </c>
       <c r="C54" t="n">
-        <v>263.6933661135803</v>
+        <v>265.6468652243614</v>
       </c>
       <c r="D54" t="n">
-        <v>256.9703910840639</v>
+        <v>258.5768260705516</v>
       </c>
       <c r="E54" t="n">
-        <v>261.9779357910156</v>
+        <v>260.1435546875</v>
       </c>
       <c r="F54" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>261.2838154474661</v>
+        <v>261.3036341846645</v>
       </c>
       <c r="C55" t="n">
-        <v>265.6468028980126</v>
+        <v>262.2654771366241</v>
       </c>
       <c r="D55" t="n">
-        <v>258.5767654029829</v>
+        <v>258.7156003126054</v>
       </c>
       <c r="E55" t="n">
-        <v>260.1434936523438</v>
+        <v>260.0245056152344</v>
       </c>
       <c r="F55" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>261.3036648523665</v>
+        <v>259.0130705063725</v>
       </c>
       <c r="C56" t="n">
-        <v>262.2655079172122</v>
+        <v>260.0740784753494</v>
       </c>
       <c r="D56" t="n">
-        <v>258.7156306765648</v>
+        <v>250.9613690531332</v>
       </c>
       <c r="E56" t="n">
-        <v>260.0245361328125</v>
+        <v>252.4388427734375</v>
       </c>
       <c r="F56" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>259.013086162544</v>
+        <v>251.8637174841621</v>
       </c>
       <c r="C57" t="n">
-        <v>260.074094195654</v>
+        <v>253.7080744457603</v>
       </c>
       <c r="D57" t="n">
-        <v>250.9613842226157</v>
+        <v>249.9896140498327</v>
       </c>
       <c r="E57" t="n">
-        <v>252.4388580322266</v>
+        <v>252.7660675048828</v>
       </c>
       <c r="F57" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>251.8637174841621</v>
+        <v>254.1741130832229</v>
       </c>
       <c r="C58" t="n">
-        <v>253.7080744457603</v>
+        <v>259.7666921654164</v>
       </c>
       <c r="D58" t="n">
-        <v>249.9896140498327</v>
+        <v>254.0947992411865</v>
       </c>
       <c r="E58" t="n">
-        <v>252.7660675048828</v>
+        <v>255.9689178466797</v>
       </c>
       <c r="F58" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,25 +1951,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>254.1741282350202</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C59" t="n">
-        <v>259.7667076505979</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D59" t="n">
-        <v>254.0948143882558</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E59" t="n">
-        <v>255.9689331054688</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F59" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1977,25 +1977,25 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>256.6601807669533</v>
+        <v>258.904790639318</v>
       </c>
       <c r="C60" t="n">
-        <v>258.2989382537239</v>
+        <v>260.2555449501942</v>
       </c>
       <c r="D60" t="n">
-        <v>254.4155616010984</v>
+        <v>253.7600731430874</v>
       </c>
       <c r="E60" t="n">
-        <v>256.0940551757812</v>
+        <v>258.1400451660156</v>
       </c>
       <c r="F60" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G60" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>258.904790639318</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="C61" t="n">
-        <v>260.2555449501942</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D61" t="n">
-        <v>253.7600731430874</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E61" t="n">
-        <v>258.1400451660156</v>
+        <v>262.827880859375</v>
       </c>
       <c r="F61" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>258.8451791646396</v>
+        <v>260.9308604798152</v>
       </c>
       <c r="C62" t="n">
-        <v>262.827880859375</v>
+        <v>262.4404982668678</v>
       </c>
       <c r="D62" t="n">
-        <v>256.6502376986757</v>
+        <v>258.7458305027313</v>
       </c>
       <c r="E62" t="n">
-        <v>262.827880859375</v>
+        <v>261.6360168457031</v>
       </c>
       <c r="F62" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>260.930890915143</v>
+        <v>261.4374083245464</v>
       </c>
       <c r="C63" t="n">
-        <v>262.4405288782817</v>
+        <v>264.4864785158107</v>
       </c>
       <c r="D63" t="n">
-        <v>258.7458606831942</v>
+        <v>260.7620161053754</v>
       </c>
       <c r="E63" t="n">
-        <v>261.6360473632812</v>
+        <v>263.4535827636719</v>
       </c>
       <c r="F63" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>261.4374386085776</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="C64" t="n">
-        <v>264.486509153036</v>
+        <v>266.0855602062323</v>
       </c>
       <c r="D64" t="n">
-        <v>260.7620463111714</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="E64" t="n">
-        <v>263.45361328125</v>
+        <v>264.2680053710938</v>
       </c>
       <c r="F64" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9072936026629</v>
       </c>
       <c r="C65" t="n">
-        <v>266.0855294787636</v>
+        <v>267.2773231615557</v>
       </c>
       <c r="D65" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9072936026629</v>
       </c>
       <c r="E65" t="n">
-        <v>264.2679748535156</v>
+        <v>264.4169616699219</v>
       </c>
       <c r="F65" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>262.9073239460033</v>
+        <v>264.8440818513142</v>
       </c>
       <c r="C66" t="n">
-        <v>267.2773540092613</v>
+        <v>266.453045001104</v>
       </c>
       <c r="D66" t="n">
-        <v>262.9073239460033</v>
+        <v>263.5231220141856</v>
       </c>
       <c r="E66" t="n">
-        <v>264.4169921875</v>
+        <v>264.109130859375</v>
       </c>
       <c r="F66" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>264.8440818513142</v>
+        <v>263.4834046285292</v>
       </c>
       <c r="C67" t="n">
-        <v>266.453045001104</v>
+        <v>264.2878861679949</v>
       </c>
       <c r="D67" t="n">
-        <v>263.5231220141856</v>
+        <v>262.5895396190958</v>
       </c>
       <c r="E67" t="n">
-        <v>264.109130859375</v>
+        <v>263.1059875488281</v>
       </c>
       <c r="F67" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>263.4833740671746</v>
+        <v>263.1953762174182</v>
       </c>
       <c r="C68" t="n">
-        <v>264.2878555133287</v>
+        <v>263.572793304574</v>
       </c>
       <c r="D68" t="n">
-        <v>262.5895091614203</v>
+        <v>250.760631935403</v>
       </c>
       <c r="E68" t="n">
-        <v>263.10595703125</v>
+        <v>251.8928680419922</v>
       </c>
       <c r="F68" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>263.1953602739627</v>
+        <v>251.8928562905814</v>
       </c>
       <c r="C69" t="n">
-        <v>263.5727773382559</v>
+        <v>257.8222021169872</v>
       </c>
       <c r="D69" t="n">
-        <v>250.7606167452008</v>
+        <v>250.5917797464572</v>
       </c>
       <c r="E69" t="n">
-        <v>251.8928527832031</v>
+        <v>254.514892578125</v>
       </c>
       <c r="F69" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>251.8928411889898</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C70" t="n">
-        <v>257.8221866599169</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D70" t="n">
-        <v>250.5917647228683</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E70" t="n">
-        <v>254.5148773193359</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F70" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>253.4620895509313</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="C71" t="n">
-        <v>261.7552171079225</v>
+        <v>266.0060858079951</v>
       </c>
       <c r="D71" t="n">
-        <v>253.2634545783159</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="E71" t="n">
-        <v>261.1096496582031</v>
+        <v>264.3077392578125</v>
       </c>
       <c r="F71" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>261.7055558804709</v>
+        <v>262.5994079508812</v>
       </c>
       <c r="C72" t="n">
-        <v>266.0060550943219</v>
+        <v>263.3939780702048</v>
       </c>
       <c r="D72" t="n">
-        <v>261.7055558804709</v>
+        <v>258.6365898818048</v>
       </c>
       <c r="E72" t="n">
-        <v>264.3077087402344</v>
+        <v>258.7557678222656</v>
       </c>
       <c r="F72" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>262.5994389217771</v>
+        <v>258.2293887773175</v>
       </c>
       <c r="C73" t="n">
-        <v>263.394009134812</v>
+        <v>259.2523732204683</v>
       </c>
       <c r="D73" t="n">
-        <v>258.6366203853271</v>
+        <v>254.7631655270811</v>
       </c>
       <c r="E73" t="n">
-        <v>258.7557983398438</v>
+        <v>258.1697998046875</v>
       </c>
       <c r="F73" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>258.2293887773175</v>
+        <v>257.2362139425806</v>
       </c>
       <c r="C74" t="n">
-        <v>259.2523732204683</v>
+        <v>259.7787779567694</v>
       </c>
       <c r="D74" t="n">
-        <v>254.7631655270811</v>
+        <v>254.028214436778</v>
       </c>
       <c r="E74" t="n">
-        <v>258.1697998046875</v>
+        <v>257.6334838867188</v>
       </c>
       <c r="F74" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>257.2362444131007</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C75" t="n">
-        <v>259.778808728465</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D75" t="n">
-        <v>254.0282445272995</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E75" t="n">
-        <v>257.6335144042969</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F75" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>255.9053572301452</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C76" t="n">
-        <v>259.1332249596227</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D76" t="n">
-        <v>238.7231659776434</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E76" t="n">
-        <v>239.4183959960938</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F76" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>237.5511941796288</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C77" t="n">
-        <v>240.5903685304685</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D77" t="n">
-        <v>234.849731125901</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E77" t="n">
-        <v>237.9385528564453</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F77" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>235.4059054123066</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C78" t="n">
-        <v>237.2135033883542</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D78" t="n">
-        <v>230.0923326840245</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E78" t="n">
-        <v>231.9396667480469</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F78" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>231.3636110626874</v>
+        <v>222.0176902636222</v>
       </c>
       <c r="C79" t="n">
-        <v>231.3636110626874</v>
+        <v>226.3877354418118</v>
       </c>
       <c r="D79" t="n">
-        <v>224.8979495180149</v>
+        <v>217.8661632569629</v>
       </c>
       <c r="E79" t="n">
-        <v>225.5633850097656</v>
+        <v>218.5713348388672</v>
       </c>
       <c r="F79" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>222.0176902636222</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="C80" t="n">
-        <v>226.3877354418118</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D80" t="n">
-        <v>217.8661632569629</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E80" t="n">
-        <v>218.5713348388672</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="F80" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>218.6507904829158</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C81" t="n">
-        <v>221.8687318042425</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D81" t="n">
-        <v>217.4689070154735</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E81" t="n">
-        <v>220.0710601806641</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F81" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>220.7265600038705</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="C82" t="n">
-        <v>227.162427221411</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D82" t="n">
-        <v>219.6042504088122</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E82" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="F82" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>225.2356384112152</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C83" t="n">
-        <v>229.2779291905748</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D83" t="n">
-        <v>225.1065188551059</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E83" t="n">
-        <v>226.4969940185547</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F83" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>227.8675783015932</v>
+        <v>230.3605061244008</v>
       </c>
       <c r="C84" t="n">
-        <v>229.3772313706373</v>
+        <v>234.1346314027617</v>
       </c>
       <c r="D84" t="n">
-        <v>226.0401123076792</v>
+        <v>224.7291202738612</v>
       </c>
       <c r="E84" t="n">
-        <v>227.8377838134766</v>
+        <v>226.9737243652344</v>
       </c>
       <c r="F84" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>230.3605061244008</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="C85" t="n">
-        <v>234.1346314027617</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D85" t="n">
-        <v>224.7291202738612</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E85" t="n">
-        <v>226.9737243652344</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="F85" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>227.8278625141174</v>
+        <v>215.1944899838427</v>
       </c>
       <c r="C86" t="n">
-        <v>230.2810431236355</v>
+        <v>215.8003365308671</v>
       </c>
       <c r="D86" t="n">
-        <v>226.1195744340916</v>
+        <v>207.3582209619344</v>
       </c>
       <c r="E86" t="n">
-        <v>226.4076080322266</v>
+        <v>212.6221313476562</v>
       </c>
       <c r="F86" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>215.1944745404488</v>
+        <v>212.7015903227142</v>
       </c>
       <c r="C87" t="n">
-        <v>215.8003210439947</v>
+        <v>214.08212392222</v>
       </c>
       <c r="D87" t="n">
-        <v>207.358206080909</v>
+        <v>209.5929005351361</v>
       </c>
       <c r="E87" t="n">
-        <v>212.6221160888672</v>
+        <v>210.8443145751953</v>
       </c>
       <c r="F87" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>212.7015749295142</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C88" t="n">
-        <v>214.0821084291109</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D88" t="n">
-        <v>209.5928853669118</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E88" t="n">
-        <v>210.8442993164062</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F88" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>212.8902908724165</v>
+        <v>203.60397273962</v>
       </c>
       <c r="C89" t="n">
-        <v>215.4129869027477</v>
+        <v>204.1601567769575</v>
       </c>
       <c r="D89" t="n">
-        <v>208.3712731650351</v>
+        <v>191.7949429269172</v>
       </c>
       <c r="E89" t="n">
-        <v>209.3743896484375</v>
+        <v>195.0426788330078</v>
       </c>
       <c r="F89" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>203.6039568110546</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C90" t="n">
-        <v>204.16014080488</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D90" t="n">
-        <v>191.7949279222085</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E90" t="n">
-        <v>195.0426635742188</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F90" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>191.993558028148</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C91" t="n">
-        <v>199.3034370934686</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D91" t="n">
-        <v>186.0046234920971</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E91" t="n">
-        <v>198.0818176269531</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F91" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>192.668943558262</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C92" t="n">
-        <v>198.2010042649258</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D92" t="n">
-        <v>187.5043431662378</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E92" t="n">
-        <v>188.6763153076172</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F92" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>190.3250127759971</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C93" t="n">
-        <v>193.2747884158856</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D93" t="n">
-        <v>185.8457159832669</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E93" t="n">
-        <v>190.0469207763672</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F93" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>188.0108792533576</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C94" t="n">
-        <v>193.8706944788449</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D94" t="n">
-        <v>184.465183505092</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E94" t="n">
-        <v>192.7086639404297</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F94" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>190.5931665112882</v>
+        <v>191.8346508751069</v>
       </c>
       <c r="C95" t="n">
-        <v>197.7441470694129</v>
+        <v>192.3511139411869</v>
       </c>
       <c r="D95" t="n">
-        <v>189.4510040038842</v>
+        <v>180.5718794169307</v>
       </c>
       <c r="E95" t="n">
-        <v>192.1326141357422</v>
+        <v>183.7401580810547</v>
       </c>
       <c r="F95" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>191.8346349441069</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C96" t="n">
-        <v>192.3510979672969</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D96" t="n">
-        <v>180.5718644212529</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E96" t="n">
-        <v>183.7401428222656</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F96" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>184.6936257308121</v>
+        <v>185.1703470279448</v>
       </c>
       <c r="C97" t="n">
-        <v>187.0375548215625</v>
+        <v>192.1326035099074</v>
       </c>
       <c r="D97" t="n">
-        <v>179.012577513483</v>
+        <v>183.0449210226253</v>
       </c>
       <c r="E97" t="n">
-        <v>184.1672210693359</v>
+        <v>188.4280090332031</v>
       </c>
       <c r="F97" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>185.1703620229303</v>
+        <v>189.6695058452945</v>
       </c>
       <c r="C98" t="n">
-        <v>192.1326190686923</v>
+        <v>191.6856804427425</v>
       </c>
       <c r="D98" t="n">
-        <v>183.0449358454951</v>
+        <v>181.9226203922807</v>
       </c>
       <c r="E98" t="n">
-        <v>188.4280242919922</v>
+        <v>183.0349884033203</v>
       </c>
       <c r="F98" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>189.6695058452945</v>
+        <v>182.6277925688313</v>
       </c>
       <c r="C99" t="n">
-        <v>191.6856804427425</v>
+        <v>186.8587767567783</v>
       </c>
       <c r="D99" t="n">
-        <v>181.9226203922807</v>
+        <v>180.6215444099069</v>
       </c>
       <c r="E99" t="n">
-        <v>183.0349884033203</v>
+        <v>186.5111541748047</v>
       </c>
       <c r="F99" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>182.6277925688313</v>
+        <v>185.3292593497056</v>
       </c>
       <c r="C100" t="n">
-        <v>186.8587767567783</v>
+        <v>185.6768667554436</v>
       </c>
       <c r="D100" t="n">
-        <v>180.6215444099069</v>
+        <v>181.9821987572526</v>
       </c>
       <c r="E100" t="n">
-        <v>186.5111541748047</v>
+        <v>184.0281677246094</v>
       </c>
       <c r="F100" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>185.3292747163753</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C101" t="n">
-        <v>185.6768821509354</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D101" t="n">
-        <v>181.9822138463991</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E101" t="n">
-        <v>184.0281829833984</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F101" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>184.0579771467211</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C102" t="n">
-        <v>190.4243134969296</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D102" t="n">
-        <v>182.4787935369736</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E102" t="n">
-        <v>183.8990631103516</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F102" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>180.0355685556146</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C103" t="n">
-        <v>181.2273936107796</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D103" t="n">
-        <v>173.3811981056387</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E103" t="n">
-        <v>176.9467468261719</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F103" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>176.4302852446972</v>
+        <v>181.7537708108397</v>
       </c>
       <c r="C104" t="n">
-        <v>187.3851706171715</v>
+        <v>191.2884009153263</v>
       </c>
       <c r="D104" t="n">
-        <v>175.0795461293982</v>
+        <v>181.0188047518053</v>
       </c>
       <c r="E104" t="n">
-        <v>184.1573028564453</v>
+        <v>190.4441833496094</v>
       </c>
       <c r="F104" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>181.7537853733346</v>
+        <v>195.420066371549</v>
       </c>
       <c r="C105" t="n">
-        <v>191.2884162417558</v>
+        <v>199.6709185207204</v>
       </c>
       <c r="D105" t="n">
-        <v>181.0188192554131</v>
+        <v>190.0270517409182</v>
       </c>
       <c r="E105" t="n">
-        <v>190.4441986083984</v>
+        <v>198.1116180419922</v>
       </c>
       <c r="F105" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>195.4200513200664</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C106" t="n">
-        <v>199.6709031418322</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D106" t="n">
-        <v>190.0270371048119</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E106" t="n">
-        <v>198.1116027832031</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F106" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>190.6031086414411</v>
+        <v>191.1890843548102</v>
       </c>
       <c r="C107" t="n">
-        <v>194.5857953386064</v>
+        <v>194.6056605467623</v>
       </c>
       <c r="D107" t="n">
-        <v>188.6266549601705</v>
+        <v>189.3814711920236</v>
       </c>
       <c r="E107" t="n">
-        <v>193.4634857177734</v>
+        <v>191.6360168457031</v>
       </c>
       <c r="F107" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>191.1890691316076</v>
+        <v>189.4509946932415</v>
       </c>
       <c r="C108" t="n">
-        <v>194.6056450515189</v>
+        <v>197.3170577657204</v>
       </c>
       <c r="D108" t="n">
-        <v>189.38145611275</v>
+        <v>188.2889641983741</v>
       </c>
       <c r="E108" t="n">
-        <v>191.6360015869141</v>
+        <v>194.7149047851562</v>
       </c>
       <c r="F108" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>189.4510095395255</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C109" t="n">
-        <v>197.3170732284266</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D109" t="n">
-        <v>188.2889789535958</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E109" t="n">
-        <v>194.7149200439453</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F109" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>193.7713848635987</v>
+        <v>193.036414733929</v>
       </c>
       <c r="C110" t="n">
-        <v>195.1320503828654</v>
+        <v>203.027904005614</v>
       </c>
       <c r="D110" t="n">
-        <v>190.7918147128814</v>
+        <v>192.9172367799533</v>
       </c>
       <c r="E110" t="n">
-        <v>191.76513671875</v>
+        <v>200.0185394287109</v>
       </c>
       <c r="F110" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>193.0364294600736</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C111" t="n">
-        <v>203.0279194939781</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D111" t="n">
-        <v>192.9172514970062</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E111" t="n">
-        <v>200.0185546875</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F111" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>199.4226244314719</v>
+        <v>197.2078193049057</v>
       </c>
       <c r="C112" t="n">
-        <v>201.5778601866405</v>
+        <v>202.2830212056148</v>
       </c>
       <c r="D112" t="n">
-        <v>196.0259162627038</v>
+        <v>194.5361355724457</v>
       </c>
       <c r="E112" t="n">
-        <v>200.733642578125</v>
+        <v>197.4362487792969</v>
       </c>
       <c r="F112" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>197.2078193049057</v>
+        <v>195.9166595935153</v>
       </c>
       <c r="C113" t="n">
-        <v>202.2830212056148</v>
+        <v>198.2109412897675</v>
       </c>
       <c r="D113" t="n">
-        <v>194.5361355724457</v>
+        <v>189.3020255204881</v>
       </c>
       <c r="E113" t="n">
-        <v>197.4362487792969</v>
+        <v>193.5826721191406</v>
       </c>
       <c r="F113" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>195.9166750362765</v>
+        <v>195.0625292691439</v>
       </c>
       <c r="C114" t="n">
-        <v>198.2109569133711</v>
+        <v>198.1910871721164</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3020404418633</v>
+        <v>189.987327259986</v>
       </c>
       <c r="E114" t="n">
-        <v>193.5826873779297</v>
+        <v>192.8079986572266</v>
       </c>
       <c r="F114" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>195.0625292691439</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C115" t="n">
-        <v>198.1910871721164</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D115" t="n">
-        <v>189.987327259986</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E115" t="n">
-        <v>192.8079986572266</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F115" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>192.8079750209554</v>
+        <v>198.3698354155112</v>
       </c>
       <c r="C116" t="n">
-        <v>203.4648992272838</v>
+        <v>199.6311909649738</v>
       </c>
       <c r="D116" t="n">
-        <v>191.8346379323055</v>
+        <v>190.4441834205658</v>
       </c>
       <c r="E116" t="n">
-        <v>197.9228973388672</v>
+        <v>191.5168304443359</v>
       </c>
       <c r="F116" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>198.3698512203022</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C117" t="n">
-        <v>199.6312068702612</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D117" t="n">
-        <v>190.4441985938934</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E117" t="n">
-        <v>191.516845703125</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F117" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>193.821025021851</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C118" t="n">
-        <v>197.2773371794379</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D118" t="n">
-        <v>193.821025021851</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E118" t="n">
-        <v>196.9893035888672</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F118" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>196.870136689126</v>
+        <v>192.0829546896537</v>
       </c>
       <c r="C119" t="n">
-        <v>201.0018110133274</v>
+        <v>194.8142273994103</v>
       </c>
       <c r="D119" t="n">
-        <v>193.1258058856387</v>
+        <v>191.3281356874407</v>
       </c>
       <c r="E119" t="n">
-        <v>193.9799499511719</v>
+        <v>193.0165557861328</v>
       </c>
       <c r="F119" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>192.0829546896537</v>
+        <v>194.2580448499211</v>
       </c>
       <c r="C120" t="n">
-        <v>194.8142273994103</v>
+        <v>199.0352867281362</v>
       </c>
       <c r="D120" t="n">
-        <v>191.3281356874407</v>
+        <v>191.9836462262046</v>
       </c>
       <c r="E120" t="n">
-        <v>193.0165557861328</v>
+        <v>193.6621398925781</v>
       </c>
       <c r="F120" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>194.2580295441802</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C121" t="n">
-        <v>199.0352710459927</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D121" t="n">
-        <v>191.9836310996653</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E121" t="n">
-        <v>193.6621246337891</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F121" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>191.8942484911283</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C122" t="n">
-        <v>194.3374874288811</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D122" t="n">
-        <v>188.7061018910339</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E122" t="n">
-        <v>194.0494689941406</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F122" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>195.7478267440036</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C123" t="n">
-        <v>196.7012958768407</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D123" t="n">
-        <v>190.6924929381777</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E123" t="n">
-        <v>193.850830078125</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F123" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>190.8315397252546</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="C124" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D124" t="n">
-        <v>181.0486114593648</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E124" t="n">
-        <v>181.7736511230469</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="F124" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B125" t="n">
-        <v>184.4353921172228</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C125" t="n">
-        <v>186.1138857525603</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D125" t="n">
-        <v>178.6252393274517</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E125" t="n">
-        <v>180.7208709716797</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F125" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B126" t="n">
-        <v>179.9461742219026</v>
+        <v>182.7469769199218</v>
       </c>
       <c r="C126" t="n">
-        <v>186.1933484091056</v>
+        <v>182.8562284362321</v>
       </c>
       <c r="D126" t="n">
-        <v>178.3074166263376</v>
+        <v>177.6022595179307</v>
       </c>
       <c r="E126" t="n">
-        <v>184.3758087158203</v>
+        <v>178.0889129638672</v>
       </c>
       <c r="F126" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B127" t="n">
-        <v>182.7469769199218</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C127" t="n">
-        <v>182.8562284362321</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D127" t="n">
-        <v>177.6022595179307</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E127" t="n">
-        <v>178.0889129638672</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F127" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" t="n">
-        <v>178.873523844959</v>
+        <v>183.6408226716892</v>
       </c>
       <c r="C128" t="n">
-        <v>185.1206822343098</v>
+        <v>187.2163126895138</v>
       </c>
       <c r="D128" t="n">
-        <v>178.3570608051074</v>
+        <v>181.0684642406058</v>
       </c>
       <c r="E128" t="n">
-        <v>183.7699432373047</v>
+        <v>185.3987731933594</v>
       </c>
       <c r="F128" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" t="n">
-        <v>183.6408226716892</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C129" t="n">
-        <v>187.2163126895138</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D129" t="n">
-        <v>181.0684642406058</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E129" t="n">
-        <v>185.3987731933594</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F129" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B130" t="n">
-        <v>185.5775567084869</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C130" t="n">
-        <v>187.6930410934417</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D130" t="n">
-        <v>181.7636956083204</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E130" t="n">
-        <v>184.9717102050781</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F130" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B131" t="n">
-        <v>184.0381169897925</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C131" t="n">
-        <v>186.3025890630262</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D131" t="n">
-        <v>180.3434488377003</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E131" t="n">
-        <v>185.9053039550781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F131" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" t="n">
-        <v>186.2231237330043</v>
+        <v>183.6904887071696</v>
       </c>
       <c r="C132" t="n">
-        <v>186.8587647224845</v>
+        <v>185.3093932676422</v>
       </c>
       <c r="D132" t="n">
-        <v>182.3496888213084</v>
+        <v>180.7804492618957</v>
       </c>
       <c r="E132" t="n">
-        <v>183.7699432373047</v>
+        <v>181.7140502929688</v>
       </c>
       <c r="F132" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" t="n">
-        <v>183.690504131923</v>
+        <v>185.2299504420264</v>
       </c>
       <c r="C133" t="n">
-        <v>185.3094088283374</v>
+        <v>185.4981160077481</v>
       </c>
       <c r="D133" t="n">
-        <v>180.7804644422889</v>
+        <v>174.5829515420302</v>
       </c>
       <c r="E133" t="n">
-        <v>181.7140655517578</v>
+        <v>175.1689300537109</v>
       </c>
       <c r="F133" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B134" t="n">
-        <v>185.2299504420264</v>
+        <v>172.4208565486944</v>
       </c>
       <c r="C134" t="n">
-        <v>185.4981160077481</v>
+        <v>173.5360065139178</v>
       </c>
       <c r="D134" t="n">
-        <v>174.5829515420302</v>
+        <v>166.3970260969056</v>
       </c>
       <c r="E134" t="n">
-        <v>175.1689300537109</v>
+        <v>170.1109008789062</v>
       </c>
       <c r="F134" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -3927,25 +3927,25 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B135" t="n">
-        <v>172.4208720146844</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C135" t="n">
-        <v>173.5360220799356</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D135" t="n">
-        <v>166.3970410225636</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E135" t="n">
-        <v>170.1109161376953</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F135" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G135" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B136" t="n">
-        <v>170.5191174814139</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C136" t="n">
-        <v>170.5191174814139</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D136" t="n">
-        <v>162.8126107290287</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E136" t="n">
-        <v>164.2463836669922</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F136" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B137" t="n">
-        <v>166.3273444705899</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C137" t="n">
-        <v>172.6498652447362</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D137" t="n">
-        <v>165.0528829680655</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E137" t="n">
-        <v>172.0723876953125</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F137" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B138" t="n">
-        <v>174.4520463656914</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C138" t="n">
-        <v>176.7321331165696</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D138" t="n">
-        <v>169.7624151908458</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E138" t="n">
-        <v>170.5689086914062</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F138" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B139" t="n">
-        <v>173.4663277892384</v>
+        <v>183.2040230257668</v>
       </c>
       <c r="C139" t="n">
-        <v>178.842961383224</v>
+        <v>183.7516467853238</v>
       </c>
       <c r="D139" t="n">
-        <v>172.1321282578628</v>
+        <v>177.7975202909648</v>
       </c>
       <c r="E139" t="n">
-        <v>176.8317108154297</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F139" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B140" t="n">
-        <v>183.2040075329009</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C140" t="n">
-        <v>183.7516312461474</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D140" t="n">
-        <v>177.7975052553062</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E140" t="n">
-        <v>180.43603515625</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F140" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="n">
-        <v>184.6278268926657</v>
+        <v>181.7104926433502</v>
       </c>
       <c r="C141" t="n">
-        <v>187.1667986912511</v>
+        <v>188.1823732032504</v>
       </c>
       <c r="D141" t="n">
-        <v>180.2468672661974</v>
+        <v>181.33213168739</v>
       </c>
       <c r="E141" t="n">
-        <v>181.3520660400391</v>
+        <v>185.4641876220703</v>
       </c>
       <c r="F141" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B142" t="n">
-        <v>181.7105075933097</v>
+        <v>185.7927793430547</v>
       </c>
       <c r="C142" t="n">
-        <v>188.1823886856741</v>
+        <v>192.7226620565929</v>
       </c>
       <c r="D142" t="n">
-        <v>181.3321466062204</v>
+        <v>183.3035942778625</v>
       </c>
       <c r="E142" t="n">
-        <v>185.4642028808594</v>
+        <v>186.3005676269531</v>
       </c>
       <c r="F142" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B143" t="n">
-        <v>185.7927641258556</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C143" t="n">
-        <v>192.7226462718077</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D143" t="n">
-        <v>183.303579264538</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E143" t="n">
-        <v>186.3005523681641</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F143" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B144" t="n">
-        <v>187.3858431404722</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C144" t="n">
-        <v>190.3230783921826</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D144" t="n">
-        <v>186.2209063874661</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E144" t="n">
-        <v>188.9789276123047</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F144" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" t="n">
-        <v>176.7918740224492</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C145" t="n">
-        <v>178.0962045390804</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D145" t="n">
-        <v>169.9117629967484</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E145" t="n">
-        <v>172.5503082275391</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F145" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B146" t="n">
-        <v>174.8602617765654</v>
+        <v>177.4888357619529</v>
       </c>
       <c r="C146" t="n">
-        <v>177.6780209996891</v>
+        <v>183.4927485632761</v>
       </c>
       <c r="D146" t="n">
-        <v>173.6455382897692</v>
+        <v>176.7420802872333</v>
       </c>
       <c r="E146" t="n">
-        <v>177.3892822265625</v>
+        <v>179.4005279541016</v>
       </c>
       <c r="F146" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="n">
-        <v>177.4888508581443</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C147" t="n">
-        <v>183.4927641701262</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D147" t="n">
-        <v>176.7420953199099</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E147" t="n">
-        <v>179.4005432128906</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F147" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B148" t="n">
-        <v>181.6407975504903</v>
+        <v>178.4247846039299</v>
       </c>
       <c r="C148" t="n">
-        <v>183.6221942474171</v>
+        <v>180.993625445577</v>
       </c>
       <c r="D148" t="n">
-        <v>180.5356140136719</v>
+        <v>176.5827967489585</v>
       </c>
       <c r="E148" t="n">
-        <v>180.5356140136719</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F148" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B149" t="n">
-        <v>178.424769515226</v>
+        <v>177.5286895189733</v>
       </c>
       <c r="C149" t="n">
-        <v>180.993610139636</v>
+        <v>177.9170017981234</v>
       </c>
       <c r="D149" t="n">
-        <v>176.5827818160244</v>
+        <v>172.2516139153796</v>
       </c>
       <c r="E149" t="n">
-        <v>180.43603515625</v>
+        <v>175.7663421630859</v>
       </c>
       <c r="F149" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B150" t="n">
-        <v>177.5286741071897</v>
+        <v>181.4018421076459</v>
       </c>
       <c r="C150" t="n">
-        <v>177.9169863526292</v>
+        <v>185.2351777570901</v>
       </c>
       <c r="D150" t="n">
-        <v>172.2515989617143</v>
+        <v>177.9767212373249</v>
       </c>
       <c r="E150" t="n">
-        <v>175.7663269042969</v>
+        <v>183.0247955322266</v>
       </c>
       <c r="F150" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="n">
-        <v>181.4018572311292</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C151" t="n">
-        <v>185.2351932001588</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D151" t="n">
-        <v>177.9767360752557</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E151" t="n">
-        <v>183.0248107910156</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F151" t="n">
-        <v>12324400</v>
+        <v>8444700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="n">
-        <v>183.4429710909726</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C152" t="n">
-        <v>189.4867039708132</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D152" t="n">
-        <v>183.1741348747832</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E152" t="n">
-        <v>184.6775970458984</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F152" t="n">
-        <v>8444700</v>
+        <v>9740800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="n">
-        <v>184.7473182824849</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C153" t="n">
-        <v>186.5793548412774</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D153" t="n">
-        <v>180.3165719120649</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E153" t="n">
-        <v>186.1810913085938</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F153" t="n">
-        <v>9740800</v>
+        <v>11303400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="n">
-        <v>184.7174439304337</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C154" t="n">
-        <v>186.2906106667237</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D154" t="n">
-        <v>178.8031379653169</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E154" t="n">
-        <v>180.4061737060547</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F154" t="n">
-        <v>11303400</v>
+        <v>13955100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="n">
-        <v>183.801426731489</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C155" t="n">
-        <v>187.7642050029951</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D155" t="n">
-        <v>183.2040162535504</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E155" t="n">
-        <v>185.5338897705078</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F155" t="n">
-        <v>13955100</v>
+        <v>15123900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B156" t="n">
-        <v>178.9027054786904</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C156" t="n">
-        <v>181.0832340725416</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D156" t="n">
-        <v>176.114830301217</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E156" t="n">
-        <v>181.0334625244141</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F156" t="n">
-        <v>15123900</v>
+        <v>11145000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B157" t="n">
-        <v>179.1317124775628</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C157" t="n">
-        <v>181.7105044839724</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D157" t="n">
-        <v>175.5472800106302</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E157" t="n">
-        <v>176.7221832275391</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F157" t="n">
-        <v>11145000</v>
+        <v>10214000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B158" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C158" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D158" t="n">
-        <v>169.8420709331304</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E158" t="n">
-        <v>170.5689086914062</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F158" t="n">
-        <v>10214000</v>
+        <v>11951900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B159" t="n">
-        <v>169.0455318751909</v>
+        <v>165.2818899628073</v>
       </c>
       <c r="C159" t="n">
-        <v>169.0455318751909</v>
+        <v>168.6174040602531</v>
       </c>
       <c r="D159" t="n">
-        <v>164.0372928300067</v>
+        <v>163.6191161459536</v>
       </c>
       <c r="E159" t="n">
-        <v>165.1225738525391</v>
+        <v>166.8550567626953</v>
       </c>
       <c r="F159" t="n">
-        <v>11951900</v>
+        <v>9749400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B160" t="n">
-        <v>165.2818748478833</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C160" t="n">
-        <v>168.6173886402985</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D160" t="n">
-        <v>163.6191011830893</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E160" t="n">
-        <v>166.8550415039062</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F160" t="n">
-        <v>9749400</v>
+        <v>13883400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B161" t="n">
-        <v>168.5178185348167</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C161" t="n">
-        <v>175.208748793394</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D161" t="n">
-        <v>168.268900043628</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E161" t="n">
-        <v>172.7593841552734</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F161" t="n">
-        <v>13883400</v>
+        <v>13671200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B162" t="n">
-        <v>172.1420794089453</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C162" t="n">
-        <v>179.9979467596552</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D162" t="n">
-        <v>171.0567983816156</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E162" t="n">
-        <v>178.7035675048828</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F162" t="n">
-        <v>13671200</v>
+        <v>17510800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B163" t="n">
-        <v>184.1996921538</v>
+        <v>175.2784580726278</v>
       </c>
       <c r="C163" t="n">
-        <v>186.6291391730516</v>
+        <v>179.5299906412754</v>
       </c>
       <c r="D163" t="n">
-        <v>178.0364675908902</v>
+        <v>172.5901410995666</v>
       </c>
       <c r="E163" t="n">
-        <v>178.6438293457031</v>
+        <v>179.3209075927734</v>
       </c>
       <c r="F163" t="n">
-        <v>17510800</v>
+        <v>13025300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B164" t="n">
-        <v>175.2784431578192</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C164" t="n">
-        <v>179.529975364695</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D164" t="n">
-        <v>172.5901264135125</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E164" t="n">
-        <v>179.3208923339844</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F164" t="n">
-        <v>13025300</v>
+        <v>10949100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B165" t="n">
-        <v>174.6213174256682</v>
+        <v>179.0620149167984</v>
       </c>
       <c r="C165" t="n">
-        <v>176.5728300297275</v>
+        <v>182.5568405051486</v>
       </c>
       <c r="D165" t="n">
-        <v>171.2459830488208</v>
+        <v>176.9113553536261</v>
       </c>
       <c r="E165" t="n">
-        <v>175.5472869873047</v>
+        <v>179.2910308837891</v>
       </c>
       <c r="F165" t="n">
-        <v>10949100</v>
+        <v>10176700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="n">
-        <v>179.0619996775001</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C166" t="n">
-        <v>182.5568249684187</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D166" t="n">
-        <v>176.9113402973623</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E166" t="n">
-        <v>179.291015625</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F166" t="n">
-        <v>10176700</v>
+        <v>13617200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="n">
-        <v>177.6581006500201</v>
+        <v>177.2299817033781</v>
       </c>
       <c r="C167" t="n">
-        <v>181.5711072848628</v>
+        <v>183.1243702829636</v>
       </c>
       <c r="D167" t="n">
-        <v>176.9113451663183</v>
+        <v>176.1247828951571</v>
       </c>
       <c r="E167" t="n">
-        <v>178.3052978515625</v>
+        <v>176.7420959472656</v>
       </c>
       <c r="F167" t="n">
-        <v>13617200</v>
+        <v>18524900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="n">
-        <v>177.2299664024681</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C168" t="n">
-        <v>183.1243544731695</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D168" t="n">
-        <v>176.1247676896629</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E168" t="n">
-        <v>176.7420806884766</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F168" t="n">
-        <v>18524900</v>
+        <v>22559400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="n">
-        <v>177.6581004088628</v>
+        <v>179.4602947300403</v>
       </c>
       <c r="C169" t="n">
-        <v>181.6905830539347</v>
+        <v>193.300157831373</v>
       </c>
       <c r="D169" t="n">
-        <v>170.9074320607842</v>
+        <v>179.2412452254626</v>
       </c>
       <c r="E169" t="n">
-        <v>175.4078826904297</v>
+        <v>190.2733154296875</v>
       </c>
       <c r="F169" t="n">
-        <v>22559400</v>
+        <v>33998900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="n">
-        <v>179.4602803383912</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C170" t="n">
-        <v>193.3001423298492</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D170" t="n">
-        <v>179.24123085138</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E170" t="n">
-        <v>190.2733001708984</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F170" t="n">
-        <v>33998900</v>
+        <v>27594800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="n">
-        <v>197.8901992931745</v>
+        <v>200.1504053799259</v>
       </c>
       <c r="C171" t="n">
-        <v>210.4257307870387</v>
+        <v>203.5058221270036</v>
       </c>
       <c r="D171" t="n">
-        <v>197.352542040295</v>
+        <v>194.9131500594789</v>
       </c>
       <c r="E171" t="n">
-        <v>208.6932678222656</v>
+        <v>199.9711761474609</v>
       </c>
       <c r="F171" t="n">
-        <v>27594800</v>
+        <v>19216600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="n">
-        <v>200.1503901074607</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C172" t="n">
-        <v>203.5058065985036</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D172" t="n">
-        <v>194.9131351866423</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E172" t="n">
-        <v>199.9711608886719</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F172" t="n">
-        <v>19216600</v>
+        <v>14154400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="n">
-        <v>196.4166079226038</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C173" t="n">
-        <v>196.8248227029743</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D173" t="n">
-        <v>188.9092176958791</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E173" t="n">
-        <v>189.7854156494141</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F173" t="n">
-        <v>14154400</v>
+        <v>14453600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="n">
-        <v>196.9542758894677</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C174" t="n">
-        <v>197.2330634002457</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D174" t="n">
-        <v>185.3048928689384</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E174" t="n">
-        <v>187.9334716796875</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F174" t="n">
-        <v>14453600</v>
+        <v>13183900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B175" t="n">
-        <v>188.9789318725711</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C175" t="n">
-        <v>191.6771999565016</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D175" t="n">
-        <v>184.0304307819904</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E175" t="n">
-        <v>184.8568420410156</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F175" t="n">
-        <v>13183900</v>
+        <v>11177800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B176" t="n">
-        <v>183.1144169895118</v>
+        <v>178.7234714192057</v>
       </c>
       <c r="C176" t="n">
-        <v>184.2196157855271</v>
+        <v>181.670672953058</v>
       </c>
       <c r="D176" t="n">
-        <v>180.92393713233</v>
+        <v>170.8178179406258</v>
       </c>
       <c r="E176" t="n">
-        <v>181.7602996826172</v>
+        <v>174.5914306640625</v>
       </c>
       <c r="F176" t="n">
-        <v>11177800</v>
+        <v>15427800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B177" t="n">
-        <v>178.7234870391233</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C177" t="n">
-        <v>181.6706888305526</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D177" t="n">
-        <v>170.8178328696119</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E177" t="n">
-        <v>174.5914459228516</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F177" t="n">
-        <v>15427800</v>
+        <v>10820500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B178" t="n">
-        <v>169.861995238658</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C178" t="n">
-        <v>174.7706609037228</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D178" t="n">
-        <v>169.2944537502145</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E178" t="n">
-        <v>170.1806030273438</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F178" t="n">
-        <v>10820500</v>
+        <v>16666000</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B179" t="n">
-        <v>167.9744954285649</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C179" t="n">
-        <v>168.6832400259219</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D179" t="n">
-        <v>163.0231992739924</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E179" t="n">
-        <v>166.1576843261719</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F179" t="n">
-        <v>16666000</v>
+        <v>13589400</v>
       </c>
       <c r="G179" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B180" t="n">
-        <v>164.4506890531704</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C180" t="n">
-        <v>166.2475157071144</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D180" t="n">
-        <v>161.1165431857153</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E180" t="n">
-        <v>165.5986633300781</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F180" t="n">
-        <v>13589400</v>
+        <v>13541800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B181" t="n">
-        <v>165.7384133733495</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C181" t="n">
-        <v>169.6515271583533</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D181" t="n">
-        <v>163.8816793355271</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E181" t="n">
-        <v>164.2610168457031</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F181" t="n">
-        <v>13541800</v>
+        <v>16385300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="n">
-        <v>163.7718739013043</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C182" t="n">
-        <v>166.0079454764833</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D182" t="n">
-        <v>160.2181284427459</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E182" t="n">
-        <v>161.4260101318359</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F182" t="n">
-        <v>16385300</v>
+        <v>19986200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="n">
-        <v>159.9685677271403</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C183" t="n">
-        <v>161.1464880907799</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D183" t="n">
-        <v>153.959135832121</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E183" t="n">
-        <v>154.7477569580078</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F183" t="n">
-        <v>19986200</v>
+        <v>57940800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B184" t="n">
-        <v>152.4617715583163</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C184" t="n">
-        <v>154.1987212566731</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D184" t="n">
-        <v>149.5369245308901</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E184" t="n">
-        <v>151.5134429931641</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F184" t="n">
-        <v>57940800</v>
+        <v>20502800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B185" t="n">
-        <v>149.8962920415152</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C185" t="n">
-        <v>153.5997679942281</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D185" t="n">
-        <v>146.0630395211035</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E185" t="n">
-        <v>149.8563537597656</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F185" t="n">
-        <v>20502800</v>
+        <v>20720700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B186" t="n">
-        <v>151.3836627210609</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C186" t="n">
-        <v>154.907462036052</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D186" t="n">
-        <v>150.5850798848861</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E186" t="n">
-        <v>153.1505584716797</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F186" t="n">
-        <v>20720700</v>
+        <v>13146800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B187" t="n">
-        <v>151.5433859321397</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C187" t="n">
-        <v>156.7841657815476</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D187" t="n">
-        <v>150.135858545478</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E187" t="n">
-        <v>152.4917144775391</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F187" t="n">
-        <v>13146800</v>
+        <v>11324700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B188" t="n">
-        <v>149.7465472087312</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C188" t="n">
-        <v>153.7295454610107</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D188" t="n">
-        <v>148.5187115976041</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E188" t="n">
-        <v>149.9262390136719</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F188" t="n">
-        <v>11324700</v>
+        <v>21267900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B189" t="n">
-        <v>151.2239658596097</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C189" t="n">
-        <v>158.1817266914859</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D189" t="n">
-        <v>151.2239658596097</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E189" t="n">
-        <v>158.0918731689453</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F189" t="n">
-        <v>21267900</v>
+        <v>12664100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B190" t="n">
-        <v>159.9885357004027</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C190" t="n">
-        <v>161.4759091917036</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D190" t="n">
-        <v>157.4230418613804</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E190" t="n">
-        <v>157.6526336669922</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F190" t="n">
-        <v>12664100</v>
+        <v>13690500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B191" t="n">
-        <v>154.8176224085462</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C191" t="n">
-        <v>157.4130622995693</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D191" t="n">
-        <v>153.7994247316601</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E191" t="n">
-        <v>156.3848724365234</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F191" t="n">
-        <v>13690500</v>
+        <v>14164600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B192" t="n">
-        <v>161.9351081174896</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C192" t="n">
-        <v>165.5187996520913</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D192" t="n">
-        <v>160.916895191227</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E192" t="n">
-        <v>162.9433288574219</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F192" t="n">
-        <v>14164600</v>
+        <v>10486300</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B193" t="n">
-        <v>162.7137441629</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C193" t="n">
-        <v>166.9163573859938</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D193" t="n">
-        <v>161.7155003336798</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E193" t="n">
-        <v>165.8182830810547</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F193" t="n">
-        <v>10486300</v>
+        <v>10595500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B194" t="n">
-        <v>163.7020118941432</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C194" t="n">
-        <v>167.425457131665</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D194" t="n">
-        <v>162.0848465245878</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E194" t="n">
-        <v>165.3590850830078</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F194" t="n">
-        <v>10595500</v>
+        <v>13057900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B195" t="n">
-        <v>168.9228138583306</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C195" t="n">
-        <v>172.0772678623225</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D195" t="n">
-        <v>167.3855099055031</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E195" t="n">
-        <v>169.2222900390625</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F195" t="n">
-        <v>13057900</v>
+        <v>9792400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B196" t="n">
-        <v>167.0760662569272</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C196" t="n">
-        <v>167.2357889266519</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D196" t="n">
-        <v>164.4906183727253</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E196" t="n">
-        <v>166.2874603271484</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F196" t="n">
-        <v>9792400</v>
+        <v>13858600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B197" t="n">
-        <v>158.05194011754</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C197" t="n">
-        <v>163.5123348335076</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D197" t="n">
-        <v>156.2051830247059</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E197" t="n">
-        <v>162.2146148681641</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F197" t="n">
-        <v>13858600</v>
+        <v>8321500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B198" t="n">
-        <v>165.309182555471</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C198" t="n">
-        <v>166.007950182526</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D198" t="n">
-        <v>162.1347592897187</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E198" t="n">
-        <v>163.0331878662109</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F198" t="n">
-        <v>8321500</v>
+        <v>14020700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>165.6286161244176</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C199" t="n">
-        <v>172.4566003351415</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D199" t="n">
-        <v>165.6286161244176</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E199" t="n">
-        <v>170.9193115234375</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F199" t="n">
-        <v>14020700</v>
+        <v>13507900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>162.2046435717354</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C200" t="n">
-        <v>171.049084414024</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D200" t="n">
-        <v>161.1864306117812</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E200" t="n">
-        <v>167.2657318115234</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F200" t="n">
-        <v>13507900</v>
+        <v>13328100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>170.2205331766167</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C201" t="n">
-        <v>172.4965277703878</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D201" t="n">
-        <v>166.2674811162824</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E201" t="n">
-        <v>166.7067108154297</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F201" t="n">
-        <v>13328100</v>
+        <v>12057500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B202" t="n">
-        <v>170.5399744864679</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C202" t="n">
-        <v>174.2334736592566</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D202" t="n">
-        <v>166.5869373980102</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E202" t="n">
-        <v>172.3767395019531</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F202" t="n">
-        <v>12057500</v>
+        <v>10191500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B203" t="n">
-        <v>171.1988064601764</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C203" t="n">
-        <v>175.1218971627477</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D203" t="n">
-        <v>169.4518798636439</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E203" t="n">
-        <v>170.4700927734375</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F203" t="n">
-        <v>10191500</v>
+        <v>13426500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B204" t="n">
-        <v>167.5652084388413</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C204" t="n">
-        <v>175.0819831940494</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D204" t="n">
-        <v>166.2075962327059</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E204" t="n">
-        <v>173.4847869873047</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F204" t="n">
-        <v>13426500</v>
+        <v>12831800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B205" t="n">
-        <v>166.7666058963373</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C205" t="n">
-        <v>172.1271701993457</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D205" t="n">
-        <v>166.6368293287962</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E205" t="n">
-        <v>169.7613372802734</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F205" t="n">
-        <v>12831800</v>
+        <v>12194500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B206" t="n">
-        <v>169.1723839486806</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C206" t="n">
-        <v>169.272214424985</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D206" t="n">
-        <v>161.925139189555</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E206" t="n">
-        <v>162.7137451171875</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F206" t="n">
-        <v>12194500</v>
+        <v>12775000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B207" t="n">
-        <v>164.7601382451291</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C207" t="n">
-        <v>165.5886824068968</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D207" t="n">
-        <v>154.877515725338</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E207" t="n">
-        <v>156.6543884277344</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F207" t="n">
-        <v>12775000</v>
+        <v>10899100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B208" t="n">
-        <v>160.0983505627206</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C208" t="n">
-        <v>164.1611950360997</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D208" t="n">
-        <v>159.2698063547753</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E208" t="n">
-        <v>163.3725891113281</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F208" t="n">
-        <v>10899100</v>
+        <v>17312000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B209" t="n">
-        <v>167.7049639405646</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C209" t="n">
-        <v>176.6392431993331</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D209" t="n">
-        <v>166.8464736349225</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E209" t="n">
-        <v>173.2951354980469</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F209" t="n">
-        <v>17312000</v>
+        <v>17204600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B210" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C210" t="n">
-        <v>184.2158982492034</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D210" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E210" t="n">
-        <v>181.1812438964844</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F210" t="n">
-        <v>17204600</v>
+        <v>18139500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B211" t="n">
-        <v>181.6903554713178</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C211" t="n">
-        <v>189.8460057999592</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D211" t="n">
-        <v>181.6903554713178</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E211" t="n">
-        <v>188.0491790771484</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F211" t="n">
-        <v>18139500</v>
+        <v>12182400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B212" t="n">
-        <v>180.6721461984077</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C212" t="n">
-        <v>182.1894657683464</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D212" t="n">
-        <v>175.5910738107855</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E212" t="n">
-        <v>180.3926391601562</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F212" t="n">
-        <v>12182400</v>
+        <v>9691500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B213" t="n">
-        <v>177.3879151720665</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C213" t="n">
-        <v>184.1260606305619</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D213" t="n">
-        <v>176.719093672914</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E213" t="n">
-        <v>183.6968231201172</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F213" t="n">
-        <v>9691500</v>
+        <v>12908000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B214" t="n">
-        <v>188.658097974018</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C214" t="n">
-        <v>193.3598176605707</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D214" t="n">
-        <v>185.5735131091938</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E214" t="n">
-        <v>185.6234283447266</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F214" t="n">
-        <v>12908000</v>
+        <v>9326900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B215" t="n">
-        <v>182.7684517177381</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C215" t="n">
-        <v>190.9540477431734</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D215" t="n">
-        <v>182.6786134323838</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E215" t="n">
-        <v>190.6545867919922</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F215" t="n">
-        <v>9326900</v>
+        <v>9605500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B216" t="n">
-        <v>192.9405589477455</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C216" t="n">
-        <v>194.5976472985604</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D216" t="n">
-        <v>190.0955580470331</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E216" t="n">
-        <v>192.6410827636719</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F216" t="n">
-        <v>9605500</v>
+        <v>13297600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B217" t="n">
-        <v>183.117847615437</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C217" t="n">
-        <v>186.6915622961891</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D217" t="n">
-        <v>182.6786179003067</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E217" t="n">
-        <v>186.4420013427734</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F217" t="n">
-        <v>13297600</v>
+        <v>11392800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B218" t="n">
-        <v>190.7544083295565</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C218" t="n">
-        <v>194.3580691369978</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D218" t="n">
-        <v>190.2652786051507</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E218" t="n">
-        <v>192.4015197753906</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F218" t="n">
-        <v>11392800</v>
+        <v>9706600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B219" t="n">
-        <v>189.8360257192551</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C219" t="n">
-        <v>197.831953246477</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D219" t="n">
-        <v>189.666326097428</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E219" t="n">
-        <v>197.1631317138672</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F219" t="n">
-        <v>9706600</v>
+        <v>11171600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B220" t="n">
-        <v>196.5941314807131</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C220" t="n">
-        <v>199.0398256830038</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D220" t="n">
-        <v>195.1566580076304</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E220" t="n">
-        <v>197.1231994628906</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F220" t="n">
-        <v>11171600</v>
+        <v>12787900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B221" t="n">
-        <v>191.6628101365335</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C221" t="n">
-        <v>196.1549072491085</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D221" t="n">
-        <v>191.4431952813594</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E221" t="n">
-        <v>192.9804992675781</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F221" t="n">
-        <v>12787900</v>
+        <v>15058700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="n">
-        <v>196.4943140399408</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C222" t="n">
-        <v>202.6335228023228</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D222" t="n">
-        <v>191.0538881519706</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E222" t="n">
-        <v>201.016357421875</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F222" t="n">
-        <v>15058700</v>
+        <v>8664800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B223" t="n">
-        <v>202.3939250564146</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C223" t="n">
-        <v>204.0410211897246</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D223" t="n">
-        <v>194.9769811314243</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E223" t="n">
-        <v>195.8654174804688</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F223" t="n">
-        <v>8664800</v>
+        <v>14378800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B224" t="n">
-        <v>193.4896063018435</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C224" t="n">
-        <v>194.5976575790598</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D224" t="n">
-        <v>189.57649225733</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E224" t="n">
-        <v>190.6346282958984</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F224" t="n">
-        <v>14378800</v>
+        <v>14152900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B225" t="n">
-        <v>193.7491445531879</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C225" t="n">
-        <v>199.0598091290667</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D225" t="n">
-        <v>192.8906542357335</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E225" t="n">
-        <v>195.7955474853516</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F225" t="n">
-        <v>14152900</v>
+        <v>17843600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B226" t="n">
-        <v>193.8689320609861</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C226" t="n">
-        <v>207.5847919095016</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D226" t="n">
-        <v>193.8689320609861</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E226" t="n">
-        <v>205.7280578613281</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F226" t="n">
-        <v>17843600</v>
+        <v>11482300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="n">
-        <v>204.8595912018172</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C227" t="n">
-        <v>207.5149233311111</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D227" t="n">
-        <v>202.6434887759544</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E227" t="n">
-        <v>205.0692138671875</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F227" t="n">
-        <v>11482300</v>
+        <v>9685400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B228" t="n">
-        <v>205.2189664215684</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C228" t="n">
-        <v>210.6993304789719</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D228" t="n">
-        <v>204.3704530814486</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E228" t="n">
-        <v>208.8026580810547</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F228" t="n">
-        <v>9685400</v>
+        <v>9580200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B229" t="n">
-        <v>208.0539803833292</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C229" t="n">
-        <v>212.7956386479058</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D229" t="n">
-        <v>207.0257904413594</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E229" t="n">
-        <v>208.6928558349609</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F229" t="n">
-        <v>9580200</v>
+        <v>10081800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B230" t="n">
-        <v>205.4884885298704</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C230" t="n">
-        <v>209.9406472657768</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D230" t="n">
-        <v>204.400391231641</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E230" t="n">
-        <v>205.3287658691406</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F230" t="n">
-        <v>10081800</v>
+        <v>14888900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B231" t="n">
-        <v>199.5888632714973</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C231" t="n">
-        <v>206.0774478239803</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D231" t="n">
-        <v>198.6005964484484</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E231" t="n">
-        <v>205.2588806152344</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F231" t="n">
-        <v>14888900</v>
+        <v>55517500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B232" t="n">
-        <v>229.6459965412689</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C232" t="n">
-        <v>254.0330860396483</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D232" t="n">
-        <v>229.6459965412689</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E232" t="n">
-        <v>251.6073608398438</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F232" t="n">
-        <v>55517500</v>
+        <v>34362700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B233" t="n">
-        <v>250.0301279952546</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C233" t="n">
-        <v>263.0671897003631</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D233" t="n">
-        <v>248.5627083778381</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E233" t="n">
-        <v>255.5504150390625</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F233" t="n">
-        <v>34362700</v>
+        <v>22471500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B234" t="n">
-        <v>253.9432305236259</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C234" t="n">
-        <v>261.8193732125837</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D234" t="n">
-        <v>253.9432305236259</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E234" t="n">
-        <v>257.0877075195312</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F234" t="n">
-        <v>22471500</v>
+        <v>15897500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B235" t="n">
-        <v>254.5621609406893</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C235" t="n">
-        <v>261.8593363431507</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D235" t="n">
-        <v>253.8035010915435</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E235" t="n">
-        <v>257.6567077636719</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F235" t="n">
-        <v>15897500</v>
+        <v>14393700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B236" t="n">
-        <v>258.9244691424316</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C236" t="n">
-        <v>264.0853722779391</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D236" t="n">
-        <v>253.154621477229</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E236" t="n">
-        <v>256.478759765625</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F236" t="n">
-        <v>14393700</v>
+        <v>16028300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B237" t="n">
-        <v>261.5199276025597</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C237" t="n">
-        <v>267.7988593124239</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D237" t="n">
-        <v>261.1405900757476</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E237" t="n">
-        <v>263.9656066894531</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F237" t="n">
-        <v>16028300</v>
+        <v>10490600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B238" t="n">
-        <v>262.8974710364521</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C238" t="n">
-        <v>263.1370702625856</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D238" t="n">
-        <v>257.3672223502596</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E238" t="n">
-        <v>258.7747497558594</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F238" t="n">
-        <v>10490600</v>
+        <v>17482700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B239" t="n">
-        <v>253.2744227737308</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C239" t="n">
-        <v>253.5539298242691</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D239" t="n">
-        <v>245.4581718493405</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E239" t="n">
-        <v>248.6824951171875</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F239" t="n">
-        <v>17482700</v>
+        <v>11853700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B240" t="n">
-        <v>249.3413418635835</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C240" t="n">
-        <v>254.3525301395604</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D240" t="n">
-        <v>243.0224566114913</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E240" t="n">
-        <v>243.7312164306641</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F240" t="n">
-        <v>11853700</v>
+        <v>10732600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B241" t="n">
-        <v>244.9191211985708</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C241" t="n">
-        <v>248.0635830600566</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D241" t="n">
-        <v>241.3254374437371</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E241" t="n">
-        <v>242.5732421875</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F241" t="n">
-        <v>10732600</v>
+        <v>9738300</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B242" t="n">
-        <v>241.5949712138984</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C242" t="n">
-        <v>250.1099896964979</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D242" t="n">
-        <v>241.5949712138984</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E242" t="n">
-        <v>247.2849578857422</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F242" t="n">
-        <v>9738300</v>
+        <v>12963700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B243" t="n">
-        <v>255.3008656803045</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C243" t="n">
-        <v>259.7230786425112</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D243" t="n">
-        <v>251.0583293004754</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E243" t="n">
-        <v>258.9743957519531</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F243" t="n">
-        <v>12963700</v>
+        <v>11502800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" t="n">
-        <v>256.43886230448</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C244" t="n">
-        <v>261.8792726915332</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D244" t="n">
-        <v>254.632028246405</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E244" t="n">
-        <v>255.2010192871094</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F244" t="n">
-        <v>11502800</v>
+        <v>9423800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,25 +6787,25 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B245" t="n">
-        <v>251.4077029961344</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C245" t="n">
-        <v>255.9497000259878</v>
+        <v>247</v>
       </c>
       <c r="D245" t="n">
-        <v>249.1616544830015</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E245" t="n">
-        <v>250.0999908447266</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F245" t="n">
-        <v>9423800</v>
+        <v>16611300</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -6813,25 +6813,25 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B246" t="n">
-        <v>244.1799926757812</v>
+        <v>244.25</v>
       </c>
       <c r="C246" t="n">
-        <v>247</v>
+        <v>244.25</v>
       </c>
       <c r="D246" t="n">
-        <v>241.5200042724609</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E246" t="n">
-        <v>242.8500061035156</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F246" t="n">
-        <v>16611300</v>
+        <v>21962400</v>
       </c>
       <c r="G246" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B247" t="n">
-        <v>244.25</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C247" t="n">
-        <v>244.25</v>
+        <v>241.3399963378906</v>
       </c>
       <c r="D247" t="n">
-        <v>236.5500030517578</v>
+        <v>236.25</v>
       </c>
       <c r="E247" t="n">
-        <v>237.9199981689453</v>
+        <v>236.4199981689453</v>
       </c>
       <c r="F247" t="n">
-        <v>21962400</v>
+        <v>10581900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B248" t="n">
-        <v>239.8000030517578</v>
+        <v>241.5</v>
       </c>
       <c r="C248" t="n">
-        <v>241.3399963378906</v>
+        <v>242.4400024414062</v>
       </c>
       <c r="D248" t="n">
-        <v>236.25</v>
+        <v>229.8099975585938</v>
       </c>
       <c r="E248" t="n">
-        <v>236.4199981689453</v>
+        <v>233.2799987792969</v>
       </c>
       <c r="F248" t="n">
-        <v>10581900</v>
+        <v>13635600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B249" t="n">
-        <v>241.5</v>
+        <v>234.4199981689453</v>
       </c>
       <c r="C249" t="n">
-        <v>242.4400024414062</v>
+        <v>241.1199951171875</v>
       </c>
       <c r="D249" t="n">
-        <v>229.8099975585938</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="E249" t="n">
-        <v>233.2799987792969</v>
+        <v>237.5800018310547</v>
       </c>
       <c r="F249" t="n">
-        <v>13635600</v>
+        <v>12353500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B250" t="n">
-        <v>234.4199981689453</v>
+        <v>240.6399993896484</v>
       </c>
       <c r="C250" t="n">
-        <v>241.1199951171875</v>
+        <v>242.0899963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>234.2400054931641</v>
+        <v>237</v>
       </c>
       <c r="E250" t="n">
-        <v>237.5800018310547</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="F250" t="n">
-        <v>12353500</v>
+        <v>11074000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B251" t="n">
-        <v>240.6399993896484</v>
+        <v>237.0299987792969</v>
       </c>
       <c r="C251" t="n">
-        <v>242.0899963378906</v>
+        <v>239.3699951171875</v>
       </c>
       <c r="D251" t="n">
-        <v>237</v>
+        <v>233.3800048828125</v>
       </c>
       <c r="E251" t="n">
-        <v>238.2200012207031</v>
+        <v>234.0200042724609</v>
       </c>
       <c r="F251" t="n">
-        <v>11074000</v>
+        <v>8735500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B252" t="n">
-        <v>237.0299987792969</v>
+        <v>224.9700012207031</v>
       </c>
       <c r="C252" t="n">
-        <v>239.3699951171875</v>
+        <v>230.5700073242188</v>
       </c>
       <c r="D252" t="n">
-        <v>233.3800048828125</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="E252" t="n">
-        <v>234.0200042724609</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="F252" t="n">
-        <v>8735500</v>
+        <v>10263200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10654,37 +10654,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="D2" t="n">
         <v>234.02</v>
       </c>
-      <c r="D2" t="n">
-        <v>238.22</v>
-      </c>
       <c r="E2" t="n">
-        <v>237.03</v>
+        <v>224.97</v>
       </c>
       <c r="F2" t="n">
-        <v>239.37</v>
+        <v>230.565</v>
       </c>
       <c r="G2" t="n">
-        <v>233.38</v>
+        <v>221.18</v>
       </c>
       <c r="H2" t="n">
-        <v>8483000</v>
+        <v>10252517</v>
       </c>
       <c r="I2" t="n">
-        <v>13894941</v>
+        <v>13774936</v>
       </c>
       <c r="J2" t="n">
-        <v>192598458368</v>
+        <v>187043217408</v>
       </c>
       <c r="K2" t="n">
-        <v>21.35219</v>
+        <v>20.79323</v>
       </c>
       <c r="L2" t="n">
-        <v>14.620091</v>
+        <v>14.198394</v>
       </c>
       <c r="M2" t="n">
-        <v>10.96</v>
+        <v>10.93</v>
       </c>
       <c r="N2" t="n">
         <v>269.11</v>
@@ -10696,7 +10696,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10720,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.018442</v>
+        <v>4.873692</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10732,7 +10732,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>223571460096</v>
+        <v>218016202752</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:50:09</t>
+          <t>2026-09-29 13:25:06</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="n">
-        <v>242.6617958656146</v>
+        <v>242.989012448683</v>
       </c>
       <c r="C2" t="n">
-        <v>243.7525504227033</v>
+        <v>243.1476704015903</v>
       </c>
       <c r="D2" t="n">
-        <v>240.8273491460897</v>
+        <v>233.8267199294288</v>
       </c>
       <c r="E2" t="n">
-        <v>243.0386047363281</v>
+        <v>235.0067138671875</v>
       </c>
       <c r="F2" t="n">
-        <v>6373500</v>
+        <v>10801100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>242.989012448683</v>
+        <v>234.5010077854061</v>
       </c>
       <c r="C3" t="n">
-        <v>243.1476704015903</v>
+        <v>240.4307087963897</v>
       </c>
       <c r="D3" t="n">
-        <v>233.8267199294288</v>
+        <v>231.5460601627856</v>
       </c>
       <c r="E3" t="n">
-        <v>235.0067138671875</v>
+        <v>233.7077331542969</v>
       </c>
       <c r="F3" t="n">
-        <v>10801100</v>
+        <v>10016600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B4" t="n">
-        <v>234.5010077854061</v>
+        <v>233.4498996394798</v>
       </c>
       <c r="C4" t="n">
-        <v>240.4307087963897</v>
+        <v>237.3865110117534</v>
       </c>
       <c r="D4" t="n">
-        <v>231.5460601627856</v>
+        <v>231.6353042398812</v>
       </c>
       <c r="E4" t="n">
-        <v>233.7077331542969</v>
+        <v>236.8708953857422</v>
       </c>
       <c r="F4" t="n">
-        <v>10016600</v>
+        <v>7679200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B5" t="n">
-        <v>233.4498996394798</v>
+        <v>236.7419954840688</v>
       </c>
       <c r="C5" t="n">
-        <v>237.3865110117534</v>
+        <v>240.7678464733125</v>
       </c>
       <c r="D5" t="n">
-        <v>231.6353042398812</v>
+        <v>236.4940981065986</v>
       </c>
       <c r="E5" t="n">
-        <v>236.8708953857422</v>
+        <v>238.3384552001953</v>
       </c>
       <c r="F5" t="n">
-        <v>7679200</v>
+        <v>8849800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B6" t="n">
-        <v>236.7419803274875</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="C6" t="n">
-        <v>240.7678310589901</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D6" t="n">
-        <v>236.4940829658881</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E6" t="n">
-        <v>238.3384399414062</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="F6" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B7" t="n">
-        <v>237.3171110157645</v>
+        <v>244.4069823156386</v>
       </c>
       <c r="C7" t="n">
-        <v>248.3634171689519</v>
+        <v>245.2795859409202</v>
       </c>
       <c r="D7" t="n">
-        <v>233.430082086989</v>
+        <v>235.5520951044222</v>
       </c>
       <c r="E7" t="n">
-        <v>243.7128601074219</v>
+        <v>237.7236785888672</v>
       </c>
       <c r="F7" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B8" t="n">
-        <v>244.4069666278678</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C8" t="n">
-        <v>245.2795701971395</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D8" t="n">
-        <v>235.5520799850208</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E8" t="n">
-        <v>237.7236633300781</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F8" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B9" t="n">
-        <v>237.7236681390551</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C9" t="n">
-        <v>239.290381338098</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D9" t="n">
-        <v>233.6680556537968</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E9" t="n">
-        <v>238.4078521728516</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F9" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B10" t="n">
-        <v>237.2576026687149</v>
+        <v>244.4466434616172</v>
       </c>
       <c r="C10" t="n">
-        <v>243.8913382509171</v>
+        <v>246.9553636418975</v>
       </c>
       <c r="D10" t="n">
-        <v>235.1554228281352</v>
+        <v>238.6954214370453</v>
       </c>
       <c r="E10" t="n">
-        <v>243.2666320800781</v>
+        <v>239.6473388671875</v>
       </c>
       <c r="F10" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B11" t="n">
-        <v>244.4466434616172</v>
+        <v>240.8471826425636</v>
       </c>
       <c r="C11" t="n">
-        <v>246.9553636418975</v>
+        <v>247.2528577250976</v>
       </c>
       <c r="D11" t="n">
-        <v>238.6954214370453</v>
+        <v>240.331551845499</v>
       </c>
       <c r="E11" t="n">
-        <v>239.6473388671875</v>
+        <v>246.6578979492188</v>
       </c>
       <c r="F11" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B12" t="n">
-        <v>240.8471677432379</v>
+        <v>246.0232707436915</v>
       </c>
       <c r="C12" t="n">
-        <v>247.252842429503</v>
+        <v>246.1918391425529</v>
       </c>
       <c r="D12" t="n">
-        <v>240.3315369780713</v>
+        <v>237.5352670689401</v>
       </c>
       <c r="E12" t="n">
-        <v>246.6578826904297</v>
+        <v>237.75341796875</v>
       </c>
       <c r="F12" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B13" t="n">
-        <v>246.0232707436915</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C13" t="n">
-        <v>246.1918391425529</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D13" t="n">
-        <v>237.5352670689401</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E13" t="n">
-        <v>237.75341796875</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F13" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B14" t="n">
-        <v>238.8441526809671</v>
+        <v>251.0605458824941</v>
       </c>
       <c r="C14" t="n">
-        <v>239.2903800503502</v>
+        <v>254.5806764744798</v>
       </c>
       <c r="D14" t="n">
-        <v>233.915951765761</v>
+        <v>240.6290201908687</v>
       </c>
       <c r="E14" t="n">
-        <v>234.5902404785156</v>
+        <v>243.9310150146484</v>
       </c>
       <c r="F14" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B15" t="n">
-        <v>251.0605458824941</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="C15" t="n">
-        <v>254.5806764744798</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D15" t="n">
-        <v>240.6290201908687</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E15" t="n">
-        <v>243.9310150146484</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="F15" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B16" t="n">
-        <v>244.4962363844956</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C16" t="n">
-        <v>248.670819810711</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D16" t="n">
-        <v>240.1233229489625</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E16" t="n">
-        <v>241.0355834960938</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F16" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B17" t="n">
-        <v>242.9394381851618</v>
+        <v>252.3595144668565</v>
       </c>
       <c r="C17" t="n">
-        <v>253.2519633865538</v>
+        <v>264.883294034403</v>
       </c>
       <c r="D17" t="n">
-        <v>242.2453285307239</v>
+        <v>251.863719742953</v>
       </c>
       <c r="E17" t="n">
-        <v>252.1413879394531</v>
+        <v>261.194580078125</v>
       </c>
       <c r="F17" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B18" t="n">
-        <v>252.359543952159</v>
+        <v>259.9947875033736</v>
       </c>
       <c r="C18" t="n">
-        <v>264.8833249829649</v>
+        <v>260.1930872533099</v>
       </c>
       <c r="D18" t="n">
-        <v>251.8637491703276</v>
+        <v>254.3526406430638</v>
       </c>
       <c r="E18" t="n">
-        <v>261.1946105957031</v>
+        <v>254.4815521240234</v>
       </c>
       <c r="F18" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B19" t="n">
-        <v>259.9947719140093</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C19" t="n">
-        <v>260.1930716520554</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D19" t="n">
-        <v>254.3526253920043</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E19" t="n">
-        <v>254.4815368652344</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F19" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B20" t="n">
-        <v>255.4334634999039</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C20" t="n">
-        <v>256.3853809552256</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D20" t="n">
-        <v>251.982721115611</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E20" t="n">
-        <v>252.9049072265625</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F20" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B21" t="n">
-        <v>255.254980605377</v>
+        <v>254.9178252470085</v>
       </c>
       <c r="C21" t="n">
-        <v>256.3258839430272</v>
+        <v>255.9292659432784</v>
       </c>
       <c r="D21" t="n">
-        <v>251.8637312244832</v>
+        <v>252.7760033429592</v>
       </c>
       <c r="E21" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213806152344</v>
       </c>
       <c r="F21" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B22" t="n">
-        <v>254.917794537107</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="C22" t="n">
-        <v>255.9292351115289</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D22" t="n">
-        <v>252.7759728910826</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E22" t="n">
-        <v>253.3213500976562</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="F22" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B23" t="n">
-        <v>253.3213661855435</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C23" t="n">
-        <v>256.663017898251</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D23" t="n">
-        <v>252.0025503587843</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E23" t="n">
-        <v>252.1215362548828</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F23" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B24" t="n">
-        <v>249.8805597170771</v>
+        <v>248.3931555366784</v>
       </c>
       <c r="C24" t="n">
-        <v>251.4373625303139</v>
+        <v>257.0993096380665</v>
       </c>
       <c r="D24" t="n">
-        <v>246.9454480725237</v>
+        <v>247.8973608150483</v>
       </c>
       <c r="E24" t="n">
-        <v>249.3451080322266</v>
+        <v>254.4914245605469</v>
       </c>
       <c r="F24" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B25" t="n">
-        <v>248.3931853229768</v>
+        <v>252.6570304305034</v>
       </c>
       <c r="C25" t="n">
-        <v>257.0993404683716</v>
+        <v>259.617993585316</v>
       </c>
       <c r="D25" t="n">
-        <v>247.897390541893</v>
+        <v>250.5052828369448</v>
       </c>
       <c r="E25" t="n">
-        <v>254.491455078125</v>
+        <v>258.2198486328125</v>
       </c>
       <c r="F25" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B26" t="n">
-        <v>252.657000570364</v>
+        <v>257.8132719821094</v>
       </c>
       <c r="C26" t="n">
-        <v>259.6179629024988</v>
+        <v>259.3601491931292</v>
       </c>
       <c r="D26" t="n">
-        <v>250.5052532311086</v>
+        <v>252.9544894469363</v>
       </c>
       <c r="E26" t="n">
-        <v>258.2198181152344</v>
+        <v>259.1419982910156</v>
       </c>
       <c r="F26" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B27" t="n">
-        <v>257.8133023432115</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C27" t="n">
-        <v>259.3601797363976</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D27" t="n">
-        <v>252.9545192358491</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E27" t="n">
-        <v>259.1420288085938</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F27" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>255.9788376046017</v>
+        <v>252.5578398334985</v>
       </c>
       <c r="C28" t="n">
-        <v>257.0795177464699</v>
+        <v>254.6699151564536</v>
       </c>
       <c r="D28" t="n">
-        <v>251.3282953006253</v>
+        <v>249.8904616870965</v>
       </c>
       <c r="E28" t="n">
-        <v>252.300048828125</v>
+        <v>250.5548248291016</v>
       </c>
       <c r="F28" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B29" t="n">
-        <v>252.5578552142711</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="C29" t="n">
-        <v>254.6699306658516</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="D29" t="n">
-        <v>249.8904769054258</v>
+        <v>232.5078921531912</v>
       </c>
       <c r="E29" t="n">
-        <v>250.5548400878906</v>
+        <v>237.2576141357422</v>
       </c>
       <c r="F29" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B30" t="n">
-        <v>248.4328164468309</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="C30" t="n">
-        <v>248.4328164468309</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D30" t="n">
-        <v>232.5078921531912</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E30" t="n">
-        <v>237.2576141357422</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="F30" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B31" t="n">
-        <v>234.1638481621394</v>
+        <v>237.9814688826704</v>
       </c>
       <c r="C31" t="n">
-        <v>238.943316687993</v>
+        <v>239.8754083705041</v>
       </c>
       <c r="D31" t="n">
-        <v>233.8068753463891</v>
+        <v>233.1028505862302</v>
       </c>
       <c r="E31" t="n">
-        <v>237.8624877929688</v>
+        <v>239.6770935058594</v>
       </c>
       <c r="F31" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="n">
-        <v>237.9814840335094</v>
+        <v>239.8655103639031</v>
       </c>
       <c r="C32" t="n">
-        <v>239.8754236419186</v>
+        <v>243.6335537470887</v>
       </c>
       <c r="D32" t="n">
-        <v>233.1028654264771</v>
+        <v>239.1317437673292</v>
       </c>
       <c r="E32" t="n">
-        <v>239.6771087646484</v>
+        <v>242.4436492919922</v>
       </c>
       <c r="F32" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B33" t="n">
-        <v>239.8654952673756</v>
+        <v>243.6732228340941</v>
       </c>
       <c r="C33" t="n">
-        <v>243.63353841341</v>
+        <v>246.3405860290093</v>
       </c>
       <c r="D33" t="n">
-        <v>239.1317287169831</v>
+        <v>241.6305356400256</v>
       </c>
       <c r="E33" t="n">
-        <v>242.4436340332031</v>
+        <v>243.9508666992188</v>
       </c>
       <c r="F33" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B34" t="n">
-        <v>243.6732075926712</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C34" t="n">
-        <v>246.3405706207466</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D34" t="n">
-        <v>241.63052052637</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E34" t="n">
-        <v>243.9508514404297</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F34" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="n">
-        <v>243.1873207442872</v>
+        <v>236.3056776848755</v>
       </c>
       <c r="C35" t="n">
-        <v>243.8318478561575</v>
+        <v>243.1178923149379</v>
       </c>
       <c r="D35" t="n">
-        <v>237.8922365355373</v>
+        <v>235.4231636860313</v>
       </c>
       <c r="E35" t="n">
-        <v>238.4078521728516</v>
+        <v>241.6106872558594</v>
       </c>
       <c r="F35" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B36" t="n">
-        <v>236.3056776848755</v>
+        <v>240.0340571163644</v>
       </c>
       <c r="C36" t="n">
-        <v>243.1178923149379</v>
+        <v>240.7876596253181</v>
       </c>
       <c r="D36" t="n">
-        <v>235.4231636860313</v>
+        <v>233.6085468088289</v>
       </c>
       <c r="E36" t="n">
-        <v>241.6106872558594</v>
+        <v>235.0364379882812</v>
       </c>
       <c r="F36" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B37" t="n">
-        <v>240.0340571163644</v>
+        <v>234.2531087461558</v>
       </c>
       <c r="C37" t="n">
-        <v>240.7876596253181</v>
+        <v>235.7900603656055</v>
       </c>
       <c r="D37" t="n">
-        <v>233.6085468088289</v>
+        <v>228.3333182252886</v>
       </c>
       <c r="E37" t="n">
-        <v>235.0364379882812</v>
+        <v>231.5361480712891</v>
       </c>
       <c r="F37" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B38" t="n">
-        <v>234.2531241839991</v>
+        <v>230.0487686636922</v>
       </c>
       <c r="C38" t="n">
-        <v>235.7900759047376</v>
+        <v>230.3264125188844</v>
       </c>
       <c r="D38" t="n">
-        <v>228.3333332730034</v>
+        <v>223.1671349733107</v>
       </c>
       <c r="E38" t="n">
-        <v>231.5361633300781</v>
+        <v>225.9634246826172</v>
       </c>
       <c r="F38" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B39" t="n">
-        <v>230.0487531290293</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C39" t="n">
-        <v>230.3263969654728</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D39" t="n">
-        <v>223.1671199033486</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E39" t="n">
-        <v>225.9634094238281</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F39" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B40" t="n">
-        <v>227.3218898732066</v>
+        <v>222.9687986720664</v>
       </c>
       <c r="C40" t="n">
-        <v>229.1265900019938</v>
+        <v>226.7566624070738</v>
       </c>
       <c r="D40" t="n">
-        <v>221.4219354522067</v>
+        <v>220.0931953922465</v>
       </c>
       <c r="E40" t="n">
-        <v>223.4745178222656</v>
+        <v>225.1998748779297</v>
       </c>
       <c r="F40" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B41" t="n">
-        <v>222.9688137796853</v>
+        <v>225.4279691980636</v>
       </c>
       <c r="C41" t="n">
-        <v>226.7566777713456</v>
+        <v>226.9153535529684</v>
       </c>
       <c r="D41" t="n">
-        <v>220.0932103050241</v>
+        <v>223.1473101611184</v>
       </c>
       <c r="E41" t="n">
-        <v>225.1998901367188</v>
+        <v>224.912353515625</v>
       </c>
       <c r="F41" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B42" t="n">
-        <v>225.4279539042935</v>
+        <v>224.8925123239678</v>
       </c>
       <c r="C42" t="n">
-        <v>226.9153381582893</v>
+        <v>232.656660293954</v>
       </c>
       <c r="D42" t="n">
-        <v>223.1472950220756</v>
+        <v>224.6148684611971</v>
       </c>
       <c r="E42" t="n">
-        <v>224.9123382568359</v>
+        <v>232.1509399414062</v>
       </c>
       <c r="F42" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="n">
-        <v>224.8924827605518</v>
+        <v>228.5712765635558</v>
       </c>
       <c r="C43" t="n">
-        <v>232.656629709896</v>
+        <v>230.8618608815026</v>
       </c>
       <c r="D43" t="n">
-        <v>224.6148389342789</v>
+        <v>224.0992136322821</v>
       </c>
       <c r="E43" t="n">
-        <v>232.1509094238281</v>
+        <v>226.2311248779297</v>
       </c>
       <c r="F43" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B44" t="n">
-        <v>228.5712919801828</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C44" t="n">
-        <v>230.8618764526245</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D44" t="n">
-        <v>224.0992287472785</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E44" t="n">
-        <v>226.2311401367188</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F44" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="n">
-        <v>227.0739873247604</v>
+        <v>226.7467795144244</v>
       </c>
       <c r="C45" t="n">
-        <v>230.6040433967966</v>
+        <v>232.2798509930075</v>
       </c>
       <c r="D45" t="n">
-        <v>226.7071040647147</v>
+        <v>226.6773761140884</v>
       </c>
       <c r="E45" t="n">
-        <v>228.6010284423828</v>
+        <v>230.8717956542969</v>
       </c>
       <c r="F45" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B46" t="n">
-        <v>226.7467645282661</v>
+        <v>231.0602036533118</v>
       </c>
       <c r="C46" t="n">
-        <v>232.2798356411572</v>
+        <v>234.6596634696697</v>
       </c>
       <c r="D46" t="n">
-        <v>226.6773611325171</v>
+        <v>229.6719691901636</v>
       </c>
       <c r="E46" t="n">
-        <v>230.8717803955078</v>
+        <v>232.7359924316406</v>
       </c>
       <c r="F46" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>231.060173355472</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="C47" t="n">
-        <v>234.6596326998496</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D47" t="n">
-        <v>229.6719390743564</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E47" t="n">
-        <v>232.7359619140625</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="F47" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B48" t="n">
-        <v>233.3805083869321</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C48" t="n">
-        <v>237.2477014354837</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D48" t="n">
-        <v>231.1990144844042</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E48" t="n">
-        <v>236.7122497558594</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F48" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B49" t="n">
-        <v>241.6404418420451</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C49" t="n">
-        <v>246.8760330652079</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D49" t="n">
-        <v>235.6016655641461</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E49" t="n">
-        <v>245.3787384033203</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F49" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B50" t="n">
-        <v>248.7203626098492</v>
+        <v>259.6774396530913</v>
       </c>
       <c r="C50" t="n">
-        <v>259.6774281355445</v>
+        <v>262.0572481860146</v>
       </c>
       <c r="D50" t="n">
-        <v>247.4015469367764</v>
+        <v>254.1840258460871</v>
       </c>
       <c r="E50" t="n">
-        <v>258.3784484863281</v>
+        <v>257.3471984863281</v>
       </c>
       <c r="F50" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B51" t="n">
-        <v>259.6774704470017</v>
+        <v>257.8132661327708</v>
       </c>
       <c r="C51" t="n">
-        <v>262.0572792621351</v>
+        <v>260.0443424743044</v>
       </c>
       <c r="D51" t="n">
-        <v>254.1840559885597</v>
+        <v>256.8216766476447</v>
       </c>
       <c r="E51" t="n">
-        <v>257.3472290039062</v>
+        <v>258.8246765136719</v>
       </c>
       <c r="F51" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B52" t="n">
-        <v>257.8132965310952</v>
+        <v>258.556940201721</v>
       </c>
       <c r="C52" t="n">
-        <v>260.0443731356912</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D52" t="n">
-        <v>256.8217069290525</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E52" t="n">
-        <v>258.82470703125</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="F52" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B53" t="n">
-        <v>258.556940201721</v>
+        <v>261.283846098816</v>
       </c>
       <c r="C53" t="n">
-        <v>263.6933661135803</v>
+        <v>265.646834061187</v>
       </c>
       <c r="D53" t="n">
-        <v>256.9703910840639</v>
+        <v>258.5767957367673</v>
       </c>
       <c r="E53" t="n">
-        <v>261.9779357910156</v>
+        <v>260.1435241699219</v>
       </c>
       <c r="F53" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B54" t="n">
-        <v>261.2838767501659</v>
+        <v>261.3036648523665</v>
       </c>
       <c r="C54" t="n">
-        <v>265.6468652243614</v>
+        <v>262.2655079172122</v>
       </c>
       <c r="D54" t="n">
-        <v>258.5768260705516</v>
+        <v>258.7156306765648</v>
       </c>
       <c r="E54" t="n">
-        <v>260.1435546875</v>
+        <v>260.0245361328125</v>
       </c>
       <c r="F54" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B55" t="n">
-        <v>261.3036341846645</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C55" t="n">
-        <v>262.2654771366241</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D55" t="n">
-        <v>258.7156003126054</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E55" t="n">
-        <v>260.0245056152344</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F55" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B56" t="n">
-        <v>259.0130705063725</v>
+        <v>251.8637326884788</v>
       </c>
       <c r="C56" t="n">
-        <v>260.0740784753494</v>
+        <v>253.7080897614157</v>
       </c>
       <c r="D56" t="n">
-        <v>250.9613690531332</v>
+        <v>249.989629141015</v>
       </c>
       <c r="E56" t="n">
-        <v>252.4388427734375</v>
+        <v>252.7660827636719</v>
       </c>
       <c r="F56" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B57" t="n">
-        <v>251.8637174841621</v>
+        <v>254.1741282350202</v>
       </c>
       <c r="C57" t="n">
-        <v>253.7080744457603</v>
+        <v>259.7667076505979</v>
       </c>
       <c r="D57" t="n">
-        <v>249.9896140498327</v>
+        <v>254.0948143882558</v>
       </c>
       <c r="E57" t="n">
-        <v>252.7660675048828</v>
+        <v>255.9689331054688</v>
       </c>
       <c r="F57" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,25 +1925,25 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B58" t="n">
-        <v>254.1741130832229</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C58" t="n">
-        <v>259.7666921654164</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D58" t="n">
-        <v>254.0947992411865</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E58" t="n">
-        <v>255.9689178466797</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F58" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1951,25 +1951,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B59" t="n">
-        <v>256.6601807669533</v>
+        <v>258.9047600313309</v>
       </c>
       <c r="C59" t="n">
-        <v>258.2989382537239</v>
+        <v>260.2555141825196</v>
       </c>
       <c r="D59" t="n">
-        <v>254.4155616010984</v>
+        <v>253.760043143314</v>
       </c>
       <c r="E59" t="n">
-        <v>256.0940551757812</v>
+        <v>258.1400146484375</v>
       </c>
       <c r="F59" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G59" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B60" t="n">
-        <v>258.904790639318</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="C60" t="n">
-        <v>260.2555449501942</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D60" t="n">
-        <v>253.7600731430874</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E60" t="n">
-        <v>258.1400451660156</v>
+        <v>262.827880859375</v>
       </c>
       <c r="F60" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B61" t="n">
-        <v>258.8451791646396</v>
+        <v>260.930890915143</v>
       </c>
       <c r="C61" t="n">
-        <v>262.827880859375</v>
+        <v>262.4405288782817</v>
       </c>
       <c r="D61" t="n">
-        <v>256.6502376986757</v>
+        <v>258.7458606831942</v>
       </c>
       <c r="E61" t="n">
-        <v>262.827880859375</v>
+        <v>261.6360473632812</v>
       </c>
       <c r="F61" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B62" t="n">
-        <v>260.9308604798152</v>
+        <v>261.4374386085776</v>
       </c>
       <c r="C62" t="n">
-        <v>262.4404982668678</v>
+        <v>264.486509153036</v>
       </c>
       <c r="D62" t="n">
-        <v>258.7458305027313</v>
+        <v>260.7620463111714</v>
       </c>
       <c r="E62" t="n">
-        <v>261.6360168457031</v>
+        <v>263.45361328125</v>
       </c>
       <c r="F62" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B63" t="n">
-        <v>261.4374083245464</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="C63" t="n">
-        <v>264.4864785158107</v>
+        <v>266.0855294787636</v>
       </c>
       <c r="D63" t="n">
-        <v>260.7620161053754</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="E63" t="n">
-        <v>263.4535827636719</v>
+        <v>264.2679748535156</v>
       </c>
       <c r="F63" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B64" t="n">
-        <v>262.9967232703997</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C64" t="n">
-        <v>266.0855602062323</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D64" t="n">
-        <v>262.9967232703997</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E64" t="n">
-        <v>264.2680053710938</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F64" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B65" t="n">
-        <v>262.9072936026629</v>
+        <v>264.8440512488132</v>
       </c>
       <c r="C65" t="n">
-        <v>267.2773231615557</v>
+        <v>266.4530142126886</v>
       </c>
       <c r="D65" t="n">
-        <v>262.9072936026629</v>
+        <v>263.5230915643202</v>
       </c>
       <c r="E65" t="n">
-        <v>264.4169616699219</v>
+        <v>264.1091003417969</v>
       </c>
       <c r="F65" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B66" t="n">
-        <v>264.8440818513142</v>
+        <v>263.4833740671746</v>
       </c>
       <c r="C66" t="n">
-        <v>266.453045001104</v>
+        <v>264.2878555133287</v>
       </c>
       <c r="D66" t="n">
-        <v>263.5231220141856</v>
+        <v>262.5895091614203</v>
       </c>
       <c r="E66" t="n">
-        <v>264.109130859375</v>
+        <v>263.10595703125</v>
       </c>
       <c r="F66" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B67" t="n">
-        <v>263.4834046285292</v>
+        <v>263.1953602739627</v>
       </c>
       <c r="C67" t="n">
-        <v>264.2878861679949</v>
+        <v>263.5727773382559</v>
       </c>
       <c r="D67" t="n">
-        <v>262.5895396190958</v>
+        <v>250.7606167452008</v>
       </c>
       <c r="E67" t="n">
-        <v>263.1059875488281</v>
+        <v>251.8928527832031</v>
       </c>
       <c r="F67" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B68" t="n">
-        <v>263.1953762174182</v>
+        <v>251.8928562905814</v>
       </c>
       <c r="C68" t="n">
-        <v>263.572793304574</v>
+        <v>257.8222021169872</v>
       </c>
       <c r="D68" t="n">
-        <v>250.760631935403</v>
+        <v>250.5917797464572</v>
       </c>
       <c r="E68" t="n">
-        <v>251.8928680419922</v>
+        <v>254.514892578125</v>
       </c>
       <c r="F68" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B69" t="n">
-        <v>251.8928562905814</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C69" t="n">
-        <v>257.8222021169872</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D69" t="n">
-        <v>250.5917797464572</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E69" t="n">
-        <v>254.514892578125</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F69" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B70" t="n">
-        <v>253.4620895509313</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="C70" t="n">
-        <v>261.7552171079225</v>
+        <v>266.0060858079951</v>
       </c>
       <c r="D70" t="n">
-        <v>253.2634545783159</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="E70" t="n">
-        <v>261.1096496582031</v>
+        <v>264.3077392578125</v>
       </c>
       <c r="F70" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B71" t="n">
-        <v>261.7055860975985</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C71" t="n">
-        <v>266.0060858079951</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D71" t="n">
-        <v>261.7055860975985</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E71" t="n">
-        <v>264.3077392578125</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F71" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B72" t="n">
-        <v>262.5994079508812</v>
+        <v>258.2294193019395</v>
       </c>
       <c r="C72" t="n">
-        <v>263.3939780702048</v>
+        <v>259.2524038660146</v>
       </c>
       <c r="D72" t="n">
-        <v>258.6365898818048</v>
+        <v>254.7631956419699</v>
       </c>
       <c r="E72" t="n">
-        <v>258.7557678222656</v>
+        <v>258.1698303222656</v>
       </c>
       <c r="F72" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B73" t="n">
-        <v>258.2293887773175</v>
+        <v>257.2362444131007</v>
       </c>
       <c r="C73" t="n">
-        <v>259.2523732204683</v>
+        <v>259.778808728465</v>
       </c>
       <c r="D73" t="n">
-        <v>254.7631655270811</v>
+        <v>254.0282445272995</v>
       </c>
       <c r="E73" t="n">
-        <v>258.1697998046875</v>
+        <v>257.6335144042969</v>
       </c>
       <c r="F73" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B74" t="n">
-        <v>257.2362139425806</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C74" t="n">
-        <v>259.7787779567694</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D74" t="n">
-        <v>254.028214436778</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E74" t="n">
-        <v>257.6334838867188</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F74" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B75" t="n">
-        <v>255.9053572301452</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C75" t="n">
-        <v>259.1332249596227</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D75" t="n">
-        <v>238.7231659776434</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E75" t="n">
-        <v>239.4183959960938</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F75" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B76" t="n">
-        <v>237.5511941796288</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C76" t="n">
-        <v>240.5903685304685</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D76" t="n">
-        <v>234.849731125901</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E76" t="n">
-        <v>237.9385528564453</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F76" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B77" t="n">
-        <v>235.4059054123066</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C77" t="n">
-        <v>237.2135033883542</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D77" t="n">
-        <v>230.0923326840245</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E77" t="n">
-        <v>231.9396667480469</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F77" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B78" t="n">
-        <v>231.3636110626874</v>
+        <v>222.0176902636222</v>
       </c>
       <c r="C78" t="n">
-        <v>231.3636110626874</v>
+        <v>226.3877354418118</v>
       </c>
       <c r="D78" t="n">
-        <v>224.8979495180149</v>
+        <v>217.8661632569629</v>
       </c>
       <c r="E78" t="n">
-        <v>225.5633850097656</v>
+        <v>218.5713348388672</v>
       </c>
       <c r="F78" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B79" t="n">
-        <v>222.0176902636222</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="C79" t="n">
-        <v>226.3877354418118</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D79" t="n">
-        <v>217.8661632569629</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E79" t="n">
-        <v>218.5713348388672</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="F79" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B80" t="n">
-        <v>218.6507904829158</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C80" t="n">
-        <v>221.8687318042425</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D80" t="n">
-        <v>217.4689070154735</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E80" t="n">
-        <v>220.0710601806641</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F80" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="n">
-        <v>220.7265600038705</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="C81" t="n">
-        <v>227.162427221411</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D81" t="n">
-        <v>219.6042504088122</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E81" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="F81" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B82" t="n">
-        <v>225.2356384112152</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C82" t="n">
-        <v>229.2779291905748</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D82" t="n">
-        <v>225.1065188551059</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E82" t="n">
-        <v>226.4969940185547</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F82" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="n">
-        <v>227.8675783015932</v>
+        <v>230.3604906379282</v>
       </c>
       <c r="C83" t="n">
-        <v>229.3772313706373</v>
+        <v>234.1346156625655</v>
       </c>
       <c r="D83" t="n">
-        <v>226.0401123076792</v>
+        <v>224.7291051659704</v>
       </c>
       <c r="E83" t="n">
-        <v>227.8377838134766</v>
+        <v>226.9737091064453</v>
       </c>
       <c r="F83" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B84" t="n">
-        <v>230.3605061244008</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="C84" t="n">
-        <v>234.1346314027617</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D84" t="n">
-        <v>224.7291202738612</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E84" t="n">
-        <v>226.9737243652344</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="F84" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="n">
-        <v>227.8278625141174</v>
+        <v>215.1944899838427</v>
       </c>
       <c r="C85" t="n">
-        <v>230.2810431236355</v>
+        <v>215.8003365308671</v>
       </c>
       <c r="D85" t="n">
-        <v>226.1195744340916</v>
+        <v>207.3582209619344</v>
       </c>
       <c r="E85" t="n">
-        <v>226.4076080322266</v>
+        <v>212.6221313476562</v>
       </c>
       <c r="F85" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="n">
-        <v>215.1944899838427</v>
+        <v>212.7015749295142</v>
       </c>
       <c r="C86" t="n">
-        <v>215.8003365308671</v>
+        <v>214.0821084291109</v>
       </c>
       <c r="D86" t="n">
-        <v>207.3582209619344</v>
+        <v>209.5928853669118</v>
       </c>
       <c r="E86" t="n">
-        <v>212.6221313476562</v>
+        <v>210.8442993164062</v>
       </c>
       <c r="F86" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B87" t="n">
-        <v>212.7015903227142</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C87" t="n">
-        <v>214.08212392222</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D87" t="n">
-        <v>209.5929005351361</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E87" t="n">
-        <v>210.8443145751953</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F87" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B88" t="n">
-        <v>212.8902908724165</v>
+        <v>203.6039568110546</v>
       </c>
       <c r="C88" t="n">
-        <v>215.4129869027477</v>
+        <v>204.16014080488</v>
       </c>
       <c r="D88" t="n">
-        <v>208.3712731650351</v>
+        <v>191.7949279222085</v>
       </c>
       <c r="E88" t="n">
-        <v>209.3743896484375</v>
+        <v>195.0426635742188</v>
       </c>
       <c r="F88" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B89" t="n">
-        <v>203.60397273962</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C89" t="n">
-        <v>204.1601567769575</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D89" t="n">
-        <v>191.7949429269172</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E89" t="n">
-        <v>195.0426788330078</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F89" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B90" t="n">
-        <v>191.993558028148</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C90" t="n">
-        <v>199.3034370934686</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D90" t="n">
-        <v>186.0046234920971</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E90" t="n">
-        <v>198.0818176269531</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F90" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B91" t="n">
-        <v>192.668943558262</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C91" t="n">
-        <v>198.2010042649258</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D91" t="n">
-        <v>187.5043431662378</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E91" t="n">
-        <v>188.6763153076172</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F91" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="n">
-        <v>190.3250127759971</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C92" t="n">
-        <v>193.2747884158856</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D92" t="n">
-        <v>185.8457159832669</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E92" t="n">
-        <v>190.0469207763672</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F92" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B93" t="n">
-        <v>188.0108792533576</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C93" t="n">
-        <v>193.8706944788449</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D93" t="n">
-        <v>184.465183505092</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E93" t="n">
-        <v>192.7086639404297</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F93" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="n">
-        <v>190.5931665112882</v>
+        <v>191.8346508751069</v>
       </c>
       <c r="C94" t="n">
-        <v>197.7441470694129</v>
+        <v>192.3511139411869</v>
       </c>
       <c r="D94" t="n">
-        <v>189.4510040038842</v>
+        <v>180.5718794169307</v>
       </c>
       <c r="E94" t="n">
-        <v>192.1326141357422</v>
+        <v>183.7401580810547</v>
       </c>
       <c r="F94" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B95" t="n">
-        <v>191.8346508751069</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C95" t="n">
-        <v>192.3511139411869</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D95" t="n">
-        <v>180.5718794169307</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E95" t="n">
-        <v>183.7401580810547</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F95" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B96" t="n">
-        <v>184.6936257308121</v>
+        <v>185.1703620229303</v>
       </c>
       <c r="C96" t="n">
-        <v>187.0375548215625</v>
+        <v>192.1326190686923</v>
       </c>
       <c r="D96" t="n">
-        <v>179.012577513483</v>
+        <v>183.0449358454951</v>
       </c>
       <c r="E96" t="n">
-        <v>184.1672210693359</v>
+        <v>188.4280242919922</v>
       </c>
       <c r="F96" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B97" t="n">
-        <v>185.1703470279448</v>
+        <v>189.6694900334161</v>
       </c>
       <c r="C97" t="n">
-        <v>192.1326035099074</v>
+        <v>191.6856644627849</v>
       </c>
       <c r="D97" t="n">
-        <v>183.0449210226253</v>
+        <v>181.9226052262247</v>
       </c>
       <c r="E97" t="n">
-        <v>188.4280090332031</v>
+        <v>183.0349731445312</v>
       </c>
       <c r="F97" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B98" t="n">
-        <v>189.6695058452945</v>
+        <v>182.6277776277465</v>
       </c>
       <c r="C98" t="n">
-        <v>191.6856804427425</v>
+        <v>186.8587614695496</v>
       </c>
       <c r="D98" t="n">
-        <v>181.9226203922807</v>
+        <v>180.6215296329567</v>
       </c>
       <c r="E98" t="n">
-        <v>183.0349884033203</v>
+        <v>186.5111389160156</v>
       </c>
       <c r="F98" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="n">
-        <v>182.6277925688313</v>
+        <v>185.3292593497056</v>
       </c>
       <c r="C99" t="n">
-        <v>186.8587767567783</v>
+        <v>185.6768667554436</v>
       </c>
       <c r="D99" t="n">
-        <v>180.6215444099069</v>
+        <v>181.9821987572526</v>
       </c>
       <c r="E99" t="n">
-        <v>186.5111541748047</v>
+        <v>184.0281677246094</v>
       </c>
       <c r="F99" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="n">
-        <v>185.3292593497056</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C100" t="n">
-        <v>185.6768667554436</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D100" t="n">
-        <v>181.9821987572526</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E100" t="n">
-        <v>184.0281677246094</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F100" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" t="n">
-        <v>184.0579771467211</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C101" t="n">
-        <v>190.4243134969296</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D101" t="n">
-        <v>182.4787935369736</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E101" t="n">
-        <v>183.8990631103516</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F101" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B102" t="n">
-        <v>180.0355685556146</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C102" t="n">
-        <v>181.2273936107796</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D102" t="n">
-        <v>173.3811981056387</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E102" t="n">
-        <v>176.9467468261719</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F102" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B103" t="n">
-        <v>176.4302852446972</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C103" t="n">
-        <v>187.3851706171715</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D103" t="n">
-        <v>175.0795461293982</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E103" t="n">
-        <v>184.1573028564453</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F103" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B104" t="n">
-        <v>181.7537708108397</v>
+        <v>195.420066371549</v>
       </c>
       <c r="C104" t="n">
-        <v>191.2884009153263</v>
+        <v>199.6709185207204</v>
       </c>
       <c r="D104" t="n">
-        <v>181.0188047518053</v>
+        <v>190.0270517409182</v>
       </c>
       <c r="E104" t="n">
-        <v>190.4441833496094</v>
+        <v>198.1116180419922</v>
       </c>
       <c r="F104" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B105" t="n">
-        <v>195.420066371549</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C105" t="n">
-        <v>199.6709185207204</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D105" t="n">
-        <v>190.0270517409182</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E105" t="n">
-        <v>198.1116180419922</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F105" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B106" t="n">
-        <v>190.6031086414411</v>
+        <v>191.1890691316076</v>
       </c>
       <c r="C106" t="n">
-        <v>194.5857953386064</v>
+        <v>194.6056450515189</v>
       </c>
       <c r="D106" t="n">
-        <v>188.6266549601705</v>
+        <v>189.38145611275</v>
       </c>
       <c r="E106" t="n">
-        <v>193.4634857177734</v>
+        <v>191.6360015869141</v>
       </c>
       <c r="F106" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B107" t="n">
-        <v>191.1890843548102</v>
+        <v>189.4510095395255</v>
       </c>
       <c r="C107" t="n">
-        <v>194.6056605467623</v>
+        <v>197.3170732284266</v>
       </c>
       <c r="D107" t="n">
-        <v>189.3814711920236</v>
+        <v>188.2889789535958</v>
       </c>
       <c r="E107" t="n">
-        <v>191.6360168457031</v>
+        <v>194.7149200439453</v>
       </c>
       <c r="F107" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B108" t="n">
-        <v>189.4509946932415</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C108" t="n">
-        <v>197.3170577657204</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D108" t="n">
-        <v>188.2889641983741</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E108" t="n">
-        <v>194.7149047851562</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F108" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B109" t="n">
-        <v>193.7713848635987</v>
+        <v>193.0364294600736</v>
       </c>
       <c r="C109" t="n">
-        <v>195.1320503828654</v>
+        <v>203.0279194939781</v>
       </c>
       <c r="D109" t="n">
-        <v>190.7918147128814</v>
+        <v>192.9172514970062</v>
       </c>
       <c r="E109" t="n">
-        <v>191.76513671875</v>
+        <v>200.0185546875</v>
       </c>
       <c r="F109" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B110" t="n">
-        <v>193.036414733929</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C110" t="n">
-        <v>203.027904005614</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D110" t="n">
-        <v>192.9172367799533</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E110" t="n">
-        <v>200.0185394287109</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F110" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B111" t="n">
-        <v>199.4226244314719</v>
+        <v>197.2078193049057</v>
       </c>
       <c r="C111" t="n">
-        <v>201.5778601866405</v>
+        <v>202.2830212056148</v>
       </c>
       <c r="D111" t="n">
-        <v>196.0259162627038</v>
+        <v>194.5361355724457</v>
       </c>
       <c r="E111" t="n">
-        <v>200.733642578125</v>
+        <v>197.4362487792969</v>
       </c>
       <c r="F111" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B112" t="n">
-        <v>197.2078193049057</v>
+        <v>195.9166595935153</v>
       </c>
       <c r="C112" t="n">
-        <v>202.2830212056148</v>
+        <v>198.2109412897675</v>
       </c>
       <c r="D112" t="n">
-        <v>194.5361355724457</v>
+        <v>189.3020255204881</v>
       </c>
       <c r="E112" t="n">
-        <v>197.4362487792969</v>
+        <v>193.5826721191406</v>
       </c>
       <c r="F112" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B113" t="n">
-        <v>195.9166595935153</v>
+        <v>195.0625292691439</v>
       </c>
       <c r="C113" t="n">
-        <v>198.2109412897675</v>
+        <v>198.1910871721164</v>
       </c>
       <c r="D113" t="n">
-        <v>189.3020255204881</v>
+        <v>189.987327259986</v>
       </c>
       <c r="E113" t="n">
-        <v>193.5826721191406</v>
+        <v>192.8079986572266</v>
       </c>
       <c r="F113" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B114" t="n">
-        <v>195.0625292691439</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C114" t="n">
-        <v>198.1910871721164</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D114" t="n">
-        <v>189.987327259986</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E114" t="n">
-        <v>192.8079986572266</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F114" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B115" t="n">
-        <v>192.8079750209554</v>
+        <v>198.3698512203022</v>
       </c>
       <c r="C115" t="n">
-        <v>203.4648992272838</v>
+        <v>199.6312068702612</v>
       </c>
       <c r="D115" t="n">
-        <v>191.8346379323055</v>
+        <v>190.4441985938934</v>
       </c>
       <c r="E115" t="n">
-        <v>197.9228973388672</v>
+        <v>191.516845703125</v>
       </c>
       <c r="F115" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B116" t="n">
-        <v>198.3698354155112</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C116" t="n">
-        <v>199.6311909649738</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D116" t="n">
-        <v>190.4441834205658</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E116" t="n">
-        <v>191.5168304443359</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F116" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B117" t="n">
-        <v>193.821025021851</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C117" t="n">
-        <v>197.2773371794379</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D117" t="n">
-        <v>193.821025021851</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E117" t="n">
-        <v>196.9893035888672</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F117" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B118" t="n">
-        <v>196.870136689126</v>
+        <v>192.0829395046699</v>
       </c>
       <c r="C118" t="n">
-        <v>201.0018110133274</v>
+        <v>194.8142119985075</v>
       </c>
       <c r="D118" t="n">
-        <v>193.1258058856387</v>
+        <v>191.3281205621285</v>
       </c>
       <c r="E118" t="n">
-        <v>193.9799499511719</v>
+        <v>193.0165405273438</v>
       </c>
       <c r="F118" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B119" t="n">
-        <v>192.0829546896537</v>
+        <v>194.2580448499211</v>
       </c>
       <c r="C119" t="n">
-        <v>194.8142273994103</v>
+        <v>199.0352867281362</v>
       </c>
       <c r="D119" t="n">
-        <v>191.3281356874407</v>
+        <v>191.9836462262046</v>
       </c>
       <c r="E119" t="n">
-        <v>193.0165557861328</v>
+        <v>193.6621398925781</v>
       </c>
       <c r="F119" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B120" t="n">
-        <v>194.2580448499211</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C120" t="n">
-        <v>199.0352867281362</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D120" t="n">
-        <v>191.9836462262046</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E120" t="n">
-        <v>193.6621398925781</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F120" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B121" t="n">
-        <v>191.8942484911283</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C121" t="n">
-        <v>194.3374874288811</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D121" t="n">
-        <v>188.7061018910339</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E121" t="n">
-        <v>194.0494689941406</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F121" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B122" t="n">
-        <v>195.7478267440036</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C122" t="n">
-        <v>196.7012958768407</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D122" t="n">
-        <v>190.6924929381777</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E122" t="n">
-        <v>193.850830078125</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F122" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B123" t="n">
-        <v>190.8315397252546</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="C123" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D123" t="n">
-        <v>181.0486114593648</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E123" t="n">
-        <v>181.7736511230469</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="F123" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B124" t="n">
-        <v>184.4353921172228</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C124" t="n">
-        <v>186.1138857525603</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D124" t="n">
-        <v>178.6252393274517</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E124" t="n">
-        <v>180.7208709716797</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F124" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B125" t="n">
-        <v>179.9461742219026</v>
+        <v>182.7469769199218</v>
       </c>
       <c r="C125" t="n">
-        <v>186.1933484091056</v>
+        <v>182.8562284362321</v>
       </c>
       <c r="D125" t="n">
-        <v>178.3074166263376</v>
+        <v>177.6022595179307</v>
       </c>
       <c r="E125" t="n">
-        <v>184.3758087158203</v>
+        <v>178.0889129638672</v>
       </c>
       <c r="F125" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B126" t="n">
-        <v>182.7469769199218</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C126" t="n">
-        <v>182.8562284362321</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D126" t="n">
-        <v>177.6022595179307</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E126" t="n">
-        <v>178.0889129638672</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F126" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" t="n">
-        <v>178.873523844959</v>
+        <v>183.6408226716892</v>
       </c>
       <c r="C127" t="n">
-        <v>185.1206822343098</v>
+        <v>187.2163126895138</v>
       </c>
       <c r="D127" t="n">
-        <v>178.3570608051074</v>
+        <v>181.0684642406058</v>
       </c>
       <c r="E127" t="n">
-        <v>183.7699432373047</v>
+        <v>185.3987731933594</v>
       </c>
       <c r="F127" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" t="n">
-        <v>183.6408226716892</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C128" t="n">
-        <v>187.2163126895138</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D128" t="n">
-        <v>181.0684642406058</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E128" t="n">
-        <v>185.3987731933594</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F128" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B129" t="n">
-        <v>185.5775567084869</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C129" t="n">
-        <v>187.6930410934417</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D129" t="n">
-        <v>181.7636956083204</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E129" t="n">
-        <v>184.9717102050781</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F129" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B130" t="n">
-        <v>184.0381169897925</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C130" t="n">
-        <v>186.3025890630262</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D130" t="n">
-        <v>180.3434488377003</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E130" t="n">
-        <v>185.9053039550781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F130" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" t="n">
-        <v>186.2231237330043</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C131" t="n">
-        <v>186.8587647224845</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D131" t="n">
-        <v>182.3496888213084</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E131" t="n">
-        <v>183.7699432373047</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F131" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" t="n">
-        <v>183.6904887071696</v>
+        <v>185.2299504420264</v>
       </c>
       <c r="C132" t="n">
-        <v>185.3093932676422</v>
+        <v>185.4981160077481</v>
       </c>
       <c r="D132" t="n">
-        <v>180.7804492618957</v>
+        <v>174.5829515420302</v>
       </c>
       <c r="E132" t="n">
-        <v>181.7140502929688</v>
+        <v>175.1689300537109</v>
       </c>
       <c r="F132" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B133" t="n">
-        <v>185.2299504420264</v>
+        <v>172.4208565486944</v>
       </c>
       <c r="C133" t="n">
-        <v>185.4981160077481</v>
+        <v>173.5360065139178</v>
       </c>
       <c r="D133" t="n">
-        <v>174.5829515420302</v>
+        <v>166.3970260969056</v>
       </c>
       <c r="E133" t="n">
-        <v>175.1689300537109</v>
+        <v>170.1109008789062</v>
       </c>
       <c r="F133" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B134" t="n">
-        <v>172.4208565486944</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C134" t="n">
-        <v>173.5360065139178</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D134" t="n">
-        <v>166.3970260969056</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E134" t="n">
-        <v>170.1109008789062</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F134" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G134" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B135" t="n">
-        <v>170.5191174814139</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C135" t="n">
-        <v>170.5191174814139</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D135" t="n">
-        <v>162.8126107290287</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E135" t="n">
-        <v>164.2463836669922</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F135" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B136" t="n">
-        <v>166.3273444705899</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C136" t="n">
-        <v>172.6498652447362</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D136" t="n">
-        <v>165.0528829680655</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E136" t="n">
-        <v>172.0723876953125</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F136" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B137" t="n">
-        <v>174.4520463656914</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C137" t="n">
-        <v>176.7321331165696</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D137" t="n">
-        <v>169.7624151908458</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E137" t="n">
-        <v>170.5689086914062</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F137" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B138" t="n">
-        <v>173.4663277892384</v>
+        <v>183.2040230257668</v>
       </c>
       <c r="C138" t="n">
-        <v>178.842961383224</v>
+        <v>183.7516467853238</v>
       </c>
       <c r="D138" t="n">
-        <v>172.1321282578628</v>
+        <v>177.7975202909648</v>
       </c>
       <c r="E138" t="n">
-        <v>176.8317108154297</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F138" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B139" t="n">
-        <v>183.2040230257668</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C139" t="n">
-        <v>183.7516467853238</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D139" t="n">
-        <v>177.7975202909648</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E139" t="n">
-        <v>180.4360504150391</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F139" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="n">
-        <v>184.6278268926657</v>
+        <v>181.7104926433502</v>
       </c>
       <c r="C140" t="n">
-        <v>187.1667986912511</v>
+        <v>188.1823732032504</v>
       </c>
       <c r="D140" t="n">
-        <v>180.2468672661974</v>
+        <v>181.33213168739</v>
       </c>
       <c r="E140" t="n">
-        <v>181.3520660400391</v>
+        <v>185.4641876220703</v>
       </c>
       <c r="F140" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B141" t="n">
-        <v>181.7104926433502</v>
+        <v>185.7927793430547</v>
       </c>
       <c r="C141" t="n">
-        <v>188.1823732032504</v>
+        <v>192.7226620565929</v>
       </c>
       <c r="D141" t="n">
-        <v>181.33213168739</v>
+        <v>183.3035942778625</v>
       </c>
       <c r="E141" t="n">
-        <v>185.4641876220703</v>
+        <v>186.3005676269531</v>
       </c>
       <c r="F141" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B142" t="n">
-        <v>185.7927793430547</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C142" t="n">
-        <v>192.7226620565929</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D142" t="n">
-        <v>183.3035942778625</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E142" t="n">
-        <v>186.3005676269531</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F142" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B143" t="n">
-        <v>187.3858431404722</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C143" t="n">
-        <v>190.3230783921826</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D143" t="n">
-        <v>186.2209063874661</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E143" t="n">
-        <v>188.9789276123047</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F143" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B144" t="n">
-        <v>176.7918740224492</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C144" t="n">
-        <v>178.0962045390804</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D144" t="n">
-        <v>169.9117629967484</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E144" t="n">
-        <v>172.5503082275391</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F144" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B145" t="n">
-        <v>174.8602617765654</v>
+        <v>177.4888357619529</v>
       </c>
       <c r="C145" t="n">
-        <v>177.6780209996891</v>
+        <v>183.4927485632761</v>
       </c>
       <c r="D145" t="n">
-        <v>173.6455382897692</v>
+        <v>176.7420802872333</v>
       </c>
       <c r="E145" t="n">
-        <v>177.3892822265625</v>
+        <v>179.4005279541016</v>
       </c>
       <c r="F145" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="n">
-        <v>177.4888357619529</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C146" t="n">
-        <v>183.4927485632761</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D146" t="n">
-        <v>176.7420802872333</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E146" t="n">
-        <v>179.4005279541016</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F146" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B147" t="n">
-        <v>181.6407975504903</v>
+        <v>178.4247846039299</v>
       </c>
       <c r="C147" t="n">
-        <v>183.6221942474171</v>
+        <v>180.993625445577</v>
       </c>
       <c r="D147" t="n">
-        <v>180.5356140136719</v>
+        <v>176.5827967489585</v>
       </c>
       <c r="E147" t="n">
-        <v>180.5356140136719</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F147" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="n">
-        <v>178.4247846039299</v>
+        <v>177.5286895189733</v>
       </c>
       <c r="C148" t="n">
-        <v>180.993625445577</v>
+        <v>177.9170017981234</v>
       </c>
       <c r="D148" t="n">
-        <v>176.5827967489585</v>
+        <v>172.2516139153796</v>
       </c>
       <c r="E148" t="n">
-        <v>180.4360504150391</v>
+        <v>175.7663421630859</v>
       </c>
       <c r="F148" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B149" t="n">
-        <v>177.5286895189733</v>
+        <v>181.4018421076459</v>
       </c>
       <c r="C149" t="n">
-        <v>177.9170017981234</v>
+        <v>185.2351777570901</v>
       </c>
       <c r="D149" t="n">
-        <v>172.2516139153796</v>
+        <v>177.9767212373249</v>
       </c>
       <c r="E149" t="n">
-        <v>175.7663421630859</v>
+        <v>183.0247955322266</v>
       </c>
       <c r="F149" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="n">
-        <v>181.4018421076459</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C150" t="n">
-        <v>185.2351777570901</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D150" t="n">
-        <v>177.9767212373249</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E150" t="n">
-        <v>183.0247955322266</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F150" t="n">
-        <v>12324400</v>
+        <v>8444700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="n">
-        <v>183.4429710909726</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C151" t="n">
-        <v>189.4867039708132</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D151" t="n">
-        <v>183.1741348747832</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E151" t="n">
-        <v>184.6775970458984</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F151" t="n">
-        <v>8444700</v>
+        <v>9740800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="n">
-        <v>184.7473182824849</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C152" t="n">
-        <v>186.5793548412774</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D152" t="n">
-        <v>180.3165719120649</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E152" t="n">
-        <v>186.1810913085938</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F152" t="n">
-        <v>9740800</v>
+        <v>11303400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="n">
-        <v>184.7174439304337</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C153" t="n">
-        <v>186.2906106667237</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D153" t="n">
-        <v>178.8031379653169</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E153" t="n">
-        <v>180.4061737060547</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F153" t="n">
-        <v>11303400</v>
+        <v>13955100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="n">
-        <v>183.801426731489</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C154" t="n">
-        <v>187.7642050029951</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D154" t="n">
-        <v>183.2040162535504</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E154" t="n">
-        <v>185.5338897705078</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F154" t="n">
-        <v>13955100</v>
+        <v>15123900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="n">
-        <v>178.9027054786904</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C155" t="n">
-        <v>181.0832340725416</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D155" t="n">
-        <v>176.114830301217</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E155" t="n">
-        <v>181.0334625244141</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F155" t="n">
-        <v>15123900</v>
+        <v>11145000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="n">
-        <v>179.1317124775628</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C156" t="n">
-        <v>181.7105044839724</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D156" t="n">
-        <v>175.5472800106302</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E156" t="n">
-        <v>176.7221832275391</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F156" t="n">
-        <v>11145000</v>
+        <v>10214000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C157" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D157" t="n">
-        <v>169.8420709331304</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E157" t="n">
-        <v>170.5689086914062</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F157" t="n">
-        <v>10214000</v>
+        <v>11951900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="n">
-        <v>169.0455318751909</v>
+        <v>165.2818899628073</v>
       </c>
       <c r="C158" t="n">
-        <v>169.0455318751909</v>
+        <v>168.6174040602531</v>
       </c>
       <c r="D158" t="n">
-        <v>164.0372928300067</v>
+        <v>163.6191161459536</v>
       </c>
       <c r="E158" t="n">
-        <v>165.1225738525391</v>
+        <v>166.8550567626953</v>
       </c>
       <c r="F158" t="n">
-        <v>11951900</v>
+        <v>9749400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="n">
-        <v>165.2818899628073</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C159" t="n">
-        <v>168.6174040602531</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D159" t="n">
-        <v>163.6191161459536</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E159" t="n">
-        <v>166.8550567626953</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F159" t="n">
-        <v>9749400</v>
+        <v>13883400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="n">
-        <v>168.5178185348167</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C160" t="n">
-        <v>175.208748793394</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D160" t="n">
-        <v>168.268900043628</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E160" t="n">
-        <v>172.7593841552734</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F160" t="n">
-        <v>13883400</v>
+        <v>13671200</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="n">
-        <v>172.1420794089453</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C161" t="n">
-        <v>179.9979467596552</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D161" t="n">
-        <v>171.0567983816156</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E161" t="n">
-        <v>178.7035675048828</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F161" t="n">
-        <v>13671200</v>
+        <v>17510800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="n">
-        <v>184.1996921538</v>
+        <v>175.2784580726278</v>
       </c>
       <c r="C162" t="n">
-        <v>186.6291391730516</v>
+        <v>179.5299906412754</v>
       </c>
       <c r="D162" t="n">
-        <v>178.0364675908902</v>
+        <v>172.5901410995666</v>
       </c>
       <c r="E162" t="n">
-        <v>178.6438293457031</v>
+        <v>179.3209075927734</v>
       </c>
       <c r="F162" t="n">
-        <v>17510800</v>
+        <v>13025300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="n">
-        <v>175.2784580726278</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C163" t="n">
-        <v>179.5299906412754</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D163" t="n">
-        <v>172.5901410995666</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E163" t="n">
-        <v>179.3209075927734</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F163" t="n">
-        <v>13025300</v>
+        <v>10949100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="n">
-        <v>174.6213174256682</v>
+        <v>179.0620149167984</v>
       </c>
       <c r="C164" t="n">
-        <v>176.5728300297275</v>
+        <v>182.5568405051486</v>
       </c>
       <c r="D164" t="n">
-        <v>171.2459830488208</v>
+        <v>176.9113553536261</v>
       </c>
       <c r="E164" t="n">
-        <v>175.5472869873047</v>
+        <v>179.2910308837891</v>
       </c>
       <c r="F164" t="n">
-        <v>10949100</v>
+        <v>10176700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B165" t="n">
-        <v>179.0620149167984</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C165" t="n">
-        <v>182.5568405051486</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D165" t="n">
-        <v>176.9113553536261</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E165" t="n">
-        <v>179.2910308837891</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F165" t="n">
-        <v>10176700</v>
+        <v>13617200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B166" t="n">
-        <v>177.6581006500201</v>
+        <v>177.2299817033781</v>
       </c>
       <c r="C166" t="n">
-        <v>181.5711072848628</v>
+        <v>183.1243702829636</v>
       </c>
       <c r="D166" t="n">
-        <v>176.9113451663183</v>
+        <v>176.1247828951571</v>
       </c>
       <c r="E166" t="n">
-        <v>178.3052978515625</v>
+        <v>176.7420959472656</v>
       </c>
       <c r="F166" t="n">
-        <v>13617200</v>
+        <v>18524900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B167" t="n">
-        <v>177.2299817033781</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C167" t="n">
-        <v>183.1243702829636</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D167" t="n">
-        <v>176.1247828951571</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E167" t="n">
-        <v>176.7420959472656</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F167" t="n">
-        <v>18524900</v>
+        <v>22559400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B168" t="n">
-        <v>177.6581004088628</v>
+        <v>179.4602947300403</v>
       </c>
       <c r="C168" t="n">
-        <v>181.6905830539347</v>
+        <v>193.300157831373</v>
       </c>
       <c r="D168" t="n">
-        <v>170.9074320607842</v>
+        <v>179.2412452254626</v>
       </c>
       <c r="E168" t="n">
-        <v>175.4078826904297</v>
+        <v>190.2733154296875</v>
       </c>
       <c r="F168" t="n">
-        <v>22559400</v>
+        <v>33998900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B169" t="n">
-        <v>179.4602947300403</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C169" t="n">
-        <v>193.300157831373</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D169" t="n">
-        <v>179.2412452254626</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E169" t="n">
-        <v>190.2733154296875</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F169" t="n">
-        <v>33998900</v>
+        <v>27594800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="n">
-        <v>197.8901992931745</v>
+        <v>200.1504053799259</v>
       </c>
       <c r="C170" t="n">
-        <v>210.4257307870387</v>
+        <v>203.5058221270036</v>
       </c>
       <c r="D170" t="n">
-        <v>197.352542040295</v>
+        <v>194.9131500594789</v>
       </c>
       <c r="E170" t="n">
-        <v>208.6932678222656</v>
+        <v>199.9711761474609</v>
       </c>
       <c r="F170" t="n">
-        <v>27594800</v>
+        <v>19216600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="n">
-        <v>200.1504053799259</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C171" t="n">
-        <v>203.5058221270036</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D171" t="n">
-        <v>194.9131500594789</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E171" t="n">
-        <v>199.9711761474609</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F171" t="n">
-        <v>19216600</v>
+        <v>14154400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B172" t="n">
-        <v>196.4166079226038</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C172" t="n">
-        <v>196.8248227029743</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D172" t="n">
-        <v>188.9092176958791</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E172" t="n">
-        <v>189.7854156494141</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F172" t="n">
-        <v>14154400</v>
+        <v>14453600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B173" t="n">
-        <v>196.9542758894677</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C173" t="n">
-        <v>197.2330634002457</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D173" t="n">
-        <v>185.3048928689384</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E173" t="n">
-        <v>187.9334716796875</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F173" t="n">
-        <v>14453600</v>
+        <v>13183900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B174" t="n">
-        <v>188.9789318725711</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C174" t="n">
-        <v>191.6771999565016</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D174" t="n">
-        <v>184.0304307819904</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E174" t="n">
-        <v>184.8568420410156</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F174" t="n">
-        <v>13183900</v>
+        <v>11177800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="n">
-        <v>183.1144169895118</v>
+        <v>178.7234714192057</v>
       </c>
       <c r="C175" t="n">
-        <v>184.2196157855271</v>
+        <v>181.670672953058</v>
       </c>
       <c r="D175" t="n">
-        <v>180.92393713233</v>
+        <v>170.8178179406258</v>
       </c>
       <c r="E175" t="n">
-        <v>181.7602996826172</v>
+        <v>174.5914306640625</v>
       </c>
       <c r="F175" t="n">
-        <v>11177800</v>
+        <v>15427800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="n">
-        <v>178.7234714192057</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C176" t="n">
-        <v>181.670672953058</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D176" t="n">
-        <v>170.8178179406258</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E176" t="n">
-        <v>174.5914306640625</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F176" t="n">
-        <v>15427800</v>
+        <v>10820500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="n">
-        <v>169.861995238658</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C177" t="n">
-        <v>174.7706609037228</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D177" t="n">
-        <v>169.2944537502145</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E177" t="n">
-        <v>170.1806030273438</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F177" t="n">
-        <v>10820500</v>
+        <v>16666000</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B178" t="n">
-        <v>167.9744954285649</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C178" t="n">
-        <v>168.6832400259219</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D178" t="n">
-        <v>163.0231992739924</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E178" t="n">
-        <v>166.1576843261719</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F178" t="n">
-        <v>16666000</v>
+        <v>13589400</v>
       </c>
       <c r="G178" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B179" t="n">
-        <v>164.4506890531704</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C179" t="n">
-        <v>166.2475157071144</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D179" t="n">
-        <v>161.1165431857153</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E179" t="n">
-        <v>165.5986633300781</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F179" t="n">
-        <v>13589400</v>
+        <v>13541800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B180" t="n">
-        <v>165.7384133733495</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C180" t="n">
-        <v>169.6515271583533</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D180" t="n">
-        <v>163.8816793355271</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E180" t="n">
-        <v>164.2610168457031</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F180" t="n">
-        <v>13541800</v>
+        <v>16385300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B181" t="n">
-        <v>163.7718739013043</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C181" t="n">
-        <v>166.0079454764833</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D181" t="n">
-        <v>160.2181284427459</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E181" t="n">
-        <v>161.4260101318359</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F181" t="n">
-        <v>16385300</v>
+        <v>19986200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B182" t="n">
-        <v>159.9685677271403</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C182" t="n">
-        <v>161.1464880907799</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D182" t="n">
-        <v>153.959135832121</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E182" t="n">
-        <v>154.7477569580078</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F182" t="n">
-        <v>19986200</v>
+        <v>57940800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B183" t="n">
-        <v>152.4617715583163</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C183" t="n">
-        <v>154.1987212566731</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D183" t="n">
-        <v>149.5369245308901</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E183" t="n">
-        <v>151.5134429931641</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F183" t="n">
-        <v>57940800</v>
+        <v>20502800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B184" t="n">
-        <v>149.8962920415152</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C184" t="n">
-        <v>153.5997679942281</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D184" t="n">
-        <v>146.0630395211035</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E184" t="n">
-        <v>149.8563537597656</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F184" t="n">
-        <v>20502800</v>
+        <v>20720700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B185" t="n">
-        <v>151.3836627210609</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C185" t="n">
-        <v>154.907462036052</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D185" t="n">
-        <v>150.5850798848861</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E185" t="n">
-        <v>153.1505584716797</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F185" t="n">
-        <v>20720700</v>
+        <v>13146800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B186" t="n">
-        <v>151.5433859321397</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C186" t="n">
-        <v>156.7841657815476</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D186" t="n">
-        <v>150.135858545478</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E186" t="n">
-        <v>152.4917144775391</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F186" t="n">
-        <v>13146800</v>
+        <v>11324700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B187" t="n">
-        <v>149.7465472087312</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C187" t="n">
-        <v>153.7295454610107</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D187" t="n">
-        <v>148.5187115976041</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E187" t="n">
-        <v>149.9262390136719</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F187" t="n">
-        <v>11324700</v>
+        <v>21267900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B188" t="n">
-        <v>151.2239658596097</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C188" t="n">
-        <v>158.1817266914859</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D188" t="n">
-        <v>151.2239658596097</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E188" t="n">
-        <v>158.0918731689453</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F188" t="n">
-        <v>21267900</v>
+        <v>12664100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B189" t="n">
-        <v>159.9885357004027</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C189" t="n">
-        <v>161.4759091917036</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D189" t="n">
-        <v>157.4230418613804</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E189" t="n">
-        <v>157.6526336669922</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F189" t="n">
-        <v>12664100</v>
+        <v>13690500</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B190" t="n">
-        <v>154.8176224085462</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C190" t="n">
-        <v>157.4130622995693</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D190" t="n">
-        <v>153.7994247316601</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E190" t="n">
-        <v>156.3848724365234</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F190" t="n">
-        <v>13690500</v>
+        <v>14164600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B191" t="n">
-        <v>161.9351081174896</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C191" t="n">
-        <v>165.5187996520913</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D191" t="n">
-        <v>160.916895191227</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E191" t="n">
-        <v>162.9433288574219</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F191" t="n">
-        <v>14164600</v>
+        <v>10486300</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B192" t="n">
-        <v>162.7137441629</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C192" t="n">
-        <v>166.9163573859938</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D192" t="n">
-        <v>161.7155003336798</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E192" t="n">
-        <v>165.8182830810547</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F192" t="n">
-        <v>10486300</v>
+        <v>10595500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B193" t="n">
-        <v>163.7020118941432</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C193" t="n">
-        <v>167.425457131665</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D193" t="n">
-        <v>162.0848465245878</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E193" t="n">
-        <v>165.3590850830078</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F193" t="n">
-        <v>10595500</v>
+        <v>13057900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B194" t="n">
-        <v>168.9228138583306</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C194" t="n">
-        <v>172.0772678623225</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D194" t="n">
-        <v>167.3855099055031</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E194" t="n">
-        <v>169.2222900390625</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F194" t="n">
-        <v>13057900</v>
+        <v>9792400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B195" t="n">
-        <v>167.0760662569272</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C195" t="n">
-        <v>167.2357889266519</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D195" t="n">
-        <v>164.4906183727253</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E195" t="n">
-        <v>166.2874603271484</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F195" t="n">
-        <v>9792400</v>
+        <v>13858600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B196" t="n">
-        <v>158.05194011754</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C196" t="n">
-        <v>163.5123348335076</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D196" t="n">
-        <v>156.2051830247059</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E196" t="n">
-        <v>162.2146148681641</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F196" t="n">
-        <v>13858600</v>
+        <v>8321500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B197" t="n">
-        <v>165.309182555471</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C197" t="n">
-        <v>166.007950182526</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D197" t="n">
-        <v>162.1347592897187</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E197" t="n">
-        <v>163.0331878662109</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F197" t="n">
-        <v>8321500</v>
+        <v>14020700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>165.6286161244176</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C198" t="n">
-        <v>172.4566003351415</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D198" t="n">
-        <v>165.6286161244176</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E198" t="n">
-        <v>170.9193115234375</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F198" t="n">
-        <v>14020700</v>
+        <v>13507900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>162.2046435717354</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C199" t="n">
-        <v>171.049084414024</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D199" t="n">
-        <v>161.1864306117812</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E199" t="n">
-        <v>167.2657318115234</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F199" t="n">
-        <v>13507900</v>
+        <v>13328100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>170.2205331766167</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C200" t="n">
-        <v>172.4965277703878</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D200" t="n">
-        <v>166.2674811162824</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E200" t="n">
-        <v>166.7067108154297</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F200" t="n">
-        <v>13328100</v>
+        <v>12057500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B201" t="n">
-        <v>170.5399744864679</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C201" t="n">
-        <v>174.2334736592566</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D201" t="n">
-        <v>166.5869373980102</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E201" t="n">
-        <v>172.3767395019531</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F201" t="n">
-        <v>12057500</v>
+        <v>10191500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B202" t="n">
-        <v>171.1988064601764</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C202" t="n">
-        <v>175.1218971627477</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D202" t="n">
-        <v>169.4518798636439</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E202" t="n">
-        <v>170.4700927734375</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F202" t="n">
-        <v>10191500</v>
+        <v>13426500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B203" t="n">
-        <v>167.5652084388413</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C203" t="n">
-        <v>175.0819831940494</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D203" t="n">
-        <v>166.2075962327059</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E203" t="n">
-        <v>173.4847869873047</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F203" t="n">
-        <v>13426500</v>
+        <v>12831800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B204" t="n">
-        <v>166.7666058963373</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C204" t="n">
-        <v>172.1271701993457</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D204" t="n">
-        <v>166.6368293287962</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E204" t="n">
-        <v>169.7613372802734</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F204" t="n">
-        <v>12831800</v>
+        <v>12194500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B205" t="n">
-        <v>169.1723839486806</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C205" t="n">
-        <v>169.272214424985</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D205" t="n">
-        <v>161.925139189555</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E205" t="n">
-        <v>162.7137451171875</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F205" t="n">
-        <v>12194500</v>
+        <v>12775000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B206" t="n">
-        <v>164.7601382451291</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C206" t="n">
-        <v>165.5886824068968</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D206" t="n">
-        <v>154.877515725338</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E206" t="n">
-        <v>156.6543884277344</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F206" t="n">
-        <v>12775000</v>
+        <v>10899100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B207" t="n">
-        <v>160.0983505627206</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C207" t="n">
-        <v>164.1611950360997</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D207" t="n">
-        <v>159.2698063547753</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E207" t="n">
-        <v>163.3725891113281</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F207" t="n">
-        <v>10899100</v>
+        <v>17312000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B208" t="n">
-        <v>167.7049639405646</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C208" t="n">
-        <v>176.6392431993331</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D208" t="n">
-        <v>166.8464736349225</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E208" t="n">
-        <v>173.2951354980469</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F208" t="n">
-        <v>17312000</v>
+        <v>17204600</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B209" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C209" t="n">
-        <v>184.2158982492034</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D209" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E209" t="n">
-        <v>181.1812438964844</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F209" t="n">
-        <v>17204600</v>
+        <v>18139500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B210" t="n">
-        <v>181.6903554713178</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C210" t="n">
-        <v>189.8460057999592</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D210" t="n">
-        <v>181.6903554713178</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E210" t="n">
-        <v>188.0491790771484</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F210" t="n">
-        <v>18139500</v>
+        <v>12182400</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B211" t="n">
-        <v>180.6721461984077</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C211" t="n">
-        <v>182.1894657683464</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D211" t="n">
-        <v>175.5910738107855</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E211" t="n">
-        <v>180.3926391601562</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F211" t="n">
-        <v>12182400</v>
+        <v>9691500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B212" t="n">
-        <v>177.3879151720665</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C212" t="n">
-        <v>184.1260606305619</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D212" t="n">
-        <v>176.719093672914</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E212" t="n">
-        <v>183.6968231201172</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F212" t="n">
-        <v>9691500</v>
+        <v>12908000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B213" t="n">
-        <v>188.658097974018</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C213" t="n">
-        <v>193.3598176605707</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D213" t="n">
-        <v>185.5735131091938</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E213" t="n">
-        <v>185.6234283447266</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F213" t="n">
-        <v>12908000</v>
+        <v>9326900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B214" t="n">
-        <v>182.7684517177381</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C214" t="n">
-        <v>190.9540477431734</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D214" t="n">
-        <v>182.6786134323838</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E214" t="n">
-        <v>190.6545867919922</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F214" t="n">
-        <v>9326900</v>
+        <v>9605500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B215" t="n">
-        <v>192.9405589477455</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C215" t="n">
-        <v>194.5976472985604</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D215" t="n">
-        <v>190.0955580470331</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E215" t="n">
-        <v>192.6410827636719</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F215" t="n">
-        <v>9605500</v>
+        <v>13297600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B216" t="n">
-        <v>183.117847615437</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C216" t="n">
-        <v>186.6915622961891</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D216" t="n">
-        <v>182.6786179003067</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E216" t="n">
-        <v>186.4420013427734</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F216" t="n">
-        <v>13297600</v>
+        <v>11392800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B217" t="n">
-        <v>190.7544083295565</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C217" t="n">
-        <v>194.3580691369978</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D217" t="n">
-        <v>190.2652786051507</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E217" t="n">
-        <v>192.4015197753906</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F217" t="n">
-        <v>11392800</v>
+        <v>9706600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B218" t="n">
-        <v>189.8360257192551</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C218" t="n">
-        <v>197.831953246477</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D218" t="n">
-        <v>189.666326097428</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E218" t="n">
-        <v>197.1631317138672</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F218" t="n">
-        <v>9706600</v>
+        <v>11171600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B219" t="n">
-        <v>196.5941314807131</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C219" t="n">
-        <v>199.0398256830038</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D219" t="n">
-        <v>195.1566580076304</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E219" t="n">
-        <v>197.1231994628906</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F219" t="n">
-        <v>11171600</v>
+        <v>12787900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B220" t="n">
-        <v>191.6628101365335</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C220" t="n">
-        <v>196.1549072491085</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D220" t="n">
-        <v>191.4431952813594</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E220" t="n">
-        <v>192.9804992675781</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F220" t="n">
-        <v>12787900</v>
+        <v>15058700</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="n">
-        <v>196.4943140399408</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C221" t="n">
-        <v>202.6335228023228</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D221" t="n">
-        <v>191.0538881519706</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E221" t="n">
-        <v>201.016357421875</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F221" t="n">
-        <v>15058700</v>
+        <v>8664800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B222" t="n">
-        <v>202.3939250564146</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C222" t="n">
-        <v>204.0410211897246</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D222" t="n">
-        <v>194.9769811314243</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E222" t="n">
-        <v>195.8654174804688</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F222" t="n">
-        <v>8664800</v>
+        <v>14378800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B223" t="n">
-        <v>193.4896063018435</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C223" t="n">
-        <v>194.5976575790598</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D223" t="n">
-        <v>189.57649225733</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E223" t="n">
-        <v>190.6346282958984</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F223" t="n">
-        <v>14378800</v>
+        <v>14152900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B224" t="n">
-        <v>193.7491445531879</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C224" t="n">
-        <v>199.0598091290667</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D224" t="n">
-        <v>192.8906542357335</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E224" t="n">
-        <v>195.7955474853516</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F224" t="n">
-        <v>14152900</v>
+        <v>17843600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B225" t="n">
-        <v>193.8689320609861</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C225" t="n">
-        <v>207.5847919095016</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D225" t="n">
-        <v>193.8689320609861</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E225" t="n">
-        <v>205.7280578613281</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F225" t="n">
-        <v>17843600</v>
+        <v>11482300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="n">
-        <v>204.8595912018172</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C226" t="n">
-        <v>207.5149233311111</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D226" t="n">
-        <v>202.6434887759544</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E226" t="n">
-        <v>205.0692138671875</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F226" t="n">
-        <v>11482300</v>
+        <v>9685400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B227" t="n">
-        <v>205.2189664215684</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C227" t="n">
-        <v>210.6993304789719</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D227" t="n">
-        <v>204.3704530814486</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E227" t="n">
-        <v>208.8026580810547</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F227" t="n">
-        <v>9685400</v>
+        <v>9580200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B228" t="n">
-        <v>208.0539803833292</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C228" t="n">
-        <v>212.7956386479058</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D228" t="n">
-        <v>207.0257904413594</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E228" t="n">
-        <v>208.6928558349609</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F228" t="n">
-        <v>9580200</v>
+        <v>10081800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B229" t="n">
-        <v>205.4884885298704</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C229" t="n">
-        <v>209.9406472657768</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D229" t="n">
-        <v>204.400391231641</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E229" t="n">
-        <v>205.3287658691406</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F229" t="n">
-        <v>10081800</v>
+        <v>14888900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B230" t="n">
-        <v>199.5888632714973</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C230" t="n">
-        <v>206.0774478239803</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D230" t="n">
-        <v>198.6005964484484</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E230" t="n">
-        <v>205.2588806152344</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F230" t="n">
-        <v>14888900</v>
+        <v>55517500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B231" t="n">
-        <v>229.6459965412689</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C231" t="n">
-        <v>254.0330860396483</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D231" t="n">
-        <v>229.6459965412689</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E231" t="n">
-        <v>251.6073608398438</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F231" t="n">
-        <v>55517500</v>
+        <v>34362700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B232" t="n">
-        <v>250.0301279952546</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C232" t="n">
-        <v>263.0671897003631</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D232" t="n">
-        <v>248.5627083778381</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E232" t="n">
-        <v>255.5504150390625</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F232" t="n">
-        <v>34362700</v>
+        <v>22471500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" t="n">
-        <v>253.9432305236259</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C233" t="n">
-        <v>261.8193732125837</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D233" t="n">
-        <v>253.9432305236259</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E233" t="n">
-        <v>257.0877075195312</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F233" t="n">
-        <v>22471500</v>
+        <v>15897500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B234" t="n">
-        <v>254.5621609406893</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C234" t="n">
-        <v>261.8593363431507</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D234" t="n">
-        <v>253.8035010915435</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E234" t="n">
-        <v>257.6567077636719</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F234" t="n">
-        <v>15897500</v>
+        <v>14393700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B235" t="n">
-        <v>258.9244691424316</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C235" t="n">
-        <v>264.0853722779391</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D235" t="n">
-        <v>253.154621477229</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E235" t="n">
-        <v>256.478759765625</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F235" t="n">
-        <v>14393700</v>
+        <v>16028300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B236" t="n">
-        <v>261.5199276025597</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C236" t="n">
-        <v>267.7988593124239</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D236" t="n">
-        <v>261.1405900757476</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E236" t="n">
-        <v>263.9656066894531</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F236" t="n">
-        <v>16028300</v>
+        <v>10490600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B237" t="n">
-        <v>262.8974710364521</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C237" t="n">
-        <v>263.1370702625856</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D237" t="n">
-        <v>257.3672223502596</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E237" t="n">
-        <v>258.7747497558594</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F237" t="n">
-        <v>10490600</v>
+        <v>17482700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B238" t="n">
-        <v>253.2744227737308</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C238" t="n">
-        <v>253.5539298242691</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D238" t="n">
-        <v>245.4581718493405</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E238" t="n">
-        <v>248.6824951171875</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F238" t="n">
-        <v>17482700</v>
+        <v>11853700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B239" t="n">
-        <v>249.3413418635835</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C239" t="n">
-        <v>254.3525301395604</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D239" t="n">
-        <v>243.0224566114913</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E239" t="n">
-        <v>243.7312164306641</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F239" t="n">
-        <v>11853700</v>
+        <v>10732600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B240" t="n">
-        <v>244.9191211985708</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C240" t="n">
-        <v>248.0635830600566</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D240" t="n">
-        <v>241.3254374437371</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E240" t="n">
-        <v>242.5732421875</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F240" t="n">
-        <v>10732600</v>
+        <v>9738300</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B241" t="n">
-        <v>241.5949712138984</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C241" t="n">
-        <v>250.1099896964979</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D241" t="n">
-        <v>241.5949712138984</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E241" t="n">
-        <v>247.2849578857422</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F241" t="n">
-        <v>9738300</v>
+        <v>12963700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B242" t="n">
-        <v>255.3008656803045</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C242" t="n">
-        <v>259.7230786425112</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D242" t="n">
-        <v>251.0583293004754</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E242" t="n">
-        <v>258.9743957519531</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F242" t="n">
-        <v>12963700</v>
+        <v>11502800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B243" t="n">
-        <v>256.43886230448</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C243" t="n">
-        <v>261.8792726915332</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D243" t="n">
-        <v>254.632028246405</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E243" t="n">
-        <v>255.2010192871094</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F243" t="n">
-        <v>11502800</v>
+        <v>9423800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,25 +6761,25 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" t="n">
-        <v>251.4077029961344</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C244" t="n">
-        <v>255.9497000259878</v>
+        <v>247</v>
       </c>
       <c r="D244" t="n">
-        <v>249.1616544830015</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E244" t="n">
-        <v>250.0999908447266</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F244" t="n">
-        <v>9423800</v>
+        <v>16611300</v>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -6787,25 +6787,25 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B245" t="n">
-        <v>244.1799926757812</v>
+        <v>244.25</v>
       </c>
       <c r="C245" t="n">
-        <v>247</v>
+        <v>244.25</v>
       </c>
       <c r="D245" t="n">
-        <v>241.5200042724609</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E245" t="n">
-        <v>242.8500061035156</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F245" t="n">
-        <v>16611300</v>
+        <v>21962400</v>
       </c>
       <c r="G245" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B246" t="n">
-        <v>244.25</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C246" t="n">
-        <v>244.25</v>
+        <v>241.3399963378906</v>
       </c>
       <c r="D246" t="n">
-        <v>236.5500030517578</v>
+        <v>236.25</v>
       </c>
       <c r="E246" t="n">
-        <v>237.9199981689453</v>
+        <v>236.4199981689453</v>
       </c>
       <c r="F246" t="n">
-        <v>21962400</v>
+        <v>10581900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B247" t="n">
-        <v>239.8000030517578</v>
+        <v>241.5</v>
       </c>
       <c r="C247" t="n">
-        <v>241.3399963378906</v>
+        <v>242.4400024414062</v>
       </c>
       <c r="D247" t="n">
-        <v>236.25</v>
+        <v>229.8099975585938</v>
       </c>
       <c r="E247" t="n">
-        <v>236.4199981689453</v>
+        <v>233.2799987792969</v>
       </c>
       <c r="F247" t="n">
-        <v>10581900</v>
+        <v>13635600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B248" t="n">
-        <v>241.5</v>
+        <v>234.4199981689453</v>
       </c>
       <c r="C248" t="n">
-        <v>242.4400024414062</v>
+        <v>241.1199951171875</v>
       </c>
       <c r="D248" t="n">
-        <v>229.8099975585938</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="E248" t="n">
-        <v>233.2799987792969</v>
+        <v>237.5800018310547</v>
       </c>
       <c r="F248" t="n">
-        <v>13635600</v>
+        <v>12353500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B249" t="n">
-        <v>234.4199981689453</v>
+        <v>240.6399993896484</v>
       </c>
       <c r="C249" t="n">
-        <v>241.1199951171875</v>
+        <v>242.0899963378906</v>
       </c>
       <c r="D249" t="n">
-        <v>234.2400054931641</v>
+        <v>237</v>
       </c>
       <c r="E249" t="n">
-        <v>237.5800018310547</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="F249" t="n">
-        <v>12353500</v>
+        <v>11074000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B250" t="n">
-        <v>240.6399993896484</v>
+        <v>237.0299987792969</v>
       </c>
       <c r="C250" t="n">
-        <v>242.0899963378906</v>
+        <v>239.3699951171875</v>
       </c>
       <c r="D250" t="n">
-        <v>237</v>
+        <v>233.3800048828125</v>
       </c>
       <c r="E250" t="n">
-        <v>238.2200012207031</v>
+        <v>234.0200042724609</v>
       </c>
       <c r="F250" t="n">
-        <v>11074000</v>
+        <v>8735500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B251" t="n">
-        <v>237.0299987792969</v>
+        <v>224.9700012207031</v>
       </c>
       <c r="C251" t="n">
-        <v>239.3699951171875</v>
+        <v>230.5700073242188</v>
       </c>
       <c r="D251" t="n">
-        <v>233.3800048828125</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="E251" t="n">
-        <v>234.0200042724609</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="F251" t="n">
-        <v>8735500</v>
+        <v>10327500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B252" t="n">
-        <v>224.9700012207031</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="C252" t="n">
-        <v>230.5700073242188</v>
+        <v>228.9799957275391</v>
       </c>
       <c r="D252" t="n">
-        <v>221.1799926757812</v>
+        <v>223.4299926757812</v>
       </c>
       <c r="E252" t="n">
-        <v>227.2700042724609</v>
+        <v>225.3099975585938</v>
       </c>
       <c r="F252" t="n">
-        <v>10263200</v>
+        <v>13506300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10654,37 +10654,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>225.31</v>
+      </c>
+      <c r="D2" t="n">
         <v>227.27</v>
       </c>
-      <c r="D2" t="n">
-        <v>234.02</v>
-      </c>
       <c r="E2" t="n">
-        <v>224.97</v>
+        <v>227.27</v>
       </c>
       <c r="F2" t="n">
-        <v>230.565</v>
+        <v>228.95</v>
       </c>
       <c r="G2" t="n">
-        <v>221.18</v>
+        <v>223.5</v>
       </c>
       <c r="H2" t="n">
-        <v>10252517</v>
+        <v>8572914</v>
       </c>
       <c r="I2" t="n">
-        <v>13774936</v>
+        <v>13773033</v>
       </c>
       <c r="J2" t="n">
-        <v>187043217408</v>
+        <v>185430130688</v>
       </c>
       <c r="K2" t="n">
-        <v>20.79323</v>
+        <v>20.842737</v>
       </c>
       <c r="L2" t="n">
-        <v>14.198394</v>
+        <v>14.075945</v>
       </c>
       <c r="M2" t="n">
-        <v>10.93</v>
+        <v>10.81</v>
       </c>
       <c r="N2" t="n">
         <v>269.11</v>
@@ -10696,7 +10696,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10720,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.873692</v>
+        <v>4.8316607</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10732,7 +10732,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>218016202752</v>
+        <v>216403132416</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:25:06</t>
+          <t>2026-09-30 16:07:35</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>242.989012448683</v>
+        <v>234.5010077854061</v>
       </c>
       <c r="C2" t="n">
-        <v>243.1476704015903</v>
+        <v>240.4307087963897</v>
       </c>
       <c r="D2" t="n">
-        <v>233.8267199294288</v>
+        <v>231.5460601627856</v>
       </c>
       <c r="E2" t="n">
-        <v>235.0067138671875</v>
+        <v>233.7077331542969</v>
       </c>
       <c r="F2" t="n">
-        <v>10801100</v>
+        <v>10016600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="n">
-        <v>234.5010077854061</v>
+        <v>233.4498996394798</v>
       </c>
       <c r="C3" t="n">
-        <v>240.4307087963897</v>
+        <v>237.3865110117534</v>
       </c>
       <c r="D3" t="n">
-        <v>231.5460601627856</v>
+        <v>231.6353042398812</v>
       </c>
       <c r="E3" t="n">
-        <v>233.7077331542969</v>
+        <v>236.8708953857422</v>
       </c>
       <c r="F3" t="n">
-        <v>10016600</v>
+        <v>7679200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B4" t="n">
-        <v>233.4498996394798</v>
+        <v>236.7419954840688</v>
       </c>
       <c r="C4" t="n">
-        <v>237.3865110117534</v>
+        <v>240.7678464733125</v>
       </c>
       <c r="D4" t="n">
-        <v>231.6353042398812</v>
+        <v>236.4940981065986</v>
       </c>
       <c r="E4" t="n">
-        <v>236.8708953857422</v>
+        <v>238.3384552001953</v>
       </c>
       <c r="F4" t="n">
-        <v>7679200</v>
+        <v>8849800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="n">
-        <v>236.7419954840688</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="C5" t="n">
-        <v>240.7678464733125</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D5" t="n">
-        <v>236.4940981065986</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E5" t="n">
-        <v>238.3384552001953</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="F5" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B6" t="n">
-        <v>237.3171110157645</v>
+        <v>244.4069666278678</v>
       </c>
       <c r="C6" t="n">
-        <v>248.3634171689519</v>
+        <v>245.2795701971395</v>
       </c>
       <c r="D6" t="n">
-        <v>233.430082086989</v>
+        <v>235.5520799850208</v>
       </c>
       <c r="E6" t="n">
-        <v>243.7128601074219</v>
+        <v>237.7236633300781</v>
       </c>
       <c r="F6" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B7" t="n">
-        <v>244.4069823156386</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C7" t="n">
-        <v>245.2795859409202</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D7" t="n">
-        <v>235.5520951044222</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E7" t="n">
-        <v>237.7236785888672</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F7" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B8" t="n">
-        <v>237.7236681390551</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C8" t="n">
-        <v>239.290381338098</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D8" t="n">
-        <v>233.6680556537968</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E8" t="n">
-        <v>238.4078521728516</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F8" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B9" t="n">
-        <v>237.2576175505903</v>
+        <v>244.4466434616172</v>
       </c>
       <c r="C9" t="n">
-        <v>243.8913535488906</v>
+        <v>246.9553636418975</v>
       </c>
       <c r="D9" t="n">
-        <v>235.1554375781523</v>
+        <v>238.6954214370453</v>
       </c>
       <c r="E9" t="n">
-        <v>243.2666473388672</v>
+        <v>239.6473388671875</v>
       </c>
       <c r="F9" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B10" t="n">
-        <v>244.4466434616172</v>
+        <v>240.8471826425636</v>
       </c>
       <c r="C10" t="n">
-        <v>246.9553636418975</v>
+        <v>247.2528577250976</v>
       </c>
       <c r="D10" t="n">
-        <v>238.6954214370453</v>
+        <v>240.331551845499</v>
       </c>
       <c r="E10" t="n">
-        <v>239.6473388671875</v>
+        <v>246.6578979492188</v>
       </c>
       <c r="F10" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B11" t="n">
-        <v>240.8471826425636</v>
+        <v>246.0232549541512</v>
       </c>
       <c r="C11" t="n">
-        <v>247.2528577250976</v>
+        <v>246.1918233421939</v>
       </c>
       <c r="D11" t="n">
-        <v>240.331551845499</v>
+        <v>237.5352518241517</v>
       </c>
       <c r="E11" t="n">
-        <v>246.6578979492188</v>
+        <v>237.7534027099609</v>
       </c>
       <c r="F11" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B12" t="n">
-        <v>246.0232707436915</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C12" t="n">
-        <v>246.1918391425529</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D12" t="n">
-        <v>237.5352670689401</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E12" t="n">
-        <v>237.75341796875</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F12" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B13" t="n">
-        <v>238.8441526809671</v>
+        <v>251.0605301777264</v>
       </c>
       <c r="C13" t="n">
-        <v>239.2903800503502</v>
+        <v>254.5806605495149</v>
       </c>
       <c r="D13" t="n">
-        <v>233.915951765761</v>
+        <v>240.6290051386317</v>
       </c>
       <c r="E13" t="n">
-        <v>234.5902404785156</v>
+        <v>243.9309997558594</v>
       </c>
       <c r="F13" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B14" t="n">
-        <v>251.0605458824941</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="C14" t="n">
-        <v>254.5806764744798</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D14" t="n">
-        <v>240.6290201908687</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E14" t="n">
-        <v>243.9310150146484</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="F14" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="n">
-        <v>244.4962363844956</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C15" t="n">
-        <v>248.670819810711</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D15" t="n">
-        <v>240.1233229489625</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E15" t="n">
-        <v>241.0355834960938</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F15" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B16" t="n">
-        <v>242.9394234832453</v>
+        <v>252.3595144668565</v>
       </c>
       <c r="C16" t="n">
-        <v>253.2519480605562</v>
+        <v>264.883294034403</v>
       </c>
       <c r="D16" t="n">
-        <v>242.2453138708127</v>
+        <v>251.863719742953</v>
       </c>
       <c r="E16" t="n">
-        <v>252.1413726806641</v>
+        <v>261.194580078125</v>
       </c>
       <c r="F16" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B17" t="n">
-        <v>252.3595144668565</v>
+        <v>259.9947875033736</v>
       </c>
       <c r="C17" t="n">
-        <v>264.883294034403</v>
+        <v>260.1930872533099</v>
       </c>
       <c r="D17" t="n">
-        <v>251.863719742953</v>
+        <v>254.3526406430638</v>
       </c>
       <c r="E17" t="n">
-        <v>261.194580078125</v>
+        <v>254.4815521240234</v>
       </c>
       <c r="F17" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B18" t="n">
-        <v>259.9947875033736</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C18" t="n">
-        <v>260.1930872533099</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D18" t="n">
-        <v>254.3526406430638</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E18" t="n">
-        <v>254.4815521240234</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F18" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B19" t="n">
-        <v>255.4334634999039</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C19" t="n">
-        <v>256.3853809552256</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D19" t="n">
-        <v>251.982721115611</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E19" t="n">
-        <v>252.9049072265625</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F19" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B20" t="n">
-        <v>255.254980605377</v>
+        <v>254.9178098920577</v>
       </c>
       <c r="C20" t="n">
-        <v>256.3258839430272</v>
+        <v>255.9292505274036</v>
       </c>
       <c r="D20" t="n">
-        <v>251.8637312244832</v>
+        <v>252.7759881170209</v>
       </c>
       <c r="E20" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213653564453</v>
       </c>
       <c r="F20" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B21" t="n">
-        <v>254.9178252470085</v>
+        <v>253.3213815169481</v>
       </c>
       <c r="C21" t="n">
-        <v>255.9292659432784</v>
+        <v>256.6630334318976</v>
       </c>
       <c r="D21" t="n">
-        <v>252.7760033429592</v>
+        <v>252.0025656103722</v>
       </c>
       <c r="E21" t="n">
-        <v>253.3213806152344</v>
+        <v>252.1215515136719</v>
       </c>
       <c r="F21" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>253.3213661855435</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C22" t="n">
-        <v>256.663017898251</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D22" t="n">
-        <v>252.0025503587843</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E22" t="n">
-        <v>252.1215362548828</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F22" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B23" t="n">
-        <v>249.8805444255208</v>
+        <v>248.3931704298276</v>
       </c>
       <c r="C23" t="n">
-        <v>251.4373471434884</v>
+        <v>257.099325053219</v>
       </c>
       <c r="D23" t="n">
-        <v>246.945432960583</v>
+        <v>247.8973756784706</v>
       </c>
       <c r="E23" t="n">
-        <v>249.3450927734375</v>
+        <v>254.4914398193359</v>
       </c>
       <c r="F23" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B24" t="n">
-        <v>248.3931555366784</v>
+        <v>252.657000570364</v>
       </c>
       <c r="C24" t="n">
-        <v>257.0993096380665</v>
+        <v>259.6179629024988</v>
       </c>
       <c r="D24" t="n">
-        <v>247.8973608150483</v>
+        <v>250.5052532311086</v>
       </c>
       <c r="E24" t="n">
-        <v>254.4914245605469</v>
+        <v>258.2198181152344</v>
       </c>
       <c r="F24" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B25" t="n">
-        <v>252.6570304305034</v>
+        <v>257.8133023432115</v>
       </c>
       <c r="C25" t="n">
-        <v>259.617993585316</v>
+        <v>259.3601797363976</v>
       </c>
       <c r="D25" t="n">
-        <v>250.5052828369448</v>
+        <v>252.9545192358491</v>
       </c>
       <c r="E25" t="n">
-        <v>258.2198486328125</v>
+        <v>259.1420288085938</v>
       </c>
       <c r="F25" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B26" t="n">
-        <v>257.8132719821094</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C26" t="n">
-        <v>259.3601491931292</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D26" t="n">
-        <v>252.9544894469363</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E26" t="n">
-        <v>259.1419982910156</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F26" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>255.9788221233241</v>
+        <v>252.5578552142711</v>
       </c>
       <c r="C27" t="n">
-        <v>257.0795021986246</v>
+        <v>254.6699306658516</v>
       </c>
       <c r="D27" t="n">
-        <v>251.3282801006067</v>
+        <v>249.8904769054258</v>
       </c>
       <c r="E27" t="n">
-        <v>252.3000335693359</v>
+        <v>250.5548400878906</v>
       </c>
       <c r="F27" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="n">
-        <v>252.5578398334985</v>
+        <v>248.4328324243326</v>
       </c>
       <c r="C28" t="n">
-        <v>254.6699151564536</v>
+        <v>248.4328324243326</v>
       </c>
       <c r="D28" t="n">
-        <v>249.8904616870965</v>
+        <v>232.5079071065105</v>
       </c>
       <c r="E28" t="n">
-        <v>250.5548248291016</v>
+        <v>237.2576293945312</v>
       </c>
       <c r="F28" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B29" t="n">
-        <v>248.4328164468309</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="C29" t="n">
-        <v>248.4328164468309</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D29" t="n">
-        <v>232.5078921531912</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E29" t="n">
-        <v>237.2576141357422</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="F29" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B30" t="n">
-        <v>234.1638481621394</v>
+        <v>237.9814840335094</v>
       </c>
       <c r="C30" t="n">
-        <v>238.943316687993</v>
+        <v>239.8754236419186</v>
       </c>
       <c r="D30" t="n">
-        <v>233.8068753463891</v>
+        <v>233.1028654264771</v>
       </c>
       <c r="E30" t="n">
-        <v>237.8624877929688</v>
+        <v>239.6771087646484</v>
       </c>
       <c r="F30" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="n">
-        <v>237.9814688826704</v>
+        <v>239.8654952673756</v>
       </c>
       <c r="C31" t="n">
-        <v>239.8754083705041</v>
+        <v>243.63353841341</v>
       </c>
       <c r="D31" t="n">
-        <v>233.1028505862302</v>
+        <v>239.1317287169831</v>
       </c>
       <c r="E31" t="n">
-        <v>239.6770935058594</v>
+        <v>242.4436340332031</v>
       </c>
       <c r="F31" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B32" t="n">
-        <v>239.8655103639031</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="C32" t="n">
-        <v>243.6335537470887</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D32" t="n">
-        <v>239.1317437673292</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E32" t="n">
-        <v>242.4436492919922</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="F32" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B33" t="n">
-        <v>243.6732228340941</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C33" t="n">
-        <v>246.3405860290093</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D33" t="n">
-        <v>241.6305356400256</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E33" t="n">
-        <v>243.9508666992188</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F33" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="n">
-        <v>243.1873207442872</v>
+        <v>236.3056926086296</v>
       </c>
       <c r="C34" t="n">
-        <v>243.8318478561575</v>
+        <v>243.1179076689137</v>
       </c>
       <c r="D34" t="n">
-        <v>237.8922365355373</v>
+        <v>235.4231785540507</v>
       </c>
       <c r="E34" t="n">
-        <v>238.4078521728516</v>
+        <v>241.6107025146484</v>
       </c>
       <c r="F34" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B35" t="n">
-        <v>236.3056776848755</v>
+        <v>240.0340571163644</v>
       </c>
       <c r="C35" t="n">
-        <v>243.1178923149379</v>
+        <v>240.7876596253181</v>
       </c>
       <c r="D35" t="n">
-        <v>235.4231636860313</v>
+        <v>233.6085468088289</v>
       </c>
       <c r="E35" t="n">
-        <v>241.6106872558594</v>
+        <v>235.0364379882812</v>
       </c>
       <c r="F35" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B36" t="n">
-        <v>240.0340571163644</v>
+        <v>234.2530933083125</v>
       </c>
       <c r="C36" t="n">
-        <v>240.7876596253181</v>
+        <v>235.7900448264734</v>
       </c>
       <c r="D36" t="n">
-        <v>233.6085468088289</v>
+        <v>228.3333031775737</v>
       </c>
       <c r="E36" t="n">
-        <v>235.0364379882812</v>
+        <v>231.5361328125</v>
       </c>
       <c r="F36" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B37" t="n">
-        <v>234.2531087461558</v>
+        <v>230.0487531290293</v>
       </c>
       <c r="C37" t="n">
-        <v>235.7900603656055</v>
+        <v>230.3263969654728</v>
       </c>
       <c r="D37" t="n">
-        <v>228.3333182252886</v>
+        <v>223.1671199033486</v>
       </c>
       <c r="E37" t="n">
-        <v>231.5361480712891</v>
+        <v>225.9634094238281</v>
       </c>
       <c r="F37" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B38" t="n">
-        <v>230.0487686636922</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C38" t="n">
-        <v>230.3264125188844</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D38" t="n">
-        <v>223.1671349733107</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E38" t="n">
-        <v>225.9634246826172</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F38" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B39" t="n">
-        <v>227.3218898732066</v>
+        <v>222.9688137796853</v>
       </c>
       <c r="C39" t="n">
-        <v>229.1265900019938</v>
+        <v>226.7566777713456</v>
       </c>
       <c r="D39" t="n">
-        <v>221.4219354522067</v>
+        <v>220.0932103050241</v>
       </c>
       <c r="E39" t="n">
-        <v>223.4745178222656</v>
+        <v>225.1998901367188</v>
       </c>
       <c r="F39" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B40" t="n">
-        <v>222.9687986720664</v>
+        <v>225.4279691980636</v>
       </c>
       <c r="C40" t="n">
-        <v>226.7566624070738</v>
+        <v>226.9153535529684</v>
       </c>
       <c r="D40" t="n">
-        <v>220.0931953922465</v>
+        <v>223.1473101611184</v>
       </c>
       <c r="E40" t="n">
-        <v>225.1998748779297</v>
+        <v>224.912353515625</v>
       </c>
       <c r="F40" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B41" t="n">
-        <v>225.4279691980636</v>
+        <v>224.8924975422598</v>
       </c>
       <c r="C41" t="n">
-        <v>226.9153535529684</v>
+        <v>232.656645001925</v>
       </c>
       <c r="D41" t="n">
-        <v>223.1473101611184</v>
+        <v>224.614853697738</v>
       </c>
       <c r="E41" t="n">
-        <v>224.912353515625</v>
+        <v>232.1509246826172</v>
       </c>
       <c r="F41" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="n">
-        <v>224.8925123239678</v>
+        <v>228.5712919801828</v>
       </c>
       <c r="C42" t="n">
-        <v>232.656660293954</v>
+        <v>230.8618764526245</v>
       </c>
       <c r="D42" t="n">
-        <v>224.6148684611971</v>
+        <v>224.0992287472785</v>
       </c>
       <c r="E42" t="n">
-        <v>232.1509399414062</v>
+        <v>226.2311401367188</v>
       </c>
       <c r="F42" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B43" t="n">
-        <v>228.5712765635558</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C43" t="n">
-        <v>230.8618608815026</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D43" t="n">
-        <v>224.0992136322821</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E43" t="n">
-        <v>226.2311248779297</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F43" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B44" t="n">
-        <v>227.0739873247604</v>
+        <v>226.7467645282661</v>
       </c>
       <c r="C44" t="n">
-        <v>230.6040433967966</v>
+        <v>232.2798356411572</v>
       </c>
       <c r="D44" t="n">
-        <v>226.7071040647147</v>
+        <v>226.6773611325171</v>
       </c>
       <c r="E44" t="n">
-        <v>228.6010284423828</v>
+        <v>230.8717803955078</v>
       </c>
       <c r="F44" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B45" t="n">
-        <v>226.7467795144244</v>
+        <v>231.0601885043919</v>
       </c>
       <c r="C45" t="n">
-        <v>232.2798509930075</v>
+        <v>234.6596480847597</v>
       </c>
       <c r="D45" t="n">
-        <v>226.6773761140884</v>
+        <v>229.67195413226</v>
       </c>
       <c r="E45" t="n">
-        <v>230.8717956542969</v>
+        <v>232.7359771728516</v>
       </c>
       <c r="F45" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B46" t="n">
-        <v>231.0602036533118</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="C46" t="n">
-        <v>234.6596634696697</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D46" t="n">
-        <v>229.6719691901636</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E46" t="n">
-        <v>232.7359924316406</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="F46" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B47" t="n">
-        <v>233.3805083869321</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C47" t="n">
-        <v>237.2477014354837</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D47" t="n">
-        <v>231.1990144844042</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E47" t="n">
-        <v>236.7122497558594</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F47" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B48" t="n">
-        <v>241.6404418420451</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C48" t="n">
-        <v>246.8760330652079</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D48" t="n">
-        <v>235.6016655641461</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E48" t="n">
-        <v>245.3787384033203</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F48" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B49" t="n">
-        <v>248.7203919866921</v>
+        <v>259.6774704470017</v>
       </c>
       <c r="C49" t="n">
-        <v>259.6774588065476</v>
+        <v>262.0572792621351</v>
       </c>
       <c r="D49" t="n">
-        <v>247.4015761578514</v>
+        <v>254.1840559885597</v>
       </c>
       <c r="E49" t="n">
-        <v>258.3784790039062</v>
+        <v>257.3472290039062</v>
       </c>
       <c r="F49" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B50" t="n">
-        <v>259.6774396530913</v>
+        <v>257.8132661327708</v>
       </c>
       <c r="C50" t="n">
-        <v>262.0572481860146</v>
+        <v>260.0443424743044</v>
       </c>
       <c r="D50" t="n">
-        <v>254.1840258460871</v>
+        <v>256.8216766476447</v>
       </c>
       <c r="E50" t="n">
-        <v>257.3471984863281</v>
+        <v>258.8246765136719</v>
       </c>
       <c r="F50" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B51" t="n">
-        <v>257.8132661327708</v>
+        <v>258.556940201721</v>
       </c>
       <c r="C51" t="n">
-        <v>260.0443424743044</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D51" t="n">
-        <v>256.8216766476447</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E51" t="n">
-        <v>258.8246765136719</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="F51" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B52" t="n">
-        <v>258.556940201721</v>
+        <v>261.283846098816</v>
       </c>
       <c r="C52" t="n">
-        <v>263.6933661135803</v>
+        <v>265.646834061187</v>
       </c>
       <c r="D52" t="n">
-        <v>256.9703910840639</v>
+        <v>258.5767957367673</v>
       </c>
       <c r="E52" t="n">
-        <v>261.9779357910156</v>
+        <v>260.1435241699219</v>
       </c>
       <c r="F52" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B53" t="n">
-        <v>261.283846098816</v>
+        <v>261.3036648523665</v>
       </c>
       <c r="C53" t="n">
-        <v>265.646834061187</v>
+        <v>262.2655079172122</v>
       </c>
       <c r="D53" t="n">
-        <v>258.5767957367673</v>
+        <v>258.7156306765648</v>
       </c>
       <c r="E53" t="n">
-        <v>260.1435241699219</v>
+        <v>260.0245361328125</v>
       </c>
       <c r="F53" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B54" t="n">
-        <v>261.3036648523665</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C54" t="n">
-        <v>262.2655079172122</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D54" t="n">
-        <v>258.7156306765648</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E54" t="n">
-        <v>260.0245361328125</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F54" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B55" t="n">
-        <v>259.013086162544</v>
+        <v>251.8637174841621</v>
       </c>
       <c r="C55" t="n">
-        <v>260.074094195654</v>
+        <v>253.7080744457603</v>
       </c>
       <c r="D55" t="n">
-        <v>250.9613842226157</v>
+        <v>249.9896140498327</v>
       </c>
       <c r="E55" t="n">
-        <v>252.4388580322266</v>
+        <v>252.7660675048828</v>
       </c>
       <c r="F55" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B56" t="n">
-        <v>251.8637326884788</v>
+        <v>254.1741130832229</v>
       </c>
       <c r="C56" t="n">
-        <v>253.7080897614157</v>
+        <v>259.7666921654164</v>
       </c>
       <c r="D56" t="n">
-        <v>249.989629141015</v>
+        <v>254.0947992411865</v>
       </c>
       <c r="E56" t="n">
-        <v>252.7660827636719</v>
+        <v>255.9689178466797</v>
       </c>
       <c r="F56" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B57" t="n">
-        <v>254.1741282350202</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C57" t="n">
-        <v>259.7667076505979</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D57" t="n">
-        <v>254.0948143882558</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E57" t="n">
-        <v>255.9689331054688</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F57" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,25 +1925,25 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B58" t="n">
-        <v>256.6601807669533</v>
+        <v>258.9047600313309</v>
       </c>
       <c r="C58" t="n">
-        <v>258.2989382537239</v>
+        <v>260.2555141825196</v>
       </c>
       <c r="D58" t="n">
-        <v>254.4155616010984</v>
+        <v>253.760043143314</v>
       </c>
       <c r="E58" t="n">
-        <v>256.0940551757812</v>
+        <v>258.1400146484375</v>
       </c>
       <c r="F58" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G58" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B59" t="n">
-        <v>258.9047600313309</v>
+        <v>258.8452092197766</v>
       </c>
       <c r="C59" t="n">
-        <v>260.2555141825196</v>
+        <v>262.8279113769531</v>
       </c>
       <c r="D59" t="n">
-        <v>253.760043143314</v>
+        <v>256.6502674989528</v>
       </c>
       <c r="E59" t="n">
-        <v>258.1400146484375</v>
+        <v>262.8279113769531</v>
       </c>
       <c r="F59" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B60" t="n">
-        <v>258.8451791646396</v>
+        <v>260.9308604798152</v>
       </c>
       <c r="C60" t="n">
-        <v>262.827880859375</v>
+        <v>262.4404982668678</v>
       </c>
       <c r="D60" t="n">
-        <v>256.6502376986757</v>
+        <v>258.7458305027313</v>
       </c>
       <c r="E60" t="n">
-        <v>262.827880859375</v>
+        <v>261.6360168457031</v>
       </c>
       <c r="F60" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B61" t="n">
-        <v>260.930890915143</v>
+        <v>261.4374083245464</v>
       </c>
       <c r="C61" t="n">
-        <v>262.4405288782817</v>
+        <v>264.4864785158107</v>
       </c>
       <c r="D61" t="n">
-        <v>258.7458606831942</v>
+        <v>260.7620161053754</v>
       </c>
       <c r="E61" t="n">
-        <v>261.6360473632812</v>
+        <v>263.4535827636719</v>
       </c>
       <c r="F61" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B62" t="n">
-        <v>261.4374386085776</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="C62" t="n">
-        <v>264.486509153036</v>
+        <v>266.0855602062323</v>
       </c>
       <c r="D62" t="n">
-        <v>260.7620463111714</v>
+        <v>262.9967232703997</v>
       </c>
       <c r="E62" t="n">
-        <v>263.45361328125</v>
+        <v>264.2680053710938</v>
       </c>
       <c r="F62" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B63" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C63" t="n">
-        <v>266.0855294787636</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D63" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E63" t="n">
-        <v>264.2679748535156</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F63" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B64" t="n">
-        <v>262.9073239460033</v>
+        <v>264.8440818513142</v>
       </c>
       <c r="C64" t="n">
-        <v>267.2773540092613</v>
+        <v>266.453045001104</v>
       </c>
       <c r="D64" t="n">
-        <v>262.9073239460033</v>
+        <v>263.5231220141856</v>
       </c>
       <c r="E64" t="n">
-        <v>264.4169921875</v>
+        <v>264.109130859375</v>
       </c>
       <c r="F64" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B65" t="n">
-        <v>264.8440512488132</v>
+        <v>263.4834046285292</v>
       </c>
       <c r="C65" t="n">
-        <v>266.4530142126886</v>
+        <v>264.2878861679949</v>
       </c>
       <c r="D65" t="n">
-        <v>263.5230915643202</v>
+        <v>262.5895396190958</v>
       </c>
       <c r="E65" t="n">
-        <v>264.1091003417969</v>
+        <v>263.1059875488281</v>
       </c>
       <c r="F65" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B66" t="n">
-        <v>263.4833740671746</v>
+        <v>263.1953762174182</v>
       </c>
       <c r="C66" t="n">
-        <v>264.2878555133287</v>
+        <v>263.572793304574</v>
       </c>
       <c r="D66" t="n">
-        <v>262.5895091614203</v>
+        <v>250.760631935403</v>
       </c>
       <c r="E66" t="n">
-        <v>263.10595703125</v>
+        <v>251.8928680419922</v>
       </c>
       <c r="F66" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>263.1953602739627</v>
+        <v>251.8928562905814</v>
       </c>
       <c r="C67" t="n">
-        <v>263.5727773382559</v>
+        <v>257.8222021169872</v>
       </c>
       <c r="D67" t="n">
-        <v>250.7606167452008</v>
+        <v>250.5917797464572</v>
       </c>
       <c r="E67" t="n">
-        <v>251.8928527832031</v>
+        <v>254.514892578125</v>
       </c>
       <c r="F67" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>251.8928562905814</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C68" t="n">
-        <v>257.8222021169872</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D68" t="n">
-        <v>250.5917797464572</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E68" t="n">
-        <v>254.514892578125</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F68" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>253.4620895509313</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="C69" t="n">
-        <v>261.7552171079225</v>
+        <v>266.0060550943219</v>
       </c>
       <c r="D69" t="n">
-        <v>253.2634545783159</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="E69" t="n">
-        <v>261.1096496582031</v>
+        <v>264.3077087402344</v>
       </c>
       <c r="F69" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>261.7055860975985</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C70" t="n">
-        <v>266.0060858079951</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D70" t="n">
-        <v>261.7055860975985</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E70" t="n">
-        <v>264.3077392578125</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F70" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>262.5994389217771</v>
+        <v>258.2294193019395</v>
       </c>
       <c r="C71" t="n">
-        <v>263.394009134812</v>
+        <v>259.2524038660146</v>
       </c>
       <c r="D71" t="n">
-        <v>258.6366203853271</v>
+        <v>254.7631956419699</v>
       </c>
       <c r="E71" t="n">
-        <v>258.7557983398438</v>
+        <v>258.1698303222656</v>
       </c>
       <c r="F71" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B72" t="n">
-        <v>258.2294193019395</v>
+        <v>257.2362139425806</v>
       </c>
       <c r="C72" t="n">
-        <v>259.2524038660146</v>
+        <v>259.7787779567694</v>
       </c>
       <c r="D72" t="n">
-        <v>254.7631956419699</v>
+        <v>254.028214436778</v>
       </c>
       <c r="E72" t="n">
-        <v>258.1698303222656</v>
+        <v>257.6334838867188</v>
       </c>
       <c r="F72" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B73" t="n">
-        <v>257.2362444131007</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C73" t="n">
-        <v>259.778808728465</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D73" t="n">
-        <v>254.0282445272995</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E73" t="n">
-        <v>257.6335144042969</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F73" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B74" t="n">
-        <v>255.9053572301452</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C74" t="n">
-        <v>259.1332249596227</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D74" t="n">
-        <v>238.7231659776434</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E74" t="n">
-        <v>239.4183959960938</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F74" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B75" t="n">
-        <v>237.5511941796288</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C75" t="n">
-        <v>240.5903685304685</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D75" t="n">
-        <v>234.849731125901</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E75" t="n">
-        <v>237.9385528564453</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F75" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B76" t="n">
-        <v>235.4059054123066</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C76" t="n">
-        <v>237.2135033883542</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D76" t="n">
-        <v>230.0923326840245</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E76" t="n">
-        <v>231.9396667480469</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F76" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B77" t="n">
-        <v>231.3636110626874</v>
+        <v>222.0177057630064</v>
       </c>
       <c r="C77" t="n">
-        <v>231.3636110626874</v>
+        <v>226.3877512462753</v>
       </c>
       <c r="D77" t="n">
-        <v>224.8979495180149</v>
+        <v>217.8661784665229</v>
       </c>
       <c r="E77" t="n">
-        <v>225.5633850097656</v>
+        <v>218.5713500976562</v>
       </c>
       <c r="F77" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B78" t="n">
-        <v>222.0176902636222</v>
+        <v>218.6507753226022</v>
       </c>
       <c r="C78" t="n">
-        <v>226.3877354418118</v>
+        <v>221.8687164208105</v>
       </c>
       <c r="D78" t="n">
-        <v>217.8661632569629</v>
+        <v>217.4688919371066</v>
       </c>
       <c r="E78" t="n">
-        <v>218.5713348388672</v>
+        <v>220.071044921875</v>
       </c>
       <c r="F78" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="n">
-        <v>218.6507904829158</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C79" t="n">
-        <v>221.8687318042425</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D79" t="n">
-        <v>217.4689070154735</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E79" t="n">
-        <v>220.0710601806641</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F79" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B80" t="n">
-        <v>220.7265600038705</v>
+        <v>225.2356232374019</v>
       </c>
       <c r="C80" t="n">
-        <v>227.162427221411</v>
+        <v>229.277913744438</v>
       </c>
       <c r="D80" t="n">
-        <v>219.6042504088122</v>
+        <v>225.1065036899912</v>
       </c>
       <c r="E80" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4969787597656</v>
       </c>
       <c r="F80" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B81" t="n">
-        <v>225.2356384112152</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C81" t="n">
-        <v>229.2779291905748</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D81" t="n">
-        <v>225.1065188551059</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E81" t="n">
-        <v>226.4969940185547</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F81" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B82" t="n">
-        <v>227.8675783015932</v>
+        <v>230.3604906379282</v>
       </c>
       <c r="C82" t="n">
-        <v>229.3772313706373</v>
+        <v>234.1346156625655</v>
       </c>
       <c r="D82" t="n">
-        <v>226.0401123076792</v>
+        <v>224.7291051659704</v>
       </c>
       <c r="E82" t="n">
-        <v>227.8377838134766</v>
+        <v>226.9737091064453</v>
       </c>
       <c r="F82" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B83" t="n">
-        <v>230.3604906379282</v>
+        <v>227.8278778686248</v>
       </c>
       <c r="C83" t="n">
-        <v>234.1346156625655</v>
+        <v>230.2810586434755</v>
       </c>
       <c r="D83" t="n">
-        <v>224.7291051659704</v>
+        <v>226.1195896734686</v>
       </c>
       <c r="E83" t="n">
-        <v>226.9737091064453</v>
+        <v>226.4076232910156</v>
       </c>
       <c r="F83" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B84" t="n">
-        <v>227.8278625141174</v>
+        <v>215.1944745404488</v>
       </c>
       <c r="C84" t="n">
-        <v>230.2810431236355</v>
+        <v>215.8003210439947</v>
       </c>
       <c r="D84" t="n">
-        <v>226.1195744340916</v>
+        <v>207.358206080909</v>
       </c>
       <c r="E84" t="n">
-        <v>226.4076080322266</v>
+        <v>212.6221160888672</v>
       </c>
       <c r="F84" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B85" t="n">
-        <v>215.1944899838427</v>
+        <v>212.7015903227142</v>
       </c>
       <c r="C85" t="n">
-        <v>215.8003365308671</v>
+        <v>214.08212392222</v>
       </c>
       <c r="D85" t="n">
-        <v>207.3582209619344</v>
+        <v>209.5929005351361</v>
       </c>
       <c r="E85" t="n">
-        <v>212.6221313476562</v>
+        <v>210.8443145751953</v>
       </c>
       <c r="F85" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B86" t="n">
-        <v>212.7015749295142</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C86" t="n">
-        <v>214.0821084291109</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D86" t="n">
-        <v>209.5928853669118</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E86" t="n">
-        <v>210.8442993164062</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F86" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B87" t="n">
-        <v>212.8902908724165</v>
+        <v>203.60397273962</v>
       </c>
       <c r="C87" t="n">
-        <v>215.4129869027477</v>
+        <v>204.1601567769575</v>
       </c>
       <c r="D87" t="n">
-        <v>208.3712731650351</v>
+        <v>191.7949429269172</v>
       </c>
       <c r="E87" t="n">
-        <v>209.3743896484375</v>
+        <v>195.0426788330078</v>
       </c>
       <c r="F87" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B88" t="n">
-        <v>203.6039568110546</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C88" t="n">
-        <v>204.16014080488</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D88" t="n">
-        <v>191.7949279222085</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E88" t="n">
-        <v>195.0426635742188</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F88" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B89" t="n">
-        <v>191.993558028148</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C89" t="n">
-        <v>199.3034370934686</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D89" t="n">
-        <v>186.0046234920971</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E89" t="n">
-        <v>198.0818176269531</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F89" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B90" t="n">
-        <v>192.668943558262</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C90" t="n">
-        <v>198.2010042649258</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D90" t="n">
-        <v>187.5043431662378</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E90" t="n">
-        <v>188.6763153076172</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F90" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="n">
-        <v>190.3250127759971</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C91" t="n">
-        <v>193.2747884158856</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D91" t="n">
-        <v>185.8457159832669</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E91" t="n">
-        <v>190.0469207763672</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F91" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B92" t="n">
-        <v>188.0108792533576</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C92" t="n">
-        <v>193.8706944788449</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D92" t="n">
-        <v>184.465183505092</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E92" t="n">
-        <v>192.7086639404297</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F92" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B93" t="n">
-        <v>190.5931665112882</v>
+        <v>191.8346349441069</v>
       </c>
       <c r="C93" t="n">
-        <v>197.7441470694129</v>
+        <v>192.3510979672969</v>
       </c>
       <c r="D93" t="n">
-        <v>189.4510040038842</v>
+        <v>180.5718644212529</v>
       </c>
       <c r="E93" t="n">
-        <v>192.1326141357422</v>
+        <v>183.7401428222656</v>
       </c>
       <c r="F93" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B94" t="n">
-        <v>191.8346508751069</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C94" t="n">
-        <v>192.3511139411869</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D94" t="n">
-        <v>180.5718794169307</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E94" t="n">
-        <v>183.7401580810547</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F94" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B95" t="n">
-        <v>184.6936257308121</v>
+        <v>185.1703620229303</v>
       </c>
       <c r="C95" t="n">
-        <v>187.0375548215625</v>
+        <v>192.1326190686923</v>
       </c>
       <c r="D95" t="n">
-        <v>179.012577513483</v>
+        <v>183.0449358454951</v>
       </c>
       <c r="E95" t="n">
-        <v>184.1672210693359</v>
+        <v>188.4280242919922</v>
       </c>
       <c r="F95" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B96" t="n">
-        <v>185.1703620229303</v>
+        <v>189.6695058452945</v>
       </c>
       <c r="C96" t="n">
-        <v>192.1326190686923</v>
+        <v>191.6856804427425</v>
       </c>
       <c r="D96" t="n">
-        <v>183.0449358454951</v>
+        <v>181.9226203922807</v>
       </c>
       <c r="E96" t="n">
-        <v>188.4280242919922</v>
+        <v>183.0349884033203</v>
       </c>
       <c r="F96" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="n">
-        <v>189.6694900334161</v>
+        <v>182.6277925688313</v>
       </c>
       <c r="C97" t="n">
-        <v>191.6856644627849</v>
+        <v>186.8587767567783</v>
       </c>
       <c r="D97" t="n">
-        <v>181.9226052262247</v>
+        <v>180.6215444099069</v>
       </c>
       <c r="E97" t="n">
-        <v>183.0349731445312</v>
+        <v>186.5111541748047</v>
       </c>
       <c r="F97" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="n">
-        <v>182.6277776277465</v>
+        <v>185.3292747163753</v>
       </c>
       <c r="C98" t="n">
-        <v>186.8587614695496</v>
+        <v>185.6768821509354</v>
       </c>
       <c r="D98" t="n">
-        <v>180.6215296329567</v>
+        <v>181.9822138463991</v>
       </c>
       <c r="E98" t="n">
-        <v>186.5111389160156</v>
+        <v>184.0281829833984</v>
       </c>
       <c r="F98" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B99" t="n">
-        <v>185.3292593497056</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C99" t="n">
-        <v>185.6768667554436</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D99" t="n">
-        <v>181.9821987572526</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E99" t="n">
-        <v>184.0281677246094</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F99" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B100" t="n">
-        <v>184.0579771467211</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C100" t="n">
-        <v>190.4243134969296</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D100" t="n">
-        <v>182.4787935369736</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E100" t="n">
-        <v>183.8990631103516</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F100" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" t="n">
-        <v>180.0355685556146</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C101" t="n">
-        <v>181.2273936107796</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D101" t="n">
-        <v>173.3811981056387</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E101" t="n">
-        <v>176.9467468261719</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F101" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B102" t="n">
-        <v>176.4302852446972</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C102" t="n">
-        <v>187.3851706171715</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D102" t="n">
-        <v>175.0795461293982</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E102" t="n">
-        <v>184.1573028564453</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F102" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B103" t="n">
-        <v>181.7537853733346</v>
+        <v>195.420066371549</v>
       </c>
       <c r="C103" t="n">
-        <v>191.2884162417558</v>
+        <v>199.6709185207204</v>
       </c>
       <c r="D103" t="n">
-        <v>181.0188192554131</v>
+        <v>190.0270517409182</v>
       </c>
       <c r="E103" t="n">
-        <v>190.4441986083984</v>
+        <v>198.1116180419922</v>
       </c>
       <c r="F103" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B104" t="n">
-        <v>195.420066371549</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C104" t="n">
-        <v>199.6709185207204</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D104" t="n">
-        <v>190.0270517409182</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E104" t="n">
-        <v>198.1116180419922</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F104" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B105" t="n">
-        <v>190.6031086414411</v>
+        <v>191.1890843548102</v>
       </c>
       <c r="C105" t="n">
-        <v>194.5857953386064</v>
+        <v>194.6056605467623</v>
       </c>
       <c r="D105" t="n">
-        <v>188.6266549601705</v>
+        <v>189.3814711920236</v>
       </c>
       <c r="E105" t="n">
-        <v>193.4634857177734</v>
+        <v>191.6360168457031</v>
       </c>
       <c r="F105" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B106" t="n">
-        <v>191.1890691316076</v>
+        <v>189.4509946932415</v>
       </c>
       <c r="C106" t="n">
-        <v>194.6056450515189</v>
+        <v>197.3170577657204</v>
       </c>
       <c r="D106" t="n">
-        <v>189.38145611275</v>
+        <v>188.2889641983741</v>
       </c>
       <c r="E106" t="n">
-        <v>191.6360015869141</v>
+        <v>194.7149047851562</v>
       </c>
       <c r="F106" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B107" t="n">
-        <v>189.4510095395255</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C107" t="n">
-        <v>197.3170732284266</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D107" t="n">
-        <v>188.2889789535958</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E107" t="n">
-        <v>194.7149200439453</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F107" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B108" t="n">
-        <v>193.7713848635987</v>
+        <v>193.036414733929</v>
       </c>
       <c r="C108" t="n">
-        <v>195.1320503828654</v>
+        <v>203.027904005614</v>
       </c>
       <c r="D108" t="n">
-        <v>190.7918147128814</v>
+        <v>192.9172367799533</v>
       </c>
       <c r="E108" t="n">
-        <v>191.76513671875</v>
+        <v>200.0185394287109</v>
       </c>
       <c r="F108" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B109" t="n">
-        <v>193.0364294600736</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C109" t="n">
-        <v>203.0279194939781</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D109" t="n">
-        <v>192.9172514970062</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E109" t="n">
-        <v>200.0185546875</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F109" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B110" t="n">
-        <v>199.4226244314719</v>
+        <v>197.2078040637707</v>
       </c>
       <c r="C110" t="n">
-        <v>201.5778601866405</v>
+        <v>202.2830055722447</v>
       </c>
       <c r="D110" t="n">
-        <v>196.0259162627038</v>
+        <v>194.5361205377908</v>
       </c>
       <c r="E110" t="n">
-        <v>200.733642578125</v>
+        <v>197.4362335205078</v>
       </c>
       <c r="F110" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B111" t="n">
-        <v>197.2078193049057</v>
+        <v>195.9166750362765</v>
       </c>
       <c r="C111" t="n">
-        <v>202.2830212056148</v>
+        <v>198.2109569133711</v>
       </c>
       <c r="D111" t="n">
-        <v>194.5361355724457</v>
+        <v>189.3020404418633</v>
       </c>
       <c r="E111" t="n">
-        <v>197.4362487792969</v>
+        <v>193.5826873779297</v>
       </c>
       <c r="F111" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B112" t="n">
-        <v>195.9166595935153</v>
+        <v>195.0625138319317</v>
       </c>
       <c r="C112" t="n">
-        <v>198.2109412897675</v>
+        <v>198.1910714873107</v>
       </c>
       <c r="D112" t="n">
-        <v>189.3020255204881</v>
+        <v>189.9873122244243</v>
       </c>
       <c r="E112" t="n">
-        <v>193.5826721191406</v>
+        <v>192.8079833984375</v>
       </c>
       <c r="F112" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B113" t="n">
-        <v>195.0625292691439</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C113" t="n">
-        <v>198.1910871721164</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D113" t="n">
-        <v>189.987327259986</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E113" t="n">
-        <v>192.8079986572266</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F113" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B114" t="n">
-        <v>192.8079750209554</v>
+        <v>198.3698354155112</v>
       </c>
       <c r="C114" t="n">
-        <v>203.4648992272838</v>
+        <v>199.6311909649738</v>
       </c>
       <c r="D114" t="n">
-        <v>191.8346379323055</v>
+        <v>190.4441834205658</v>
       </c>
       <c r="E114" t="n">
-        <v>197.9228973388672</v>
+        <v>191.5168304443359</v>
       </c>
       <c r="F114" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B115" t="n">
-        <v>198.3698512203022</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C115" t="n">
-        <v>199.6312068702612</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D115" t="n">
-        <v>190.4441985938934</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E115" t="n">
-        <v>191.516845703125</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F115" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B116" t="n">
-        <v>193.821025021851</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C116" t="n">
-        <v>197.2773371794379</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D116" t="n">
-        <v>193.821025021851</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E116" t="n">
-        <v>196.9893035888672</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F116" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B117" t="n">
-        <v>196.870136689126</v>
+        <v>192.0829546896537</v>
       </c>
       <c r="C117" t="n">
-        <v>201.0018110133274</v>
+        <v>194.8142273994103</v>
       </c>
       <c r="D117" t="n">
-        <v>193.1258058856387</v>
+        <v>191.3281356874407</v>
       </c>
       <c r="E117" t="n">
-        <v>193.9799499511719</v>
+        <v>193.0165557861328</v>
       </c>
       <c r="F117" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B118" t="n">
-        <v>192.0829395046699</v>
+        <v>194.2580448499211</v>
       </c>
       <c r="C118" t="n">
-        <v>194.8142119985075</v>
+        <v>199.0352867281362</v>
       </c>
       <c r="D118" t="n">
-        <v>191.3281205621285</v>
+        <v>191.9836462262046</v>
       </c>
       <c r="E118" t="n">
-        <v>193.0165405273438</v>
+        <v>193.6621398925781</v>
       </c>
       <c r="F118" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B119" t="n">
-        <v>194.2580448499211</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C119" t="n">
-        <v>199.0352867281362</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D119" t="n">
-        <v>191.9836462262046</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E119" t="n">
-        <v>193.6621398925781</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F119" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B120" t="n">
-        <v>191.8942484911283</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C120" t="n">
-        <v>194.3374874288811</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D120" t="n">
-        <v>188.7061018910339</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E120" t="n">
-        <v>194.0494689941406</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F120" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B121" t="n">
-        <v>195.7478267440036</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C121" t="n">
-        <v>196.7012958768407</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D121" t="n">
-        <v>190.6924929381777</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E121" t="n">
-        <v>193.850830078125</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F121" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B122" t="n">
-        <v>190.8315397252546</v>
+        <v>184.4353765448059</v>
       </c>
       <c r="C122" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1138700384234</v>
       </c>
       <c r="D122" t="n">
-        <v>181.0486114593648</v>
+        <v>178.625224245603</v>
       </c>
       <c r="E122" t="n">
-        <v>181.7736511230469</v>
+        <v>180.7208557128906</v>
       </c>
       <c r="F122" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B123" t="n">
-        <v>184.4353921172228</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C123" t="n">
-        <v>186.1138857525603</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D123" t="n">
-        <v>178.6252393274517</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E123" t="n">
-        <v>180.7208709716797</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F123" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B124" t="n">
-        <v>179.9461742219026</v>
+        <v>182.7469612620264</v>
       </c>
       <c r="C124" t="n">
-        <v>186.1933484091056</v>
+        <v>182.8562127689759</v>
       </c>
       <c r="D124" t="n">
-        <v>178.3074166263376</v>
+        <v>177.6022443008385</v>
       </c>
       <c r="E124" t="n">
-        <v>184.3758087158203</v>
+        <v>178.0888977050781</v>
       </c>
       <c r="F124" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B125" t="n">
-        <v>182.7469769199218</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C125" t="n">
-        <v>182.8562284362321</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D125" t="n">
-        <v>177.6022595179307</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E125" t="n">
-        <v>178.0889129638672</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F125" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" t="n">
-        <v>178.873523844959</v>
+        <v>183.6408377857945</v>
       </c>
       <c r="C126" t="n">
-        <v>185.1206822343098</v>
+        <v>187.216328097891</v>
       </c>
       <c r="D126" t="n">
-        <v>178.3570608051074</v>
+        <v>181.0684791429995</v>
       </c>
       <c r="E126" t="n">
-        <v>183.7699432373047</v>
+        <v>185.3987884521484</v>
       </c>
       <c r="F126" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" t="n">
-        <v>183.6408226716892</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C127" t="n">
-        <v>187.2163126895138</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D127" t="n">
-        <v>181.0684642406058</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E127" t="n">
-        <v>185.3987731933594</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F127" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B128" t="n">
-        <v>185.5775567084869</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C128" t="n">
-        <v>187.6930410934417</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D128" t="n">
-        <v>181.7636956083204</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E128" t="n">
-        <v>184.9717102050781</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F128" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B129" t="n">
-        <v>184.0381169897925</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C129" t="n">
-        <v>186.3025890630262</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D129" t="n">
-        <v>180.3434488377003</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E129" t="n">
-        <v>185.9053039550781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F129" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B130" t="n">
-        <v>186.2231237330043</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C130" t="n">
-        <v>186.8587647224845</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D130" t="n">
-        <v>182.3496888213084</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E130" t="n">
-        <v>183.7699432373047</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F130" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" t="n">
-        <v>183.690504131923</v>
+        <v>185.229934306832</v>
       </c>
       <c r="C131" t="n">
-        <v>185.3094088283374</v>
+        <v>185.498099849194</v>
       </c>
       <c r="D131" t="n">
-        <v>180.7804644422889</v>
+        <v>174.5829363342851</v>
       </c>
       <c r="E131" t="n">
-        <v>181.7140655517578</v>
+        <v>175.1689147949219</v>
       </c>
       <c r="F131" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,25 +3849,25 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B132" t="n">
-        <v>185.2299504420264</v>
+        <v>172.4208720146844</v>
       </c>
       <c r="C132" t="n">
-        <v>185.4981160077481</v>
+        <v>173.5360220799356</v>
       </c>
       <c r="D132" t="n">
-        <v>174.5829515420302</v>
+        <v>166.3970410225636</v>
       </c>
       <c r="E132" t="n">
-        <v>175.1689300537109</v>
+        <v>170.1109161376953</v>
       </c>
       <c r="F132" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B133" t="n">
-        <v>172.4208565486944</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C133" t="n">
-        <v>173.5360065139178</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D133" t="n">
-        <v>166.3970260969056</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E133" t="n">
-        <v>170.1109008789062</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F133" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G133" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B134" t="n">
-        <v>170.5191174814139</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C134" t="n">
-        <v>170.5191174814139</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D134" t="n">
-        <v>162.8126107290287</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E134" t="n">
-        <v>164.2463836669922</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F134" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B135" t="n">
-        <v>166.3273444705899</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C135" t="n">
-        <v>172.6498652447362</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D135" t="n">
-        <v>165.0528829680655</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E135" t="n">
-        <v>172.0723876953125</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F135" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B136" t="n">
-        <v>174.4520463656914</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C136" t="n">
-        <v>176.7321331165696</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D136" t="n">
-        <v>169.7624151908458</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E136" t="n">
-        <v>170.5689086914062</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F136" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B137" t="n">
-        <v>173.4663277892384</v>
+        <v>183.2040075329009</v>
       </c>
       <c r="C137" t="n">
-        <v>178.842961383224</v>
+        <v>183.7516312461474</v>
       </c>
       <c r="D137" t="n">
-        <v>172.1321282578628</v>
+        <v>177.7975052553062</v>
       </c>
       <c r="E137" t="n">
-        <v>176.8317108154297</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F137" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B138" t="n">
-        <v>183.2040230257668</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C138" t="n">
-        <v>183.7516467853238</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D138" t="n">
-        <v>177.7975202909648</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E138" t="n">
-        <v>180.4360504150391</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F138" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="n">
-        <v>184.6278268926657</v>
+        <v>181.7105075933097</v>
       </c>
       <c r="C139" t="n">
-        <v>187.1667986912511</v>
+        <v>188.1823886856741</v>
       </c>
       <c r="D139" t="n">
-        <v>180.2468672661974</v>
+        <v>181.3321466062204</v>
       </c>
       <c r="E139" t="n">
-        <v>181.3520660400391</v>
+        <v>185.4642028808594</v>
       </c>
       <c r="F139" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B140" t="n">
-        <v>181.7104926433502</v>
+        <v>185.7927641258556</v>
       </c>
       <c r="C140" t="n">
-        <v>188.1823732032504</v>
+        <v>192.7226462718077</v>
       </c>
       <c r="D140" t="n">
-        <v>181.33213168739</v>
+        <v>183.303579264538</v>
       </c>
       <c r="E140" t="n">
-        <v>185.4641876220703</v>
+        <v>186.3005523681641</v>
       </c>
       <c r="F140" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B141" t="n">
-        <v>185.7927793430547</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C141" t="n">
-        <v>192.7226620565929</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D141" t="n">
-        <v>183.3035942778625</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E141" t="n">
-        <v>186.3005676269531</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F141" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B142" t="n">
-        <v>187.3858431404722</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C142" t="n">
-        <v>190.3230783921826</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D142" t="n">
-        <v>186.2209063874661</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E142" t="n">
-        <v>188.9789276123047</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F142" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B143" t="n">
-        <v>176.7918740224492</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C143" t="n">
-        <v>178.0962045390804</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D143" t="n">
-        <v>169.9117629967484</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E143" t="n">
-        <v>172.5503082275391</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F143" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B144" t="n">
-        <v>174.8602617765654</v>
+        <v>177.4888508581443</v>
       </c>
       <c r="C144" t="n">
-        <v>177.6780209996891</v>
+        <v>183.4927641701262</v>
       </c>
       <c r="D144" t="n">
-        <v>173.6455382897692</v>
+        <v>176.7420953199099</v>
       </c>
       <c r="E144" t="n">
-        <v>177.3892822265625</v>
+        <v>179.4005432128906</v>
       </c>
       <c r="F144" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="n">
-        <v>177.4888357619529</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C145" t="n">
-        <v>183.4927485632761</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D145" t="n">
-        <v>176.7420802872333</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E145" t="n">
-        <v>179.4005279541016</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F145" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B146" t="n">
-        <v>181.6407975504903</v>
+        <v>178.424769515226</v>
       </c>
       <c r="C146" t="n">
-        <v>183.6221942474171</v>
+        <v>180.993610139636</v>
       </c>
       <c r="D146" t="n">
-        <v>180.5356140136719</v>
+        <v>176.5827818160244</v>
       </c>
       <c r="E146" t="n">
-        <v>180.5356140136719</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F146" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="n">
-        <v>178.4247846039299</v>
+        <v>177.5286741071897</v>
       </c>
       <c r="C147" t="n">
-        <v>180.993625445577</v>
+        <v>177.9169863526292</v>
       </c>
       <c r="D147" t="n">
-        <v>176.5827967489585</v>
+        <v>172.2515989617143</v>
       </c>
       <c r="E147" t="n">
-        <v>180.4360504150391</v>
+        <v>175.7663269042969</v>
       </c>
       <c r="F147" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B148" t="n">
-        <v>177.5286895189733</v>
+        <v>181.4018572311292</v>
       </c>
       <c r="C148" t="n">
-        <v>177.9170017981234</v>
+        <v>185.2351932001588</v>
       </c>
       <c r="D148" t="n">
-        <v>172.2516139153796</v>
+        <v>177.9767360752557</v>
       </c>
       <c r="E148" t="n">
-        <v>175.7663421630859</v>
+        <v>183.0248107910156</v>
       </c>
       <c r="F148" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="n">
-        <v>181.4018421076459</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C149" t="n">
-        <v>185.2351777570901</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D149" t="n">
-        <v>177.9767212373249</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E149" t="n">
-        <v>183.0247955322266</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F149" t="n">
-        <v>12324400</v>
+        <v>8444700</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="n">
-        <v>183.4429710909726</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C150" t="n">
-        <v>189.4867039708132</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D150" t="n">
-        <v>183.1741348747832</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E150" t="n">
-        <v>184.6775970458984</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F150" t="n">
-        <v>8444700</v>
+        <v>9740800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="n">
-        <v>184.7473182824849</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C151" t="n">
-        <v>186.5793548412774</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D151" t="n">
-        <v>180.3165719120649</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E151" t="n">
-        <v>186.1810913085938</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F151" t="n">
-        <v>9740800</v>
+        <v>11303400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="n">
-        <v>184.7174439304337</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C152" t="n">
-        <v>186.2906106667237</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D152" t="n">
-        <v>178.8031379653169</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E152" t="n">
-        <v>180.4061737060547</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F152" t="n">
-        <v>11303400</v>
+        <v>13955100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="n">
-        <v>183.801426731489</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C153" t="n">
-        <v>187.7642050029951</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D153" t="n">
-        <v>183.2040162535504</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E153" t="n">
-        <v>185.5338897705078</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F153" t="n">
-        <v>13955100</v>
+        <v>15123900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="n">
-        <v>178.9027054786904</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C154" t="n">
-        <v>181.0832340725416</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D154" t="n">
-        <v>176.114830301217</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E154" t="n">
-        <v>181.0334625244141</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F154" t="n">
-        <v>15123900</v>
+        <v>11145000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="n">
-        <v>179.1317124775628</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C155" t="n">
-        <v>181.7105044839724</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D155" t="n">
-        <v>175.5472800106302</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E155" t="n">
-        <v>176.7221832275391</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F155" t="n">
-        <v>11145000</v>
+        <v>10214000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C156" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D156" t="n">
-        <v>169.8420709331304</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E156" t="n">
-        <v>170.5689086914062</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F156" t="n">
-        <v>10214000</v>
+        <v>11951900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="n">
-        <v>169.0455318751909</v>
+        <v>165.2818748478833</v>
       </c>
       <c r="C157" t="n">
-        <v>169.0455318751909</v>
+        <v>168.6173886402985</v>
       </c>
       <c r="D157" t="n">
-        <v>164.0372928300067</v>
+        <v>163.6191011830893</v>
       </c>
       <c r="E157" t="n">
-        <v>165.1225738525391</v>
+        <v>166.8550415039062</v>
       </c>
       <c r="F157" t="n">
-        <v>11951900</v>
+        <v>9749400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="n">
-        <v>165.2818899628073</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C158" t="n">
-        <v>168.6174040602531</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D158" t="n">
-        <v>163.6191161459536</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E158" t="n">
-        <v>166.8550567626953</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F158" t="n">
-        <v>9749400</v>
+        <v>13883400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="n">
-        <v>168.5178185348167</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C159" t="n">
-        <v>175.208748793394</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D159" t="n">
-        <v>168.268900043628</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E159" t="n">
-        <v>172.7593841552734</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F159" t="n">
-        <v>13883400</v>
+        <v>13671200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="n">
-        <v>172.1420794089453</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C160" t="n">
-        <v>179.9979467596552</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D160" t="n">
-        <v>171.0567983816156</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E160" t="n">
-        <v>178.7035675048828</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F160" t="n">
-        <v>13671200</v>
+        <v>17510800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="n">
-        <v>184.1996921538</v>
+        <v>175.2784431578192</v>
       </c>
       <c r="C161" t="n">
-        <v>186.6291391730516</v>
+        <v>179.529975364695</v>
       </c>
       <c r="D161" t="n">
-        <v>178.0364675908902</v>
+        <v>172.5901264135125</v>
       </c>
       <c r="E161" t="n">
-        <v>178.6438293457031</v>
+        <v>179.3208923339844</v>
       </c>
       <c r="F161" t="n">
-        <v>17510800</v>
+        <v>13025300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="n">
-        <v>175.2784580726278</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C162" t="n">
-        <v>179.5299906412754</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D162" t="n">
-        <v>172.5901410995666</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E162" t="n">
-        <v>179.3209075927734</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F162" t="n">
-        <v>13025300</v>
+        <v>10949100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="n">
-        <v>174.6213174256682</v>
+        <v>179.0619996775001</v>
       </c>
       <c r="C163" t="n">
-        <v>176.5728300297275</v>
+        <v>182.5568249684187</v>
       </c>
       <c r="D163" t="n">
-        <v>171.2459830488208</v>
+        <v>176.9113402973623</v>
       </c>
       <c r="E163" t="n">
-        <v>175.5472869873047</v>
+        <v>179.291015625</v>
       </c>
       <c r="F163" t="n">
-        <v>10949100</v>
+        <v>10176700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B164" t="n">
-        <v>179.0620149167984</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C164" t="n">
-        <v>182.5568405051486</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D164" t="n">
-        <v>176.9113553536261</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E164" t="n">
-        <v>179.2910308837891</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F164" t="n">
-        <v>10176700</v>
+        <v>13617200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B165" t="n">
-        <v>177.6581006500201</v>
+        <v>177.2299664024681</v>
       </c>
       <c r="C165" t="n">
-        <v>181.5711072848628</v>
+        <v>183.1243544731695</v>
       </c>
       <c r="D165" t="n">
-        <v>176.9113451663183</v>
+        <v>176.1247676896629</v>
       </c>
       <c r="E165" t="n">
-        <v>178.3052978515625</v>
+        <v>176.7420806884766</v>
       </c>
       <c r="F165" t="n">
-        <v>13617200</v>
+        <v>18524900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B166" t="n">
-        <v>177.2299817033781</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C166" t="n">
-        <v>183.1243702829636</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D166" t="n">
-        <v>176.1247828951571</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E166" t="n">
-        <v>176.7420959472656</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F166" t="n">
-        <v>18524900</v>
+        <v>22559400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B167" t="n">
-        <v>177.6581004088628</v>
+        <v>179.4602803383912</v>
       </c>
       <c r="C167" t="n">
-        <v>181.6905830539347</v>
+        <v>193.3001423298492</v>
       </c>
       <c r="D167" t="n">
-        <v>170.9074320607842</v>
+        <v>179.24123085138</v>
       </c>
       <c r="E167" t="n">
-        <v>175.4078826904297</v>
+        <v>190.2733001708984</v>
       </c>
       <c r="F167" t="n">
-        <v>22559400</v>
+        <v>33998900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="n">
-        <v>179.4602947300403</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C168" t="n">
-        <v>193.300157831373</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D168" t="n">
-        <v>179.2412452254626</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E168" t="n">
-        <v>190.2733154296875</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F168" t="n">
-        <v>33998900</v>
+        <v>27594800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="n">
-        <v>197.8901992931745</v>
+        <v>200.1503901074607</v>
       </c>
       <c r="C169" t="n">
-        <v>210.4257307870387</v>
+        <v>203.5058065985036</v>
       </c>
       <c r="D169" t="n">
-        <v>197.352542040295</v>
+        <v>194.9131351866423</v>
       </c>
       <c r="E169" t="n">
-        <v>208.6932678222656</v>
+        <v>199.9711608886719</v>
       </c>
       <c r="F169" t="n">
-        <v>27594800</v>
+        <v>19216600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B170" t="n">
-        <v>200.1504053799259</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C170" t="n">
-        <v>203.5058221270036</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D170" t="n">
-        <v>194.9131500594789</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E170" t="n">
-        <v>199.9711761474609</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F170" t="n">
-        <v>19216600</v>
+        <v>14154400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B171" t="n">
-        <v>196.4166079226038</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C171" t="n">
-        <v>196.8248227029743</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D171" t="n">
-        <v>188.9092176958791</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E171" t="n">
-        <v>189.7854156494141</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F171" t="n">
-        <v>14154400</v>
+        <v>14453600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B172" t="n">
-        <v>196.9542758894677</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C172" t="n">
-        <v>197.2330634002457</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D172" t="n">
-        <v>185.3048928689384</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E172" t="n">
-        <v>187.9334716796875</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F172" t="n">
-        <v>14453600</v>
+        <v>13183900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B173" t="n">
-        <v>188.9789318725711</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C173" t="n">
-        <v>191.6771999565016</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D173" t="n">
-        <v>184.0304307819904</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E173" t="n">
-        <v>184.8568420410156</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F173" t="n">
-        <v>13183900</v>
+        <v>11177800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B174" t="n">
-        <v>183.1144169895118</v>
+        <v>178.7234870391233</v>
       </c>
       <c r="C174" t="n">
-        <v>184.2196157855271</v>
+        <v>181.6706888305526</v>
       </c>
       <c r="D174" t="n">
-        <v>180.92393713233</v>
+        <v>170.8178328696119</v>
       </c>
       <c r="E174" t="n">
-        <v>181.7602996826172</v>
+        <v>174.5914459228516</v>
       </c>
       <c r="F174" t="n">
-        <v>11177800</v>
+        <v>15427800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B175" t="n">
-        <v>178.7234714192057</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C175" t="n">
-        <v>181.670672953058</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D175" t="n">
-        <v>170.8178179406258</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E175" t="n">
-        <v>174.5914306640625</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F175" t="n">
-        <v>15427800</v>
+        <v>10820500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,25 +4993,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B176" t="n">
-        <v>169.861995238658</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C176" t="n">
-        <v>174.7706609037228</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D176" t="n">
-        <v>169.2944537502145</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E176" t="n">
-        <v>170.1806030273438</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F176" t="n">
-        <v>10820500</v>
+        <v>16666000</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B177" t="n">
-        <v>167.9744954285649</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C177" t="n">
-        <v>168.6832400259219</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D177" t="n">
-        <v>163.0231992739924</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E177" t="n">
-        <v>166.1576843261719</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F177" t="n">
-        <v>16666000</v>
+        <v>13589400</v>
       </c>
       <c r="G177" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B178" t="n">
-        <v>164.4506890531704</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C178" t="n">
-        <v>166.2475157071144</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D178" t="n">
-        <v>161.1165431857153</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E178" t="n">
-        <v>165.5986633300781</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F178" t="n">
-        <v>13589400</v>
+        <v>13541800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B179" t="n">
-        <v>165.7384133733495</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C179" t="n">
-        <v>169.6515271583533</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D179" t="n">
-        <v>163.8816793355271</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E179" t="n">
-        <v>164.2610168457031</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F179" t="n">
-        <v>13541800</v>
+        <v>16385300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B180" t="n">
-        <v>163.7718739013043</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C180" t="n">
-        <v>166.0079454764833</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D180" t="n">
-        <v>160.2181284427459</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E180" t="n">
-        <v>161.4260101318359</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F180" t="n">
-        <v>16385300</v>
+        <v>19986200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B181" t="n">
-        <v>159.9685677271403</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C181" t="n">
-        <v>161.1464880907799</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D181" t="n">
-        <v>153.959135832121</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E181" t="n">
-        <v>154.7477569580078</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F181" t="n">
-        <v>19986200</v>
+        <v>57940800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B182" t="n">
-        <v>152.4617715583163</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C182" t="n">
-        <v>154.1987212566731</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D182" t="n">
-        <v>149.5369245308901</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E182" t="n">
-        <v>151.5134429931641</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F182" t="n">
-        <v>57940800</v>
+        <v>20502800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B183" t="n">
-        <v>149.8962920415152</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C183" t="n">
-        <v>153.5997679942281</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D183" t="n">
-        <v>146.0630395211035</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E183" t="n">
-        <v>149.8563537597656</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F183" t="n">
-        <v>20502800</v>
+        <v>20720700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B184" t="n">
-        <v>151.3836627210609</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C184" t="n">
-        <v>154.907462036052</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D184" t="n">
-        <v>150.5850798848861</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E184" t="n">
-        <v>153.1505584716797</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F184" t="n">
-        <v>20720700</v>
+        <v>13146800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B185" t="n">
-        <v>151.5433859321397</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C185" t="n">
-        <v>156.7841657815476</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D185" t="n">
-        <v>150.135858545478</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E185" t="n">
-        <v>152.4917144775391</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F185" t="n">
-        <v>13146800</v>
+        <v>11324700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B186" t="n">
-        <v>149.7465472087312</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C186" t="n">
-        <v>153.7295454610107</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D186" t="n">
-        <v>148.5187115976041</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E186" t="n">
-        <v>149.9262390136719</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F186" t="n">
-        <v>11324700</v>
+        <v>21267900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B187" t="n">
-        <v>151.2239658596097</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C187" t="n">
-        <v>158.1817266914859</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D187" t="n">
-        <v>151.2239658596097</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E187" t="n">
-        <v>158.0918731689453</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F187" t="n">
-        <v>21267900</v>
+        <v>12664100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B188" t="n">
-        <v>159.9885357004027</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C188" t="n">
-        <v>161.4759091917036</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D188" t="n">
-        <v>157.4230418613804</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E188" t="n">
-        <v>157.6526336669922</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F188" t="n">
-        <v>12664100</v>
+        <v>13690500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B189" t="n">
-        <v>154.8176224085462</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C189" t="n">
-        <v>157.4130622995693</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D189" t="n">
-        <v>153.7994247316601</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E189" t="n">
-        <v>156.3848724365234</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F189" t="n">
-        <v>13690500</v>
+        <v>14164600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B190" t="n">
-        <v>161.9351081174896</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C190" t="n">
-        <v>165.5187996520913</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D190" t="n">
-        <v>160.916895191227</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E190" t="n">
-        <v>162.9433288574219</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F190" t="n">
-        <v>14164600</v>
+        <v>10486300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B191" t="n">
-        <v>162.7137441629</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C191" t="n">
-        <v>166.9163573859938</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D191" t="n">
-        <v>161.7155003336798</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E191" t="n">
-        <v>165.8182830810547</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F191" t="n">
-        <v>10486300</v>
+        <v>10595500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B192" t="n">
-        <v>163.7020118941432</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C192" t="n">
-        <v>167.425457131665</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D192" t="n">
-        <v>162.0848465245878</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E192" t="n">
-        <v>165.3590850830078</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F192" t="n">
-        <v>10595500</v>
+        <v>13057900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B193" t="n">
-        <v>168.9228138583306</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C193" t="n">
-        <v>172.0772678623225</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D193" t="n">
-        <v>167.3855099055031</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E193" t="n">
-        <v>169.2222900390625</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F193" t="n">
-        <v>13057900</v>
+        <v>9792400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B194" t="n">
-        <v>167.0760662569272</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C194" t="n">
-        <v>167.2357889266519</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D194" t="n">
-        <v>164.4906183727253</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E194" t="n">
-        <v>166.2874603271484</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F194" t="n">
-        <v>9792400</v>
+        <v>13858600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B195" t="n">
-        <v>158.05194011754</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C195" t="n">
-        <v>163.5123348335076</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D195" t="n">
-        <v>156.2051830247059</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E195" t="n">
-        <v>162.2146148681641</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F195" t="n">
-        <v>13858600</v>
+        <v>8321500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B196" t="n">
-        <v>165.309182555471</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C196" t="n">
-        <v>166.007950182526</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D196" t="n">
-        <v>162.1347592897187</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E196" t="n">
-        <v>163.0331878662109</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F196" t="n">
-        <v>8321500</v>
+        <v>14020700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>165.6286161244176</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C197" t="n">
-        <v>172.4566003351415</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D197" t="n">
-        <v>165.6286161244176</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E197" t="n">
-        <v>170.9193115234375</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F197" t="n">
-        <v>14020700</v>
+        <v>13507900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>162.2046435717354</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C198" t="n">
-        <v>171.049084414024</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D198" t="n">
-        <v>161.1864306117812</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E198" t="n">
-        <v>167.2657318115234</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F198" t="n">
-        <v>13507900</v>
+        <v>13328100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>170.2205331766167</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C199" t="n">
-        <v>172.4965277703878</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D199" t="n">
-        <v>166.2674811162824</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E199" t="n">
-        <v>166.7067108154297</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F199" t="n">
-        <v>13328100</v>
+        <v>12057500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B200" t="n">
-        <v>170.5399744864679</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C200" t="n">
-        <v>174.2334736592566</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D200" t="n">
-        <v>166.5869373980102</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E200" t="n">
-        <v>172.3767395019531</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F200" t="n">
-        <v>12057500</v>
+        <v>10191500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B201" t="n">
-        <v>171.1988064601764</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C201" t="n">
-        <v>175.1218971627477</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D201" t="n">
-        <v>169.4518798636439</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E201" t="n">
-        <v>170.4700927734375</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F201" t="n">
-        <v>10191500</v>
+        <v>13426500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B202" t="n">
-        <v>167.5652084388413</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C202" t="n">
-        <v>175.0819831940494</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D202" t="n">
-        <v>166.2075962327059</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E202" t="n">
-        <v>173.4847869873047</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F202" t="n">
-        <v>13426500</v>
+        <v>12831800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B203" t="n">
-        <v>166.7666058963373</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C203" t="n">
-        <v>172.1271701993457</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D203" t="n">
-        <v>166.6368293287962</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E203" t="n">
-        <v>169.7613372802734</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F203" t="n">
-        <v>12831800</v>
+        <v>12194500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B204" t="n">
-        <v>169.1723839486806</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C204" t="n">
-        <v>169.272214424985</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D204" t="n">
-        <v>161.925139189555</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E204" t="n">
-        <v>162.7137451171875</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F204" t="n">
-        <v>12194500</v>
+        <v>12775000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B205" t="n">
-        <v>164.7601382451291</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C205" t="n">
-        <v>165.5886824068968</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D205" t="n">
-        <v>154.877515725338</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E205" t="n">
-        <v>156.6543884277344</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F205" t="n">
-        <v>12775000</v>
+        <v>10899100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B206" t="n">
-        <v>160.0983505627206</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C206" t="n">
-        <v>164.1611950360997</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D206" t="n">
-        <v>159.2698063547753</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E206" t="n">
-        <v>163.3725891113281</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F206" t="n">
-        <v>10899100</v>
+        <v>17312000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B207" t="n">
-        <v>167.7049639405646</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C207" t="n">
-        <v>176.6392431993331</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D207" t="n">
-        <v>166.8464736349225</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E207" t="n">
-        <v>173.2951354980469</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F207" t="n">
-        <v>17312000</v>
+        <v>17204600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B208" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C208" t="n">
-        <v>184.2158982492034</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D208" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E208" t="n">
-        <v>181.1812438964844</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F208" t="n">
-        <v>17204600</v>
+        <v>18139500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B209" t="n">
-        <v>181.6903554713178</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C209" t="n">
-        <v>189.8460057999592</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D209" t="n">
-        <v>181.6903554713178</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E209" t="n">
-        <v>188.0491790771484</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F209" t="n">
-        <v>18139500</v>
+        <v>12182400</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B210" t="n">
-        <v>180.6721461984077</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C210" t="n">
-        <v>182.1894657683464</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D210" t="n">
-        <v>175.5910738107855</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E210" t="n">
-        <v>180.3926391601562</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F210" t="n">
-        <v>12182400</v>
+        <v>9691500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B211" t="n">
-        <v>177.3879151720665</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C211" t="n">
-        <v>184.1260606305619</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D211" t="n">
-        <v>176.719093672914</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E211" t="n">
-        <v>183.6968231201172</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F211" t="n">
-        <v>9691500</v>
+        <v>12908000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B212" t="n">
-        <v>188.658097974018</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C212" t="n">
-        <v>193.3598176605707</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D212" t="n">
-        <v>185.5735131091938</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E212" t="n">
-        <v>185.6234283447266</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F212" t="n">
-        <v>12908000</v>
+        <v>9326900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B213" t="n">
-        <v>182.7684517177381</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C213" t="n">
-        <v>190.9540477431734</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D213" t="n">
-        <v>182.6786134323838</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E213" t="n">
-        <v>190.6545867919922</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F213" t="n">
-        <v>9326900</v>
+        <v>9605500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B214" t="n">
-        <v>192.9405589477455</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C214" t="n">
-        <v>194.5976472985604</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D214" t="n">
-        <v>190.0955580470331</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E214" t="n">
-        <v>192.6410827636719</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F214" t="n">
-        <v>9605500</v>
+        <v>13297600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B215" t="n">
-        <v>183.117847615437</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C215" t="n">
-        <v>186.6915622961891</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D215" t="n">
-        <v>182.6786179003067</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E215" t="n">
-        <v>186.4420013427734</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F215" t="n">
-        <v>13297600</v>
+        <v>11392800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B216" t="n">
-        <v>190.7544083295565</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C216" t="n">
-        <v>194.3580691369978</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D216" t="n">
-        <v>190.2652786051507</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E216" t="n">
-        <v>192.4015197753906</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F216" t="n">
-        <v>11392800</v>
+        <v>9706600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B217" t="n">
-        <v>189.8360257192551</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C217" t="n">
-        <v>197.831953246477</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D217" t="n">
-        <v>189.666326097428</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E217" t="n">
-        <v>197.1631317138672</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F217" t="n">
-        <v>9706600</v>
+        <v>11171600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B218" t="n">
-        <v>196.5941314807131</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C218" t="n">
-        <v>199.0398256830038</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D218" t="n">
-        <v>195.1566580076304</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E218" t="n">
-        <v>197.1231994628906</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F218" t="n">
-        <v>11171600</v>
+        <v>12787900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B219" t="n">
-        <v>191.6628101365335</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C219" t="n">
-        <v>196.1549072491085</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D219" t="n">
-        <v>191.4431952813594</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E219" t="n">
-        <v>192.9804992675781</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F219" t="n">
-        <v>12787900</v>
+        <v>15058700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="n">
-        <v>196.4943140399408</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C220" t="n">
-        <v>202.6335228023228</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D220" t="n">
-        <v>191.0538881519706</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E220" t="n">
-        <v>201.016357421875</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F220" t="n">
-        <v>15058700</v>
+        <v>8664800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B221" t="n">
-        <v>202.3939250564146</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C221" t="n">
-        <v>204.0410211897246</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D221" t="n">
-        <v>194.9769811314243</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E221" t="n">
-        <v>195.8654174804688</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F221" t="n">
-        <v>8664800</v>
+        <v>14378800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" t="n">
-        <v>193.4896063018435</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C222" t="n">
-        <v>194.5976575790598</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D222" t="n">
-        <v>189.57649225733</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E222" t="n">
-        <v>190.6346282958984</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F222" t="n">
-        <v>14378800</v>
+        <v>14152900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B223" t="n">
-        <v>193.7491445531879</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C223" t="n">
-        <v>199.0598091290667</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D223" t="n">
-        <v>192.8906542357335</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E223" t="n">
-        <v>195.7955474853516</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F223" t="n">
-        <v>14152900</v>
+        <v>17843600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B224" t="n">
-        <v>193.8689320609861</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C224" t="n">
-        <v>207.5847919095016</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D224" t="n">
-        <v>193.8689320609861</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E224" t="n">
-        <v>205.7280578613281</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F224" t="n">
-        <v>17843600</v>
+        <v>11482300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="n">
-        <v>204.8595912018172</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C225" t="n">
-        <v>207.5149233311111</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D225" t="n">
-        <v>202.6434887759544</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E225" t="n">
-        <v>205.0692138671875</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F225" t="n">
-        <v>11482300</v>
+        <v>9685400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B226" t="n">
-        <v>205.2189664215684</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C226" t="n">
-        <v>210.6993304789719</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D226" t="n">
-        <v>204.3704530814486</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E226" t="n">
-        <v>208.8026580810547</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F226" t="n">
-        <v>9685400</v>
+        <v>9580200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B227" t="n">
-        <v>208.0539803833292</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C227" t="n">
-        <v>212.7956386479058</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D227" t="n">
-        <v>207.0257904413594</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E227" t="n">
-        <v>208.6928558349609</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F227" t="n">
-        <v>9580200</v>
+        <v>10081800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="n">
-        <v>205.4884885298704</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C228" t="n">
-        <v>209.9406472657768</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D228" t="n">
-        <v>204.400391231641</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E228" t="n">
-        <v>205.3287658691406</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F228" t="n">
-        <v>10081800</v>
+        <v>14888900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B229" t="n">
-        <v>199.5888632714973</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C229" t="n">
-        <v>206.0774478239803</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D229" t="n">
-        <v>198.6005964484484</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E229" t="n">
-        <v>205.2588806152344</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F229" t="n">
-        <v>14888900</v>
+        <v>55517500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B230" t="n">
-        <v>229.6459965412689</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C230" t="n">
-        <v>254.0330860396483</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D230" t="n">
-        <v>229.6459965412689</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E230" t="n">
-        <v>251.6073608398438</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F230" t="n">
-        <v>55517500</v>
+        <v>34362700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B231" t="n">
-        <v>250.0301279952546</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C231" t="n">
-        <v>263.0671897003631</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D231" t="n">
-        <v>248.5627083778381</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E231" t="n">
-        <v>255.5504150390625</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F231" t="n">
-        <v>34362700</v>
+        <v>22471500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B232" t="n">
-        <v>253.9432305236259</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C232" t="n">
-        <v>261.8193732125837</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D232" t="n">
-        <v>253.9432305236259</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E232" t="n">
-        <v>257.0877075195312</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F232" t="n">
-        <v>22471500</v>
+        <v>15897500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B233" t="n">
-        <v>254.5621609406893</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C233" t="n">
-        <v>261.8593363431507</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D233" t="n">
-        <v>253.8035010915435</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E233" t="n">
-        <v>257.6567077636719</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F233" t="n">
-        <v>15897500</v>
+        <v>14393700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B234" t="n">
-        <v>258.9244691424316</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C234" t="n">
-        <v>264.0853722779391</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D234" t="n">
-        <v>253.154621477229</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E234" t="n">
-        <v>256.478759765625</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F234" t="n">
-        <v>14393700</v>
+        <v>16028300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B235" t="n">
-        <v>261.5199276025597</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C235" t="n">
-        <v>267.7988593124239</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D235" t="n">
-        <v>261.1405900757476</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E235" t="n">
-        <v>263.9656066894531</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F235" t="n">
-        <v>16028300</v>
+        <v>10490600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B236" t="n">
-        <v>262.8974710364521</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C236" t="n">
-        <v>263.1370702625856</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D236" t="n">
-        <v>257.3672223502596</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E236" t="n">
-        <v>258.7747497558594</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F236" t="n">
-        <v>10490600</v>
+        <v>17482700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B237" t="n">
-        <v>253.2744227737308</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C237" t="n">
-        <v>253.5539298242691</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D237" t="n">
-        <v>245.4581718493405</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E237" t="n">
-        <v>248.6824951171875</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F237" t="n">
-        <v>17482700</v>
+        <v>11853700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B238" t="n">
-        <v>249.3413418635835</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C238" t="n">
-        <v>254.3525301395604</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D238" t="n">
-        <v>243.0224566114913</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E238" t="n">
-        <v>243.7312164306641</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F238" t="n">
-        <v>11853700</v>
+        <v>10732600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B239" t="n">
-        <v>244.9191211985708</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C239" t="n">
-        <v>248.0635830600566</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D239" t="n">
-        <v>241.3254374437371</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E239" t="n">
-        <v>242.5732421875</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F239" t="n">
-        <v>10732600</v>
+        <v>9738300</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B240" t="n">
-        <v>241.5949712138984</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C240" t="n">
-        <v>250.1099896964979</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D240" t="n">
-        <v>241.5949712138984</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E240" t="n">
-        <v>247.2849578857422</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F240" t="n">
-        <v>9738300</v>
+        <v>12963700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B241" t="n">
-        <v>255.3008656803045</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C241" t="n">
-        <v>259.7230786425112</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D241" t="n">
-        <v>251.0583293004754</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E241" t="n">
-        <v>258.9743957519531</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F241" t="n">
-        <v>12963700</v>
+        <v>11502800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B242" t="n">
-        <v>256.43886230448</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C242" t="n">
-        <v>261.8792726915332</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D242" t="n">
-        <v>254.632028246405</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E242" t="n">
-        <v>255.2010192871094</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F242" t="n">
-        <v>11502800</v>
+        <v>9423800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B243" t="n">
-        <v>251.4077029961344</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C243" t="n">
-        <v>255.9497000259878</v>
+        <v>247</v>
       </c>
       <c r="D243" t="n">
-        <v>249.1616544830015</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E243" t="n">
-        <v>250.0999908447266</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F243" t="n">
-        <v>9423800</v>
+        <v>16611300</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,25 +6761,25 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" t="n">
-        <v>244.1799926757812</v>
+        <v>244.25</v>
       </c>
       <c r="C244" t="n">
-        <v>247</v>
+        <v>244.25</v>
       </c>
       <c r="D244" t="n">
-        <v>241.5200042724609</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E244" t="n">
-        <v>242.8500061035156</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F244" t="n">
-        <v>16611300</v>
+        <v>21962400</v>
       </c>
       <c r="G244" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B245" t="n">
-        <v>244.25</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C245" t="n">
-        <v>244.25</v>
+        <v>241.3399963378906</v>
       </c>
       <c r="D245" t="n">
-        <v>236.5500030517578</v>
+        <v>236.25</v>
       </c>
       <c r="E245" t="n">
-        <v>237.9199981689453</v>
+        <v>236.4199981689453</v>
       </c>
       <c r="F245" t="n">
-        <v>21962400</v>
+        <v>10581900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B246" t="n">
-        <v>239.8000030517578</v>
+        <v>241.5</v>
       </c>
       <c r="C246" t="n">
-        <v>241.3399963378906</v>
+        <v>242.4400024414062</v>
       </c>
       <c r="D246" t="n">
-        <v>236.25</v>
+        <v>229.8099975585938</v>
       </c>
       <c r="E246" t="n">
-        <v>236.4199981689453</v>
+        <v>233.2799987792969</v>
       </c>
       <c r="F246" t="n">
-        <v>10581900</v>
+        <v>13635600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B247" t="n">
-        <v>241.5</v>
+        <v>234.4199981689453</v>
       </c>
       <c r="C247" t="n">
-        <v>242.4400024414062</v>
+        <v>241.1199951171875</v>
       </c>
       <c r="D247" t="n">
-        <v>229.8099975585938</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="E247" t="n">
-        <v>233.2799987792969</v>
+        <v>237.5800018310547</v>
       </c>
       <c r="F247" t="n">
-        <v>13635600</v>
+        <v>12353500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B248" t="n">
-        <v>234.4199981689453</v>
+        <v>240.6399993896484</v>
       </c>
       <c r="C248" t="n">
-        <v>241.1199951171875</v>
+        <v>242.0899963378906</v>
       </c>
       <c r="D248" t="n">
-        <v>234.2400054931641</v>
+        <v>237</v>
       </c>
       <c r="E248" t="n">
-        <v>237.5800018310547</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="F248" t="n">
-        <v>12353500</v>
+        <v>11074000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B249" t="n">
-        <v>240.6399993896484</v>
+        <v>237.0299987792969</v>
       </c>
       <c r="C249" t="n">
-        <v>242.0899963378906</v>
+        <v>239.3699951171875</v>
       </c>
       <c r="D249" t="n">
-        <v>237</v>
+        <v>233.3800048828125</v>
       </c>
       <c r="E249" t="n">
-        <v>238.2200012207031</v>
+        <v>234.0200042724609</v>
       </c>
       <c r="F249" t="n">
-        <v>11074000</v>
+        <v>8735500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B250" t="n">
-        <v>237.0299987792969</v>
+        <v>224.9700012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>239.3699951171875</v>
+        <v>230.5700073242188</v>
       </c>
       <c r="D250" t="n">
-        <v>233.3800048828125</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="E250" t="n">
-        <v>234.0200042724609</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="F250" t="n">
-        <v>8735500</v>
+        <v>10327500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B251" t="n">
-        <v>224.9700012207031</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="C251" t="n">
-        <v>230.5700073242188</v>
+        <v>228.9799957275391</v>
       </c>
       <c r="D251" t="n">
-        <v>221.1799926757812</v>
+        <v>223.4299926757812</v>
       </c>
       <c r="E251" t="n">
-        <v>227.2700042724609</v>
+        <v>225.3099975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>10327500</v>
+        <v>13506300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B252" t="n">
-        <v>227.2700042724609</v>
+        <v>225.3999938964844</v>
       </c>
       <c r="C252" t="n">
-        <v>228.9799957275391</v>
+        <v>233.7599945068359</v>
       </c>
       <c r="D252" t="n">
-        <v>223.4299926757812</v>
+        <v>224.4299926757812</v>
       </c>
       <c r="E252" t="n">
-        <v>225.3099975585938</v>
+        <v>229.5700073242188</v>
       </c>
       <c r="F252" t="n">
-        <v>13506300</v>
+        <v>11228200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10654,37 +10654,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>229.57</v>
+      </c>
+      <c r="D2" t="n">
         <v>225.31</v>
       </c>
-      <c r="D2" t="n">
-        <v>227.27</v>
-      </c>
       <c r="E2" t="n">
-        <v>227.27</v>
+        <v>225.4</v>
       </c>
       <c r="F2" t="n">
-        <v>228.95</v>
+        <v>233.7299</v>
       </c>
       <c r="G2" t="n">
-        <v>223.5</v>
+        <v>224.4301</v>
       </c>
       <c r="H2" t="n">
-        <v>8572914</v>
+        <v>9706861</v>
       </c>
       <c r="I2" t="n">
         <v>13773033</v>
       </c>
       <c r="J2" t="n">
-        <v>185430130688</v>
+        <v>188936110080</v>
       </c>
       <c r="K2" t="n">
-        <v>20.842737</v>
+        <v>20.626236</v>
       </c>
       <c r="L2" t="n">
-        <v>14.075945</v>
+        <v>14.342083</v>
       </c>
       <c r="M2" t="n">
-        <v>10.81</v>
+        <v>11.13</v>
       </c>
       <c r="N2" t="n">
         <v>269.11</v>
@@ -10696,7 +10696,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10720,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.8316607</v>
+        <v>4.923014</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10732,7 +10732,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>216403132416</v>
+        <v>219909111808</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:07:35</t>
+          <t>2026-10-01 17:03:13</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B2" t="n">
-        <v>234.5010077854061</v>
+        <v>233.4498996394798</v>
       </c>
       <c r="C2" t="n">
-        <v>240.4307087963897</v>
+        <v>237.3865110117534</v>
       </c>
       <c r="D2" t="n">
-        <v>231.5460601627856</v>
+        <v>231.6353042398812</v>
       </c>
       <c r="E2" t="n">
-        <v>233.7077331542969</v>
+        <v>236.8708953857422</v>
       </c>
       <c r="F2" t="n">
-        <v>10016600</v>
+        <v>7679200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B3" t="n">
-        <v>233.4498996394798</v>
+        <v>236.7419803274875</v>
       </c>
       <c r="C3" t="n">
-        <v>237.3865110117534</v>
+        <v>240.7678310589901</v>
       </c>
       <c r="D3" t="n">
-        <v>231.6353042398812</v>
+        <v>236.4940829658881</v>
       </c>
       <c r="E3" t="n">
-        <v>236.8708953857422</v>
+        <v>238.3384399414062</v>
       </c>
       <c r="F3" t="n">
-        <v>7679200</v>
+        <v>8849800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B4" t="n">
-        <v>236.7419954840688</v>
+        <v>237.3171110157645</v>
       </c>
       <c r="C4" t="n">
-        <v>240.7678464733125</v>
+        <v>248.3634171689519</v>
       </c>
       <c r="D4" t="n">
-        <v>236.4940981065986</v>
+        <v>233.430082086989</v>
       </c>
       <c r="E4" t="n">
-        <v>238.3384552001953</v>
+        <v>243.7128601074219</v>
       </c>
       <c r="F4" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B5" t="n">
-        <v>237.3171110157645</v>
+        <v>244.406950940097</v>
       </c>
       <c r="C5" t="n">
-        <v>248.3634171689519</v>
+        <v>245.2795544533588</v>
       </c>
       <c r="D5" t="n">
-        <v>233.430082086989</v>
+        <v>235.5520648656193</v>
       </c>
       <c r="E5" t="n">
-        <v>243.7128601074219</v>
+        <v>237.7236480712891</v>
       </c>
       <c r="F5" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B6" t="n">
-        <v>244.4069666278678</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C6" t="n">
-        <v>245.2795701971395</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D6" t="n">
-        <v>235.5520799850208</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E6" t="n">
-        <v>237.7236633300781</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F6" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B7" t="n">
-        <v>237.7236681390551</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C7" t="n">
-        <v>239.290381338098</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D7" t="n">
-        <v>233.6680556537968</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E7" t="n">
-        <v>238.4078521728516</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F7" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B8" t="n">
-        <v>237.2576175505903</v>
+        <v>244.4466590259869</v>
       </c>
       <c r="C8" t="n">
-        <v>243.8913535488906</v>
+        <v>246.955379366002</v>
       </c>
       <c r="D8" t="n">
-        <v>235.1554375781523</v>
+        <v>238.695436635224</v>
       </c>
       <c r="E8" t="n">
-        <v>243.2666473388672</v>
+        <v>239.6473541259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="n">
-        <v>244.4466434616172</v>
+        <v>240.8471528439123</v>
       </c>
       <c r="C9" t="n">
-        <v>246.9553636418975</v>
+        <v>247.2528271339085</v>
       </c>
       <c r="D9" t="n">
-        <v>238.6954214370453</v>
+        <v>240.3315221106437</v>
       </c>
       <c r="E9" t="n">
-        <v>239.6473388671875</v>
+        <v>246.6578674316406</v>
       </c>
       <c r="F9" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B10" t="n">
-        <v>240.8471826425636</v>
+        <v>246.0232549541512</v>
       </c>
       <c r="C10" t="n">
-        <v>247.2528577250976</v>
+        <v>246.1918233421939</v>
       </c>
       <c r="D10" t="n">
-        <v>240.331551845499</v>
+        <v>237.5352518241517</v>
       </c>
       <c r="E10" t="n">
-        <v>246.6578979492188</v>
+        <v>237.7534027099609</v>
       </c>
       <c r="F10" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="n">
-        <v>246.0232549541512</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C11" t="n">
-        <v>246.1918233421939</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D11" t="n">
-        <v>237.5352518241517</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E11" t="n">
-        <v>237.7534027099609</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F11" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B12" t="n">
-        <v>238.8441526809671</v>
+        <v>251.0605458824941</v>
       </c>
       <c r="C12" t="n">
-        <v>239.2903800503502</v>
+        <v>254.5806764744798</v>
       </c>
       <c r="D12" t="n">
-        <v>233.915951765761</v>
+        <v>240.6290201908687</v>
       </c>
       <c r="E12" t="n">
-        <v>234.5902404785156</v>
+        <v>243.9310150146484</v>
       </c>
       <c r="F12" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B13" t="n">
-        <v>251.0605301777264</v>
+        <v>244.4962518623618</v>
       </c>
       <c r="C13" t="n">
-        <v>254.5806605495149</v>
+        <v>248.6708355528497</v>
       </c>
       <c r="D13" t="n">
-        <v>240.6290051386317</v>
+        <v>240.1233381500007</v>
       </c>
       <c r="E13" t="n">
-        <v>243.9309997558594</v>
+        <v>241.0355987548828</v>
       </c>
       <c r="F13" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B14" t="n">
-        <v>244.4962363844956</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C14" t="n">
-        <v>248.670819810711</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D14" t="n">
-        <v>240.1233229489625</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E14" t="n">
-        <v>241.0355834960938</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F14" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="n">
-        <v>242.9394234832453</v>
+        <v>252.359543952159</v>
       </c>
       <c r="C15" t="n">
-        <v>253.2519480605562</v>
+        <v>264.8833249829649</v>
       </c>
       <c r="D15" t="n">
-        <v>242.2453138708127</v>
+        <v>251.8637491703276</v>
       </c>
       <c r="E15" t="n">
-        <v>252.1413726806641</v>
+        <v>261.1946105957031</v>
       </c>
       <c r="F15" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B16" t="n">
-        <v>252.3595144668565</v>
+        <v>259.9947719140093</v>
       </c>
       <c r="C16" t="n">
-        <v>264.883294034403</v>
+        <v>260.1930716520554</v>
       </c>
       <c r="D16" t="n">
-        <v>251.863719742953</v>
+        <v>254.3526253920043</v>
       </c>
       <c r="E16" t="n">
-        <v>261.194580078125</v>
+        <v>254.4815368652344</v>
       </c>
       <c r="F16" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B17" t="n">
-        <v>259.9947875033736</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C17" t="n">
-        <v>260.1930872533099</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D17" t="n">
-        <v>254.3526406430638</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E17" t="n">
-        <v>254.4815521240234</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F17" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B18" t="n">
-        <v>255.4334634999039</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C18" t="n">
-        <v>256.3853809552256</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D18" t="n">
-        <v>251.982721115611</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E18" t="n">
-        <v>252.9049072265625</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F18" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B19" t="n">
-        <v>255.254980605377</v>
+        <v>254.917794537107</v>
       </c>
       <c r="C19" t="n">
-        <v>256.3258839430272</v>
+        <v>255.9292351115289</v>
       </c>
       <c r="D19" t="n">
-        <v>251.8637312244832</v>
+        <v>252.7759728910826</v>
       </c>
       <c r="E19" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213500976562</v>
       </c>
       <c r="F19" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B20" t="n">
-        <v>254.9178098920577</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="C20" t="n">
-        <v>255.9292505274036</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D20" t="n">
-        <v>252.7759881170209</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E20" t="n">
-        <v>253.3213653564453</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="F20" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B21" t="n">
-        <v>253.3213815169481</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C21" t="n">
-        <v>256.6630334318976</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D21" t="n">
-        <v>252.0025656103722</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E21" t="n">
-        <v>252.1215515136719</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F21" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B22" t="n">
-        <v>249.8805444255208</v>
+        <v>248.3931555366784</v>
       </c>
       <c r="C22" t="n">
-        <v>251.4373471434884</v>
+        <v>257.0993096380665</v>
       </c>
       <c r="D22" t="n">
-        <v>246.945432960583</v>
+        <v>247.8973608150483</v>
       </c>
       <c r="E22" t="n">
-        <v>249.3450927734375</v>
+        <v>254.4914245605469</v>
       </c>
       <c r="F22" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="n">
-        <v>248.3931704298276</v>
+        <v>252.657000570364</v>
       </c>
       <c r="C23" t="n">
-        <v>257.099325053219</v>
+        <v>259.6179629024988</v>
       </c>
       <c r="D23" t="n">
-        <v>247.8973756784706</v>
+        <v>250.5052532311086</v>
       </c>
       <c r="E23" t="n">
-        <v>254.4914398193359</v>
+        <v>258.2198181152344</v>
       </c>
       <c r="F23" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B24" t="n">
-        <v>252.657000570364</v>
+        <v>257.8132719821094</v>
       </c>
       <c r="C24" t="n">
-        <v>259.6179629024988</v>
+        <v>259.3601491931292</v>
       </c>
       <c r="D24" t="n">
-        <v>250.5052532311086</v>
+        <v>252.9544894469363</v>
       </c>
       <c r="E24" t="n">
-        <v>258.2198181152344</v>
+        <v>259.1419982910156</v>
       </c>
       <c r="F24" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B25" t="n">
-        <v>257.8133023432115</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C25" t="n">
-        <v>259.3601797363976</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D25" t="n">
-        <v>252.9545192358491</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E25" t="n">
-        <v>259.1420288085938</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F25" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B26" t="n">
-        <v>255.9788221233241</v>
+        <v>252.5578398334985</v>
       </c>
       <c r="C26" t="n">
-        <v>257.0795021986246</v>
+        <v>254.6699151564536</v>
       </c>
       <c r="D26" t="n">
-        <v>251.3282801006067</v>
+        <v>249.8904616870965</v>
       </c>
       <c r="E26" t="n">
-        <v>252.3000335693359</v>
+        <v>250.5548248291016</v>
       </c>
       <c r="F26" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B27" t="n">
-        <v>252.5578552142711</v>
+        <v>248.4328324243326</v>
       </c>
       <c r="C27" t="n">
-        <v>254.6699306658516</v>
+        <v>248.4328324243326</v>
       </c>
       <c r="D27" t="n">
-        <v>249.8904769054258</v>
+        <v>232.5079071065105</v>
       </c>
       <c r="E27" t="n">
-        <v>250.5548400878906</v>
+        <v>237.2576293945312</v>
       </c>
       <c r="F27" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B28" t="n">
-        <v>248.4328324243326</v>
+        <v>234.1638631836621</v>
       </c>
       <c r="C28" t="n">
-        <v>248.4328324243326</v>
+        <v>238.9433320161168</v>
       </c>
       <c r="D28" t="n">
-        <v>232.5079071065105</v>
+        <v>233.8068903450121</v>
       </c>
       <c r="E28" t="n">
-        <v>237.2576293945312</v>
+        <v>237.8625030517578</v>
       </c>
       <c r="F28" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="n">
-        <v>234.1638481621394</v>
+        <v>237.9814840335094</v>
       </c>
       <c r="C29" t="n">
-        <v>238.943316687993</v>
+        <v>239.8754236419186</v>
       </c>
       <c r="D29" t="n">
-        <v>233.8068753463891</v>
+        <v>233.1028654264771</v>
       </c>
       <c r="E29" t="n">
-        <v>237.8624877929688</v>
+        <v>239.6771087646484</v>
       </c>
       <c r="F29" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="n">
-        <v>237.9814840335094</v>
+        <v>239.865480170848</v>
       </c>
       <c r="C30" t="n">
-        <v>239.8754236419186</v>
+        <v>243.6335230797314</v>
       </c>
       <c r="D30" t="n">
-        <v>233.1028654264771</v>
+        <v>239.131713666637</v>
       </c>
       <c r="E30" t="n">
-        <v>239.6771087646484</v>
+        <v>242.4436187744141</v>
       </c>
       <c r="F30" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B31" t="n">
-        <v>239.8654952673756</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="C31" t="n">
-        <v>243.63353841341</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D31" t="n">
-        <v>239.1317287169831</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E31" t="n">
-        <v>242.4436340332031</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="F31" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B32" t="n">
-        <v>243.6732075926712</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C32" t="n">
-        <v>246.3405706207466</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D32" t="n">
-        <v>241.63052052637</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E32" t="n">
-        <v>243.9508514404297</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F32" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="n">
-        <v>243.1873207442872</v>
+        <v>236.3056926086296</v>
       </c>
       <c r="C33" t="n">
-        <v>243.8318478561575</v>
+        <v>243.1179076689137</v>
       </c>
       <c r="D33" t="n">
-        <v>237.8922365355373</v>
+        <v>235.4231785540507</v>
       </c>
       <c r="E33" t="n">
-        <v>238.4078521728516</v>
+        <v>241.6107025146484</v>
       </c>
       <c r="F33" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B34" t="n">
-        <v>236.3056926086296</v>
+        <v>240.0340726996036</v>
       </c>
       <c r="C34" t="n">
-        <v>243.1179076689137</v>
+        <v>240.787675257482</v>
       </c>
       <c r="D34" t="n">
-        <v>235.4231785540507</v>
+        <v>233.6085619749179</v>
       </c>
       <c r="E34" t="n">
-        <v>241.6107025146484</v>
+        <v>235.0364532470703</v>
       </c>
       <c r="F34" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B35" t="n">
-        <v>240.0340571163644</v>
+        <v>234.2531087461558</v>
       </c>
       <c r="C35" t="n">
-        <v>240.7876596253181</v>
+        <v>235.7900603656055</v>
       </c>
       <c r="D35" t="n">
-        <v>233.6085468088289</v>
+        <v>228.3333182252886</v>
       </c>
       <c r="E35" t="n">
-        <v>235.0364379882812</v>
+        <v>231.5361480712891</v>
       </c>
       <c r="F35" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B36" t="n">
-        <v>234.2530933083125</v>
+        <v>230.0487531290293</v>
       </c>
       <c r="C36" t="n">
-        <v>235.7900448264734</v>
+        <v>230.3263969654728</v>
       </c>
       <c r="D36" t="n">
-        <v>228.3333031775737</v>
+        <v>223.1671199033486</v>
       </c>
       <c r="E36" t="n">
-        <v>231.5361328125</v>
+        <v>225.9634094238281</v>
       </c>
       <c r="F36" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B37" t="n">
-        <v>230.0487531290293</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C37" t="n">
-        <v>230.3263969654728</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D37" t="n">
-        <v>223.1671199033486</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E37" t="n">
-        <v>225.9634094238281</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F37" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B38" t="n">
-        <v>227.3218898732066</v>
+        <v>222.9688137796853</v>
       </c>
       <c r="C38" t="n">
-        <v>229.1265900019938</v>
+        <v>226.7566777713456</v>
       </c>
       <c r="D38" t="n">
-        <v>221.4219354522067</v>
+        <v>220.0932103050241</v>
       </c>
       <c r="E38" t="n">
-        <v>223.4745178222656</v>
+        <v>225.1998901367188</v>
       </c>
       <c r="F38" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B39" t="n">
-        <v>222.9688137796853</v>
+        <v>225.4279386105234</v>
       </c>
       <c r="C39" t="n">
-        <v>226.7566777713456</v>
+        <v>226.9153227636102</v>
       </c>
       <c r="D39" t="n">
-        <v>220.0932103050241</v>
+        <v>223.1472798830329</v>
       </c>
       <c r="E39" t="n">
-        <v>225.1998901367188</v>
+        <v>224.9123229980469</v>
       </c>
       <c r="F39" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B40" t="n">
-        <v>225.4279691980636</v>
+        <v>224.8924827605518</v>
       </c>
       <c r="C40" t="n">
-        <v>226.9153535529684</v>
+        <v>232.656629709896</v>
       </c>
       <c r="D40" t="n">
-        <v>223.1473101611184</v>
+        <v>224.6148389342789</v>
       </c>
       <c r="E40" t="n">
-        <v>224.912353515625</v>
+        <v>232.1509094238281</v>
       </c>
       <c r="F40" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B41" t="n">
-        <v>224.8924975422598</v>
+        <v>228.5712765635558</v>
       </c>
       <c r="C41" t="n">
-        <v>232.656645001925</v>
+        <v>230.8618608815026</v>
       </c>
       <c r="D41" t="n">
-        <v>224.614853697738</v>
+        <v>224.0992136322821</v>
       </c>
       <c r="E41" t="n">
-        <v>232.1509246826172</v>
+        <v>226.2311248779297</v>
       </c>
       <c r="F41" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B42" t="n">
-        <v>228.5712919801828</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C42" t="n">
-        <v>230.8618764526245</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D42" t="n">
-        <v>224.0992287472785</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E42" t="n">
-        <v>226.2311401367188</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F42" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B43" t="n">
-        <v>227.0739873247604</v>
+        <v>226.7467495421078</v>
       </c>
       <c r="C43" t="n">
-        <v>230.6040433967966</v>
+        <v>232.2798202893068</v>
       </c>
       <c r="D43" t="n">
-        <v>226.7071040647147</v>
+        <v>226.6773461509458</v>
       </c>
       <c r="E43" t="n">
-        <v>228.6010284423828</v>
+        <v>230.8717651367188</v>
       </c>
       <c r="F43" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B44" t="n">
-        <v>226.7467645282661</v>
+        <v>231.060173355472</v>
       </c>
       <c r="C44" t="n">
-        <v>232.2798356411572</v>
+        <v>234.6596326998496</v>
       </c>
       <c r="D44" t="n">
-        <v>226.6773611325171</v>
+        <v>229.6719390743564</v>
       </c>
       <c r="E44" t="n">
-        <v>230.8717803955078</v>
+        <v>232.7359619140625</v>
       </c>
       <c r="F44" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B45" t="n">
-        <v>231.0601885043919</v>
+        <v>233.3804933429116</v>
       </c>
       <c r="C45" t="n">
-        <v>234.6596480847597</v>
+        <v>237.2476861421788</v>
       </c>
       <c r="D45" t="n">
-        <v>229.67195413226</v>
+        <v>231.1989995810056</v>
       </c>
       <c r="E45" t="n">
-        <v>232.7359771728516</v>
+        <v>236.7122344970703</v>
       </c>
       <c r="F45" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B46" t="n">
-        <v>233.3805083869321</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C46" t="n">
-        <v>237.2477014354837</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D46" t="n">
-        <v>231.1990144844042</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E46" t="n">
-        <v>236.7122497558594</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F46" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B47" t="n">
-        <v>241.6404418420451</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C47" t="n">
-        <v>246.8760330652079</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D47" t="n">
-        <v>235.6016655641461</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E47" t="n">
-        <v>245.3787384033203</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F47" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B48" t="n">
-        <v>248.7203919866921</v>
+        <v>259.6774396530913</v>
       </c>
       <c r="C48" t="n">
-        <v>259.6774588065476</v>
+        <v>262.0572481860146</v>
       </c>
       <c r="D48" t="n">
-        <v>247.4015761578514</v>
+        <v>254.1840258460871</v>
       </c>
       <c r="E48" t="n">
-        <v>258.3784790039062</v>
+        <v>257.3471984863281</v>
       </c>
       <c r="F48" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B49" t="n">
-        <v>259.6774704470017</v>
+        <v>257.8132661327708</v>
       </c>
       <c r="C49" t="n">
-        <v>262.0572792621351</v>
+        <v>260.0443424743044</v>
       </c>
       <c r="D49" t="n">
-        <v>254.1840559885597</v>
+        <v>256.8216766476447</v>
       </c>
       <c r="E49" t="n">
-        <v>257.3472290039062</v>
+        <v>258.8246765136719</v>
       </c>
       <c r="F49" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B50" t="n">
-        <v>257.8132661327708</v>
+        <v>258.5569100826516</v>
       </c>
       <c r="C50" t="n">
-        <v>260.0443424743044</v>
+        <v>263.6933353961732</v>
       </c>
       <c r="D50" t="n">
-        <v>256.8216766476447</v>
+        <v>256.9703611498102</v>
       </c>
       <c r="E50" t="n">
-        <v>258.8246765136719</v>
+        <v>261.9779052734375</v>
       </c>
       <c r="F50" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B51" t="n">
-        <v>258.556940201721</v>
+        <v>261.2838154474661</v>
       </c>
       <c r="C51" t="n">
-        <v>263.6933661135803</v>
+        <v>265.6468028980126</v>
       </c>
       <c r="D51" t="n">
-        <v>256.9703910840639</v>
+        <v>258.5767654029829</v>
       </c>
       <c r="E51" t="n">
-        <v>261.9779357910156</v>
+        <v>260.1434936523438</v>
       </c>
       <c r="F51" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B52" t="n">
-        <v>261.283846098816</v>
+        <v>261.3036341846645</v>
       </c>
       <c r="C52" t="n">
-        <v>265.646834061187</v>
+        <v>262.2654771366241</v>
       </c>
       <c r="D52" t="n">
-        <v>258.5767957367673</v>
+        <v>258.7156003126054</v>
       </c>
       <c r="E52" t="n">
-        <v>260.1435241699219</v>
+        <v>260.0245056152344</v>
       </c>
       <c r="F52" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B53" t="n">
-        <v>261.3036648523665</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C53" t="n">
-        <v>262.2655079172122</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D53" t="n">
-        <v>258.7156306765648</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E53" t="n">
-        <v>260.0245361328125</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F53" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B54" t="n">
-        <v>259.013086162544</v>
+        <v>251.8637174841621</v>
       </c>
       <c r="C54" t="n">
-        <v>260.074094195654</v>
+        <v>253.7080744457603</v>
       </c>
       <c r="D54" t="n">
-        <v>250.9613842226157</v>
+        <v>249.9896140498327</v>
       </c>
       <c r="E54" t="n">
-        <v>252.4388580322266</v>
+        <v>252.7660675048828</v>
       </c>
       <c r="F54" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B55" t="n">
-        <v>251.8637174841621</v>
+        <v>254.1741282350202</v>
       </c>
       <c r="C55" t="n">
-        <v>253.7080744457603</v>
+        <v>259.7667076505979</v>
       </c>
       <c r="D55" t="n">
-        <v>249.9896140498327</v>
+        <v>254.0948143882558</v>
       </c>
       <c r="E55" t="n">
-        <v>252.7660675048828</v>
+        <v>255.9689331054688</v>
       </c>
       <c r="F55" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B56" t="n">
-        <v>254.1741130832229</v>
+        <v>256.6602113519941</v>
       </c>
       <c r="C56" t="n">
-        <v>259.7666921654164</v>
+        <v>258.298969034048</v>
       </c>
       <c r="D56" t="n">
-        <v>254.0947992411865</v>
+        <v>254.415591918658</v>
       </c>
       <c r="E56" t="n">
-        <v>255.9689178466797</v>
+        <v>256.0940856933594</v>
       </c>
       <c r="F56" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B57" t="n">
-        <v>256.6601807669533</v>
+        <v>258.904790639318</v>
       </c>
       <c r="C57" t="n">
-        <v>258.2989382537239</v>
+        <v>260.2555449501942</v>
       </c>
       <c r="D57" t="n">
-        <v>254.4155616010984</v>
+        <v>253.7600731430874</v>
       </c>
       <c r="E57" t="n">
-        <v>256.0940551757812</v>
+        <v>258.1400451660156</v>
       </c>
       <c r="F57" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G57" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B58" t="n">
-        <v>258.9047600313309</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="C58" t="n">
-        <v>260.2555141825196</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D58" t="n">
-        <v>253.760043143314</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E58" t="n">
-        <v>258.1400146484375</v>
+        <v>262.827880859375</v>
       </c>
       <c r="F58" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B59" t="n">
-        <v>258.8452092197766</v>
+        <v>260.930890915143</v>
       </c>
       <c r="C59" t="n">
-        <v>262.8279113769531</v>
+        <v>262.4405288782817</v>
       </c>
       <c r="D59" t="n">
-        <v>256.6502674989528</v>
+        <v>258.7458606831942</v>
       </c>
       <c r="E59" t="n">
-        <v>262.8279113769531</v>
+        <v>261.6360473632812</v>
       </c>
       <c r="F59" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B60" t="n">
-        <v>260.9308604798152</v>
+        <v>261.4374083245464</v>
       </c>
       <c r="C60" t="n">
-        <v>262.4404982668678</v>
+        <v>264.4864785158107</v>
       </c>
       <c r="D60" t="n">
-        <v>258.7458305027313</v>
+        <v>260.7620161053754</v>
       </c>
       <c r="E60" t="n">
-        <v>261.6360168457031</v>
+        <v>263.4535827636719</v>
       </c>
       <c r="F60" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B61" t="n">
-        <v>261.4374083245464</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="C61" t="n">
-        <v>264.4864785158107</v>
+        <v>266.0855294787636</v>
       </c>
       <c r="D61" t="n">
-        <v>260.7620161053754</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="E61" t="n">
-        <v>263.4535827636719</v>
+        <v>264.2679748535156</v>
       </c>
       <c r="F61" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B62" t="n">
-        <v>262.9967232703997</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C62" t="n">
-        <v>266.0855602062323</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D62" t="n">
-        <v>262.9967232703997</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E62" t="n">
-        <v>264.2680053710938</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F62" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B63" t="n">
-        <v>262.9073239460033</v>
+        <v>264.8440818513142</v>
       </c>
       <c r="C63" t="n">
-        <v>267.2773540092613</v>
+        <v>266.453045001104</v>
       </c>
       <c r="D63" t="n">
-        <v>262.9073239460033</v>
+        <v>263.5231220141856</v>
       </c>
       <c r="E63" t="n">
-        <v>264.4169921875</v>
+        <v>264.109130859375</v>
       </c>
       <c r="F63" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B64" t="n">
-        <v>264.8440818513142</v>
+        <v>263.4833740671746</v>
       </c>
       <c r="C64" t="n">
-        <v>266.453045001104</v>
+        <v>264.2878555133287</v>
       </c>
       <c r="D64" t="n">
-        <v>263.5231220141856</v>
+        <v>262.5895091614203</v>
       </c>
       <c r="E64" t="n">
-        <v>264.109130859375</v>
+        <v>263.10595703125</v>
       </c>
       <c r="F64" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B65" t="n">
-        <v>263.4834046285292</v>
+        <v>263.1953762174182</v>
       </c>
       <c r="C65" t="n">
-        <v>264.2878861679949</v>
+        <v>263.572793304574</v>
       </c>
       <c r="D65" t="n">
-        <v>262.5895396190958</v>
+        <v>250.760631935403</v>
       </c>
       <c r="E65" t="n">
-        <v>263.1059875488281</v>
+        <v>251.8928680419922</v>
       </c>
       <c r="F65" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B66" t="n">
-        <v>263.1953762174182</v>
+        <v>251.8928411889898</v>
       </c>
       <c r="C66" t="n">
-        <v>263.572793304574</v>
+        <v>257.8221866599169</v>
       </c>
       <c r="D66" t="n">
-        <v>250.760631935403</v>
+        <v>250.5917647228683</v>
       </c>
       <c r="E66" t="n">
-        <v>251.8928680419922</v>
+        <v>254.5148773193359</v>
       </c>
       <c r="F66" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B67" t="n">
-        <v>251.8928562905814</v>
+        <v>253.4621191746895</v>
       </c>
       <c r="C67" t="n">
-        <v>257.8222021169872</v>
+        <v>261.7552477009523</v>
       </c>
       <c r="D67" t="n">
-        <v>250.5917797464572</v>
+        <v>253.2634841788583</v>
       </c>
       <c r="E67" t="n">
-        <v>254.514892578125</v>
+        <v>261.1096801757812</v>
       </c>
       <c r="F67" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B68" t="n">
-        <v>253.4620895509313</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="C68" t="n">
-        <v>261.7552171079225</v>
+        <v>266.0060550943219</v>
       </c>
       <c r="D68" t="n">
-        <v>253.2634545783159</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="E68" t="n">
-        <v>261.1096496582031</v>
+        <v>264.3077087402344</v>
       </c>
       <c r="F68" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B69" t="n">
-        <v>261.7055558804709</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C69" t="n">
-        <v>266.0060550943219</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D69" t="n">
-        <v>261.7055558804709</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E69" t="n">
-        <v>264.3077087402344</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F69" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B70" t="n">
-        <v>262.5994389217771</v>
+        <v>258.2294193019395</v>
       </c>
       <c r="C70" t="n">
-        <v>263.394009134812</v>
+        <v>259.2524038660146</v>
       </c>
       <c r="D70" t="n">
-        <v>258.6366203853271</v>
+        <v>254.7631956419699</v>
       </c>
       <c r="E70" t="n">
-        <v>258.7557983398438</v>
+        <v>258.1698303222656</v>
       </c>
       <c r="F70" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B71" t="n">
-        <v>258.2294193019395</v>
+        <v>257.2362139425806</v>
       </c>
       <c r="C71" t="n">
-        <v>259.2524038660146</v>
+        <v>259.7787779567694</v>
       </c>
       <c r="D71" t="n">
-        <v>254.7631956419699</v>
+        <v>254.028214436778</v>
       </c>
       <c r="E71" t="n">
-        <v>258.1698303222656</v>
+        <v>257.6334838867188</v>
       </c>
       <c r="F71" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B72" t="n">
-        <v>257.2362139425806</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C72" t="n">
-        <v>259.7787779567694</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D72" t="n">
-        <v>254.028214436778</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E72" t="n">
-        <v>257.6334838867188</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F72" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B73" t="n">
-        <v>255.9053572301452</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C73" t="n">
-        <v>259.1332249596227</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D73" t="n">
-        <v>238.7231659776434</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E73" t="n">
-        <v>239.4183959960938</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F73" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B74" t="n">
-        <v>237.5511941796288</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C74" t="n">
-        <v>240.5903685304685</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D74" t="n">
-        <v>234.849731125901</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E74" t="n">
-        <v>237.9385528564453</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F74" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B75" t="n">
-        <v>235.4059054123066</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C75" t="n">
-        <v>237.2135033883542</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D75" t="n">
-        <v>230.0923326840245</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E75" t="n">
-        <v>231.9396667480469</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F75" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B76" t="n">
-        <v>231.3636110626874</v>
+        <v>222.0177057630064</v>
       </c>
       <c r="C76" t="n">
-        <v>231.3636110626874</v>
+        <v>226.3877512462753</v>
       </c>
       <c r="D76" t="n">
-        <v>224.8979495180149</v>
+        <v>217.8661784665229</v>
       </c>
       <c r="E76" t="n">
-        <v>225.5633850097656</v>
+        <v>218.5713500976562</v>
       </c>
       <c r="F76" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B77" t="n">
-        <v>222.0177057630064</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="C77" t="n">
-        <v>226.3877512462753</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D77" t="n">
-        <v>217.8661784665229</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E77" t="n">
-        <v>218.5713500976562</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="F77" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B78" t="n">
-        <v>218.6507753226022</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C78" t="n">
-        <v>221.8687164208105</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D78" t="n">
-        <v>217.4688919371066</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E78" t="n">
-        <v>220.071044921875</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F78" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B79" t="n">
-        <v>220.7265600038705</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="C79" t="n">
-        <v>227.162427221411</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D79" t="n">
-        <v>219.6042504088122</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E79" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="F79" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B80" t="n">
-        <v>225.2356232374019</v>
+        <v>227.8675935623777</v>
       </c>
       <c r="C80" t="n">
-        <v>229.277913744438</v>
+        <v>229.3772467325265</v>
       </c>
       <c r="D80" t="n">
-        <v>225.1065036899912</v>
+        <v>226.0401274460743</v>
       </c>
       <c r="E80" t="n">
-        <v>226.4969787597656</v>
+        <v>227.8377990722656</v>
       </c>
       <c r="F80" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B81" t="n">
-        <v>227.8675783015932</v>
+        <v>230.3604906379282</v>
       </c>
       <c r="C81" t="n">
-        <v>229.3772313706373</v>
+        <v>234.1346156625655</v>
       </c>
       <c r="D81" t="n">
-        <v>226.0401123076792</v>
+        <v>224.7291051659704</v>
       </c>
       <c r="E81" t="n">
-        <v>227.8377838134766</v>
+        <v>226.9737091064453</v>
       </c>
       <c r="F81" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B82" t="n">
-        <v>230.3604906379282</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="C82" t="n">
-        <v>234.1346156625655</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D82" t="n">
-        <v>224.7291051659704</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E82" t="n">
-        <v>226.9737091064453</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="F82" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B83" t="n">
-        <v>227.8278778686248</v>
+        <v>215.1944745404488</v>
       </c>
       <c r="C83" t="n">
-        <v>230.2810586434755</v>
+        <v>215.8003210439947</v>
       </c>
       <c r="D83" t="n">
-        <v>226.1195896734686</v>
+        <v>207.358206080909</v>
       </c>
       <c r="E83" t="n">
-        <v>226.4076232910156</v>
+        <v>212.6221160888672</v>
       </c>
       <c r="F83" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B84" t="n">
-        <v>215.1944745404488</v>
+        <v>212.7015749295142</v>
       </c>
       <c r="C84" t="n">
-        <v>215.8003210439947</v>
+        <v>214.0821084291109</v>
       </c>
       <c r="D84" t="n">
-        <v>207.358206080909</v>
+        <v>209.5928853669118</v>
       </c>
       <c r="E84" t="n">
-        <v>212.6221160888672</v>
+        <v>210.8442993164062</v>
       </c>
       <c r="F84" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B85" t="n">
-        <v>212.7015903227142</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C85" t="n">
-        <v>214.08212392222</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D85" t="n">
-        <v>209.5929005351361</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E85" t="n">
-        <v>210.8443145751953</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F85" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B86" t="n">
-        <v>212.8902908724165</v>
+        <v>203.6039568110546</v>
       </c>
       <c r="C86" t="n">
-        <v>215.4129869027477</v>
+        <v>204.16014080488</v>
       </c>
       <c r="D86" t="n">
-        <v>208.3712731650351</v>
+        <v>191.7949279222085</v>
       </c>
       <c r="E86" t="n">
-        <v>209.3743896484375</v>
+        <v>195.0426635742188</v>
       </c>
       <c r="F86" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B87" t="n">
-        <v>203.60397273962</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C87" t="n">
-        <v>204.1601567769575</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D87" t="n">
-        <v>191.7949429269172</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E87" t="n">
-        <v>195.0426788330078</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F87" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B88" t="n">
-        <v>191.993558028148</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C88" t="n">
-        <v>199.3034370934686</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D88" t="n">
-        <v>186.0046234920971</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E88" t="n">
-        <v>198.0818176269531</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F88" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B89" t="n">
-        <v>192.668943558262</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C89" t="n">
-        <v>198.2010042649258</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D89" t="n">
-        <v>187.5043431662378</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E89" t="n">
-        <v>188.6763153076172</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F89" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="n">
-        <v>190.3250127759971</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C90" t="n">
-        <v>193.2747884158856</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D90" t="n">
-        <v>185.8457159832669</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E90" t="n">
-        <v>190.0469207763672</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F90" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B91" t="n">
-        <v>188.0108792533576</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C91" t="n">
-        <v>193.8706944788449</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D91" t="n">
-        <v>184.465183505092</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E91" t="n">
-        <v>192.7086639404297</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F91" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="n">
-        <v>190.5931665112882</v>
+        <v>191.8346349441069</v>
       </c>
       <c r="C92" t="n">
-        <v>197.7441470694129</v>
+        <v>192.3510979672969</v>
       </c>
       <c r="D92" t="n">
-        <v>189.4510040038842</v>
+        <v>180.5718644212529</v>
       </c>
       <c r="E92" t="n">
-        <v>192.1326141357422</v>
+        <v>183.7401428222656</v>
       </c>
       <c r="F92" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B93" t="n">
-        <v>191.8346349441069</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C93" t="n">
-        <v>192.3510979672969</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D93" t="n">
-        <v>180.5718644212529</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E93" t="n">
-        <v>183.7401428222656</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F93" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B94" t="n">
-        <v>184.6936257308121</v>
+        <v>185.1703470279448</v>
       </c>
       <c r="C94" t="n">
-        <v>187.0375548215625</v>
+        <v>192.1326035099074</v>
       </c>
       <c r="D94" t="n">
-        <v>179.012577513483</v>
+        <v>183.0449210226253</v>
       </c>
       <c r="E94" t="n">
-        <v>184.1672210693359</v>
+        <v>188.4280090332031</v>
       </c>
       <c r="F94" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="n">
-        <v>185.1703620229303</v>
+        <v>189.6695058452945</v>
       </c>
       <c r="C95" t="n">
-        <v>192.1326190686923</v>
+        <v>191.6856804427425</v>
       </c>
       <c r="D95" t="n">
-        <v>183.0449358454951</v>
+        <v>181.9226203922807</v>
       </c>
       <c r="E95" t="n">
-        <v>188.4280242919922</v>
+        <v>183.0349884033203</v>
       </c>
       <c r="F95" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="n">
-        <v>189.6695058452945</v>
+        <v>182.6277925688313</v>
       </c>
       <c r="C96" t="n">
-        <v>191.6856804427425</v>
+        <v>186.8587767567783</v>
       </c>
       <c r="D96" t="n">
-        <v>181.9226203922807</v>
+        <v>180.6215444099069</v>
       </c>
       <c r="E96" t="n">
-        <v>183.0349884033203</v>
+        <v>186.5111541748047</v>
       </c>
       <c r="F96" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B97" t="n">
-        <v>182.6277925688313</v>
+        <v>185.3292747163753</v>
       </c>
       <c r="C97" t="n">
-        <v>186.8587767567783</v>
+        <v>185.6768821509354</v>
       </c>
       <c r="D97" t="n">
-        <v>180.6215444099069</v>
+        <v>181.9822138463991</v>
       </c>
       <c r="E97" t="n">
-        <v>186.5111541748047</v>
+        <v>184.0281829833984</v>
       </c>
       <c r="F97" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B98" t="n">
-        <v>185.3292747163753</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C98" t="n">
-        <v>185.6768821509354</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D98" t="n">
-        <v>181.9822138463991</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E98" t="n">
-        <v>184.0281829833984</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F98" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="n">
-        <v>184.0579771467211</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C99" t="n">
-        <v>190.4243134969296</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D99" t="n">
-        <v>182.4787935369736</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E99" t="n">
-        <v>183.8990631103516</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F99" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B100" t="n">
-        <v>180.0355685556146</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C100" t="n">
-        <v>181.2273936107796</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D100" t="n">
-        <v>173.3811981056387</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E100" t="n">
-        <v>176.9467468261719</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F100" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B101" t="n">
-        <v>176.4302852446972</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C101" t="n">
-        <v>187.3851706171715</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D101" t="n">
-        <v>175.0795461293982</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E101" t="n">
-        <v>184.1573028564453</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F101" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B102" t="n">
-        <v>181.7537853733346</v>
+        <v>195.4200513200664</v>
       </c>
       <c r="C102" t="n">
-        <v>191.2884162417558</v>
+        <v>199.6709031418322</v>
       </c>
       <c r="D102" t="n">
-        <v>181.0188192554131</v>
+        <v>190.0270371048119</v>
       </c>
       <c r="E102" t="n">
-        <v>190.4441986083984</v>
+        <v>198.1116027832031</v>
       </c>
       <c r="F102" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B103" t="n">
-        <v>195.420066371549</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C103" t="n">
-        <v>199.6709185207204</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D103" t="n">
-        <v>190.0270517409182</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E103" t="n">
-        <v>198.1116180419922</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F103" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B104" t="n">
-        <v>190.6031086414411</v>
+        <v>191.1890843548102</v>
       </c>
       <c r="C104" t="n">
-        <v>194.5857953386064</v>
+        <v>194.6056605467623</v>
       </c>
       <c r="D104" t="n">
-        <v>188.6266549601705</v>
+        <v>189.3814711920236</v>
       </c>
       <c r="E104" t="n">
-        <v>193.4634857177734</v>
+        <v>191.6360168457031</v>
       </c>
       <c r="F104" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B105" t="n">
-        <v>191.1890843548102</v>
+        <v>189.4509946932415</v>
       </c>
       <c r="C105" t="n">
-        <v>194.6056605467623</v>
+        <v>197.3170577657204</v>
       </c>
       <c r="D105" t="n">
-        <v>189.3814711920236</v>
+        <v>188.2889641983741</v>
       </c>
       <c r="E105" t="n">
-        <v>191.6360168457031</v>
+        <v>194.7149047851562</v>
       </c>
       <c r="F105" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B106" t="n">
-        <v>189.4509946932415</v>
+        <v>193.771369445172</v>
       </c>
       <c r="C106" t="n">
-        <v>197.3170577657204</v>
+        <v>195.1320348561704</v>
       </c>
       <c r="D106" t="n">
-        <v>188.2889641983741</v>
+        <v>190.7917995315397</v>
       </c>
       <c r="E106" t="n">
-        <v>194.7149047851562</v>
+        <v>191.7651214599609</v>
       </c>
       <c r="F106" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B107" t="n">
-        <v>193.7713848635987</v>
+        <v>193.036414733929</v>
       </c>
       <c r="C107" t="n">
-        <v>195.1320503828654</v>
+        <v>203.027904005614</v>
       </c>
       <c r="D107" t="n">
-        <v>190.7918147128814</v>
+        <v>192.9172367799533</v>
       </c>
       <c r="E107" t="n">
-        <v>191.76513671875</v>
+        <v>200.0185394287109</v>
       </c>
       <c r="F107" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B108" t="n">
-        <v>193.036414733929</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C108" t="n">
-        <v>203.027904005614</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D108" t="n">
-        <v>192.9172367799533</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E108" t="n">
-        <v>200.0185394287109</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F108" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B109" t="n">
-        <v>199.4226244314719</v>
+        <v>197.2078040637707</v>
       </c>
       <c r="C109" t="n">
-        <v>201.5778601866405</v>
+        <v>202.2830055722447</v>
       </c>
       <c r="D109" t="n">
-        <v>196.0259162627038</v>
+        <v>194.5361205377908</v>
       </c>
       <c r="E109" t="n">
-        <v>200.733642578125</v>
+        <v>197.4362335205078</v>
       </c>
       <c r="F109" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B110" t="n">
-        <v>197.2078040637707</v>
+        <v>195.9166750362765</v>
       </c>
       <c r="C110" t="n">
-        <v>202.2830055722447</v>
+        <v>198.2109569133711</v>
       </c>
       <c r="D110" t="n">
-        <v>194.5361205377908</v>
+        <v>189.3020404418633</v>
       </c>
       <c r="E110" t="n">
-        <v>197.4362335205078</v>
+        <v>193.5826873779297</v>
       </c>
       <c r="F110" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B111" t="n">
-        <v>195.9166750362765</v>
+        <v>195.0625138319317</v>
       </c>
       <c r="C111" t="n">
-        <v>198.2109569133711</v>
+        <v>198.1910714873107</v>
       </c>
       <c r="D111" t="n">
-        <v>189.3020404418633</v>
+        <v>189.9873122244243</v>
       </c>
       <c r="E111" t="n">
-        <v>193.5826873779297</v>
+        <v>192.8079833984375</v>
       </c>
       <c r="F111" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B112" t="n">
-        <v>195.0625138319317</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C112" t="n">
-        <v>198.1910714873107</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D112" t="n">
-        <v>189.9873122244243</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E112" t="n">
-        <v>192.8079833984375</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F112" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B113" t="n">
-        <v>192.8079750209554</v>
+        <v>198.3698354155112</v>
       </c>
       <c r="C113" t="n">
-        <v>203.4648992272838</v>
+        <v>199.6311909649738</v>
       </c>
       <c r="D113" t="n">
-        <v>191.8346379323055</v>
+        <v>190.4441834205658</v>
       </c>
       <c r="E113" t="n">
-        <v>197.9228973388672</v>
+        <v>191.5168304443359</v>
       </c>
       <c r="F113" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B114" t="n">
-        <v>198.3698354155112</v>
+        <v>193.8210400352253</v>
       </c>
       <c r="C114" t="n">
-        <v>199.6311909649738</v>
+        <v>197.277352460538</v>
       </c>
       <c r="D114" t="n">
-        <v>190.4441834205658</v>
+        <v>193.8210400352253</v>
       </c>
       <c r="E114" t="n">
-        <v>191.5168304443359</v>
+        <v>196.9893188476562</v>
       </c>
       <c r="F114" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B115" t="n">
-        <v>193.821025021851</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C115" t="n">
-        <v>197.2773371794379</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D115" t="n">
-        <v>193.821025021851</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E115" t="n">
-        <v>196.9893035888672</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F115" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B116" t="n">
-        <v>196.870136689126</v>
+        <v>192.0829546896537</v>
       </c>
       <c r="C116" t="n">
-        <v>201.0018110133274</v>
+        <v>194.8142273994103</v>
       </c>
       <c r="D116" t="n">
-        <v>193.1258058856387</v>
+        <v>191.3281356874407</v>
       </c>
       <c r="E116" t="n">
-        <v>193.9799499511719</v>
+        <v>193.0165557861328</v>
       </c>
       <c r="F116" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B117" t="n">
-        <v>192.0829546896537</v>
+        <v>194.2580295441802</v>
       </c>
       <c r="C117" t="n">
-        <v>194.8142273994103</v>
+        <v>199.0352710459927</v>
       </c>
       <c r="D117" t="n">
-        <v>191.3281356874407</v>
+        <v>191.9836310996653</v>
       </c>
       <c r="E117" t="n">
-        <v>193.0165557861328</v>
+        <v>193.6621246337891</v>
       </c>
       <c r="F117" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B118" t="n">
-        <v>194.2580448499211</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C118" t="n">
-        <v>199.0352867281362</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D118" t="n">
-        <v>191.9836462262046</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E118" t="n">
-        <v>193.6621398925781</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F118" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B119" t="n">
-        <v>191.8942484911283</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C119" t="n">
-        <v>194.3374874288811</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D119" t="n">
-        <v>188.7061018910339</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E119" t="n">
-        <v>194.0494689941406</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F119" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B120" t="n">
-        <v>195.7478267440036</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C120" t="n">
-        <v>196.7012958768407</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D120" t="n">
-        <v>190.6924929381777</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E120" t="n">
-        <v>193.850830078125</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F120" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B121" t="n">
-        <v>190.8315397252546</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="C121" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D121" t="n">
-        <v>181.0486114593648</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E121" t="n">
-        <v>181.7736511230469</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="F121" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B122" t="n">
-        <v>184.4353765448059</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C122" t="n">
-        <v>186.1138700384234</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D122" t="n">
-        <v>178.625224245603</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E122" t="n">
-        <v>180.7208557128906</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F122" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B123" t="n">
-        <v>179.9461742219026</v>
+        <v>182.7469612620264</v>
       </c>
       <c r="C123" t="n">
-        <v>186.1933484091056</v>
+        <v>182.8562127689759</v>
       </c>
       <c r="D123" t="n">
-        <v>178.3074166263376</v>
+        <v>177.6022443008385</v>
       </c>
       <c r="E123" t="n">
-        <v>184.3758087158203</v>
+        <v>178.0888977050781</v>
       </c>
       <c r="F123" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B124" t="n">
-        <v>182.7469612620264</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C124" t="n">
-        <v>182.8562127689759</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D124" t="n">
-        <v>177.6022443008385</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E124" t="n">
-        <v>178.0888977050781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F124" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>178.873523844959</v>
+        <v>183.6408377857945</v>
       </c>
       <c r="C125" t="n">
-        <v>185.1206822343098</v>
+        <v>187.216328097891</v>
       </c>
       <c r="D125" t="n">
-        <v>178.3570608051074</v>
+        <v>181.0684791429995</v>
       </c>
       <c r="E125" t="n">
-        <v>183.7699432373047</v>
+        <v>185.3987884521484</v>
       </c>
       <c r="F125" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" t="n">
-        <v>183.6408377857945</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C126" t="n">
-        <v>187.216328097891</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D126" t="n">
-        <v>181.0684791429995</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E126" t="n">
-        <v>185.3987884521484</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F126" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B127" t="n">
-        <v>185.5775567084869</v>
+        <v>184.0381320953261</v>
       </c>
       <c r="C127" t="n">
-        <v>187.6930410934417</v>
+        <v>186.3026043544238</v>
       </c>
       <c r="D127" t="n">
-        <v>181.7636956083204</v>
+        <v>180.3434636399818</v>
       </c>
       <c r="E127" t="n">
-        <v>184.9717102050781</v>
+        <v>185.9053192138672</v>
       </c>
       <c r="F127" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B128" t="n">
-        <v>184.0381169897925</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C128" t="n">
-        <v>186.3025890630262</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D128" t="n">
-        <v>180.3434488377003</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E128" t="n">
-        <v>185.9053039550781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F128" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" t="n">
-        <v>186.2231237330043</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C129" t="n">
-        <v>186.8587647224845</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D129" t="n">
-        <v>182.3496888213084</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E129" t="n">
-        <v>183.7699432373047</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F129" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" t="n">
-        <v>183.690504131923</v>
+        <v>185.229934306832</v>
       </c>
       <c r="C130" t="n">
-        <v>185.3094088283374</v>
+        <v>185.498099849194</v>
       </c>
       <c r="D130" t="n">
-        <v>180.7804644422889</v>
+        <v>174.5829363342851</v>
       </c>
       <c r="E130" t="n">
-        <v>181.7140655517578</v>
+        <v>175.1689147949219</v>
       </c>
       <c r="F130" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,25 +3823,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" t="n">
-        <v>185.229934306832</v>
+        <v>172.4208720146844</v>
       </c>
       <c r="C131" t="n">
-        <v>185.498099849194</v>
+        <v>173.5360220799356</v>
       </c>
       <c r="D131" t="n">
-        <v>174.5829363342851</v>
+        <v>166.3970410225636</v>
       </c>
       <c r="E131" t="n">
-        <v>175.1689147949219</v>
+        <v>170.1109161376953</v>
       </c>
       <c r="F131" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -3849,25 +3849,25 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B132" t="n">
-        <v>172.4208720146844</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C132" t="n">
-        <v>173.5360220799356</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D132" t="n">
-        <v>166.3970410225636</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E132" t="n">
-        <v>170.1109161376953</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F132" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G132" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B133" t="n">
-        <v>170.5191174814139</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C133" t="n">
-        <v>170.5191174814139</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D133" t="n">
-        <v>162.8126107290287</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E133" t="n">
-        <v>164.2463836669922</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F133" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" t="n">
-        <v>166.3273444705899</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C134" t="n">
-        <v>172.6498652447362</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D134" t="n">
-        <v>165.0528829680655</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E134" t="n">
-        <v>172.0723876953125</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F134" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B135" t="n">
-        <v>174.4520463656914</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C135" t="n">
-        <v>176.7321331165696</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D135" t="n">
-        <v>169.7624151908458</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E135" t="n">
-        <v>170.5689086914062</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F135" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B136" t="n">
-        <v>173.4663277892384</v>
+        <v>183.2040075329009</v>
       </c>
       <c r="C136" t="n">
-        <v>178.842961383224</v>
+        <v>183.7516312461474</v>
       </c>
       <c r="D136" t="n">
-        <v>172.1321282578628</v>
+        <v>177.7975052553062</v>
       </c>
       <c r="E136" t="n">
-        <v>176.8317108154297</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F136" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B137" t="n">
-        <v>183.2040075329009</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C137" t="n">
-        <v>183.7516312461474</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D137" t="n">
-        <v>177.7975052553062</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E137" t="n">
-        <v>180.43603515625</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F137" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="n">
-        <v>184.6278268926657</v>
+        <v>181.7105075933097</v>
       </c>
       <c r="C138" t="n">
-        <v>187.1667986912511</v>
+        <v>188.1823886856741</v>
       </c>
       <c r="D138" t="n">
-        <v>180.2468672661974</v>
+        <v>181.3321466062204</v>
       </c>
       <c r="E138" t="n">
-        <v>181.3520660400391</v>
+        <v>185.4642028808594</v>
       </c>
       <c r="F138" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B139" t="n">
-        <v>181.7105075933097</v>
+        <v>185.7927641258556</v>
       </c>
       <c r="C139" t="n">
-        <v>188.1823886856741</v>
+        <v>192.7226462718077</v>
       </c>
       <c r="D139" t="n">
-        <v>181.3321466062204</v>
+        <v>183.303579264538</v>
       </c>
       <c r="E139" t="n">
-        <v>185.4642028808594</v>
+        <v>186.3005523681641</v>
       </c>
       <c r="F139" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B140" t="n">
-        <v>185.7927641258556</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C140" t="n">
-        <v>192.7226462718077</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D140" t="n">
-        <v>183.303579264538</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E140" t="n">
-        <v>186.3005523681641</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F140" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B141" t="n">
-        <v>187.3858431404722</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C141" t="n">
-        <v>190.3230783921826</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D141" t="n">
-        <v>186.2209063874661</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E141" t="n">
-        <v>188.9789276123047</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F141" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B142" t="n">
-        <v>176.7918740224492</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C142" t="n">
-        <v>178.0962045390804</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D142" t="n">
-        <v>169.9117629967484</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E142" t="n">
-        <v>172.5503082275391</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F142" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B143" t="n">
-        <v>174.8602617765654</v>
+        <v>177.4888508581443</v>
       </c>
       <c r="C143" t="n">
-        <v>177.6780209996891</v>
+        <v>183.4927641701262</v>
       </c>
       <c r="D143" t="n">
-        <v>173.6455382897692</v>
+        <v>176.7420953199099</v>
       </c>
       <c r="E143" t="n">
-        <v>177.3892822265625</v>
+        <v>179.4005432128906</v>
       </c>
       <c r="F143" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="n">
-        <v>177.4888508581443</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C144" t="n">
-        <v>183.4927641701262</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D144" t="n">
-        <v>176.7420953199099</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E144" t="n">
-        <v>179.4005432128906</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F144" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B145" t="n">
-        <v>181.6407975504903</v>
+        <v>178.424769515226</v>
       </c>
       <c r="C145" t="n">
-        <v>183.6221942474171</v>
+        <v>180.993610139636</v>
       </c>
       <c r="D145" t="n">
-        <v>180.5356140136719</v>
+        <v>176.5827818160244</v>
       </c>
       <c r="E145" t="n">
-        <v>180.5356140136719</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F145" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="n">
-        <v>178.424769515226</v>
+        <v>177.5286741071897</v>
       </c>
       <c r="C146" t="n">
-        <v>180.993610139636</v>
+        <v>177.9169863526292</v>
       </c>
       <c r="D146" t="n">
-        <v>176.5827818160244</v>
+        <v>172.2515989617143</v>
       </c>
       <c r="E146" t="n">
-        <v>180.43603515625</v>
+        <v>175.7663269042969</v>
       </c>
       <c r="F146" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B147" t="n">
-        <v>177.5286741071897</v>
+        <v>181.4018572311292</v>
       </c>
       <c r="C147" t="n">
-        <v>177.9169863526292</v>
+        <v>185.2351932001588</v>
       </c>
       <c r="D147" t="n">
-        <v>172.2515989617143</v>
+        <v>177.9767360752557</v>
       </c>
       <c r="E147" t="n">
-        <v>175.7663269042969</v>
+        <v>183.0248107910156</v>
       </c>
       <c r="F147" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B148" t="n">
-        <v>181.4018572311292</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C148" t="n">
-        <v>185.2351932001588</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D148" t="n">
-        <v>177.9767360752557</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E148" t="n">
-        <v>183.0248107910156</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F148" t="n">
-        <v>12324400</v>
+        <v>8444700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="n">
-        <v>183.4429710909726</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C149" t="n">
-        <v>189.4867039708132</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D149" t="n">
-        <v>183.1741348747832</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E149" t="n">
-        <v>184.6775970458984</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F149" t="n">
-        <v>8444700</v>
+        <v>9740800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="n">
-        <v>184.7473182824849</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C150" t="n">
-        <v>186.5793548412774</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D150" t="n">
-        <v>180.3165719120649</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E150" t="n">
-        <v>186.1810913085938</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F150" t="n">
-        <v>9740800</v>
+        <v>11303400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="n">
-        <v>184.7174439304337</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C151" t="n">
-        <v>186.2906106667237</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D151" t="n">
-        <v>178.8031379653169</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E151" t="n">
-        <v>180.4061737060547</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F151" t="n">
-        <v>11303400</v>
+        <v>13955100</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B152" t="n">
-        <v>183.801426731489</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C152" t="n">
-        <v>187.7642050029951</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D152" t="n">
-        <v>183.2040162535504</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E152" t="n">
-        <v>185.5338897705078</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F152" t="n">
-        <v>13955100</v>
+        <v>15123900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B153" t="n">
-        <v>178.9027054786904</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C153" t="n">
-        <v>181.0832340725416</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D153" t="n">
-        <v>176.114830301217</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E153" t="n">
-        <v>181.0334625244141</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F153" t="n">
-        <v>15123900</v>
+        <v>11145000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B154" t="n">
-        <v>179.1317124775628</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C154" t="n">
-        <v>181.7105044839724</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D154" t="n">
-        <v>175.5472800106302</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E154" t="n">
-        <v>176.7221832275391</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F154" t="n">
-        <v>11145000</v>
+        <v>10214000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B155" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C155" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D155" t="n">
-        <v>169.8420709331304</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E155" t="n">
-        <v>170.5689086914062</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F155" t="n">
-        <v>10214000</v>
+        <v>11951900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" t="n">
-        <v>169.0455318751909</v>
+        <v>165.2818748478833</v>
       </c>
       <c r="C156" t="n">
-        <v>169.0455318751909</v>
+        <v>168.6173886402985</v>
       </c>
       <c r="D156" t="n">
-        <v>164.0372928300067</v>
+        <v>163.6191011830893</v>
       </c>
       <c r="E156" t="n">
-        <v>165.1225738525391</v>
+        <v>166.8550415039062</v>
       </c>
       <c r="F156" t="n">
-        <v>11951900</v>
+        <v>9749400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B157" t="n">
-        <v>165.2818748478833</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C157" t="n">
-        <v>168.6173886402985</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D157" t="n">
-        <v>163.6191011830893</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E157" t="n">
-        <v>166.8550415039062</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F157" t="n">
-        <v>9749400</v>
+        <v>13883400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B158" t="n">
-        <v>168.5178185348167</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C158" t="n">
-        <v>175.208748793394</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D158" t="n">
-        <v>168.268900043628</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E158" t="n">
-        <v>172.7593841552734</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F158" t="n">
-        <v>13883400</v>
+        <v>13671200</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B159" t="n">
-        <v>172.1420794089453</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C159" t="n">
-        <v>179.9979467596552</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D159" t="n">
-        <v>171.0567983816156</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E159" t="n">
-        <v>178.7035675048828</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F159" t="n">
-        <v>13671200</v>
+        <v>17510800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B160" t="n">
-        <v>184.1996921538</v>
+        <v>175.2784431578192</v>
       </c>
       <c r="C160" t="n">
-        <v>186.6291391730516</v>
+        <v>179.529975364695</v>
       </c>
       <c r="D160" t="n">
-        <v>178.0364675908902</v>
+        <v>172.5901264135125</v>
       </c>
       <c r="E160" t="n">
-        <v>178.6438293457031</v>
+        <v>179.3208923339844</v>
       </c>
       <c r="F160" t="n">
-        <v>17510800</v>
+        <v>13025300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B161" t="n">
-        <v>175.2784431578192</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C161" t="n">
-        <v>179.529975364695</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D161" t="n">
-        <v>172.5901264135125</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E161" t="n">
-        <v>179.3208923339844</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F161" t="n">
-        <v>13025300</v>
+        <v>10949100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B162" t="n">
-        <v>174.6213174256682</v>
+        <v>179.0619996775001</v>
       </c>
       <c r="C162" t="n">
-        <v>176.5728300297275</v>
+        <v>182.5568249684187</v>
       </c>
       <c r="D162" t="n">
-        <v>171.2459830488208</v>
+        <v>176.9113402973623</v>
       </c>
       <c r="E162" t="n">
-        <v>175.5472869873047</v>
+        <v>179.291015625</v>
       </c>
       <c r="F162" t="n">
-        <v>10949100</v>
+        <v>10176700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B163" t="n">
-        <v>179.0619996775001</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C163" t="n">
-        <v>182.5568249684187</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D163" t="n">
-        <v>176.9113402973623</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E163" t="n">
-        <v>179.291015625</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F163" t="n">
-        <v>10176700</v>
+        <v>13617200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B164" t="n">
-        <v>177.6581006500201</v>
+        <v>177.2299664024681</v>
       </c>
       <c r="C164" t="n">
-        <v>181.5711072848628</v>
+        <v>183.1243544731695</v>
       </c>
       <c r="D164" t="n">
-        <v>176.9113451663183</v>
+        <v>176.1247676896629</v>
       </c>
       <c r="E164" t="n">
-        <v>178.3052978515625</v>
+        <v>176.7420806884766</v>
       </c>
       <c r="F164" t="n">
-        <v>13617200</v>
+        <v>18524900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B165" t="n">
-        <v>177.2299664024681</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C165" t="n">
-        <v>183.1243544731695</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D165" t="n">
-        <v>176.1247676896629</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E165" t="n">
-        <v>176.7420806884766</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F165" t="n">
-        <v>18524900</v>
+        <v>22559400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B166" t="n">
-        <v>177.6581004088628</v>
+        <v>179.4602803383912</v>
       </c>
       <c r="C166" t="n">
-        <v>181.6905830539347</v>
+        <v>193.3001423298492</v>
       </c>
       <c r="D166" t="n">
-        <v>170.9074320607842</v>
+        <v>179.24123085138</v>
       </c>
       <c r="E166" t="n">
-        <v>175.4078826904297</v>
+        <v>190.2733001708984</v>
       </c>
       <c r="F166" t="n">
-        <v>22559400</v>
+        <v>33998900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="n">
-        <v>179.4602803383912</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C167" t="n">
-        <v>193.3001423298492</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D167" t="n">
-        <v>179.24123085138</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E167" t="n">
-        <v>190.2733001708984</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F167" t="n">
-        <v>33998900</v>
+        <v>27594800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B168" t="n">
-        <v>197.8901992931745</v>
+        <v>200.1503901074607</v>
       </c>
       <c r="C168" t="n">
-        <v>210.4257307870387</v>
+        <v>203.5058065985036</v>
       </c>
       <c r="D168" t="n">
-        <v>197.352542040295</v>
+        <v>194.9131351866423</v>
       </c>
       <c r="E168" t="n">
-        <v>208.6932678222656</v>
+        <v>199.9711608886719</v>
       </c>
       <c r="F168" t="n">
-        <v>27594800</v>
+        <v>19216600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B169" t="n">
-        <v>200.1503901074607</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C169" t="n">
-        <v>203.5058065985036</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D169" t="n">
-        <v>194.9131351866423</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E169" t="n">
-        <v>199.9711608886719</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F169" t="n">
-        <v>19216600</v>
+        <v>14154400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B170" t="n">
-        <v>196.4166079226038</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C170" t="n">
-        <v>196.8248227029743</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D170" t="n">
-        <v>188.9092176958791</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E170" t="n">
-        <v>189.7854156494141</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F170" t="n">
-        <v>14154400</v>
+        <v>14453600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B171" t="n">
-        <v>196.9542758894677</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C171" t="n">
-        <v>197.2330634002457</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D171" t="n">
-        <v>185.3048928689384</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E171" t="n">
-        <v>187.9334716796875</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F171" t="n">
-        <v>14453600</v>
+        <v>13183900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B172" t="n">
-        <v>188.9789318725711</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C172" t="n">
-        <v>191.6771999565016</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D172" t="n">
-        <v>184.0304307819904</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E172" t="n">
-        <v>184.8568420410156</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F172" t="n">
-        <v>13183900</v>
+        <v>11177800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B173" t="n">
-        <v>183.1144169895118</v>
+        <v>178.7234870391233</v>
       </c>
       <c r="C173" t="n">
-        <v>184.2196157855271</v>
+        <v>181.6706888305526</v>
       </c>
       <c r="D173" t="n">
-        <v>180.92393713233</v>
+        <v>170.8178328696119</v>
       </c>
       <c r="E173" t="n">
-        <v>181.7602996826172</v>
+        <v>174.5914459228516</v>
       </c>
       <c r="F173" t="n">
-        <v>11177800</v>
+        <v>15427800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B174" t="n">
-        <v>178.7234870391233</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C174" t="n">
-        <v>181.6706888305526</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D174" t="n">
-        <v>170.8178328696119</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E174" t="n">
-        <v>174.5914459228516</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F174" t="n">
-        <v>15427800</v>
+        <v>10820500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,25 +4967,25 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B175" t="n">
-        <v>169.861995238658</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C175" t="n">
-        <v>174.7706609037228</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D175" t="n">
-        <v>169.2944537502145</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E175" t="n">
-        <v>170.1806030273438</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F175" t="n">
-        <v>10820500</v>
+        <v>16666000</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -4993,25 +4993,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B176" t="n">
-        <v>167.9744954285649</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C176" t="n">
-        <v>168.6832400259219</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D176" t="n">
-        <v>163.0231992739924</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E176" t="n">
-        <v>166.1576843261719</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F176" t="n">
-        <v>16666000</v>
+        <v>13589400</v>
       </c>
       <c r="G176" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B177" t="n">
-        <v>164.4506890531704</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C177" t="n">
-        <v>166.2475157071144</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D177" t="n">
-        <v>161.1165431857153</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E177" t="n">
-        <v>165.5986633300781</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F177" t="n">
-        <v>13589400</v>
+        <v>13541800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B178" t="n">
-        <v>165.7384133733495</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C178" t="n">
-        <v>169.6515271583533</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D178" t="n">
-        <v>163.8816793355271</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E178" t="n">
-        <v>164.2610168457031</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F178" t="n">
-        <v>13541800</v>
+        <v>16385300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B179" t="n">
-        <v>163.7718739013043</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C179" t="n">
-        <v>166.0079454764833</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D179" t="n">
-        <v>160.2181284427459</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E179" t="n">
-        <v>161.4260101318359</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F179" t="n">
-        <v>16385300</v>
+        <v>19986200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B180" t="n">
-        <v>159.9685677271403</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C180" t="n">
-        <v>161.1464880907799</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D180" t="n">
-        <v>153.959135832121</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E180" t="n">
-        <v>154.7477569580078</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F180" t="n">
-        <v>19986200</v>
+        <v>57940800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B181" t="n">
-        <v>152.4617715583163</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C181" t="n">
-        <v>154.1987212566731</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D181" t="n">
-        <v>149.5369245308901</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E181" t="n">
-        <v>151.5134429931641</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F181" t="n">
-        <v>57940800</v>
+        <v>20502800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B182" t="n">
-        <v>149.8962920415152</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C182" t="n">
-        <v>153.5997679942281</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D182" t="n">
-        <v>146.0630395211035</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E182" t="n">
-        <v>149.8563537597656</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F182" t="n">
-        <v>20502800</v>
+        <v>20720700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B183" t="n">
-        <v>151.3836627210609</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C183" t="n">
-        <v>154.907462036052</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D183" t="n">
-        <v>150.5850798848861</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E183" t="n">
-        <v>153.1505584716797</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F183" t="n">
-        <v>20720700</v>
+        <v>13146800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B184" t="n">
-        <v>151.5433859321397</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C184" t="n">
-        <v>156.7841657815476</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D184" t="n">
-        <v>150.135858545478</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E184" t="n">
-        <v>152.4917144775391</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F184" t="n">
-        <v>13146800</v>
+        <v>11324700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B185" t="n">
-        <v>149.7465472087312</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C185" t="n">
-        <v>153.7295454610107</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D185" t="n">
-        <v>148.5187115976041</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E185" t="n">
-        <v>149.9262390136719</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F185" t="n">
-        <v>11324700</v>
+        <v>21267900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B186" t="n">
-        <v>151.2239658596097</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C186" t="n">
-        <v>158.1817266914859</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D186" t="n">
-        <v>151.2239658596097</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E186" t="n">
-        <v>158.0918731689453</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F186" t="n">
-        <v>21267900</v>
+        <v>12664100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B187" t="n">
-        <v>159.9885357004027</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C187" t="n">
-        <v>161.4759091917036</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D187" t="n">
-        <v>157.4230418613804</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E187" t="n">
-        <v>157.6526336669922</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F187" t="n">
-        <v>12664100</v>
+        <v>13690500</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>154.8176224085462</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C188" t="n">
-        <v>157.4130622995693</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D188" t="n">
-        <v>153.7994247316601</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E188" t="n">
-        <v>156.3848724365234</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F188" t="n">
-        <v>13690500</v>
+        <v>14164600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B189" t="n">
-        <v>161.9351081174896</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C189" t="n">
-        <v>165.5187996520913</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D189" t="n">
-        <v>160.916895191227</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E189" t="n">
-        <v>162.9433288574219</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F189" t="n">
-        <v>14164600</v>
+        <v>10486300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B190" t="n">
-        <v>162.7137441629</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C190" t="n">
-        <v>166.9163573859938</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D190" t="n">
-        <v>161.7155003336798</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E190" t="n">
-        <v>165.8182830810547</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F190" t="n">
-        <v>10486300</v>
+        <v>10595500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B191" t="n">
-        <v>163.7020118941432</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C191" t="n">
-        <v>167.425457131665</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D191" t="n">
-        <v>162.0848465245878</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E191" t="n">
-        <v>165.3590850830078</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F191" t="n">
-        <v>10595500</v>
+        <v>13057900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B192" t="n">
-        <v>168.9228138583306</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C192" t="n">
-        <v>172.0772678623225</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D192" t="n">
-        <v>167.3855099055031</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E192" t="n">
-        <v>169.2222900390625</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F192" t="n">
-        <v>13057900</v>
+        <v>9792400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B193" t="n">
-        <v>167.0760662569272</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C193" t="n">
-        <v>167.2357889266519</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D193" t="n">
-        <v>164.4906183727253</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E193" t="n">
-        <v>166.2874603271484</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F193" t="n">
-        <v>9792400</v>
+        <v>13858600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B194" t="n">
-        <v>158.05194011754</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C194" t="n">
-        <v>163.5123348335076</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D194" t="n">
-        <v>156.2051830247059</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E194" t="n">
-        <v>162.2146148681641</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F194" t="n">
-        <v>13858600</v>
+        <v>8321500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B195" t="n">
-        <v>165.309182555471</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C195" t="n">
-        <v>166.007950182526</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D195" t="n">
-        <v>162.1347592897187</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E195" t="n">
-        <v>163.0331878662109</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F195" t="n">
-        <v>8321500</v>
+        <v>14020700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>165.6286161244176</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C196" t="n">
-        <v>172.4566003351415</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D196" t="n">
-        <v>165.6286161244176</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E196" t="n">
-        <v>170.9193115234375</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F196" t="n">
-        <v>14020700</v>
+        <v>13507900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>162.2046435717354</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C197" t="n">
-        <v>171.049084414024</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D197" t="n">
-        <v>161.1864306117812</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E197" t="n">
-        <v>167.2657318115234</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F197" t="n">
-        <v>13507900</v>
+        <v>13328100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>170.2205331766167</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C198" t="n">
-        <v>172.4965277703878</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D198" t="n">
-        <v>166.2674811162824</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E198" t="n">
-        <v>166.7067108154297</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F198" t="n">
-        <v>13328100</v>
+        <v>12057500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B199" t="n">
-        <v>170.5399744864679</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C199" t="n">
-        <v>174.2334736592566</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D199" t="n">
-        <v>166.5869373980102</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E199" t="n">
-        <v>172.3767395019531</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F199" t="n">
-        <v>12057500</v>
+        <v>10191500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B200" t="n">
-        <v>171.1988064601764</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C200" t="n">
-        <v>175.1218971627477</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D200" t="n">
-        <v>169.4518798636439</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E200" t="n">
-        <v>170.4700927734375</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F200" t="n">
-        <v>10191500</v>
+        <v>13426500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B201" t="n">
-        <v>167.5652084388413</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C201" t="n">
-        <v>175.0819831940494</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D201" t="n">
-        <v>166.2075962327059</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E201" t="n">
-        <v>173.4847869873047</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F201" t="n">
-        <v>13426500</v>
+        <v>12831800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B202" t="n">
-        <v>166.7666058963373</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C202" t="n">
-        <v>172.1271701993457</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D202" t="n">
-        <v>166.6368293287962</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E202" t="n">
-        <v>169.7613372802734</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F202" t="n">
-        <v>12831800</v>
+        <v>12194500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B203" t="n">
-        <v>169.1723839486806</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C203" t="n">
-        <v>169.272214424985</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D203" t="n">
-        <v>161.925139189555</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E203" t="n">
-        <v>162.7137451171875</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F203" t="n">
-        <v>12194500</v>
+        <v>12775000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B204" t="n">
-        <v>164.7601382451291</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C204" t="n">
-        <v>165.5886824068968</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D204" t="n">
-        <v>154.877515725338</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E204" t="n">
-        <v>156.6543884277344</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F204" t="n">
-        <v>12775000</v>
+        <v>10899100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B205" t="n">
-        <v>160.0983505627206</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C205" t="n">
-        <v>164.1611950360997</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D205" t="n">
-        <v>159.2698063547753</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E205" t="n">
-        <v>163.3725891113281</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F205" t="n">
-        <v>10899100</v>
+        <v>17312000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B206" t="n">
-        <v>167.7049639405646</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C206" t="n">
-        <v>176.6392431993331</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D206" t="n">
-        <v>166.8464736349225</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E206" t="n">
-        <v>173.2951354980469</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F206" t="n">
-        <v>17312000</v>
+        <v>17204600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B207" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C207" t="n">
-        <v>184.2158982492034</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D207" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E207" t="n">
-        <v>181.1812438964844</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F207" t="n">
-        <v>17204600</v>
+        <v>18139500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B208" t="n">
-        <v>181.6903554713178</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C208" t="n">
-        <v>189.8460057999592</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D208" t="n">
-        <v>181.6903554713178</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E208" t="n">
-        <v>188.0491790771484</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F208" t="n">
-        <v>18139500</v>
+        <v>12182400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B209" t="n">
-        <v>180.6721461984077</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C209" t="n">
-        <v>182.1894657683464</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D209" t="n">
-        <v>175.5910738107855</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E209" t="n">
-        <v>180.3926391601562</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F209" t="n">
-        <v>12182400</v>
+        <v>9691500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B210" t="n">
-        <v>177.3879151720665</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C210" t="n">
-        <v>184.1260606305619</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D210" t="n">
-        <v>176.719093672914</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E210" t="n">
-        <v>183.6968231201172</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F210" t="n">
-        <v>9691500</v>
+        <v>12908000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B211" t="n">
-        <v>188.658097974018</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C211" t="n">
-        <v>193.3598176605707</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D211" t="n">
-        <v>185.5735131091938</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E211" t="n">
-        <v>185.6234283447266</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F211" t="n">
-        <v>12908000</v>
+        <v>9326900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B212" t="n">
-        <v>182.7684517177381</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C212" t="n">
-        <v>190.9540477431734</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D212" t="n">
-        <v>182.6786134323838</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E212" t="n">
-        <v>190.6545867919922</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F212" t="n">
-        <v>9326900</v>
+        <v>9605500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B213" t="n">
-        <v>192.9405589477455</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C213" t="n">
-        <v>194.5976472985604</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D213" t="n">
-        <v>190.0955580470331</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E213" t="n">
-        <v>192.6410827636719</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F213" t="n">
-        <v>9605500</v>
+        <v>13297600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B214" t="n">
-        <v>183.117847615437</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C214" t="n">
-        <v>186.6915622961891</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D214" t="n">
-        <v>182.6786179003067</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E214" t="n">
-        <v>186.4420013427734</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F214" t="n">
-        <v>13297600</v>
+        <v>11392800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B215" t="n">
-        <v>190.7544083295565</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C215" t="n">
-        <v>194.3580691369978</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D215" t="n">
-        <v>190.2652786051507</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E215" t="n">
-        <v>192.4015197753906</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F215" t="n">
-        <v>11392800</v>
+        <v>9706600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B216" t="n">
-        <v>189.8360257192551</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C216" t="n">
-        <v>197.831953246477</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D216" t="n">
-        <v>189.666326097428</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E216" t="n">
-        <v>197.1631317138672</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F216" t="n">
-        <v>9706600</v>
+        <v>11171600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B217" t="n">
-        <v>196.5941314807131</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C217" t="n">
-        <v>199.0398256830038</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D217" t="n">
-        <v>195.1566580076304</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E217" t="n">
-        <v>197.1231994628906</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F217" t="n">
-        <v>11171600</v>
+        <v>12787900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B218" t="n">
-        <v>191.6628101365335</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C218" t="n">
-        <v>196.1549072491085</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D218" t="n">
-        <v>191.4431952813594</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E218" t="n">
-        <v>192.9804992675781</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F218" t="n">
-        <v>12787900</v>
+        <v>15058700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="n">
-        <v>196.4943140399408</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C219" t="n">
-        <v>202.6335228023228</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D219" t="n">
-        <v>191.0538881519706</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E219" t="n">
-        <v>201.016357421875</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F219" t="n">
-        <v>15058700</v>
+        <v>8664800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B220" t="n">
-        <v>202.3939250564146</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C220" t="n">
-        <v>204.0410211897246</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D220" t="n">
-        <v>194.9769811314243</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E220" t="n">
-        <v>195.8654174804688</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F220" t="n">
-        <v>8664800</v>
+        <v>14378800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B221" t="n">
-        <v>193.4896063018435</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C221" t="n">
-        <v>194.5976575790598</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D221" t="n">
-        <v>189.57649225733</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E221" t="n">
-        <v>190.6346282958984</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F221" t="n">
-        <v>14378800</v>
+        <v>14152900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B222" t="n">
-        <v>193.7491445531879</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C222" t="n">
-        <v>199.0598091290667</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D222" t="n">
-        <v>192.8906542357335</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E222" t="n">
-        <v>195.7955474853516</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F222" t="n">
-        <v>14152900</v>
+        <v>17843600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B223" t="n">
-        <v>193.8689320609861</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C223" t="n">
-        <v>207.5847919095016</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D223" t="n">
-        <v>193.8689320609861</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E223" t="n">
-        <v>205.7280578613281</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F223" t="n">
-        <v>17843600</v>
+        <v>11482300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="n">
-        <v>204.8595912018172</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C224" t="n">
-        <v>207.5149233311111</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D224" t="n">
-        <v>202.6434887759544</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E224" t="n">
-        <v>205.0692138671875</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F224" t="n">
-        <v>11482300</v>
+        <v>9685400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B225" t="n">
-        <v>205.2189664215684</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C225" t="n">
-        <v>210.6993304789719</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D225" t="n">
-        <v>204.3704530814486</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E225" t="n">
-        <v>208.8026580810547</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F225" t="n">
-        <v>9685400</v>
+        <v>9580200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B226" t="n">
-        <v>208.0539803833292</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C226" t="n">
-        <v>212.7956386479058</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D226" t="n">
-        <v>207.0257904413594</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E226" t="n">
-        <v>208.6928558349609</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F226" t="n">
-        <v>9580200</v>
+        <v>10081800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B227" t="n">
-        <v>205.4884885298704</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C227" t="n">
-        <v>209.9406472657768</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D227" t="n">
-        <v>204.400391231641</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E227" t="n">
-        <v>205.3287658691406</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F227" t="n">
-        <v>10081800</v>
+        <v>14888900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B228" t="n">
-        <v>199.5888632714973</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C228" t="n">
-        <v>206.0774478239803</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D228" t="n">
-        <v>198.6005964484484</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E228" t="n">
-        <v>205.2588806152344</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F228" t="n">
-        <v>14888900</v>
+        <v>55517500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B229" t="n">
-        <v>229.6459965412689</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C229" t="n">
-        <v>254.0330860396483</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D229" t="n">
-        <v>229.6459965412689</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E229" t="n">
-        <v>251.6073608398438</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F229" t="n">
-        <v>55517500</v>
+        <v>34362700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B230" t="n">
-        <v>250.0301279952546</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C230" t="n">
-        <v>263.0671897003631</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D230" t="n">
-        <v>248.5627083778381</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E230" t="n">
-        <v>255.5504150390625</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F230" t="n">
-        <v>34362700</v>
+        <v>22471500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B231" t="n">
-        <v>253.9432305236259</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C231" t="n">
-        <v>261.8193732125837</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D231" t="n">
-        <v>253.9432305236259</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E231" t="n">
-        <v>257.0877075195312</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F231" t="n">
-        <v>22471500</v>
+        <v>15897500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B232" t="n">
-        <v>254.5621609406893</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C232" t="n">
-        <v>261.8593363431507</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D232" t="n">
-        <v>253.8035010915435</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E232" t="n">
-        <v>257.6567077636719</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F232" t="n">
-        <v>15897500</v>
+        <v>14393700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B233" t="n">
-        <v>258.9244691424316</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C233" t="n">
-        <v>264.0853722779391</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D233" t="n">
-        <v>253.154621477229</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E233" t="n">
-        <v>256.478759765625</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F233" t="n">
-        <v>14393700</v>
+        <v>16028300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B234" t="n">
-        <v>261.5199276025597</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C234" t="n">
-        <v>267.7988593124239</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D234" t="n">
-        <v>261.1405900757476</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E234" t="n">
-        <v>263.9656066894531</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F234" t="n">
-        <v>16028300</v>
+        <v>10490600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B235" t="n">
-        <v>262.8974710364521</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C235" t="n">
-        <v>263.1370702625856</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D235" t="n">
-        <v>257.3672223502596</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E235" t="n">
-        <v>258.7747497558594</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F235" t="n">
-        <v>10490600</v>
+        <v>17482700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B236" t="n">
-        <v>253.2744227737308</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C236" t="n">
-        <v>253.5539298242691</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D236" t="n">
-        <v>245.4581718493405</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E236" t="n">
-        <v>248.6824951171875</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F236" t="n">
-        <v>17482700</v>
+        <v>11853700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B237" t="n">
-        <v>249.3413418635835</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C237" t="n">
-        <v>254.3525301395604</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D237" t="n">
-        <v>243.0224566114913</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E237" t="n">
-        <v>243.7312164306641</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F237" t="n">
-        <v>11853700</v>
+        <v>10732600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B238" t="n">
-        <v>244.9191211985708</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C238" t="n">
-        <v>248.0635830600566</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D238" t="n">
-        <v>241.3254374437371</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E238" t="n">
-        <v>242.5732421875</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F238" t="n">
-        <v>10732600</v>
+        <v>9738300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B239" t="n">
-        <v>241.5949712138984</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C239" t="n">
-        <v>250.1099896964979</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D239" t="n">
-        <v>241.5949712138984</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E239" t="n">
-        <v>247.2849578857422</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F239" t="n">
-        <v>9738300</v>
+        <v>12963700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B240" t="n">
-        <v>255.3008656803045</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C240" t="n">
-        <v>259.7230786425112</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D240" t="n">
-        <v>251.0583293004754</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E240" t="n">
-        <v>258.9743957519531</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F240" t="n">
-        <v>12963700</v>
+        <v>11502800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B241" t="n">
-        <v>256.43886230448</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C241" t="n">
-        <v>261.8792726915332</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D241" t="n">
-        <v>254.632028246405</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E241" t="n">
-        <v>255.2010192871094</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F241" t="n">
-        <v>11502800</v>
+        <v>9423800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B242" t="n">
-        <v>251.4077029961344</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C242" t="n">
-        <v>255.9497000259878</v>
+        <v>247</v>
       </c>
       <c r="D242" t="n">
-        <v>249.1616544830015</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E242" t="n">
-        <v>250.0999908447266</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F242" t="n">
-        <v>9423800</v>
+        <v>16611300</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B243" t="n">
-        <v>244.1799926757812</v>
+        <v>244.25</v>
       </c>
       <c r="C243" t="n">
-        <v>247</v>
+        <v>244.25</v>
       </c>
       <c r="D243" t="n">
-        <v>241.5200042724609</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E243" t="n">
-        <v>242.8500061035156</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F243" t="n">
-        <v>16611300</v>
+        <v>21962400</v>
       </c>
       <c r="G243" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B244" t="n">
-        <v>244.25</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C244" t="n">
-        <v>244.25</v>
+        <v>241.3399963378906</v>
       </c>
       <c r="D244" t="n">
-        <v>236.5500030517578</v>
+        <v>236.25</v>
       </c>
       <c r="E244" t="n">
-        <v>237.9199981689453</v>
+        <v>236.4199981689453</v>
       </c>
       <c r="F244" t="n">
-        <v>21962400</v>
+        <v>10581900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B245" t="n">
-        <v>239.8000030517578</v>
+        <v>241.5</v>
       </c>
       <c r="C245" t="n">
-        <v>241.3399963378906</v>
+        <v>242.4400024414062</v>
       </c>
       <c r="D245" t="n">
-        <v>236.25</v>
+        <v>229.8099975585938</v>
       </c>
       <c r="E245" t="n">
-        <v>236.4199981689453</v>
+        <v>233.2799987792969</v>
       </c>
       <c r="F245" t="n">
-        <v>10581900</v>
+        <v>13635600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B246" t="n">
-        <v>241.5</v>
+        <v>234.4199981689453</v>
       </c>
       <c r="C246" t="n">
-        <v>242.4400024414062</v>
+        <v>241.1199951171875</v>
       </c>
       <c r="D246" t="n">
-        <v>229.8099975585938</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="E246" t="n">
-        <v>233.2799987792969</v>
+        <v>237.5800018310547</v>
       </c>
       <c r="F246" t="n">
-        <v>13635600</v>
+        <v>12353500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B247" t="n">
-        <v>234.4199981689453</v>
+        <v>240.6399993896484</v>
       </c>
       <c r="C247" t="n">
-        <v>241.1199951171875</v>
+        <v>242.0899963378906</v>
       </c>
       <c r="D247" t="n">
-        <v>234.2400054931641</v>
+        <v>237</v>
       </c>
       <c r="E247" t="n">
-        <v>237.5800018310547</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="F247" t="n">
-        <v>12353500</v>
+        <v>11074000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B248" t="n">
-        <v>240.6399993896484</v>
+        <v>237.0299987792969</v>
       </c>
       <c r="C248" t="n">
-        <v>242.0899963378906</v>
+        <v>239.3699951171875</v>
       </c>
       <c r="D248" t="n">
-        <v>237</v>
+        <v>233.3800048828125</v>
       </c>
       <c r="E248" t="n">
-        <v>238.2200012207031</v>
+        <v>234.0200042724609</v>
       </c>
       <c r="F248" t="n">
-        <v>11074000</v>
+        <v>8735500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B249" t="n">
-        <v>237.0299987792969</v>
+        <v>224.9700012207031</v>
       </c>
       <c r="C249" t="n">
-        <v>239.3699951171875</v>
+        <v>230.5700073242188</v>
       </c>
       <c r="D249" t="n">
-        <v>233.3800048828125</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="E249" t="n">
-        <v>234.0200042724609</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="F249" t="n">
-        <v>8735500</v>
+        <v>10327500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B250" t="n">
-        <v>224.9700012207031</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="C250" t="n">
-        <v>230.5700073242188</v>
+        <v>228.9799957275391</v>
       </c>
       <c r="D250" t="n">
-        <v>221.1799926757812</v>
+        <v>223.4299926757812</v>
       </c>
       <c r="E250" t="n">
-        <v>227.2700042724609</v>
+        <v>225.3099975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>10327500</v>
+        <v>13506300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B251" t="n">
-        <v>227.2700042724609</v>
+        <v>225.3999938964844</v>
       </c>
       <c r="C251" t="n">
-        <v>228.9799957275391</v>
+        <v>233.7599945068359</v>
       </c>
       <c r="D251" t="n">
-        <v>223.4299926757812</v>
+        <v>224.4299926757812</v>
       </c>
       <c r="E251" t="n">
-        <v>225.3099975585938</v>
+        <v>229.5700073242188</v>
       </c>
       <c r="F251" t="n">
-        <v>13506300</v>
+        <v>11228200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B252" t="n">
-        <v>225.3999938964844</v>
+        <v>235.2799987792969</v>
       </c>
       <c r="C252" t="n">
-        <v>233.7599945068359</v>
+        <v>239.4499969482422</v>
       </c>
       <c r="D252" t="n">
-        <v>224.4299926757812</v>
+        <v>230.75</v>
       </c>
       <c r="E252" t="n">
-        <v>229.5700073242188</v>
+        <v>236.6900024414062</v>
       </c>
       <c r="F252" t="n">
-        <v>11228200</v>
+        <v>9571200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10654,34 +10654,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>236.69</v>
+      </c>
+      <c r="D2" t="n">
         <v>229.57</v>
       </c>
-      <c r="D2" t="n">
-        <v>225.31</v>
-      </c>
       <c r="E2" t="n">
-        <v>225.4</v>
+        <v>235.28</v>
       </c>
       <c r="F2" t="n">
-        <v>233.7299</v>
+        <v>239.4499</v>
       </c>
       <c r="G2" t="n">
-        <v>224.4301</v>
+        <v>230.75</v>
       </c>
       <c r="H2" t="n">
-        <v>9706861</v>
+        <v>9563732</v>
       </c>
       <c r="I2" t="n">
-        <v>13773033</v>
+        <v>13711898</v>
       </c>
       <c r="J2" t="n">
-        <v>188936110080</v>
+        <v>194795864064</v>
       </c>
       <c r="K2" t="n">
-        <v>20.626236</v>
+        <v>21.265947</v>
       </c>
       <c r="L2" t="n">
-        <v>14.342083</v>
+        <v>14.786896</v>
       </c>
       <c r="M2" t="n">
         <v>11.13</v>
@@ -10696,7 +10696,7 @@
         <v>1.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="R2" t="n">
         <v>0.2199</v>
@@ -10720,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.923014</v>
+        <v>5.0756993</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10732,7 +10732,7 @@
         <v>43938000896</v>
       </c>
       <c r="AC2" t="n">
-        <v>219909111808</v>
+        <v>225768865792</v>
       </c>
       <c r="AD2" t="n">
         <v>12899000320</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:03:13</t>
+          <t>2026-10-02 19:38:54</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B2" t="n">
-        <v>233.4498996394798</v>
+        <v>236.7419954840688</v>
       </c>
       <c r="C2" t="n">
-        <v>237.3865110117534</v>
+        <v>240.7678464733125</v>
       </c>
       <c r="D2" t="n">
-        <v>231.6353042398812</v>
+        <v>236.4940981065986</v>
       </c>
       <c r="E2" t="n">
-        <v>236.8708953857422</v>
+        <v>238.3384552001953</v>
       </c>
       <c r="F2" t="n">
-        <v>7679200</v>
+        <v>8849800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B3" t="n">
-        <v>236.7419803274875</v>
+        <v>237.3171258741176</v>
       </c>
       <c r="C3" t="n">
-        <v>240.7678310589901</v>
+        <v>248.363432718911</v>
       </c>
       <c r="D3" t="n">
-        <v>236.4940829658881</v>
+        <v>233.4300967019765</v>
       </c>
       <c r="E3" t="n">
-        <v>238.3384399414062</v>
+        <v>243.7128753662109</v>
       </c>
       <c r="F3" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B4" t="n">
-        <v>237.3171110157645</v>
+        <v>244.4069666278678</v>
       </c>
       <c r="C4" t="n">
-        <v>248.3634171689519</v>
+        <v>245.2795701971395</v>
       </c>
       <c r="D4" t="n">
-        <v>233.430082086989</v>
+        <v>235.5520799850208</v>
       </c>
       <c r="E4" t="n">
-        <v>243.7128601074219</v>
+        <v>237.7236633300781</v>
       </c>
       <c r="F4" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B5" t="n">
-        <v>244.406950940097</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C5" t="n">
-        <v>245.2795544533588</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D5" t="n">
-        <v>235.5520648656193</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E5" t="n">
-        <v>237.7236480712891</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F5" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B6" t="n">
-        <v>237.7236681390551</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C6" t="n">
-        <v>239.290381338098</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D6" t="n">
-        <v>233.6680556537968</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E6" t="n">
-        <v>238.4078521728516</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F6" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B7" t="n">
-        <v>237.2576175505903</v>
+        <v>244.4466590259869</v>
       </c>
       <c r="C7" t="n">
-        <v>243.8913535488906</v>
+        <v>246.955379366002</v>
       </c>
       <c r="D7" t="n">
-        <v>235.1554375781523</v>
+        <v>238.695436635224</v>
       </c>
       <c r="E7" t="n">
-        <v>243.2666473388672</v>
+        <v>239.6473541259766</v>
       </c>
       <c r="F7" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B8" t="n">
-        <v>244.4466590259869</v>
+        <v>240.8471677432379</v>
       </c>
       <c r="C8" t="n">
-        <v>246.955379366002</v>
+        <v>247.252842429503</v>
       </c>
       <c r="D8" t="n">
-        <v>238.695436635224</v>
+        <v>240.3315369780713</v>
       </c>
       <c r="E8" t="n">
-        <v>239.6473541259766</v>
+        <v>246.6578826904297</v>
       </c>
       <c r="F8" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B9" t="n">
-        <v>240.8471528439123</v>
+        <v>246.0232865332319</v>
       </c>
       <c r="C9" t="n">
-        <v>247.2528271339085</v>
+        <v>246.1918549429118</v>
       </c>
       <c r="D9" t="n">
-        <v>240.3315221106437</v>
+        <v>237.5352823137284</v>
       </c>
       <c r="E9" t="n">
-        <v>246.6578674316406</v>
+        <v>237.7534332275391</v>
       </c>
       <c r="F9" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" t="n">
-        <v>246.0232549541512</v>
+        <v>238.8441526809671</v>
       </c>
       <c r="C10" t="n">
-        <v>246.1918233421939</v>
+        <v>239.2903800503502</v>
       </c>
       <c r="D10" t="n">
-        <v>237.5352518241517</v>
+        <v>233.915951765761</v>
       </c>
       <c r="E10" t="n">
-        <v>237.7534027099609</v>
+        <v>234.5902404785156</v>
       </c>
       <c r="F10" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="n">
-        <v>238.8441526809671</v>
+        <v>251.0605458824941</v>
       </c>
       <c r="C11" t="n">
-        <v>239.2903800503502</v>
+        <v>254.5806764744798</v>
       </c>
       <c r="D11" t="n">
-        <v>233.915951765761</v>
+        <v>240.6290201908687</v>
       </c>
       <c r="E11" t="n">
-        <v>234.5902404785156</v>
+        <v>243.9310150146484</v>
       </c>
       <c r="F11" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B12" t="n">
-        <v>251.0605458824941</v>
+        <v>244.4962363844956</v>
       </c>
       <c r="C12" t="n">
-        <v>254.5806764744798</v>
+        <v>248.670819810711</v>
       </c>
       <c r="D12" t="n">
-        <v>240.6290201908687</v>
+        <v>240.1233229489625</v>
       </c>
       <c r="E12" t="n">
-        <v>243.9310150146484</v>
+        <v>241.0355834960938</v>
       </c>
       <c r="F12" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="n">
-        <v>244.4962518623618</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C13" t="n">
-        <v>248.6708355528497</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D13" t="n">
-        <v>240.1233381500007</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E13" t="n">
-        <v>241.0355987548828</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F13" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B14" t="n">
-        <v>242.9394234832453</v>
+        <v>252.3595144668565</v>
       </c>
       <c r="C14" t="n">
-        <v>253.2519480605562</v>
+        <v>264.883294034403</v>
       </c>
       <c r="D14" t="n">
-        <v>242.2453138708127</v>
+        <v>251.863719742953</v>
       </c>
       <c r="E14" t="n">
-        <v>252.1413726806641</v>
+        <v>261.194580078125</v>
       </c>
       <c r="F14" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B15" t="n">
-        <v>252.359543952159</v>
+        <v>259.9947719140093</v>
       </c>
       <c r="C15" t="n">
-        <v>264.8833249829649</v>
+        <v>260.1930716520554</v>
       </c>
       <c r="D15" t="n">
-        <v>251.8637491703276</v>
+        <v>254.3526253920043</v>
       </c>
       <c r="E15" t="n">
-        <v>261.1946105957031</v>
+        <v>254.4815368652344</v>
       </c>
       <c r="F15" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B16" t="n">
-        <v>259.9947719140093</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C16" t="n">
-        <v>260.1930716520554</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D16" t="n">
-        <v>254.3526253920043</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E16" t="n">
-        <v>254.4815368652344</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F16" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B17" t="n">
-        <v>255.4334634999039</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C17" t="n">
-        <v>256.3853809552256</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D17" t="n">
-        <v>251.982721115611</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E17" t="n">
-        <v>252.9049072265625</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F17" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B18" t="n">
-        <v>255.254980605377</v>
+        <v>254.9178252470085</v>
       </c>
       <c r="C18" t="n">
-        <v>256.3258839430272</v>
+        <v>255.9292659432784</v>
       </c>
       <c r="D18" t="n">
-        <v>251.8637312244832</v>
+        <v>252.7760033429592</v>
       </c>
       <c r="E18" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213806152344</v>
       </c>
       <c r="F18" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="n">
-        <v>254.917794537107</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="C19" t="n">
-        <v>255.9292351115289</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D19" t="n">
-        <v>252.7759728910826</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E19" t="n">
-        <v>253.3213500976562</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="F19" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B20" t="n">
-        <v>253.3213661855435</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C20" t="n">
-        <v>256.663017898251</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D20" t="n">
-        <v>252.0025503587843</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E20" t="n">
-        <v>252.1215362548828</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F20" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B21" t="n">
-        <v>249.8805444255208</v>
+        <v>248.3931555366784</v>
       </c>
       <c r="C21" t="n">
-        <v>251.4373471434884</v>
+        <v>257.0993096380665</v>
       </c>
       <c r="D21" t="n">
-        <v>246.945432960583</v>
+        <v>247.8973608150483</v>
       </c>
       <c r="E21" t="n">
-        <v>249.3450927734375</v>
+        <v>254.4914245605469</v>
       </c>
       <c r="F21" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B22" t="n">
-        <v>248.3931555366784</v>
+        <v>252.6570304305034</v>
       </c>
       <c r="C22" t="n">
-        <v>257.0993096380665</v>
+        <v>259.617993585316</v>
       </c>
       <c r="D22" t="n">
-        <v>247.8973608150483</v>
+        <v>250.5052828369448</v>
       </c>
       <c r="E22" t="n">
-        <v>254.4914245605469</v>
+        <v>258.2198486328125</v>
       </c>
       <c r="F22" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B23" t="n">
-        <v>252.657000570364</v>
+        <v>257.8132719821094</v>
       </c>
       <c r="C23" t="n">
-        <v>259.6179629024988</v>
+        <v>259.3601491931292</v>
       </c>
       <c r="D23" t="n">
-        <v>250.5052532311086</v>
+        <v>252.9544894469363</v>
       </c>
       <c r="E23" t="n">
-        <v>258.2198181152344</v>
+        <v>259.1419982910156</v>
       </c>
       <c r="F23" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B24" t="n">
-        <v>257.8132719821094</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C24" t="n">
-        <v>259.3601491931292</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D24" t="n">
-        <v>252.9544894469363</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E24" t="n">
-        <v>259.1419982910156</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F24" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B25" t="n">
-        <v>255.9788221233241</v>
+        <v>252.5578552142711</v>
       </c>
       <c r="C25" t="n">
-        <v>257.0795021986246</v>
+        <v>254.6699306658516</v>
       </c>
       <c r="D25" t="n">
-        <v>251.3282801006067</v>
+        <v>249.8904769054258</v>
       </c>
       <c r="E25" t="n">
-        <v>252.3000335693359</v>
+        <v>250.5548400878906</v>
       </c>
       <c r="F25" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B26" t="n">
-        <v>252.5578398334985</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="C26" t="n">
-        <v>254.6699151564536</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="D26" t="n">
-        <v>249.8904616870965</v>
+        <v>232.5078921531912</v>
       </c>
       <c r="E26" t="n">
-        <v>250.5548248291016</v>
+        <v>237.2576141357422</v>
       </c>
       <c r="F26" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B27" t="n">
-        <v>248.4328324243326</v>
+        <v>234.1638481621394</v>
       </c>
       <c r="C27" t="n">
-        <v>248.4328324243326</v>
+        <v>238.943316687993</v>
       </c>
       <c r="D27" t="n">
-        <v>232.5079071065105</v>
+        <v>233.8068753463891</v>
       </c>
       <c r="E27" t="n">
-        <v>237.2576293945312</v>
+        <v>237.8624877929688</v>
       </c>
       <c r="F27" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="n">
-        <v>234.1638631836621</v>
+        <v>237.9814688826704</v>
       </c>
       <c r="C28" t="n">
-        <v>238.9433320161168</v>
+        <v>239.8754083705041</v>
       </c>
       <c r="D28" t="n">
-        <v>233.8068903450121</v>
+        <v>233.1028505862302</v>
       </c>
       <c r="E28" t="n">
-        <v>237.8625030517578</v>
+        <v>239.6770935058594</v>
       </c>
       <c r="F28" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B29" t="n">
-        <v>237.9814840335094</v>
+        <v>239.8654952673756</v>
       </c>
       <c r="C29" t="n">
-        <v>239.8754236419186</v>
+        <v>243.63353841341</v>
       </c>
       <c r="D29" t="n">
-        <v>233.1028654264771</v>
+        <v>239.1317287169831</v>
       </c>
       <c r="E29" t="n">
-        <v>239.6771087646484</v>
+        <v>242.4436340332031</v>
       </c>
       <c r="F29" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B30" t="n">
-        <v>239.865480170848</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="C30" t="n">
-        <v>243.6335230797314</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D30" t="n">
-        <v>239.131713666637</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E30" t="n">
-        <v>242.4436187744141</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="F30" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B31" t="n">
-        <v>243.6732075926712</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C31" t="n">
-        <v>246.3405706207466</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D31" t="n">
-        <v>241.63052052637</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E31" t="n">
-        <v>243.9508514404297</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F31" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="n">
-        <v>243.1873207442872</v>
+        <v>236.3056926086296</v>
       </c>
       <c r="C32" t="n">
-        <v>243.8318478561575</v>
+        <v>243.1179076689137</v>
       </c>
       <c r="D32" t="n">
-        <v>237.8922365355373</v>
+        <v>235.4231785540507</v>
       </c>
       <c r="E32" t="n">
-        <v>238.4078521728516</v>
+        <v>241.6107025146484</v>
       </c>
       <c r="F32" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B33" t="n">
-        <v>236.3056926086296</v>
+        <v>240.0340726996036</v>
       </c>
       <c r="C33" t="n">
-        <v>243.1179076689137</v>
+        <v>240.787675257482</v>
       </c>
       <c r="D33" t="n">
-        <v>235.4231785540507</v>
+        <v>233.6085619749179</v>
       </c>
       <c r="E33" t="n">
-        <v>241.6107025146484</v>
+        <v>235.0364532470703</v>
       </c>
       <c r="F33" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B34" t="n">
-        <v>240.0340726996036</v>
+        <v>234.2531087461558</v>
       </c>
       <c r="C34" t="n">
-        <v>240.787675257482</v>
+        <v>235.7900603656055</v>
       </c>
       <c r="D34" t="n">
-        <v>233.6085619749179</v>
+        <v>228.3333182252886</v>
       </c>
       <c r="E34" t="n">
-        <v>235.0364532470703</v>
+        <v>231.5361480712891</v>
       </c>
       <c r="F34" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B35" t="n">
-        <v>234.2531087461558</v>
+        <v>230.0487686636922</v>
       </c>
       <c r="C35" t="n">
-        <v>235.7900603656055</v>
+        <v>230.3264125188844</v>
       </c>
       <c r="D35" t="n">
-        <v>228.3333182252886</v>
+        <v>223.1671349733107</v>
       </c>
       <c r="E35" t="n">
-        <v>231.5361480712891</v>
+        <v>225.9634246826172</v>
       </c>
       <c r="F35" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B36" t="n">
-        <v>230.0487531290293</v>
+        <v>227.3218898732066</v>
       </c>
       <c r="C36" t="n">
-        <v>230.3263969654728</v>
+        <v>229.1265900019938</v>
       </c>
       <c r="D36" t="n">
-        <v>223.1671199033486</v>
+        <v>221.4219354522067</v>
       </c>
       <c r="E36" t="n">
-        <v>225.9634094238281</v>
+        <v>223.4745178222656</v>
       </c>
       <c r="F36" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B37" t="n">
-        <v>227.3218898732066</v>
+        <v>222.9687986720664</v>
       </c>
       <c r="C37" t="n">
-        <v>229.1265900019938</v>
+        <v>226.7566624070738</v>
       </c>
       <c r="D37" t="n">
-        <v>221.4219354522067</v>
+        <v>220.0931953922465</v>
       </c>
       <c r="E37" t="n">
-        <v>223.4745178222656</v>
+        <v>225.1998748779297</v>
       </c>
       <c r="F37" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B38" t="n">
-        <v>222.9688137796853</v>
+        <v>225.4279691980636</v>
       </c>
       <c r="C38" t="n">
-        <v>226.7566777713456</v>
+        <v>226.9153535529684</v>
       </c>
       <c r="D38" t="n">
-        <v>220.0932103050241</v>
+        <v>223.1473101611184</v>
       </c>
       <c r="E38" t="n">
-        <v>225.1998901367188</v>
+        <v>224.912353515625</v>
       </c>
       <c r="F38" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B39" t="n">
-        <v>225.4279386105234</v>
+        <v>224.8924975422598</v>
       </c>
       <c r="C39" t="n">
-        <v>226.9153227636102</v>
+        <v>232.656645001925</v>
       </c>
       <c r="D39" t="n">
-        <v>223.1472798830329</v>
+        <v>224.614853697738</v>
       </c>
       <c r="E39" t="n">
-        <v>224.9123229980469</v>
+        <v>232.1509246826172</v>
       </c>
       <c r="F39" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B40" t="n">
-        <v>224.8924827605518</v>
+        <v>228.5712919801828</v>
       </c>
       <c r="C40" t="n">
-        <v>232.656629709896</v>
+        <v>230.8618764526245</v>
       </c>
       <c r="D40" t="n">
-        <v>224.6148389342789</v>
+        <v>224.0992287472785</v>
       </c>
       <c r="E40" t="n">
-        <v>232.1509094238281</v>
+        <v>226.2311401367188</v>
       </c>
       <c r="F40" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B41" t="n">
-        <v>228.5712765635558</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C41" t="n">
-        <v>230.8618608815026</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D41" t="n">
-        <v>224.0992136322821</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E41" t="n">
-        <v>226.2311248779297</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F41" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B42" t="n">
-        <v>227.0739873247604</v>
+        <v>226.7467645282661</v>
       </c>
       <c r="C42" t="n">
-        <v>230.6040433967966</v>
+        <v>232.2798356411572</v>
       </c>
       <c r="D42" t="n">
-        <v>226.7071040647147</v>
+        <v>226.6773611325171</v>
       </c>
       <c r="E42" t="n">
-        <v>228.6010284423828</v>
+        <v>230.8717803955078</v>
       </c>
       <c r="F42" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B43" t="n">
-        <v>226.7467495421078</v>
+        <v>231.0602036533118</v>
       </c>
       <c r="C43" t="n">
-        <v>232.2798202893068</v>
+        <v>234.6596634696697</v>
       </c>
       <c r="D43" t="n">
-        <v>226.6773461509458</v>
+        <v>229.6719691901636</v>
       </c>
       <c r="E43" t="n">
-        <v>230.8717651367188</v>
+        <v>232.7359924316406</v>
       </c>
       <c r="F43" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B44" t="n">
-        <v>231.060173355472</v>
+        <v>233.3804933429116</v>
       </c>
       <c r="C44" t="n">
-        <v>234.6596326998496</v>
+        <v>237.2476861421788</v>
       </c>
       <c r="D44" t="n">
-        <v>229.6719390743564</v>
+        <v>231.1989995810056</v>
       </c>
       <c r="E44" t="n">
-        <v>232.7359619140625</v>
+        <v>236.7122344970703</v>
       </c>
       <c r="F44" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B45" t="n">
-        <v>233.3804933429116</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C45" t="n">
-        <v>237.2476861421788</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D45" t="n">
-        <v>231.1989995810056</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E45" t="n">
-        <v>236.7122344970703</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F45" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B46" t="n">
-        <v>241.6404418420451</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C46" t="n">
-        <v>246.8760330652079</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D46" t="n">
-        <v>235.6016655641461</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E46" t="n">
-        <v>245.3787384033203</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F46" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B47" t="n">
-        <v>248.7203919866921</v>
+        <v>259.6774396530913</v>
       </c>
       <c r="C47" t="n">
-        <v>259.6774588065476</v>
+        <v>262.0572481860146</v>
       </c>
       <c r="D47" t="n">
-        <v>247.4015761578514</v>
+        <v>254.1840258460871</v>
       </c>
       <c r="E47" t="n">
-        <v>258.3784790039062</v>
+        <v>257.3471984863281</v>
       </c>
       <c r="F47" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B48" t="n">
-        <v>259.6774396530913</v>
+        <v>257.8132661327708</v>
       </c>
       <c r="C48" t="n">
-        <v>262.0572481860146</v>
+        <v>260.0443424743044</v>
       </c>
       <c r="D48" t="n">
-        <v>254.1840258460871</v>
+        <v>256.8216766476447</v>
       </c>
       <c r="E48" t="n">
-        <v>257.3471984863281</v>
+        <v>258.8246765136719</v>
       </c>
       <c r="F48" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B49" t="n">
-        <v>257.8132661327708</v>
+        <v>258.5569703207904</v>
       </c>
       <c r="C49" t="n">
-        <v>260.0443424743044</v>
+        <v>263.6933968309874</v>
       </c>
       <c r="D49" t="n">
-        <v>256.8216766476447</v>
+        <v>256.9704210183176</v>
       </c>
       <c r="E49" t="n">
-        <v>258.8246765136719</v>
+        <v>261.9779663085938</v>
       </c>
       <c r="F49" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B50" t="n">
-        <v>258.5569100826516</v>
+        <v>261.2838154474661</v>
       </c>
       <c r="C50" t="n">
-        <v>263.6933353961732</v>
+        <v>265.6468028980126</v>
       </c>
       <c r="D50" t="n">
-        <v>256.9703611498102</v>
+        <v>258.5767654029829</v>
       </c>
       <c r="E50" t="n">
-        <v>261.9779052734375</v>
+        <v>260.1434936523438</v>
       </c>
       <c r="F50" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B51" t="n">
-        <v>261.2838154474661</v>
+        <v>261.3036341846645</v>
       </c>
       <c r="C51" t="n">
-        <v>265.6468028980126</v>
+        <v>262.2654771366241</v>
       </c>
       <c r="D51" t="n">
-        <v>258.5767654029829</v>
+        <v>258.7156003126054</v>
       </c>
       <c r="E51" t="n">
-        <v>260.1434936523438</v>
+        <v>260.0245056152344</v>
       </c>
       <c r="F51" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B52" t="n">
-        <v>261.3036341846645</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C52" t="n">
-        <v>262.2654771366241</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D52" t="n">
-        <v>258.7156003126054</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E52" t="n">
-        <v>260.0245056152344</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F52" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B53" t="n">
-        <v>259.013086162544</v>
+        <v>251.8637326884788</v>
       </c>
       <c r="C53" t="n">
-        <v>260.074094195654</v>
+        <v>253.7080897614157</v>
       </c>
       <c r="D53" t="n">
-        <v>250.9613842226157</v>
+        <v>249.989629141015</v>
       </c>
       <c r="E53" t="n">
-        <v>252.4388580322266</v>
+        <v>252.7660827636719</v>
       </c>
       <c r="F53" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B54" t="n">
-        <v>251.8637174841621</v>
+        <v>254.1741282350202</v>
       </c>
       <c r="C54" t="n">
-        <v>253.7080744457603</v>
+        <v>259.7667076505979</v>
       </c>
       <c r="D54" t="n">
-        <v>249.9896140498327</v>
+        <v>254.0948143882558</v>
       </c>
       <c r="E54" t="n">
-        <v>252.7660675048828</v>
+        <v>255.9689331054688</v>
       </c>
       <c r="F54" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B55" t="n">
-        <v>254.1741282350202</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C55" t="n">
-        <v>259.7667076505979</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D55" t="n">
-        <v>254.0948143882558</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E55" t="n">
-        <v>255.9689331054688</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F55" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B56" t="n">
-        <v>256.6602113519941</v>
+        <v>258.9047600313309</v>
       </c>
       <c r="C56" t="n">
-        <v>258.298969034048</v>
+        <v>260.2555141825196</v>
       </c>
       <c r="D56" t="n">
-        <v>254.415591918658</v>
+        <v>253.760043143314</v>
       </c>
       <c r="E56" t="n">
-        <v>256.0940856933594</v>
+        <v>258.1400146484375</v>
       </c>
       <c r="F56" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G56" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B57" t="n">
-        <v>258.904790639318</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="C57" t="n">
-        <v>260.2555449501942</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D57" t="n">
-        <v>253.7600731430874</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E57" t="n">
-        <v>258.1400451660156</v>
+        <v>262.827880859375</v>
       </c>
       <c r="F57" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B58" t="n">
-        <v>258.8451791646396</v>
+        <v>260.930890915143</v>
       </c>
       <c r="C58" t="n">
-        <v>262.827880859375</v>
+        <v>262.4405288782817</v>
       </c>
       <c r="D58" t="n">
-        <v>256.6502376986757</v>
+        <v>258.7458606831942</v>
       </c>
       <c r="E58" t="n">
-        <v>262.827880859375</v>
+        <v>261.6360473632812</v>
       </c>
       <c r="F58" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B59" t="n">
-        <v>260.930890915143</v>
+        <v>261.4374386085776</v>
       </c>
       <c r="C59" t="n">
-        <v>262.4405288782817</v>
+        <v>264.486509153036</v>
       </c>
       <c r="D59" t="n">
-        <v>258.7458606831942</v>
+        <v>260.7620463111714</v>
       </c>
       <c r="E59" t="n">
-        <v>261.6360473632812</v>
+        <v>263.45361328125</v>
       </c>
       <c r="F59" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B60" t="n">
-        <v>261.4374083245464</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="C60" t="n">
-        <v>264.4864785158107</v>
+        <v>266.0855294787636</v>
       </c>
       <c r="D60" t="n">
-        <v>260.7620161053754</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="E60" t="n">
-        <v>263.4535827636719</v>
+        <v>264.2679748535156</v>
       </c>
       <c r="F60" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B61" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C61" t="n">
-        <v>266.0855294787636</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D61" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E61" t="n">
-        <v>264.2679748535156</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F61" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B62" t="n">
-        <v>262.9073239460033</v>
+        <v>264.8440512488132</v>
       </c>
       <c r="C62" t="n">
-        <v>267.2773540092613</v>
+        <v>266.4530142126886</v>
       </c>
       <c r="D62" t="n">
-        <v>262.9073239460033</v>
+        <v>263.5230915643202</v>
       </c>
       <c r="E62" t="n">
-        <v>264.4169921875</v>
+        <v>264.1091003417969</v>
       </c>
       <c r="F62" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B63" t="n">
-        <v>264.8440818513142</v>
+        <v>263.4833740671746</v>
       </c>
       <c r="C63" t="n">
-        <v>266.453045001104</v>
+        <v>264.2878555133287</v>
       </c>
       <c r="D63" t="n">
-        <v>263.5231220141856</v>
+        <v>262.5895091614203</v>
       </c>
       <c r="E63" t="n">
-        <v>264.109130859375</v>
+        <v>263.10595703125</v>
       </c>
       <c r="F63" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>263.4833740671746</v>
+        <v>263.1953602739627</v>
       </c>
       <c r="C64" t="n">
-        <v>264.2878555133287</v>
+        <v>263.5727773382559</v>
       </c>
       <c r="D64" t="n">
-        <v>262.5895091614203</v>
+        <v>250.7606167452008</v>
       </c>
       <c r="E64" t="n">
-        <v>263.10595703125</v>
+        <v>251.8928527832031</v>
       </c>
       <c r="F64" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B65" t="n">
-        <v>263.1953762174182</v>
+        <v>251.8928562905814</v>
       </c>
       <c r="C65" t="n">
-        <v>263.572793304574</v>
+        <v>257.8222021169872</v>
       </c>
       <c r="D65" t="n">
-        <v>250.760631935403</v>
+        <v>250.5917797464572</v>
       </c>
       <c r="E65" t="n">
-        <v>251.8928680419922</v>
+        <v>254.514892578125</v>
       </c>
       <c r="F65" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B66" t="n">
-        <v>251.8928411889898</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C66" t="n">
-        <v>257.8221866599169</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D66" t="n">
-        <v>250.5917647228683</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E66" t="n">
-        <v>254.5148773193359</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F66" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B67" t="n">
-        <v>253.4621191746895</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="C67" t="n">
-        <v>261.7552477009523</v>
+        <v>266.0060858079951</v>
       </c>
       <c r="D67" t="n">
-        <v>253.2634841788583</v>
+        <v>261.7055860975985</v>
       </c>
       <c r="E67" t="n">
-        <v>261.1096801757812</v>
+        <v>264.3077392578125</v>
       </c>
       <c r="F67" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B68" t="n">
-        <v>261.7055558804709</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C68" t="n">
-        <v>266.0060550943219</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D68" t="n">
-        <v>261.7055558804709</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E68" t="n">
-        <v>264.3077087402344</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F68" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B69" t="n">
-        <v>262.5994389217771</v>
+        <v>258.2294193019395</v>
       </c>
       <c r="C69" t="n">
-        <v>263.394009134812</v>
+        <v>259.2524038660146</v>
       </c>
       <c r="D69" t="n">
-        <v>258.6366203853271</v>
+        <v>254.7631956419699</v>
       </c>
       <c r="E69" t="n">
-        <v>258.7557983398438</v>
+        <v>258.1698303222656</v>
       </c>
       <c r="F69" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B70" t="n">
-        <v>258.2294193019395</v>
+        <v>257.2362444131007</v>
       </c>
       <c r="C70" t="n">
-        <v>259.2524038660146</v>
+        <v>259.778808728465</v>
       </c>
       <c r="D70" t="n">
-        <v>254.7631956419699</v>
+        <v>254.0282445272995</v>
       </c>
       <c r="E70" t="n">
-        <v>258.1698303222656</v>
+        <v>257.6335144042969</v>
       </c>
       <c r="F70" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B71" t="n">
-        <v>257.2362139425806</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C71" t="n">
-        <v>259.7787779567694</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D71" t="n">
-        <v>254.028214436778</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E71" t="n">
-        <v>257.6334838867188</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F71" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B72" t="n">
-        <v>255.9053572301452</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C72" t="n">
-        <v>259.1332249596227</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D72" t="n">
-        <v>238.7231659776434</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E72" t="n">
-        <v>239.4183959960938</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F72" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B73" t="n">
-        <v>237.5511941796288</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C73" t="n">
-        <v>240.5903685304685</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D73" t="n">
-        <v>234.849731125901</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E73" t="n">
-        <v>237.9385528564453</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F73" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B74" t="n">
-        <v>235.4059054123066</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C74" t="n">
-        <v>237.2135033883542</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D74" t="n">
-        <v>230.0923326840245</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E74" t="n">
-        <v>231.9396667480469</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F74" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B75" t="n">
-        <v>231.3636110626874</v>
+        <v>222.0176902636222</v>
       </c>
       <c r="C75" t="n">
-        <v>231.3636110626874</v>
+        <v>226.3877354418118</v>
       </c>
       <c r="D75" t="n">
-        <v>224.8979495180149</v>
+        <v>217.8661632569629</v>
       </c>
       <c r="E75" t="n">
-        <v>225.5633850097656</v>
+        <v>218.5713348388672</v>
       </c>
       <c r="F75" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B76" t="n">
-        <v>222.0177057630064</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="C76" t="n">
-        <v>226.3877512462753</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D76" t="n">
-        <v>217.8661784665229</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E76" t="n">
-        <v>218.5713500976562</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="F76" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B77" t="n">
-        <v>218.6507904829158</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C77" t="n">
-        <v>221.8687318042425</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D77" t="n">
-        <v>217.4689070154735</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E77" t="n">
-        <v>220.0710601806641</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F77" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B78" t="n">
-        <v>220.7265600038705</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="C78" t="n">
-        <v>227.162427221411</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D78" t="n">
-        <v>219.6042504088122</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E78" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="F78" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B79" t="n">
-        <v>225.2356384112152</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C79" t="n">
-        <v>229.2779291905748</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D79" t="n">
-        <v>225.1065188551059</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E79" t="n">
-        <v>226.4969940185547</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F79" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B80" t="n">
-        <v>227.8675935623777</v>
+        <v>230.3604906379282</v>
       </c>
       <c r="C80" t="n">
-        <v>229.3772467325265</v>
+        <v>234.1346156625655</v>
       </c>
       <c r="D80" t="n">
-        <v>226.0401274460743</v>
+        <v>224.7291051659704</v>
       </c>
       <c r="E80" t="n">
-        <v>227.8377990722656</v>
+        <v>226.9737091064453</v>
       </c>
       <c r="F80" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B81" t="n">
-        <v>230.3604906379282</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="C81" t="n">
-        <v>234.1346156625655</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D81" t="n">
-        <v>224.7291051659704</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E81" t="n">
-        <v>226.9737091064453</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="F81" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B82" t="n">
-        <v>227.8278625141174</v>
+        <v>215.1944899838427</v>
       </c>
       <c r="C82" t="n">
-        <v>230.2810431236355</v>
+        <v>215.8003365308671</v>
       </c>
       <c r="D82" t="n">
-        <v>226.1195744340916</v>
+        <v>207.3582209619344</v>
       </c>
       <c r="E82" t="n">
-        <v>226.4076080322266</v>
+        <v>212.6221313476562</v>
       </c>
       <c r="F82" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B83" t="n">
-        <v>215.1944745404488</v>
+        <v>212.7015749295142</v>
       </c>
       <c r="C83" t="n">
-        <v>215.8003210439947</v>
+        <v>214.0821084291109</v>
       </c>
       <c r="D83" t="n">
-        <v>207.358206080909</v>
+        <v>209.5928853669118</v>
       </c>
       <c r="E83" t="n">
-        <v>212.6221160888672</v>
+        <v>210.8442993164062</v>
       </c>
       <c r="F83" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B84" t="n">
-        <v>212.7015749295142</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C84" t="n">
-        <v>214.0821084291109</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D84" t="n">
-        <v>209.5928853669118</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E84" t="n">
-        <v>210.8442993164062</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F84" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B85" t="n">
-        <v>212.8902908724165</v>
+        <v>203.6039568110546</v>
       </c>
       <c r="C85" t="n">
-        <v>215.4129869027477</v>
+        <v>204.16014080488</v>
       </c>
       <c r="D85" t="n">
-        <v>208.3712731650351</v>
+        <v>191.7949279222085</v>
       </c>
       <c r="E85" t="n">
-        <v>209.3743896484375</v>
+        <v>195.0426635742188</v>
       </c>
       <c r="F85" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B86" t="n">
-        <v>203.6039568110546</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C86" t="n">
-        <v>204.16014080488</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D86" t="n">
-        <v>191.7949279222085</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E86" t="n">
-        <v>195.0426635742188</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F86" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B87" t="n">
-        <v>191.993558028148</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C87" t="n">
-        <v>199.3034370934686</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D87" t="n">
-        <v>186.0046234920971</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E87" t="n">
-        <v>198.0818176269531</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F87" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B88" t="n">
-        <v>192.668943558262</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C88" t="n">
-        <v>198.2010042649258</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D88" t="n">
-        <v>187.5043431662378</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E88" t="n">
-        <v>188.6763153076172</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F88" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B89" t="n">
-        <v>190.3250127759971</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C89" t="n">
-        <v>193.2747884158856</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D89" t="n">
-        <v>185.8457159832669</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E89" t="n">
-        <v>190.0469207763672</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F89" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" t="n">
-        <v>188.0108792533576</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C90" t="n">
-        <v>193.8706944788449</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D90" t="n">
-        <v>184.465183505092</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E90" t="n">
-        <v>192.7086639404297</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F90" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B91" t="n">
-        <v>190.5931665112882</v>
+        <v>191.8346508751069</v>
       </c>
       <c r="C91" t="n">
-        <v>197.7441470694129</v>
+        <v>192.3511139411869</v>
       </c>
       <c r="D91" t="n">
-        <v>189.4510040038842</v>
+        <v>180.5718794169307</v>
       </c>
       <c r="E91" t="n">
-        <v>192.1326141357422</v>
+        <v>183.7401580810547</v>
       </c>
       <c r="F91" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B92" t="n">
-        <v>191.8346349441069</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C92" t="n">
-        <v>192.3510979672969</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D92" t="n">
-        <v>180.5718644212529</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E92" t="n">
-        <v>183.7401428222656</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F92" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B93" t="n">
-        <v>184.6936257308121</v>
+        <v>185.1703620229303</v>
       </c>
       <c r="C93" t="n">
-        <v>187.0375548215625</v>
+        <v>192.1326190686923</v>
       </c>
       <c r="D93" t="n">
-        <v>179.012577513483</v>
+        <v>183.0449358454951</v>
       </c>
       <c r="E93" t="n">
-        <v>184.1672210693359</v>
+        <v>188.4280242919922</v>
       </c>
       <c r="F93" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B94" t="n">
-        <v>185.1703470279448</v>
+        <v>189.6694900334161</v>
       </c>
       <c r="C94" t="n">
-        <v>192.1326035099074</v>
+        <v>191.6856644627849</v>
       </c>
       <c r="D94" t="n">
-        <v>183.0449210226253</v>
+        <v>181.9226052262247</v>
       </c>
       <c r="E94" t="n">
-        <v>188.4280090332031</v>
+        <v>183.0349731445312</v>
       </c>
       <c r="F94" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B95" t="n">
-        <v>189.6695058452945</v>
+        <v>182.6277776277465</v>
       </c>
       <c r="C95" t="n">
-        <v>191.6856804427425</v>
+        <v>186.8587614695496</v>
       </c>
       <c r="D95" t="n">
-        <v>181.9226203922807</v>
+        <v>180.6215296329567</v>
       </c>
       <c r="E95" t="n">
-        <v>183.0349884033203</v>
+        <v>186.5111389160156</v>
       </c>
       <c r="F95" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B96" t="n">
-        <v>182.6277925688313</v>
+        <v>185.3292593497056</v>
       </c>
       <c r="C96" t="n">
-        <v>186.8587767567783</v>
+        <v>185.6768667554436</v>
       </c>
       <c r="D96" t="n">
-        <v>180.6215444099069</v>
+        <v>181.9821987572526</v>
       </c>
       <c r="E96" t="n">
-        <v>186.5111541748047</v>
+        <v>184.0281677246094</v>
       </c>
       <c r="F96" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B97" t="n">
-        <v>185.3292747163753</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C97" t="n">
-        <v>185.6768821509354</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D97" t="n">
-        <v>181.9822138463991</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E97" t="n">
-        <v>184.0281829833984</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F97" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B98" t="n">
-        <v>184.0579771467211</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C98" t="n">
-        <v>190.4243134969296</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D98" t="n">
-        <v>182.4787935369736</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E98" t="n">
-        <v>183.8990631103516</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F98" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B99" t="n">
-        <v>180.0355685556146</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C99" t="n">
-        <v>181.2273936107796</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D99" t="n">
-        <v>173.3811981056387</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E99" t="n">
-        <v>176.9467468261719</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F99" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" t="n">
-        <v>176.4302852446972</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C100" t="n">
-        <v>187.3851706171715</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D100" t="n">
-        <v>175.0795461293982</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E100" t="n">
-        <v>184.1573028564453</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F100" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="n">
-        <v>181.7537853733346</v>
+        <v>195.420066371549</v>
       </c>
       <c r="C101" t="n">
-        <v>191.2884162417558</v>
+        <v>199.6709185207204</v>
       </c>
       <c r="D101" t="n">
-        <v>181.0188192554131</v>
+        <v>190.0270517409182</v>
       </c>
       <c r="E101" t="n">
-        <v>190.4441986083984</v>
+        <v>198.1116180419922</v>
       </c>
       <c r="F101" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B102" t="n">
-        <v>195.4200513200664</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C102" t="n">
-        <v>199.6709031418322</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D102" t="n">
-        <v>190.0270371048119</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E102" t="n">
-        <v>198.1116027832031</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F102" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B103" t="n">
-        <v>190.6031086414411</v>
+        <v>191.1890691316076</v>
       </c>
       <c r="C103" t="n">
-        <v>194.5857953386064</v>
+        <v>194.6056450515189</v>
       </c>
       <c r="D103" t="n">
-        <v>188.6266549601705</v>
+        <v>189.38145611275</v>
       </c>
       <c r="E103" t="n">
-        <v>193.4634857177734</v>
+        <v>191.6360015869141</v>
       </c>
       <c r="F103" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B104" t="n">
-        <v>191.1890843548102</v>
+        <v>189.4510095395255</v>
       </c>
       <c r="C104" t="n">
-        <v>194.6056605467623</v>
+        <v>197.3170732284266</v>
       </c>
       <c r="D104" t="n">
-        <v>189.3814711920236</v>
+        <v>188.2889789535958</v>
       </c>
       <c r="E104" t="n">
-        <v>191.6360168457031</v>
+        <v>194.7149200439453</v>
       </c>
       <c r="F104" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B105" t="n">
-        <v>189.4509946932415</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C105" t="n">
-        <v>197.3170577657204</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D105" t="n">
-        <v>188.2889641983741</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E105" t="n">
-        <v>194.7149047851562</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F105" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B106" t="n">
-        <v>193.771369445172</v>
+        <v>193.0364294600736</v>
       </c>
       <c r="C106" t="n">
-        <v>195.1320348561704</v>
+        <v>203.0279194939781</v>
       </c>
       <c r="D106" t="n">
-        <v>190.7917995315397</v>
+        <v>192.9172514970062</v>
       </c>
       <c r="E106" t="n">
-        <v>191.7651214599609</v>
+        <v>200.0185546875</v>
       </c>
       <c r="F106" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B107" t="n">
-        <v>193.036414733929</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C107" t="n">
-        <v>203.027904005614</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D107" t="n">
-        <v>192.9172367799533</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E107" t="n">
-        <v>200.0185394287109</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F107" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B108" t="n">
-        <v>199.4226244314719</v>
+        <v>197.2078193049057</v>
       </c>
       <c r="C108" t="n">
-        <v>201.5778601866405</v>
+        <v>202.2830212056148</v>
       </c>
       <c r="D108" t="n">
-        <v>196.0259162627038</v>
+        <v>194.5361355724457</v>
       </c>
       <c r="E108" t="n">
-        <v>200.733642578125</v>
+        <v>197.4362487792969</v>
       </c>
       <c r="F108" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B109" t="n">
-        <v>197.2078040637707</v>
+        <v>195.9166595935153</v>
       </c>
       <c r="C109" t="n">
-        <v>202.2830055722447</v>
+        <v>198.2109412897675</v>
       </c>
       <c r="D109" t="n">
-        <v>194.5361205377908</v>
+        <v>189.3020255204881</v>
       </c>
       <c r="E109" t="n">
-        <v>197.4362335205078</v>
+        <v>193.5826721191406</v>
       </c>
       <c r="F109" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B110" t="n">
-        <v>195.9166750362765</v>
+        <v>195.0625292691439</v>
       </c>
       <c r="C110" t="n">
-        <v>198.2109569133711</v>
+        <v>198.1910871721164</v>
       </c>
       <c r="D110" t="n">
-        <v>189.3020404418633</v>
+        <v>189.987327259986</v>
       </c>
       <c r="E110" t="n">
-        <v>193.5826873779297</v>
+        <v>192.8079986572266</v>
       </c>
       <c r="F110" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B111" t="n">
-        <v>195.0625138319317</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C111" t="n">
-        <v>198.1910714873107</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D111" t="n">
-        <v>189.9873122244243</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E111" t="n">
-        <v>192.8079833984375</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F111" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B112" t="n">
-        <v>192.8079750209554</v>
+        <v>198.3698512203022</v>
       </c>
       <c r="C112" t="n">
-        <v>203.4648992272838</v>
+        <v>199.6312068702612</v>
       </c>
       <c r="D112" t="n">
-        <v>191.8346379323055</v>
+        <v>190.4441985938934</v>
       </c>
       <c r="E112" t="n">
-        <v>197.9228973388672</v>
+        <v>191.516845703125</v>
       </c>
       <c r="F112" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B113" t="n">
-        <v>198.3698354155112</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C113" t="n">
-        <v>199.6311909649738</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D113" t="n">
-        <v>190.4441834205658</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E113" t="n">
-        <v>191.5168304443359</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F113" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B114" t="n">
-        <v>193.8210400352253</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C114" t="n">
-        <v>197.277352460538</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D114" t="n">
-        <v>193.8210400352253</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E114" t="n">
-        <v>196.9893188476562</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F114" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B115" t="n">
-        <v>196.870136689126</v>
+        <v>192.0829395046699</v>
       </c>
       <c r="C115" t="n">
-        <v>201.0018110133274</v>
+        <v>194.8142119985075</v>
       </c>
       <c r="D115" t="n">
-        <v>193.1258058856387</v>
+        <v>191.3281205621285</v>
       </c>
       <c r="E115" t="n">
-        <v>193.9799499511719</v>
+        <v>193.0165405273438</v>
       </c>
       <c r="F115" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B116" t="n">
-        <v>192.0829546896537</v>
+        <v>194.2580448499211</v>
       </c>
       <c r="C116" t="n">
-        <v>194.8142273994103</v>
+        <v>199.0352867281362</v>
       </c>
       <c r="D116" t="n">
-        <v>191.3281356874407</v>
+        <v>191.9836462262046</v>
       </c>
       <c r="E116" t="n">
-        <v>193.0165557861328</v>
+        <v>193.6621398925781</v>
       </c>
       <c r="F116" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B117" t="n">
-        <v>194.2580295441802</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C117" t="n">
-        <v>199.0352710459927</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D117" t="n">
-        <v>191.9836310996653</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E117" t="n">
-        <v>193.6621246337891</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F117" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B118" t="n">
-        <v>191.8942484911283</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C118" t="n">
-        <v>194.3374874288811</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D118" t="n">
-        <v>188.7061018910339</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E118" t="n">
-        <v>194.0494689941406</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F118" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B119" t="n">
-        <v>195.7478267440036</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C119" t="n">
-        <v>196.7012958768407</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D119" t="n">
-        <v>190.6924929381777</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E119" t="n">
-        <v>193.850830078125</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F119" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B120" t="n">
-        <v>190.8315397252546</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="C120" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D120" t="n">
-        <v>181.0486114593648</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E120" t="n">
-        <v>181.7736511230469</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="F120" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B121" t="n">
-        <v>184.4353921172228</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C121" t="n">
-        <v>186.1138857525603</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D121" t="n">
-        <v>178.6252393274517</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E121" t="n">
-        <v>180.7208709716797</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F121" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B122" t="n">
-        <v>179.9461742219026</v>
+        <v>182.7469769199218</v>
       </c>
       <c r="C122" t="n">
-        <v>186.1933484091056</v>
+        <v>182.8562284362321</v>
       </c>
       <c r="D122" t="n">
-        <v>178.3074166263376</v>
+        <v>177.6022595179307</v>
       </c>
       <c r="E122" t="n">
-        <v>184.3758087158203</v>
+        <v>178.0889129638672</v>
       </c>
       <c r="F122" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="n">
-        <v>182.7469612620264</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C123" t="n">
-        <v>182.8562127689759</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D123" t="n">
-        <v>177.6022443008385</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E123" t="n">
-        <v>178.0888977050781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F123" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>178.873523844959</v>
+        <v>183.6408226716892</v>
       </c>
       <c r="C124" t="n">
-        <v>185.1206822343098</v>
+        <v>187.2163126895138</v>
       </c>
       <c r="D124" t="n">
-        <v>178.3570608051074</v>
+        <v>181.0684642406058</v>
       </c>
       <c r="E124" t="n">
-        <v>183.7699432373047</v>
+        <v>185.3987731933594</v>
       </c>
       <c r="F124" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" t="n">
-        <v>183.6408377857945</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C125" t="n">
-        <v>187.216328097891</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D125" t="n">
-        <v>181.0684791429995</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E125" t="n">
-        <v>185.3987884521484</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F125" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="n">
-        <v>185.5775567084869</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C126" t="n">
-        <v>187.6930410934417</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D126" t="n">
-        <v>181.7636956083204</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E126" t="n">
-        <v>184.9717102050781</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F126" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B127" t="n">
-        <v>184.0381320953261</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C127" t="n">
-        <v>186.3026043544238</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D127" t="n">
-        <v>180.3434636399818</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E127" t="n">
-        <v>185.9053192138672</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F127" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" t="n">
-        <v>186.2231237330043</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C128" t="n">
-        <v>186.8587647224845</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D128" t="n">
-        <v>182.3496888213084</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E128" t="n">
-        <v>183.7699432373047</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F128" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B129" t="n">
-        <v>183.690504131923</v>
+        <v>185.2299504420264</v>
       </c>
       <c r="C129" t="n">
-        <v>185.3094088283374</v>
+        <v>185.4981160077481</v>
       </c>
       <c r="D129" t="n">
-        <v>180.7804644422889</v>
+        <v>174.5829515420302</v>
       </c>
       <c r="E129" t="n">
-        <v>181.7140655517578</v>
+        <v>175.1689300537109</v>
       </c>
       <c r="F129" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,25 +3797,25 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B130" t="n">
-        <v>185.229934306832</v>
+        <v>172.4208565486944</v>
       </c>
       <c r="C130" t="n">
-        <v>185.498099849194</v>
+        <v>173.5360065139178</v>
       </c>
       <c r="D130" t="n">
-        <v>174.5829363342851</v>
+        <v>166.3970260969056</v>
       </c>
       <c r="E130" t="n">
-        <v>175.1689147949219</v>
+        <v>170.1109008789062</v>
       </c>
       <c r="F130" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -3823,25 +3823,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B131" t="n">
-        <v>172.4208720146844</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C131" t="n">
-        <v>173.5360220799356</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D131" t="n">
-        <v>166.3970410225636</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E131" t="n">
-        <v>170.1109161376953</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F131" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G131" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B132" t="n">
-        <v>170.5191174814139</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C132" t="n">
-        <v>170.5191174814139</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D132" t="n">
-        <v>162.8126107290287</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E132" t="n">
-        <v>164.2463836669922</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F132" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B133" t="n">
-        <v>166.3273444705899</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C133" t="n">
-        <v>172.6498652447362</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D133" t="n">
-        <v>165.0528829680655</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E133" t="n">
-        <v>172.0723876953125</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F133" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="n">
-        <v>174.4520463656914</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C134" t="n">
-        <v>176.7321331165696</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D134" t="n">
-        <v>169.7624151908458</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E134" t="n">
-        <v>170.5689086914062</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F134" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B135" t="n">
-        <v>173.4663277892384</v>
+        <v>183.2040230257668</v>
       </c>
       <c r="C135" t="n">
-        <v>178.842961383224</v>
+        <v>183.7516467853238</v>
       </c>
       <c r="D135" t="n">
-        <v>172.1321282578628</v>
+        <v>177.7975202909648</v>
       </c>
       <c r="E135" t="n">
-        <v>176.8317108154297</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F135" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B136" t="n">
-        <v>183.2040075329009</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C136" t="n">
-        <v>183.7516312461474</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D136" t="n">
-        <v>177.7975052553062</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E136" t="n">
-        <v>180.43603515625</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F136" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="n">
-        <v>184.6278268926657</v>
+        <v>181.7104926433502</v>
       </c>
       <c r="C137" t="n">
-        <v>187.1667986912511</v>
+        <v>188.1823732032504</v>
       </c>
       <c r="D137" t="n">
-        <v>180.2468672661974</v>
+        <v>181.33213168739</v>
       </c>
       <c r="E137" t="n">
-        <v>181.3520660400391</v>
+        <v>185.4641876220703</v>
       </c>
       <c r="F137" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B138" t="n">
-        <v>181.7105075933097</v>
+        <v>185.7927793430547</v>
       </c>
       <c r="C138" t="n">
-        <v>188.1823886856741</v>
+        <v>192.7226620565929</v>
       </c>
       <c r="D138" t="n">
-        <v>181.3321466062204</v>
+        <v>183.3035942778625</v>
       </c>
       <c r="E138" t="n">
-        <v>185.4642028808594</v>
+        <v>186.3005676269531</v>
       </c>
       <c r="F138" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B139" t="n">
-        <v>185.7927641258556</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C139" t="n">
-        <v>192.7226462718077</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D139" t="n">
-        <v>183.303579264538</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E139" t="n">
-        <v>186.3005523681641</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F139" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B140" t="n">
-        <v>187.3858431404722</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C140" t="n">
-        <v>190.3230783921826</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D140" t="n">
-        <v>186.2209063874661</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E140" t="n">
-        <v>188.9789276123047</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F140" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B141" t="n">
-        <v>176.7918740224492</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C141" t="n">
-        <v>178.0962045390804</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D141" t="n">
-        <v>169.9117629967484</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E141" t="n">
-        <v>172.5503082275391</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F141" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B142" t="n">
-        <v>174.8602617765654</v>
+        <v>177.4888357619529</v>
       </c>
       <c r="C142" t="n">
-        <v>177.6780209996891</v>
+        <v>183.4927485632761</v>
       </c>
       <c r="D142" t="n">
-        <v>173.6455382897692</v>
+        <v>176.7420802872333</v>
       </c>
       <c r="E142" t="n">
-        <v>177.3892822265625</v>
+        <v>179.4005279541016</v>
       </c>
       <c r="F142" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="n">
-        <v>177.4888508581443</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C143" t="n">
-        <v>183.4927641701262</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D143" t="n">
-        <v>176.7420953199099</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E143" t="n">
-        <v>179.4005432128906</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F143" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B144" t="n">
-        <v>181.6407975504903</v>
+        <v>178.4247846039299</v>
       </c>
       <c r="C144" t="n">
-        <v>183.6221942474171</v>
+        <v>180.993625445577</v>
       </c>
       <c r="D144" t="n">
-        <v>180.5356140136719</v>
+        <v>176.5827967489585</v>
       </c>
       <c r="E144" t="n">
-        <v>180.5356140136719</v>
+        <v>180.4360504150391</v>
       </c>
       <c r="F144" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B145" t="n">
-        <v>178.424769515226</v>
+        <v>177.5286895189733</v>
       </c>
       <c r="C145" t="n">
-        <v>180.993610139636</v>
+        <v>177.9170017981234</v>
       </c>
       <c r="D145" t="n">
-        <v>176.5827818160244</v>
+        <v>172.2516139153796</v>
       </c>
       <c r="E145" t="n">
-        <v>180.43603515625</v>
+        <v>175.7663421630859</v>
       </c>
       <c r="F145" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B146" t="n">
-        <v>177.5286741071897</v>
+        <v>181.4018421076459</v>
       </c>
       <c r="C146" t="n">
-        <v>177.9169863526292</v>
+        <v>185.2351777570901</v>
       </c>
       <c r="D146" t="n">
-        <v>172.2515989617143</v>
+        <v>177.9767212373249</v>
       </c>
       <c r="E146" t="n">
-        <v>175.7663269042969</v>
+        <v>183.0247955322266</v>
       </c>
       <c r="F146" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B147" t="n">
-        <v>181.4018572311292</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C147" t="n">
-        <v>185.2351932001588</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D147" t="n">
-        <v>177.9767360752557</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E147" t="n">
-        <v>183.0248107910156</v>
+        <v>184.6775970458984</v>
       </c>
       <c r="F147" t="n">
-        <v>12324400</v>
+        <v>8444700</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="n">
-        <v>183.4429710909726</v>
+        <v>184.7473182824849</v>
       </c>
       <c r="C148" t="n">
-        <v>189.4867039708132</v>
+        <v>186.5793548412774</v>
       </c>
       <c r="D148" t="n">
-        <v>183.1741348747832</v>
+        <v>180.3165719120649</v>
       </c>
       <c r="E148" t="n">
-        <v>184.6775970458984</v>
+        <v>186.1810913085938</v>
       </c>
       <c r="F148" t="n">
-        <v>8444700</v>
+        <v>9740800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="n">
-        <v>184.7473182824849</v>
+        <v>184.7174439304337</v>
       </c>
       <c r="C149" t="n">
-        <v>186.5793548412774</v>
+        <v>186.2906106667237</v>
       </c>
       <c r="D149" t="n">
-        <v>180.3165719120649</v>
+        <v>178.8031379653169</v>
       </c>
       <c r="E149" t="n">
-        <v>186.1810913085938</v>
+        <v>180.4061737060547</v>
       </c>
       <c r="F149" t="n">
-        <v>9740800</v>
+        <v>11303400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="n">
-        <v>184.7174439304337</v>
+        <v>183.801426731489</v>
       </c>
       <c r="C150" t="n">
-        <v>186.2906106667237</v>
+        <v>187.7642050029951</v>
       </c>
       <c r="D150" t="n">
-        <v>178.8031379653169</v>
+        <v>183.2040162535504</v>
       </c>
       <c r="E150" t="n">
-        <v>180.4061737060547</v>
+        <v>185.5338897705078</v>
       </c>
       <c r="F150" t="n">
-        <v>11303400</v>
+        <v>13955100</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B151" t="n">
-        <v>183.801426731489</v>
+        <v>178.9027054786904</v>
       </c>
       <c r="C151" t="n">
-        <v>187.7642050029951</v>
+        <v>181.0832340725416</v>
       </c>
       <c r="D151" t="n">
-        <v>183.2040162535504</v>
+        <v>176.114830301217</v>
       </c>
       <c r="E151" t="n">
-        <v>185.5338897705078</v>
+        <v>181.0334625244141</v>
       </c>
       <c r="F151" t="n">
-        <v>13955100</v>
+        <v>15123900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B152" t="n">
-        <v>178.9027054786904</v>
+        <v>179.1317124775628</v>
       </c>
       <c r="C152" t="n">
-        <v>181.0832340725416</v>
+        <v>181.7105044839724</v>
       </c>
       <c r="D152" t="n">
-        <v>176.114830301217</v>
+        <v>175.5472800106302</v>
       </c>
       <c r="E152" t="n">
-        <v>181.0334625244141</v>
+        <v>176.7221832275391</v>
       </c>
       <c r="F152" t="n">
-        <v>15123900</v>
+        <v>11145000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B153" t="n">
-        <v>179.1317124775628</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="C153" t="n">
-        <v>181.7105044839724</v>
+        <v>176.8117888588543</v>
       </c>
       <c r="D153" t="n">
-        <v>175.5472800106302</v>
+        <v>169.8420709331304</v>
       </c>
       <c r="E153" t="n">
-        <v>176.7221832275391</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F153" t="n">
-        <v>11145000</v>
+        <v>10214000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B154" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="C154" t="n">
-        <v>176.8117888588543</v>
+        <v>169.0455318751909</v>
       </c>
       <c r="D154" t="n">
-        <v>169.8420709331304</v>
+        <v>164.0372928300067</v>
       </c>
       <c r="E154" t="n">
-        <v>170.5689086914062</v>
+        <v>165.1225738525391</v>
       </c>
       <c r="F154" t="n">
-        <v>10214000</v>
+        <v>11951900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B155" t="n">
-        <v>169.0455318751909</v>
+        <v>165.2818899628073</v>
       </c>
       <c r="C155" t="n">
-        <v>169.0455318751909</v>
+        <v>168.6174040602531</v>
       </c>
       <c r="D155" t="n">
-        <v>164.0372928300067</v>
+        <v>163.6191161459536</v>
       </c>
       <c r="E155" t="n">
-        <v>165.1225738525391</v>
+        <v>166.8550567626953</v>
       </c>
       <c r="F155" t="n">
-        <v>11951900</v>
+        <v>9749400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" t="n">
-        <v>165.2818748478833</v>
+        <v>168.5178185348167</v>
       </c>
       <c r="C156" t="n">
-        <v>168.6173886402985</v>
+        <v>175.208748793394</v>
       </c>
       <c r="D156" t="n">
-        <v>163.6191011830893</v>
+        <v>168.268900043628</v>
       </c>
       <c r="E156" t="n">
-        <v>166.8550415039062</v>
+        <v>172.7593841552734</v>
       </c>
       <c r="F156" t="n">
-        <v>9749400</v>
+        <v>13883400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B157" t="n">
-        <v>168.5178185348167</v>
+        <v>172.1420794089453</v>
       </c>
       <c r="C157" t="n">
-        <v>175.208748793394</v>
+        <v>179.9979467596552</v>
       </c>
       <c r="D157" t="n">
-        <v>168.268900043628</v>
+        <v>171.0567983816156</v>
       </c>
       <c r="E157" t="n">
-        <v>172.7593841552734</v>
+        <v>178.7035675048828</v>
       </c>
       <c r="F157" t="n">
-        <v>13883400</v>
+        <v>13671200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B158" t="n">
-        <v>172.1420794089453</v>
+        <v>184.1996921538</v>
       </c>
       <c r="C158" t="n">
-        <v>179.9979467596552</v>
+        <v>186.6291391730516</v>
       </c>
       <c r="D158" t="n">
-        <v>171.0567983816156</v>
+        <v>178.0364675908902</v>
       </c>
       <c r="E158" t="n">
-        <v>178.7035675048828</v>
+        <v>178.6438293457031</v>
       </c>
       <c r="F158" t="n">
-        <v>13671200</v>
+        <v>17510800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B159" t="n">
-        <v>184.1996921538</v>
+        <v>175.2784580726278</v>
       </c>
       <c r="C159" t="n">
-        <v>186.6291391730516</v>
+        <v>179.5299906412754</v>
       </c>
       <c r="D159" t="n">
-        <v>178.0364675908902</v>
+        <v>172.5901410995666</v>
       </c>
       <c r="E159" t="n">
-        <v>178.6438293457031</v>
+        <v>179.3209075927734</v>
       </c>
       <c r="F159" t="n">
-        <v>17510800</v>
+        <v>13025300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B160" t="n">
-        <v>175.2784431578192</v>
+        <v>174.6213174256682</v>
       </c>
       <c r="C160" t="n">
-        <v>179.529975364695</v>
+        <v>176.5728300297275</v>
       </c>
       <c r="D160" t="n">
-        <v>172.5901264135125</v>
+        <v>171.2459830488208</v>
       </c>
       <c r="E160" t="n">
-        <v>179.3208923339844</v>
+        <v>175.5472869873047</v>
       </c>
       <c r="F160" t="n">
-        <v>13025300</v>
+        <v>10949100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B161" t="n">
-        <v>174.6213174256682</v>
+        <v>179.0620149167984</v>
       </c>
       <c r="C161" t="n">
-        <v>176.5728300297275</v>
+        <v>182.5568405051486</v>
       </c>
       <c r="D161" t="n">
-        <v>171.2459830488208</v>
+        <v>176.9113553536261</v>
       </c>
       <c r="E161" t="n">
-        <v>175.5472869873047</v>
+        <v>179.2910308837891</v>
       </c>
       <c r="F161" t="n">
-        <v>10949100</v>
+        <v>10176700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B162" t="n">
-        <v>179.0619996775001</v>
+        <v>177.6581006500201</v>
       </c>
       <c r="C162" t="n">
-        <v>182.5568249684187</v>
+        <v>181.5711072848628</v>
       </c>
       <c r="D162" t="n">
-        <v>176.9113402973623</v>
+        <v>176.9113451663183</v>
       </c>
       <c r="E162" t="n">
-        <v>179.291015625</v>
+        <v>178.3052978515625</v>
       </c>
       <c r="F162" t="n">
-        <v>10176700</v>
+        <v>13617200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B163" t="n">
-        <v>177.6581006500201</v>
+        <v>177.2299817033781</v>
       </c>
       <c r="C163" t="n">
-        <v>181.5711072848628</v>
+        <v>183.1243702829636</v>
       </c>
       <c r="D163" t="n">
-        <v>176.9113451663183</v>
+        <v>176.1247828951571</v>
       </c>
       <c r="E163" t="n">
-        <v>178.3052978515625</v>
+        <v>176.7420959472656</v>
       </c>
       <c r="F163" t="n">
-        <v>13617200</v>
+        <v>18524900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B164" t="n">
-        <v>177.2299664024681</v>
+        <v>177.6581004088628</v>
       </c>
       <c r="C164" t="n">
-        <v>183.1243544731695</v>
+        <v>181.6905830539347</v>
       </c>
       <c r="D164" t="n">
-        <v>176.1247676896629</v>
+        <v>170.9074320607842</v>
       </c>
       <c r="E164" t="n">
-        <v>176.7420806884766</v>
+        <v>175.4078826904297</v>
       </c>
       <c r="F164" t="n">
-        <v>18524900</v>
+        <v>22559400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B165" t="n">
-        <v>177.6581004088628</v>
+        <v>179.4602947300403</v>
       </c>
       <c r="C165" t="n">
-        <v>181.6905830539347</v>
+        <v>193.300157831373</v>
       </c>
       <c r="D165" t="n">
-        <v>170.9074320607842</v>
+        <v>179.2412452254626</v>
       </c>
       <c r="E165" t="n">
-        <v>175.4078826904297</v>
+        <v>190.2733154296875</v>
       </c>
       <c r="F165" t="n">
-        <v>22559400</v>
+        <v>33998900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="n">
-        <v>179.4602803383912</v>
+        <v>197.8901992931745</v>
       </c>
       <c r="C166" t="n">
-        <v>193.3001423298492</v>
+        <v>210.4257307870387</v>
       </c>
       <c r="D166" t="n">
-        <v>179.24123085138</v>
+        <v>197.352542040295</v>
       </c>
       <c r="E166" t="n">
-        <v>190.2733001708984</v>
+        <v>208.6932678222656</v>
       </c>
       <c r="F166" t="n">
-        <v>33998900</v>
+        <v>27594800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B167" t="n">
-        <v>197.8901992931745</v>
+        <v>200.1504053799259</v>
       </c>
       <c r="C167" t="n">
-        <v>210.4257307870387</v>
+        <v>203.5058221270036</v>
       </c>
       <c r="D167" t="n">
-        <v>197.352542040295</v>
+        <v>194.9131500594789</v>
       </c>
       <c r="E167" t="n">
-        <v>208.6932678222656</v>
+        <v>199.9711761474609</v>
       </c>
       <c r="F167" t="n">
-        <v>27594800</v>
+        <v>19216600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B168" t="n">
-        <v>200.1503901074607</v>
+        <v>196.4166079226038</v>
       </c>
       <c r="C168" t="n">
-        <v>203.5058065985036</v>
+        <v>196.8248227029743</v>
       </c>
       <c r="D168" t="n">
-        <v>194.9131351866423</v>
+        <v>188.9092176958791</v>
       </c>
       <c r="E168" t="n">
-        <v>199.9711608886719</v>
+        <v>189.7854156494141</v>
       </c>
       <c r="F168" t="n">
-        <v>19216600</v>
+        <v>14154400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B169" t="n">
-        <v>196.4166079226038</v>
+        <v>196.9542758894677</v>
       </c>
       <c r="C169" t="n">
-        <v>196.8248227029743</v>
+        <v>197.2330634002457</v>
       </c>
       <c r="D169" t="n">
-        <v>188.9092176958791</v>
+        <v>185.3048928689384</v>
       </c>
       <c r="E169" t="n">
-        <v>189.7854156494141</v>
+        <v>187.9334716796875</v>
       </c>
       <c r="F169" t="n">
-        <v>14154400</v>
+        <v>14453600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B170" t="n">
-        <v>196.9542758894677</v>
+        <v>188.9789318725711</v>
       </c>
       <c r="C170" t="n">
-        <v>197.2330634002457</v>
+        <v>191.6771999565016</v>
       </c>
       <c r="D170" t="n">
-        <v>185.3048928689384</v>
+        <v>184.0304307819904</v>
       </c>
       <c r="E170" t="n">
-        <v>187.9334716796875</v>
+        <v>184.8568420410156</v>
       </c>
       <c r="F170" t="n">
-        <v>14453600</v>
+        <v>13183900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B171" t="n">
-        <v>188.9789318725711</v>
+        <v>183.1144169895118</v>
       </c>
       <c r="C171" t="n">
-        <v>191.6771999565016</v>
+        <v>184.2196157855271</v>
       </c>
       <c r="D171" t="n">
-        <v>184.0304307819904</v>
+        <v>180.92393713233</v>
       </c>
       <c r="E171" t="n">
-        <v>184.8568420410156</v>
+        <v>181.7602996826172</v>
       </c>
       <c r="F171" t="n">
-        <v>13183900</v>
+        <v>11177800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B172" t="n">
-        <v>183.1144169895118</v>
+        <v>178.7234714192057</v>
       </c>
       <c r="C172" t="n">
-        <v>184.2196157855271</v>
+        <v>181.670672953058</v>
       </c>
       <c r="D172" t="n">
-        <v>180.92393713233</v>
+        <v>170.8178179406258</v>
       </c>
       <c r="E172" t="n">
-        <v>181.7602996826172</v>
+        <v>174.5914306640625</v>
       </c>
       <c r="F172" t="n">
-        <v>11177800</v>
+        <v>15427800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B173" t="n">
-        <v>178.7234870391233</v>
+        <v>169.861995238658</v>
       </c>
       <c r="C173" t="n">
-        <v>181.6706888305526</v>
+        <v>174.7706609037228</v>
       </c>
       <c r="D173" t="n">
-        <v>170.8178328696119</v>
+        <v>169.2944537502145</v>
       </c>
       <c r="E173" t="n">
-        <v>174.5914459228516</v>
+        <v>170.1806030273438</v>
       </c>
       <c r="F173" t="n">
-        <v>15427800</v>
+        <v>10820500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,25 +4941,25 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B174" t="n">
-        <v>169.861995238658</v>
+        <v>167.9744954285649</v>
       </c>
       <c r="C174" t="n">
-        <v>174.7706609037228</v>
+        <v>168.6832400259219</v>
       </c>
       <c r="D174" t="n">
-        <v>169.2944537502145</v>
+        <v>163.0231992739924</v>
       </c>
       <c r="E174" t="n">
-        <v>170.1806030273438</v>
+        <v>166.1576843261719</v>
       </c>
       <c r="F174" t="n">
-        <v>10820500</v>
+        <v>16666000</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -4967,25 +4967,25 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B175" t="n">
-        <v>167.9744954285649</v>
+        <v>164.4506890531704</v>
       </c>
       <c r="C175" t="n">
-        <v>168.6832400259219</v>
+        <v>166.2475157071144</v>
       </c>
       <c r="D175" t="n">
-        <v>163.0231992739924</v>
+        <v>161.1165431857153</v>
       </c>
       <c r="E175" t="n">
-        <v>166.1576843261719</v>
+        <v>165.5986633300781</v>
       </c>
       <c r="F175" t="n">
-        <v>16666000</v>
+        <v>13589400</v>
       </c>
       <c r="G175" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B176" t="n">
-        <v>164.4506890531704</v>
+        <v>165.7384133733495</v>
       </c>
       <c r="C176" t="n">
-        <v>166.2475157071144</v>
+        <v>169.6515271583533</v>
       </c>
       <c r="D176" t="n">
-        <v>161.1165431857153</v>
+        <v>163.8816793355271</v>
       </c>
       <c r="E176" t="n">
-        <v>165.5986633300781</v>
+        <v>164.2610168457031</v>
       </c>
       <c r="F176" t="n">
-        <v>13589400</v>
+        <v>13541800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B177" t="n">
-        <v>165.7384133733495</v>
+        <v>163.7718739013043</v>
       </c>
       <c r="C177" t="n">
-        <v>169.6515271583533</v>
+        <v>166.0079454764833</v>
       </c>
       <c r="D177" t="n">
-        <v>163.8816793355271</v>
+        <v>160.2181284427459</v>
       </c>
       <c r="E177" t="n">
-        <v>164.2610168457031</v>
+        <v>161.4260101318359</v>
       </c>
       <c r="F177" t="n">
-        <v>13541800</v>
+        <v>16385300</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B178" t="n">
-        <v>163.7718739013043</v>
+        <v>159.9685677271403</v>
       </c>
       <c r="C178" t="n">
-        <v>166.0079454764833</v>
+        <v>161.1464880907799</v>
       </c>
       <c r="D178" t="n">
-        <v>160.2181284427459</v>
+        <v>153.959135832121</v>
       </c>
       <c r="E178" t="n">
-        <v>161.4260101318359</v>
+        <v>154.7477569580078</v>
       </c>
       <c r="F178" t="n">
-        <v>16385300</v>
+        <v>19986200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B179" t="n">
-        <v>159.9685677271403</v>
+        <v>152.4617715583163</v>
       </c>
       <c r="C179" t="n">
-        <v>161.1464880907799</v>
+        <v>154.1987212566731</v>
       </c>
       <c r="D179" t="n">
-        <v>153.959135832121</v>
+        <v>149.5369245308901</v>
       </c>
       <c r="E179" t="n">
-        <v>154.7477569580078</v>
+        <v>151.5134429931641</v>
       </c>
       <c r="F179" t="n">
-        <v>19986200</v>
+        <v>57940800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B180" t="n">
-        <v>152.4617715583163</v>
+        <v>149.8962920415152</v>
       </c>
       <c r="C180" t="n">
-        <v>154.1987212566731</v>
+        <v>153.5997679942281</v>
       </c>
       <c r="D180" t="n">
-        <v>149.5369245308901</v>
+        <v>146.0630395211035</v>
       </c>
       <c r="E180" t="n">
-        <v>151.5134429931641</v>
+        <v>149.8563537597656</v>
       </c>
       <c r="F180" t="n">
-        <v>57940800</v>
+        <v>20502800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B181" t="n">
-        <v>149.8962920415152</v>
+        <v>151.3836627210609</v>
       </c>
       <c r="C181" t="n">
-        <v>153.5997679942281</v>
+        <v>154.907462036052</v>
       </c>
       <c r="D181" t="n">
-        <v>146.0630395211035</v>
+        <v>150.5850798848861</v>
       </c>
       <c r="E181" t="n">
-        <v>149.8563537597656</v>
+        <v>153.1505584716797</v>
       </c>
       <c r="F181" t="n">
-        <v>20502800</v>
+        <v>20720700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B182" t="n">
-        <v>151.3836627210609</v>
+        <v>151.5433859321397</v>
       </c>
       <c r="C182" t="n">
-        <v>154.907462036052</v>
+        <v>156.7841657815476</v>
       </c>
       <c r="D182" t="n">
-        <v>150.5850798848861</v>
+        <v>150.135858545478</v>
       </c>
       <c r="E182" t="n">
-        <v>153.1505584716797</v>
+        <v>152.4917144775391</v>
       </c>
       <c r="F182" t="n">
-        <v>20720700</v>
+        <v>13146800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B183" t="n">
-        <v>151.5433859321397</v>
+        <v>149.7465472087312</v>
       </c>
       <c r="C183" t="n">
-        <v>156.7841657815476</v>
+        <v>153.7295454610107</v>
       </c>
       <c r="D183" t="n">
-        <v>150.135858545478</v>
+        <v>148.5187115976041</v>
       </c>
       <c r="E183" t="n">
-        <v>152.4917144775391</v>
+        <v>149.9262390136719</v>
       </c>
       <c r="F183" t="n">
-        <v>13146800</v>
+        <v>11324700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B184" t="n">
-        <v>149.7465472087312</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="C184" t="n">
-        <v>153.7295454610107</v>
+        <v>158.1817266914859</v>
       </c>
       <c r="D184" t="n">
-        <v>148.5187115976041</v>
+        <v>151.2239658596097</v>
       </c>
       <c r="E184" t="n">
-        <v>149.9262390136719</v>
+        <v>158.0918731689453</v>
       </c>
       <c r="F184" t="n">
-        <v>11324700</v>
+        <v>21267900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B185" t="n">
-        <v>151.2239658596097</v>
+        <v>159.9885357004027</v>
       </c>
       <c r="C185" t="n">
-        <v>158.1817266914859</v>
+        <v>161.4759091917036</v>
       </c>
       <c r="D185" t="n">
-        <v>151.2239658596097</v>
+        <v>157.4230418613804</v>
       </c>
       <c r="E185" t="n">
-        <v>158.0918731689453</v>
+        <v>157.6526336669922</v>
       </c>
       <c r="F185" t="n">
-        <v>21267900</v>
+        <v>12664100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B186" t="n">
-        <v>159.9885357004027</v>
+        <v>154.8176224085462</v>
       </c>
       <c r="C186" t="n">
-        <v>161.4759091917036</v>
+        <v>157.4130622995693</v>
       </c>
       <c r="D186" t="n">
-        <v>157.4230418613804</v>
+        <v>153.7994247316601</v>
       </c>
       <c r="E186" t="n">
-        <v>157.6526336669922</v>
+        <v>156.3848724365234</v>
       </c>
       <c r="F186" t="n">
-        <v>12664100</v>
+        <v>13690500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B187" t="n">
-        <v>154.8176224085462</v>
+        <v>161.9351081174896</v>
       </c>
       <c r="C187" t="n">
-        <v>157.4130622995693</v>
+        <v>165.5187996520913</v>
       </c>
       <c r="D187" t="n">
-        <v>153.7994247316601</v>
+        <v>160.916895191227</v>
       </c>
       <c r="E187" t="n">
-        <v>156.3848724365234</v>
+        <v>162.9433288574219</v>
       </c>
       <c r="F187" t="n">
-        <v>13690500</v>
+        <v>14164600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B188" t="n">
-        <v>161.9351081174896</v>
+        <v>162.7137441629</v>
       </c>
       <c r="C188" t="n">
-        <v>165.5187996520913</v>
+        <v>166.9163573859938</v>
       </c>
       <c r="D188" t="n">
-        <v>160.916895191227</v>
+        <v>161.7155003336798</v>
       </c>
       <c r="E188" t="n">
-        <v>162.9433288574219</v>
+        <v>165.8182830810547</v>
       </c>
       <c r="F188" t="n">
-        <v>14164600</v>
+        <v>10486300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B189" t="n">
-        <v>162.7137441629</v>
+        <v>163.7020118941432</v>
       </c>
       <c r="C189" t="n">
-        <v>166.9163573859938</v>
+        <v>167.425457131665</v>
       </c>
       <c r="D189" t="n">
-        <v>161.7155003336798</v>
+        <v>162.0848465245878</v>
       </c>
       <c r="E189" t="n">
-        <v>165.8182830810547</v>
+        <v>165.3590850830078</v>
       </c>
       <c r="F189" t="n">
-        <v>10486300</v>
+        <v>10595500</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B190" t="n">
-        <v>163.7020118941432</v>
+        <v>168.9228138583306</v>
       </c>
       <c r="C190" t="n">
-        <v>167.425457131665</v>
+        <v>172.0772678623225</v>
       </c>
       <c r="D190" t="n">
-        <v>162.0848465245878</v>
+        <v>167.3855099055031</v>
       </c>
       <c r="E190" t="n">
-        <v>165.3590850830078</v>
+        <v>169.2222900390625</v>
       </c>
       <c r="F190" t="n">
-        <v>10595500</v>
+        <v>13057900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B191" t="n">
-        <v>168.9228138583306</v>
+        <v>167.0760662569272</v>
       </c>
       <c r="C191" t="n">
-        <v>172.0772678623225</v>
+        <v>167.2357889266519</v>
       </c>
       <c r="D191" t="n">
-        <v>167.3855099055031</v>
+        <v>164.4906183727253</v>
       </c>
       <c r="E191" t="n">
-        <v>169.2222900390625</v>
+        <v>166.2874603271484</v>
       </c>
       <c r="F191" t="n">
-        <v>13057900</v>
+        <v>9792400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B192" t="n">
-        <v>167.0760662569272</v>
+        <v>158.05194011754</v>
       </c>
       <c r="C192" t="n">
-        <v>167.2357889266519</v>
+        <v>163.5123348335076</v>
       </c>
       <c r="D192" t="n">
-        <v>164.4906183727253</v>
+        <v>156.2051830247059</v>
       </c>
       <c r="E192" t="n">
-        <v>166.2874603271484</v>
+        <v>162.2146148681641</v>
       </c>
       <c r="F192" t="n">
-        <v>9792400</v>
+        <v>13858600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B193" t="n">
-        <v>158.05194011754</v>
+        <v>165.309182555471</v>
       </c>
       <c r="C193" t="n">
-        <v>163.5123348335076</v>
+        <v>166.007950182526</v>
       </c>
       <c r="D193" t="n">
-        <v>156.2051830247059</v>
+        <v>162.1347592897187</v>
       </c>
       <c r="E193" t="n">
-        <v>162.2146148681641</v>
+        <v>163.0331878662109</v>
       </c>
       <c r="F193" t="n">
-        <v>13858600</v>
+        <v>8321500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B194" t="n">
-        <v>165.309182555471</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="C194" t="n">
-        <v>166.007950182526</v>
+        <v>172.4566003351415</v>
       </c>
       <c r="D194" t="n">
-        <v>162.1347592897187</v>
+        <v>165.6286161244176</v>
       </c>
       <c r="E194" t="n">
-        <v>163.0331878662109</v>
+        <v>170.9193115234375</v>
       </c>
       <c r="F194" t="n">
-        <v>8321500</v>
+        <v>14020700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>165.6286161244176</v>
+        <v>162.2046435717354</v>
       </c>
       <c r="C195" t="n">
-        <v>172.4566003351415</v>
+        <v>171.049084414024</v>
       </c>
       <c r="D195" t="n">
-        <v>165.6286161244176</v>
+        <v>161.1864306117812</v>
       </c>
       <c r="E195" t="n">
-        <v>170.9193115234375</v>
+        <v>167.2657318115234</v>
       </c>
       <c r="F195" t="n">
-        <v>14020700</v>
+        <v>13507900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>162.2046435717354</v>
+        <v>170.2205331766167</v>
       </c>
       <c r="C196" t="n">
-        <v>171.049084414024</v>
+        <v>172.4965277703878</v>
       </c>
       <c r="D196" t="n">
-        <v>161.1864306117812</v>
+        <v>166.2674811162824</v>
       </c>
       <c r="E196" t="n">
-        <v>167.2657318115234</v>
+        <v>166.7067108154297</v>
       </c>
       <c r="F196" t="n">
-        <v>13507900</v>
+        <v>13328100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>170.2205331766167</v>
+        <v>170.5399744864679</v>
       </c>
       <c r="C197" t="n">
-        <v>172.4965277703878</v>
+        <v>174.2334736592566</v>
       </c>
       <c r="D197" t="n">
-        <v>166.2674811162824</v>
+        <v>166.5869373980102</v>
       </c>
       <c r="E197" t="n">
-        <v>166.7067108154297</v>
+        <v>172.3767395019531</v>
       </c>
       <c r="F197" t="n">
-        <v>13328100</v>
+        <v>12057500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B198" t="n">
-        <v>170.5399744864679</v>
+        <v>171.1988064601764</v>
       </c>
       <c r="C198" t="n">
-        <v>174.2334736592566</v>
+        <v>175.1218971627477</v>
       </c>
       <c r="D198" t="n">
-        <v>166.5869373980102</v>
+        <v>169.4518798636439</v>
       </c>
       <c r="E198" t="n">
-        <v>172.3767395019531</v>
+        <v>170.4700927734375</v>
       </c>
       <c r="F198" t="n">
-        <v>12057500</v>
+        <v>10191500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B199" t="n">
-        <v>171.1988064601764</v>
+        <v>167.5652084388413</v>
       </c>
       <c r="C199" t="n">
-        <v>175.1218971627477</v>
+        <v>175.0819831940494</v>
       </c>
       <c r="D199" t="n">
-        <v>169.4518798636439</v>
+        <v>166.2075962327059</v>
       </c>
       <c r="E199" t="n">
-        <v>170.4700927734375</v>
+        <v>173.4847869873047</v>
       </c>
       <c r="F199" t="n">
-        <v>10191500</v>
+        <v>13426500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B200" t="n">
-        <v>167.5652084388413</v>
+        <v>166.7666058963373</v>
       </c>
       <c r="C200" t="n">
-        <v>175.0819831940494</v>
+        <v>172.1271701993457</v>
       </c>
       <c r="D200" t="n">
-        <v>166.2075962327059</v>
+        <v>166.6368293287962</v>
       </c>
       <c r="E200" t="n">
-        <v>173.4847869873047</v>
+        <v>169.7613372802734</v>
       </c>
       <c r="F200" t="n">
-        <v>13426500</v>
+        <v>12831800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B201" t="n">
-        <v>166.7666058963373</v>
+        <v>169.1723839486806</v>
       </c>
       <c r="C201" t="n">
-        <v>172.1271701993457</v>
+        <v>169.272214424985</v>
       </c>
       <c r="D201" t="n">
-        <v>166.6368293287962</v>
+        <v>161.925139189555</v>
       </c>
       <c r="E201" t="n">
-        <v>169.7613372802734</v>
+        <v>162.7137451171875</v>
       </c>
       <c r="F201" t="n">
-        <v>12831800</v>
+        <v>12194500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B202" t="n">
-        <v>169.1723839486806</v>
+        <v>164.7601382451291</v>
       </c>
       <c r="C202" t="n">
-        <v>169.272214424985</v>
+        <v>165.5886824068968</v>
       </c>
       <c r="D202" t="n">
-        <v>161.925139189555</v>
+        <v>154.877515725338</v>
       </c>
       <c r="E202" t="n">
-        <v>162.7137451171875</v>
+        <v>156.6543884277344</v>
       </c>
       <c r="F202" t="n">
-        <v>12194500</v>
+        <v>12775000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B203" t="n">
-        <v>164.7601382451291</v>
+        <v>160.0983505627206</v>
       </c>
       <c r="C203" t="n">
-        <v>165.5886824068968</v>
+        <v>164.1611950360997</v>
       </c>
       <c r="D203" t="n">
-        <v>154.877515725338</v>
+        <v>159.2698063547753</v>
       </c>
       <c r="E203" t="n">
-        <v>156.6543884277344</v>
+        <v>163.3725891113281</v>
       </c>
       <c r="F203" t="n">
-        <v>12775000</v>
+        <v>10899100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B204" t="n">
-        <v>160.0983505627206</v>
+        <v>167.7049639405646</v>
       </c>
       <c r="C204" t="n">
-        <v>164.1611950360997</v>
+        <v>176.6392431993331</v>
       </c>
       <c r="D204" t="n">
-        <v>159.2698063547753</v>
+        <v>166.8464736349225</v>
       </c>
       <c r="E204" t="n">
-        <v>163.3725891113281</v>
+        <v>173.2951354980469</v>
       </c>
       <c r="F204" t="n">
-        <v>10899100</v>
+        <v>17312000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B205" t="n">
-        <v>167.7049639405646</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="C205" t="n">
-        <v>176.6392431993331</v>
+        <v>184.2158982492034</v>
       </c>
       <c r="D205" t="n">
-        <v>166.8464736349225</v>
+        <v>176.5993086569288</v>
       </c>
       <c r="E205" t="n">
-        <v>173.2951354980469</v>
+        <v>181.1812438964844</v>
       </c>
       <c r="F205" t="n">
-        <v>17312000</v>
+        <v>17204600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B206" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="C206" t="n">
-        <v>184.2158982492034</v>
+        <v>189.8460057999592</v>
       </c>
       <c r="D206" t="n">
-        <v>176.5993086569288</v>
+        <v>181.6903554713178</v>
       </c>
       <c r="E206" t="n">
-        <v>181.1812438964844</v>
+        <v>188.0491790771484</v>
       </c>
       <c r="F206" t="n">
-        <v>17204600</v>
+        <v>18139500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B207" t="n">
-        <v>181.6903554713178</v>
+        <v>180.6721461984077</v>
       </c>
       <c r="C207" t="n">
-        <v>189.8460057999592</v>
+        <v>182.1894657683464</v>
       </c>
       <c r="D207" t="n">
-        <v>181.6903554713178</v>
+        <v>175.5910738107855</v>
       </c>
       <c r="E207" t="n">
-        <v>188.0491790771484</v>
+        <v>180.3926391601562</v>
       </c>
       <c r="F207" t="n">
-        <v>18139500</v>
+        <v>12182400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B208" t="n">
-        <v>180.6721461984077</v>
+        <v>177.3879151720665</v>
       </c>
       <c r="C208" t="n">
-        <v>182.1894657683464</v>
+        <v>184.1260606305619</v>
       </c>
       <c r="D208" t="n">
-        <v>175.5910738107855</v>
+        <v>176.719093672914</v>
       </c>
       <c r="E208" t="n">
-        <v>180.3926391601562</v>
+        <v>183.6968231201172</v>
       </c>
       <c r="F208" t="n">
-        <v>12182400</v>
+        <v>9691500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B209" t="n">
-        <v>177.3879151720665</v>
+        <v>188.658097974018</v>
       </c>
       <c r="C209" t="n">
-        <v>184.1260606305619</v>
+        <v>193.3598176605707</v>
       </c>
       <c r="D209" t="n">
-        <v>176.719093672914</v>
+        <v>185.5735131091938</v>
       </c>
       <c r="E209" t="n">
-        <v>183.6968231201172</v>
+        <v>185.6234283447266</v>
       </c>
       <c r="F209" t="n">
-        <v>9691500</v>
+        <v>12908000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B210" t="n">
-        <v>188.658097974018</v>
+        <v>182.7684517177381</v>
       </c>
       <c r="C210" t="n">
-        <v>193.3598176605707</v>
+        <v>190.9540477431734</v>
       </c>
       <c r="D210" t="n">
-        <v>185.5735131091938</v>
+        <v>182.6786134323838</v>
       </c>
       <c r="E210" t="n">
-        <v>185.6234283447266</v>
+        <v>190.6545867919922</v>
       </c>
       <c r="F210" t="n">
-        <v>12908000</v>
+        <v>9326900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B211" t="n">
-        <v>182.7684517177381</v>
+        <v>192.9405589477455</v>
       </c>
       <c r="C211" t="n">
-        <v>190.9540477431734</v>
+        <v>194.5976472985604</v>
       </c>
       <c r="D211" t="n">
-        <v>182.6786134323838</v>
+        <v>190.0955580470331</v>
       </c>
       <c r="E211" t="n">
-        <v>190.6545867919922</v>
+        <v>192.6410827636719</v>
       </c>
       <c r="F211" t="n">
-        <v>9326900</v>
+        <v>9605500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B212" t="n">
-        <v>192.9405589477455</v>
+        <v>183.117847615437</v>
       </c>
       <c r="C212" t="n">
-        <v>194.5976472985604</v>
+        <v>186.6915622961891</v>
       </c>
       <c r="D212" t="n">
-        <v>190.0955580470331</v>
+        <v>182.6786179003067</v>
       </c>
       <c r="E212" t="n">
-        <v>192.6410827636719</v>
+        <v>186.4420013427734</v>
       </c>
       <c r="F212" t="n">
-        <v>9605500</v>
+        <v>13297600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B213" t="n">
-        <v>183.117847615437</v>
+        <v>190.7544083295565</v>
       </c>
       <c r="C213" t="n">
-        <v>186.6915622961891</v>
+        <v>194.3580691369978</v>
       </c>
       <c r="D213" t="n">
-        <v>182.6786179003067</v>
+        <v>190.2652786051507</v>
       </c>
       <c r="E213" t="n">
-        <v>186.4420013427734</v>
+        <v>192.4015197753906</v>
       </c>
       <c r="F213" t="n">
-        <v>13297600</v>
+        <v>11392800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B214" t="n">
-        <v>190.7544083295565</v>
+        <v>189.8360257192551</v>
       </c>
       <c r="C214" t="n">
-        <v>194.3580691369978</v>
+        <v>197.831953246477</v>
       </c>
       <c r="D214" t="n">
-        <v>190.2652786051507</v>
+        <v>189.666326097428</v>
       </c>
       <c r="E214" t="n">
-        <v>192.4015197753906</v>
+        <v>197.1631317138672</v>
       </c>
       <c r="F214" t="n">
-        <v>11392800</v>
+        <v>9706600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B215" t="n">
-        <v>189.8360257192551</v>
+        <v>196.5941314807131</v>
       </c>
       <c r="C215" t="n">
-        <v>197.831953246477</v>
+        <v>199.0398256830038</v>
       </c>
       <c r="D215" t="n">
-        <v>189.666326097428</v>
+        <v>195.1566580076304</v>
       </c>
       <c r="E215" t="n">
-        <v>197.1631317138672</v>
+        <v>197.1231994628906</v>
       </c>
       <c r="F215" t="n">
-        <v>9706600</v>
+        <v>11171600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B216" t="n">
-        <v>196.5941314807131</v>
+        <v>191.6628101365335</v>
       </c>
       <c r="C216" t="n">
-        <v>199.0398256830038</v>
+        <v>196.1549072491085</v>
       </c>
       <c r="D216" t="n">
-        <v>195.1566580076304</v>
+        <v>191.4431952813594</v>
       </c>
       <c r="E216" t="n">
-        <v>197.1231994628906</v>
+        <v>192.9804992675781</v>
       </c>
       <c r="F216" t="n">
-        <v>11171600</v>
+        <v>12787900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B217" t="n">
-        <v>191.6628101365335</v>
+        <v>196.4943140399408</v>
       </c>
       <c r="C217" t="n">
-        <v>196.1549072491085</v>
+        <v>202.6335228023228</v>
       </c>
       <c r="D217" t="n">
-        <v>191.4431952813594</v>
+        <v>191.0538881519706</v>
       </c>
       <c r="E217" t="n">
-        <v>192.9804992675781</v>
+        <v>201.016357421875</v>
       </c>
       <c r="F217" t="n">
-        <v>12787900</v>
+        <v>15058700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="n">
-        <v>196.4943140399408</v>
+        <v>202.3939250564146</v>
       </c>
       <c r="C218" t="n">
-        <v>202.6335228023228</v>
+        <v>204.0410211897246</v>
       </c>
       <c r="D218" t="n">
-        <v>191.0538881519706</v>
+        <v>194.9769811314243</v>
       </c>
       <c r="E218" t="n">
-        <v>201.016357421875</v>
+        <v>195.8654174804688</v>
       </c>
       <c r="F218" t="n">
-        <v>15058700</v>
+        <v>8664800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B219" t="n">
-        <v>202.3939250564146</v>
+        <v>193.4896063018435</v>
       </c>
       <c r="C219" t="n">
-        <v>204.0410211897246</v>
+        <v>194.5976575790598</v>
       </c>
       <c r="D219" t="n">
-        <v>194.9769811314243</v>
+        <v>189.57649225733</v>
       </c>
       <c r="E219" t="n">
-        <v>195.8654174804688</v>
+        <v>190.6346282958984</v>
       </c>
       <c r="F219" t="n">
-        <v>8664800</v>
+        <v>14378800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B220" t="n">
-        <v>193.4896063018435</v>
+        <v>193.7491445531879</v>
       </c>
       <c r="C220" t="n">
-        <v>194.5976575790598</v>
+        <v>199.0598091290667</v>
       </c>
       <c r="D220" t="n">
-        <v>189.57649225733</v>
+        <v>192.8906542357335</v>
       </c>
       <c r="E220" t="n">
-        <v>190.6346282958984</v>
+        <v>195.7955474853516</v>
       </c>
       <c r="F220" t="n">
-        <v>14378800</v>
+        <v>14152900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B221" t="n">
-        <v>193.7491445531879</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="C221" t="n">
-        <v>199.0598091290667</v>
+        <v>207.5847919095016</v>
       </c>
       <c r="D221" t="n">
-        <v>192.8906542357335</v>
+        <v>193.8689320609861</v>
       </c>
       <c r="E221" t="n">
-        <v>195.7955474853516</v>
+        <v>205.7280578613281</v>
       </c>
       <c r="F221" t="n">
-        <v>14152900</v>
+        <v>17843600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B222" t="n">
-        <v>193.8689320609861</v>
+        <v>204.8595912018172</v>
       </c>
       <c r="C222" t="n">
-        <v>207.5847919095016</v>
+        <v>207.5149233311111</v>
       </c>
       <c r="D222" t="n">
-        <v>193.8689320609861</v>
+        <v>202.6434887759544</v>
       </c>
       <c r="E222" t="n">
-        <v>205.7280578613281</v>
+        <v>205.0692138671875</v>
       </c>
       <c r="F222" t="n">
-        <v>17843600</v>
+        <v>11482300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="n">
-        <v>204.8595912018172</v>
+        <v>205.2189664215684</v>
       </c>
       <c r="C223" t="n">
-        <v>207.5149233311111</v>
+        <v>210.6993304789719</v>
       </c>
       <c r="D223" t="n">
-        <v>202.6434887759544</v>
+        <v>204.3704530814486</v>
       </c>
       <c r="E223" t="n">
-        <v>205.0692138671875</v>
+        <v>208.8026580810547</v>
       </c>
       <c r="F223" t="n">
-        <v>11482300</v>
+        <v>9685400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B224" t="n">
-        <v>205.2189664215684</v>
+        <v>208.0539803833292</v>
       </c>
       <c r="C224" t="n">
-        <v>210.6993304789719</v>
+        <v>212.7956386479058</v>
       </c>
       <c r="D224" t="n">
-        <v>204.3704530814486</v>
+        <v>207.0257904413594</v>
       </c>
       <c r="E224" t="n">
-        <v>208.8026580810547</v>
+        <v>208.6928558349609</v>
       </c>
       <c r="F224" t="n">
-        <v>9685400</v>
+        <v>9580200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B225" t="n">
-        <v>208.0539803833292</v>
+        <v>205.4884885298704</v>
       </c>
       <c r="C225" t="n">
-        <v>212.7956386479058</v>
+        <v>209.9406472657768</v>
       </c>
       <c r="D225" t="n">
-        <v>207.0257904413594</v>
+        <v>204.400391231641</v>
       </c>
       <c r="E225" t="n">
-        <v>208.6928558349609</v>
+        <v>205.3287658691406</v>
       </c>
       <c r="F225" t="n">
-        <v>9580200</v>
+        <v>10081800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B226" t="n">
-        <v>205.4884885298704</v>
+        <v>199.5888632714973</v>
       </c>
       <c r="C226" t="n">
-        <v>209.9406472657768</v>
+        <v>206.0774478239803</v>
       </c>
       <c r="D226" t="n">
-        <v>204.400391231641</v>
+        <v>198.6005964484484</v>
       </c>
       <c r="E226" t="n">
-        <v>205.3287658691406</v>
+        <v>205.2588806152344</v>
       </c>
       <c r="F226" t="n">
-        <v>10081800</v>
+        <v>14888900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B227" t="n">
-        <v>199.5888632714973</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="C227" t="n">
-        <v>206.0774478239803</v>
+        <v>254.0330860396483</v>
       </c>
       <c r="D227" t="n">
-        <v>198.6005964484484</v>
+        <v>229.6459965412689</v>
       </c>
       <c r="E227" t="n">
-        <v>205.2588806152344</v>
+        <v>251.6073608398438</v>
       </c>
       <c r="F227" t="n">
-        <v>14888900</v>
+        <v>55517500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B228" t="n">
-        <v>229.6459965412689</v>
+        <v>250.0301279952546</v>
       </c>
       <c r="C228" t="n">
-        <v>254.0330860396483</v>
+        <v>263.0671897003631</v>
       </c>
       <c r="D228" t="n">
-        <v>229.6459965412689</v>
+        <v>248.5627083778381</v>
       </c>
       <c r="E228" t="n">
-        <v>251.6073608398438</v>
+        <v>255.5504150390625</v>
       </c>
       <c r="F228" t="n">
-        <v>55517500</v>
+        <v>34362700</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B229" t="n">
-        <v>250.0301279952546</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="C229" t="n">
-        <v>263.0671897003631</v>
+        <v>261.8193732125837</v>
       </c>
       <c r="D229" t="n">
-        <v>248.5627083778381</v>
+        <v>253.9432305236259</v>
       </c>
       <c r="E229" t="n">
-        <v>255.5504150390625</v>
+        <v>257.0877075195312</v>
       </c>
       <c r="F229" t="n">
-        <v>34362700</v>
+        <v>22471500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B230" t="n">
-        <v>253.9432305236259</v>
+        <v>254.5621609406893</v>
       </c>
       <c r="C230" t="n">
-        <v>261.8193732125837</v>
+        <v>261.8593363431507</v>
       </c>
       <c r="D230" t="n">
-        <v>253.9432305236259</v>
+        <v>253.8035010915435</v>
       </c>
       <c r="E230" t="n">
-        <v>257.0877075195312</v>
+        <v>257.6567077636719</v>
       </c>
       <c r="F230" t="n">
-        <v>22471500</v>
+        <v>15897500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B231" t="n">
-        <v>254.5621609406893</v>
+        <v>258.9244691424316</v>
       </c>
       <c r="C231" t="n">
-        <v>261.8593363431507</v>
+        <v>264.0853722779391</v>
       </c>
       <c r="D231" t="n">
-        <v>253.8035010915435</v>
+        <v>253.154621477229</v>
       </c>
       <c r="E231" t="n">
-        <v>257.6567077636719</v>
+        <v>256.478759765625</v>
       </c>
       <c r="F231" t="n">
-        <v>15897500</v>
+        <v>14393700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B232" t="n">
-        <v>258.9244691424316</v>
+        <v>261.5199276025597</v>
       </c>
       <c r="C232" t="n">
-        <v>264.0853722779391</v>
+        <v>267.7988593124239</v>
       </c>
       <c r="D232" t="n">
-        <v>253.154621477229</v>
+        <v>261.1405900757476</v>
       </c>
       <c r="E232" t="n">
-        <v>256.478759765625</v>
+        <v>263.9656066894531</v>
       </c>
       <c r="F232" t="n">
-        <v>14393700</v>
+        <v>16028300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="n">
-        <v>261.5199276025597</v>
+        <v>262.8974710364521</v>
       </c>
       <c r="C233" t="n">
-        <v>267.7988593124239</v>
+        <v>263.1370702625856</v>
       </c>
       <c r="D233" t="n">
-        <v>261.1405900757476</v>
+        <v>257.3672223502596</v>
       </c>
       <c r="E233" t="n">
-        <v>263.9656066894531</v>
+        <v>258.7747497558594</v>
       </c>
       <c r="F233" t="n">
-        <v>16028300</v>
+        <v>10490600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B234" t="n">
-        <v>262.8974710364521</v>
+        <v>253.2744227737308</v>
       </c>
       <c r="C234" t="n">
-        <v>263.1370702625856</v>
+        <v>253.5539298242691</v>
       </c>
       <c r="D234" t="n">
-        <v>257.3672223502596</v>
+        <v>245.4581718493405</v>
       </c>
       <c r="E234" t="n">
-        <v>258.7747497558594</v>
+        <v>248.6824951171875</v>
       </c>
       <c r="F234" t="n">
-        <v>10490600</v>
+        <v>17482700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B235" t="n">
-        <v>253.2744227737308</v>
+        <v>249.3413418635835</v>
       </c>
       <c r="C235" t="n">
-        <v>253.5539298242691</v>
+        <v>254.3525301395604</v>
       </c>
       <c r="D235" t="n">
-        <v>245.4581718493405</v>
+        <v>243.0224566114913</v>
       </c>
       <c r="E235" t="n">
-        <v>248.6824951171875</v>
+        <v>243.7312164306641</v>
       </c>
       <c r="F235" t="n">
-        <v>17482700</v>
+        <v>11853700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B236" t="n">
-        <v>249.3413418635835</v>
+        <v>244.9191211985708</v>
       </c>
       <c r="C236" t="n">
-        <v>254.3525301395604</v>
+        <v>248.0635830600566</v>
       </c>
       <c r="D236" t="n">
-        <v>243.0224566114913</v>
+        <v>241.3254374437371</v>
       </c>
       <c r="E236" t="n">
-        <v>243.7312164306641</v>
+        <v>242.5732421875</v>
       </c>
       <c r="F236" t="n">
-        <v>11853700</v>
+        <v>10732600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B237" t="n">
-        <v>244.9191211985708</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="C237" t="n">
-        <v>248.0635830600566</v>
+        <v>250.1099896964979</v>
       </c>
       <c r="D237" t="n">
-        <v>241.3254374437371</v>
+        <v>241.5949712138984</v>
       </c>
       <c r="E237" t="n">
-        <v>242.5732421875</v>
+        <v>247.2849578857422</v>
       </c>
       <c r="F237" t="n">
-        <v>10732600</v>
+        <v>9738300</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B238" t="n">
-        <v>241.5949712138984</v>
+        <v>255.3008656803045</v>
       </c>
       <c r="C238" t="n">
-        <v>250.1099896964979</v>
+        <v>259.7230786425112</v>
       </c>
       <c r="D238" t="n">
-        <v>241.5949712138984</v>
+        <v>251.0583293004754</v>
       </c>
       <c r="E238" t="n">
-        <v>247.2849578857422</v>
+        <v>258.9743957519531</v>
       </c>
       <c r="F238" t="n">
-        <v>9738300</v>
+        <v>12963700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B239" t="n">
-        <v>255.3008656803045</v>
+        <v>256.43886230448</v>
       </c>
       <c r="C239" t="n">
-        <v>259.7230786425112</v>
+        <v>261.8792726915332</v>
       </c>
       <c r="D239" t="n">
-        <v>251.0583293004754</v>
+        <v>254.632028246405</v>
       </c>
       <c r="E239" t="n">
-        <v>258.9743957519531</v>
+        <v>255.2010192871094</v>
       </c>
       <c r="F239" t="n">
-        <v>12963700</v>
+        <v>11502800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B240" t="n">
-        <v>256.43886230448</v>
+        <v>251.4077029961344</v>
       </c>
       <c r="C240" t="n">
-        <v>261.8792726915332</v>
+        <v>255.9497000259878</v>
       </c>
       <c r="D240" t="n">
-        <v>254.632028246405</v>
+        <v>249.1616544830015</v>
       </c>
       <c r="E240" t="n">
-        <v>255.2010192871094</v>
+        <v>250.0999908447266</v>
       </c>
       <c r="F240" t="n">
-        <v>11502800</v>
+        <v>9423800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B241" t="n">
-        <v>251.4077029961344</v>
+        <v>244.1799926757812</v>
       </c>
       <c r="C241" t="n">
-        <v>255.9497000259878</v>
+        <v>247</v>
       </c>
       <c r="D241" t="n">
-        <v>249.1616544830015</v>
+        <v>241.5200042724609</v>
       </c>
       <c r="E241" t="n">
-        <v>250.0999908447266</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F241" t="n">
-        <v>9423800</v>
+        <v>16611300</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B242" t="n">
-        <v>244.1799926757812</v>
+        <v>244.25</v>
       </c>
       <c r="C242" t="n">
-        <v>247</v>
+        <v>244.25</v>
       </c>
       <c r="D242" t="n">
-        <v>241.5200042724609</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="E242" t="n">
-        <v>242.8500061035156</v>
+        <v>237.9199981689453</v>
       </c>
       <c r="F242" t="n">
-        <v>16611300</v>
+        <v>21962400</v>
       </c>
       <c r="G242" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B243" t="n">
-        <v>244.25</v>
+        <v>239.8000030517578</v>
       </c>
       <c r="C243" t="n">
-        <v>244.25</v>
+        <v>241.3399963378906</v>
       </c>
       <c r="D243" t="n">
-        <v>236.5500030517578</v>
+        <v>236.25</v>
       </c>
       <c r="E243" t="n">
-        <v>237.9199981689453</v>
+        <v>236.4199981689453</v>
       </c>
       <c r="F243" t="n">
-        <v>21962400</v>
+        <v>10581900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B244" t="n">
-        <v>239.8000030517578</v>
+        <v>241.5</v>
       </c>
       <c r="C244" t="n">
-        <v>241.3399963378906</v>
+        <v>242.4400024414062</v>
       </c>
       <c r="D244" t="n">
-        <v>236.25</v>
+        <v>229.8099975585938</v>
       </c>
       <c r="E244" t="n">
-        <v>236.4199981689453</v>
+        <v>233.2799987792969</v>
       </c>
       <c r="F244" t="n">
-        <v>10581900</v>
+        <v>13635600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B245" t="n">
-        <v>241.5</v>
+        <v>234.4199981689453</v>
       </c>
       <c r="C245" t="n">
-        <v>242.4400024414062</v>
+        <v>241.1199951171875</v>
       </c>
       <c r="D245" t="n">
-        <v>229.8099975585938</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="E245" t="n">
-        <v>233.2799987792969</v>
+        <v>237.5800018310547</v>
       </c>
       <c r="F245" t="n">
-        <v>13635600</v>
+        <v>12353500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B246" t="n">
-        <v>234.4199981689453</v>
+        <v>240.6399993896484</v>
       </c>
       <c r="C246" t="n">
-        <v>241.1199951171875</v>
+        <v>242.0899963378906</v>
       </c>
       <c r="D246" t="n">
-        <v>234.2400054931641</v>
+        <v>237</v>
       </c>
       <c r="E246" t="n">
-        <v>237.5800018310547</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="F246" t="n">
-        <v>12353500</v>
+        <v>11074000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B247" t="n">
-        <v>240.6399993896484</v>
+        <v>237.0299987792969</v>
       </c>
       <c r="C247" t="n">
-        <v>242.0899963378906</v>
+        <v>239.3699951171875</v>
       </c>
       <c r="D247" t="n">
-        <v>237</v>
+        <v>233.3800048828125</v>
       </c>
       <c r="E247" t="n">
-        <v>238.2200012207031</v>
+        <v>234.0200042724609</v>
       </c>
       <c r="F247" t="n">
-        <v>11074000</v>
+        <v>8735500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B248" t="n">
-        <v>237.0299987792969</v>
+        <v>224.9700012207031</v>
       </c>
       <c r="C248" t="n">
-        <v>239.3699951171875</v>
+        <v>230.5700073242188</v>
       </c>
       <c r="D248" t="n">
-        <v>233.3800048828125</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="E248" t="n">
-        <v>234.0200042724609</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="F248" t="n">
-        <v>8735500</v>
+        <v>10327500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B249" t="n">
-        <v>224.9700012207031</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="C249" t="n">
-        <v>230.5700073242188</v>
+        <v>228.9799957275391</v>
       </c>
       <c r="D249" t="n">
-        <v>221.1799926757812</v>
+        <v>223.4299926757812</v>
       </c>
       <c r="E249" t="n">
-        <v>227.2700042724609</v>
+        <v>225.3099975585938</v>
       </c>
       <c r="F249" t="n">
-        <v>10327500</v>
+        <v>13506300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>227.2700042724609</v>
+        <v>225.3999938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>228.9799957275391</v>
+        <v>233.7599945068359</v>
       </c>
       <c r="D250" t="n">
-        <v>223.4299926757812</v>
+        <v>224.4299926757812</v>
       </c>
       <c r="E250" t="n">
-        <v>225.3099975585938</v>
+        <v>229.5700073242188</v>
       </c>
       <c r="F250" t="n">
-        <v>13506300</v>
+        <v>11228200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B251" t="n">
-        <v>225.3999938964844</v>
+        <v>235.2799987792969</v>
       </c>
       <c r="C251" t="n">
-        <v>233.7599945068359</v>
+        <v>239.4499969482422</v>
       </c>
       <c r="D251" t="n">
-        <v>224.4299926757812</v>
+        <v>230.75</v>
       </c>
       <c r="E251" t="n">
-        <v>229.5700073242188</v>
+        <v>236.6900024414062</v>
       </c>
       <c r="F251" t="n">
-        <v>11228200</v>
+        <v>9571200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B252" t="n">
-        <v>235.2799987792969</v>
+        <v>238.1100006103516</v>
       </c>
       <c r="C252" t="n">
-        <v>239.4499969482422</v>
+        <v>238.9799957275391</v>
       </c>
       <c r="D252" t="n">
-        <v>230.75</v>
+        <v>233.1699981689453</v>
       </c>
       <c r="E252" t="n">
-        <v>236.6900024414062</v>
+        <v>234.6900024414062</v>
       </c>
       <c r="F252" t="n">
-        <v>9571200</v>
+        <v>7840153</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10654,34 +10654,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>234.69</v>
+      </c>
+      <c r="D2" t="n">
         <v>236.69</v>
       </c>
-      <c r="D2" t="n">
-        <v>229.57</v>
-      </c>
       <c r="E2" t="n">
-        <v>235.28</v>
+        <v>238.11</v>
       </c>
       <c r="F2" t="n">
-        <v>239.4499</v>
+        <v>238.98</v>
       </c>
       <c r="G2" t="n">
-        <v>230.75</v>
+        <v>233.17</v>
       </c>
       <c r="H2" t="n">
-        <v>9563732</v>
+        <v>7840153</v>
       </c>
       <c r="I2" t="n">
         <v>13711898</v>
       </c>
       <c r="J2" t="n">
-        <v>194795864064</v>
+        <v>193149878272</v>
       </c>
       <c r="K2" t="n">
-        <v>21.265947</v>
+        <v>21.086254</v>
       </c>
       <c r="L2" t="n">
-        <v>14.786896</v>
+        <v>14.661948</v>
       </c>
       <c r="M2" t="n">
         <v>11.13</v>
@@ -10720,7 +10720,7 @@
         <v>46.632</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.0756993</v>
+        <v>5.03281</v>
       </c>
       <c r="Z2" t="n">
         <v>1.189</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:38:54</t>
+          <t>2026-10-03 05:34:57</t>
         </is>
       </c>
     </row>

--- a/data/CRM_data.xlsx
+++ b/data/CRM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B2" t="n">
-        <v>236.7419954840688</v>
+        <v>237.3171258741176</v>
       </c>
       <c r="C2" t="n">
-        <v>240.7678464733125</v>
+        <v>248.363432718911</v>
       </c>
       <c r="D2" t="n">
-        <v>236.4940981065986</v>
+        <v>233.4300967019765</v>
       </c>
       <c r="E2" t="n">
-        <v>238.3384552001953</v>
+        <v>243.7128753662109</v>
       </c>
       <c r="F2" t="n">
-        <v>8849800</v>
+        <v>13922600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B3" t="n">
-        <v>237.3171258741176</v>
+        <v>244.406950940097</v>
       </c>
       <c r="C3" t="n">
-        <v>248.363432718911</v>
+        <v>245.2795544533588</v>
       </c>
       <c r="D3" t="n">
-        <v>233.4300967019765</v>
+        <v>235.5520648656193</v>
       </c>
       <c r="E3" t="n">
-        <v>243.7128753662109</v>
+        <v>237.7236480712891</v>
       </c>
       <c r="F3" t="n">
-        <v>13922600</v>
+        <v>8387400</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B4" t="n">
-        <v>244.4069666278678</v>
+        <v>237.7236681390551</v>
       </c>
       <c r="C4" t="n">
-        <v>245.2795701971395</v>
+        <v>239.290381338098</v>
       </c>
       <c r="D4" t="n">
-        <v>235.5520799850208</v>
+        <v>233.6680556537968</v>
       </c>
       <c r="E4" t="n">
-        <v>237.7236633300781</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F4" t="n">
-        <v>8387400</v>
+        <v>7120200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="n">
-        <v>237.7236681390551</v>
+        <v>237.2576175505903</v>
       </c>
       <c r="C5" t="n">
-        <v>239.290381338098</v>
+        <v>243.8913535488906</v>
       </c>
       <c r="D5" t="n">
-        <v>233.6680556537968</v>
+        <v>235.1554375781523</v>
       </c>
       <c r="E5" t="n">
-        <v>238.4078521728516</v>
+        <v>243.2666473388672</v>
       </c>
       <c r="F5" t="n">
-        <v>7120200</v>
+        <v>7929100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B6" t="n">
-        <v>237.2576175505903</v>
+        <v>244.4466590259869</v>
       </c>
       <c r="C6" t="n">
-        <v>243.8913535488906</v>
+        <v>246.955379366002</v>
       </c>
       <c r="D6" t="n">
-        <v>235.1554375781523</v>
+        <v>238.695436635224</v>
       </c>
       <c r="E6" t="n">
-        <v>243.2666473388672</v>
+        <v>239.6473541259766</v>
       </c>
       <c r="F6" t="n">
-        <v>7929100</v>
+        <v>7988300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B7" t="n">
-        <v>244.4466590259869</v>
+        <v>240.8471677432379</v>
       </c>
       <c r="C7" t="n">
-        <v>246.955379366002</v>
+        <v>247.252842429503</v>
       </c>
       <c r="D7" t="n">
-        <v>238.695436635224</v>
+        <v>240.3315369780713</v>
       </c>
       <c r="E7" t="n">
-        <v>239.6473541259766</v>
+        <v>246.6578826904297</v>
       </c>
       <c r="F7" t="n">
-        <v>7988300</v>
+        <v>8276500</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B8" t="n">
-        <v>240.8471677432379</v>
+        <v>246.0232707436915</v>
       </c>
       <c r="C8" t="n">
-        <v>247.252842429503</v>
+        <v>246.1918391425529</v>
       </c>
       <c r="D8" t="n">
-        <v>240.3315369780713</v>
+        <v>237.5352670689401</v>
       </c>
       <c r="E8" t="n">
-        <v>246.6578826904297</v>
+        <v>237.75341796875</v>
       </c>
       <c r="F8" t="n">
-        <v>8276500</v>
+        <v>9123900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="n">
-        <v>246.0232865332319</v>
+        <v>238.8441682164495</v>
       </c>
       <c r="C9" t="n">
-        <v>246.1918549429118</v>
+        <v>239.2903956148572</v>
       </c>
       <c r="D9" t="n">
-        <v>237.5352823137284</v>
+        <v>233.9159669806913</v>
       </c>
       <c r="E9" t="n">
-        <v>237.7534332275391</v>
+        <v>234.5902557373047</v>
       </c>
       <c r="F9" t="n">
-        <v>9123900</v>
+        <v>8389200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B10" t="n">
-        <v>238.8441526809671</v>
+        <v>251.0605615872617</v>
       </c>
       <c r="C10" t="n">
-        <v>239.2903800503502</v>
+        <v>254.5806923994446</v>
       </c>
       <c r="D10" t="n">
-        <v>233.915951765761</v>
+        <v>240.6290352431058</v>
       </c>
       <c r="E10" t="n">
-        <v>234.5902404785156</v>
+        <v>243.9310302734375</v>
       </c>
       <c r="F10" t="n">
-        <v>8389200</v>
+        <v>24869700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B11" t="n">
-        <v>251.0605458824941</v>
+        <v>244.4962209066295</v>
       </c>
       <c r="C11" t="n">
-        <v>254.5806764744798</v>
+        <v>248.6708040685723</v>
       </c>
       <c r="D11" t="n">
-        <v>240.6290201908687</v>
+        <v>240.1233077479242</v>
       </c>
       <c r="E11" t="n">
-        <v>243.9310150146484</v>
+        <v>241.0355682373047</v>
       </c>
       <c r="F11" t="n">
-        <v>24869700</v>
+        <v>10851200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B12" t="n">
-        <v>244.4962363844956</v>
+        <v>242.9394234832453</v>
       </c>
       <c r="C12" t="n">
-        <v>248.670819810711</v>
+        <v>253.2519480605562</v>
       </c>
       <c r="D12" t="n">
-        <v>240.1233229489625</v>
+        <v>242.2453138708127</v>
       </c>
       <c r="E12" t="n">
-        <v>241.0355834960938</v>
+        <v>252.1413726806641</v>
       </c>
       <c r="F12" t="n">
-        <v>10851200</v>
+        <v>9963900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B13" t="n">
-        <v>242.9394234832453</v>
+        <v>252.359543952159</v>
       </c>
       <c r="C13" t="n">
-        <v>253.2519480605562</v>
+        <v>264.8833249829649</v>
       </c>
       <c r="D13" t="n">
-        <v>242.2453138708127</v>
+        <v>251.8637491703276</v>
       </c>
       <c r="E13" t="n">
-        <v>252.1413726806641</v>
+        <v>261.1946105957031</v>
       </c>
       <c r="F13" t="n">
-        <v>9963900</v>
+        <v>13354700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B14" t="n">
-        <v>252.3595144668565</v>
+        <v>259.9947719140093</v>
       </c>
       <c r="C14" t="n">
-        <v>264.883294034403</v>
+        <v>260.1930716520554</v>
       </c>
       <c r="D14" t="n">
-        <v>251.863719742953</v>
+        <v>254.3526253920043</v>
       </c>
       <c r="E14" t="n">
-        <v>261.194580078125</v>
+        <v>254.4815368652344</v>
       </c>
       <c r="F14" t="n">
-        <v>13354700</v>
+        <v>9370000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B15" t="n">
-        <v>259.9947719140093</v>
+        <v>255.4334634999039</v>
       </c>
       <c r="C15" t="n">
-        <v>260.1930716520554</v>
+        <v>256.3853809552256</v>
       </c>
       <c r="D15" t="n">
-        <v>254.3526253920043</v>
+        <v>251.982721115611</v>
       </c>
       <c r="E15" t="n">
-        <v>254.4815368652344</v>
+        <v>252.9049072265625</v>
       </c>
       <c r="F15" t="n">
-        <v>9370000</v>
+        <v>6110100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B16" t="n">
-        <v>255.4334634999039</v>
+        <v>255.254980605377</v>
       </c>
       <c r="C16" t="n">
-        <v>256.3853809552256</v>
+        <v>256.3258839430272</v>
       </c>
       <c r="D16" t="n">
-        <v>251.982721115611</v>
+        <v>251.8637312244832</v>
       </c>
       <c r="E16" t="n">
-        <v>252.9049072265625</v>
+        <v>252.6867523193359</v>
       </c>
       <c r="F16" t="n">
-        <v>6110100</v>
+        <v>5490800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B17" t="n">
-        <v>255.254980605377</v>
+        <v>254.9178252470085</v>
       </c>
       <c r="C17" t="n">
-        <v>256.3258839430272</v>
+        <v>255.9292659432784</v>
       </c>
       <c r="D17" t="n">
-        <v>251.8637312244832</v>
+        <v>252.7760033429592</v>
       </c>
       <c r="E17" t="n">
-        <v>252.6867523193359</v>
+        <v>253.3213806152344</v>
       </c>
       <c r="F17" t="n">
-        <v>5490800</v>
+        <v>4942400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B18" t="n">
-        <v>254.9178252470085</v>
+        <v>253.3213661855435</v>
       </c>
       <c r="C18" t="n">
-        <v>255.9292659432784</v>
+        <v>256.663017898251</v>
       </c>
       <c r="D18" t="n">
-        <v>252.7760033429592</v>
+        <v>252.0025503587843</v>
       </c>
       <c r="E18" t="n">
-        <v>253.3213806152344</v>
+        <v>252.1215362548828</v>
       </c>
       <c r="F18" t="n">
-        <v>4942400</v>
+        <v>6435600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B19" t="n">
-        <v>253.3213661855435</v>
+        <v>249.8805444255208</v>
       </c>
       <c r="C19" t="n">
-        <v>256.663017898251</v>
+        <v>251.4373471434884</v>
       </c>
       <c r="D19" t="n">
-        <v>252.0025503587843</v>
+        <v>246.945432960583</v>
       </c>
       <c r="E19" t="n">
-        <v>252.1215362548828</v>
+        <v>249.3450927734375</v>
       </c>
       <c r="F19" t="n">
-        <v>6435600</v>
+        <v>7904200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B20" t="n">
-        <v>249.8805444255208</v>
+        <v>248.3931555366784</v>
       </c>
       <c r="C20" t="n">
-        <v>251.4373471434884</v>
+        <v>257.0993096380665</v>
       </c>
       <c r="D20" t="n">
-        <v>246.945432960583</v>
+        <v>247.8973608150483</v>
       </c>
       <c r="E20" t="n">
-        <v>249.3450927734375</v>
+        <v>254.4914245605469</v>
       </c>
       <c r="F20" t="n">
-        <v>7904200</v>
+        <v>7767800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B21" t="n">
-        <v>248.3931555366784</v>
+        <v>252.657000570364</v>
       </c>
       <c r="C21" t="n">
-        <v>257.0993096380665</v>
+        <v>259.6179629024988</v>
       </c>
       <c r="D21" t="n">
-        <v>247.8973608150483</v>
+        <v>250.5052532311086</v>
       </c>
       <c r="E21" t="n">
-        <v>254.4914245605469</v>
+        <v>258.2198181152344</v>
       </c>
       <c r="F21" t="n">
-        <v>7767800</v>
+        <v>6878300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B22" t="n">
-        <v>252.6570304305034</v>
+        <v>257.8132719821094</v>
       </c>
       <c r="C22" t="n">
-        <v>259.617993585316</v>
+        <v>259.3601491931292</v>
       </c>
       <c r="D22" t="n">
-        <v>250.5052828369448</v>
+        <v>252.9544894469363</v>
       </c>
       <c r="E22" t="n">
-        <v>258.2198486328125</v>
+        <v>259.1419982910156</v>
       </c>
       <c r="F22" t="n">
-        <v>6878300</v>
+        <v>7054300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B23" t="n">
-        <v>257.8132719821094</v>
+        <v>255.9788221233241</v>
       </c>
       <c r="C23" t="n">
-        <v>259.3601491931292</v>
+        <v>257.0795021986246</v>
       </c>
       <c r="D23" t="n">
-        <v>252.9544894469363</v>
+        <v>251.3282801006067</v>
       </c>
       <c r="E23" t="n">
-        <v>259.1419982910156</v>
+        <v>252.3000335693359</v>
       </c>
       <c r="F23" t="n">
-        <v>7054300</v>
+        <v>6792200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B24" t="n">
-        <v>255.9788221233241</v>
+        <v>252.5578398334985</v>
       </c>
       <c r="C24" t="n">
-        <v>257.0795021986246</v>
+        <v>254.6699151564536</v>
       </c>
       <c r="D24" t="n">
-        <v>251.3282801006067</v>
+        <v>249.8904616870965</v>
       </c>
       <c r="E24" t="n">
-        <v>252.3000335693359</v>
+        <v>250.5548248291016</v>
       </c>
       <c r="F24" t="n">
-        <v>6792200</v>
+        <v>5241200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B25" t="n">
-        <v>252.5578552142711</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="C25" t="n">
-        <v>254.6699306658516</v>
+        <v>248.4328164468309</v>
       </c>
       <c r="D25" t="n">
-        <v>249.8904769054258</v>
+        <v>232.5078921531912</v>
       </c>
       <c r="E25" t="n">
-        <v>250.5548400878906</v>
+        <v>237.2576141357422</v>
       </c>
       <c r="F25" t="n">
-        <v>5241200</v>
+        <v>11041800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B26" t="n">
-        <v>248.4328164468309</v>
+        <v>234.1638631836621</v>
       </c>
       <c r="C26" t="n">
-        <v>248.4328164468309</v>
+        <v>238.9433320161168</v>
       </c>
       <c r="D26" t="n">
-        <v>232.5078921531912</v>
+        <v>233.8068903450121</v>
       </c>
       <c r="E26" t="n">
-        <v>237.2576141357422</v>
+        <v>237.8625030517578</v>
       </c>
       <c r="F26" t="n">
-        <v>11041800</v>
+        <v>5741500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B27" t="n">
-        <v>234.1638481621394</v>
+        <v>237.9814688826704</v>
       </c>
       <c r="C27" t="n">
-        <v>238.943316687993</v>
+        <v>239.8754083705041</v>
       </c>
       <c r="D27" t="n">
-        <v>233.8068753463891</v>
+        <v>233.1028505862302</v>
       </c>
       <c r="E27" t="n">
-        <v>237.8624877929688</v>
+        <v>239.6770935058594</v>
       </c>
       <c r="F27" t="n">
-        <v>5741500</v>
+        <v>6486600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B28" t="n">
-        <v>237.9814688826704</v>
+        <v>239.865480170848</v>
       </c>
       <c r="C28" t="n">
-        <v>239.8754083705041</v>
+        <v>243.6335230797314</v>
       </c>
       <c r="D28" t="n">
-        <v>233.1028505862302</v>
+        <v>239.131713666637</v>
       </c>
       <c r="E28" t="n">
-        <v>239.6770935058594</v>
+        <v>242.4436187744141</v>
       </c>
       <c r="F28" t="n">
-        <v>6486600</v>
+        <v>5762800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B29" t="n">
-        <v>239.8654952673756</v>
+        <v>243.6732075926712</v>
       </c>
       <c r="C29" t="n">
-        <v>243.63353841341</v>
+        <v>246.3405706207466</v>
       </c>
       <c r="D29" t="n">
-        <v>239.1317287169831</v>
+        <v>241.63052052637</v>
       </c>
       <c r="E29" t="n">
-        <v>242.4436340332031</v>
+        <v>243.9508514404297</v>
       </c>
       <c r="F29" t="n">
-        <v>5762800</v>
+        <v>4278200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B30" t="n">
-        <v>243.6732075926712</v>
+        <v>243.1873207442872</v>
       </c>
       <c r="C30" t="n">
-        <v>246.3405706207466</v>
+        <v>243.8318478561575</v>
       </c>
       <c r="D30" t="n">
-        <v>241.63052052637</v>
+        <v>237.8922365355373</v>
       </c>
       <c r="E30" t="n">
-        <v>243.9508514404297</v>
+        <v>238.4078521728516</v>
       </c>
       <c r="F30" t="n">
-        <v>4278200</v>
+        <v>5542100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B31" t="n">
-        <v>243.1873207442872</v>
+        <v>236.3056926086296</v>
       </c>
       <c r="C31" t="n">
-        <v>243.8318478561575</v>
+        <v>243.1179076689137</v>
       </c>
       <c r="D31" t="n">
-        <v>237.8922365355373</v>
+        <v>235.4231785540507</v>
       </c>
       <c r="E31" t="n">
-        <v>238.4078521728516</v>
+        <v>241.6107025146484</v>
       </c>
       <c r="F31" t="n">
-        <v>5542100</v>
+        <v>5512900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B32" t="n">
-        <v>236.3056926086296</v>
+        <v>240.0340726996036</v>
       </c>
       <c r="C32" t="n">
-        <v>243.1179076689137</v>
+        <v>240.787675257482</v>
       </c>
       <c r="D32" t="n">
-        <v>235.4231785540507</v>
+        <v>233.6085619749179</v>
       </c>
       <c r="E32" t="n">
-        <v>241.6107025146484</v>
+        <v>235.0364532470703</v>
       </c>
       <c r="F32" t="n">
-        <v>5512900</v>
+        <v>5280900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B33" t="n">
-        <v>240.0340726996036</v>
+        <v>234.2531087461558</v>
       </c>
       <c r="C33" t="n">
-        <v>240.787675257482</v>
+        <v>235.7900603656055</v>
       </c>
       <c r="D33" t="n">
-        <v>233.6085619749179</v>
+        <v>228.3333182252886</v>
       </c>
       <c r="E33" t="n">
-        <v>235.0364532470703</v>
+        <v>231.5361480712891</v>
       </c>
       <c r="F33" t="n">
-        <v>5280900</v>
+        <v>8045100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B34" t="n">
-        <v>234.2531087461558</v>
+        <v>230.0487686636922</v>
       </c>
       <c r="C34" t="n">
-        <v>235.7900603656055</v>
+        <v>230.3264125188844</v>
       </c>
       <c r="D34" t="n">
-        <v>228.3333182252886</v>
+        <v>223.1671349733107</v>
       </c>
       <c r="E34" t="n">
-        <v>231.5361480712891</v>
+        <v>225.9634246826172</v>
       </c>
       <c r="F34" t="n">
-        <v>8045100</v>
+        <v>9710700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B35" t="n">
-        <v>230.0487686636922</v>
+        <v>227.3218743517198</v>
       </c>
       <c r="C35" t="n">
-        <v>230.3264125188844</v>
+        <v>229.1265743572826</v>
       </c>
       <c r="D35" t="n">
-        <v>223.1671349733107</v>
+        <v>221.4219203335674</v>
       </c>
       <c r="E35" t="n">
-        <v>225.9634246826172</v>
+        <v>223.4745025634766</v>
       </c>
       <c r="F35" t="n">
-        <v>9710700</v>
+        <v>7521100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B36" t="n">
-        <v>227.3218898732066</v>
+        <v>222.9688137796853</v>
       </c>
       <c r="C36" t="n">
-        <v>229.1265900019938</v>
+        <v>226.7566777713456</v>
       </c>
       <c r="D36" t="n">
-        <v>221.4219354522067</v>
+        <v>220.0932103050241</v>
       </c>
       <c r="E36" t="n">
-        <v>223.4745178222656</v>
+        <v>225.1998901367188</v>
       </c>
       <c r="F36" t="n">
-        <v>7521100</v>
+        <v>7479300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B37" t="n">
-        <v>222.9687986720664</v>
+        <v>225.4279386105234</v>
       </c>
       <c r="C37" t="n">
-        <v>226.7566624070738</v>
+        <v>226.9153227636102</v>
       </c>
       <c r="D37" t="n">
-        <v>220.0931953922465</v>
+        <v>223.1472798830329</v>
       </c>
       <c r="E37" t="n">
-        <v>225.1998748779297</v>
+        <v>224.9123229980469</v>
       </c>
       <c r="F37" t="n">
-        <v>7479300</v>
+        <v>8563300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B38" t="n">
-        <v>225.4279691980636</v>
+        <v>224.8924975422598</v>
       </c>
       <c r="C38" t="n">
-        <v>226.9153535529684</v>
+        <v>232.656645001925</v>
       </c>
       <c r="D38" t="n">
-        <v>223.1473101611184</v>
+        <v>224.614853697738</v>
       </c>
       <c r="E38" t="n">
-        <v>224.912353515625</v>
+        <v>232.1509246826172</v>
       </c>
       <c r="F38" t="n">
-        <v>8563300</v>
+        <v>10233000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B39" t="n">
-        <v>224.8924975422598</v>
+        <v>228.5712765635558</v>
       </c>
       <c r="C39" t="n">
-        <v>232.656645001925</v>
+        <v>230.8618608815026</v>
       </c>
       <c r="D39" t="n">
-        <v>224.614853697738</v>
+        <v>224.0992136322821</v>
       </c>
       <c r="E39" t="n">
-        <v>232.1509246826172</v>
+        <v>226.2311248779297</v>
       </c>
       <c r="F39" t="n">
-        <v>10233000</v>
+        <v>8506600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B40" t="n">
-        <v>228.5712919801828</v>
+        <v>227.0739873247604</v>
       </c>
       <c r="C40" t="n">
-        <v>230.8618764526245</v>
+        <v>230.6040433967966</v>
       </c>
       <c r="D40" t="n">
-        <v>224.0992287472785</v>
+        <v>226.7071040647147</v>
       </c>
       <c r="E40" t="n">
-        <v>226.2311401367188</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="F40" t="n">
-        <v>8506600</v>
+        <v>3691500</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B41" t="n">
-        <v>227.0739873247604</v>
+        <v>226.7467645282661</v>
       </c>
       <c r="C41" t="n">
-        <v>230.6040433967966</v>
+        <v>232.2798356411572</v>
       </c>
       <c r="D41" t="n">
-        <v>226.7071040647147</v>
+        <v>226.6773611325171</v>
       </c>
       <c r="E41" t="n">
-        <v>228.6010284423828</v>
+        <v>230.8717803955078</v>
       </c>
       <c r="F41" t="n">
-        <v>3691500</v>
+        <v>5634700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B42" t="n">
-        <v>226.7467645282661</v>
+        <v>231.0601885043919</v>
       </c>
       <c r="C42" t="n">
-        <v>232.2798356411572</v>
+        <v>234.6596480847597</v>
       </c>
       <c r="D42" t="n">
-        <v>226.6773611325171</v>
+        <v>229.67195413226</v>
       </c>
       <c r="E42" t="n">
-        <v>230.8717803955078</v>
+        <v>232.7359771728516</v>
       </c>
       <c r="F42" t="n">
-        <v>5634700</v>
+        <v>7626200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B43" t="n">
-        <v>231.0602036533118</v>
+        <v>233.3805083869321</v>
       </c>
       <c r="C43" t="n">
-        <v>234.6596634696697</v>
+        <v>237.2477014354837</v>
       </c>
       <c r="D43" t="n">
-        <v>229.6719691901636</v>
+        <v>231.1990144844042</v>
       </c>
       <c r="E43" t="n">
-        <v>232.7359924316406</v>
+        <v>236.7122497558594</v>
       </c>
       <c r="F43" t="n">
-        <v>7626200</v>
+        <v>13782000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B44" t="n">
-        <v>233.3804933429116</v>
+        <v>241.6404418420451</v>
       </c>
       <c r="C44" t="n">
-        <v>237.2476861421788</v>
+        <v>246.8760330652079</v>
       </c>
       <c r="D44" t="n">
-        <v>231.1989995810056</v>
+        <v>235.6016655641461</v>
       </c>
       <c r="E44" t="n">
-        <v>236.7122344970703</v>
+        <v>245.3787384033203</v>
       </c>
       <c r="F44" t="n">
-        <v>13782000</v>
+        <v>20912100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B45" t="n">
-        <v>241.6404418420451</v>
+        <v>248.7203919866921</v>
       </c>
       <c r="C45" t="n">
-        <v>246.8760330652079</v>
+        <v>259.6774588065476</v>
       </c>
       <c r="D45" t="n">
-        <v>235.6016655641461</v>
+        <v>247.4015761578514</v>
       </c>
       <c r="E45" t="n">
-        <v>245.3787384033203</v>
+        <v>258.3784790039062</v>
       </c>
       <c r="F45" t="n">
-        <v>20912100</v>
+        <v>15852400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B46" t="n">
-        <v>248.7203919866921</v>
+        <v>259.6774396530913</v>
       </c>
       <c r="C46" t="n">
-        <v>259.6774588065476</v>
+        <v>262.0572481860146</v>
       </c>
       <c r="D46" t="n">
-        <v>247.4015761578514</v>
+        <v>254.1840258460871</v>
       </c>
       <c r="E46" t="n">
-        <v>258.3784790039062</v>
+        <v>257.3471984863281</v>
       </c>
       <c r="F46" t="n">
-        <v>15852400</v>
+        <v>10805400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B47" t="n">
-        <v>259.6774396530913</v>
+        <v>257.8132357344463</v>
       </c>
       <c r="C47" t="n">
-        <v>262.0572481860146</v>
+        <v>260.0443118129175</v>
       </c>
       <c r="D47" t="n">
-        <v>254.1840258460871</v>
+        <v>256.8216463662369</v>
       </c>
       <c r="E47" t="n">
-        <v>257.3471984863281</v>
+        <v>258.8246459960938</v>
       </c>
       <c r="F47" t="n">
-        <v>10805400</v>
+        <v>8045900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B48" t="n">
-        <v>257.8132661327708</v>
+        <v>258.556940201721</v>
       </c>
       <c r="C48" t="n">
-        <v>260.0443424743044</v>
+        <v>263.6933661135803</v>
       </c>
       <c r="D48" t="n">
-        <v>256.8216766476447</v>
+        <v>256.9703910840639</v>
       </c>
       <c r="E48" t="n">
-        <v>258.8246765136719</v>
+        <v>261.9779357910156</v>
       </c>
       <c r="F48" t="n">
-        <v>8045900</v>
+        <v>8894700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B49" t="n">
-        <v>258.5569703207904</v>
+        <v>261.2838154474661</v>
       </c>
       <c r="C49" t="n">
-        <v>263.6933968309874</v>
+        <v>265.6468028980126</v>
       </c>
       <c r="D49" t="n">
-        <v>256.9704210183176</v>
+        <v>258.5767654029829</v>
       </c>
       <c r="E49" t="n">
-        <v>261.9779663085938</v>
+        <v>260.1434936523438</v>
       </c>
       <c r="F49" t="n">
-        <v>8894700</v>
+        <v>7783800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B50" t="n">
-        <v>261.2838154474661</v>
+        <v>261.3036648523665</v>
       </c>
       <c r="C50" t="n">
-        <v>265.6468028980126</v>
+        <v>262.2655079172122</v>
       </c>
       <c r="D50" t="n">
-        <v>258.5767654029829</v>
+        <v>258.7156306765648</v>
       </c>
       <c r="E50" t="n">
-        <v>260.1434936523438</v>
+        <v>260.0245361328125</v>
       </c>
       <c r="F50" t="n">
-        <v>7783800</v>
+        <v>6006600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B51" t="n">
-        <v>261.3036341846645</v>
+        <v>259.013086162544</v>
       </c>
       <c r="C51" t="n">
-        <v>262.2654771366241</v>
+        <v>260.074094195654</v>
       </c>
       <c r="D51" t="n">
-        <v>258.7156003126054</v>
+        <v>250.9613842226157</v>
       </c>
       <c r="E51" t="n">
-        <v>260.0245056152344</v>
+        <v>252.4388580322266</v>
       </c>
       <c r="F51" t="n">
-        <v>6006600</v>
+        <v>10271800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B52" t="n">
-        <v>259.013086162544</v>
+        <v>251.8637174841621</v>
       </c>
       <c r="C52" t="n">
-        <v>260.074094195654</v>
+        <v>253.7080744457603</v>
       </c>
       <c r="D52" t="n">
-        <v>250.9613842226157</v>
+        <v>249.9896140498327</v>
       </c>
       <c r="E52" t="n">
-        <v>252.4388580322266</v>
+        <v>252.7660675048828</v>
       </c>
       <c r="F52" t="n">
-        <v>10271800</v>
+        <v>6145300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B53" t="n">
-        <v>251.8637326884788</v>
+        <v>254.174158538615</v>
       </c>
       <c r="C53" t="n">
-        <v>253.7080897614157</v>
+        <v>259.766738620961</v>
       </c>
       <c r="D53" t="n">
-        <v>249.989629141015</v>
+        <v>254.0948446823945</v>
       </c>
       <c r="E53" t="n">
-        <v>252.7660827636719</v>
+        <v>255.9689636230469</v>
       </c>
       <c r="F53" t="n">
-        <v>6145300</v>
+        <v>6269000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,25 +1821,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B54" t="n">
-        <v>254.1741282350202</v>
+        <v>256.6601807669533</v>
       </c>
       <c r="C54" t="n">
-        <v>259.7667076505979</v>
+        <v>258.2989382537239</v>
       </c>
       <c r="D54" t="n">
-        <v>254.0948143882558</v>
+        <v>254.4155616010984</v>
       </c>
       <c r="E54" t="n">
-        <v>255.9689331054688</v>
+        <v>256.0940551757812</v>
       </c>
       <c r="F54" t="n">
-        <v>6269000</v>
+        <v>5654200</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B55" t="n">
-        <v>256.6601807669533</v>
+        <v>258.904790639318</v>
       </c>
       <c r="C55" t="n">
-        <v>258.2989382537239</v>
+        <v>260.2555449501942</v>
       </c>
       <c r="D55" t="n">
-        <v>254.4155616010984</v>
+        <v>253.7600731430874</v>
       </c>
       <c r="E55" t="n">
-        <v>256.0940551757812</v>
+        <v>258.1400451660156</v>
       </c>
       <c r="F55" t="n">
-        <v>5654200</v>
+        <v>20732100</v>
       </c>
       <c r="G55" t="n">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B56" t="n">
-        <v>258.9047600313309</v>
+        <v>258.8451791646396</v>
       </c>
       <c r="C56" t="n">
-        <v>260.2555141825196</v>
+        <v>262.827880859375</v>
       </c>
       <c r="D56" t="n">
-        <v>253.760043143314</v>
+        <v>256.6502376986757</v>
       </c>
       <c r="E56" t="n">
-        <v>258.1400146484375</v>
+        <v>262.827880859375</v>
       </c>
       <c r="F56" t="n">
-        <v>20732100</v>
+        <v>5664200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B57" t="n">
-        <v>258.8451791646396</v>
+        <v>260.930890915143</v>
       </c>
       <c r="C57" t="n">
-        <v>262.827880859375</v>
+        <v>262.4405288782817</v>
       </c>
       <c r="D57" t="n">
-        <v>256.6502376986757</v>
+        <v>258.7458606831942</v>
       </c>
       <c r="E57" t="n">
-        <v>262.827880859375</v>
+        <v>261.6360473632812</v>
       </c>
       <c r="F57" t="n">
-        <v>5664200</v>
+        <v>4745100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B58" t="n">
-        <v>260.930890915143</v>
+        <v>261.4374386085776</v>
       </c>
       <c r="C58" t="n">
-        <v>262.4405288782817</v>
+        <v>264.486509153036</v>
       </c>
       <c r="D58" t="n">
-        <v>258.7458606831942</v>
+        <v>260.7620463111714</v>
       </c>
       <c r="E58" t="n">
-        <v>261.6360473632812</v>
+        <v>263.45361328125</v>
       </c>
       <c r="F58" t="n">
-        <v>4745100</v>
+        <v>2076600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B59" t="n">
-        <v>261.4374386085776</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="C59" t="n">
-        <v>264.486509153036</v>
+        <v>266.0855294787636</v>
       </c>
       <c r="D59" t="n">
-        <v>260.7620463111714</v>
+        <v>262.9966928996288</v>
       </c>
       <c r="E59" t="n">
-        <v>263.45361328125</v>
+        <v>264.2679748535156</v>
       </c>
       <c r="F59" t="n">
-        <v>2076600</v>
+        <v>2456400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B60" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="C60" t="n">
-        <v>266.0855294787636</v>
+        <v>267.2773540092613</v>
       </c>
       <c r="D60" t="n">
-        <v>262.9966928996288</v>
+        <v>262.9073239460033</v>
       </c>
       <c r="E60" t="n">
-        <v>264.2679748535156</v>
+        <v>264.4169921875</v>
       </c>
       <c r="F60" t="n">
-        <v>2456400</v>
+        <v>4300100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B61" t="n">
-        <v>262.9073239460033</v>
+        <v>264.8440818513142</v>
       </c>
       <c r="C61" t="n">
-        <v>267.2773540092613</v>
+        <v>266.453045001104</v>
       </c>
       <c r="D61" t="n">
-        <v>262.9073239460033</v>
+        <v>263.5231220141856</v>
       </c>
       <c r="E61" t="n">
-        <v>264.4169921875</v>
+        <v>264.109130859375</v>
       </c>
       <c r="F61" t="n">
-        <v>4300100</v>
+        <v>3291800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B62" t="n">
-        <v>264.8440512488132</v>
+        <v>263.4833740671746</v>
       </c>
       <c r="C62" t="n">
-        <v>266.4530142126886</v>
+        <v>264.2878555133287</v>
       </c>
       <c r="D62" t="n">
-        <v>263.5230915643202</v>
+        <v>262.5895091614203</v>
       </c>
       <c r="E62" t="n">
-        <v>264.1091003417969</v>
+        <v>263.10595703125</v>
       </c>
       <c r="F62" t="n">
-        <v>3291800</v>
+        <v>3367900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B63" t="n">
-        <v>263.4833740671746</v>
+        <v>263.1953602739627</v>
       </c>
       <c r="C63" t="n">
-        <v>264.2878555133287</v>
+        <v>263.5727773382559</v>
       </c>
       <c r="D63" t="n">
-        <v>262.5895091614203</v>
+        <v>250.7606167452008</v>
       </c>
       <c r="E63" t="n">
-        <v>263.10595703125</v>
+        <v>251.8928527832031</v>
       </c>
       <c r="F63" t="n">
-        <v>3367900</v>
+        <v>9680600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B64" t="n">
-        <v>263.1953602739627</v>
+        <v>251.8928411889898</v>
       </c>
       <c r="C64" t="n">
-        <v>263.5727773382559</v>
+        <v>257.8221866599169</v>
       </c>
       <c r="D64" t="n">
-        <v>250.7606167452008</v>
+        <v>250.5917647228683</v>
       </c>
       <c r="E64" t="n">
-        <v>251.8928527832031</v>
+        <v>254.5148773193359</v>
       </c>
       <c r="F64" t="n">
-        <v>9680600</v>
+        <v>6421500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B65" t="n">
-        <v>251.8928562905814</v>
+        <v>253.4620895509313</v>
       </c>
       <c r="C65" t="n">
-        <v>257.8222021169872</v>
+        <v>261.7552171079225</v>
       </c>
       <c r="D65" t="n">
-        <v>250.5917797464572</v>
+        <v>253.2634545783159</v>
       </c>
       <c r="E65" t="n">
-        <v>254.514892578125</v>
+        <v>261.1096496582031</v>
       </c>
       <c r="F65" t="n">
-        <v>6421500</v>
+        <v>6103300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B66" t="n">
-        <v>253.4620895509313</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="C66" t="n">
-        <v>261.7552171079225</v>
+        <v>266.0060550943219</v>
       </c>
       <c r="D66" t="n">
-        <v>253.2634545783159</v>
+        <v>261.7055558804709</v>
       </c>
       <c r="E66" t="n">
-        <v>261.1096496582031</v>
+        <v>264.3077087402344</v>
       </c>
       <c r="F66" t="n">
-        <v>6103300</v>
+        <v>5976200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B67" t="n">
-        <v>261.7055860975985</v>
+        <v>262.5994389217771</v>
       </c>
       <c r="C67" t="n">
-        <v>266.0060858079951</v>
+        <v>263.394009134812</v>
       </c>
       <c r="D67" t="n">
-        <v>261.7055860975985</v>
+        <v>258.6366203853271</v>
       </c>
       <c r="E67" t="n">
-        <v>264.3077392578125</v>
+        <v>258.7557983398438</v>
       </c>
       <c r="F67" t="n">
-        <v>5976200</v>
+        <v>5243500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B68" t="n">
-        <v>262.5994389217771</v>
+        <v>258.2293887773175</v>
       </c>
       <c r="C68" t="n">
-        <v>263.394009134812</v>
+        <v>259.2523732204683</v>
       </c>
       <c r="D68" t="n">
-        <v>258.6366203853271</v>
+        <v>254.7631655270811</v>
       </c>
       <c r="E68" t="n">
-        <v>258.7557983398438</v>
+        <v>258.1697998046875</v>
       </c>
       <c r="F68" t="n">
-        <v>5243500</v>
+        <v>5174400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B69" t="n">
-        <v>258.2294193019395</v>
+        <v>257.2362444131007</v>
       </c>
       <c r="C69" t="n">
-        <v>259.2524038660146</v>
+        <v>259.778808728465</v>
       </c>
       <c r="D69" t="n">
-        <v>254.7631956419699</v>
+        <v>254.0282445272995</v>
       </c>
       <c r="E69" t="n">
-        <v>258.1698303222656</v>
+        <v>257.6335144042969</v>
       </c>
       <c r="F69" t="n">
-        <v>5174400</v>
+        <v>4927700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B70" t="n">
-        <v>257.2362444131007</v>
+        <v>255.9053572301452</v>
       </c>
       <c r="C70" t="n">
-        <v>259.778808728465</v>
+        <v>259.1332249596227</v>
       </c>
       <c r="D70" t="n">
-        <v>254.0282445272995</v>
+        <v>238.7231659776434</v>
       </c>
       <c r="E70" t="n">
-        <v>257.6335144042969</v>
+        <v>239.4183959960938</v>
       </c>
       <c r="F70" t="n">
-        <v>4927700</v>
+        <v>13661000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B71" t="n">
-        <v>255.9053572301452</v>
+        <v>237.5511941796288</v>
       </c>
       <c r="C71" t="n">
-        <v>259.1332249596227</v>
+        <v>240.5903685304685</v>
       </c>
       <c r="D71" t="n">
-        <v>238.7231659776434</v>
+        <v>234.849731125901</v>
       </c>
       <c r="E71" t="n">
-        <v>239.4183959960938</v>
+        <v>237.9385528564453</v>
       </c>
       <c r="F71" t="n">
-        <v>13661000</v>
+        <v>10149300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B72" t="n">
-        <v>237.5511941796288</v>
+        <v>235.4059054123066</v>
       </c>
       <c r="C72" t="n">
-        <v>240.5903685304685</v>
+        <v>237.2135033883542</v>
       </c>
       <c r="D72" t="n">
-        <v>234.849731125901</v>
+        <v>230.0923326840245</v>
       </c>
       <c r="E72" t="n">
-        <v>237.9385528564453</v>
+        <v>231.9396667480469</v>
       </c>
       <c r="F72" t="n">
-        <v>10149300</v>
+        <v>11489600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B73" t="n">
-        <v>235.4059054123066</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="C73" t="n">
-        <v>237.2135033883542</v>
+        <v>231.3636110626874</v>
       </c>
       <c r="D73" t="n">
-        <v>230.0923326840245</v>
+        <v>224.8979495180149</v>
       </c>
       <c r="E73" t="n">
-        <v>231.9396667480469</v>
+        <v>225.5633850097656</v>
       </c>
       <c r="F73" t="n">
-        <v>11489600</v>
+        <v>13902600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B74" t="n">
-        <v>231.3636110626874</v>
+        <v>222.0176902636222</v>
       </c>
       <c r="C74" t="n">
-        <v>231.3636110626874</v>
+        <v>226.3877354418118</v>
       </c>
       <c r="D74" t="n">
-        <v>224.8979495180149</v>
+        <v>217.8661632569629</v>
       </c>
       <c r="E74" t="n">
-        <v>225.5633850097656</v>
+        <v>218.5713348388672</v>
       </c>
       <c r="F74" t="n">
-        <v>13902600</v>
+        <v>13050800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B75" t="n">
-        <v>222.0176902636222</v>
+        <v>218.6507904829158</v>
       </c>
       <c r="C75" t="n">
-        <v>226.3877354418118</v>
+        <v>221.8687318042425</v>
       </c>
       <c r="D75" t="n">
-        <v>217.8661632569629</v>
+        <v>217.4689070154735</v>
       </c>
       <c r="E75" t="n">
-        <v>218.5713348388672</v>
+        <v>220.0710601806641</v>
       </c>
       <c r="F75" t="n">
-        <v>13050800</v>
+        <v>12616600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B76" t="n">
-        <v>218.6507904829158</v>
+        <v>220.7265600038705</v>
       </c>
       <c r="C76" t="n">
-        <v>221.8687318042425</v>
+        <v>227.162427221411</v>
       </c>
       <c r="D76" t="n">
-        <v>217.4689070154735</v>
+        <v>219.6042504088122</v>
       </c>
       <c r="E76" t="n">
-        <v>220.0710601806641</v>
+        <v>226.5367126464844</v>
       </c>
       <c r="F76" t="n">
-        <v>12616600</v>
+        <v>9483000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B77" t="n">
-        <v>220.7265600038705</v>
+        <v>225.2356384112152</v>
       </c>
       <c r="C77" t="n">
-        <v>227.162427221411</v>
+        <v>229.2779291905748</v>
       </c>
       <c r="D77" t="n">
-        <v>219.6042504088122</v>
+        <v>225.1065188551059</v>
       </c>
       <c r="E77" t="n">
-        <v>226.5367126464844</v>
+        <v>226.4969940185547</v>
       </c>
       <c r="F77" t="n">
-        <v>9483000</v>
+        <v>9408000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B78" t="n">
-        <v>225.2356384112152</v>
+        <v>227.8675783015932</v>
       </c>
       <c r="C78" t="n">
-        <v>229.2779291905748</v>
+        <v>229.3772313706373</v>
       </c>
       <c r="D78" t="n">
-        <v>225.1065188551059</v>
+        <v>226.0401123076792</v>
       </c>
       <c r="E78" t="n">
-        <v>226.4969940185547</v>
+        <v>227.8377838134766</v>
       </c>
       <c r="F78" t="n">
-        <v>9408000</v>
+        <v>7239600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B79" t="n">
-        <v>227.8675783015932</v>
+        <v>230.3605061244008</v>
       </c>
       <c r="C79" t="n">
-        <v>229.3772313706373</v>
+        <v>234.1346314027617</v>
       </c>
       <c r="D79" t="n">
-        <v>226.0401123076792</v>
+        <v>224.7291202738612</v>
       </c>
       <c r="E79" t="n">
-        <v>227.8377838134766</v>
+        <v>226.9737243652344</v>
       </c>
       <c r="F79" t="n">
-        <v>7239600</v>
+        <v>9838400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B80" t="n">
-        <v>230.3604906379282</v>
+        <v>227.8278625141174</v>
       </c>
       <c r="C80" t="n">
-        <v>234.1346156625655</v>
+        <v>230.2810431236355</v>
       </c>
       <c r="D80" t="n">
-        <v>224.7291051659704</v>
+        <v>226.1195744340916</v>
       </c>
       <c r="E80" t="n">
-        <v>226.9737091064453</v>
+        <v>226.4076080322266</v>
       </c>
       <c r="F80" t="n">
-        <v>9838400</v>
+        <v>8465900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B81" t="n">
-        <v>227.8278625141174</v>
+        <v>215.1944745404488</v>
       </c>
       <c r="C81" t="n">
-        <v>230.2810431236355</v>
+        <v>215.8003210439947</v>
       </c>
       <c r="D81" t="n">
-        <v>226.1195744340916</v>
+        <v>207.358206080909</v>
       </c>
       <c r="E81" t="n">
-        <v>226.4076080322266</v>
+        <v>212.6221160888672</v>
       </c>
       <c r="F81" t="n">
-        <v>8465900</v>
+        <v>18555600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B82" t="n">
-        <v>215.1944899838427</v>
+        <v>212.7015749295142</v>
       </c>
       <c r="C82" t="n">
-        <v>215.8003365308671</v>
+        <v>214.0821084291109</v>
       </c>
       <c r="D82" t="n">
-        <v>207.3582209619344</v>
+        <v>209.5928853669118</v>
       </c>
       <c r="E82" t="n">
-        <v>212.6221313476562</v>
+        <v>210.8442993164062</v>
       </c>
       <c r="F82" t="n">
-        <v>18555600</v>
+        <v>11090400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B83" t="n">
-        <v>212.7015749295142</v>
+        <v>212.8902908724165</v>
       </c>
       <c r="C83" t="n">
-        <v>214.0821084291109</v>
+        <v>215.4129869027477</v>
       </c>
       <c r="D83" t="n">
-        <v>209.5928853669118</v>
+        <v>208.3712731650351</v>
       </c>
       <c r="E83" t="n">
-        <v>210.8442993164062</v>
+        <v>209.3743896484375</v>
       </c>
       <c r="F83" t="n">
-        <v>11090400</v>
+        <v>7950900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B84" t="n">
-        <v>212.8902908724165</v>
+        <v>203.6039568110546</v>
       </c>
       <c r="C84" t="n">
-        <v>215.4129869027477</v>
+        <v>204.16014080488</v>
       </c>
       <c r="D84" t="n">
-        <v>208.3712731650351</v>
+        <v>191.7949279222085</v>
       </c>
       <c r="E84" t="n">
-        <v>209.3743896484375</v>
+        <v>195.0426635742188</v>
       </c>
       <c r="F84" t="n">
-        <v>7950900</v>
+        <v>20194200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B85" t="n">
-        <v>203.6039568110546</v>
+        <v>191.993558028148</v>
       </c>
       <c r="C85" t="n">
-        <v>204.16014080488</v>
+        <v>199.3034370934686</v>
       </c>
       <c r="D85" t="n">
-        <v>191.7949279222085</v>
+        <v>186.0046234920971</v>
       </c>
       <c r="E85" t="n">
-        <v>195.0426635742188</v>
+        <v>198.0818176269531</v>
       </c>
       <c r="F85" t="n">
-        <v>20194200</v>
+        <v>23010000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B86" t="n">
-        <v>191.993558028148</v>
+        <v>192.668943558262</v>
       </c>
       <c r="C86" t="n">
-        <v>199.3034370934686</v>
+        <v>198.2010042649258</v>
       </c>
       <c r="D86" t="n">
-        <v>186.0046234920971</v>
+        <v>187.5043431662378</v>
       </c>
       <c r="E86" t="n">
-        <v>198.0818176269531</v>
+        <v>188.6763153076172</v>
       </c>
       <c r="F86" t="n">
-        <v>23010000</v>
+        <v>21956300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B87" t="n">
-        <v>192.668943558262</v>
+        <v>190.3250127759971</v>
       </c>
       <c r="C87" t="n">
-        <v>198.2010042649258</v>
+        <v>193.2747884158856</v>
       </c>
       <c r="D87" t="n">
-        <v>187.5043431662378</v>
+        <v>185.8457159832669</v>
       </c>
       <c r="E87" t="n">
-        <v>188.6763153076172</v>
+        <v>190.0469207763672</v>
       </c>
       <c r="F87" t="n">
-        <v>21956300</v>
+        <v>13652600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B88" t="n">
-        <v>190.3250127759971</v>
+        <v>188.0108792533576</v>
       </c>
       <c r="C88" t="n">
-        <v>193.2747884158856</v>
+        <v>193.8706944788449</v>
       </c>
       <c r="D88" t="n">
-        <v>185.8457159832669</v>
+        <v>184.465183505092</v>
       </c>
       <c r="E88" t="n">
-        <v>190.0469207763672</v>
+        <v>192.7086639404297</v>
       </c>
       <c r="F88" t="n">
-        <v>13652600</v>
+        <v>12112000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B89" t="n">
-        <v>188.0108792533576</v>
+        <v>190.5931665112882</v>
       </c>
       <c r="C89" t="n">
-        <v>193.8706944788449</v>
+        <v>197.7441470694129</v>
       </c>
       <c r="D89" t="n">
-        <v>184.465183505092</v>
+        <v>189.4510040038842</v>
       </c>
       <c r="E89" t="n">
-        <v>192.7086639404297</v>
+        <v>192.1326141357422</v>
       </c>
       <c r="F89" t="n">
-        <v>12112000</v>
+        <v>13393000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B90" t="n">
-        <v>190.5931665112882</v>
+        <v>191.8346349441069</v>
       </c>
       <c r="C90" t="n">
-        <v>197.7441470694129</v>
+        <v>192.3510979672969</v>
       </c>
       <c r="D90" t="n">
-        <v>189.4510040038842</v>
+        <v>180.5718644212529</v>
       </c>
       <c r="E90" t="n">
-        <v>192.1326141357422</v>
+        <v>183.7401428222656</v>
       </c>
       <c r="F90" t="n">
-        <v>13393000</v>
+        <v>16350200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B91" t="n">
-        <v>191.8346508751069</v>
+        <v>184.6936257308121</v>
       </c>
       <c r="C91" t="n">
-        <v>192.3511139411869</v>
+        <v>187.0375548215625</v>
       </c>
       <c r="D91" t="n">
-        <v>180.5718794169307</v>
+        <v>179.012577513483</v>
       </c>
       <c r="E91" t="n">
-        <v>183.7401580810547</v>
+        <v>184.1672210693359</v>
       </c>
       <c r="F91" t="n">
-        <v>16350200</v>
+        <v>16849100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B92" t="n">
-        <v>184.6936257308121</v>
+        <v>185.1703620229303</v>
       </c>
       <c r="C92" t="n">
-        <v>187.0375548215625</v>
+        <v>192.1326190686923</v>
       </c>
       <c r="D92" t="n">
-        <v>179.012577513483</v>
+        <v>183.0449358454951</v>
       </c>
       <c r="E92" t="n">
-        <v>184.1672210693359</v>
+        <v>188.4280242919922</v>
       </c>
       <c r="F92" t="n">
-        <v>16849100</v>
+        <v>14822900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B93" t="n">
-        <v>185.1703620229303</v>
+        <v>189.6695058452945</v>
       </c>
       <c r="C93" t="n">
-        <v>192.1326190686923</v>
+        <v>191.6856804427425</v>
       </c>
       <c r="D93" t="n">
-        <v>183.0449358454951</v>
+        <v>181.9226203922807</v>
       </c>
       <c r="E93" t="n">
-        <v>188.4280242919922</v>
+        <v>183.0349884033203</v>
       </c>
       <c r="F93" t="n">
-        <v>14822900</v>
+        <v>13692900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B94" t="n">
-        <v>189.6694900334161</v>
+        <v>182.6277925688313</v>
       </c>
       <c r="C94" t="n">
-        <v>191.6856644627849</v>
+        <v>186.8587767567783</v>
       </c>
       <c r="D94" t="n">
-        <v>181.9226052262247</v>
+        <v>180.6215444099069</v>
       </c>
       <c r="E94" t="n">
-        <v>183.0349731445312</v>
+        <v>186.5111541748047</v>
       </c>
       <c r="F94" t="n">
-        <v>13692900</v>
+        <v>9852900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B95" t="n">
-        <v>182.6277776277465</v>
+        <v>185.3292747163753</v>
       </c>
       <c r="C95" t="n">
-        <v>186.8587614695496</v>
+        <v>185.6768821509354</v>
       </c>
       <c r="D95" t="n">
-        <v>180.6215296329567</v>
+        <v>181.9822138463991</v>
       </c>
       <c r="E95" t="n">
-        <v>186.5111389160156</v>
+        <v>184.0281829833984</v>
       </c>
       <c r="F95" t="n">
-        <v>9852900</v>
+        <v>9565100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B96" t="n">
-        <v>185.3292593497056</v>
+        <v>184.0579771467211</v>
       </c>
       <c r="C96" t="n">
-        <v>185.6768667554436</v>
+        <v>190.4243134969296</v>
       </c>
       <c r="D96" t="n">
-        <v>181.9821987572526</v>
+        <v>182.4787935369736</v>
       </c>
       <c r="E96" t="n">
-        <v>184.0281677246094</v>
+        <v>183.8990631103516</v>
       </c>
       <c r="F96" t="n">
-        <v>9565100</v>
+        <v>10816200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B97" t="n">
-        <v>184.0579771467211</v>
+        <v>180.0355685556146</v>
       </c>
       <c r="C97" t="n">
-        <v>190.4243134969296</v>
+        <v>181.2273936107796</v>
       </c>
       <c r="D97" t="n">
-        <v>182.4787935369736</v>
+        <v>173.3811981056387</v>
       </c>
       <c r="E97" t="n">
-        <v>183.8990631103516</v>
+        <v>176.9467468261719</v>
       </c>
       <c r="F97" t="n">
-        <v>10816200</v>
+        <v>15498600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B98" t="n">
-        <v>180.0355685556146</v>
+        <v>176.4302852446972</v>
       </c>
       <c r="C98" t="n">
-        <v>181.2273936107796</v>
+        <v>187.3851706171715</v>
       </c>
       <c r="D98" t="n">
-        <v>173.3811981056387</v>
+        <v>175.0795461293982</v>
       </c>
       <c r="E98" t="n">
-        <v>176.9467468261719</v>
+        <v>184.1573028564453</v>
       </c>
       <c r="F98" t="n">
-        <v>15498600</v>
+        <v>15564700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B99" t="n">
-        <v>176.4302852446972</v>
+        <v>181.7537853733346</v>
       </c>
       <c r="C99" t="n">
-        <v>187.3851706171715</v>
+        <v>191.2884162417558</v>
       </c>
       <c r="D99" t="n">
-        <v>175.0795461293982</v>
+        <v>181.0188192554131</v>
       </c>
       <c r="E99" t="n">
-        <v>184.1573028564453</v>
+        <v>190.4441986083984</v>
       </c>
       <c r="F99" t="n">
-        <v>15564700</v>
+        <v>21875100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B100" t="n">
-        <v>181.7537853733346</v>
+        <v>195.4200513200664</v>
       </c>
       <c r="C100" t="n">
-        <v>191.2884162417558</v>
+        <v>199.6709031418322</v>
       </c>
       <c r="D100" t="n">
-        <v>181.0188192554131</v>
+        <v>190.0270371048119</v>
       </c>
       <c r="E100" t="n">
-        <v>190.4441986083984</v>
+        <v>198.1116027832031</v>
       </c>
       <c r="F100" t="n">
-        <v>21875100</v>
+        <v>26680500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B101" t="n">
-        <v>195.420066371549</v>
+        <v>190.6031086414411</v>
       </c>
       <c r="C101" t="n">
-        <v>199.6709185207204</v>
+        <v>194.5857953386064</v>
       </c>
       <c r="D101" t="n">
-        <v>190.0270517409182</v>
+        <v>188.6266549601705</v>
       </c>
       <c r="E101" t="n">
-        <v>198.1116180419922</v>
+        <v>193.4634857177734</v>
       </c>
       <c r="F101" t="n">
-        <v>26680500</v>
+        <v>16346500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B102" t="n">
-        <v>190.6031086414411</v>
+        <v>191.1890691316076</v>
       </c>
       <c r="C102" t="n">
-        <v>194.5857953386064</v>
+        <v>194.6056450515189</v>
       </c>
       <c r="D102" t="n">
-        <v>188.6266549601705</v>
+        <v>189.38145611275</v>
       </c>
       <c r="E102" t="n">
-        <v>193.4634857177734</v>
+        <v>191.6360015869141</v>
       </c>
       <c r="F102" t="n">
-        <v>16346500</v>
+        <v>9932700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B103" t="n">
-        <v>191.1890691316076</v>
+        <v>189.4510095395255</v>
       </c>
       <c r="C103" t="n">
-        <v>194.6056450515189</v>
+        <v>197.3170732284266</v>
       </c>
       <c r="D103" t="n">
-        <v>189.38145611275</v>
+        <v>188.2889789535958</v>
       </c>
       <c r="E103" t="n">
-        <v>191.6360015869141</v>
+        <v>194.7149200439453</v>
       </c>
       <c r="F103" t="n">
-        <v>9932700</v>
+        <v>13208900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B104" t="n">
-        <v>189.4510095395255</v>
+        <v>193.7713848635987</v>
       </c>
       <c r="C104" t="n">
-        <v>197.3170732284266</v>
+        <v>195.1320503828654</v>
       </c>
       <c r="D104" t="n">
-        <v>188.2889789535958</v>
+        <v>190.7918147128814</v>
       </c>
       <c r="E104" t="n">
-        <v>194.7149200439453</v>
+        <v>191.76513671875</v>
       </c>
       <c r="F104" t="n">
-        <v>13208900</v>
+        <v>11583700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B105" t="n">
-        <v>193.7713848635987</v>
+        <v>193.0364294600736</v>
       </c>
       <c r="C105" t="n">
-        <v>195.1320503828654</v>
+        <v>203.0279194939781</v>
       </c>
       <c r="D105" t="n">
-        <v>190.7918147128814</v>
+        <v>192.9172514970062</v>
       </c>
       <c r="E105" t="n">
-        <v>191.76513671875</v>
+        <v>200.0185546875</v>
       </c>
       <c r="F105" t="n">
-        <v>11583700</v>
+        <v>15860900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B106" t="n">
-        <v>193.0364294600736</v>
+        <v>199.4226244314719</v>
       </c>
       <c r="C106" t="n">
-        <v>203.0279194939781</v>
+        <v>201.5778601866405</v>
       </c>
       <c r="D106" t="n">
-        <v>192.9172514970062</v>
+        <v>196.0259162627038</v>
       </c>
       <c r="E106" t="n">
-        <v>200.0185546875</v>
+        <v>200.733642578125</v>
       </c>
       <c r="F106" t="n">
-        <v>15860900</v>
+        <v>9657400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B107" t="n">
-        <v>199.4226244314719</v>
+        <v>197.2078193049057</v>
       </c>
       <c r="C107" t="n">
-        <v>201.5778601866405</v>
+        <v>202.2830212056148</v>
       </c>
       <c r="D107" t="n">
-        <v>196.0259162627038</v>
+        <v>194.5361355724457</v>
       </c>
       <c r="E107" t="n">
-        <v>200.733642578125</v>
+        <v>197.4362487792969</v>
       </c>
       <c r="F107" t="n">
-        <v>9657400</v>
+        <v>10754800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B108" t="n">
-        <v>197.2078193049057</v>
+        <v>195.9166750362765</v>
       </c>
       <c r="C108" t="n">
-        <v>202.2830212056148</v>
+        <v>198.2109569133711</v>
       </c>
       <c r="D108" t="n">
-        <v>194.5361355724457</v>
+        <v>189.3020404418633</v>
       </c>
       <c r="E108" t="n">
-        <v>197.4362487792969</v>
+        <v>193.5826873779297</v>
       </c>
       <c r="F108" t="n">
-        <v>10754800</v>
+        <v>14467400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B109" t="n">
-        <v>195.9166595935153</v>
+        <v>195.0625292691439</v>
       </c>
       <c r="C109" t="n">
-        <v>198.2109412897675</v>
+        <v>198.1910871721164</v>
       </c>
       <c r="D109" t="n">
-        <v>189.3020255204881</v>
+        <v>189.987327259986</v>
       </c>
       <c r="E109" t="n">
-        <v>193.5826721191406</v>
+        <v>192.8079986572266</v>
       </c>
       <c r="F109" t="n">
-        <v>14467400</v>
+        <v>9580000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B110" t="n">
-        <v>195.0625292691439</v>
+        <v>192.8079750209554</v>
       </c>
       <c r="C110" t="n">
-        <v>198.1910871721164</v>
+        <v>203.4648992272838</v>
       </c>
       <c r="D110" t="n">
-        <v>189.987327259986</v>
+        <v>191.8346379323055</v>
       </c>
       <c r="E110" t="n">
-        <v>192.8079986572266</v>
+        <v>197.9228973388672</v>
       </c>
       <c r="F110" t="n">
-        <v>9580000</v>
+        <v>26309700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B111" t="n">
-        <v>192.8079750209554</v>
+        <v>198.3698512203022</v>
       </c>
       <c r="C111" t="n">
-        <v>203.4648992272838</v>
+        <v>199.6312068702612</v>
       </c>
       <c r="D111" t="n">
-        <v>191.8346379323055</v>
+        <v>190.4441985938934</v>
       </c>
       <c r="E111" t="n">
-        <v>197.9228973388672</v>
+        <v>191.516845703125</v>
       </c>
       <c r="F111" t="n">
-        <v>26309700</v>
+        <v>14834700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B112" t="n">
-        <v>198.3698512203022</v>
+        <v>193.821025021851</v>
       </c>
       <c r="C112" t="n">
-        <v>199.6312068702612</v>
+        <v>197.2773371794379</v>
       </c>
       <c r="D112" t="n">
-        <v>190.4441985938934</v>
+        <v>193.821025021851</v>
       </c>
       <c r="E112" t="n">
-        <v>191.516845703125</v>
+        <v>196.9893035888672</v>
       </c>
       <c r="F112" t="n">
-        <v>14834700</v>
+        <v>13419600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B113" t="n">
-        <v>193.821025021851</v>
+        <v>196.870136689126</v>
       </c>
       <c r="C113" t="n">
-        <v>197.2773371794379</v>
+        <v>201.0018110133274</v>
       </c>
       <c r="D113" t="n">
-        <v>193.821025021851</v>
+        <v>193.1258058856387</v>
       </c>
       <c r="E113" t="n">
-        <v>196.9893035888672</v>
+        <v>193.9799499511719</v>
       </c>
       <c r="F113" t="n">
-        <v>13419600</v>
+        <v>11559300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B114" t="n">
-        <v>196.870136689126</v>
+        <v>192.0829546896537</v>
       </c>
       <c r="C114" t="n">
-        <v>201.0018110133274</v>
+        <v>194.8142273994103</v>
       </c>
       <c r="D114" t="n">
-        <v>193.1258058856387</v>
+        <v>191.3281356874407</v>
       </c>
       <c r="E114" t="n">
-        <v>193.9799499511719</v>
+        <v>193.0165557861328</v>
       </c>
       <c r="F114" t="n">
-        <v>11559300</v>
+        <v>10525100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0829395046699</v>
+        <v>194.2580295441802</v>
       </c>
       <c r="C115" t="n">
-        <v>194.8142119985075</v>
+        <v>199.0352710459927</v>
       </c>
       <c r="D115" t="n">
-        <v>191.3281205621285</v>
+        <v>191.9836310996653</v>
       </c>
       <c r="E115" t="n">
-        <v>193.0165405273438</v>
+        <v>193.6621246337891</v>
       </c>
       <c r="F115" t="n">
-        <v>10525100</v>
+        <v>9254300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B116" t="n">
-        <v>194.2580448499211</v>
+        <v>191.8942484911283</v>
       </c>
       <c r="C116" t="n">
-        <v>199.0352867281362</v>
+        <v>194.3374874288811</v>
       </c>
       <c r="D116" t="n">
-        <v>191.9836462262046</v>
+        <v>188.7061018910339</v>
       </c>
       <c r="E116" t="n">
-        <v>193.6621398925781</v>
+        <v>194.0494689941406</v>
       </c>
       <c r="F116" t="n">
-        <v>9254300</v>
+        <v>20201100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B117" t="n">
-        <v>191.8942484911283</v>
+        <v>195.7478267440036</v>
       </c>
       <c r="C117" t="n">
-        <v>194.3374874288811</v>
+        <v>196.7012958768407</v>
       </c>
       <c r="D117" t="n">
-        <v>188.7061018910339</v>
+        <v>190.6924929381777</v>
       </c>
       <c r="E117" t="n">
-        <v>194.0494689941406</v>
+        <v>193.850830078125</v>
       </c>
       <c r="F117" t="n">
-        <v>20201100</v>
+        <v>13976200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B118" t="n">
-        <v>195.7478267440036</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="C118" t="n">
-        <v>196.7012958768407</v>
+        <v>190.8315397252546</v>
       </c>
       <c r="D118" t="n">
-        <v>190.6924929381777</v>
+        <v>181.0486114593648</v>
       </c>
       <c r="E118" t="n">
-        <v>193.850830078125</v>
+        <v>181.7736511230469</v>
       </c>
       <c r="F118" t="n">
-        <v>13976200</v>
+        <v>18631400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B119" t="n">
-        <v>190.8315397252546</v>
+        <v>184.4353921172228</v>
       </c>
       <c r="C119" t="n">
-        <v>190.8315397252546</v>
+        <v>186.1138857525603</v>
       </c>
       <c r="D119" t="n">
-        <v>181.0486114593648</v>
+        <v>178.6252393274517</v>
       </c>
       <c r="E119" t="n">
-        <v>181.7736511230469</v>
+        <v>180.7208709716797</v>
       </c>
       <c r="F119" t="n">
-        <v>18631400</v>
+        <v>12565200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B120" t="n">
-        <v>184.4353921172228</v>
+        <v>179.9461742219026</v>
       </c>
       <c r="C120" t="n">
-        <v>186.1138857525603</v>
+        <v>186.1933484091056</v>
       </c>
       <c r="D120" t="n">
-        <v>178.6252393274517</v>
+        <v>178.3074166263376</v>
       </c>
       <c r="E120" t="n">
-        <v>180.7208709716797</v>
+        <v>184.3758087158203</v>
       </c>
       <c r="F120" t="n">
-        <v>12565200</v>
+        <v>10330700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B121" t="n">
-        <v>179.9461742219026</v>
+        <v>182.7469769199218</v>
       </c>
       <c r="C121" t="n">
-        <v>186.1933484091056</v>
+        <v>182.8562284362321</v>
       </c>
       <c r="D121" t="n">
-        <v>178.3074166263376</v>
+        <v>177.6022595179307</v>
       </c>
       <c r="E121" t="n">
-        <v>184.3758087158203</v>
+        <v>178.0889129638672</v>
       </c>
       <c r="F121" t="n">
-        <v>10330700</v>
+        <v>9902000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B122" t="n">
-        <v>182.7469769199218</v>
+        <v>178.873523844959</v>
       </c>
       <c r="C122" t="n">
-        <v>182.8562284362321</v>
+        <v>185.1206822343098</v>
       </c>
       <c r="D122" t="n">
-        <v>177.6022595179307</v>
+        <v>178.3570608051074</v>
       </c>
       <c r="E122" t="n">
-        <v>178.0889129638672</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F122" t="n">
-        <v>9902000</v>
+        <v>11617700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B123" t="n">
-        <v>178.873523844959</v>
+        <v>183.6408226716892</v>
       </c>
       <c r="C123" t="n">
-        <v>185.1206822343098</v>
+        <v>187.2163126895138</v>
       </c>
       <c r="D123" t="n">
-        <v>178.3570608051074</v>
+        <v>181.0684642406058</v>
       </c>
       <c r="E123" t="n">
-        <v>183.7699432373047</v>
+        <v>185.3987731933594</v>
       </c>
       <c r="F123" t="n">
-        <v>11617700</v>
+        <v>11041400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B124" t="n">
-        <v>183.6408226716892</v>
+        <v>185.5775567084869</v>
       </c>
       <c r="C124" t="n">
-        <v>187.2163126895138</v>
+        <v>187.6930410934417</v>
       </c>
       <c r="D124" t="n">
-        <v>181.0684642406058</v>
+        <v>181.7636956083204</v>
       </c>
       <c r="E124" t="n">
-        <v>185.3987731933594</v>
+        <v>184.9717102050781</v>
       </c>
       <c r="F124" t="n">
-        <v>11041400</v>
+        <v>11677700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B125" t="n">
-        <v>185.5775567084869</v>
+        <v>184.0381169897925</v>
       </c>
       <c r="C125" t="n">
-        <v>187.6930410934417</v>
+        <v>186.3025890630262</v>
       </c>
       <c r="D125" t="n">
-        <v>181.7636956083204</v>
+        <v>180.3434488377003</v>
       </c>
       <c r="E125" t="n">
-        <v>184.9717102050781</v>
+        <v>185.9053039550781</v>
       </c>
       <c r="F125" t="n">
-        <v>11677700</v>
+        <v>11635500</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B126" t="n">
-        <v>184.0381169897925</v>
+        <v>186.2231237330043</v>
       </c>
       <c r="C126" t="n">
-        <v>186.3025890630262</v>
+        <v>186.8587647224845</v>
       </c>
       <c r="D126" t="n">
-        <v>180.3434488377003</v>
+        <v>182.3496888213084</v>
       </c>
       <c r="E126" t="n">
-        <v>185.9053039550781</v>
+        <v>183.7699432373047</v>
       </c>
       <c r="F126" t="n">
-        <v>11635500</v>
+        <v>14391000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B127" t="n">
-        <v>186.2231237330043</v>
+        <v>183.690504131923</v>
       </c>
       <c r="C127" t="n">
-        <v>186.8587647224845</v>
+        <v>185.3094088283374</v>
       </c>
       <c r="D127" t="n">
-        <v>182.3496888213084</v>
+        <v>180.7804644422889</v>
       </c>
       <c r="E127" t="n">
-        <v>183.7699432373047</v>
+        <v>181.7140655517578</v>
       </c>
       <c r="F127" t="n">
-        <v>14391000</v>
+        <v>12344600</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B128" t="n">
-        <v>183.690504131923</v>
+        <v>185.2299504420264</v>
       </c>
       <c r="C128" t="n">
-        <v>185.3094088283374</v>
+        <v>185.4981160077481</v>
       </c>
       <c r="D128" t="n">
-        <v>180.7804644422889</v>
+        <v>174.5829515420302</v>
       </c>
       <c r="E128" t="n">
-        <v>181.7140655517578</v>
+        <v>175.1689300537109</v>
       </c>
       <c r="F128" t="n">
-        <v>12344600</v>
+        <v>13472100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,25 +3771,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B129" t="n">
-        <v>185.2299504420264</v>
+        <v>172.4208720146844</v>
       </c>
       <c r="C129" t="n">
-        <v>185.4981160077481</v>
+        <v>173.5360220799356</v>
       </c>
       <c r="D129" t="n">
-        <v>174.5829515420302</v>
+        <v>166.3970410225636</v>
       </c>
       <c r="E129" t="n">
-        <v>175.1689300537109</v>
+        <v>170.1109161376953</v>
       </c>
       <c r="F129" t="n">
-        <v>13472100</v>
+        <v>20855400</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -3797,25 +3797,25 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B130" t="n">
-        <v>172.4208565486944</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="C130" t="n">
-        <v>173.5360065139178</v>
+        <v>170.5191174814139</v>
       </c>
       <c r="D130" t="n">
-        <v>166.3970260969056</v>
+        <v>162.8126107290287</v>
       </c>
       <c r="E130" t="n">
-        <v>170.1109008789062</v>
+        <v>164.2463836669922</v>
       </c>
       <c r="F130" t="n">
-        <v>20855400</v>
+        <v>18109300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B131" t="n">
-        <v>170.5191174814139</v>
+        <v>166.3273444705899</v>
       </c>
       <c r="C131" t="n">
-        <v>170.5191174814139</v>
+        <v>172.6498652447362</v>
       </c>
       <c r="D131" t="n">
-        <v>162.8126107290287</v>
+        <v>165.0528829680655</v>
       </c>
       <c r="E131" t="n">
-        <v>164.2463836669922</v>
+        <v>172.0723876953125</v>
       </c>
       <c r="F131" t="n">
-        <v>18109300</v>
+        <v>12390800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B132" t="n">
-        <v>166.3273444705899</v>
+        <v>174.4520463656914</v>
       </c>
       <c r="C132" t="n">
-        <v>172.6498652447362</v>
+        <v>176.7321331165696</v>
       </c>
       <c r="D132" t="n">
-        <v>165.0528829680655</v>
+        <v>169.7624151908458</v>
       </c>
       <c r="E132" t="n">
-        <v>172.0723876953125</v>
+        <v>170.5689086914062</v>
       </c>
       <c r="F132" t="n">
-        <v>12390800</v>
+        <v>13123600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B133" t="n">
-        <v>174.4520463656914</v>
+        <v>173.4663277892384</v>
       </c>
       <c r="C133" t="n">
-        <v>176.7321331165696</v>
+        <v>178.842961383224</v>
       </c>
       <c r="D133" t="n">
-        <v>169.7624151908458</v>
+        <v>172.1321282578628</v>
       </c>
       <c r="E133" t="n">
-        <v>170.5689086914062</v>
+        <v>176.8317108154297</v>
       </c>
       <c r="F133" t="n">
-        <v>13123600</v>
+        <v>14340300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B134" t="n">
-        <v>173.4663277892384</v>
+        <v>183.2040075329009</v>
       </c>
       <c r="C134" t="n">
-        <v>178.842961383224</v>
+        <v>183.7516312461474</v>
       </c>
       <c r="D134" t="n">
-        <v>172.1321282578628</v>
+        <v>177.7975052553062</v>
       </c>
       <c r="E134" t="n">
-        <v>176.8317108154297</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F134" t="n">
-        <v>14340300</v>
+        <v>11866700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B135" t="n">
-        <v>183.2040230257668</v>
+        <v>184.6278268926657</v>
       </c>
       <c r="C135" t="n">
-        <v>183.7516467853238</v>
+        <v>187.1667986912511</v>
       </c>
       <c r="D135" t="n">
-        <v>177.7975202909648</v>
+        <v>180.2468672661974</v>
       </c>
       <c r="E135" t="n">
-        <v>180.4360504150391</v>
+        <v>181.3520660400391</v>
       </c>
       <c r="F135" t="n">
-        <v>11866700</v>
+        <v>17225700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B136" t="n">
-        <v>184.6278268926657</v>
+        <v>181.7105075933097</v>
       </c>
       <c r="C136" t="n">
-        <v>187.1667986912511</v>
+        <v>188.1823886856741</v>
       </c>
       <c r="D136" t="n">
-        <v>180.2468672661974</v>
+        <v>181.3321466062204</v>
       </c>
       <c r="E136" t="n">
-        <v>181.3520660400391</v>
+        <v>185.4642028808594</v>
       </c>
       <c r="F136" t="n">
-        <v>17225700</v>
+        <v>14382300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B137" t="n">
-        <v>181.7104926433502</v>
+        <v>185.7927641258556</v>
       </c>
       <c r="C137" t="n">
-        <v>188.1823732032504</v>
+        <v>192.7226462718077</v>
       </c>
       <c r="D137" t="n">
-        <v>181.33213168739</v>
+        <v>183.303579264538</v>
       </c>
       <c r="E137" t="n">
-        <v>185.4641876220703</v>
+        <v>186.3005523681641</v>
       </c>
       <c r="F137" t="n">
-        <v>14382300</v>
+        <v>12073700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B138" t="n">
-        <v>185.7927793430547</v>
+        <v>187.3858431404722</v>
       </c>
       <c r="C138" t="n">
-        <v>192.7226620565929</v>
+        <v>190.3230783921826</v>
       </c>
       <c r="D138" t="n">
-        <v>183.3035942778625</v>
+        <v>186.2209063874661</v>
       </c>
       <c r="E138" t="n">
-        <v>186.3005676269531</v>
+        <v>188.9789276123047</v>
       </c>
       <c r="F138" t="n">
-        <v>12073700</v>
+        <v>14565900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B139" t="n">
-        <v>187.3858431404722</v>
+        <v>176.7918740224492</v>
       </c>
       <c r="C139" t="n">
-        <v>190.3230783921826</v>
+        <v>178.0962045390804</v>
       </c>
       <c r="D139" t="n">
-        <v>186.2209063874661</v>
+        <v>169.9117629967484</v>
       </c>
       <c r="E139" t="n">
-        <v>188.9789276123047</v>
+        <v>172.5503082275391</v>
       </c>
       <c r="F139" t="n">
-        <v>14565900</v>
+        <v>22719900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B140" t="n">
-        <v>176.7918740224492</v>
+        <v>174.8602617765654</v>
       </c>
       <c r="C140" t="n">
-        <v>178.0962045390804</v>
+        <v>177.6780209996891</v>
       </c>
       <c r="D140" t="n">
-        <v>169.9117629967484</v>
+        <v>173.6455382897692</v>
       </c>
       <c r="E140" t="n">
-        <v>172.5503082275391</v>
+        <v>177.3892822265625</v>
       </c>
       <c r="F140" t="n">
-        <v>22719900</v>
+        <v>10817600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B141" t="n">
-        <v>174.8602617765654</v>
+        <v>177.4888508581443</v>
       </c>
       <c r="C141" t="n">
-        <v>177.6780209996891</v>
+        <v>183.4927641701262</v>
       </c>
       <c r="D141" t="n">
-        <v>173.6455382897692</v>
+        <v>176.7420953199099</v>
       </c>
       <c r="E141" t="n">
-        <v>177.3892822265625</v>
+        <v>179.4005432128906</v>
       </c>
       <c r="F141" t="n">
-        <v>10817600</v>
+        <v>11907000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B142" t="n">
-        <v>177.4888357619529</v>
+        <v>181.6407975504903</v>
       </c>
       <c r="C142" t="n">
-        <v>183.4927485632761</v>
+        <v>183.6221942474171</v>
       </c>
       <c r="D142" t="n">
-        <v>176.7420802872333</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="E142" t="n">
-        <v>179.4005279541016</v>
+        <v>180.5356140136719</v>
       </c>
       <c r="F142" t="n">
-        <v>11907000</v>
+        <v>8711700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B143" t="n">
-        <v>181.6407975504903</v>
+        <v>178.424769515226</v>
       </c>
       <c r="C143" t="n">
-        <v>183.6221942474171</v>
+        <v>180.993610139636</v>
       </c>
       <c r="D143" t="n">
-        <v>180.5356140136719</v>
+        <v>176.5827818160244</v>
       </c>
       <c r="E143" t="n">
-        <v>180.5356140136719</v>
+        <v>180.43603515625</v>
       </c>
       <c r="F143" t="n">
-        <v>8711700</v>
+        <v>6882800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B144" t="n">
-        <v>178.4247846039299</v>
+        <v>177.5286741071897</v>
       </c>
       <c r="C144" t="n">
-        <v>180.993625445577</v>
+        <v>177.9169863526292</v>
       </c>
       <c r="D144" t="n">
-        <v>176.5827967489585</v>
+        <v>172.2515989617143</v>
       </c>
       <c r="E144" t="n">
-        <v>180.4360504150391</v>
+        <v>175.7663269042969</v>
       </c>
       <c r="F144" t="n">
-        <v>6882800</v>
+        <v>14408300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B145" t="n">
-        <v>177.5286895189733</v>
+        <v>181.4018572311292</v>
       </c>
       <c r="C145" t="n">
-        <v>177.9170017981234</v>
+        <v>185.2351932001588</v>
       </c>
       <c r="D145" t="n">
-        <v>172.2516139153796</v>
+        <v>177.9767360752557</v>
       </c>
       <c r="E145" t="n">
-        <v>175.7663421630859</v>
+        <v>183.0248107910156</v>
       </c>
       <c r="F145" t="n">
-        <v>14408300</v>
+        <v>12324400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B146" t="n">
-        <v>181.4018421076459</v>
+        <v>183.4429710909726</v>
       </c>
       <c r="C146" t="n">
-        <v>185.2351777570901</v>
+        <v>189.4867039708132</v>
       </c>
       <c r="D146" t="n">
-        <v>177.9767212373249</v>
+        <v>183.1741348747832</v>
       </c>
       <c r="E146" t="n">
-       